--- a/outputs/sem_coredata.xlsx
+++ b/outputs/sem_coredata.xlsx
@@ -2745,148 +2745,148 @@
         <v>347360</v>
       </c>
       <c r="FZ2" t="n">
-        <v>350569.786020005</v>
+        <v>349205</v>
       </c>
       <c r="GA2" t="n">
-        <v>353180.572988745</v>
+        <v>352663</v>
       </c>
       <c r="GB2" t="n">
-        <v>355998.931293701</v>
+        <v>354377</v>
       </c>
       <c r="GC2" t="n">
-        <v>358795.838872174</v>
+        <v>355157.211293678</v>
       </c>
       <c r="GD2" t="n">
-        <v>361791.147315457</v>
+        <v>358795.472538645</v>
       </c>
       <c r="GE2" t="n">
-        <v>364559.917672748</v>
+        <v>363166.339057702</v>
       </c>
       <c r="GF2" t="n">
-        <v>367439.624277036</v>
+        <v>367650.213879468</v>
       </c>
       <c r="GG2" t="n">
-        <v>370255.314382408</v>
+        <v>371143.62270974</v>
       </c>
       <c r="GH2" t="n">
-        <v>372799.672679197</v>
+        <v>374105.929735411</v>
       </c>
       <c r="GI2" t="n">
-        <v>375029.72479978</v>
+        <v>376457.827635005</v>
       </c>
       <c r="GJ2" t="n">
-        <v>377104.873185019</v>
+        <v>378540.773444217</v>
       </c>
       <c r="GK2" t="n">
-        <v>379284.862843887</v>
+        <v>380629.132057787</v>
       </c>
       <c r="GL2" t="n">
-        <v>381517.407898264</v>
+        <v>382707.623938109</v>
       </c>
       <c r="GM2" t="n">
-        <v>383602.853548622</v>
+        <v>384581.546054179</v>
       </c>
       <c r="GN2" t="n">
-        <v>385431.962576448</v>
+        <v>386322.088478483</v>
       </c>
       <c r="GO2" t="n">
-        <v>387466.243146817</v>
+        <v>388283.797267691</v>
       </c>
       <c r="GP2" t="n">
-        <v>389643.059315583</v>
+        <v>390434.065806365</v>
       </c>
       <c r="GQ2" t="n">
-        <v>391610.103392981</v>
+        <v>392412.02767212</v>
       </c>
       <c r="GR2" t="n">
-        <v>393781.997663888</v>
+        <v>394597.99112062</v>
       </c>
       <c r="GS2" t="n">
-        <v>396128.479287384</v>
+        <v>396985.896919367</v>
       </c>
       <c r="GT2" t="n">
-        <v>398632.05398897</v>
+        <v>399547.322144343</v>
       </c>
       <c r="GU2" t="n">
-        <v>400872.187783373</v>
+        <v>401899.780984293</v>
       </c>
       <c r="GV2" t="n">
-        <v>403261.175593451</v>
+        <v>404423.370124193</v>
       </c>
       <c r="GW2" t="n">
-        <v>405817.120423883</v>
+        <v>407169.976809224</v>
       </c>
       <c r="GX2" t="n">
-        <v>408498.312529432</v>
+        <v>410087.993020951</v>
       </c>
       <c r="GY2" t="n">
-        <v>410918.282681266</v>
+        <v>412808.52472221</v>
       </c>
       <c r="GZ2" t="n">
-        <v>413479.725044692</v>
+        <v>415706.700004259</v>
       </c>
       <c r="HA2" t="n">
-        <v>416192.360269139</v>
+        <v>418802.93209611</v>
       </c>
       <c r="HB2" t="n">
-        <v>419029.167211491</v>
+        <v>422045.121670563</v>
       </c>
       <c r="HC2" t="n">
-        <v>421477.217660733</v>
+        <v>424954.464956965</v>
       </c>
       <c r="HD2" t="n">
-        <v>424111.418509631</v>
+        <v>428026.260558339</v>
       </c>
       <c r="HE2" t="n">
-        <v>426831.334873674</v>
+        <v>431207.240512452</v>
       </c>
       <c r="HF2" t="n">
-        <v>429620.214759845</v>
+        <v>434446.926106401</v>
       </c>
       <c r="HG2" t="n">
-        <v>432068.010626061</v>
+        <v>437344.351655797</v>
       </c>
       <c r="HH2" t="n">
-        <v>434573.17106672</v>
+        <v>440275.019485886</v>
       </c>
       <c r="HI2" t="n">
-        <v>437203.807584838</v>
+        <v>443313.483905751</v>
       </c>
       <c r="HJ2" t="n">
-        <v>439890.351987598</v>
+        <v>446380.114608649</v>
       </c>
       <c r="HK2" t="n">
-        <v>442222.43984065</v>
+        <v>449075.286123769</v>
       </c>
       <c r="HL2" t="n">
-        <v>444628.398675269</v>
+        <v>451805.672775336</v>
       </c>
       <c r="HM2" t="n">
-        <v>447149.71257049</v>
+        <v>454627.786980069</v>
       </c>
       <c r="HN2" t="n">
-        <v>449723.710946837</v>
+        <v>457468.176717751</v>
       </c>
       <c r="HO2" t="n">
-        <v>451927.006967574</v>
+        <v>459917.610137924</v>
       </c>
       <c r="HP2" t="n">
-        <v>454164.237983189</v>
+        <v>462364.310810752</v>
       </c>
       <c r="HQ2" t="n">
-        <v>456534.452954729</v>
+        <v>464918.803431897</v>
       </c>
       <c r="HR2" t="n">
-        <v>458968.03457598</v>
+        <v>467504.594496089</v>
       </c>
       <c r="HS2" t="n">
-        <v>460897.29878781</v>
+        <v>469602.354376046</v>
       </c>
       <c r="HT2" t="n">
-        <v>462990.965352124</v>
+        <v>471794.542768185</v>
       </c>
       <c r="HU2" t="n">
-        <v>465173.583542319</v>
+        <v>474075.522608443</v>
       </c>
     </row>
     <row r="3">
@@ -3434,13 +3434,13 @@
         <v>154528</v>
       </c>
       <c r="FZ3" t="n">
-        <v>156125.597503725</v>
+        <v>155114</v>
       </c>
       <c r="GA3" t="n">
-        <v>157739.711870309</v>
+        <v>156588</v>
       </c>
       <c r="GB3" t="n">
-        <v>158813.164968927</v>
+        <v>158467</v>
       </c>
       <c r="GC3" t="n">
         <v>159893.923149704</v>
@@ -4123,148 +4123,148 @@
         <v>35136</v>
       </c>
       <c r="FZ4" t="n">
-        <v>35109.7372357658</v>
+        <v>35996</v>
       </c>
       <c r="GA4" t="n">
-        <v>34985.5321404622</v>
+        <v>35990</v>
       </c>
       <c r="GB4" t="n">
-        <v>34862.0561289003</v>
+        <v>36720</v>
       </c>
       <c r="GC4" t="n">
-        <v>34747.5232868529</v>
+        <v>36864.8957689682</v>
       </c>
       <c r="GD4" t="n">
-        <v>34697.6980396631</v>
+        <v>37067.579590602</v>
       </c>
       <c r="GE4" t="n">
-        <v>34697.2261192711</v>
+        <v>37232.0945730057</v>
       </c>
       <c r="GF4" t="n">
-        <v>34722.9326936955</v>
+        <v>37384.7093034521</v>
       </c>
       <c r="GG4" t="n">
-        <v>34742.1616325712</v>
+        <v>37395.9464072406</v>
       </c>
       <c r="GH4" t="n">
-        <v>34745.4533833637</v>
+        <v>37300.8875628905</v>
       </c>
       <c r="GI4" t="n">
-        <v>34731.314056131</v>
+        <v>37133.0849542831</v>
       </c>
       <c r="GJ4" t="n">
-        <v>34712.8807376051</v>
+        <v>36988.8803212363</v>
       </c>
       <c r="GK4" t="n">
-        <v>34706.9605374344</v>
+        <v>36928.5927044009</v>
       </c>
       <c r="GL4" t="n">
-        <v>34727.8687886099</v>
+        <v>36987.3778775673</v>
       </c>
       <c r="GM4" t="n">
-        <v>34780.7180125836</v>
+        <v>37159.138764331</v>
       </c>
       <c r="GN4" t="n">
-        <v>34858.1800872736</v>
+        <v>37414.2955412779</v>
       </c>
       <c r="GO4" t="n">
-        <v>34949.6054311503</v>
+        <v>37712.9075474498</v>
       </c>
       <c r="GP4" t="n">
-        <v>35048.7342141302</v>
+        <v>38020.6559440737</v>
       </c>
       <c r="GQ4" t="n">
-        <v>35151.8818420371</v>
+        <v>38310.2404010462</v>
       </c>
       <c r="GR4" t="n">
-        <v>35250.3072547363</v>
+        <v>38557.886508678</v>
       </c>
       <c r="GS4" t="n">
-        <v>35341.1250372016</v>
+        <v>38753.4085763936</v>
       </c>
       <c r="GT4" t="n">
-        <v>35420.9674022131</v>
+        <v>38895.2390487472</v>
       </c>
       <c r="GU4" t="n">
-        <v>35489.2005332863</v>
+        <v>38990.8772461067</v>
       </c>
       <c r="GV4" t="n">
-        <v>35546.0981166681</v>
+        <v>39051.4495482478</v>
       </c>
       <c r="GW4" t="n">
-        <v>35597.17893894</v>
+        <v>39094.1199430444</v>
       </c>
       <c r="GX4" t="n">
-        <v>35649.9148686235</v>
+        <v>39136.1900024676</v>
       </c>
       <c r="GY4" t="n">
-        <v>35709.4100571145</v>
+        <v>39189.8880787792</v>
       </c>
       <c r="GZ4" t="n">
-        <v>35777.3124723607</v>
+        <v>39260.2366443864</v>
       </c>
       <c r="HA4" t="n">
-        <v>35856.1655988353</v>
+        <v>39351.0923769263</v>
       </c>
       <c r="HB4" t="n">
-        <v>35947.4212055551</v>
+        <v>39463.388119257</v>
       </c>
       <c r="HC4" t="n">
-        <v>36050.0045001612</v>
+        <v>39594.8856538842</v>
       </c>
       <c r="HD4" t="n">
-        <v>36159.8628485509</v>
+        <v>39739.3400578102</v>
       </c>
       <c r="HE4" t="n">
-        <v>36276.8556236671</v>
+        <v>39895.6548545581</v>
       </c>
       <c r="HF4" t="n">
-        <v>36400.89171465</v>
+        <v>40063.0974125211</v>
       </c>
       <c r="HG4" t="n">
-        <v>36529.9084596336</v>
+        <v>40239.7858033261</v>
       </c>
       <c r="HH4" t="n">
-        <v>36661.0211344785</v>
+        <v>40422.5193760021</v>
       </c>
       <c r="HI4" t="n">
-        <v>36793.9212516167</v>
+        <v>40611.3091185359</v>
       </c>
       <c r="HJ4" t="n">
-        <v>36930.1689281851</v>
+        <v>40808.0356530005</v>
       </c>
       <c r="HK4" t="n">
-        <v>37069.4246076972</v>
+        <v>41012.5218897412</v>
       </c>
       <c r="HL4" t="n">
-        <v>37208.8420748795</v>
+        <v>41221.2532767052</v>
       </c>
       <c r="HM4" t="n">
-        <v>37348.6991416241</v>
+        <v>41433.9381958378</v>
       </c>
       <c r="HN4" t="n">
-        <v>37489.7935415296</v>
+        <v>41650.6668559899</v>
       </c>
       <c r="HO4" t="n">
-        <v>37631.6165367447</v>
+        <v>41870.1129300453</v>
       </c>
       <c r="HP4" t="n">
-        <v>37771.3431251277</v>
+        <v>42088.0421911433</v>
       </c>
       <c r="HQ4" t="n">
-        <v>37909.4823883889</v>
+        <v>42303.8769232235</v>
       </c>
       <c r="HR4" t="n">
-        <v>38047.8984314676</v>
+        <v>42518.8223500639</v>
       </c>
       <c r="HS4" t="n">
-        <v>38186.8781376323</v>
+        <v>42732.719289882</v>
       </c>
       <c r="HT4" t="n">
-        <v>38323.573532922</v>
+        <v>42941.256434801</v>
       </c>
       <c r="HU4" t="n">
-        <v>38460.0462689424</v>
+        <v>43146.0493414534</v>
       </c>
     </row>
     <row r="5">
@@ -4812,148 +4812,148 @@
         <v>10512</v>
       </c>
       <c r="FZ5" t="n">
-        <v>10391.1709586367</v>
+        <v>10516</v>
       </c>
       <c r="GA5" t="n">
-        <v>10354.4108891846</v>
+        <v>10750</v>
       </c>
       <c r="GB5" t="n">
-        <v>10317.8666012905</v>
+        <v>11236</v>
       </c>
       <c r="GC5" t="n">
-        <v>10283.9691575671</v>
+        <v>11150.4565404427</v>
       </c>
       <c r="GD5" t="n">
-        <v>10269.2227452505</v>
+        <v>11211.7619394527</v>
       </c>
       <c r="GE5" t="n">
-        <v>10269.0830744395</v>
+        <v>11261.5224805659</v>
       </c>
       <c r="GF5" t="n">
-        <v>10276.6912603912</v>
+        <v>11307.6835745763</v>
       </c>
       <c r="GG5" t="n">
-        <v>10282.3823081444</v>
+        <v>11311.0824404843</v>
       </c>
       <c r="GH5" t="n">
-        <v>10283.3565434401</v>
+        <v>11282.3301684217</v>
       </c>
       <c r="GI5" t="n">
-        <v>10279.1718306487</v>
+        <v>11231.575225118</v>
       </c>
       <c r="GJ5" t="n">
-        <v>10273.7162568045</v>
+        <v>11187.9579176449</v>
       </c>
       <c r="GK5" t="n">
-        <v>10271.9640986591</v>
+        <v>11169.7228341752</v>
       </c>
       <c r="GL5" t="n">
-        <v>10278.1521601348</v>
+        <v>11187.5034762994</v>
       </c>
       <c r="GM5" t="n">
-        <v>10293.7935566412</v>
+        <v>11239.4556726438</v>
       </c>
       <c r="GN5" t="n">
-        <v>10316.7194377297</v>
+        <v>11316.63246897</v>
       </c>
       <c r="GO5" t="n">
-        <v>10343.7779250034</v>
+        <v>11406.9530877543</v>
       </c>
       <c r="GP5" t="n">
-        <v>10373.1163425469</v>
+        <v>11500.0371735863</v>
       </c>
       <c r="GQ5" t="n">
-        <v>10403.6441880947</v>
+        <v>11587.6272463345</v>
       </c>
       <c r="GR5" t="n">
-        <v>10432.7744343043</v>
+        <v>11662.5323044653</v>
       </c>
       <c r="GS5" t="n">
-        <v>10459.6531060911</v>
+        <v>11721.6715010718</v>
       </c>
       <c r="GT5" t="n">
-        <v>10483.2834642167</v>
+        <v>11764.5707005705</v>
       </c>
       <c r="GU5" t="n">
-        <v>10503.4779226731</v>
+        <v>11793.4982084616</v>
       </c>
       <c r="GV5" t="n">
-        <v>10520.317482368</v>
+        <v>11811.8194001669</v>
       </c>
       <c r="GW5" t="n">
-        <v>10535.4354980162</v>
+        <v>11824.7258352135</v>
       </c>
       <c r="GX5" t="n">
-        <v>10551.0433636441</v>
+        <v>11837.450687935</v>
       </c>
       <c r="GY5" t="n">
-        <v>10568.651717437</v>
+        <v>11853.6926453237</v>
       </c>
       <c r="GZ5" t="n">
-        <v>10588.7482963601</v>
+        <v>11874.9708452785</v>
       </c>
       <c r="HA5" t="n">
-        <v>10612.0858768244</v>
+        <v>11902.4518099199</v>
       </c>
       <c r="HB5" t="n">
-        <v>10639.0941282389</v>
+        <v>11936.4176944943</v>
       </c>
       <c r="HC5" t="n">
-        <v>10669.4549522062</v>
+        <v>11976.191509514</v>
       </c>
       <c r="HD5" t="n">
-        <v>10701.9689203879</v>
+        <v>12019.8843647209</v>
       </c>
       <c r="HE5" t="n">
-        <v>10736.5944124271</v>
+        <v>12067.164610912</v>
       </c>
       <c r="HF5" t="n">
-        <v>10773.3044629123</v>
+        <v>12117.8106503661</v>
       </c>
       <c r="HG5" t="n">
-        <v>10811.4886009663</v>
+        <v>12171.2532597043</v>
       </c>
       <c r="HH5" t="n">
-        <v>10850.2930559814</v>
+        <v>12226.524343973</v>
       </c>
       <c r="HI5" t="n">
-        <v>10889.6265271587</v>
+        <v>12283.6272266882</v>
       </c>
       <c r="HJ5" t="n">
-        <v>10929.9507509042</v>
+        <v>12343.1307361148</v>
       </c>
       <c r="HK5" t="n">
-        <v>10971.1652311794</v>
+        <v>12404.9813082739</v>
       </c>
       <c r="HL5" t="n">
-        <v>11012.4275945626</v>
+        <v>12468.1159031349</v>
       </c>
       <c r="HM5" t="n">
-        <v>11053.8200629983</v>
+        <v>12532.4463155266</v>
       </c>
       <c r="HN5" t="n">
-        <v>11095.5787358382</v>
+        <v>12597.9998307526</v>
       </c>
       <c r="HO5" t="n">
-        <v>11137.5530456785</v>
+        <v>12664.3752771138</v>
       </c>
       <c r="HP5" t="n">
-        <v>11178.9068973922</v>
+        <v>12730.2919358776</v>
       </c>
       <c r="HQ5" t="n">
-        <v>11219.7909601526</v>
+        <v>12795.5750663402</v>
       </c>
       <c r="HR5" t="n">
-        <v>11260.7569394019</v>
+        <v>12860.5892102991</v>
       </c>
       <c r="HS5" t="n">
-        <v>11301.8897418732</v>
+        <v>12925.286220336</v>
       </c>
       <c r="HT5" t="n">
-        <v>11342.346473639</v>
+        <v>12988.3620631666</v>
       </c>
       <c r="HU5" t="n">
-        <v>11382.7373065768</v>
+        <v>13050.3053932041</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>27283</v>
       </c>
       <c r="FZ6" t="n">
-        <v>27565.0670214726</v>
+        <v>27037</v>
       </c>
       <c r="GA6" t="n">
-        <v>27850.0502106908</v>
+        <v>25898</v>
       </c>
       <c r="GB6" t="n">
-        <v>28039.5758687567</v>
+        <v>26565</v>
       </c>
       <c r="GC6" t="n">
         <v>28230.3912902088</v>
@@ -6190,13 +6190,13 @@
         <v>11653</v>
       </c>
       <c r="FZ7" t="n">
-        <v>11773.4752776902</v>
+        <v>11332</v>
       </c>
       <c r="GA7" t="n">
-        <v>11895.1960966602</v>
+        <v>11392</v>
       </c>
       <c r="GB7" t="n">
-        <v>11976.1454971455</v>
+        <v>11797</v>
       </c>
       <c r="GC7" t="n">
         <v>12057.6457759338</v>
@@ -6838,149 +6838,143 @@
       <c r="FY8" t="n">
         <v>428</v>
       </c>
-      <c r="FZ8" t="n">
-        <v>147.492102615593</v>
-      </c>
-      <c r="GA8" t="n">
-        <v>521.688404694112</v>
-      </c>
-      <c r="GB8" t="n">
-        <v>627.537276173302</v>
-      </c>
+      <c r="FZ8"/>
+      <c r="GA8"/>
+      <c r="GB8"/>
       <c r="GC8" t="n">
-        <v>696.972025702911</v>
+        <v>-20.3573504657543</v>
       </c>
       <c r="GD8" t="n">
-        <v>806.724253721244</v>
+        <v>-86.2444237894379</v>
       </c>
       <c r="GE8" t="n">
-        <v>919.071972608217</v>
+        <v>1219.64349159921</v>
       </c>
       <c r="GF8" t="n">
-        <v>991.685472438141</v>
+        <v>811.938125303452</v>
       </c>
       <c r="GG8" t="n">
-        <v>1066.02315052148</v>
+        <v>1674.03522173257</v>
       </c>
       <c r="GH8" t="n">
-        <v>1110.85557868032</v>
+        <v>1459.73639659776</v>
       </c>
       <c r="GI8" t="n">
-        <v>1136.9162642099</v>
+        <v>1621.6259701231</v>
       </c>
       <c r="GJ8" t="n">
-        <v>1157.9296580455</v>
+        <v>1583.09384903437</v>
       </c>
       <c r="GK8" t="n">
-        <v>1108.58731288012</v>
+        <v>1527.65100318374</v>
       </c>
       <c r="GL8" t="n">
-        <v>1138.9776586848</v>
+        <v>1516.84339071735</v>
       </c>
       <c r="GM8" t="n">
-        <v>1137.96560638939</v>
+        <v>1481.36079962549</v>
       </c>
       <c r="GN8" t="n">
-        <v>1165.59344235971</v>
+        <v>1452.67988099172</v>
       </c>
       <c r="GO8" t="n">
-        <v>1071.56725579308</v>
+        <v>1341.62620409662</v>
       </c>
       <c r="GP8" t="n">
-        <v>1086.84457485299</v>
+        <v>1317.97650527916</v>
       </c>
       <c r="GQ8" t="n">
-        <v>1068.22608391949</v>
+        <v>1275.98397671347</v>
       </c>
       <c r="GR8" t="n">
-        <v>1037.40234020739</v>
+        <v>1211.96942826631</v>
       </c>
       <c r="GS8" t="n">
-        <v>1039.67459916446</v>
+        <v>1183.64247538027</v>
       </c>
       <c r="GT8" t="n">
-        <v>1031.6497895222</v>
+        <v>1142.76756671391</v>
       </c>
       <c r="GU8" t="n">
-        <v>1034.84054956312</v>
+        <v>1114.77220027073</v>
       </c>
       <c r="GV8" t="n">
-        <v>999.474758389551</v>
+        <v>1051.09702684908</v>
       </c>
       <c r="GW8" t="n">
-        <v>1011.52374890671</v>
+        <v>1035.7870373055</v>
       </c>
       <c r="GX8" t="n">
-        <v>1001.6165805968</v>
+        <v>1004.10479868005</v>
       </c>
       <c r="GY8" t="n">
-        <v>1007.14077394229</v>
+        <v>991.222463514277</v>
       </c>
       <c r="GZ8" t="n">
-        <v>987.874152464356</v>
+        <v>959.116524622426</v>
       </c>
       <c r="HA8" t="n">
-        <v>992.15570162033</v>
+        <v>952.879553189792</v>
       </c>
       <c r="HB8" t="n">
-        <v>995.816728823818</v>
+        <v>950.541812029551</v>
       </c>
       <c r="HC8" t="n">
-        <v>1005.12807259447</v>
+        <v>955.564338994824</v>
       </c>
       <c r="HD8" t="n">
-        <v>957.442335860658</v>
+        <v>909.117595001386</v>
       </c>
       <c r="HE8" t="n">
-        <v>994.164436073566</v>
+        <v>943.3863621692</v>
       </c>
       <c r="HF8" t="n">
-        <v>974.516742240958</v>
+        <v>927.052805730666</v>
       </c>
       <c r="HG8" t="n">
-        <v>984.51444379444</v>
+        <v>938.8360416918</v>
       </c>
       <c r="HH8" t="n">
-        <v>963.148749962013</v>
+        <v>921.873694327747</v>
       </c>
       <c r="HI8" t="n">
-        <v>962.634875916789</v>
+        <v>924.784851582983</v>
       </c>
       <c r="HJ8" t="n">
-        <v>963.71530490421</v>
+        <v>930.290907974617</v>
       </c>
       <c r="HK8" t="n">
-        <v>965.789958582638</v>
+        <v>936.445456705464</v>
       </c>
       <c r="HL8" t="n">
-        <v>945.826655979356</v>
+        <v>921.768969940924</v>
       </c>
       <c r="HM8" t="n">
-        <v>944.671659850836</v>
+        <v>924.284906714311</v>
       </c>
       <c r="HN8" t="n">
-        <v>944.543816294114</v>
+        <v>928.369585165288</v>
       </c>
       <c r="HO8" t="n">
-        <v>945.004680849059</v>
+        <v>931.949207925965</v>
       </c>
       <c r="HP8" t="n">
-        <v>922.56265971277</v>
+        <v>913.382726779993</v>
       </c>
       <c r="HQ8" t="n">
-        <v>916.784302784479</v>
+        <v>909.58827835953</v>
       </c>
       <c r="HR8" t="n">
-        <v>914.603677626321</v>
+        <v>909.178261956171</v>
       </c>
       <c r="HS8" t="n">
-        <v>912.723597795703</v>
+        <v>907.81022613839</v>
       </c>
       <c r="HT8" t="n">
-        <v>835.334002589807</v>
+        <v>835.035050034698</v>
       </c>
       <c r="HU8" t="n">
-        <v>866.488049999578</v>
+        <v>861.630821008002</v>
       </c>
     </row>
     <row r="9">
@@ -7527,15 +7521,9 @@
       <c r="FY9" t="n">
         <v>-187</v>
       </c>
-      <c r="FZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="GA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="GB9" t="n">
-        <v>0</v>
-      </c>
+      <c r="FZ9"/>
+      <c r="GA9"/>
+      <c r="GB9"/>
       <c r="GC9" t="n">
         <v>0</v>
       </c>
@@ -8217,148 +8205,148 @@
         <v>666693</v>
       </c>
       <c r="FZ10" t="n">
-        <v>672297.485574295</v>
+        <v>670389</v>
       </c>
       <c r="GA10" t="n">
-        <v>678360.167274833</v>
+        <v>674469</v>
       </c>
       <c r="GB10" t="n">
-        <v>683539.398644077</v>
+        <v>680205</v>
       </c>
       <c r="GC10" t="n">
-        <v>688937.723388228</v>
+        <v>686223.124478682</v>
       </c>
       <c r="GD10" t="n">
-        <v>694600.812831772</v>
+        <v>693013.045561194</v>
       </c>
       <c r="GE10" t="n">
-        <v>700169.089034781</v>
+        <v>701634.778565277</v>
       </c>
       <c r="GF10" t="n">
-        <v>705937.910548495</v>
+        <v>709081.328200931</v>
       </c>
       <c r="GG10" t="n">
-        <v>711644.248699413</v>
+        <v>716531.461448296</v>
       </c>
       <c r="GH10" t="n">
-        <v>716905.130299628</v>
+        <v>722008.181389185</v>
       </c>
       <c r="GI10" t="n">
-        <v>721791.374586147</v>
+        <v>726926.707812795</v>
       </c>
       <c r="GJ10" t="n">
-        <v>726182.765534147</v>
+        <v>731020.962508596</v>
       </c>
       <c r="GK10" t="n">
-        <v>730608.018226034</v>
+        <v>735083.313938925</v>
       </c>
       <c r="GL10" t="n">
-        <v>735163.724928415</v>
+        <v>739314.48528744</v>
       </c>
       <c r="GM10" t="n">
-        <v>739572.934017951</v>
+        <v>743394.882933294</v>
       </c>
       <c r="GN10" t="n">
-        <v>742995.880200524</v>
+        <v>746757.694098163</v>
       </c>
       <c r="GO10" t="n">
-        <v>746457.290113405</v>
+        <v>750164.412244528</v>
       </c>
       <c r="GP10" t="n">
-        <v>750151.567081315</v>
+        <v>753956.215412481</v>
       </c>
       <c r="GQ10" t="n">
-        <v>753557.804220865</v>
+        <v>757450.525144089</v>
       </c>
       <c r="GR10" t="n">
-        <v>757167.687541223</v>
+        <v>761133.415928168</v>
       </c>
       <c r="GS10" t="n">
-        <v>760980.783628016</v>
+        <v>764969.634094479</v>
       </c>
       <c r="GT10" t="n">
-        <v>764939.865797952</v>
+        <v>768920.776099925</v>
       </c>
       <c r="GU10" t="n">
-        <v>768607.374458679</v>
+        <v>772586.251578874</v>
       </c>
       <c r="GV10" t="n">
-        <v>772376.411949455</v>
+        <v>776358.319606314</v>
       </c>
       <c r="GW10" t="n">
-        <v>776349.983602408</v>
+        <v>780386.020572208</v>
       </c>
       <c r="GX10" t="n">
-        <v>780432.059703863</v>
+        <v>784591.128115529</v>
       </c>
       <c r="GY10" t="n">
-        <v>784255.176530579</v>
+        <v>788633.802564281</v>
       </c>
       <c r="GZ10" t="n">
-        <v>788208.41107687</v>
+        <v>792885.344044633</v>
       </c>
       <c r="HA10" t="n">
-        <v>792352.427654032</v>
+        <v>797415.297849055</v>
       </c>
       <c r="HB10" t="n">
-        <v>796659.668763709</v>
+        <v>802170.039867806</v>
       </c>
       <c r="HC10" t="n">
-        <v>800567.494317225</v>
+        <v>806619.1587935</v>
       </c>
       <c r="HD10" t="n">
-        <v>804616.898887417</v>
+        <v>811215.928635726</v>
       </c>
       <c r="HE10" t="n">
-        <v>808845.979435455</v>
+        <v>816034.661115189</v>
       </c>
       <c r="HF10" t="n">
-        <v>813094.353255207</v>
+        <v>820886.203095505</v>
       </c>
       <c r="HG10" t="n">
-        <v>817012.126111852</v>
+        <v>825419.865027868</v>
       </c>
       <c r="HH10" t="n">
-        <v>820933.558745458</v>
+        <v>829948.182957116</v>
       </c>
       <c r="HI10" t="n">
-        <v>824994.584324393</v>
+        <v>834607.458061932</v>
       </c>
       <c r="HJ10" t="n">
-        <v>829114.017851547</v>
+        <v>839306.34603109</v>
       </c>
       <c r="HK10" t="n">
-        <v>832851.006369303</v>
+        <v>843613.301166003</v>
       </c>
       <c r="HL10" t="n">
-        <v>836616.157167051</v>
+        <v>847914.921680958</v>
       </c>
       <c r="HM10" t="n">
-        <v>840507.533040829</v>
+        <v>852319.962678997</v>
       </c>
       <c r="HN10" t="n">
-        <v>844448.267303734</v>
+        <v>856740.20747032</v>
       </c>
       <c r="HO10" t="n">
-        <v>847986.068232007</v>
+        <v>860734.748746418</v>
       </c>
       <c r="HP10" t="n">
-        <v>851501.923978403</v>
+        <v>864666.510551157</v>
       </c>
       <c r="HQ10" t="n">
-        <v>855155.600188935</v>
+        <v>868701.870546178</v>
       </c>
       <c r="HR10" t="n">
-        <v>858870.754757173</v>
+        <v>872757.511676905</v>
       </c>
       <c r="HS10" t="n">
-        <v>862038.272039485</v>
+        <v>876274.557709986</v>
       </c>
       <c r="HT10" t="n">
-        <v>865263.880092127</v>
+        <v>879770.663465525</v>
       </c>
       <c r="HU10" t="n">
-        <v>868686.183366863</v>
+        <v>883441.963389559</v>
       </c>
     </row>
     <row r="11">
@@ -8906,148 +8894,148 @@
         <v>165029</v>
       </c>
       <c r="FZ11" t="n">
-        <v>165964.144949875</v>
+        <v>166237</v>
       </c>
       <c r="GA11" t="n">
-        <v>167104.60697095</v>
+        <v>168540</v>
       </c>
       <c r="GB11" t="n">
-        <v>167779.914095522</v>
+        <v>170963</v>
       </c>
       <c r="GC11" t="n">
-        <v>168618.672562836</v>
+        <v>167277.531103325</v>
       </c>
       <c r="GD11" t="n">
-        <v>169702.723339195</v>
+        <v>175895.12656163</v>
       </c>
       <c r="GE11" t="n">
-        <v>170740.84325468</v>
+        <v>170895.683828467</v>
       </c>
       <c r="GF11" t="n">
-        <v>171727.910635627</v>
+        <v>176754.459816398</v>
       </c>
       <c r="GG11" t="n">
-        <v>172584.044809137</v>
+        <v>176358.026882616</v>
       </c>
       <c r="GH11" t="n">
-        <v>173515.028270933</v>
+        <v>177586.173408747</v>
       </c>
       <c r="GI11" t="n">
-        <v>174467.768561475</v>
+        <v>178392.101007113</v>
       </c>
       <c r="GJ11" t="n">
-        <v>174679.989074725</v>
+        <v>178532.095522213</v>
       </c>
       <c r="GK11" t="n">
-        <v>175356.016469086</v>
+        <v>179111.666639002</v>
       </c>
       <c r="GL11" t="n">
-        <v>175922.133071828</v>
+        <v>179576.174739626</v>
       </c>
       <c r="GM11" t="n">
-        <v>176837.607512771</v>
+        <v>180360.836221725</v>
       </c>
       <c r="GN11" t="n">
-        <v>176940.653627839</v>
+        <v>180349.671612747</v>
       </c>
       <c r="GO11" t="n">
-        <v>177513.48877013</v>
+        <v>180805.6273347</v>
       </c>
       <c r="GP11" t="n">
-        <v>177991.369407385</v>
+        <v>181171.716468612</v>
       </c>
       <c r="GQ11" t="n">
-        <v>178342.634135549</v>
+        <v>181396.462367013</v>
       </c>
       <c r="GR11" t="n">
-        <v>178817.446796277</v>
+        <v>181735.980473077</v>
       </c>
       <c r="GS11" t="n">
-        <v>179222.306204363</v>
+        <v>181994.665490263</v>
       </c>
       <c r="GT11" t="n">
-        <v>179672.552494023</v>
+        <v>182290.263925667</v>
       </c>
       <c r="GU11" t="n">
-        <v>179900.004443717</v>
+        <v>182356.457073952</v>
       </c>
       <c r="GV11" t="n">
-        <v>180398.185127787</v>
+        <v>182688.187904009</v>
       </c>
       <c r="GW11" t="n">
-        <v>180745.221344192</v>
+        <v>182868.671888492</v>
       </c>
       <c r="GX11" t="n">
-        <v>181161.72761774</v>
+        <v>183119.63108947</v>
       </c>
       <c r="GY11" t="n">
-        <v>181534.909628825</v>
+        <v>183331.073787876</v>
       </c>
       <c r="GZ11" t="n">
-        <v>181952.310784948</v>
+        <v>183589.127776555</v>
       </c>
       <c r="HA11" t="n">
-        <v>182386.549011744</v>
+        <v>183868.898548623</v>
       </c>
       <c r="HB11" t="n">
-        <v>182852.858451259</v>
+        <v>184183.103904358</v>
       </c>
       <c r="HC11" t="n">
-        <v>182902.63060861</v>
+        <v>184088.665504951</v>
       </c>
       <c r="HD11" t="n">
-        <v>183549.832318405</v>
+        <v>184585.881670206</v>
       </c>
       <c r="HE11" t="n">
-        <v>183831.821185918</v>
+        <v>184724.624347844</v>
       </c>
       <c r="HF11" t="n">
-        <v>184240.731965617</v>
+        <v>184990.31937484</v>
       </c>
       <c r="HG11" t="n">
-        <v>184611.878160636</v>
+        <v>185221.175727776</v>
       </c>
       <c r="HH11" t="n">
-        <v>185017.313125898</v>
+        <v>185486.805786536</v>
       </c>
       <c r="HI11" t="n">
-        <v>185450.917224236</v>
+        <v>185781.932542608</v>
       </c>
       <c r="HJ11" t="n">
-        <v>185905.616800516</v>
+        <v>186098.481925697</v>
       </c>
       <c r="HK11" t="n">
-        <v>186344.857433593</v>
+        <v>186401.018414366</v>
       </c>
       <c r="HL11" t="n">
-        <v>186811.379735515</v>
+        <v>186729.997246618</v>
       </c>
       <c r="HM11" t="n">
-        <v>187304.247942958</v>
+        <v>187085.599091703</v>
       </c>
       <c r="HN11" t="n">
-        <v>187814.741962928</v>
+        <v>187457.757176859</v>
       </c>
       <c r="HO11" t="n">
-        <v>188306.294831338</v>
+        <v>187811.1271084</v>
       </c>
       <c r="HP11" t="n">
-        <v>188818.677590237</v>
+        <v>188183.477860671</v>
       </c>
       <c r="HQ11" t="n">
-        <v>189356.919299403</v>
+        <v>188580.305781173</v>
       </c>
       <c r="HR11" t="n">
-        <v>189911.186067659</v>
+        <v>188990.832562807</v>
       </c>
       <c r="HS11" t="n">
-        <v>189824.094511674</v>
+        <v>188776.358860941</v>
       </c>
       <c r="HT11" t="n">
-        <v>190513.420544814</v>
+        <v>189309.582121317</v>
       </c>
       <c r="HU11" t="n">
-        <v>190698.289748831</v>
+        <v>189353.895806941</v>
       </c>
     </row>
     <row r="12">
@@ -9595,148 +9583,148 @@
         <v>154215</v>
       </c>
       <c r="FZ12" t="n">
-        <v>155775.318036827</v>
+        <v>155776</v>
       </c>
       <c r="GA12" t="n">
-        <v>157724.661689785</v>
+        <v>158522</v>
       </c>
       <c r="GB12" t="n">
-        <v>159617.812212152</v>
+        <v>162177</v>
       </c>
       <c r="GC12" t="n">
-        <v>161375.061677129</v>
+        <v>164151.220763404</v>
       </c>
       <c r="GD12" t="n">
-        <v>163146.997531615</v>
+        <v>165737.970888426</v>
       </c>
       <c r="GE12" t="n">
-        <v>164984.943861335</v>
+        <v>167732.560208389</v>
       </c>
       <c r="GF12" t="n">
-        <v>166933.981140394</v>
+        <v>169731.054353171</v>
       </c>
       <c r="GG12" t="n">
-        <v>168894.210182327</v>
+        <v>171601.617270488</v>
       </c>
       <c r="GH12" t="n">
-        <v>170774.083792876</v>
+        <v>172921.505779413</v>
       </c>
       <c r="GI12" t="n">
-        <v>172422.633347256</v>
+        <v>173770.17594194</v>
       </c>
       <c r="GJ12" t="n">
-        <v>173803.071064718</v>
+        <v>174257.041115777</v>
       </c>
       <c r="GK12" t="n">
-        <v>175120.351064698</v>
+        <v>174748.322137028</v>
       </c>
       <c r="GL12" t="n">
-        <v>176482.305957273</v>
+        <v>175441.710350346</v>
       </c>
       <c r="GM12" t="n">
-        <v>177813.664033018</v>
+        <v>176401.67044174</v>
       </c>
       <c r="GN12" t="n">
-        <v>178810.990634378</v>
+        <v>177039.577270137</v>
       </c>
       <c r="GO12" t="n">
-        <v>179699.063779387</v>
+        <v>177696.753367226</v>
       </c>
       <c r="GP12" t="n">
-        <v>180691.964044531</v>
+        <v>178594.719967597</v>
       </c>
       <c r="GQ12" t="n">
-        <v>181646.062803435</v>
+        <v>179554.13247014</v>
       </c>
       <c r="GR12" t="n">
-        <v>182642.468918271</v>
+        <v>180618.422744395</v>
       </c>
       <c r="GS12" t="n">
-        <v>183763.836653914</v>
+        <v>181853.630070112</v>
       </c>
       <c r="GT12" t="n">
-        <v>184989.653538105</v>
+        <v>183233.619959234</v>
       </c>
       <c r="GU12" t="n">
-        <v>186163.872429526</v>
+        <v>184612.859591181</v>
       </c>
       <c r="GV12" t="n">
-        <v>187351.628855238</v>
+        <v>186052.491501856</v>
       </c>
       <c r="GW12" t="n">
-        <v>188646.550081688</v>
+        <v>187652.545292179</v>
       </c>
       <c r="GX12" t="n">
-        <v>190029.39170195</v>
+        <v>189398.5445605</v>
       </c>
       <c r="GY12" t="n">
-        <v>191358.897008286</v>
+        <v>191153.774298721</v>
       </c>
       <c r="GZ12" t="n">
-        <v>192712.299414277</v>
+        <v>192984.659658753</v>
       </c>
       <c r="HA12" t="n">
-        <v>194165.127049979</v>
+        <v>194959.224310341</v>
       </c>
       <c r="HB12" t="n">
-        <v>195719.936662272</v>
+        <v>197065.805925496</v>
       </c>
       <c r="HC12" t="n">
-        <v>197173.875560103</v>
+        <v>199102.769701954</v>
       </c>
       <c r="HD12" t="n">
-        <v>198630.689119812</v>
+        <v>201142.45591873</v>
       </c>
       <c r="HE12" t="n">
-        <v>200181.6057864</v>
+        <v>203272.430266631</v>
       </c>
       <c r="HF12" t="n">
-        <v>201775.167614523</v>
+        <v>205433.2597091</v>
       </c>
       <c r="HG12" t="n">
-        <v>203267.067703145</v>
+        <v>207472.203709057</v>
       </c>
       <c r="HH12" t="n">
-        <v>204720.273769292</v>
+        <v>209443.57294523</v>
       </c>
       <c r="HI12" t="n">
-        <v>206234.259866701</v>
+        <v>211444.041286388</v>
       </c>
       <c r="HJ12" t="n">
-        <v>207799.607877436</v>
+        <v>213461.186804231</v>
       </c>
       <c r="HK12" t="n">
-        <v>209251.982284928</v>
+        <v>215330.567650062</v>
       </c>
       <c r="HL12" t="n">
-        <v>210667.972117096</v>
+        <v>217124.012060864</v>
       </c>
       <c r="HM12" t="n">
-        <v>212147.634205376</v>
+        <v>218945.287952665</v>
       </c>
       <c r="HN12" t="n">
-        <v>213678.319847066</v>
+        <v>220781.471910402</v>
       </c>
       <c r="HO12" t="n">
-        <v>215091.056181499</v>
+        <v>222465.130732645</v>
       </c>
       <c r="HP12" t="n">
-        <v>216452.534402047</v>
+        <v>224061.977433061</v>
       </c>
       <c r="HQ12" t="n">
-        <v>217879.592655066</v>
+        <v>225693.437708638</v>
       </c>
       <c r="HR12" t="n">
-        <v>219368.355269194</v>
+        <v>227356.992484466</v>
       </c>
       <c r="HS12" t="n">
-        <v>220694.62984155</v>
+        <v>228843.814168888</v>
       </c>
       <c r="HT12" t="n">
-        <v>221979.865574255</v>
+        <v>230255.578390563</v>
       </c>
       <c r="HU12" t="n">
-        <v>223368.211627249</v>
+        <v>231749.682344607</v>
       </c>
     </row>
     <row r="13">
@@ -10284,148 +10272,148 @@
         <v>677077</v>
       </c>
       <c r="FZ13" t="n">
-        <v>682056.331589137</v>
+        <v>679519</v>
       </c>
       <c r="GA13" t="n">
-        <v>687310.132940827</v>
+        <v>684822</v>
       </c>
       <c r="GB13" t="n">
-        <v>691271.520754247</v>
+        <v>688271</v>
       </c>
       <c r="GC13" t="n">
-        <v>695751.354395851</v>
+        <v>688919.4526957</v>
       </c>
       <c r="GD13" t="n">
-        <v>700726.559077568</v>
+        <v>702740.222489689</v>
       </c>
       <c r="GE13" t="n">
-        <v>705495.009977356</v>
+        <v>704367.925018541</v>
       </c>
       <c r="GF13" t="n">
-        <v>710301.861727193</v>
+        <v>715674.756586436</v>
       </c>
       <c r="GG13" t="n">
-        <v>714904.104764168</v>
+        <v>720857.895280625</v>
       </c>
       <c r="GH13" t="n">
-        <v>719216.098101294</v>
+        <v>726242.873442222</v>
       </c>
       <c r="GI13" t="n">
-        <v>723406.532859782</v>
+        <v>731118.656860063</v>
       </c>
       <c r="GJ13" t="n">
-        <v>726629.706805515</v>
+        <v>734866.04047816</v>
       </c>
       <c r="GK13" t="n">
-        <v>730413.706740859</v>
+        <v>739016.681336514</v>
       </c>
       <c r="GL13" t="n">
-        <v>734173.574825043</v>
+        <v>743018.973918343</v>
       </c>
       <c r="GM13" t="n">
-        <v>738166.901448307</v>
+        <v>746924.072368229</v>
       </c>
       <c r="GN13" t="n">
-        <v>740695.565959707</v>
+        <v>749637.81189496</v>
       </c>
       <c r="GO13" t="n">
-        <v>743841.738322759</v>
+        <v>752843.309376913</v>
       </c>
       <c r="GP13" t="n">
-        <v>747020.99584957</v>
+        <v>756103.236710332</v>
       </c>
       <c r="GQ13" t="n">
-        <v>749824.399125121</v>
+        <v>758862.879452743</v>
       </c>
       <c r="GR13" t="n">
-        <v>752912.68867117</v>
+        <v>761820.997457159</v>
       </c>
       <c r="GS13" t="n">
-        <v>756009.275970578</v>
+        <v>764680.69268911</v>
       </c>
       <c r="GT13" t="n">
-        <v>759192.788664545</v>
+        <v>767547.444488612</v>
       </c>
       <c r="GU13" t="n">
-        <v>761913.529711362</v>
+        <v>769899.87274692</v>
       </c>
       <c r="GV13" t="n">
-        <v>764992.992370151</v>
+        <v>772564.040785468</v>
       </c>
       <c r="GW13" t="n">
-        <v>768018.677880552</v>
+        <v>775172.170852822</v>
       </c>
       <c r="GX13" t="n">
-        <v>771134.419153049</v>
+        <v>777882.239059528</v>
       </c>
       <c r="GY13" t="n">
-        <v>774001.213183132</v>
+        <v>780381.127076647</v>
       </c>
       <c r="GZ13" t="n">
-        <v>777018.446669993</v>
+        <v>783059.837484371</v>
       </c>
       <c r="HA13" t="n">
-        <v>780143.873852708</v>
+        <v>785894.99747057</v>
       </c>
       <c r="HB13" t="n">
-        <v>783362.614487101</v>
+        <v>788857.362977756</v>
       </c>
       <c r="HC13" t="n">
-        <v>785866.273360823</v>
+        <v>791175.081737902</v>
       </c>
       <c r="HD13" t="n">
-        <v>789106.067456277</v>
+        <v>794229.380824643</v>
       </c>
       <c r="HE13" t="n">
-        <v>792066.219675151</v>
+        <v>797056.883120157</v>
       </c>
       <c r="HF13" t="n">
-        <v>795129.94373341</v>
+        <v>800013.28967364</v>
       </c>
       <c r="HG13" t="n">
-        <v>797926.962030986</v>
+        <v>802738.865166105</v>
       </c>
       <c r="HH13" t="n">
-        <v>800800.624846803</v>
+        <v>805561.442768552</v>
       </c>
       <c r="HI13" t="n">
-        <v>803781.267504392</v>
+        <v>808515.377338633</v>
       </c>
       <c r="HJ13" t="n">
-        <v>806790.053580935</v>
+        <v>811513.67013494</v>
       </c>
       <c r="HK13" t="n">
-        <v>809513.907375128</v>
+        <v>814253.781906246</v>
       </c>
       <c r="HL13" t="n">
-        <v>812329.591700811</v>
+        <v>817090.935250896</v>
       </c>
       <c r="HM13" t="n">
-        <v>815234.174702791</v>
+        <v>820030.302995427</v>
       </c>
       <c r="HN13" t="n">
-        <v>818154.71609854</v>
+        <v>822986.52269929</v>
       </c>
       <c r="HO13" t="n">
-        <v>820771.334626896</v>
+        <v>825650.775952311</v>
       </c>
       <c r="HP13" t="n">
-        <v>823438.093848951</v>
+        <v>828358.042779065</v>
       </c>
       <c r="HQ13" t="n">
-        <v>826202.954548032</v>
+        <v>831158.768637887</v>
       </c>
       <c r="HR13" t="n">
-        <v>828983.61420137</v>
+        <v>833961.382594759</v>
       </c>
       <c r="HS13" t="n">
-        <v>830737.764883198</v>
+        <v>835777.134655104</v>
       </c>
       <c r="HT13" t="n">
-        <v>833367.464496681</v>
+        <v>838394.697813545</v>
       </c>
       <c r="HU13" t="n">
-        <v>835586.290105598</v>
+        <v>840616.20867275</v>
       </c>
     </row>
     <row r="14">
@@ -10805,148 +10793,148 @@
         <v>666293</v>
       </c>
       <c r="FZ14" t="n">
-        <v>671991.008902272</v>
+        <v>669101</v>
       </c>
       <c r="GA14" t="n">
-        <v>677679.493175377</v>
+        <v>673000</v>
       </c>
       <c r="GB14" t="n">
-        <v>682752.874677611</v>
+        <v>681761</v>
       </c>
       <c r="GC14" t="n">
-        <v>688081.763821884</v>
+        <v>686084.528352771</v>
       </c>
       <c r="GD14" t="n">
-        <v>693635.100252694</v>
+        <v>692940.300289779</v>
       </c>
       <c r="GE14" t="n">
-        <v>699091.028891445</v>
+        <v>700256.148166028</v>
       </c>
       <c r="GF14" t="n">
-        <v>704787.236450423</v>
+        <v>708110.399358663</v>
       </c>
       <c r="GG14" t="n">
-        <v>710419.236270555</v>
+        <v>714698.437045676</v>
       </c>
       <c r="GH14" t="n">
-        <v>715635.286650245</v>
+        <v>720389.45648651</v>
       </c>
       <c r="GI14" t="n">
-        <v>720495.469891951</v>
+        <v>725146.093502638</v>
       </c>
       <c r="GJ14" t="n">
-        <v>724865.847536133</v>
+        <v>729278.880214815</v>
       </c>
       <c r="GK14" t="n">
-        <v>729340.442324792</v>
+        <v>733396.674036147</v>
       </c>
       <c r="GL14" t="n">
-        <v>733865.75832669</v>
+        <v>737638.653752083</v>
       </c>
       <c r="GM14" t="n">
-        <v>738275.980110831</v>
+        <v>741754.533752303</v>
       </c>
       <c r="GN14" t="n">
-        <v>741671.298014145</v>
+        <v>745146.025341888</v>
       </c>
       <c r="GO14" t="n">
-        <v>745226.734829246</v>
+        <v>748663.7966459</v>
       </c>
       <c r="GP14" t="n">
-        <v>748905.734997029</v>
+        <v>752479.250311252</v>
       </c>
       <c r="GQ14" t="n">
-        <v>752330.591260766</v>
+        <v>756015.552247049</v>
       </c>
       <c r="GR14" t="n">
-        <v>755971.298479218</v>
+        <v>759762.45716806</v>
       </c>
       <c r="GS14" t="n">
-        <v>759782.122330769</v>
+        <v>763627.001935156</v>
       </c>
       <c r="GT14" t="n">
-        <v>763749.230524399</v>
+        <v>767619.019762511</v>
       </c>
       <c r="GU14" t="n">
-        <v>767413.548324744</v>
+        <v>771312.490334562</v>
       </c>
       <c r="GV14" t="n">
-        <v>771217.952729154</v>
+        <v>775148.234474587</v>
       </c>
       <c r="GW14" t="n">
-        <v>775179.474741465</v>
+        <v>779191.244856735</v>
       </c>
       <c r="GX14" t="n">
-        <v>779271.458672068</v>
+        <v>783428.035265202</v>
       </c>
       <c r="GY14" t="n">
-        <v>783089.052005762</v>
+        <v>787483.592612095</v>
       </c>
       <c r="GZ14" t="n">
-        <v>787061.553514676</v>
+        <v>791767.240308352</v>
       </c>
       <c r="HA14" t="n">
-        <v>791201.288643835</v>
+        <v>796303.431095597</v>
       </c>
       <c r="HB14" t="n">
-        <v>795504.868409285</v>
+        <v>801060.510537646</v>
       </c>
       <c r="HC14" t="n">
-        <v>799403.382813814</v>
+        <v>805504.6082705</v>
       </c>
       <c r="HD14" t="n">
-        <v>803500.474251307</v>
+        <v>810147.824150371</v>
       </c>
       <c r="HE14" t="n">
-        <v>807692.832158508</v>
+        <v>814932.288643449</v>
       </c>
       <c r="HF14" t="n">
-        <v>811960.854645804</v>
+        <v>819800.163186731</v>
       </c>
       <c r="HG14" t="n">
-        <v>815868.62914798</v>
+        <v>824322.042502967</v>
       </c>
       <c r="HH14" t="n">
-        <v>819811.428512289</v>
+        <v>828867.321643037</v>
       </c>
       <c r="HI14" t="n">
-        <v>823872.967032825</v>
+        <v>833523.685817943</v>
       </c>
       <c r="HJ14" t="n">
-        <v>827991.320826667</v>
+        <v>838217.067870954</v>
       </c>
       <c r="HK14" t="n">
-        <v>831726.233768475</v>
+        <v>842517.868685344</v>
       </c>
       <c r="HL14" t="n">
-        <v>835511.3485816</v>
+        <v>846834.164249379</v>
       </c>
       <c r="HM14" t="n">
-        <v>839403.880075149</v>
+        <v>851236.689378027</v>
       </c>
       <c r="HN14" t="n">
-        <v>843344.740856707</v>
+        <v>855652.849476477</v>
       </c>
       <c r="HO14" t="n">
-        <v>846882.081622034</v>
+        <v>859643.811267498</v>
       </c>
       <c r="HP14" t="n">
-        <v>850420.378403406</v>
+        <v>863594.139755411</v>
       </c>
       <c r="HQ14" t="n">
-        <v>854079.833636971</v>
+        <v>867633.292785636</v>
       </c>
       <c r="HR14" t="n">
-        <v>857797.169381721</v>
+        <v>871689.344045084</v>
       </c>
       <c r="HS14" t="n">
-        <v>860966.566478543</v>
+        <v>875207.758667639</v>
       </c>
       <c r="HT14" t="n">
-        <v>864269.565146466</v>
+        <v>878776.638425049</v>
       </c>
       <c r="HU14" t="n">
-        <v>867660.713708613</v>
+        <v>882421.343076414</v>
       </c>
     </row>
     <row r="15">
@@ -11494,148 +11482,148 @@
         <v>690352</v>
       </c>
       <c r="FZ15" t="n">
-        <v>703719.528268736</v>
+        <v>699150</v>
       </c>
       <c r="GA15" t="n">
-        <v>715281.997948853</v>
+        <v>705456</v>
       </c>
       <c r="GB15" t="n">
-        <v>725484.118569073</v>
+        <v>718591</v>
       </c>
       <c r="GC15" t="n">
-        <v>736497.319397187</v>
+        <v>722503.917694143</v>
       </c>
       <c r="GD15" t="n">
-        <v>749596.654229395</v>
+        <v>745057.79470314</v>
       </c>
       <c r="GE15" t="n">
-        <v>762897.057923681</v>
+        <v>757298.70344948</v>
       </c>
       <c r="GF15" t="n">
-        <v>776481.447060038</v>
+        <v>778452.083424455</v>
       </c>
       <c r="GG15" t="n">
-        <v>790183.548801809</v>
+        <v>794307.940319648</v>
       </c>
       <c r="GH15" t="n">
-        <v>802379.623685296</v>
+        <v>808925.051257746</v>
       </c>
       <c r="GI15" t="n">
-        <v>814530.995474338</v>
+        <v>823142.830981455</v>
       </c>
       <c r="GJ15" t="n">
-        <v>825924.403800134</v>
+        <v>836451.494189787</v>
       </c>
       <c r="GK15" t="n">
-        <v>838037.27760897</v>
+        <v>850207.474244808</v>
       </c>
       <c r="GL15" t="n">
-        <v>850169.292735606</v>
+        <v>863679.50219178</v>
       </c>
       <c r="GM15" t="n">
-        <v>862554.857495875</v>
+        <v>876622.487374243</v>
       </c>
       <c r="GN15" t="n">
-        <v>873336.980136029</v>
+        <v>888555.705693557</v>
       </c>
       <c r="GO15" t="n">
-        <v>884791.379213478</v>
+        <v>901008.451226819</v>
       </c>
       <c r="GP15" t="n">
-        <v>896425.307156296</v>
+        <v>913648.153304255</v>
       </c>
       <c r="GQ15" t="n">
-        <v>907693.021488228</v>
+        <v>925671.942457966</v>
       </c>
       <c r="GR15" t="n">
-        <v>919366.779288336</v>
+        <v>937910.775864315</v>
       </c>
       <c r="GS15" t="n">
-        <v>931140.975480953</v>
+        <v>950043.445541395</v>
       </c>
       <c r="GT15" t="n">
-        <v>943197.543612835</v>
+        <v>962280.463938404</v>
       </c>
       <c r="GU15" t="n">
-        <v>954825.139107545</v>
+        <v>973956.025713916</v>
       </c>
       <c r="GV15" t="n">
-        <v>966958.343825072</v>
+        <v>986009.001759324</v>
       </c>
       <c r="GW15" t="n">
-        <v>979188.205072464</v>
+        <v>998118.827857557</v>
       </c>
       <c r="GX15" t="n">
-        <v>991682.845081904</v>
+        <v>1010468.35416493</v>
       </c>
       <c r="GY15" t="n">
-        <v>1004000.52914365</v>
+        <v>1022657.20685399</v>
       </c>
       <c r="GZ15" t="n">
-        <v>1016659.47466627</v>
+        <v>1035212.56531707</v>
       </c>
       <c r="HA15" t="n">
-        <v>1029625.48643453</v>
+        <v>1048136.83072038</v>
       </c>
       <c r="HB15" t="n">
-        <v>1043166.96534263</v>
+        <v>1061665.66408999</v>
       </c>
       <c r="HC15" t="n">
-        <v>1056038.00671748</v>
+        <v>1074641.36257305</v>
       </c>
       <c r="HD15" t="n">
-        <v>1069926.1669328</v>
+        <v>1088609.89195036</v>
       </c>
       <c r="HE15" t="n">
-        <v>1083758.44141504</v>
+        <v>1102640.51166372</v>
       </c>
       <c r="HF15" t="n">
-        <v>1097919.55407473</v>
+        <v>1117044.60380535</v>
       </c>
       <c r="HG15" t="n">
-        <v>1111914.41636243</v>
+        <v>1131345.4023421</v>
       </c>
       <c r="HH15" t="n">
-        <v>1126210.59369145</v>
+        <v>1145999.49843295</v>
       </c>
       <c r="HI15" t="n">
-        <v>1140864.06037963</v>
+        <v>1161077.10335679</v>
       </c>
       <c r="HJ15" t="n">
-        <v>1155771.92984501</v>
+        <v>1176462.2005985</v>
       </c>
       <c r="HK15" t="n">
-        <v>1170464.41518363</v>
+        <v>1191690.75327024</v>
       </c>
       <c r="HL15" t="n">
-        <v>1185486.77471634</v>
+        <v>1207289.52999797</v>
       </c>
       <c r="HM15" t="n">
-        <v>1200846.20186832</v>
+        <v>1223283.48436327</v>
       </c>
       <c r="HN15" t="n">
-        <v>1216443.74059932</v>
+        <v>1239552.32481554</v>
       </c>
       <c r="HO15" t="n">
-        <v>1231775.41489649</v>
+        <v>1255597.33814202</v>
       </c>
       <c r="HP15" t="n">
-        <v>1247365.59800837</v>
+        <v>1271924.47473347</v>
       </c>
       <c r="HQ15" t="n">
-        <v>1263306.67096059</v>
+        <v>1288633.63281366</v>
       </c>
       <c r="HR15" t="n">
-        <v>1279484.24042689</v>
+        <v>1305591.44198557</v>
       </c>
       <c r="HS15" t="n">
-        <v>1294491.12201623</v>
+        <v>1321492.40868137</v>
       </c>
       <c r="HT15" t="n">
-        <v>1310723.32017215</v>
+        <v>1338505.12178683</v>
       </c>
       <c r="HU15" t="n">
-        <v>1326716.47762596</v>
+        <v>1355358.82584273</v>
       </c>
     </row>
     <row r="16">
@@ -12183,148 +12171,148 @@
         <v>1.01960633724082</v>
       </c>
       <c r="FZ16" t="n">
-        <v>1.03176160819493</v>
+        <v>1.02888955275717</v>
       </c>
       <c r="GA16" t="n">
-        <v>1.04069759868465</v>
+        <v>1.03013045725751</v>
       </c>
       <c r="GB16" t="n">
-        <v>1.0494922782811</v>
+        <v>1.04405241540033</v>
       </c>
       <c r="GC16" t="n">
-        <v>1.05856397978347</v>
+        <v>1.04874943516838</v>
       </c>
       <c r="GD16" t="n">
-        <v>1.06974203640265</v>
+        <v>1.06021794612125</v>
       </c>
       <c r="GE16" t="n">
-        <v>1.0813642170923</v>
+        <v>1.07514649246532</v>
       </c>
       <c r="GF16" t="n">
-        <v>1.09317107089913</v>
+        <v>1.08771766747202</v>
       </c>
       <c r="GG16" t="n">
-        <v>1.10530005627378</v>
+        <v>1.10189253313743</v>
       </c>
       <c r="GH16" t="n">
-        <v>1.11563078737725</v>
+        <v>1.11384919854822</v>
       </c>
       <c r="GI16" t="n">
-        <v>1.12596576909029</v>
+        <v>1.12586762042517</v>
       </c>
       <c r="GJ16" t="n">
-        <v>1.13665102601341</v>
+        <v>1.13823668578227</v>
       </c>
       <c r="GK16" t="n">
-        <v>1.14734604234118</v>
+        <v>1.15045774803798</v>
       </c>
       <c r="GL16" t="n">
-        <v>1.15799494838709</v>
+        <v>1.16239224805361</v>
       </c>
       <c r="GM16" t="n">
-        <v>1.16850925482913</v>
+        <v>1.17364336397154</v>
       </c>
       <c r="GN16" t="n">
-        <v>1.17907682942711</v>
+        <v>1.1853133419446</v>
       </c>
       <c r="GO16" t="n">
-        <v>1.18948875041301</v>
+        <v>1.19680740348115</v>
       </c>
       <c r="GP16" t="n">
-        <v>1.20000015229706</v>
+        <v>1.20836428800328</v>
       </c>
       <c r="GQ16" t="n">
-        <v>1.21054079498627</v>
+        <v>1.21981449362494</v>
       </c>
       <c r="GR16" t="n">
-        <v>1.22108020822101</v>
+        <v>1.23114324220087</v>
       </c>
       <c r="GS16" t="n">
-        <v>1.23165284984506</v>
+        <v>1.2424054271835</v>
       </c>
       <c r="GT16" t="n">
-        <v>1.24236895077663</v>
+        <v>1.25370811728533</v>
       </c>
       <c r="GU16" t="n">
-        <v>1.25319358006768</v>
+        <v>1.2650424527813</v>
       </c>
       <c r="GV16" t="n">
-        <v>1.26400942123541</v>
+        <v>1.27628125027775</v>
       </c>
       <c r="GW16" t="n">
-        <v>1.27495364197549</v>
+        <v>1.28760920883485</v>
       </c>
       <c r="GX16" t="n">
-        <v>1.28600517131302</v>
+        <v>1.29899913007127</v>
       </c>
       <c r="GY16" t="n">
-        <v>1.29715628108624</v>
+        <v>1.31045865780579</v>
       </c>
       <c r="GZ16" t="n">
-        <v>1.30841099746083</v>
+        <v>1.32200952317615</v>
       </c>
       <c r="HA16" t="n">
-        <v>1.31978924270531</v>
+        <v>1.33368558190408</v>
       </c>
       <c r="HB16" t="n">
-        <v>1.33165273854729</v>
+        <v>1.34582715343616</v>
       </c>
       <c r="HC16" t="n">
-        <v>1.34378843827175</v>
+        <v>1.35828514071597</v>
       </c>
       <c r="HD16" t="n">
-        <v>1.35587117722461</v>
+        <v>1.37064922499956</v>
       </c>
       <c r="HE16" t="n">
-        <v>1.36826747503712</v>
+        <v>1.38338997786188</v>
       </c>
       <c r="HF16" t="n">
-        <v>1.38080519769263</v>
+        <v>1.39628254799879</v>
       </c>
       <c r="HG16" t="n">
-        <v>1.39350400930808</v>
+        <v>1.40935669249114</v>
       </c>
       <c r="HH16" t="n">
-        <v>1.40635579348594</v>
+        <v>1.42260965550787</v>
       </c>
       <c r="HI16" t="n">
-        <v>1.41937130174071</v>
+        <v>1.43606061477482</v>
       </c>
       <c r="HJ16" t="n">
-        <v>1.43255600155267</v>
+        <v>1.44971333024404</v>
       </c>
       <c r="HK16" t="n">
-        <v>1.44588549631425</v>
+        <v>1.46353724448202</v>
       </c>
       <c r="HL16" t="n">
-        <v>1.45936672647768</v>
+        <v>1.47754608395669</v>
       </c>
       <c r="HM16" t="n">
-        <v>1.4730076843283</v>
+        <v>1.49175397513009</v>
       </c>
       <c r="HN16" t="n">
-        <v>1.48681382315527</v>
+        <v>1.50616355005497</v>
       </c>
       <c r="HO16" t="n">
-        <v>1.50075345394352</v>
+        <v>1.52073655205317</v>
       </c>
       <c r="HP16" t="n">
-        <v>1.51482619874522</v>
+        <v>1.53547666993771</v>
       </c>
       <c r="HQ16" t="n">
-        <v>1.52905126180109</v>
+        <v>1.55040607728885</v>
       </c>
       <c r="HR16" t="n">
-        <v>1.54343730943779</v>
+        <v>1.5655298202253</v>
       </c>
       <c r="HS16" t="n">
-        <v>1.55824277534055</v>
+        <v>1.58115402252339</v>
       </c>
       <c r="HT16" t="n">
-        <v>1.57280356406921</v>
+        <v>1.59650948936678</v>
       </c>
       <c r="HU16" t="n">
-        <v>1.5877671652509</v>
+        <v>1.61233959015163</v>
       </c>
     </row>
     <row r="17">
@@ -12872,148 +12860,148 @@
         <v>139.6</v>
       </c>
       <c r="FZ17" t="n">
-        <v>140.031862754532</v>
+        <v>140.9</v>
       </c>
       <c r="GA17" t="n">
-        <v>140.599706676254</v>
+        <v>141.9</v>
       </c>
       <c r="GB17" t="n">
-        <v>141.329719995302</v>
+        <v>143.5</v>
       </c>
       <c r="GC17" t="n">
-        <v>142.196179582441</v>
+        <v>144.862254063989</v>
       </c>
       <c r="GD17" t="n">
-        <v>143.220125637523</v>
+        <v>146.357242915682</v>
       </c>
       <c r="GE17" t="n">
-        <v>144.372331198218</v>
+        <v>148.035797596925</v>
       </c>
       <c r="GF17" t="n">
-        <v>145.639061748736</v>
+        <v>149.827169875167</v>
       </c>
       <c r="GG17" t="n">
-        <v>147.004263036338</v>
+        <v>151.669239888509</v>
       </c>
       <c r="GH17" t="n">
-        <v>148.43961866706</v>
+        <v>153.565957247488</v>
       </c>
       <c r="GI17" t="n">
-        <v>149.948025862154</v>
+        <v>155.508650265794</v>
       </c>
       <c r="GJ17" t="n">
-        <v>151.505515085874</v>
+        <v>157.470226368625</v>
       </c>
       <c r="GK17" t="n">
-        <v>153.113850479583</v>
+        <v>159.435009998264</v>
       </c>
       <c r="GL17" t="n">
-        <v>154.764042586615</v>
+        <v>161.387801777659</v>
       </c>
       <c r="GM17" t="n">
-        <v>156.456361528517</v>
+        <v>163.306508113754</v>
       </c>
       <c r="GN17" t="n">
-        <v>158.148707378578</v>
+        <v>165.194361556554</v>
       </c>
       <c r="GO17" t="n">
-        <v>159.86824945787</v>
+        <v>167.061308222207</v>
       </c>
       <c r="GP17" t="n">
-        <v>161.607011372269</v>
+        <v>168.906198716389</v>
       </c>
       <c r="GQ17" t="n">
-        <v>163.361277725096</v>
+        <v>170.726198556729</v>
       </c>
       <c r="GR17" t="n">
-        <v>165.14157795204</v>
+        <v>172.534325627709</v>
       </c>
       <c r="GS17" t="n">
-        <v>166.940658585809</v>
+        <v>174.326565264684</v>
       </c>
       <c r="GT17" t="n">
-        <v>168.762496402075</v>
+        <v>176.10884447365</v>
       </c>
       <c r="GU17" t="n">
-        <v>170.599726611923</v>
+        <v>177.878635893466</v>
       </c>
       <c r="GV17" t="n">
-        <v>172.460386726461</v>
+        <v>179.645382062699</v>
       </c>
       <c r="GW17" t="n">
-        <v>174.339854165942</v>
+        <v>181.40947572753</v>
       </c>
       <c r="GX17" t="n">
-        <v>176.238948247898</v>
+        <v>183.174934279189</v>
       </c>
       <c r="GY17" t="n">
-        <v>178.153058960589</v>
+        <v>184.942058949788</v>
       </c>
       <c r="GZ17" t="n">
-        <v>180.088948774833</v>
+        <v>186.720421057976</v>
       </c>
       <c r="HA17" t="n">
-        <v>182.042101605875</v>
+        <v>188.509566801523</v>
       </c>
       <c r="HB17" t="n">
-        <v>184.015421843889</v>
+        <v>190.314776816744</v>
       </c>
       <c r="HC17" t="n">
-        <v>185.999467730928</v>
+        <v>192.132653520934</v>
       </c>
       <c r="HD17" t="n">
-        <v>188.009681493195</v>
+        <v>193.977013365663</v>
       </c>
       <c r="HE17" t="n">
-        <v>190.034665207412</v>
+        <v>195.841915167937</v>
       </c>
       <c r="HF17" t="n">
-        <v>192.079652551578</v>
+        <v>197.732627905663</v>
       </c>
       <c r="HG17" t="n">
-        <v>194.139658585201</v>
+        <v>199.647084584644</v>
       </c>
       <c r="HH17" t="n">
-        <v>196.219442814874</v>
+        <v>201.590180284239</v>
       </c>
       <c r="HI17" t="n">
-        <v>198.317669352106</v>
+        <v>203.561548851848</v>
       </c>
       <c r="HJ17" t="n">
-        <v>200.434420988199</v>
+        <v>205.561789550175</v>
       </c>
       <c r="HK17" t="n">
-        <v>202.566000470008</v>
+        <v>207.588446625889</v>
       </c>
       <c r="HL17" t="n">
-        <v>204.71888383637</v>
+        <v>209.647141830796</v>
       </c>
       <c r="HM17" t="n">
-        <v>206.889671219782</v>
+        <v>211.734845988832</v>
       </c>
       <c r="HN17" t="n">
-        <v>209.079209289457</v>
+        <v>213.851984504877</v>
       </c>
       <c r="HO17" t="n">
-        <v>211.28316315863</v>
+        <v>215.995040848376</v>
       </c>
       <c r="HP17" t="n">
-        <v>213.504569801471</v>
+        <v>218.165733270247</v>
       </c>
       <c r="HQ17" t="n">
-        <v>215.743729131753</v>
+        <v>220.363982118621</v>
       </c>
       <c r="HR17" t="n">
-        <v>218.000363363015</v>
+        <v>222.588969256056</v>
       </c>
       <c r="HS17" t="n">
-        <v>220.262158618861</v>
+        <v>224.831397922271</v>
       </c>
       <c r="HT17" t="n">
-        <v>222.546000641149</v>
+        <v>227.101960331755</v>
       </c>
       <c r="HU17" t="n">
-        <v>224.839944632737</v>
+        <v>229.392254250843</v>
       </c>
     </row>
     <row r="18">
@@ -13561,148 +13549,148 @@
         <v>25130</v>
       </c>
       <c r="FZ18" t="n">
-        <v>25428.610719376</v>
+        <v>25444</v>
       </c>
       <c r="GA18" t="n">
-        <v>25725.445699039</v>
+        <v>25674</v>
       </c>
       <c r="GB18" t="n">
-        <v>26008.4022944315</v>
+        <v>26114</v>
       </c>
       <c r="GC18" t="n">
-        <v>26304.9627961952</v>
+        <v>26415.6169173493</v>
       </c>
       <c r="GD18" t="n">
-        <v>26589.002462567</v>
+        <v>26545.6319008916</v>
       </c>
       <c r="GE18" t="n">
-        <v>26879.1800243095</v>
+        <v>26811.7021522808</v>
       </c>
       <c r="GF18" t="n">
-        <v>27168.4807357025</v>
+        <v>27123.753736279</v>
       </c>
       <c r="GG18" t="n">
-        <v>27472.3387569935</v>
+        <v>27512.2954823832</v>
       </c>
       <c r="GH18" t="n">
-        <v>27783.2584411024</v>
+        <v>27892.5580172674</v>
       </c>
       <c r="GI18" t="n">
-        <v>28090.8941616397</v>
+        <v>28274.062501718</v>
       </c>
       <c r="GJ18" t="n">
-        <v>28401.0339524814</v>
+        <v>28657.8806859865</v>
       </c>
       <c r="GK18" t="n">
-        <v>28700.0863361499</v>
+        <v>29033.5125787946</v>
       </c>
       <c r="GL18" t="n">
-        <v>29000.081426174</v>
+        <v>29407.0782705767</v>
       </c>
       <c r="GM18" t="n">
-        <v>29297.8291655367</v>
+        <v>29775.6384747486</v>
       </c>
       <c r="GN18" t="n">
-        <v>29609.8685495542</v>
+        <v>30144.6426493512</v>
       </c>
       <c r="GO18" t="n">
-        <v>29894.8097083675</v>
+        <v>30489.5265744513</v>
       </c>
       <c r="GP18" t="n">
-        <v>30179.1869068894</v>
+        <v>30826.5888987611</v>
       </c>
       <c r="GQ18" t="n">
-        <v>30463.1427529336</v>
+        <v>31160.2782789414</v>
       </c>
       <c r="GR18" t="n">
-        <v>30739.0378471745</v>
+        <v>31483.4007852103</v>
       </c>
       <c r="GS18" t="n">
-        <v>31018.8791408324</v>
+        <v>31805.6179555175</v>
       </c>
       <c r="GT18" t="n">
-        <v>31297.1503707654</v>
+        <v>32122.8117266421</v>
       </c>
       <c r="GU18" t="n">
-        <v>31581.3610914426</v>
+        <v>32440.6005204012</v>
       </c>
       <c r="GV18" t="n">
-        <v>31859.5712406884</v>
+        <v>32750.6354804978</v>
       </c>
       <c r="GW18" t="n">
-        <v>32141.3612137549</v>
+        <v>33059.7850313389</v>
       </c>
       <c r="GX18" t="n">
-        <v>32423.8128568776</v>
+        <v>33366.9000682279</v>
       </c>
       <c r="GY18" t="n">
-        <v>32711.1969303773</v>
+        <v>33675.740869753</v>
       </c>
       <c r="GZ18" t="n">
-        <v>32995.2053205049</v>
+        <v>33980.5292790159</v>
       </c>
       <c r="HA18" t="n">
-        <v>33284.3272636924</v>
+        <v>34288.793911643</v>
       </c>
       <c r="HB18" t="n">
-        <v>33574.8859216124</v>
+        <v>34598.2043040145</v>
       </c>
       <c r="HC18" t="n">
-        <v>33876.2283184817</v>
+        <v>34916.2007337387</v>
       </c>
       <c r="HD18" t="n">
-        <v>34166.0259537175</v>
+        <v>35226.4862350193</v>
       </c>
       <c r="HE18" t="n">
-        <v>34468.4060067217</v>
+        <v>35547.2459297503</v>
       </c>
       <c r="HF18" t="n">
-        <v>34770.704364306</v>
+        <v>35869.7827049842</v>
       </c>
       <c r="HG18" t="n">
-        <v>35079.48880468</v>
+        <v>36198.7961744808</v>
       </c>
       <c r="HH18" t="n">
-        <v>35386.7419326216</v>
+        <v>36528.3056958398</v>
       </c>
       <c r="HI18" t="n">
-        <v>35696.8369879974</v>
+        <v>36861.7186895341</v>
       </c>
       <c r="HJ18" t="n">
-        <v>36010.3645919842</v>
+        <v>37199.5750981687</v>
       </c>
       <c r="HK18" t="n">
-        <v>36329.8460727799</v>
+        <v>37543.8974677047</v>
       </c>
       <c r="HL18" t="n">
-        <v>36646.8949896022</v>
+        <v>37888.0463811786</v>
       </c>
       <c r="HM18" t="n">
-        <v>36968.3896649248</v>
+        <v>38237.5478034141</v>
       </c>
       <c r="HN18" t="n">
-        <v>37292.8060097412</v>
+        <v>38591.1518921627</v>
       </c>
       <c r="HO18" t="n">
-        <v>37623.4430982782</v>
+        <v>38951.3048385788</v>
       </c>
       <c r="HP18" t="n">
-        <v>37952.8348153432</v>
+        <v>39312.2681794222</v>
       </c>
       <c r="HQ18" t="n">
-        <v>38282.9812985102</v>
+        <v>39675.0792946149</v>
       </c>
       <c r="HR18" t="n">
-        <v>38616.1575680126</v>
+        <v>40041.6745591154</v>
       </c>
       <c r="HS18" t="n">
-        <v>38960.8497692361</v>
+        <v>40418.2737270209</v>
       </c>
       <c r="HT18" t="n">
-        <v>39288.1770915736</v>
+        <v>40783.4519320773</v>
       </c>
       <c r="HU18" t="n">
-        <v>39626.5356062706</v>
+        <v>41157.0410353487</v>
       </c>
     </row>
     <row r="19">
@@ -14250,148 +14238,148 @@
         <v>14473.697393</v>
       </c>
       <c r="FZ19" t="n">
-        <v>14584.999574711</v>
+        <v>14503.3755150333</v>
       </c>
       <c r="GA19" t="n">
-        <v>14687.2577686923</v>
+        <v>14589.9722275667</v>
       </c>
       <c r="GB19" t="n">
-        <v>14752.8573612502</v>
+        <v>14608.7589597667</v>
       </c>
       <c r="GC19" t="n">
-        <v>14813.1402780935</v>
+        <v>14660.3950488162</v>
       </c>
       <c r="GD19" t="n">
-        <v>14877.1973303458</v>
+        <v>14722.7882826688</v>
       </c>
       <c r="GE19" t="n">
-        <v>14942.6348786702</v>
+        <v>14830.0545137079</v>
       </c>
       <c r="GF19" t="n">
-        <v>15006.3003515153</v>
+        <v>14955.6989196308</v>
       </c>
       <c r="GG19" t="n">
-        <v>15069.5372193607</v>
+        <v>15063.7168242669</v>
       </c>
       <c r="GH19" t="n">
-        <v>15127.5358072883</v>
+        <v>15155.4470116612</v>
       </c>
       <c r="GI19" t="n">
-        <v>15181.3954571645</v>
+        <v>15232.2590334466</v>
       </c>
       <c r="GJ19" t="n">
-        <v>15225.4228374055</v>
+        <v>15292.6703916153</v>
       </c>
       <c r="GK19" t="n">
-        <v>15267.9461756248</v>
+        <v>15344.8892364035</v>
       </c>
       <c r="GL19" t="n">
-        <v>15309.7658461772</v>
+        <v>15391.1973804989</v>
       </c>
       <c r="GM19" t="n">
-        <v>15352.8538991259</v>
+        <v>15432.4035666243</v>
       </c>
       <c r="GN19" t="n">
-        <v>15382.8414478653</v>
+        <v>15460.9833278645</v>
       </c>
       <c r="GO19" t="n">
-        <v>15411.9466617547</v>
+        <v>15486.6106031578</v>
       </c>
       <c r="GP19" t="n">
-        <v>15441.8247629023</v>
+        <v>15512.0220426587</v>
       </c>
       <c r="GQ19" t="n">
-        <v>15470.5948169616</v>
+        <v>15535.7189821885</v>
       </c>
       <c r="GR19" t="n">
-        <v>15500.8253365974</v>
+        <v>15559.5018382907</v>
       </c>
       <c r="GS19" t="n">
-        <v>15533.2268667754</v>
+        <v>15584.3499649709</v>
       </c>
       <c r="GT19" t="n">
-        <v>15568.3564698186</v>
+        <v>15610.8400989514</v>
       </c>
       <c r="GU19" t="n">
-        <v>15602.6266129602</v>
+        <v>15636.5158373773</v>
       </c>
       <c r="GV19" t="n">
-        <v>15639.5046869279</v>
+        <v>15664.1701854255</v>
       </c>
       <c r="GW19" t="n">
-        <v>15678.0679494142</v>
+        <v>15693.5807587928</v>
       </c>
       <c r="GX19" t="n">
-        <v>15718.7616019257</v>
+        <v>15725.4495931215</v>
       </c>
       <c r="GY19" t="n">
-        <v>15759.3115612654</v>
+        <v>15758.3525516107</v>
       </c>
       <c r="GZ19" t="n">
-        <v>15800.8388898375</v>
+        <v>15793.0951799754</v>
       </c>
       <c r="HA19" t="n">
-        <v>15844.1543616334</v>
+        <v>15830.7599956591</v>
       </c>
       <c r="HB19" t="n">
-        <v>15890.0810160059</v>
+        <v>15871.9427330168</v>
       </c>
       <c r="HC19" t="n">
-        <v>15932.7996136155</v>
+        <v>15912.2207039045</v>
       </c>
       <c r="HD19" t="n">
-        <v>15978.4233598879</v>
+        <v>15955.6907680824</v>
       </c>
       <c r="HE19" t="n">
-        <v>16024.4027895356</v>
+        <v>16000.7248109194</v>
       </c>
       <c r="HF19" t="n">
-        <v>16071.4476788532</v>
+        <v>16047.5521666464</v>
       </c>
       <c r="HG19" t="n">
-        <v>16117.3020025781</v>
+        <v>16094.2488340664</v>
       </c>
       <c r="HH19" t="n">
-        <v>16162.9446989985</v>
+        <v>16141.2297831363</v>
       </c>
       <c r="HI19" t="n">
-        <v>16209.3992786704</v>
+        <v>16189.3058352382</v>
       </c>
       <c r="HJ19" t="n">
-        <v>16256.6581124714</v>
+        <v>16238.3431742982</v>
       </c>
       <c r="HK19" t="n">
-        <v>16302.3809167292</v>
+        <v>16286.4002769119</v>
       </c>
       <c r="HL19" t="n">
-        <v>16347.5932303249</v>
+        <v>16333.915578992</v>
       </c>
       <c r="HM19" t="n">
-        <v>16393.3796987277</v>
+        <v>16381.9065052165</v>
       </c>
       <c r="HN19" t="n">
-        <v>16439.7024354948</v>
+        <v>16430.2385645666</v>
       </c>
       <c r="HO19" t="n">
-        <v>16484.1865440316</v>
+        <v>16477.0057305422</v>
       </c>
       <c r="HP19" t="n">
-        <v>16528.0189785387</v>
+        <v>16522.9616970224</v>
       </c>
       <c r="HQ19" t="n">
-        <v>16572.2716951998</v>
+        <v>16568.9524240839</v>
       </c>
       <c r="HR19" t="n">
-        <v>16617.0142518489</v>
+        <v>16615.0172105473</v>
       </c>
       <c r="HS19" t="n">
-        <v>16655.3026282284</v>
+        <v>16655.9320671393</v>
       </c>
       <c r="HT19" t="n">
-        <v>16695.6380575897</v>
+        <v>16697.6572733749</v>
       </c>
       <c r="HU19" t="n">
-        <v>16734.9941979838</v>
+        <v>16738.3352329029</v>
       </c>
     </row>
     <row r="20">
@@ -14939,148 +14927,148 @@
         <v>0.670117</v>
       </c>
       <c r="FZ20" t="n">
-        <v>0.669951756248767</v>
+        <v>0.668511013333333</v>
       </c>
       <c r="GA20" t="n">
-        <v>0.669799231562062</v>
+        <v>0.670083922</v>
       </c>
       <c r="GB20" t="n">
-        <v>0.669539090710189</v>
+        <v>0.669101939</v>
       </c>
       <c r="GC20" t="n">
-        <v>0.669394561974283</v>
+        <v>0.668738884891616</v>
       </c>
       <c r="GD20" t="n">
-        <v>0.669369702640581</v>
+        <v>0.668104349144647</v>
       </c>
       <c r="GE20" t="n">
-        <v>0.669436768632958</v>
+        <v>0.668180977843649</v>
       </c>
       <c r="GF20" t="n">
-        <v>0.669552716442287</v>
+        <v>0.668722682001945</v>
       </c>
       <c r="GG20" t="n">
-        <v>0.669720345206143</v>
+        <v>0.669619386691245</v>
       </c>
       <c r="GH20" t="n">
-        <v>0.669882716226483</v>
+        <v>0.670359521745614</v>
       </c>
       <c r="GI20" t="n">
-        <v>0.669973160287017</v>
+        <v>0.670821639131195</v>
       </c>
       <c r="GJ20" t="n">
-        <v>0.669998136675722</v>
+        <v>0.671108643900959</v>
       </c>
       <c r="GK20" t="n">
-        <v>0.669929001299299</v>
+        <v>0.671228037497873</v>
       </c>
       <c r="GL20" t="n">
-        <v>0.669828761118828</v>
+        <v>0.671261426590887</v>
       </c>
       <c r="GM20" t="n">
-        <v>0.669709863447765</v>
+        <v>0.671200101340799</v>
       </c>
       <c r="GN20" t="n">
-        <v>0.669572118538407</v>
+        <v>0.671041247386026</v>
       </c>
       <c r="GO20" t="n">
-        <v>0.669304951483236</v>
+        <v>0.670742546189251</v>
       </c>
       <c r="GP20" t="n">
-        <v>0.669011292804413</v>
+        <v>0.670386750691926</v>
       </c>
       <c r="GQ20" t="n">
-        <v>0.668705623544291</v>
+        <v>0.670004498602766</v>
       </c>
       <c r="GR20" t="n">
-        <v>0.668383991565772</v>
+        <v>0.669599080456645</v>
       </c>
       <c r="GS20" t="n">
-        <v>0.668103764190531</v>
+        <v>0.669212240065775</v>
       </c>
       <c r="GT20" t="n">
-        <v>0.667837645377789</v>
+        <v>0.668828755252668</v>
       </c>
       <c r="GU20" t="n">
-        <v>0.667597436162315</v>
+        <v>0.66845774282884</v>
       </c>
       <c r="GV20" t="n">
-        <v>0.667355915820956</v>
+        <v>0.668085222283685</v>
       </c>
       <c r="GW20" t="n">
-        <v>0.667138583256789</v>
+        <v>0.667731470822169</v>
       </c>
       <c r="GX20" t="n">
-        <v>0.666943300653046</v>
+        <v>0.667401837419328</v>
       </c>
       <c r="GY20" t="n">
-        <v>0.666770982346455</v>
+        <v>0.667101122871593</v>
       </c>
       <c r="GZ20" t="n">
-        <v>0.666607971341531</v>
+        <v>0.666824116592973</v>
       </c>
       <c r="HA20" t="n">
-        <v>0.666474297007358</v>
+        <v>0.666589588616054</v>
       </c>
       <c r="HB20" t="n">
-        <v>0.666364843252076</v>
+        <v>0.666395098490258</v>
       </c>
       <c r="HC20" t="n">
-        <v>0.666279822177756</v>
+        <v>0.666240004665862</v>
       </c>
       <c r="HD20" t="n">
-        <v>0.666177363827818</v>
+        <v>0.666094799855863</v>
       </c>
       <c r="HE20" t="n">
-        <v>0.666115577069368</v>
+        <v>0.665998594136542</v>
       </c>
       <c r="HF20" t="n">
-        <v>0.666061290594567</v>
+        <v>0.665927411620081</v>
       </c>
       <c r="HG20" t="n">
-        <v>0.66601920734667</v>
+        <v>0.665880281646713</v>
       </c>
       <c r="HH20" t="n">
-        <v>0.665973769928464</v>
+        <v>0.665843438494312</v>
       </c>
       <c r="HI20" t="n">
-        <v>0.665930724122717</v>
+        <v>0.665818544737377</v>
       </c>
       <c r="HJ20" t="n">
-        <v>0.665899541495939</v>
+        <v>0.665810471424564</v>
       </c>
       <c r="HK20" t="n">
-        <v>0.665874439670637</v>
+        <v>0.665812802917293</v>
       </c>
       <c r="HL20" t="n">
-        <v>0.665839995977804</v>
+        <v>0.665812421915824</v>
       </c>
       <c r="HM20" t="n">
-        <v>0.665813557273051</v>
+        <v>0.665820838397558</v>
       </c>
       <c r="HN20" t="n">
-        <v>0.665792725688036</v>
+        <v>0.665834747090709</v>
       </c>
       <c r="HO20" t="n">
-        <v>0.665775515517613</v>
+        <v>0.665850766949961</v>
       </c>
       <c r="HP20" t="n">
-        <v>0.665743523968919</v>
+        <v>0.66585404150585</v>
       </c>
       <c r="HQ20" t="n">
-        <v>0.665703777863118</v>
+        <v>0.665847716940437</v>
       </c>
       <c r="HR20" t="n">
-        <v>0.665667042298681</v>
+        <v>0.665840006598921</v>
       </c>
       <c r="HS20" t="n">
-        <v>0.665625618452987</v>
+        <v>0.665823912377123</v>
       </c>
       <c r="HT20" t="n">
-        <v>0.66553159889491</v>
+        <v>0.665765351057625</v>
       </c>
       <c r="HU20" t="n">
-        <v>0.66545176922196</v>
+        <v>0.665708719802019</v>
       </c>
     </row>
     <row r="21">
@@ -15628,148 +15616,148 @@
         <v>0.0401043172136999</v>
       </c>
       <c r="FZ21" t="n">
-        <v>0.0392687294678991</v>
+        <v>0.040946291793016</v>
       </c>
       <c r="GA21" t="n">
-        <v>0.0390740674259115</v>
+        <v>0.0415799332516735</v>
       </c>
       <c r="GB21" t="n">
-        <v>0.0385981525179423</v>
+        <v>0.0430614370315685</v>
       </c>
       <c r="GC21" t="n">
-        <v>0.0386392866724199</v>
+        <v>0.0476194964539835</v>
       </c>
       <c r="GD21" t="n">
-        <v>0.0386115994873672</v>
+        <v>0.0467878396010844</v>
       </c>
       <c r="GE21" t="n">
-        <v>0.0386323521850818</v>
+        <v>0.044082262953602</v>
       </c>
       <c r="GF21" t="n">
-        <v>0.0384063852631822</v>
+        <v>0.0404593632002649</v>
       </c>
       <c r="GG21" t="n">
-        <v>0.0382893797724542</v>
+        <v>0.0385158869070906</v>
       </c>
       <c r="GH21" t="n">
-        <v>0.0385048442483449</v>
+        <v>0.0374159735004161</v>
       </c>
       <c r="GI21" t="n">
-        <v>0.0388834447648027</v>
+        <v>0.036883060289665</v>
       </c>
       <c r="GJ21" t="n">
-        <v>0.0396166089239728</v>
+        <v>0.0369709958530386</v>
       </c>
       <c r="GK21" t="n">
-        <v>0.0403081846741093</v>
+        <v>0.0373384691789247</v>
       </c>
       <c r="GL21" t="n">
-        <v>0.0409975119476579</v>
+        <v>0.037954324645462</v>
       </c>
       <c r="GM21" t="n">
-        <v>0.0415789260786963</v>
+        <v>0.0387519106339942</v>
       </c>
       <c r="GN21" t="n">
-        <v>0.0428983231576381</v>
+        <v>0.0401424861602343</v>
       </c>
       <c r="GO21" t="n">
-        <v>0.0440806742693279</v>
+        <v>0.0415084144418024</v>
       </c>
       <c r="GP21" t="n">
-        <v>0.0451705521932834</v>
+        <v>0.0427979424136913</v>
       </c>
       <c r="GQ21" t="n">
-        <v>0.0463051404752305</v>
+        <v>0.0441471423578482</v>
       </c>
       <c r="GR21" t="n">
-        <v>0.0472010800355525</v>
+        <v>0.0453299188655787</v>
       </c>
       <c r="GS21" t="n">
-        <v>0.0480169615273496</v>
+        <v>0.0464658313558459</v>
       </c>
       <c r="GT21" t="n">
-        <v>0.0486810094753953</v>
+        <v>0.0474985757445043</v>
       </c>
       <c r="GU21" t="n">
-        <v>0.0494300962784344</v>
+        <v>0.0485914823576374</v>
       </c>
       <c r="GV21" t="n">
-        <v>0.050026132192193</v>
+        <v>0.0495665641743774</v>
       </c>
       <c r="GW21" t="n">
-        <v>0.0505506418945779</v>
+        <v>0.050455063225831</v>
       </c>
       <c r="GX21" t="n">
-        <v>0.0509746324325546</v>
+        <v>0.051223145577907</v>
       </c>
       <c r="GY21" t="n">
-        <v>0.0514374644007083</v>
+        <v>0.0519645913894242</v>
       </c>
       <c r="GZ21" t="n">
-        <v>0.0517451222948922</v>
+        <v>0.0525170626803358</v>
       </c>
       <c r="HA21" t="n">
-        <v>0.0519852566698578</v>
+        <v>0.0529505185485808</v>
       </c>
       <c r="HB21" t="n">
-        <v>0.0521024621132365</v>
+        <v>0.0532274588080092</v>
       </c>
       <c r="HC21" t="n">
-        <v>0.0524445443714409</v>
+        <v>0.0536118552349334</v>
       </c>
       <c r="HD21" t="n">
-        <v>0.0525049437757247</v>
+        <v>0.053735672619993</v>
       </c>
       <c r="HE21" t="n">
-        <v>0.052601505619043</v>
+        <v>0.0538352345582879</v>
       </c>
       <c r="HF21" t="n">
-        <v>0.0526454053610854</v>
+        <v>0.05386378587845</v>
       </c>
       <c r="HG21" t="n">
-        <v>0.0527764855406062</v>
+        <v>0.0539339922243921</v>
       </c>
       <c r="HH21" t="n">
-        <v>0.0528705356449133</v>
+        <v>0.0539578626525296</v>
       </c>
       <c r="HI21" t="n">
-        <v>0.0529200051367122</v>
+        <v>0.0539346510063354</v>
       </c>
       <c r="HJ21" t="n">
-        <v>0.0529392274876428</v>
+        <v>0.0538796439172522</v>
       </c>
       <c r="HK21" t="n">
-        <v>0.0530563312484757</v>
+        <v>0.0538970085865502</v>
       </c>
       <c r="HL21" t="n">
-        <v>0.0531085885987919</v>
+        <v>0.0538616478097304</v>
       </c>
       <c r="HM21" t="n">
-        <v>0.0531384736833085</v>
+        <v>0.0538114975809192</v>
       </c>
       <c r="HN21" t="n">
-        <v>0.0531450444081242</v>
+        <v>0.0537498430797217</v>
       </c>
       <c r="HO21" t="n">
-        <v>0.0532621385210844</v>
+        <v>0.0537815029340418</v>
       </c>
       <c r="HP21" t="n">
-        <v>0.0533981660114532</v>
+        <v>0.0538448752008098</v>
       </c>
       <c r="HQ21" t="n">
-        <v>0.0534982085787796</v>
+        <v>0.0538923510487717</v>
       </c>
       <c r="HR21" t="n">
-        <v>0.0535738195143452</v>
+        <v>0.0539333824455213</v>
       </c>
       <c r="HS21" t="n">
-        <v>0.0540086988765067</v>
+        <v>0.0542546893041514</v>
       </c>
       <c r="HT21" t="n">
-        <v>0.0542395005412845</v>
+        <v>0.0544572157832091</v>
       </c>
       <c r="HU21" t="n">
-        <v>0.0545438200964858</v>
+        <v>0.0547200644284365</v>
       </c>
     </row>
     <row r="22">
@@ -16317,148 +16305,148 @@
         <v>604.7092</v>
       </c>
       <c r="FZ22" t="n">
-        <v>596.144308663288</v>
+        <v>619.213961366667</v>
       </c>
       <c r="GA22" t="n">
-        <v>597.227086003642</v>
+        <v>632.968874933333</v>
       </c>
       <c r="GB22" t="n">
-        <v>592.294609981183</v>
+        <v>657.3819662</v>
       </c>
       <c r="GC22" t="n">
-        <v>595.374101171092</v>
+        <v>733.026573007064</v>
       </c>
       <c r="GD22" t="n">
-        <v>597.503037015636</v>
+        <v>722.659242606804</v>
       </c>
       <c r="GE22" t="n">
-        <v>600.466685358406</v>
+        <v>683.889877162612</v>
       </c>
       <c r="GF22" t="n">
-        <v>599.357000870745</v>
+        <v>630.612333861736</v>
       </c>
       <c r="GG22" t="n">
-        <v>599.97605625598</v>
+        <v>603.434314973267</v>
       </c>
       <c r="GH22" t="n">
-        <v>605.810154462473</v>
+        <v>589.097546511361</v>
       </c>
       <c r="GI22" t="n">
-        <v>614.18676833232</v>
+        <v>583.327302877726</v>
       </c>
       <c r="GJ22" t="n">
-        <v>628.061409495735</v>
+        <v>587.090657918128</v>
       </c>
       <c r="GK22" t="n">
-        <v>641.271824816058</v>
+        <v>595.177779430764</v>
       </c>
       <c r="GL22" t="n">
-        <v>654.495109466568</v>
+        <v>607.208787751015</v>
       </c>
       <c r="GM22" t="n">
-        <v>666.04891506049</v>
+        <v>622.144498261514</v>
       </c>
       <c r="GN22" t="n">
-        <v>689.475587653737</v>
+        <v>646.598474437968</v>
       </c>
       <c r="GO22" t="n">
-        <v>710.697152589149</v>
+        <v>670.662907773753</v>
       </c>
       <c r="GP22" t="n">
-        <v>730.513598754625</v>
+        <v>693.565937649377</v>
       </c>
       <c r="GQ22" t="n">
-        <v>751.150333605463</v>
+        <v>717.534831442272</v>
       </c>
       <c r="GR22" t="n">
-        <v>767.901627322743</v>
+        <v>738.800863007898</v>
       </c>
       <c r="GS22" t="n">
-        <v>783.478767288771</v>
+        <v>759.427324019127</v>
       </c>
       <c r="GT22" t="n">
-        <v>796.665955583236</v>
+        <v>778.468970727867</v>
       </c>
       <c r="GU22" t="n">
-        <v>811.344300865389</v>
+        <v>798.607117837913</v>
       </c>
       <c r="GV22" t="n">
-        <v>823.584831847487</v>
+        <v>816.91068893374</v>
       </c>
       <c r="GW22" t="n">
-        <v>834.732810053141</v>
+        <v>833.894963996427</v>
       </c>
       <c r="GX22" t="n">
-        <v>844.295899942241</v>
+        <v>848.995339760775</v>
       </c>
       <c r="GY22" t="n">
-        <v>854.576401556958</v>
+        <v>863.761500591401</v>
       </c>
       <c r="GZ22" t="n">
-        <v>862.232812283884</v>
+        <v>875.379463571448</v>
       </c>
       <c r="HA22" t="n">
-        <v>868.828849435573</v>
+        <v>885.114349740386</v>
       </c>
       <c r="HB22" t="n">
-        <v>873.419791274726</v>
+        <v>892.319194414271</v>
       </c>
       <c r="HC22" t="n">
-        <v>881.836028766425</v>
+        <v>901.410079959503</v>
       </c>
       <c r="HD22" t="n">
-        <v>885.436121626462</v>
+        <v>906.078658595346</v>
       </c>
       <c r="HE22" t="n">
-        <v>889.707808996176</v>
+        <v>910.415338741263</v>
       </c>
       <c r="HF22" t="n">
-        <v>893.10593100058</v>
+        <v>913.591551247002</v>
       </c>
       <c r="HG22" t="n">
-        <v>898.008410718092</v>
+        <v>917.512336380496</v>
       </c>
       <c r="HH22" t="n">
-        <v>902.245898124447</v>
+        <v>920.621146772999</v>
       </c>
       <c r="HI22" t="n">
-        <v>905.733016196533</v>
+        <v>922.94332937014</v>
       </c>
       <c r="HJ22" t="n">
-        <v>908.722098167877</v>
+        <v>924.741011872959</v>
       </c>
       <c r="HK22" t="n">
-        <v>913.40665516809</v>
+        <v>927.793713389539</v>
       </c>
       <c r="HL22" t="n">
-        <v>916.892606640566</v>
+        <v>929.855293409313</v>
       </c>
       <c r="HM22" t="n">
-        <v>920.007082775115</v>
+        <v>931.669609956982</v>
       </c>
       <c r="HN22" t="n">
-        <v>922.727227367017</v>
+        <v>933.286925299679</v>
       </c>
       <c r="HO22" t="n">
-        <v>927.377259040455</v>
+        <v>936.52607087919</v>
       </c>
       <c r="HP22" t="n">
-        <v>932.351915915111</v>
+        <v>940.307726843483</v>
       </c>
       <c r="HQ22" t="n">
-        <v>936.698685486943</v>
+        <v>943.803762129566</v>
       </c>
       <c r="HR22" t="n">
-        <v>940.630215343965</v>
+        <v>947.189365772498</v>
       </c>
       <c r="HS22" t="n">
-        <v>950.887560667627</v>
+        <v>955.503113002327</v>
       </c>
       <c r="HT22" t="n">
-        <v>957.497389124837</v>
+        <v>961.67841777013</v>
       </c>
       <c r="HU22" t="n">
-        <v>965.449978737008</v>
+        <v>968.943608039826</v>
       </c>
     </row>
     <row r="23">
@@ -17006,148 +16994,148 @@
         <v>0.044233</v>
       </c>
       <c r="FZ23" t="n">
-        <v>0.0437782648188369</v>
+        <v>0.0420666666666667</v>
       </c>
       <c r="GA23" t="n">
-        <v>0.0386090978853748</v>
+        <v>0.0383</v>
       </c>
       <c r="GB23" t="n">
-        <v>0.0372744417276959</v>
+        <v>0.0362333333333333</v>
       </c>
       <c r="GC23" t="n">
-        <v>0.0368362461908914</v>
+        <v>0.0314324768579786</v>
       </c>
       <c r="GD23" t="n">
-        <v>0.0386649324962645</v>
+        <v>0.0348543638906952</v>
       </c>
       <c r="GE23" t="n">
-        <v>0.0419154055477493</v>
+        <v>0.0436972390686142</v>
       </c>
       <c r="GF23" t="n">
-        <v>0.0464019111382157</v>
+        <v>0.0537096185593085</v>
       </c>
       <c r="GG23" t="n">
-        <v>0.051166793547428</v>
+        <v>0.0621418743937844</v>
       </c>
       <c r="GH23" t="n">
-        <v>0.0553220581492405</v>
+        <v>0.0693982950866891</v>
       </c>
       <c r="GI23" t="n">
-        <v>0.0588790736887421</v>
+        <v>0.0751266995945514</v>
       </c>
       <c r="GJ23" t="n">
-        <v>0.061330349349501</v>
+        <v>0.0789270555252945</v>
       </c>
       <c r="GK23" t="n">
-        <v>0.0632243535815134</v>
+        <v>0.0813311499510839</v>
       </c>
       <c r="GL23" t="n">
-        <v>0.0645712674355491</v>
+        <v>0.0823529045752757</v>
       </c>
       <c r="GM23" t="n">
-        <v>0.0655766001224467</v>
+        <v>0.0820389443938099</v>
       </c>
       <c r="GN23" t="n">
-        <v>0.0648592762524967</v>
+        <v>0.0798310352026281</v>
       </c>
       <c r="GO23" t="n">
-        <v>0.0638022081441815</v>
+        <v>0.0768451048619875</v>
       </c>
       <c r="GP23" t="n">
-        <v>0.0624341553319498</v>
+        <v>0.0733860711481737</v>
       </c>
       <c r="GQ23" t="n">
-        <v>0.0605866391446929</v>
+        <v>0.0694736632836268</v>
       </c>
       <c r="GR23" t="n">
-        <v>0.0589412696578986</v>
+        <v>0.0656528789725724</v>
       </c>
       <c r="GS23" t="n">
-        <v>0.0573000265577333</v>
+        <v>0.0618334384477611</v>
       </c>
       <c r="GT23" t="n">
-        <v>0.0558435594072501</v>
+        <v>0.0581863589962903</v>
       </c>
       <c r="GU23" t="n">
-        <v>0.05423350340282</v>
+        <v>0.0545136734386255</v>
       </c>
       <c r="GV23" t="n">
-        <v>0.0528393344740737</v>
+        <v>0.0511090815793214</v>
       </c>
       <c r="GW23" t="n">
-        <v>0.051561459905307</v>
+        <v>0.0479649970324944</v>
       </c>
       <c r="GX23" t="n">
-        <v>0.0504456422903688</v>
+        <v>0.0451527663040569</v>
       </c>
       <c r="GY23" t="n">
-        <v>0.0492826471078849</v>
+        <v>0.0425472301887731</v>
       </c>
       <c r="GZ23" t="n">
-        <v>0.0483696869482906</v>
+        <v>0.0404121247134287</v>
       </c>
       <c r="HA23" t="n">
-        <v>0.0475814269913548</v>
+        <v>0.0386536812384047</v>
       </c>
       <c r="HB23" t="n">
-        <v>0.0470132169394001</v>
+        <v>0.0373387037918807</v>
       </c>
       <c r="HC23" t="n">
-        <v>0.0461039414526211</v>
+        <v>0.0360408506936373</v>
       </c>
       <c r="HD23" t="n">
-        <v>0.0456472101824892</v>
+        <v>0.0353261163169835</v>
       </c>
       <c r="HE23" t="n">
-        <v>0.0451606998827933</v>
+        <v>0.03482595342113</v>
       </c>
       <c r="HF23" t="n">
-        <v>0.0447739661669404</v>
+        <v>0.034592153634563</v>
       </c>
       <c r="HG23" t="n">
-        <v>0.0442806643699795</v>
+        <v>0.0344378672927621</v>
       </c>
       <c r="HH23" t="n">
-        <v>0.0438380316716759</v>
+        <v>0.0344556990227998</v>
       </c>
       <c r="HI23" t="n">
-        <v>0.043477890187448</v>
+        <v>0.0346415120396794</v>
       </c>
       <c r="HJ23" t="n">
-        <v>0.0431747075029965</v>
+        <v>0.0349519298951971</v>
       </c>
       <c r="HK23" t="n">
-        <v>0.0427246308681462</v>
+        <v>0.0352042283943284</v>
       </c>
       <c r="HL23" t="n">
-        <v>0.0423779785256065</v>
+        <v>0.0355763679184775</v>
       </c>
       <c r="HM23" t="n">
-        <v>0.0420729916826968</v>
+        <v>0.0359992234833284</v>
       </c>
       <c r="HN23" t="n">
-        <v>0.0418126783413797</v>
+        <v>0.0364566357147273</v>
       </c>
       <c r="HO23" t="n">
-        <v>0.0413825638971479</v>
+        <v>0.0367702256368655</v>
       </c>
       <c r="HP23" t="n">
-        <v>0.0409019747207556</v>
+        <v>0.0370068986073209</v>
       </c>
       <c r="HQ23" t="n">
-        <v>0.0404621986663455</v>
+        <v>0.0372373190343826</v>
       </c>
       <c r="HR23" t="n">
-        <v>0.0400503759692404</v>
+        <v>0.0374449678545547</v>
       </c>
       <c r="HS23" t="n">
-        <v>0.0390330876817905</v>
+        <v>0.0371537085540228</v>
       </c>
       <c r="HT23" t="n">
-        <v>0.0382913248424236</v>
+        <v>0.0369807857756109</v>
       </c>
       <c r="HU23" t="n">
-        <v>0.0373997546624957</v>
+        <v>0.0366500948994805</v>
       </c>
     </row>
     <row r="24">
@@ -17647,148 +17635,148 @@
         <v>0.0437466666666667</v>
       </c>
       <c r="FZ24" t="n">
-        <v>0.0436439237058131</v>
+        <v>0.0444166666666667</v>
       </c>
       <c r="GA24" t="n">
-        <v>0.0432359645697224</v>
+        <v>0.04275</v>
       </c>
       <c r="GB24" t="n">
-        <v>0.042775335038333</v>
+        <v>0.04288</v>
       </c>
       <c r="GC24" t="n">
-        <v>0.0423197968645285</v>
+        <v>0.0420196903969125</v>
       </c>
       <c r="GD24" t="n">
-        <v>0.0420059376465676</v>
+        <v>0.0414256897351744</v>
       </c>
       <c r="GE24" t="n">
-        <v>0.041909936212782</v>
+        <v>0.0414092127342414</v>
       </c>
       <c r="GF24" t="n">
-        <v>0.0420915308080125</v>
+        <v>0.0420020707591373</v>
       </c>
       <c r="GG24" t="n">
-        <v>0.0425485170090851</v>
+        <v>0.0430668842733689</v>
       </c>
       <c r="GH24" t="n">
-        <v>0.043225199985203</v>
+        <v>0.0445001651346085</v>
       </c>
       <c r="GI24" t="n">
-        <v>0.044070387784405</v>
+        <v>0.0461840615363322</v>
       </c>
       <c r="GJ24" t="n">
-        <v>0.0450057398435711</v>
+        <v>0.0479844269505533</v>
       </c>
       <c r="GK24" t="n">
-        <v>0.0459914149280081</v>
+        <v>0.0498085316966101</v>
       </c>
       <c r="GL24" t="n">
-        <v>0.0469909166727895</v>
+        <v>0.051570791009773</v>
       </c>
       <c r="GM24" t="n">
-        <v>0.0479826636648478</v>
+        <v>0.0531942662860947</v>
       </c>
       <c r="GN24" t="n">
-        <v>0.0488631260349396</v>
+        <v>0.05457333473799</v>
       </c>
       <c r="GO24" t="n">
-        <v>0.0496194057629149</v>
+        <v>0.0556773372114963</v>
       </c>
       <c r="GP24" t="n">
-        <v>0.0502412258695847</v>
+        <v>0.0564962199092162</v>
       </c>
       <c r="GQ24" t="n">
-        <v>0.0507088361788923</v>
+        <v>0.0570218104772714</v>
       </c>
       <c r="GR24" t="n">
-        <v>0.0510450140619169</v>
+        <v>0.0572795983513382</v>
       </c>
       <c r="GS24" t="n">
-        <v>0.0512590143266541</v>
+        <v>0.057287857275107</v>
       </c>
       <c r="GT24" t="n">
-        <v>0.0513703702275362</v>
+        <v>0.0570740083176781</v>
       </c>
       <c r="GU24" t="n">
-        <v>0.0513768368912261</v>
+        <v>0.0566515840187387</v>
       </c>
       <c r="GV24" t="n">
-        <v>0.051298642341798</v>
+        <v>0.0560510388360761</v>
       </c>
       <c r="GW24" t="n">
-        <v>0.0511486124733081</v>
+        <v>0.0553002975792943</v>
       </c>
       <c r="GX24" t="n">
-        <v>0.0509414587692223</v>
+        <v>0.0544297221382116</v>
       </c>
       <c r="GY24" t="n">
-        <v>0.050678245390711</v>
+        <v>0.0534600089205147</v>
       </c>
       <c r="GZ24" t="n">
-        <v>0.0503779174256857</v>
+        <v>0.0524264694122572</v>
       </c>
       <c r="HA24" t="n">
-        <v>0.0500505507230739</v>
+        <v>0.0513563202491445</v>
       </c>
       <c r="HB24" t="n">
-        <v>0.0497112905785479</v>
+        <v>0.0502789873150397</v>
       </c>
       <c r="HC24" t="n">
-        <v>0.0493403490341537</v>
+        <v>0.0491959988529505</v>
       </c>
       <c r="HD24" t="n">
-        <v>0.0489672338716038</v>
+        <v>0.0481431613953398</v>
       </c>
       <c r="HE24" t="n">
-        <v>0.048590295149898</v>
+        <v>0.0471314611922666</v>
       </c>
       <c r="HF24" t="n">
-        <v>0.0482158220978467</v>
+        <v>0.046174284339993</v>
       </c>
       <c r="HG24" t="n">
-        <v>0.0478372082703706</v>
+        <v>0.045272757164266</v>
       </c>
       <c r="HH24" t="n">
-        <v>0.0474577981756829</v>
+        <v>0.0444335548734587</v>
       </c>
       <c r="HI24" t="n">
-        <v>0.0470826294529621</v>
+        <v>0.0436626479274672</v>
       </c>
       <c r="HJ24" t="n">
-        <v>0.0467148522233547</v>
+        <v>0.0429629662448357</v>
       </c>
       <c r="HK24" t="n">
-        <v>0.0463450865509561</v>
+        <v>0.0423261408798465</v>
       </c>
       <c r="HL24" t="n">
-        <v>0.0459797162738858</v>
+        <v>0.0417551818453838</v>
       </c>
       <c r="HM24" t="n">
-        <v>0.0456209571312714</v>
+        <v>0.0412486955890567</v>
       </c>
       <c r="HN24" t="n">
-        <v>0.0452710547488647</v>
+        <v>0.040804401600579</v>
       </c>
       <c r="HO24" t="n">
-        <v>0.0449191450313133</v>
+        <v>0.0404093384115149</v>
       </c>
       <c r="HP24" t="n">
-        <v>0.044562316470472</v>
+        <v>0.0400554892970848</v>
       </c>
       <c r="HQ24" t="n">
-        <v>0.0442033715125667</v>
+        <v>0.0397396747233135</v>
       </c>
       <c r="HR24" t="n">
-        <v>0.0438441437595871</v>
+        <v>0.0394579276720809</v>
       </c>
       <c r="HS24" t="n">
-        <v>0.0434480779829274</v>
+        <v>0.0391776270432565</v>
       </c>
       <c r="HT24" t="n">
-        <v>0.0430343420435857</v>
+        <v>0.0389058630942309</v>
       </c>
       <c r="HU24" t="n">
-        <v>0.0425950972006611</v>
+        <v>0.0386324720800233</v>
       </c>
     </row>
     <row r="25">
@@ -18336,148 +18324,144 @@
         <v>0.415500131875166</v>
       </c>
       <c r="FZ25" t="n">
-        <v>0.416230692222928</v>
-      </c>
-      <c r="GA25" t="n">
-        <v>0.412546007985485</v>
-      </c>
-      <c r="GB25" t="n">
-        <v>0.412121882347438</v>
-      </c>
+        <v>0.403650882464745</v>
+      </c>
+      <c r="GA25"/>
+      <c r="GB25"/>
       <c r="GC25" t="n">
-        <v>0.40834997098803</v>
+        <v>0.411049170711751</v>
       </c>
       <c r="GD25" t="n">
-        <v>0.403984256031465</v>
+        <v>0.397475392828582</v>
       </c>
       <c r="GE25" t="n">
-        <v>0.40197490625217</v>
+        <v>0.386022578275659</v>
       </c>
       <c r="GF25" t="n">
-        <v>0.401772299398358</v>
+        <v>0.381485965594769</v>
       </c>
       <c r="GG25" t="n">
-        <v>0.40166613335857</v>
+        <v>0.379042923835335</v>
       </c>
       <c r="GH25" t="n">
-        <v>0.401288004778815</v>
+        <v>0.376917367879265</v>
       </c>
       <c r="GI25" t="n">
-        <v>0.399736039663008</v>
+        <v>0.374208320319648</v>
       </c>
       <c r="GJ25" t="n">
-        <v>0.396850864350697</v>
+        <v>0.370244093699359</v>
       </c>
       <c r="GK25" t="n">
-        <v>0.394004938251847</v>
+        <v>0.36795557090265</v>
       </c>
       <c r="GL25" t="n">
-        <v>0.391326409792432</v>
+        <v>0.367151901146304</v>
       </c>
       <c r="GM25" t="n">
-        <v>0.388842349244652</v>
+        <v>0.369995550387041</v>
       </c>
       <c r="GN25" t="n">
-        <v>0.386705003046884</v>
+        <v>0.368595293502731</v>
       </c>
       <c r="GO25" t="n">
-        <v>0.384695841645308</v>
+        <v>0.367830348067817</v>
       </c>
       <c r="GP25" t="n">
-        <v>0.382833986597607</v>
+        <v>0.367596036252939</v>
       </c>
       <c r="GQ25" t="n">
-        <v>0.381094133602241</v>
+        <v>0.367759644203277</v>
       </c>
       <c r="GR25" t="n">
-        <v>0.379360355688795</v>
+        <v>0.36800520832696</v>
       </c>
       <c r="GS25" t="n">
-        <v>0.377911322664567</v>
+        <v>0.368586790139145</v>
       </c>
       <c r="GT25" t="n">
-        <v>0.376712751883248</v>
+        <v>0.369393010015748</v>
       </c>
       <c r="GU25" t="n">
-        <v>0.375683181392215</v>
+        <v>0.370298925617966</v>
       </c>
       <c r="GV25" t="n">
-        <v>0.374732094931171</v>
+        <v>0.371168080576732</v>
       </c>
       <c r="GW25" t="n">
-        <v>0.373886929411068</v>
+        <v>0.371994397786668</v>
       </c>
       <c r="GX25" t="n">
-        <v>0.373106707596935</v>
+        <v>0.372708962202849</v>
       </c>
       <c r="GY25" t="n">
-        <v>0.372372639219318</v>
+        <v>0.373269126559153</v>
       </c>
       <c r="GZ25" t="n">
-        <v>0.37166373030796</v>
+        <v>0.373641919538927</v>
       </c>
       <c r="HA25" t="n">
-        <v>0.37095265287929</v>
+        <v>0.373789475208652</v>
       </c>
       <c r="HB25" t="n">
-        <v>0.370295999870135</v>
+        <v>0.373765520191825</v>
       </c>
       <c r="HC25" t="n">
-        <v>0.369662619712634</v>
+        <v>0.373547481510742</v>
       </c>
       <c r="HD25" t="n">
-        <v>0.369053239566586</v>
+        <v>0.373140250318404</v>
       </c>
       <c r="HE25" t="n">
-        <v>0.368419543993751</v>
+        <v>0.372519231715524</v>
       </c>
       <c r="HF25" t="n">
-        <v>0.367763131313332</v>
+        <v>0.371701281876149</v>
       </c>
       <c r="HG25" t="n">
-        <v>0.367097711128637</v>
+        <v>0.370720441871777</v>
       </c>
       <c r="HH25" t="n">
-        <v>0.366402401271334</v>
+        <v>0.369586712277114</v>
       </c>
       <c r="HI25" t="n">
-        <v>0.365714069333023</v>
+        <v>0.368355709684803</v>
       </c>
       <c r="HJ25" t="n">
-        <v>0.365023282421655</v>
+        <v>0.367046677099376</v>
       </c>
       <c r="HK25" t="n">
-        <v>0.364338626394369</v>
+        <v>0.365689194091352</v>
       </c>
       <c r="HL25" t="n">
-        <v>0.363641803206217</v>
+        <v>0.364287608461997</v>
       </c>
       <c r="HM25" t="n">
-        <v>0.362981986260834</v>
+        <v>0.362911547008825</v>
       </c>
       <c r="HN25" t="n">
-        <v>0.362357868581453</v>
+        <v>0.361576183771784</v>
       </c>
       <c r="HO25" t="n">
-        <v>0.361768076609797</v>
+        <v>0.360294100623796</v>
       </c>
       <c r="HP25" t="n">
-        <v>0.361206373085928</v>
+        <v>0.359071913341043</v>
       </c>
       <c r="HQ25" t="n">
-        <v>0.360676418360111</v>
+        <v>0.357922864001368</v>
       </c>
       <c r="HR25" t="n">
-        <v>0.360172809431291</v>
+        <v>0.356849621022097</v>
       </c>
       <c r="HS25" t="n">
-        <v>0.359712662599999</v>
+        <v>0.355876102374133</v>
       </c>
       <c r="HT25" t="n">
-        <v>0.359267839574877</v>
+        <v>0.354971615796481</v>
       </c>
       <c r="HU25" t="n">
-        <v>0.358845236197844</v>
+        <v>0.354154015039799</v>
       </c>
     </row>
     <row r="26">
@@ -19025,148 +19009,148 @@
         <v>0.643433</v>
       </c>
       <c r="FZ26" t="n">
-        <v>0.64136359850273</v>
+        <v>0.623966666666667</v>
       </c>
       <c r="GA26" t="n">
-        <v>0.633020579420639</v>
+        <v>0.646733333333333</v>
       </c>
       <c r="GB26" t="n">
-        <v>0.62981883469631</v>
+        <v>0.653633333333333</v>
       </c>
       <c r="GC26" t="n">
-        <v>0.62143845153343</v>
+        <v>0.667381241604625</v>
       </c>
       <c r="GD26" t="n">
-        <v>0.61201535686753</v>
+        <v>0.642170274514971</v>
       </c>
       <c r="GE26" t="n">
-        <v>0.606211394631547</v>
+        <v>0.62009041074678</v>
       </c>
       <c r="GF26" t="n">
-        <v>0.603185323632356</v>
+        <v>0.609831132315981</v>
       </c>
       <c r="GG26" t="n">
-        <v>0.600290507018584</v>
+        <v>0.602803360965677</v>
       </c>
       <c r="GH26" t="n">
-        <v>0.597004662096507</v>
+        <v>0.596416649053182</v>
       </c>
       <c r="GI26" t="n">
-        <v>0.591989359059251</v>
+        <v>0.589158251952803</v>
       </c>
       <c r="GJ26" t="n">
-        <v>0.584979633457004</v>
+        <v>0.579934085563705</v>
       </c>
       <c r="GK26" t="n">
-        <v>0.578093345618179</v>
+        <v>0.573472879254707</v>
       </c>
       <c r="GL26" t="n">
-        <v>0.571493577131532</v>
+        <v>0.569419165037289</v>
       </c>
       <c r="GM26" t="n">
-        <v>0.565260575646086</v>
+        <v>0.571203777211181</v>
       </c>
       <c r="GN26" t="n">
-        <v>0.559586238734993</v>
+        <v>0.566313023897683</v>
       </c>
       <c r="GO26" t="n">
-        <v>0.554171825818004</v>
+        <v>0.562478596182733</v>
       </c>
       <c r="GP26" t="n">
-        <v>0.549009895371885</v>
+        <v>0.559494335424508</v>
       </c>
       <c r="GQ26" t="n">
-        <v>0.544067508726748</v>
+        <v>0.557164408003792</v>
       </c>
       <c r="GR26" t="n">
-        <v>0.539178692571791</v>
+        <v>0.554998559407035</v>
       </c>
       <c r="GS26" t="n">
-        <v>0.534737746051517</v>
+        <v>0.553373424754604</v>
       </c>
       <c r="GT26" t="n">
-        <v>0.530678391461427</v>
+        <v>0.552101391916154</v>
       </c>
       <c r="GU26" t="n">
-        <v>0.526882685464675</v>
+        <v>0.550988631220378</v>
       </c>
       <c r="GV26" t="n">
-        <v>0.52323320387536</v>
+        <v>0.54984375016105</v>
       </c>
       <c r="GW26" t="n">
-        <v>0.519750700831493</v>
+        <v>0.548635500658005</v>
       </c>
       <c r="GX26" t="n">
-        <v>0.516370802840193</v>
+        <v>0.547257618354413</v>
       </c>
       <c r="GY26" t="n">
-        <v>0.513074595215352</v>
+        <v>0.545656237505498</v>
       </c>
       <c r="GZ26" t="n">
-        <v>0.509831614610079</v>
+        <v>0.54378325367761</v>
       </c>
       <c r="HA26" t="n">
-        <v>0.506601456641368</v>
+        <v>0.541582942342526</v>
       </c>
       <c r="HB26" t="n">
-        <v>0.503392835840062</v>
+        <v>0.539066959991254</v>
       </c>
       <c r="HC26" t="n">
-        <v>0.500217410431374</v>
+        <v>0.536257473628932</v>
       </c>
       <c r="HD26" t="n">
-        <v>0.497110234738241</v>
+        <v>0.533211658431727</v>
       </c>
       <c r="HE26" t="n">
-        <v>0.493967052886701</v>
+        <v>0.529845906395881</v>
       </c>
       <c r="HF26" t="n">
-        <v>0.490808744804917</v>
+        <v>0.526213995065924</v>
       </c>
       <c r="HG26" t="n">
-        <v>0.487652365397931</v>
+        <v>0.522365516033066</v>
       </c>
       <c r="HH26" t="n">
-        <v>0.484471119661234</v>
+        <v>0.518318531960276</v>
       </c>
       <c r="HI26" t="n">
-        <v>0.481313838550252</v>
+        <v>0.514153057075548</v>
       </c>
       <c r="HJ26" t="n">
-        <v>0.478167560166428</v>
+        <v>0.509898083690448</v>
       </c>
       <c r="HK26" t="n">
-        <v>0.475046147741755</v>
+        <v>0.505599919086597</v>
       </c>
       <c r="HL26" t="n">
-        <v>0.471924897227968</v>
+        <v>0.501264430806642</v>
       </c>
       <c r="HM26" t="n">
-        <v>0.468867761178554</v>
+        <v>0.496987949691623</v>
       </c>
       <c r="HN26" t="n">
-        <v>0.465872016923751</v>
+        <v>0.492790935785272</v>
       </c>
       <c r="HO26" t="n">
-        <v>0.462938153004094</v>
+        <v>0.488693605462124</v>
       </c>
       <c r="HP26" t="n">
-        <v>0.460057552124862</v>
+        <v>0.484703683455324</v>
       </c>
       <c r="HQ26" t="n">
-        <v>0.457232797844422</v>
+        <v>0.480836137189948</v>
       </c>
       <c r="HR26" t="n">
-        <v>0.45445578006845</v>
+        <v>0.47709288137884</v>
       </c>
       <c r="HS26" t="n">
-        <v>0.451726724425629</v>
+        <v>0.473478923581311</v>
       </c>
       <c r="HT26" t="n">
-        <v>0.449063928761026</v>
+        <v>0.470016697589686</v>
       </c>
       <c r="HU26" t="n">
-        <v>0.446422921857105</v>
+        <v>0.466666034452179</v>
       </c>
     </row>
     <row r="27">
@@ -19714,148 +19698,148 @@
         <v>96.6966278318299</v>
       </c>
       <c r="FZ27" t="n">
-        <v>97.4494141077573</v>
+        <v>96.1276985648781</v>
       </c>
       <c r="GA27" t="n">
-        <v>97.8891451108714</v>
+        <v>95.3367073947052</v>
       </c>
       <c r="GB27" t="n">
-        <v>98.2764642455875</v>
+        <v>95.2225040638737</v>
       </c>
       <c r="GC27" t="n">
-        <v>98.6516783884803</v>
+        <v>93.6633754503115</v>
       </c>
       <c r="GD27" t="n">
-        <v>99.7219454786604</v>
+        <v>95.0789547531596</v>
       </c>
       <c r="GE27" t="n">
-        <v>100.841311611377</v>
+        <v>96.4700640273838</v>
       </c>
       <c r="GF27" t="n">
-        <v>101.943825131207</v>
+        <v>97.3261626562374</v>
       </c>
       <c r="GG27" t="n">
-        <v>103.074708160252</v>
+        <v>98.3577949966798</v>
       </c>
       <c r="GH27" t="n">
-        <v>103.455466541183</v>
+        <v>98.5979353160846</v>
       </c>
       <c r="GI27" t="n">
-        <v>103.735802921199</v>
+        <v>98.7474624155861</v>
       </c>
       <c r="GJ27" t="n">
-        <v>104.040145130788</v>
+        <v>98.9209815332057</v>
       </c>
       <c r="GK27" t="n">
-        <v>104.294487481358</v>
+        <v>99.0279128943074</v>
       </c>
       <c r="GL27" t="n">
-        <v>104.459963205752</v>
+        <v>99.0321042042083</v>
       </c>
       <c r="GM27" t="n">
-        <v>104.531911513912</v>
+        <v>98.9000137210997</v>
       </c>
       <c r="GN27" t="n">
-        <v>104.58638094594</v>
+        <v>98.8663987513156</v>
       </c>
       <c r="GO27" t="n">
-        <v>104.583702327257</v>
+        <v>98.8216817046992</v>
       </c>
       <c r="GP27" t="n">
-        <v>104.587154561273</v>
+        <v>98.7947371547535</v>
       </c>
       <c r="GQ27" t="n">
-        <v>104.567397010141</v>
+        <v>98.7597561628269</v>
       </c>
       <c r="GR27" t="n">
-        <v>104.518593260027</v>
+        <v>98.7164822291532</v>
       </c>
       <c r="GS27" t="n">
-        <v>104.446121020827</v>
+        <v>98.6708230827035</v>
       </c>
       <c r="GT27" t="n">
-        <v>104.393146135457</v>
+        <v>98.662944876069</v>
       </c>
       <c r="GU27" t="n">
-        <v>104.335768247853</v>
+        <v>98.6709981225525</v>
       </c>
       <c r="GV27" t="n">
-        <v>104.253267523699</v>
+        <v>98.6731740832994</v>
       </c>
       <c r="GW27" t="n">
-        <v>104.168603288037</v>
+        <v>98.6918848512787</v>
       </c>
       <c r="GX27" t="n">
-        <v>104.0821024797</v>
+        <v>98.7241899618761</v>
       </c>
       <c r="GY27" t="n">
-        <v>103.987862528696</v>
+        <v>98.76286118019</v>
       </c>
       <c r="GZ27" t="n">
-        <v>103.887756362845</v>
+        <v>98.8078199701371</v>
       </c>
       <c r="HA27" t="n">
-        <v>103.783613419939</v>
+        <v>98.8588653817152</v>
       </c>
       <c r="HB27" t="n">
-        <v>103.803901105432</v>
+        <v>99.0317551123686</v>
       </c>
       <c r="HC27" t="n">
-        <v>103.844455150013</v>
+        <v>99.2320301701466</v>
       </c>
       <c r="HD27" t="n">
-        <v>103.856923938</v>
+        <v>99.4040477087109</v>
       </c>
       <c r="HE27" t="n">
-        <v>103.899886041797</v>
+        <v>99.6101570255765</v>
       </c>
       <c r="HF27" t="n">
-        <v>103.943309403773</v>
+        <v>99.8148902693611</v>
       </c>
       <c r="HG27" t="n">
-        <v>103.992494081907</v>
+        <v>100.022909342796</v>
       </c>
       <c r="HH27" t="n">
-        <v>104.046207125583</v>
+        <v>100.231807427716</v>
       </c>
       <c r="HI27" t="n">
-        <v>104.103665522568</v>
+        <v>100.440331137313</v>
       </c>
       <c r="HJ27" t="n">
-        <v>104.164545349036</v>
+        <v>100.646944513488</v>
       </c>
       <c r="HK27" t="n">
-        <v>104.227071289901</v>
+        <v>100.848784707362</v>
       </c>
       <c r="HL27" t="n">
-        <v>104.292606265223</v>
+        <v>101.04724026667</v>
       </c>
       <c r="HM27" t="n">
-        <v>104.359649713302</v>
+        <v>101.240999940788</v>
       </c>
       <c r="HN27" t="n">
-        <v>104.428388158487</v>
+        <v>101.429727369879</v>
       </c>
       <c r="HO27" t="n">
-        <v>104.496904827912</v>
+        <v>101.611099402849</v>
       </c>
       <c r="HP27" t="n">
-        <v>104.567250400822</v>
+        <v>101.787658746321</v>
       </c>
       <c r="HQ27" t="n">
-        <v>104.639104867472</v>
+        <v>101.959485942845</v>
       </c>
       <c r="HR27" t="n">
-        <v>104.712559413165</v>
+        <v>102.126584505326</v>
       </c>
       <c r="HS27" t="n">
-        <v>104.827686409774</v>
+        <v>102.331326545642</v>
       </c>
       <c r="HT27" t="n">
-        <v>104.89397444373</v>
+        <v>102.479154211534</v>
       </c>
       <c r="HU27" t="n">
-        <v>104.99817003643</v>
+        <v>102.661784573796</v>
       </c>
     </row>
     <row r="28">
@@ -20220,149 +20204,143 @@
       <c r="FY28" t="n">
         <v>14.1375</v>
       </c>
-      <c r="FZ28" t="n">
-        <v>14.50104636841</v>
-      </c>
-      <c r="GA28" t="n">
-        <v>14.8977616030285</v>
-      </c>
-      <c r="GB28" t="n">
-        <v>15.4283311454179</v>
-      </c>
+      <c r="FZ28"/>
+      <c r="GA28"/>
+      <c r="GB28"/>
       <c r="GC28" t="n">
-        <v>15.6539171299942</v>
+        <v>15.0818305090182</v>
       </c>
       <c r="GD28" t="n">
-        <v>15.7943610785104</v>
+        <v>15.1209870698774</v>
       </c>
       <c r="GE28" t="n">
-        <v>15.9368907263421</v>
+        <v>15.3246302205419</v>
       </c>
       <c r="GF28" t="n">
-        <v>16.3138290617651</v>
+        <v>15.3881792217293</v>
       </c>
       <c r="GG28" t="n">
-        <v>16.3810180919352</v>
+        <v>15.3165608344826</v>
       </c>
       <c r="GH28" t="n">
-        <v>16.5791852594192</v>
+        <v>15.3897647048699</v>
       </c>
       <c r="GI28" t="n">
-        <v>16.8181011832246</v>
+        <v>15.5538069866276</v>
       </c>
       <c r="GJ28" t="n">
-        <v>17.3694415064457</v>
+        <v>16.0550773548501</v>
       </c>
       <c r="GK28" t="n">
-        <v>17.5826848519175</v>
+        <v>16.2582282963799</v>
       </c>
       <c r="GL28" t="n">
-        <v>17.8346772725713</v>
+        <v>16.5317222475186</v>
       </c>
       <c r="GM28" t="n">
-        <v>18.1027445997468</v>
+        <v>16.8617075280417</v>
       </c>
       <c r="GN28" t="n">
-        <v>18.6641630184771</v>
+        <v>17.4763720194443</v>
       </c>
       <c r="GO28" t="n">
-        <v>18.852304804923</v>
+        <v>17.7308493186448</v>
       </c>
       <c r="GP28" t="n">
-        <v>19.0644793043099</v>
+        <v>18.0092058204772</v>
       </c>
       <c r="GQ28" t="n">
-        <v>19.304360760493</v>
+        <v>18.3186406572699</v>
       </c>
       <c r="GR28" t="n">
-        <v>19.8508458025872</v>
+        <v>18.9345758461819</v>
       </c>
       <c r="GS28" t="n">
-        <v>19.9932653011659</v>
+        <v>19.1465152371563</v>
       </c>
       <c r="GT28" t="n">
-        <v>20.1462604216027</v>
+        <v>19.3690106279217</v>
       </c>
       <c r="GU28" t="n">
-        <v>20.3319725633379</v>
+        <v>19.6196334421423</v>
       </c>
       <c r="GV28" t="n">
-        <v>20.8486255462734</v>
+        <v>20.2008558914036</v>
       </c>
       <c r="GW28" t="n">
-        <v>20.9342751961535</v>
+        <v>20.3400078370309</v>
       </c>
       <c r="GX28" t="n">
-        <v>21.0399115379015</v>
+        <v>20.4933621807569</v>
       </c>
       <c r="GY28" t="n">
-        <v>21.1752076133185</v>
+        <v>20.6670913981306</v>
       </c>
       <c r="GZ28" t="n">
-        <v>21.6723027499772</v>
+        <v>21.2002101493623</v>
       </c>
       <c r="HA28" t="n">
-        <v>21.7054593962163</v>
+        <v>21.251274228048</v>
       </c>
       <c r="HB28" t="n">
-        <v>21.7493065441041</v>
+        <v>21.3074273629296</v>
       </c>
       <c r="HC28" t="n">
-        <v>21.8482043678108</v>
+        <v>21.4071670063718</v>
       </c>
       <c r="HD28" t="n">
-        <v>22.3120389244481</v>
+        <v>21.8771090739949</v>
       </c>
       <c r="HE28" t="n">
-        <v>22.3022701482588</v>
+        <v>21.8532354649022</v>
       </c>
       <c r="HF28" t="n">
-        <v>22.3228658783757</v>
+        <v>21.8579629430614</v>
       </c>
       <c r="HG28" t="n">
-        <v>22.3865354100463</v>
+        <v>21.9014051002978</v>
       </c>
       <c r="HH28" t="n">
-        <v>22.8677459980127</v>
+        <v>22.3689990812288</v>
       </c>
       <c r="HI28" t="n">
-        <v>22.8360660732651</v>
+        <v>22.3092529586145</v>
       </c>
       <c r="HJ28" t="n">
-        <v>22.8444826189272</v>
+        <v>22.2913953675577</v>
       </c>
       <c r="HK28" t="n">
-        <v>22.899475060598</v>
+        <v>22.3202568136696</v>
       </c>
       <c r="HL28" t="n">
-        <v>23.3959483646302</v>
+        <v>22.8008322103916</v>
       </c>
       <c r="HM28" t="n">
-        <v>23.3530781594462</v>
+        <v>22.7307119437586</v>
       </c>
       <c r="HN28" t="n">
-        <v>23.3542628142643</v>
+        <v>22.7095575179022</v>
       </c>
       <c r="HO28" t="n">
-        <v>23.4068048372416</v>
+        <v>22.7424736625849</v>
       </c>
       <c r="HP28" t="n">
-        <v>23.9313536513403</v>
+        <v>23.2595050795287</v>
       </c>
       <c r="HQ28" t="n">
-        <v>23.88836237744</v>
+        <v>23.2001501593153</v>
       </c>
       <c r="HR28" t="n">
-        <v>23.8934368339672</v>
+        <v>23.1956294865779</v>
       </c>
       <c r="HS28" t="n">
-        <v>23.9876659541772</v>
+        <v>23.2795214885363</v>
       </c>
       <c r="HT28" t="n">
-        <v>24.5467397381846</v>
+        <v>23.8471900110401</v>
       </c>
       <c r="HU28" t="n">
-        <v>24.5293686959168</v>
+        <v>23.8267244703807</v>
       </c>
     </row>
     <row r="29">
@@ -20727,149 +20705,143 @@
       <c r="FY29" t="n">
         <v>0.0000204786833383549</v>
       </c>
-      <c r="FZ29" t="n">
-        <v>0.000020606286717785</v>
-      </c>
-      <c r="GA29" t="n">
-        <v>0.0000208278156667572</v>
-      </c>
-      <c r="GB29" t="n">
-        <v>0.0000212662562150201</v>
-      </c>
+      <c r="FZ29"/>
+      <c r="GA29"/>
+      <c r="GB29"/>
       <c r="GC29" t="n">
-        <v>0.0000212545473251779</v>
+        <v>0.0000208743927052349</v>
       </c>
       <c r="GD29" t="n">
-        <v>0.0000210704796898372</v>
+        <v>0.0000202950525145532</v>
       </c>
       <c r="GE29" t="n">
-        <v>0.0000208899622312299</v>
+        <v>0.0000202359123959127</v>
       </c>
       <c r="GF29" t="n">
-        <v>0.0000210099405768593</v>
+        <v>0.000019767663995497</v>
       </c>
       <c r="GG29" t="n">
-        <v>0.000020730649374787</v>
+        <v>0.0000192829003173742</v>
       </c>
       <c r="GH29" t="n">
-        <v>0.0000206625202959064</v>
+        <v>0.0000190249574802281</v>
       </c>
       <c r="GI29" t="n">
-        <v>0.0000206475889520087</v>
+        <v>0.0000188956356068635</v>
       </c>
       <c r="GJ29" t="n">
-        <v>0.0000210303042585105</v>
+        <v>0.0000191942718333016</v>
       </c>
       <c r="GK29" t="n">
-        <v>0.0000209807908570406</v>
+        <v>0.0000191226598082087</v>
       </c>
       <c r="GL29" t="n">
-        <v>0.0000209777951579318</v>
+        <v>0.0000191410380882789</v>
       </c>
       <c r="GM29" t="n">
-        <v>0.0000209873545345298</v>
+        <v>0.0000192348562475824</v>
       </c>
       <c r="GN29" t="n">
-        <v>0.0000213710897889266</v>
+        <v>0.0000196682908088505</v>
       </c>
       <c r="GO29" t="n">
-        <v>0.0000213070620349867</v>
+        <v>0.0000196788934604357</v>
       </c>
       <c r="GP29" t="n">
-        <v>0.0000212672256708008</v>
+        <v>0.0000197113142026785</v>
       </c>
       <c r="GQ29" t="n">
-        <v>0.0000212674993676189</v>
+        <v>0.0000197895602286786</v>
       </c>
       <c r="GR29" t="n">
-        <v>0.0000215918676308419</v>
+        <v>0.0000201880352944373</v>
       </c>
       <c r="GS29" t="n">
-        <v>0.0000214717919494832</v>
+        <v>0.0000201533049114879</v>
       </c>
       <c r="GT29" t="n">
-        <v>0.0000213595344453869</v>
+        <v>0.0000201282384437574</v>
       </c>
       <c r="GU29" t="n">
-        <v>0.0000212939225525019</v>
+        <v>0.0000201442702998434</v>
       </c>
       <c r="GV29" t="n">
-        <v>0.0000215610379489574</v>
+        <v>0.00002048749641774</v>
       </c>
       <c r="GW29" t="n">
-        <v>0.0000213792150351773</v>
+        <v>0.000020378343008207</v>
       </c>
       <c r="GX29" t="n">
-        <v>0.0000212163713855147</v>
+        <v>0.0000202810529357874</v>
       </c>
       <c r="GY29" t="n">
-        <v>0.0000210908331207551</v>
+        <v>0.000020209207210018</v>
       </c>
       <c r="GZ29" t="n">
-        <v>0.0000213171698981032</v>
+        <v>0.0000204790888940467</v>
       </c>
       <c r="HA29" t="n">
-        <v>0.0000210809266885766</v>
+        <v>0.000020275286208044</v>
       </c>
       <c r="HB29" t="n">
-        <v>0.0000208493053046024</v>
+        <v>0.0000200698092475218</v>
       </c>
       <c r="HC29" t="n">
-        <v>0.0000206888428530355</v>
+        <v>0.0000199202894583508</v>
       </c>
       <c r="HD29" t="n">
-        <v>0.0000208538117993795</v>
+        <v>0.00002009637174507</v>
       </c>
       <c r="HE29" t="n">
-        <v>0.0000205786356959206</v>
+        <v>0.0000198190028696923</v>
       </c>
       <c r="HF29" t="n">
-        <v>0.0000203319685814215</v>
+        <v>0.0000195676724712688</v>
       </c>
       <c r="HG29" t="n">
-        <v>0.0000201333259832017</v>
+        <v>0.0000193587255094312</v>
       </c>
       <c r="HH29" t="n">
-        <v>0.0000203050354224228</v>
+        <v>0.0000195192049488821</v>
       </c>
       <c r="HI29" t="n">
-        <v>0.0000200164654723774</v>
+        <v>0.0000192142734484353</v>
       </c>
       <c r="HJ29" t="n">
-        <v>0.0000197655627628806</v>
+        <v>0.0000189478211507497</v>
       </c>
       <c r="HK29" t="n">
-        <v>0.0000195644350768284</v>
+        <v>0.0000187299068591564</v>
       </c>
       <c r="HL29" t="n">
-        <v>0.0000197353094641046</v>
+        <v>0.0000188859686461706</v>
       </c>
       <c r="HM29" t="n">
-        <v>0.0000194471849293545</v>
+        <v>0.0000185817206185777</v>
       </c>
       <c r="HN29" t="n">
-        <v>0.0000191988022419829</v>
+        <v>0.0000183207736077472</v>
       </c>
       <c r="HO29" t="n">
-        <v>0.00001900249392395</v>
+        <v>0.0000181128718353595</v>
       </c>
       <c r="HP29" t="n">
-        <v>0.0000191855168120323</v>
+        <v>0.0000182868602197491</v>
       </c>
       <c r="HQ29" t="n">
-        <v>0.0000189093930449016</v>
+        <v>0.0000180036820152358</v>
       </c>
       <c r="HR29" t="n">
-        <v>0.000018674272084817</v>
+        <v>0.0000177663767857588</v>
       </c>
       <c r="HS29" t="n">
-        <v>0.0000185305758735644</v>
+        <v>0.0000176160841603059</v>
       </c>
       <c r="HT29" t="n">
-        <v>0.0000187276287530771</v>
+        <v>0.0000178162859617642</v>
       </c>
       <c r="HU29" t="n">
-        <v>0.0000184887797126104</v>
+        <v>0.0000175796431292398</v>
       </c>
     </row>
     <row r="30">
@@ -21234,149 +21206,143 @@
       <c r="FY30" t="n">
         <v>825.6</v>
       </c>
-      <c r="FZ30" t="n">
-        <v>844.78581461489</v>
-      </c>
-      <c r="GA30" t="n">
-        <v>864.096526255102</v>
-      </c>
-      <c r="GB30" t="n">
-        <v>884.222030725671</v>
-      </c>
+      <c r="FZ30"/>
+      <c r="GA30"/>
+      <c r="GB30"/>
       <c r="GC30" t="n">
-        <v>904.453708974963</v>
+        <v>844.956095850485</v>
       </c>
       <c r="GD30" t="n">
-        <v>925.275326265355</v>
+        <v>864.773631499334</v>
       </c>
       <c r="GE30" t="n">
-        <v>946.343127944802</v>
+        <v>884.978579592451</v>
       </c>
       <c r="GF30" t="n">
-        <v>967.855641887571</v>
+        <v>905.173697542289</v>
       </c>
       <c r="GG30" t="n">
-        <v>989.496877630395</v>
+        <v>925.421842103574</v>
       </c>
       <c r="GH30" t="n">
-        <v>1011.39662737137</v>
+        <v>945.752350242807</v>
       </c>
       <c r="GI30" t="n">
-        <v>1033.612716282</v>
+        <v>966.284065456896</v>
       </c>
       <c r="GJ30" t="n">
-        <v>1056.48610870043</v>
+        <v>987.423095497003</v>
       </c>
       <c r="GK30" t="n">
-        <v>1079.71892068774</v>
+        <v>1008.95087575841</v>
       </c>
       <c r="GL30" t="n">
-        <v>1103.3906672407</v>
+        <v>1031.00353998853</v>
       </c>
       <c r="GM30" t="n">
-        <v>1127.55331977096</v>
+        <v>1053.6946157155</v>
       </c>
       <c r="GN30" t="n">
-        <v>1152.53117880719</v>
+        <v>1077.35409231819</v>
       </c>
       <c r="GO30" t="n">
-        <v>1177.97401293621</v>
+        <v>1101.65332491332</v>
       </c>
       <c r="GP30" t="n">
-        <v>1203.92203776392</v>
+        <v>1126.63438655524</v>
       </c>
       <c r="GQ30" t="n">
-        <v>1230.41446342594</v>
+        <v>1152.33523905317</v>
       </c>
       <c r="GR30" t="n">
-        <v>1257.76659117368</v>
+        <v>1179.05812749796</v>
       </c>
       <c r="GS30" t="n">
-        <v>1285.56859733877</v>
+        <v>1206.38016333406</v>
       </c>
       <c r="GT30" t="n">
-        <v>1313.81973651942</v>
+        <v>1234.28336484837</v>
       </c>
       <c r="GU30" t="n">
-        <v>1342.53849809481</v>
+        <v>1262.76300345139</v>
       </c>
       <c r="GV30" t="n">
-        <v>1372.03700398354</v>
+        <v>1292.1126261937</v>
       </c>
       <c r="GW30" t="n">
-        <v>1401.8698213039</v>
+        <v>1321.85636168206</v>
       </c>
       <c r="GX30" t="n">
-        <v>1432.03987723012</v>
+        <v>1351.97130734975</v>
       </c>
       <c r="GY30" t="n">
-        <v>1462.56198311016</v>
+        <v>1382.44244964767</v>
       </c>
       <c r="GZ30" t="n">
-        <v>1493.78160305256</v>
+        <v>1413.59347879923</v>
       </c>
       <c r="HA30" t="n">
-        <v>1525.22333418019</v>
+        <v>1444.91193473522</v>
       </c>
       <c r="HB30" t="n">
-        <v>1556.88477110995</v>
+        <v>1476.37175823028</v>
       </c>
       <c r="HC30" t="n">
-        <v>1588.80988957318</v>
+        <v>1507.98906188493</v>
       </c>
       <c r="HD30" t="n">
-        <v>1621.3523425916</v>
+        <v>1540.10916515589</v>
       </c>
       <c r="HE30" t="n">
-        <v>1654.03270009565</v>
+        <v>1572.22132492699</v>
       </c>
       <c r="HF30" t="n">
-        <v>1686.87403809437</v>
+        <v>1604.3383412445</v>
       </c>
       <c r="HG30" t="n">
-        <v>1719.91517966142</v>
+        <v>1636.48876285672</v>
       </c>
       <c r="HH30" t="n">
-        <v>1753.56516468546</v>
+        <v>1669.08698192652</v>
       </c>
       <c r="HI30" t="n">
-        <v>1787.31129202741</v>
+        <v>1701.60594200095</v>
       </c>
       <c r="HJ30" t="n">
-        <v>1821.1901929768</v>
+        <v>1734.08722995369</v>
       </c>
       <c r="HK30" t="n">
-        <v>1855.24659493238</v>
+        <v>1766.58099688677</v>
       </c>
       <c r="HL30" t="n">
-        <v>1889.91885775306</v>
+        <v>1799.54361889706</v>
       </c>
       <c r="HM30" t="n">
-        <v>1924.66788372979</v>
+        <v>1832.43384982829</v>
       </c>
       <c r="HN30" t="n">
-        <v>1959.53588121182</v>
+        <v>1865.30912595582</v>
       </c>
       <c r="HO30" t="n">
-        <v>1994.57344106318</v>
+        <v>1898.23387366782</v>
       </c>
       <c r="HP30" t="n">
-        <v>2030.24980598274</v>
+        <v>1931.70178865946</v>
       </c>
       <c r="HQ30" t="n">
-        <v>2065.99900906114</v>
+        <v>1965.15019963794</v>
       </c>
       <c r="HR30" t="n">
-        <v>2101.86796119153</v>
+        <v>1998.64508095983</v>
       </c>
       <c r="HS30" t="n">
-        <v>2137.94561185765</v>
+        <v>2032.28657412079</v>
       </c>
       <c r="HT30" t="n">
-        <v>2174.69426230778</v>
+        <v>2066.56813807197</v>
       </c>
       <c r="HU30" t="n">
-        <v>2211.53668192622</v>
+        <v>2100.91233731129</v>
       </c>
     </row>
     <row r="31">
@@ -21924,148 +21890,148 @@
         <v>0.0492819335711963</v>
       </c>
       <c r="FZ31" t="n">
-        <v>0.0292147291199923</v>
+        <v>0.0610480423650282</v>
       </c>
       <c r="GA31" t="n">
-        <v>0.0292147291199921</v>
+        <v>0.0531869977702769</v>
       </c>
       <c r="GB31" t="n">
-        <v>0.0292147291199923</v>
+        <v>0.0546735510183915</v>
       </c>
       <c r="GC31" t="n">
-        <v>0.0292147291199921</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GD31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.0435353050242881</v>
       </c>
       <c r="GE31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GF31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GG31" t="n">
-        <v>0.0292147291199921</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GH31" t="n">
-        <v>0.0292147291199921</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GI31" t="n">
-        <v>0.0292147291199921</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GJ31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GK31" t="n">
-        <v>0.0292147291199921</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GL31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GM31" t="n">
-        <v>0.0292147291199921</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GN31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GO31" t="n">
-        <v>0.0292147291199923</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GP31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GQ31" t="n">
-        <v>0.0292147291199921</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GR31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GS31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GT31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GU31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GV31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GW31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GX31" t="n">
-        <v>0.0292147291199921</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GY31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GZ31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HA31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HB31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HC31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HD31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HE31" t="n">
-        <v>0.0292147291199923</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HF31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HG31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HH31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HI31" t="n">
-        <v>0.0292147291199921</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HJ31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HK31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.0435353050242881</v>
       </c>
       <c r="HL31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HM31" t="n">
-        <v>0.0292147291199921</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HN31" t="n">
-        <v>0.0292147291199921</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HO31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HP31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.0435353050242881</v>
       </c>
       <c r="HQ31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HR31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HS31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HT31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HU31" t="n">
-        <v>0.0292147291199922</v>
+        <v>0.043535305024288</v>
       </c>
     </row>
     <row r="32">
@@ -22613,148 +22579,148 @@
         <v>0.230188367673303</v>
       </c>
       <c r="FZ32" t="n">
-        <v>0.230669093273481</v>
+        <v>0.230361152828435</v>
       </c>
       <c r="GA32" t="n">
-        <v>0.231713909515452</v>
+        <v>0.23262683994466</v>
       </c>
       <c r="GB32" t="n">
-        <v>0.232461806107272</v>
+        <v>0.233491652414238</v>
       </c>
       <c r="GC32" t="n">
-        <v>0.23298398692248</v>
+        <v>0.236915441958085</v>
       </c>
       <c r="GD32" t="n">
-        <v>0.232864851644454</v>
+        <v>0.232967223869263</v>
       </c>
       <c r="GE32" t="n">
-        <v>0.232750278172798</v>
+        <v>0.233285362694306</v>
       </c>
       <c r="GF32" t="n">
-        <v>0.232590309182084</v>
+        <v>0.230386352538882</v>
       </c>
       <c r="GG32" t="n">
-        <v>0.232481271336328</v>
+        <v>0.229682814104195</v>
       </c>
       <c r="GH32" t="n">
-        <v>0.232871782343898</v>
+        <v>0.229291897872356</v>
       </c>
       <c r="GI32" t="n">
-        <v>0.233318507700291</v>
+        <v>0.229177580453934</v>
       </c>
       <c r="GJ32" t="n">
-        <v>0.233905613048543</v>
+        <v>0.229270887243102</v>
       </c>
       <c r="GK32" t="n">
-        <v>0.234275795890422</v>
+        <v>0.229281157994434</v>
       </c>
       <c r="GL32" t="n">
-        <v>0.234677730238207</v>
+        <v>0.229440217133751</v>
       </c>
       <c r="GM32" t="n">
-        <v>0.235017806843936</v>
+        <v>0.229788350846039</v>
       </c>
       <c r="GN32" t="n">
-        <v>0.235121020604063</v>
+        <v>0.229758904663866</v>
       </c>
       <c r="GO32" t="n">
-        <v>0.234991270220823</v>
+        <v>0.229572533583784</v>
       </c>
       <c r="GP32" t="n">
-        <v>0.23483838278998</v>
+        <v>0.229372213777244</v>
       </c>
       <c r="GQ32" t="n">
-        <v>0.234796362357731</v>
+        <v>0.229362590090049</v>
       </c>
       <c r="GR32" t="n">
-        <v>0.234647226807426</v>
+        <v>0.229311054630818</v>
       </c>
       <c r="GS32" t="n">
-        <v>0.234491225318753</v>
+        <v>0.229314819202131</v>
       </c>
       <c r="GT32" t="n">
-        <v>0.234270966354543</v>
+        <v>0.229308372073925</v>
       </c>
       <c r="GU32" t="n">
-        <v>0.234195889244567</v>
+        <v>0.229477862430882</v>
       </c>
       <c r="GV32" t="n">
-        <v>0.234007686746148</v>
+        <v>0.229574105575368</v>
       </c>
       <c r="GW32" t="n">
-        <v>0.233826679032129</v>
+        <v>0.229685801284219</v>
       </c>
       <c r="GX32" t="n">
-        <v>0.233598229387969</v>
+        <v>0.229757012045051</v>
       </c>
       <c r="GY32" t="n">
-        <v>0.233448431896662</v>
+        <v>0.229897817676451</v>
       </c>
       <c r="GZ32" t="n">
-        <v>0.233241910304654</v>
+        <v>0.229976973640873</v>
       </c>
       <c r="HA32" t="n">
-        <v>0.232994489071274</v>
+        <v>0.229999062546598</v>
       </c>
       <c r="HB32" t="n">
-        <v>0.232642924251142</v>
+        <v>0.22991113978964</v>
       </c>
       <c r="HC32" t="n">
-        <v>0.232504007197961</v>
+        <v>0.230000539404424</v>
       </c>
       <c r="HD32" t="n">
-        <v>0.232127643241732</v>
+        <v>0.22986544911674</v>
       </c>
       <c r="HE32" t="n">
-        <v>0.231825986782035</v>
+        <v>0.22977288174354</v>
       </c>
       <c r="HF32" t="n">
-        <v>0.231475292742955</v>
+        <v>0.229623209822612</v>
       </c>
       <c r="HG32" t="n">
-        <v>0.231210546244008</v>
+        <v>0.229541915414041</v>
       </c>
       <c r="HH32" t="n">
-        <v>0.230905208349934</v>
+        <v>0.229410400450314</v>
       </c>
       <c r="HI32" t="n">
-        <v>0.23056200680725</v>
+        <v>0.229227077436351</v>
       </c>
       <c r="HJ32" t="n">
-        <v>0.230203195089921</v>
+        <v>0.229017082365737</v>
       </c>
       <c r="HK32" t="n">
-        <v>0.229934535592634</v>
+        <v>0.228882703239293</v>
       </c>
       <c r="HL32" t="n">
-        <v>0.229623856830191</v>
+        <v>0.228700019617698</v>
       </c>
       <c r="HM32" t="n">
-        <v>0.229285187104251</v>
+        <v>0.228478022519514</v>
       </c>
       <c r="HN32" t="n">
-        <v>0.228936498346371</v>
+        <v>0.228239542695448</v>
       </c>
       <c r="HO32" t="n">
-        <v>0.228685699151106</v>
+        <v>0.228088937498853</v>
       </c>
       <c r="HP32" t="n">
-        <v>0.228412586993001</v>
+        <v>0.227913806713349</v>
       </c>
       <c r="HQ32" t="n">
-        <v>0.228108481013975</v>
+        <v>0.227703253067986</v>
       </c>
       <c r="HR32" t="n">
-        <v>0.227797291166236</v>
+        <v>0.227484648268088</v>
       </c>
       <c r="HS32" t="n">
-        <v>0.227765445835632</v>
+        <v>0.227520128769301</v>
       </c>
       <c r="HT32" t="n">
-        <v>0.227502686460144</v>
+        <v>0.227355780362617</v>
       </c>
       <c r="HU32" t="n">
-        <v>0.227345247542255</v>
+        <v>0.227279342235415</v>
       </c>
     </row>
     <row r="33">
@@ -23134,148 +23100,148 @@
         <v>79821</v>
       </c>
       <c r="FZ33" t="n">
-        <v>80456.1748849765</v>
+        <v>79901</v>
       </c>
       <c r="GA33" t="n">
-        <v>81674.0189793255</v>
+        <v>79719</v>
       </c>
       <c r="GB33" t="n">
-        <v>82745.1343188903</v>
+        <v>82599</v>
       </c>
       <c r="GC33" t="n">
-        <v>84072.4722894432</v>
+        <v>82730.0045338344</v>
       </c>
       <c r="GD33" t="n">
-        <v>85332.7900929681</v>
+        <v>84321.2441617233</v>
       </c>
       <c r="GE33" t="n">
-        <v>86649.007497441</v>
+        <v>85680.3975272089</v>
       </c>
       <c r="GF33" t="n">
-        <v>88051.3075102634</v>
+        <v>87471.1118921292</v>
       </c>
       <c r="GG33" t="n">
-        <v>89452.413825649</v>
+        <v>89160.8213664285</v>
       </c>
       <c r="GH33" t="n">
-        <v>90720.0953282569</v>
+        <v>90613.6003037998</v>
       </c>
       <c r="GI33" t="n">
-        <v>91959.2803283393</v>
+        <v>91827.62681118</v>
       </c>
       <c r="GJ33" t="n">
-        <v>92987.3400205407</v>
+        <v>92774.2311955532</v>
       </c>
       <c r="GK33" t="n">
-        <v>93990.5644975363</v>
+        <v>93583.1360925084</v>
       </c>
       <c r="GL33" t="n">
-        <v>94949.142065061</v>
+        <v>94362.9610454857</v>
       </c>
       <c r="GM33" t="n">
-        <v>95890.2366440052</v>
+        <v>95066.0149121704</v>
       </c>
       <c r="GN33" t="n">
-        <v>96719.5596086517</v>
+        <v>95748.1325491151</v>
       </c>
       <c r="GO33" t="n">
-        <v>97485.7340671719</v>
+        <v>96278.764483901</v>
       </c>
       <c r="GP33" t="n">
-        <v>98222.9529106025</v>
+        <v>96906.6191730615</v>
       </c>
       <c r="GQ33" t="n">
-        <v>98910.5916684247</v>
+        <v>97451.2867583201</v>
       </c>
       <c r="GR33" t="n">
-        <v>99607.343567222</v>
+        <v>98045.1716752286</v>
       </c>
       <c r="GS33" t="n">
-        <v>100309.483951185</v>
+        <v>98622.6439894171</v>
       </c>
       <c r="GT33" t="n">
-        <v>101025.039330252</v>
+        <v>99224.0015301039</v>
       </c>
       <c r="GU33" t="n">
-        <v>101716.290356826</v>
+        <v>99795.9421671155</v>
       </c>
       <c r="GV33" t="n">
-        <v>102398.753084582</v>
+        <v>100369.986949894</v>
       </c>
       <c r="GW33" t="n">
-        <v>103078.914705041</v>
+        <v>100951.597093669</v>
       </c>
       <c r="GX33" t="n">
-        <v>103762.146011285</v>
+        <v>101556.359654764</v>
       </c>
       <c r="GY33" t="n">
-        <v>104423.448927362</v>
+        <v>102162.228543199</v>
       </c>
       <c r="GZ33" t="n">
-        <v>105076.677848616</v>
+        <v>102786.24296178</v>
       </c>
       <c r="HA33" t="n">
-        <v>105731.755816325</v>
+        <v>103438.03372993</v>
       </c>
       <c r="HB33" t="n">
-        <v>106410.433551225</v>
+        <v>104136.830740556</v>
       </c>
       <c r="HC33" t="n">
-        <v>107058.122157874</v>
+        <v>104830.482607297</v>
       </c>
       <c r="HD33" t="n">
-        <v>107711.416271622</v>
+        <v>105546.531468385</v>
       </c>
       <c r="HE33" t="n">
-        <v>108365.015389348</v>
+        <v>106279.196806135</v>
       </c>
       <c r="HF33" t="n">
-        <v>109016.187690729</v>
+        <v>107022.072999774</v>
       </c>
       <c r="HG33" t="n">
-        <v>109641.741285375</v>
+        <v>107749.171608195</v>
       </c>
       <c r="HH33" t="n">
-        <v>110245.03221209</v>
+        <v>108461.347394156</v>
       </c>
       <c r="HI33" t="n">
-        <v>110839.269759118</v>
+        <v>109168.923656873</v>
       </c>
       <c r="HJ33" t="n">
-        <v>111430.07638281</v>
+        <v>109875.01409602</v>
       </c>
       <c r="HK33" t="n">
-        <v>111988.000444704</v>
+        <v>110549.875719315</v>
       </c>
       <c r="HL33" t="n">
-        <v>112524.652797358</v>
+        <v>111202.094854671</v>
       </c>
       <c r="HM33" t="n">
-        <v>113052.797065218</v>
+        <v>111843.666651775</v>
       </c>
       <c r="HN33" t="n">
-        <v>113574.982602396</v>
+        <v>112475.331041877</v>
       </c>
       <c r="HO33" t="n">
-        <v>114063.406246643</v>
+        <v>113069.214097022</v>
       </c>
       <c r="HP33" t="n">
-        <v>114524.174848804</v>
+        <v>113629.779268746</v>
       </c>
       <c r="HQ33" t="n">
-        <v>114975.175061309</v>
+        <v>114174.105091784</v>
       </c>
       <c r="HR33" t="n">
-        <v>115420.330438981</v>
+        <v>114705.188992741</v>
       </c>
       <c r="HS33" t="n">
-        <v>115821.134091837</v>
+        <v>115188.033061984</v>
       </c>
       <c r="HT33" t="n">
-        <v>116194.097344891</v>
+        <v>115633.894716007</v>
       </c>
       <c r="HU33" t="n">
-        <v>116566.547424386</v>
+        <v>116071.666566925</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sem_coredata.xlsx
+++ b/outputs/sem_coredata.xlsx
@@ -2754,139 +2754,139 @@
         <v>354377</v>
       </c>
       <c r="GC2" t="n">
-        <v>355157.211293678</v>
+        <v>355091.626663159</v>
       </c>
       <c r="GD2" t="n">
-        <v>358795.472538645</v>
+        <v>360111.637408295</v>
       </c>
       <c r="GE2" t="n">
-        <v>363166.339057702</v>
+        <v>362966.815723289</v>
       </c>
       <c r="GF2" t="n">
-        <v>367650.213879468</v>
+        <v>366513.56131485</v>
       </c>
       <c r="GG2" t="n">
-        <v>371143.62270974</v>
+        <v>369343.65653203</v>
       </c>
       <c r="GH2" t="n">
-        <v>374105.929735411</v>
+        <v>371764.515144055</v>
       </c>
       <c r="GI2" t="n">
-        <v>376457.827635005</v>
+        <v>373741.073389824</v>
       </c>
       <c r="GJ2" t="n">
-        <v>378540.773444217</v>
+        <v>375470.918781582</v>
       </c>
       <c r="GK2" t="n">
-        <v>380629.132057787</v>
+        <v>377283.567466032</v>
       </c>
       <c r="GL2" t="n">
-        <v>382707.623938109</v>
+        <v>379125.691403618</v>
       </c>
       <c r="GM2" t="n">
-        <v>384581.546054179</v>
+        <v>380784.317869581</v>
       </c>
       <c r="GN2" t="n">
-        <v>386322.088478483</v>
+        <v>382307.490345511</v>
       </c>
       <c r="GO2" t="n">
-        <v>388283.797267691</v>
+        <v>384059.18819393</v>
       </c>
       <c r="GP2" t="n">
-        <v>390434.065806365</v>
+        <v>386011.016192965</v>
       </c>
       <c r="GQ2" t="n">
-        <v>392412.02767212</v>
+        <v>387799.538502192</v>
       </c>
       <c r="GR2" t="n">
-        <v>394597.99112062</v>
+        <v>389804.350803684</v>
       </c>
       <c r="GS2" t="n">
-        <v>396985.896919367</v>
+        <v>392020.281682245</v>
       </c>
       <c r="GT2" t="n">
-        <v>399547.322144343</v>
+        <v>394422.916539436</v>
       </c>
       <c r="GU2" t="n">
-        <v>401899.780984293</v>
+        <v>396625.977989916</v>
       </c>
       <c r="GV2" t="n">
-        <v>404423.370124193</v>
+        <v>399001.770005034</v>
       </c>
       <c r="GW2" t="n">
-        <v>407169.976809224</v>
+        <v>401600.960317238</v>
       </c>
       <c r="GX2" t="n">
-        <v>410087.993020951</v>
+        <v>404372.766736747</v>
       </c>
       <c r="GY2" t="n">
-        <v>412808.52472221</v>
+        <v>406945.693507214</v>
       </c>
       <c r="GZ2" t="n">
-        <v>415706.700004259</v>
+        <v>409686.461696267</v>
       </c>
       <c r="HA2" t="n">
-        <v>418802.93209611</v>
+        <v>412616.81008759</v>
       </c>
       <c r="HB2" t="n">
-        <v>422045.121670563</v>
+        <v>415689.571892267</v>
       </c>
       <c r="HC2" t="n">
-        <v>424954.464956965</v>
+        <v>418425.864141988</v>
       </c>
       <c r="HD2" t="n">
-        <v>428026.260558339</v>
+        <v>421316.136811352</v>
       </c>
       <c r="HE2" t="n">
-        <v>431207.240512452</v>
+        <v>424308.953161687</v>
       </c>
       <c r="HF2" t="n">
-        <v>434446.926106401</v>
+        <v>427360.250800108</v>
       </c>
       <c r="HG2" t="n">
-        <v>437344.351655797</v>
+        <v>430071.644645782</v>
       </c>
       <c r="HH2" t="n">
-        <v>440275.019485886</v>
+        <v>432810.305022509</v>
       </c>
       <c r="HI2" t="n">
-        <v>443313.483905751</v>
+        <v>435654.380400393</v>
       </c>
       <c r="HJ2" t="n">
-        <v>446380.114608649</v>
+        <v>438529.293802569</v>
       </c>
       <c r="HK2" t="n">
-        <v>449075.286123769</v>
+        <v>441038.018122278</v>
       </c>
       <c r="HL2" t="n">
-        <v>451805.672775336</v>
+        <v>443578.065262381</v>
       </c>
       <c r="HM2" t="n">
-        <v>454627.786980069</v>
+        <v>446209.067710323</v>
       </c>
       <c r="HN2" t="n">
-        <v>457468.176717751</v>
+        <v>448862.974386194</v>
       </c>
       <c r="HO2" t="n">
-        <v>459917.610137924</v>
+        <v>451133.358667824</v>
       </c>
       <c r="HP2" t="n">
-        <v>462364.310810752</v>
+        <v>453398.438581173</v>
       </c>
       <c r="HQ2" t="n">
-        <v>464918.803431897</v>
+        <v>455771.87818481</v>
       </c>
       <c r="HR2" t="n">
-        <v>467504.594496089</v>
+        <v>458182.393794065</v>
       </c>
       <c r="HS2" t="n">
-        <v>469602.354376046</v>
+        <v>460112.011705037</v>
       </c>
       <c r="HT2" t="n">
-        <v>471794.542768185</v>
+        <v>462135.122624696</v>
       </c>
       <c r="HU2" t="n">
-        <v>474075.522608443</v>
+        <v>464246.863894274</v>
       </c>
     </row>
     <row r="3">
@@ -4135,136 +4135,136 @@
         <v>36864.8957689682</v>
       </c>
       <c r="GD4" t="n">
-        <v>37067.579590602</v>
+        <v>37067.0321234082</v>
       </c>
       <c r="GE4" t="n">
-        <v>37232.0945730057</v>
+        <v>37241.6529393243</v>
       </c>
       <c r="GF4" t="n">
-        <v>37384.7093034521</v>
+        <v>37366.1984493942</v>
       </c>
       <c r="GG4" t="n">
-        <v>37395.9464072406</v>
+        <v>37326.3949317088</v>
       </c>
       <c r="GH4" t="n">
-        <v>37300.8875628905</v>
+        <v>37201.5948014705</v>
       </c>
       <c r="GI4" t="n">
-        <v>37133.0849542831</v>
+        <v>37027.6696104432</v>
       </c>
       <c r="GJ4" t="n">
-        <v>36988.8803212363</v>
+        <v>36908.9972932988</v>
       </c>
       <c r="GK4" t="n">
-        <v>36928.5927044009</v>
+        <v>36880.2350066421</v>
       </c>
       <c r="GL4" t="n">
-        <v>36987.3778775673</v>
+        <v>36964.5856614639</v>
       </c>
       <c r="GM4" t="n">
-        <v>37159.138764331</v>
+        <v>37146.4706531439</v>
       </c>
       <c r="GN4" t="n">
-        <v>37414.2955412779</v>
+        <v>37391.9150101135</v>
       </c>
       <c r="GO4" t="n">
-        <v>37712.9075474498</v>
+        <v>37661.9482885952</v>
       </c>
       <c r="GP4" t="n">
-        <v>38020.6559440737</v>
+        <v>37926.6214422795</v>
       </c>
       <c r="GQ4" t="n">
-        <v>38310.2404010462</v>
+        <v>38165.0447148107</v>
       </c>
       <c r="GR4" t="n">
-        <v>38557.886508678</v>
+        <v>38359.8279116673</v>
       </c>
       <c r="GS4" t="n">
-        <v>38753.4085763936</v>
+        <v>38506.0423271157</v>
       </c>
       <c r="GT4" t="n">
-        <v>38895.2390487472</v>
+        <v>38605.4985004893</v>
       </c>
       <c r="GU4" t="n">
-        <v>38990.8772461067</v>
+        <v>38667.1035923455</v>
       </c>
       <c r="GV4" t="n">
-        <v>39051.4495482478</v>
+        <v>38701.6561206232</v>
       </c>
       <c r="GW4" t="n">
-        <v>39094.1199430444</v>
+        <v>38724.7990810531</v>
       </c>
       <c r="GX4" t="n">
-        <v>39136.1900024676</v>
+        <v>38751.8275568061</v>
       </c>
       <c r="GY4" t="n">
-        <v>39189.8880787792</v>
+        <v>38792.9873961775</v>
       </c>
       <c r="GZ4" t="n">
-        <v>39260.2366443864</v>
+        <v>38851.6988369897</v>
       </c>
       <c r="HA4" t="n">
-        <v>39351.0923769263</v>
+        <v>38930.7195260791</v>
       </c>
       <c r="HB4" t="n">
-        <v>39463.388119257</v>
+        <v>39030.4748121544</v>
       </c>
       <c r="HC4" t="n">
-        <v>39594.8856538842</v>
+        <v>39148.6878407098</v>
       </c>
       <c r="HD4" t="n">
-        <v>39739.3400578102</v>
+        <v>39279.3211405225</v>
       </c>
       <c r="HE4" t="n">
-        <v>39895.6548545581</v>
+        <v>39421.5453587658</v>
       </c>
       <c r="HF4" t="n">
-        <v>40063.0974125211</v>
+        <v>39574.8636973929</v>
       </c>
       <c r="HG4" t="n">
-        <v>40239.7858033261</v>
+        <v>39737.5408647172</v>
       </c>
       <c r="HH4" t="n">
-        <v>40422.5193760021</v>
+        <v>39906.3997087168</v>
       </c>
       <c r="HI4" t="n">
-        <v>40611.3091185359</v>
+        <v>40081.2831975642</v>
       </c>
       <c r="HJ4" t="n">
-        <v>40808.0356530005</v>
+        <v>40263.8838515558</v>
       </c>
       <c r="HK4" t="n">
-        <v>41012.5218897412</v>
+        <v>40453.8474176129</v>
       </c>
       <c r="HL4" t="n">
-        <v>41221.2532767052</v>
+        <v>40647.5150528972</v>
       </c>
       <c r="HM4" t="n">
-        <v>41433.9381958378</v>
+        <v>40844.4435422706</v>
       </c>
       <c r="HN4" t="n">
-        <v>41650.6668559899</v>
+        <v>41044.6781158459</v>
       </c>
       <c r="HO4" t="n">
-        <v>41870.1129300453</v>
+        <v>41246.9612813887</v>
       </c>
       <c r="HP4" t="n">
-        <v>42088.0421911433</v>
+        <v>41447.1816180583</v>
       </c>
       <c r="HQ4" t="n">
-        <v>42303.8769232235</v>
+        <v>41644.8419514268</v>
       </c>
       <c r="HR4" t="n">
-        <v>42518.8223500639</v>
+        <v>41841.2713522708</v>
       </c>
       <c r="HS4" t="n">
-        <v>42732.719289882</v>
+        <v>42036.4696194232</v>
       </c>
       <c r="HT4" t="n">
-        <v>42941.256434801</v>
+        <v>42226.2625025448</v>
       </c>
       <c r="HU4" t="n">
-        <v>43146.0493414534</v>
+        <v>42412.3421229126</v>
       </c>
     </row>
     <row r="5">
@@ -4824,136 +4824,136 @@
         <v>11150.4565404427</v>
       </c>
       <c r="GD5" t="n">
-        <v>11211.7619394527</v>
+        <v>11211.5963480676</v>
       </c>
       <c r="GE5" t="n">
-        <v>11261.5224805659</v>
+        <v>11264.41358187</v>
       </c>
       <c r="GF5" t="n">
-        <v>11307.6835745763</v>
+        <v>11302.0846309364</v>
       </c>
       <c r="GG5" t="n">
-        <v>11311.0824404843</v>
+        <v>11290.0453348839</v>
       </c>
       <c r="GH5" t="n">
-        <v>11282.3301684217</v>
+        <v>11252.2972713281</v>
       </c>
       <c r="GI5" t="n">
-        <v>11231.575225118</v>
+        <v>11199.6904418937</v>
       </c>
       <c r="GJ5" t="n">
-        <v>11187.9579176449</v>
+        <v>11163.795846581</v>
       </c>
       <c r="GK5" t="n">
-        <v>11169.7228341752</v>
+        <v>11155.0961711667</v>
       </c>
       <c r="GL5" t="n">
-        <v>11187.5034762994</v>
+        <v>11180.609557035</v>
       </c>
       <c r="GM5" t="n">
-        <v>11239.4556726438</v>
+        <v>11235.6239725862</v>
       </c>
       <c r="GN5" t="n">
-        <v>11316.63246897</v>
+        <v>11309.8630712843</v>
       </c>
       <c r="GO5" t="n">
-        <v>11406.9530877543</v>
+        <v>11391.5395353941</v>
       </c>
       <c r="GP5" t="n">
-        <v>11500.0371735863</v>
+        <v>11471.5947325137</v>
       </c>
       <c r="GQ5" t="n">
-        <v>11587.6272463345</v>
+        <v>11543.7101768445</v>
       </c>
       <c r="GR5" t="n">
-        <v>11662.5323044653</v>
+        <v>11602.6258885549</v>
       </c>
       <c r="GS5" t="n">
-        <v>11721.6715010718</v>
+        <v>11646.8510911775</v>
       </c>
       <c r="GT5" t="n">
-        <v>11764.5707005705</v>
+        <v>11676.9334151811</v>
       </c>
       <c r="GU5" t="n">
-        <v>11793.4982084616</v>
+        <v>11695.5669928729</v>
       </c>
       <c r="GV5" t="n">
-        <v>11811.8194001669</v>
+        <v>11706.0180319139</v>
       </c>
       <c r="GW5" t="n">
-        <v>11824.7258352135</v>
+        <v>11713.0180401632</v>
       </c>
       <c r="GX5" t="n">
-        <v>11837.450687935</v>
+        <v>11721.1932930142</v>
       </c>
       <c r="GY5" t="n">
-        <v>11853.6926453237</v>
+        <v>11733.6428331675</v>
       </c>
       <c r="GZ5" t="n">
-        <v>11874.9708452785</v>
+        <v>11751.4011736035</v>
       </c>
       <c r="HA5" t="n">
-        <v>11902.4518099199</v>
+        <v>11775.302414638</v>
       </c>
       <c r="HB5" t="n">
-        <v>11936.4176944943</v>
+        <v>11805.4752107048</v>
       </c>
       <c r="HC5" t="n">
-        <v>11976.191509514</v>
+        <v>11841.2308858513</v>
       </c>
       <c r="HD5" t="n">
-        <v>12019.8843647209</v>
+        <v>11880.7432973721</v>
       </c>
       <c r="HE5" t="n">
-        <v>12067.164610912</v>
+        <v>11923.7615924585</v>
       </c>
       <c r="HF5" t="n">
-        <v>12117.8106503661</v>
+        <v>11970.1355055283</v>
       </c>
       <c r="HG5" t="n">
-        <v>12171.2532597043</v>
+        <v>12019.3401661284</v>
       </c>
       <c r="HH5" t="n">
-        <v>12226.524343973</v>
+        <v>12070.414586989</v>
       </c>
       <c r="HI5" t="n">
-        <v>12283.6272266882</v>
+        <v>12123.3112709849</v>
       </c>
       <c r="HJ5" t="n">
-        <v>12343.1307361148</v>
+        <v>12178.5421515861</v>
       </c>
       <c r="HK5" t="n">
-        <v>12404.9813082739</v>
+        <v>12236.0000785218</v>
       </c>
       <c r="HL5" t="n">
-        <v>12468.1159031349</v>
+        <v>12294.5783683958</v>
       </c>
       <c r="HM5" t="n">
-        <v>12532.4463155266</v>
+        <v>12354.1429627485</v>
       </c>
       <c r="HN5" t="n">
-        <v>12597.9998307526</v>
+        <v>12414.7075422481</v>
       </c>
       <c r="HO5" t="n">
-        <v>12664.3752771138</v>
+        <v>12475.8917555546</v>
       </c>
       <c r="HP5" t="n">
-        <v>12730.2919358776</v>
+        <v>12536.4520288438</v>
       </c>
       <c r="HQ5" t="n">
-        <v>12795.5750663402</v>
+        <v>12596.2379826901</v>
       </c>
       <c r="HR5" t="n">
-        <v>12860.5892102991</v>
+        <v>12655.6516186625</v>
       </c>
       <c r="HS5" t="n">
-        <v>12925.286220336</v>
+        <v>12714.6928759142</v>
       </c>
       <c r="HT5" t="n">
-        <v>12988.3620631666</v>
+        <v>12772.0991766995</v>
       </c>
       <c r="HU5" t="n">
-        <v>13050.3053932041</v>
+        <v>12828.3823337977</v>
       </c>
     </row>
     <row r="6">
@@ -6845,136 +6845,136 @@
         <v>-20.3573504657543</v>
       </c>
       <c r="GD8" t="n">
-        <v>-86.2444237894379</v>
+        <v>-90.2267479885777</v>
       </c>
       <c r="GE8" t="n">
-        <v>1219.64349159921</v>
+        <v>1300.15462222291</v>
       </c>
       <c r="GF8" t="n">
-        <v>811.938125303452</v>
+        <v>750.115392871114</v>
       </c>
       <c r="GG8" t="n">
-        <v>1674.03522173257</v>
+        <v>1622.84160752018</v>
       </c>
       <c r="GH8" t="n">
-        <v>1459.73639659776</v>
+        <v>1388.8628645789</v>
       </c>
       <c r="GI8" t="n">
-        <v>1621.6259701231</v>
+        <v>1542.66794898894</v>
       </c>
       <c r="GJ8" t="n">
-        <v>1583.09384903437</v>
+        <v>1504.82924879182</v>
       </c>
       <c r="GK8" t="n">
-        <v>1527.65100318374</v>
+        <v>1448.01765546089</v>
       </c>
       <c r="GL8" t="n">
-        <v>1516.84339071735</v>
+        <v>1438.90367095036</v>
       </c>
       <c r="GM8" t="n">
-        <v>1481.36079962549</v>
+        <v>1405.02280541571</v>
       </c>
       <c r="GN8" t="n">
-        <v>1452.67988099172</v>
+        <v>1376.3765251381</v>
       </c>
       <c r="GO8" t="n">
-        <v>1341.62620409662</v>
+        <v>1263.83030050105</v>
       </c>
       <c r="GP8" t="n">
-        <v>1317.97650527916</v>
+        <v>1238.66428104902</v>
       </c>
       <c r="GQ8" t="n">
-        <v>1275.98397671347</v>
+        <v>1195.64947604897</v>
       </c>
       <c r="GR8" t="n">
-        <v>1211.96942826631</v>
+        <v>1131.03053443233</v>
       </c>
       <c r="GS8" t="n">
-        <v>1183.64247538027</v>
+        <v>1103.15937470915</v>
       </c>
       <c r="GT8" t="n">
-        <v>1142.76756671391</v>
+        <v>1063.8476710351</v>
       </c>
       <c r="GU8" t="n">
-        <v>1114.77220027073</v>
+        <v>1038.7648048368</v>
       </c>
       <c r="GV8" t="n">
-        <v>1051.09702684908</v>
+        <v>978.7361161359</v>
       </c>
       <c r="GW8" t="n">
-        <v>1035.7870373055</v>
+        <v>967.462204679439</v>
       </c>
       <c r="GX8" t="n">
-        <v>1004.10479868005</v>
+        <v>940.092699646426</v>
       </c>
       <c r="GY8" t="n">
-        <v>991.222463514277</v>
+        <v>931.674309202732</v>
       </c>
       <c r="GZ8" t="n">
-        <v>959.116524622426</v>
+        <v>903.798658655636</v>
       </c>
       <c r="HA8" t="n">
-        <v>952.879553189792</v>
+        <v>901.146800741553</v>
       </c>
       <c r="HB8" t="n">
-        <v>950.541812029551</v>
+        <v>902.067197531054</v>
       </c>
       <c r="HC8" t="n">
-        <v>955.564338994824</v>
+        <v>910.19703106425</v>
       </c>
       <c r="HD8" t="n">
-        <v>909.117595001386</v>
+        <v>866.462253498321</v>
       </c>
       <c r="HE8" t="n">
-        <v>943.3863621692</v>
+        <v>902.9678716505</v>
       </c>
       <c r="HF8" t="n">
-        <v>927.052805730666</v>
+        <v>888.612360439292</v>
       </c>
       <c r="HG8" t="n">
-        <v>938.8360416918</v>
+        <v>902.411000748863</v>
       </c>
       <c r="HH8" t="n">
-        <v>921.873694327747</v>
+        <v>887.3638488836</v>
       </c>
       <c r="HI8" t="n">
-        <v>924.784851582983</v>
+        <v>891.597339597734</v>
       </c>
       <c r="HJ8" t="n">
-        <v>930.290907974617</v>
+        <v>898.380844859144</v>
       </c>
       <c r="HK8" t="n">
-        <v>936.445456705464</v>
+        <v>905.821548136766</v>
       </c>
       <c r="HL8" t="n">
-        <v>921.768969940924</v>
+        <v>892.35852920037</v>
       </c>
       <c r="HM8" t="n">
-        <v>924.284906714311</v>
+        <v>895.498647183762</v>
       </c>
       <c r="HN8" t="n">
-        <v>928.369585165288</v>
+        <v>900.192165837361</v>
       </c>
       <c r="HO8" t="n">
-        <v>931.949207925965</v>
+        <v>904.466480011732</v>
       </c>
       <c r="HP8" t="n">
-        <v>913.382726779993</v>
+        <v>886.597160114878</v>
       </c>
       <c r="HQ8" t="n">
-        <v>909.58827835953</v>
+        <v>882.962041089049</v>
       </c>
       <c r="HR8" t="n">
-        <v>909.178261956171</v>
+        <v>882.816956517723</v>
       </c>
       <c r="HS8" t="n">
-        <v>907.81022613839</v>
+        <v>881.895998697844</v>
       </c>
       <c r="HT8" t="n">
-        <v>835.035050034698</v>
+        <v>809.527680856292</v>
       </c>
       <c r="HU8" t="n">
-        <v>861.630821008002</v>
+        <v>836.217219480255</v>
       </c>
     </row>
     <row r="9">
@@ -8214,139 +8214,139 @@
         <v>680205</v>
       </c>
       <c r="GC10" t="n">
-        <v>686223.124478682</v>
+        <v>686151.698852826</v>
       </c>
       <c r="GD10" t="n">
-        <v>693013.045561194</v>
+        <v>694469.036893127</v>
       </c>
       <c r="GE10" t="n">
-        <v>701634.778565277</v>
+        <v>701634.083487739</v>
       </c>
       <c r="GF10" t="n">
-        <v>709081.328200931</v>
+        <v>707838.19366459</v>
       </c>
       <c r="GG10" t="n">
-        <v>716531.461448296</v>
+        <v>714453.261756663</v>
       </c>
       <c r="GH10" t="n">
-        <v>722008.181389185</v>
+        <v>719156.513632876</v>
       </c>
       <c r="GI10" t="n">
-        <v>726926.707812795</v>
+        <v>723584.950029542</v>
       </c>
       <c r="GJ10" t="n">
-        <v>731020.962508596</v>
+        <v>727300.58684029</v>
       </c>
       <c r="GK10" t="n">
-        <v>735083.313938925</v>
+        <v>731077.234952298</v>
       </c>
       <c r="GL10" t="n">
-        <v>739314.48528744</v>
+        <v>735084.969436484</v>
       </c>
       <c r="GM10" t="n">
-        <v>743394.882933294</v>
+        <v>738943.676405493</v>
       </c>
       <c r="GN10" t="n">
-        <v>746757.694098163</v>
+        <v>742061.275995762</v>
       </c>
       <c r="GO10" t="n">
-        <v>750164.412244528</v>
+        <v>745200.995788866</v>
       </c>
       <c r="GP10" t="n">
-        <v>753956.215412481</v>
+        <v>748718.239887547</v>
       </c>
       <c r="GQ10" t="n">
-        <v>757450.525144089</v>
+        <v>751936.576780454</v>
       </c>
       <c r="GR10" t="n">
-        <v>761133.415928168</v>
+        <v>755352.39725432</v>
       </c>
       <c r="GS10" t="n">
-        <v>764969.634094479</v>
+        <v>758940.218613026</v>
       </c>
       <c r="GT10" t="n">
-        <v>768920.776099925</v>
+        <v>762671.887613351</v>
       </c>
       <c r="GU10" t="n">
-        <v>772586.251578874</v>
+        <v>766145.60080231</v>
       </c>
       <c r="GV10" t="n">
-        <v>776358.319606314</v>
+        <v>769744.054506591</v>
       </c>
       <c r="GW10" t="n">
-        <v>780386.020572208</v>
+        <v>773611.605871397</v>
       </c>
       <c r="GX10" t="n">
-        <v>784591.128115529</v>
+        <v>777666.857876584</v>
       </c>
       <c r="GY10" t="n">
-        <v>788633.802564281</v>
+        <v>781563.220815747</v>
       </c>
       <c r="GZ10" t="n">
-        <v>792885.344044633</v>
+        <v>785659.281869438</v>
       </c>
       <c r="HA10" t="n">
-        <v>797415.297849055</v>
+        <v>790022.802555796</v>
       </c>
       <c r="HB10" t="n">
-        <v>802170.039867806</v>
+        <v>794604.300495477</v>
       </c>
       <c r="HC10" t="n">
-        <v>806619.1587935</v>
+        <v>798873.090572194</v>
       </c>
       <c r="HD10" t="n">
-        <v>811215.928635726</v>
+        <v>803277.304734073</v>
       </c>
       <c r="HE10" t="n">
-        <v>816034.661115189</v>
+        <v>807893.32236988</v>
       </c>
       <c r="HF10" t="n">
-        <v>820886.203095505</v>
+        <v>812539.416419429</v>
       </c>
       <c r="HG10" t="n">
-        <v>825419.865027868</v>
+        <v>816868.543109336</v>
       </c>
       <c r="HH10" t="n">
-        <v>829948.182957116</v>
+        <v>821184.554477399</v>
       </c>
       <c r="HI10" t="n">
-        <v>834607.458061932</v>
+        <v>825626.773308382</v>
       </c>
       <c r="HJ10" t="n">
-        <v>839306.34603109</v>
+        <v>830109.660420463</v>
       </c>
       <c r="HK10" t="n">
-        <v>843613.301166003</v>
+        <v>834204.465185141</v>
       </c>
       <c r="HL10" t="n">
-        <v>847914.921680958</v>
+        <v>838288.076598739</v>
       </c>
       <c r="HM10" t="n">
-        <v>852319.962678997</v>
+        <v>842471.635115262</v>
       </c>
       <c r="HN10" t="n">
-        <v>856740.20747032</v>
+        <v>846673.326402296</v>
       </c>
       <c r="HO10" t="n">
-        <v>860734.748746418</v>
+        <v>850455.69044143</v>
       </c>
       <c r="HP10" t="n">
-        <v>864666.510551157</v>
+        <v>854171.453958644</v>
       </c>
       <c r="HQ10" t="n">
-        <v>868701.870546178</v>
+        <v>857989.739573044</v>
       </c>
       <c r="HR10" t="n">
-        <v>872757.511676905</v>
+        <v>861833.759763501</v>
       </c>
       <c r="HS10" t="n">
-        <v>876274.557709986</v>
+        <v>865146.576287026</v>
       </c>
       <c r="HT10" t="n">
-        <v>879770.663465525</v>
+        <v>868437.579641716</v>
       </c>
       <c r="HU10" t="n">
-        <v>883441.963389559</v>
+        <v>871903.39121881</v>
       </c>
     </row>
     <row r="11">
@@ -8903,139 +8903,139 @@
         <v>170963</v>
       </c>
       <c r="GC11" t="n">
-        <v>167277.531103325</v>
+        <v>167271.046249549</v>
       </c>
       <c r="GD11" t="n">
-        <v>175895.12656163</v>
+        <v>176031.075689716</v>
       </c>
       <c r="GE11" t="n">
-        <v>170895.683828467</v>
+        <v>170865.182394169</v>
       </c>
       <c r="GF11" t="n">
-        <v>176754.459816398</v>
+        <v>176644.965638819</v>
       </c>
       <c r="GG11" t="n">
-        <v>176358.026882616</v>
+        <v>176200.884370134</v>
       </c>
       <c r="GH11" t="n">
-        <v>177586.173408747</v>
+        <v>177377.736414144</v>
       </c>
       <c r="GI11" t="n">
-        <v>178392.101007113</v>
+        <v>178151.71278162</v>
       </c>
       <c r="GJ11" t="n">
-        <v>178532.095522213</v>
+        <v>178261.754958415</v>
       </c>
       <c r="GK11" t="n">
-        <v>179111.666639002</v>
+        <v>178815.627147161</v>
       </c>
       <c r="GL11" t="n">
-        <v>179576.174739626</v>
+        <v>179257.031787558</v>
       </c>
       <c r="GM11" t="n">
-        <v>180360.836221725</v>
+        <v>180016.825957266</v>
       </c>
       <c r="GN11" t="n">
-        <v>180349.671612747</v>
+        <v>179978.181390585</v>
       </c>
       <c r="GO11" t="n">
-        <v>180805.6273347</v>
+        <v>180405.008175008</v>
       </c>
       <c r="GP11" t="n">
-        <v>181171.716468612</v>
+        <v>180741.978653783</v>
       </c>
       <c r="GQ11" t="n">
-        <v>181396.462367013</v>
+        <v>180938.133373195</v>
       </c>
       <c r="GR11" t="n">
-        <v>181735.980473077</v>
+        <v>181250.524981689</v>
       </c>
       <c r="GS11" t="n">
-        <v>181994.665490263</v>
+        <v>181484.448091708</v>
       </c>
       <c r="GT11" t="n">
-        <v>182290.263925667</v>
+        <v>181758.469971378</v>
       </c>
       <c r="GU11" t="n">
-        <v>182356.457073952</v>
+        <v>181806.108455316</v>
       </c>
       <c r="GV11" t="n">
-        <v>182688.187904009</v>
+        <v>182121.450541807</v>
       </c>
       <c r="GW11" t="n">
-        <v>182868.671888492</v>
+        <v>182287.604716295</v>
       </c>
       <c r="GX11" t="n">
-        <v>183119.63108947</v>
+        <v>182526.076302904</v>
       </c>
       <c r="GY11" t="n">
-        <v>183331.073787876</v>
+        <v>182726.345893527</v>
       </c>
       <c r="GZ11" t="n">
-        <v>183589.127776555</v>
+        <v>182973.490123307</v>
       </c>
       <c r="HA11" t="n">
-        <v>183868.898548623</v>
+        <v>183242.679900441</v>
       </c>
       <c r="HB11" t="n">
-        <v>184183.103904358</v>
+        <v>183546.983033183</v>
       </c>
       <c r="HC11" t="n">
-        <v>184088.665504951</v>
+        <v>183443.217284496</v>
       </c>
       <c r="HD11" t="n">
-        <v>184585.881670206</v>
+        <v>183930.945772444</v>
       </c>
       <c r="HE11" t="n">
-        <v>184724.624347844</v>
+        <v>184060.468258546</v>
       </c>
       <c r="HF11" t="n">
-        <v>184990.31937484</v>
+        <v>184317.628546567</v>
       </c>
       <c r="HG11" t="n">
-        <v>185221.175727776</v>
+        <v>184540.729144367</v>
       </c>
       <c r="HH11" t="n">
-        <v>185486.805786536</v>
+        <v>184798.479703433</v>
       </c>
       <c r="HI11" t="n">
-        <v>185781.932542608</v>
+        <v>185086.010393281</v>
       </c>
       <c r="HJ11" t="n">
-        <v>186098.481925697</v>
+        <v>185395.630212838</v>
       </c>
       <c r="HK11" t="n">
-        <v>186401.018414366</v>
+        <v>185691.925744991</v>
       </c>
       <c r="HL11" t="n">
-        <v>186729.997246618</v>
+        <v>186014.436284361</v>
       </c>
       <c r="HM11" t="n">
-        <v>187085.599091703</v>
+        <v>186363.765723082</v>
       </c>
       <c r="HN11" t="n">
-        <v>187457.757176859</v>
+        <v>186730.311996738</v>
       </c>
       <c r="HO11" t="n">
-        <v>187811.1271084</v>
+        <v>187078.793668092</v>
       </c>
       <c r="HP11" t="n">
-        <v>188183.477860671</v>
+        <v>187446.061250915</v>
       </c>
       <c r="HQ11" t="n">
-        <v>188580.305781173</v>
+        <v>187838.127408312</v>
       </c>
       <c r="HR11" t="n">
-        <v>188990.832562807</v>
+        <v>188244.707910165</v>
       </c>
       <c r="HS11" t="n">
-        <v>188776.358860941</v>
+        <v>188027.033738587</v>
       </c>
       <c r="HT11" t="n">
-        <v>189309.582121317</v>
+        <v>188557.058287394</v>
       </c>
       <c r="HU11" t="n">
-        <v>189353.895806941</v>
+        <v>188598.578621348</v>
       </c>
     </row>
     <row r="12">
@@ -9592,139 +9592,139 @@
         <v>162177</v>
       </c>
       <c r="GC12" t="n">
-        <v>164151.220763404</v>
+        <v>164127.999631379</v>
       </c>
       <c r="GD12" t="n">
-        <v>165737.970888426</v>
+        <v>166239.28472695</v>
       </c>
       <c r="GE12" t="n">
-        <v>167732.560208389</v>
+        <v>167937.232204659</v>
       </c>
       <c r="GF12" t="n">
-        <v>169731.054353171</v>
+        <v>169303.160264164</v>
       </c>
       <c r="GG12" t="n">
-        <v>171601.617270488</v>
+        <v>170725.438426201</v>
       </c>
       <c r="GH12" t="n">
-        <v>172921.505779413</v>
+        <v>171680.898325422</v>
       </c>
       <c r="GI12" t="n">
-        <v>173770.17594194</v>
+        <v>172317.179089587</v>
       </c>
       <c r="GJ12" t="n">
-        <v>174257.041115777</v>
+        <v>172682.899339875</v>
       </c>
       <c r="GK12" t="n">
-        <v>174748.322137028</v>
+        <v>173114.338580482</v>
       </c>
       <c r="GL12" t="n">
-        <v>175441.710350346</v>
+        <v>173789.024288664</v>
       </c>
       <c r="GM12" t="n">
-        <v>176401.67044174</v>
+        <v>174742.11602585</v>
       </c>
       <c r="GN12" t="n">
-        <v>177039.577270137</v>
+        <v>175369.851845832</v>
       </c>
       <c r="GO12" t="n">
-        <v>177696.753367226</v>
+        <v>176004.791162634</v>
       </c>
       <c r="GP12" t="n">
-        <v>178594.719967597</v>
+        <v>176870.73038177</v>
       </c>
       <c r="GQ12" t="n">
-        <v>179554.13247014</v>
+        <v>177791.069599422</v>
       </c>
       <c r="GR12" t="n">
-        <v>180618.422744395</v>
+        <v>178811.854088297</v>
       </c>
       <c r="GS12" t="n">
-        <v>181853.630070112</v>
+        <v>180002.215002907</v>
       </c>
       <c r="GT12" t="n">
-        <v>183233.619959234</v>
+        <v>181339.807857352</v>
       </c>
       <c r="GU12" t="n">
-        <v>184612.859591181</v>
+        <v>182679.735025345</v>
       </c>
       <c r="GV12" t="n">
-        <v>186052.491501856</v>
+        <v>184079.125247573</v>
       </c>
       <c r="GW12" t="n">
-        <v>187652.545292179</v>
+        <v>185634.647243332</v>
       </c>
       <c r="GX12" t="n">
-        <v>189398.5445605</v>
+        <v>187330.211164966</v>
       </c>
       <c r="GY12" t="n">
-        <v>191153.774298721</v>
+        <v>189027.074370099</v>
       </c>
       <c r="GZ12" t="n">
-        <v>192984.659658753</v>
+        <v>190786.82471245</v>
       </c>
       <c r="HA12" t="n">
-        <v>194959.224310341</v>
+        <v>192675.659863394</v>
       </c>
       <c r="HB12" t="n">
-        <v>197065.805925496</v>
+        <v>194683.920846349</v>
       </c>
       <c r="HC12" t="n">
-        <v>199102.769701954</v>
+        <v>196612.082723308</v>
       </c>
       <c r="HD12" t="n">
-        <v>201142.45591873</v>
+        <v>198531.443002212</v>
       </c>
       <c r="HE12" t="n">
-        <v>203272.430266631</v>
+        <v>200530.244647584</v>
       </c>
       <c r="HF12" t="n">
-        <v>205433.2597091</v>
+        <v>202553.034821691</v>
       </c>
       <c r="HG12" t="n">
-        <v>207472.203709057</v>
+        <v>204450.972474851</v>
       </c>
       <c r="HH12" t="n">
-        <v>209443.57294523</v>
+        <v>206276.578665875</v>
       </c>
       <c r="HI12" t="n">
-        <v>211444.041286388</v>
+        <v>208126.568088835</v>
       </c>
       <c r="HJ12" t="n">
-        <v>213461.186804231</v>
+        <v>209991.700053094</v>
       </c>
       <c r="HK12" t="n">
-        <v>215330.567650062</v>
+        <v>211710.894272675</v>
       </c>
       <c r="HL12" t="n">
-        <v>217124.012060864</v>
+        <v>213353.146507385</v>
       </c>
       <c r="HM12" t="n">
-        <v>218945.287952665</v>
+        <v>215021.366850103</v>
       </c>
       <c r="HN12" t="n">
-        <v>220781.471910402</v>
+        <v>216705.657919522</v>
       </c>
       <c r="HO12" t="n">
-        <v>222465.130732645</v>
+        <v>218242.222005186</v>
       </c>
       <c r="HP12" t="n">
-        <v>224061.977433061</v>
+        <v>219693.46952269</v>
       </c>
       <c r="HQ12" t="n">
-        <v>225693.437708638</v>
+        <v>221179.431208337</v>
       </c>
       <c r="HR12" t="n">
-        <v>227356.992484466</v>
+        <v>222700.395233656</v>
       </c>
       <c r="HS12" t="n">
-        <v>228843.814168888</v>
+        <v>224050.96023316</v>
       </c>
       <c r="HT12" t="n">
-        <v>230255.578390563</v>
+        <v>225329.288560287</v>
       </c>
       <c r="HU12" t="n">
-        <v>231749.682344607</v>
+        <v>226690.202499314</v>
       </c>
     </row>
     <row r="13">
@@ -10281,139 +10281,139 @@
         <v>688271</v>
       </c>
       <c r="GC13" t="n">
-        <v>688919.4526957</v>
+        <v>688864.763365552</v>
       </c>
       <c r="GD13" t="n">
-        <v>702740.222489689</v>
+        <v>703830.84954872</v>
       </c>
       <c r="GE13" t="n">
-        <v>704367.925018541</v>
+        <v>704132.055984009</v>
       </c>
       <c r="GF13" t="n">
-        <v>715674.756586436</v>
+        <v>714750.021573421</v>
       </c>
       <c r="GG13" t="n">
-        <v>720857.895280625</v>
+        <v>719498.731692409</v>
       </c>
       <c r="GH13" t="n">
-        <v>726242.873442222</v>
+        <v>724423.374010534</v>
       </c>
       <c r="GI13" t="n">
-        <v>731118.656860063</v>
+        <v>728989.507649247</v>
       </c>
       <c r="GJ13" t="n">
-        <v>734866.04047816</v>
+        <v>732449.466179321</v>
       </c>
       <c r="GK13" t="n">
-        <v>739016.681336514</v>
+        <v>736348.54674915</v>
       </c>
       <c r="GL13" t="n">
-        <v>743018.973918343</v>
+        <v>740122.999693959</v>
       </c>
       <c r="GM13" t="n">
-        <v>746924.072368229</v>
+        <v>743788.40869606</v>
       </c>
       <c r="GN13" t="n">
-        <v>749637.81189496</v>
+        <v>746239.627935882</v>
       </c>
       <c r="GO13" t="n">
-        <v>752843.309376913</v>
+        <v>749171.237096983</v>
       </c>
       <c r="GP13" t="n">
-        <v>756103.236710332</v>
+        <v>752159.512213833</v>
       </c>
       <c r="GQ13" t="n">
-        <v>758862.879452743</v>
+        <v>754653.664396219</v>
       </c>
       <c r="GR13" t="n">
-        <v>761820.997457159</v>
+        <v>757361.091511131</v>
       </c>
       <c r="GS13" t="n">
-        <v>764680.69268911</v>
+        <v>759992.474538354</v>
       </c>
       <c r="GT13" t="n">
-        <v>767547.444488612</v>
+        <v>762660.573817417</v>
       </c>
       <c r="GU13" t="n">
-        <v>769899.87274692</v>
+        <v>764841.997617819</v>
       </c>
       <c r="GV13" t="n">
-        <v>772564.040785468</v>
+        <v>767356.404221362</v>
       </c>
       <c r="GW13" t="n">
-        <v>775172.170852822</v>
+        <v>769834.58665443</v>
       </c>
       <c r="GX13" t="n">
-        <v>777882.239059528</v>
+        <v>772432.746960698</v>
       </c>
       <c r="GY13" t="n">
-        <v>780381.127076647</v>
+        <v>774832.516786322</v>
       </c>
       <c r="GZ13" t="n">
-        <v>783059.837484371</v>
+        <v>777415.971921536</v>
       </c>
       <c r="HA13" t="n">
-        <v>785894.99747057</v>
+        <v>780159.847202067</v>
       </c>
       <c r="HB13" t="n">
-        <v>788857.362977756</v>
+        <v>783037.389057773</v>
       </c>
       <c r="HC13" t="n">
-        <v>791175.081737902</v>
+        <v>785274.251252425</v>
       </c>
       <c r="HD13" t="n">
-        <v>794229.380824643</v>
+        <v>788246.832876149</v>
       </c>
       <c r="HE13" t="n">
-        <v>797056.883120157</v>
+        <v>790993.572697295</v>
       </c>
       <c r="HF13" t="n">
-        <v>800013.28967364</v>
+        <v>793874.03583562</v>
       </c>
       <c r="HG13" t="n">
-        <v>802738.865166105</v>
+        <v>796528.326599885</v>
       </c>
       <c r="HH13" t="n">
-        <v>805561.442768552</v>
+        <v>799276.483460888</v>
       </c>
       <c r="HI13" t="n">
-        <v>808515.377338633</v>
+        <v>802156.242258312</v>
       </c>
       <c r="HJ13" t="n">
-        <v>811513.67013494</v>
+        <v>805083.61810318</v>
       </c>
       <c r="HK13" t="n">
-        <v>814253.781906246</v>
+        <v>807755.525110946</v>
       </c>
       <c r="HL13" t="n">
-        <v>817090.935250896</v>
+        <v>810519.395674786</v>
       </c>
       <c r="HM13" t="n">
-        <v>820030.302995427</v>
+        <v>813384.061657148</v>
       </c>
       <c r="HN13" t="n">
-        <v>822986.52269929</v>
+        <v>816268.00886243</v>
       </c>
       <c r="HO13" t="n">
-        <v>825650.775952311</v>
+        <v>818862.291296526</v>
       </c>
       <c r="HP13" t="n">
-        <v>828358.042779065</v>
+        <v>821494.075798863</v>
       </c>
       <c r="HQ13" t="n">
-        <v>831158.768637887</v>
+        <v>824218.466765003</v>
       </c>
       <c r="HR13" t="n">
-        <v>833961.382594759</v>
+        <v>826948.101658237</v>
       </c>
       <c r="HS13" t="n">
-        <v>835777.134655104</v>
+        <v>828692.680348822</v>
       </c>
       <c r="HT13" t="n">
-        <v>838394.697813545</v>
+        <v>831235.381014186</v>
       </c>
       <c r="HU13" t="n">
-        <v>840616.20867275</v>
+        <v>833381.797542954</v>
       </c>
     </row>
     <row r="14">
@@ -10802,139 +10802,139 @@
         <v>681761</v>
       </c>
       <c r="GC14" t="n">
-        <v>686084.528352771</v>
+        <v>686013.110077929</v>
       </c>
       <c r="GD14" t="n">
-        <v>692940.300289779</v>
+        <v>694400.273349485</v>
       </c>
       <c r="GE14" t="n">
-        <v>700256.148166028</v>
+        <v>700174.941883743</v>
       </c>
       <c r="GF14" t="n">
-        <v>708110.399358663</v>
+        <v>706929.088411136</v>
       </c>
       <c r="GG14" t="n">
-        <v>714698.437045676</v>
+        <v>712671.431778864</v>
       </c>
       <c r="GH14" t="n">
-        <v>720389.45648651</v>
+        <v>717608.661606568</v>
       </c>
       <c r="GI14" t="n">
-        <v>725146.093502638</v>
+        <v>721883.294219463</v>
       </c>
       <c r="GJ14" t="n">
-        <v>729278.880214815</v>
+        <v>725636.769639405</v>
       </c>
       <c r="GK14" t="n">
-        <v>733396.674036147</v>
+        <v>729470.228951247</v>
       </c>
       <c r="GL14" t="n">
-        <v>737638.653752083</v>
+        <v>733487.077052758</v>
       </c>
       <c r="GM14" t="n">
-        <v>741754.533752303</v>
+        <v>737379.66480841</v>
       </c>
       <c r="GN14" t="n">
-        <v>745146.025341888</v>
+        <v>740525.910482556</v>
       </c>
       <c r="GO14" t="n">
-        <v>748663.7966459</v>
+        <v>743778.177580505</v>
       </c>
       <c r="GP14" t="n">
-        <v>752479.250311252</v>
+        <v>747320.587442893</v>
       </c>
       <c r="GQ14" t="n">
-        <v>756015.552247049</v>
+        <v>750581.939056286</v>
       </c>
       <c r="GR14" t="n">
-        <v>759762.45716806</v>
+        <v>754062.378227655</v>
       </c>
       <c r="GS14" t="n">
-        <v>763627.001935156</v>
+        <v>757678.07051085</v>
       </c>
       <c r="GT14" t="n">
-        <v>767619.019762511</v>
+        <v>761449.052235006</v>
       </c>
       <c r="GU14" t="n">
-        <v>771312.490334562</v>
+        <v>764947.848035862</v>
       </c>
       <c r="GV14" t="n">
-        <v>775148.234474587</v>
+        <v>768606.331382509</v>
       </c>
       <c r="GW14" t="n">
-        <v>779191.244856735</v>
+        <v>772485.156007613</v>
       </c>
       <c r="GX14" t="n">
-        <v>783428.035265202</v>
+        <v>776567.77807509</v>
       </c>
       <c r="GY14" t="n">
-        <v>787483.592612095</v>
+        <v>780472.559873225</v>
       </c>
       <c r="GZ14" t="n">
-        <v>791767.240308352</v>
+        <v>784596.496739006</v>
       </c>
       <c r="HA14" t="n">
-        <v>796303.431095597</v>
+        <v>788962.669178936</v>
       </c>
       <c r="HB14" t="n">
-        <v>801060.510537646</v>
+        <v>793543.247837884</v>
       </c>
       <c r="HC14" t="n">
-        <v>805504.6082705</v>
+        <v>797803.907770255</v>
       </c>
       <c r="HD14" t="n">
-        <v>810147.824150371</v>
+        <v>802251.85591178</v>
       </c>
       <c r="HE14" t="n">
-        <v>814932.288643449</v>
+        <v>806831.368628584</v>
       </c>
       <c r="HF14" t="n">
-        <v>819800.163186731</v>
+        <v>811491.817153433</v>
       </c>
       <c r="HG14" t="n">
-        <v>824322.042502967</v>
+        <v>815807.145706852</v>
       </c>
       <c r="HH14" t="n">
-        <v>828867.321643037</v>
+        <v>820138.204594016</v>
       </c>
       <c r="HI14" t="n">
-        <v>833523.685817943</v>
+        <v>824576.188596444</v>
       </c>
       <c r="HJ14" t="n">
-        <v>838217.067870954</v>
+        <v>829052.292312132</v>
       </c>
       <c r="HK14" t="n">
-        <v>842517.868685344</v>
+        <v>833139.656556559</v>
       </c>
       <c r="HL14" t="n">
-        <v>846834.164249379</v>
+        <v>837236.731124829</v>
       </c>
       <c r="HM14" t="n">
-        <v>851236.689378027</v>
+        <v>841417.148015816</v>
       </c>
       <c r="HN14" t="n">
-        <v>855652.849476477</v>
+        <v>845614.145780745</v>
       </c>
       <c r="HO14" t="n">
-        <v>859643.811267498</v>
+        <v>849392.235641785</v>
       </c>
       <c r="HP14" t="n">
-        <v>863594.139755411</v>
+        <v>853125.868677454</v>
       </c>
       <c r="HQ14" t="n">
-        <v>867633.292785636</v>
+        <v>856947.789587209</v>
       </c>
       <c r="HR14" t="n">
-        <v>871689.344045084</v>
+        <v>860791.953423659</v>
       </c>
       <c r="HS14" t="n">
-        <v>875207.758667639</v>
+        <v>864105.691493479</v>
       </c>
       <c r="HT14" t="n">
-        <v>878776.638425049</v>
+        <v>867469.06358935</v>
       </c>
       <c r="HU14" t="n">
-        <v>882421.343076414</v>
+        <v>870908.184557711</v>
       </c>
     </row>
     <row r="15">
@@ -11491,139 +11491,139 @@
         <v>718591</v>
       </c>
       <c r="GC15" t="n">
-        <v>722503.917694143</v>
+        <v>722446.302045062</v>
       </c>
       <c r="GD15" t="n">
-        <v>745057.79470314</v>
+        <v>746841.514138348</v>
       </c>
       <c r="GE15" t="n">
-        <v>757298.70344948</v>
+        <v>757812.555747706</v>
       </c>
       <c r="GF15" t="n">
-        <v>778452.083424455</v>
+        <v>778371.835122549</v>
       </c>
       <c r="GG15" t="n">
-        <v>794307.940319648</v>
+        <v>793842.402552691</v>
       </c>
       <c r="GH15" t="n">
-        <v>808925.051257746</v>
+        <v>807990.766741129</v>
       </c>
       <c r="GI15" t="n">
-        <v>823142.830981455</v>
+        <v>821810.431404711</v>
       </c>
       <c r="GJ15" t="n">
-        <v>836451.494189787</v>
+        <v>834703.713560883</v>
       </c>
       <c r="GK15" t="n">
-        <v>850207.474244808</v>
+        <v>848043.203719166</v>
       </c>
       <c r="GL15" t="n">
-        <v>863679.50219178</v>
+        <v>861102.643279916</v>
       </c>
       <c r="GM15" t="n">
-        <v>876622.487374243</v>
+        <v>873597.576270051</v>
       </c>
       <c r="GN15" t="n">
-        <v>888555.705693557</v>
+        <v>885059.331284632</v>
       </c>
       <c r="GO15" t="n">
-        <v>901008.451226819</v>
+        <v>897019.262146209</v>
       </c>
       <c r="GP15" t="n">
-        <v>913648.153304255</v>
+        <v>909164.944193245</v>
       </c>
       <c r="GQ15" t="n">
-        <v>925671.942457966</v>
+        <v>920700.640583452</v>
       </c>
       <c r="GR15" t="n">
-        <v>937910.775864315</v>
+        <v>932467.547069454</v>
       </c>
       <c r="GS15" t="n">
-        <v>950043.445541395</v>
+        <v>944155.413596801</v>
       </c>
       <c r="GT15" t="n">
-        <v>962280.463938404</v>
+        <v>955984.012813794</v>
       </c>
       <c r="GU15" t="n">
-        <v>973956.025713916</v>
+        <v>967288.147677384</v>
       </c>
       <c r="GV15" t="n">
-        <v>986009.001759324</v>
+        <v>978997.28482864</v>
       </c>
       <c r="GW15" t="n">
-        <v>998118.827857557</v>
+        <v>990789.867865746</v>
       </c>
       <c r="GX15" t="n">
-        <v>1010468.35416493</v>
+        <v>1002845.58428255</v>
       </c>
       <c r="GY15" t="n">
-        <v>1022657.20685399</v>
+        <v>1014757.8865042</v>
       </c>
       <c r="GZ15" t="n">
-        <v>1035212.56531707</v>
+        <v>1027039.49946996</v>
       </c>
       <c r="HA15" t="n">
-        <v>1048136.83072038</v>
+        <v>1039691.65308855</v>
       </c>
       <c r="HB15" t="n">
-        <v>1061665.66408999</v>
+        <v>1052952.94733534</v>
       </c>
       <c r="HC15" t="n">
-        <v>1074641.36257305</v>
+        <v>1065661.62884991</v>
       </c>
       <c r="HD15" t="n">
-        <v>1088609.89195036</v>
+        <v>1079358.52194496</v>
       </c>
       <c r="HE15" t="n">
-        <v>1102640.51166372</v>
+        <v>1093109.61096019</v>
       </c>
       <c r="HF15" t="n">
-        <v>1117044.60380535</v>
+        <v>1107234.20815783</v>
       </c>
       <c r="HG15" t="n">
-        <v>1131345.4023421</v>
+        <v>1121256.68955603</v>
       </c>
       <c r="HH15" t="n">
-        <v>1145999.49843295</v>
+        <v>1135620.57414407</v>
       </c>
       <c r="HI15" t="n">
-        <v>1161077.10335679</v>
+        <v>1150398.95882404</v>
       </c>
       <c r="HJ15" t="n">
-        <v>1176462.2005985</v>
+        <v>1165479.96961579</v>
       </c>
       <c r="HK15" t="n">
-        <v>1191690.75327024</v>
+        <v>1180401.49897993</v>
       </c>
       <c r="HL15" t="n">
-        <v>1207289.52999797</v>
+        <v>1195675.87276343</v>
       </c>
       <c r="HM15" t="n">
-        <v>1223283.48436327</v>
+        <v>1211331.22806387</v>
       </c>
       <c r="HN15" t="n">
-        <v>1239552.32481554</v>
+        <v>1227252.81136499</v>
       </c>
       <c r="HO15" t="n">
-        <v>1255597.33814202</v>
+        <v>1242945.33516719</v>
       </c>
       <c r="HP15" t="n">
-        <v>1271924.47473347</v>
+        <v>1258900.15350632</v>
       </c>
       <c r="HQ15" t="n">
-        <v>1288633.63281366</v>
+        <v>1275221.73057883</v>
       </c>
       <c r="HR15" t="n">
-        <v>1305591.44198557</v>
+        <v>1291783.46875486</v>
       </c>
       <c r="HS15" t="n">
-        <v>1321492.40868137</v>
+        <v>1307274.16872154</v>
       </c>
       <c r="HT15" t="n">
-        <v>1338505.12178683</v>
+        <v>1323868.70714823</v>
       </c>
       <c r="HU15" t="n">
-        <v>1355358.82584273</v>
+        <v>1340281.99477371</v>
       </c>
     </row>
     <row r="16">
@@ -12180,139 +12180,139 @@
         <v>1.04405241540033</v>
       </c>
       <c r="GC16" t="n">
-        <v>1.04874943516838</v>
+        <v>1.04874901737806</v>
       </c>
       <c r="GD16" t="n">
-        <v>1.06021794612125</v>
+        <v>1.06110937297941</v>
       </c>
       <c r="GE16" t="n">
-        <v>1.07514649246532</v>
+        <v>1.0762364089767</v>
       </c>
       <c r="GF16" t="n">
-        <v>1.08771766747202</v>
+        <v>1.08901267043912</v>
       </c>
       <c r="GG16" t="n">
-        <v>1.10189253313743</v>
+        <v>1.10332702677654</v>
       </c>
       <c r="GH16" t="n">
-        <v>1.11384919854822</v>
+        <v>1.11535710904923</v>
       </c>
       <c r="GI16" t="n">
-        <v>1.12586762042517</v>
+        <v>1.12732819417544</v>
       </c>
       <c r="GJ16" t="n">
-        <v>1.13823668578227</v>
+        <v>1.13960586602926</v>
       </c>
       <c r="GK16" t="n">
-        <v>1.15045774803798</v>
+        <v>1.15168720392873</v>
       </c>
       <c r="GL16" t="n">
-        <v>1.16239224805361</v>
+        <v>1.16345882946938</v>
       </c>
       <c r="GM16" t="n">
-        <v>1.17364336397154</v>
+        <v>1.17452431628372</v>
       </c>
       <c r="GN16" t="n">
-        <v>1.1853133419446</v>
+        <v>1.18602563439812</v>
       </c>
       <c r="GO16" t="n">
-        <v>1.19680740348115</v>
+        <v>1.19734877146588</v>
       </c>
       <c r="GP16" t="n">
-        <v>1.20836428800328</v>
+        <v>1.20873954028807</v>
       </c>
       <c r="GQ16" t="n">
-        <v>1.21981449362494</v>
+        <v>1.22003070218728</v>
       </c>
       <c r="GR16" t="n">
-        <v>1.23114324220087</v>
+        <v>1.23120603552548</v>
       </c>
       <c r="GS16" t="n">
-        <v>1.2424054271835</v>
+        <v>1.24232205618705</v>
       </c>
       <c r="GT16" t="n">
-        <v>1.25370811728533</v>
+        <v>1.25348555610129</v>
       </c>
       <c r="GU16" t="n">
-        <v>1.2650424527813</v>
+        <v>1.26469016000331</v>
       </c>
       <c r="GV16" t="n">
-        <v>1.27628125027775</v>
+        <v>1.27580519375047</v>
       </c>
       <c r="GW16" t="n">
-        <v>1.28760920883485</v>
+        <v>1.28701656908349</v>
       </c>
       <c r="GX16" t="n">
-        <v>1.29899913007127</v>
+        <v>1.29829501498549</v>
       </c>
       <c r="GY16" t="n">
-        <v>1.31045865780579</v>
+        <v>1.30964803986344</v>
       </c>
       <c r="GZ16" t="n">
-        <v>1.32200952317615</v>
+        <v>1.3210939013468</v>
       </c>
       <c r="HA16" t="n">
-        <v>1.33368558190408</v>
+        <v>1.33266490950204</v>
       </c>
       <c r="HB16" t="n">
-        <v>1.34582715343616</v>
+        <v>1.34470328059357</v>
       </c>
       <c r="HC16" t="n">
-        <v>1.35828514071597</v>
+        <v>1.35705662675721</v>
       </c>
       <c r="HD16" t="n">
-        <v>1.37064922499956</v>
+        <v>1.36931538863851</v>
       </c>
       <c r="HE16" t="n">
-        <v>1.38338997786188</v>
+        <v>1.3819449919264</v>
       </c>
       <c r="HF16" t="n">
-        <v>1.39628254799879</v>
+        <v>1.39472277999806</v>
       </c>
       <c r="HG16" t="n">
-        <v>1.40935669249114</v>
+        <v>1.40767960809104</v>
       </c>
       <c r="HH16" t="n">
-        <v>1.42260965550787</v>
+        <v>1.42081068251165</v>
       </c>
       <c r="HI16" t="n">
-        <v>1.43606061477482</v>
+        <v>1.43413326300208</v>
       </c>
       <c r="HJ16" t="n">
-        <v>1.44971333024404</v>
+        <v>1.44765081817792</v>
       </c>
       <c r="HK16" t="n">
-        <v>1.46353724448202</v>
+        <v>1.46133508187091</v>
       </c>
       <c r="HL16" t="n">
-        <v>1.47754608395669</v>
+        <v>1.47519709607504</v>
       </c>
       <c r="HM16" t="n">
-        <v>1.49175397513009</v>
+        <v>1.48924876921977</v>
       </c>
       <c r="HN16" t="n">
-        <v>1.50616355005497</v>
+        <v>1.50349245726812</v>
       </c>
       <c r="HO16" t="n">
-        <v>1.52073655205317</v>
+        <v>1.51789297178096</v>
       </c>
       <c r="HP16" t="n">
-        <v>1.53547666993771</v>
+        <v>1.53245187132347</v>
       </c>
       <c r="HQ16" t="n">
-        <v>1.55040607728885</v>
+        <v>1.547188956263</v>
       </c>
       <c r="HR16" t="n">
-        <v>1.5655298202253</v>
+        <v>1.56210945261425</v>
       </c>
       <c r="HS16" t="n">
-        <v>1.58115402252339</v>
+        <v>1.5775138072232</v>
       </c>
       <c r="HT16" t="n">
-        <v>1.59650948936678</v>
+        <v>1.59265198835721</v>
       </c>
       <c r="HU16" t="n">
-        <v>1.61233959015163</v>
+        <v>1.60824483242988</v>
       </c>
     </row>
     <row r="17">
@@ -12869,139 +12869,139 @@
         <v>143.5</v>
       </c>
       <c r="GC17" t="n">
-        <v>144.862254063989</v>
+        <v>144.861693768467</v>
       </c>
       <c r="GD17" t="n">
-        <v>146.357242915682</v>
+        <v>146.572442197371</v>
       </c>
       <c r="GE17" t="n">
-        <v>148.035797596925</v>
+        <v>148.246978513999</v>
       </c>
       <c r="GF17" t="n">
-        <v>149.827169875167</v>
+        <v>150.071786547243</v>
       </c>
       <c r="GG17" t="n">
-        <v>151.669239888509</v>
+        <v>151.922234841203</v>
       </c>
       <c r="GH17" t="n">
-        <v>153.565957247488</v>
+        <v>153.814321481773</v>
       </c>
       <c r="GI17" t="n">
-        <v>155.508650265794</v>
+        <v>155.7401265663</v>
       </c>
       <c r="GJ17" t="n">
-        <v>157.470226368625</v>
+        <v>157.671477678942</v>
       </c>
       <c r="GK17" t="n">
-        <v>159.435009998264</v>
+        <v>159.601649428925</v>
       </c>
       <c r="GL17" t="n">
-        <v>161.387801777659</v>
+        <v>161.516062281551</v>
       </c>
       <c r="GM17" t="n">
-        <v>163.306508113754</v>
+        <v>163.39466789876</v>
       </c>
       <c r="GN17" t="n">
-        <v>165.194361556554</v>
+        <v>165.242238262515</v>
       </c>
       <c r="GO17" t="n">
-        <v>167.061308222207</v>
+        <v>167.069663394763</v>
       </c>
       <c r="GP17" t="n">
-        <v>168.906198716389</v>
+        <v>168.876185763166</v>
       </c>
       <c r="GQ17" t="n">
-        <v>170.726198556729</v>
+        <v>170.659398523144</v>
       </c>
       <c r="GR17" t="n">
-        <v>172.534325627709</v>
+        <v>172.432569548588</v>
       </c>
       <c r="GS17" t="n">
-        <v>174.326565264684</v>
+        <v>174.191904282396</v>
       </c>
       <c r="GT17" t="n">
-        <v>176.10884447365</v>
+        <v>175.943644203024</v>
       </c>
       <c r="GU17" t="n">
-        <v>177.878635893466</v>
+        <v>177.685588533037</v>
       </c>
       <c r="GV17" t="n">
-        <v>179.645382062699</v>
+        <v>179.427279954816</v>
       </c>
       <c r="GW17" t="n">
-        <v>181.40947572753</v>
+        <v>181.169140122598</v>
       </c>
       <c r="GX17" t="n">
-        <v>183.174934279189</v>
+        <v>182.915188843591</v>
       </c>
       <c r="GY17" t="n">
-        <v>184.942058949788</v>
+        <v>184.665705424226</v>
       </c>
       <c r="GZ17" t="n">
-        <v>186.720421057976</v>
+        <v>186.429953443277</v>
       </c>
       <c r="HA17" t="n">
-        <v>188.509566801523</v>
+        <v>188.207223893322</v>
       </c>
       <c r="HB17" t="n">
-        <v>190.314776816744</v>
+        <v>190.002523766819</v>
       </c>
       <c r="HC17" t="n">
-        <v>192.132653520934</v>
+        <v>191.812302508562</v>
       </c>
       <c r="HD17" t="n">
-        <v>193.977013365663</v>
+        <v>193.649904101166</v>
       </c>
       <c r="HE17" t="n">
-        <v>195.841915167937</v>
+        <v>195.509052412018</v>
       </c>
       <c r="HF17" t="n">
-        <v>197.732627905663</v>
+        <v>197.394813030331</v>
       </c>
       <c r="HG17" t="n">
-        <v>199.647084584644</v>
+        <v>199.304926863459</v>
       </c>
       <c r="HH17" t="n">
-        <v>201.590180284239</v>
+        <v>201.243989917157</v>
       </c>
       <c r="HI17" t="n">
-        <v>203.561548851848</v>
+        <v>203.211414099388</v>
       </c>
       <c r="HJ17" t="n">
-        <v>205.561789550175</v>
+        <v>205.207627810989</v>
       </c>
       <c r="HK17" t="n">
-        <v>207.588446625889</v>
+        <v>207.230117487494</v>
       </c>
       <c r="HL17" t="n">
-        <v>209.647141830796</v>
+        <v>209.284264076582</v>
       </c>
       <c r="HM17" t="n">
-        <v>211.734845988832</v>
+        <v>211.366910118493</v>
       </c>
       <c r="HN17" t="n">
-        <v>213.851984504877</v>
+        <v>213.478403201183</v>
       </c>
       <c r="HO17" t="n">
-        <v>215.995040848376</v>
+        <v>215.61524459475</v>
       </c>
       <c r="HP17" t="n">
-        <v>218.165733270247</v>
+        <v>217.779053027811</v>
       </c>
       <c r="HQ17" t="n">
-        <v>220.363982118621</v>
+        <v>219.969664715775</v>
       </c>
       <c r="HR17" t="n">
-        <v>222.588969256056</v>
+        <v>222.186232501744</v>
       </c>
       <c r="HS17" t="n">
-        <v>224.831397922271</v>
+        <v>224.419645633369</v>
       </c>
       <c r="HT17" t="n">
-        <v>227.101960331755</v>
+        <v>226.680508107175</v>
       </c>
       <c r="HU17" t="n">
-        <v>229.392254250843</v>
+        <v>228.960312390774</v>
       </c>
     </row>
     <row r="18">
@@ -13558,139 +13558,139 @@
         <v>26114</v>
       </c>
       <c r="GC18" t="n">
-        <v>26415.6169173493</v>
+        <v>26415.8830093047</v>
       </c>
       <c r="GD18" t="n">
-        <v>26545.6319008916</v>
+        <v>26492.9760390177</v>
       </c>
       <c r="GE18" t="n">
-        <v>26811.7021522808</v>
+        <v>26908.4998345478</v>
       </c>
       <c r="GF18" t="n">
-        <v>27123.753736279</v>
+        <v>27194.188425767</v>
       </c>
       <c r="GG18" t="n">
-        <v>27512.2954823832</v>
+        <v>27579.0279012739</v>
       </c>
       <c r="GH18" t="n">
-        <v>27892.5580172674</v>
+        <v>27948.2647503312</v>
       </c>
       <c r="GI18" t="n">
-        <v>28274.062501718</v>
+        <v>28319.2813117101</v>
       </c>
       <c r="GJ18" t="n">
-        <v>28657.8806859865</v>
+        <v>28694.0313009322</v>
       </c>
       <c r="GK18" t="n">
-        <v>29033.5125787946</v>
+        <v>29056.4632192764</v>
       </c>
       <c r="GL18" t="n">
-        <v>29407.0782705767</v>
+        <v>29417.2781784838</v>
       </c>
       <c r="GM18" t="n">
-        <v>29775.6384747486</v>
+        <v>29772.853481495</v>
       </c>
       <c r="GN18" t="n">
-        <v>30144.6426493512</v>
+        <v>30129.496390783</v>
       </c>
       <c r="GO18" t="n">
-        <v>30489.5265744513</v>
+        <v>30461.5077241288</v>
       </c>
       <c r="GP18" t="n">
-        <v>30826.5888987611</v>
+        <v>30785.7252249589</v>
       </c>
       <c r="GQ18" t="n">
-        <v>31160.2782789414</v>
+        <v>31106.8539232835</v>
       </c>
       <c r="GR18" t="n">
-        <v>31483.4007852103</v>
+        <v>31417.3019428128</v>
       </c>
       <c r="GS18" t="n">
-        <v>31805.6179555175</v>
+        <v>31727.1166548907</v>
       </c>
       <c r="GT18" t="n">
-        <v>32122.8117266421</v>
+        <v>32032.024829105</v>
       </c>
       <c r="GU18" t="n">
-        <v>32440.6005204012</v>
+        <v>32338.0159717256</v>
       </c>
       <c r="GV18" t="n">
-        <v>32750.6354804978</v>
+        <v>32636.5399257858</v>
       </c>
       <c r="GW18" t="n">
-        <v>33059.7850313389</v>
+        <v>32934.7109528472</v>
       </c>
       <c r="GX18" t="n">
-        <v>33366.9000682279</v>
+        <v>33231.3112814155</v>
       </c>
       <c r="GY18" t="n">
-        <v>33675.740869753</v>
+        <v>33530.2055487578</v>
       </c>
       <c r="GZ18" t="n">
-        <v>33980.5292790159</v>
+        <v>33825.4120834859</v>
       </c>
       <c r="HA18" t="n">
-        <v>34288.793911643</v>
+        <v>34124.4773785053</v>
       </c>
       <c r="HB18" t="n">
-        <v>34598.2043040145</v>
+        <v>34424.8658973166</v>
       </c>
       <c r="HC18" t="n">
-        <v>34916.2007337387</v>
+        <v>34734.1806153503</v>
       </c>
       <c r="HD18" t="n">
-        <v>35226.4862350193</v>
+        <v>35035.6348260656</v>
       </c>
       <c r="HE18" t="n">
-        <v>35547.2459297503</v>
+        <v>35347.7493426255</v>
       </c>
       <c r="HF18" t="n">
-        <v>35869.7827049842</v>
+        <v>35661.4931649903</v>
       </c>
       <c r="HG18" t="n">
-        <v>36198.7961744808</v>
+        <v>35981.6872041953</v>
       </c>
       <c r="HH18" t="n">
-        <v>36528.3056958398</v>
+        <v>36302.2672054098</v>
       </c>
       <c r="HI18" t="n">
-        <v>36861.7186895341</v>
+        <v>36626.5902284406</v>
       </c>
       <c r="HJ18" t="n">
-        <v>37199.5750981687</v>
+        <v>36955.1738117896</v>
       </c>
       <c r="HK18" t="n">
-        <v>37543.8974677047</v>
+        <v>37290.0971982124</v>
       </c>
       <c r="HL18" t="n">
-        <v>37888.0463811786</v>
+        <v>37624.649403052</v>
       </c>
       <c r="HM18" t="n">
-        <v>38237.5478034141</v>
+        <v>37964.3450682821</v>
       </c>
       <c r="HN18" t="n">
-        <v>38591.1518921627</v>
+        <v>38307.8809545883</v>
       </c>
       <c r="HO18" t="n">
-        <v>38951.3048385788</v>
+        <v>38657.7902660193</v>
       </c>
       <c r="HP18" t="n">
-        <v>39312.2681794222</v>
+        <v>39008.3076459045</v>
       </c>
       <c r="HQ18" t="n">
-        <v>39675.0792946149</v>
+        <v>39360.4019992674</v>
       </c>
       <c r="HR18" t="n">
-        <v>40041.6745591154</v>
+        <v>39716.0245306316</v>
       </c>
       <c r="HS18" t="n">
-        <v>40418.2737270209</v>
+        <v>40081.6510225739</v>
       </c>
       <c r="HT18" t="n">
-        <v>40783.4519320773</v>
+        <v>40435.3896746406</v>
       </c>
       <c r="HU18" t="n">
-        <v>41157.0410353487</v>
+        <v>40797.5470071353</v>
       </c>
     </row>
     <row r="19">
@@ -14247,139 +14247,139 @@
         <v>14608.7589597667</v>
       </c>
       <c r="GC19" t="n">
-        <v>14660.3950488162</v>
+        <v>14660.0841628213</v>
       </c>
       <c r="GD19" t="n">
-        <v>14722.7882826688</v>
+        <v>14786.4151985371</v>
       </c>
       <c r="GE19" t="n">
-        <v>14830.0545137079</v>
+        <v>14875.5153552457</v>
       </c>
       <c r="GF19" t="n">
-        <v>14955.6989196308</v>
+        <v>14981.754526318</v>
       </c>
       <c r="GG19" t="n">
-        <v>15063.7168242669</v>
+        <v>15075.0817687218</v>
       </c>
       <c r="GH19" t="n">
-        <v>15155.4470116612</v>
+        <v>15155.1216279783</v>
       </c>
       <c r="GI19" t="n">
-        <v>15232.2590334466</v>
+        <v>15222.3257128973</v>
       </c>
       <c r="GJ19" t="n">
-        <v>15292.6703916153</v>
+        <v>15276.2876915861</v>
       </c>
       <c r="GK19" t="n">
-        <v>15344.8892364035</v>
+        <v>15323.2132188084</v>
       </c>
       <c r="GL19" t="n">
-        <v>15391.1973804989</v>
+        <v>15365.5244142257</v>
       </c>
       <c r="GM19" t="n">
-        <v>15432.4035666243</v>
+        <v>15403.5976853831</v>
       </c>
       <c r="GN19" t="n">
-        <v>15460.9833278645</v>
+        <v>15429.3415231498</v>
       </c>
       <c r="GO19" t="n">
-        <v>15486.6106031578</v>
+        <v>15452.5589983592</v>
       </c>
       <c r="GP19" t="n">
-        <v>15512.0220426587</v>
+        <v>15475.904271072</v>
       </c>
       <c r="GQ19" t="n">
-        <v>15535.7189821885</v>
+        <v>15497.7356650074</v>
       </c>
       <c r="GR19" t="n">
-        <v>15559.5018382907</v>
+        <v>15519.973628704</v>
       </c>
       <c r="GS19" t="n">
-        <v>15584.3499649709</v>
+        <v>15543.5665950894</v>
       </c>
       <c r="GT19" t="n">
-        <v>15610.8400989514</v>
+        <v>15569.1731281506</v>
       </c>
       <c r="GU19" t="n">
-        <v>15636.5158373773</v>
+        <v>15594.2685174887</v>
       </c>
       <c r="GV19" t="n">
-        <v>15664.1701854255</v>
+        <v>15621.7117540327</v>
       </c>
       <c r="GW19" t="n">
-        <v>15693.5807587928</v>
+        <v>15651.2247484682</v>
       </c>
       <c r="GX19" t="n">
-        <v>15725.4495931215</v>
+        <v>15683.4772501057</v>
       </c>
       <c r="GY19" t="n">
-        <v>15758.3525516107</v>
+        <v>15716.9262464326</v>
       </c>
       <c r="GZ19" t="n">
-        <v>15793.0951799754</v>
+        <v>15752.3422455204</v>
       </c>
       <c r="HA19" t="n">
-        <v>15830.7599956591</v>
+        <v>15790.7055481895</v>
       </c>
       <c r="HB19" t="n">
-        <v>15871.9427330168</v>
+        <v>15832.59851018</v>
       </c>
       <c r="HC19" t="n">
-        <v>15912.2207039045</v>
+        <v>15873.4466149731</v>
       </c>
       <c r="HD19" t="n">
-        <v>15955.6907680824</v>
+        <v>15917.4689822978</v>
       </c>
       <c r="HE19" t="n">
-        <v>16000.7248109194</v>
+        <v>15962.9273050483</v>
       </c>
       <c r="HF19" t="n">
-        <v>16047.5521666464</v>
+        <v>16010.0970849613</v>
       </c>
       <c r="HG19" t="n">
-        <v>16094.2488340664</v>
+        <v>16057.0335658978</v>
       </c>
       <c r="HH19" t="n">
-        <v>16141.2297831363</v>
+        <v>16104.1631580298</v>
       </c>
       <c r="HI19" t="n">
-        <v>16189.3058352382</v>
+        <v>16152.3105114046</v>
       </c>
       <c r="HJ19" t="n">
-        <v>16238.3431742982</v>
+        <v>16201.368606645</v>
       </c>
       <c r="HK19" t="n">
-        <v>16286.4002769119</v>
+        <v>16249.3746566893</v>
       </c>
       <c r="HL19" t="n">
-        <v>16333.915578992</v>
+        <v>16296.7874904412</v>
       </c>
       <c r="HM19" t="n">
-        <v>16381.9065052165</v>
+        <v>16344.6206480772</v>
       </c>
       <c r="HN19" t="n">
-        <v>16430.2385645666</v>
+        <v>16392.7683198211</v>
       </c>
       <c r="HO19" t="n">
-        <v>16477.0057305422</v>
+        <v>16439.301931376</v>
       </c>
       <c r="HP19" t="n">
-        <v>16522.9616970224</v>
+        <v>16484.9699858475</v>
       </c>
       <c r="HQ19" t="n">
-        <v>16568.9524240839</v>
+        <v>16530.6479813617</v>
       </c>
       <c r="HR19" t="n">
-        <v>16615.0172105473</v>
+        <v>16576.4040907042</v>
       </c>
       <c r="HS19" t="n">
-        <v>16655.9320671393</v>
+        <v>16616.8771073567</v>
       </c>
       <c r="HT19" t="n">
-        <v>16697.6572733749</v>
+        <v>16658.2078999565</v>
       </c>
       <c r="HU19" t="n">
-        <v>16738.3352329029</v>
+        <v>16698.4480025269</v>
       </c>
     </row>
     <row r="20">
@@ -14936,139 +14936,139 @@
         <v>0.669101939</v>
       </c>
       <c r="GC20" t="n">
-        <v>0.668738884891616</v>
+        <v>0.668738350026895</v>
       </c>
       <c r="GD20" t="n">
-        <v>0.668104349144647</v>
+        <v>0.668210262714031</v>
       </c>
       <c r="GE20" t="n">
-        <v>0.668180977843649</v>
+        <v>0.668897178462775</v>
       </c>
       <c r="GF20" t="n">
-        <v>0.668722682001945</v>
+        <v>0.669289317781248</v>
       </c>
       <c r="GG20" t="n">
-        <v>0.669619386691245</v>
+        <v>0.670019318874565</v>
       </c>
       <c r="GH20" t="n">
-        <v>0.670359521745614</v>
+        <v>0.670583167884301</v>
       </c>
       <c r="GI20" t="n">
-        <v>0.670821639131195</v>
+        <v>0.67083355469851</v>
       </c>
       <c r="GJ20" t="n">
-        <v>0.671108643900959</v>
+        <v>0.671046577454215</v>
       </c>
       <c r="GK20" t="n">
-        <v>0.671228037497873</v>
+        <v>0.671066602822236</v>
       </c>
       <c r="GL20" t="n">
-        <v>0.671261426590887</v>
+        <v>0.671018836037757</v>
       </c>
       <c r="GM20" t="n">
-        <v>0.671200101340799</v>
+        <v>0.67088942289252</v>
       </c>
       <c r="GN20" t="n">
-        <v>0.671041247386026</v>
+        <v>0.670675377966698</v>
       </c>
       <c r="GO20" t="n">
-        <v>0.670742546189251</v>
+        <v>0.670330680446722</v>
       </c>
       <c r="GP20" t="n">
-        <v>0.670386750691926</v>
+        <v>0.669935462460628</v>
       </c>
       <c r="GQ20" t="n">
-        <v>0.670004498602766</v>
+        <v>0.669520034157097</v>
       </c>
       <c r="GR20" t="n">
-        <v>0.669599080456645</v>
+        <v>0.669085946566653</v>
       </c>
       <c r="GS20" t="n">
-        <v>0.669212240065775</v>
+        <v>0.668675887292883</v>
       </c>
       <c r="GT20" t="n">
-        <v>0.668828755252668</v>
+        <v>0.668273778135251</v>
       </c>
       <c r="GU20" t="n">
-        <v>0.66845774282884</v>
+        <v>0.667889334423273</v>
       </c>
       <c r="GV20" t="n">
-        <v>0.668085222283685</v>
+        <v>0.6675080847</v>
       </c>
       <c r="GW20" t="n">
-        <v>0.667731470822169</v>
+        <v>0.667150595683309</v>
       </c>
       <c r="GX20" t="n">
-        <v>0.667401837419328</v>
+        <v>0.66682171722335</v>
       </c>
       <c r="GY20" t="n">
-        <v>0.667101122871593</v>
+        <v>0.66652563566975</v>
       </c>
       <c r="GZ20" t="n">
-        <v>0.666824116592973</v>
+        <v>0.666255995128093</v>
       </c>
       <c r="HA20" t="n">
-        <v>0.666589588616054</v>
+        <v>0.666030795073682</v>
       </c>
       <c r="HB20" t="n">
-        <v>0.666395098490258</v>
+        <v>0.665846575317287</v>
       </c>
       <c r="HC20" t="n">
-        <v>0.666240004665862</v>
+        <v>0.665702108430934</v>
       </c>
       <c r="HD20" t="n">
-        <v>0.666094799855863</v>
+        <v>0.665566555365318</v>
       </c>
       <c r="HE20" t="n">
-        <v>0.665998594136542</v>
+        <v>0.665479652936596</v>
       </c>
       <c r="HF20" t="n">
-        <v>0.665927411620081</v>
+        <v>0.665416462469405</v>
       </c>
       <c r="HG20" t="n">
-        <v>0.665880281646713</v>
+        <v>0.665376240024433</v>
       </c>
       <c r="HH20" t="n">
-        <v>0.665843438494312</v>
+        <v>0.665345047743474</v>
       </c>
       <c r="HI20" t="n">
-        <v>0.665818544737377</v>
+        <v>0.665324469772037</v>
       </c>
       <c r="HJ20" t="n">
-        <v>0.665810471424564</v>
+        <v>0.665319669279469</v>
       </c>
       <c r="HK20" t="n">
-        <v>0.665812802917293</v>
+        <v>0.665324357713518</v>
       </c>
       <c r="HL20" t="n">
-        <v>0.665812421915824</v>
+        <v>0.665325332771863</v>
       </c>
       <c r="HM20" t="n">
-        <v>0.665820838397558</v>
+        <v>0.665334261103139</v>
       </c>
       <c r="HN20" t="n">
-        <v>0.665834747090709</v>
+        <v>0.665347896150233</v>
       </c>
       <c r="HO20" t="n">
-        <v>0.665850766949961</v>
+        <v>0.665363094446729</v>
       </c>
       <c r="HP20" t="n">
-        <v>0.66585404150585</v>
+        <v>0.665364856244272</v>
       </c>
       <c r="HQ20" t="n">
-        <v>0.665847716940437</v>
+        <v>0.665356329439756</v>
       </c>
       <c r="HR20" t="n">
-        <v>0.665840006598921</v>
+        <v>0.665346031744335</v>
       </c>
       <c r="HS20" t="n">
-        <v>0.665823912377123</v>
+        <v>0.665327017754076</v>
       </c>
       <c r="HT20" t="n">
-        <v>0.665765351057625</v>
+        <v>0.665264358126137</v>
       </c>
       <c r="HU20" t="n">
-        <v>0.665708719802019</v>
+        <v>0.66520377417675</v>
       </c>
     </row>
     <row r="21">
@@ -15625,139 +15625,139 @@
         <v>0.0430614370315685</v>
       </c>
       <c r="GC21" t="n">
-        <v>0.0476194964539835</v>
+        <v>0.047638941993144</v>
       </c>
       <c r="GD21" t="n">
-        <v>0.0467878396010844</v>
+        <v>0.042820119813057</v>
       </c>
       <c r="GE21" t="n">
-        <v>0.044082262953602</v>
+        <v>0.0421785988397355</v>
       </c>
       <c r="GF21" t="n">
-        <v>0.0404593632002649</v>
+        <v>0.039601450334911</v>
       </c>
       <c r="GG21" t="n">
-        <v>0.0385158869070906</v>
+        <v>0.0383648270973903</v>
       </c>
       <c r="GH21" t="n">
-        <v>0.0374159735004161</v>
+        <v>0.0377576647260996</v>
       </c>
       <c r="GI21" t="n">
-        <v>0.036883060289665</v>
+        <v>0.0375282277070139</v>
       </c>
       <c r="GJ21" t="n">
-        <v>0.0369709958530386</v>
+        <v>0.0379136900922971</v>
       </c>
       <c r="GK21" t="n">
-        <v>0.0373384691789247</v>
+        <v>0.0384670586359749</v>
       </c>
       <c r="GL21" t="n">
-        <v>0.037954324645462</v>
+        <v>0.0392118206718482</v>
       </c>
       <c r="GM21" t="n">
-        <v>0.0387519106339942</v>
+        <v>0.0401018528669038</v>
       </c>
       <c r="GN21" t="n">
-        <v>0.0401424861602343</v>
+        <v>0.041584336870502</v>
       </c>
       <c r="GO21" t="n">
-        <v>0.0415084144418024</v>
+        <v>0.0430282999846384</v>
       </c>
       <c r="GP21" t="n">
-        <v>0.0427979424136913</v>
+        <v>0.0443833674735848</v>
       </c>
       <c r="GQ21" t="n">
-        <v>0.0441471423578482</v>
+        <v>0.0457941454911124</v>
       </c>
       <c r="GR21" t="n">
-        <v>0.0453299188655787</v>
+        <v>0.0470249214543294</v>
       </c>
       <c r="GS21" t="n">
-        <v>0.0464658313558459</v>
+        <v>0.0481983373583822</v>
       </c>
       <c r="GT21" t="n">
-        <v>0.0474985757445043</v>
+        <v>0.0492519954716373</v>
       </c>
       <c r="GU21" t="n">
-        <v>0.0485914823576374</v>
+        <v>0.0503545230638067</v>
       </c>
       <c r="GV21" t="n">
-        <v>0.0495665641743774</v>
+        <v>0.0513232247433072</v>
       </c>
       <c r="GW21" t="n">
-        <v>0.050455063225831</v>
+        <v>0.0521933076971457</v>
       </c>
       <c r="GX21" t="n">
-        <v>0.051223145577907</v>
+        <v>0.0529322867467246</v>
       </c>
       <c r="GY21" t="n">
-        <v>0.0519645913894242</v>
+        <v>0.0536404373561586</v>
       </c>
       <c r="GZ21" t="n">
-        <v>0.0525170626803358</v>
+        <v>0.0541561327556985</v>
       </c>
       <c r="HA21" t="n">
-        <v>0.0529505185485808</v>
+        <v>0.0545541557683491</v>
       </c>
       <c r="HB21" t="n">
-        <v>0.0532274588080092</v>
+        <v>0.0547963529653803</v>
       </c>
       <c r="HC21" t="n">
-        <v>0.0536118552349334</v>
+        <v>0.0551551349157153</v>
       </c>
       <c r="HD21" t="n">
-        <v>0.053735672619993</v>
+        <v>0.0552532161444418</v>
       </c>
       <c r="HE21" t="n">
-        <v>0.0538352345582879</v>
+        <v>0.0553342236378556</v>
       </c>
       <c r="HF21" t="n">
-        <v>0.05386378587845</v>
+        <v>0.0553472655612472</v>
       </c>
       <c r="HG21" t="n">
-        <v>0.0539339922243921</v>
+        <v>0.0554065973024424</v>
       </c>
       <c r="HH21" t="n">
-        <v>0.0539578626525296</v>
+        <v>0.055423322310881</v>
       </c>
       <c r="HI21" t="n">
-        <v>0.0539346510063354</v>
+        <v>0.0553956218826285</v>
       </c>
       <c r="HJ21" t="n">
-        <v>0.0538796439172522</v>
+        <v>0.0553375940419492</v>
       </c>
       <c r="HK21" t="n">
-        <v>0.0538970085865502</v>
+        <v>0.0553548873343689</v>
       </c>
       <c r="HL21" t="n">
-        <v>0.0538616478097304</v>
+        <v>0.0553211836005975</v>
       </c>
       <c r="HM21" t="n">
-        <v>0.0538114975809192</v>
+        <v>0.0552746606293788</v>
       </c>
       <c r="HN21" t="n">
-        <v>0.0537498430797217</v>
+        <v>0.0552170142599571</v>
       </c>
       <c r="HO21" t="n">
-        <v>0.0537815029340418</v>
+        <v>0.055254767809915</v>
       </c>
       <c r="HP21" t="n">
-        <v>0.0538448752008098</v>
+        <v>0.0553263696373388</v>
       </c>
       <c r="HQ21" t="n">
-        <v>0.0538923510487717</v>
+        <v>0.055382465089571</v>
       </c>
       <c r="HR21" t="n">
-        <v>0.0539333824455213</v>
+        <v>0.0554312721345353</v>
       </c>
       <c r="HS21" t="n">
-        <v>0.0542546893041514</v>
+        <v>0.0557676133854563</v>
       </c>
       <c r="HT21" t="n">
-        <v>0.0544572157832091</v>
+        <v>0.0559807445390241</v>
       </c>
       <c r="HU21" t="n">
-        <v>0.0547200644284365</v>
+        <v>0.0562568166774583</v>
       </c>
     </row>
     <row r="22">
@@ -16314,139 +16314,139 @@
         <v>657.3819662</v>
       </c>
       <c r="GC22" t="n">
-        <v>733.026573007064</v>
+        <v>733.325147173915</v>
       </c>
       <c r="GD22" t="n">
-        <v>722.659242606804</v>
+        <v>661.480870113943</v>
       </c>
       <c r="GE22" t="n">
-        <v>683.889877162612</v>
+        <v>655.057908559333</v>
       </c>
       <c r="GF22" t="n">
-        <v>630.612333861736</v>
+        <v>617.76363918953</v>
       </c>
       <c r="GG22" t="n">
-        <v>603.434314973267</v>
+        <v>601.4266234385</v>
       </c>
       <c r="GH22" t="n">
-        <v>589.097546511361</v>
+        <v>594.675643822669</v>
       </c>
       <c r="GI22" t="n">
-        <v>583.327302877726</v>
+        <v>593.541550088641</v>
       </c>
       <c r="GJ22" t="n">
-        <v>587.090657918128</v>
+        <v>602.00474276495</v>
       </c>
       <c r="GK22" t="n">
-        <v>595.177779430764</v>
+        <v>613.020108019176</v>
       </c>
       <c r="GL22" t="n">
-        <v>607.208787751015</v>
+        <v>627.100009315198</v>
       </c>
       <c r="GM22" t="n">
-        <v>622.144498261514</v>
+        <v>643.519209467659</v>
       </c>
       <c r="GN22" t="n">
-        <v>646.598474437968</v>
+        <v>669.457999935479</v>
       </c>
       <c r="GO22" t="n">
-        <v>670.662907773753</v>
+        <v>694.793228333447</v>
       </c>
       <c r="GP22" t="n">
-        <v>693.565937649377</v>
+        <v>718.774497308385</v>
       </c>
       <c r="GQ22" t="n">
-        <v>717.534831442272</v>
+        <v>743.765804250173</v>
       </c>
       <c r="GR22" t="n">
-        <v>738.800863007898</v>
+        <v>765.839193636459</v>
       </c>
       <c r="GS22" t="n">
-        <v>759.427324019127</v>
+        <v>787.111665306009</v>
       </c>
       <c r="GT22" t="n">
-        <v>778.468970727867</v>
+        <v>806.536509039401</v>
       </c>
       <c r="GU22" t="n">
-        <v>798.607117837913</v>
+        <v>826.879190772568</v>
       </c>
       <c r="GV22" t="n">
-        <v>816.91068893374</v>
+        <v>845.131638527697</v>
       </c>
       <c r="GW22" t="n">
-        <v>833.894963996427</v>
+        <v>861.873338736932</v>
       </c>
       <c r="GX22" t="n">
-        <v>848.995339760775</v>
+        <v>876.560814674587</v>
       </c>
       <c r="GY22" t="n">
-        <v>863.761500591401</v>
+        <v>890.84842965896</v>
       </c>
       <c r="GZ22" t="n">
-        <v>875.379463571448</v>
+        <v>901.931174651043</v>
       </c>
       <c r="HA22" t="n">
-        <v>885.114349740386</v>
+        <v>911.156093143134</v>
       </c>
       <c r="HB22" t="n">
-        <v>892.319194414271</v>
+        <v>917.864416979552</v>
       </c>
       <c r="HC22" t="n">
-        <v>901.410079959503</v>
+        <v>926.609498155445</v>
       </c>
       <c r="HD22" t="n">
-        <v>906.078658595346</v>
+        <v>930.928268523903</v>
       </c>
       <c r="HE22" t="n">
-        <v>910.415338741263</v>
+        <v>935.035808746257</v>
       </c>
       <c r="HF22" t="n">
-        <v>913.591551247002</v>
+        <v>938.032779130679</v>
       </c>
       <c r="HG22" t="n">
-        <v>917.512336380496</v>
+        <v>941.850461413065</v>
       </c>
       <c r="HH22" t="n">
-        <v>920.621146772999</v>
+        <v>944.916798698639</v>
       </c>
       <c r="HI22" t="n">
-        <v>922.94332937014</v>
+        <v>947.24039783113</v>
       </c>
       <c r="HJ22" t="n">
-        <v>924.741011872959</v>
+        <v>949.063813150355</v>
       </c>
       <c r="HK22" t="n">
-        <v>927.793713389539</v>
+        <v>952.190873398507</v>
       </c>
       <c r="HL22" t="n">
-        <v>929.855293409313</v>
+        <v>954.353705644407</v>
       </c>
       <c r="HM22" t="n">
-        <v>931.669609956982</v>
+        <v>956.302824617953</v>
       </c>
       <c r="HN22" t="n">
-        <v>933.286925299679</v>
+        <v>958.061153876519</v>
       </c>
       <c r="HO22" t="n">
-        <v>936.52607087919</v>
+        <v>961.476110396539</v>
       </c>
       <c r="HP22" t="n">
-        <v>940.307726843483</v>
+        <v>965.469638259608</v>
       </c>
       <c r="HQ22" t="n">
-        <v>943.803762129566</v>
+        <v>969.184004207298</v>
       </c>
       <c r="HR22" t="n">
-        <v>947.189365772498</v>
+        <v>972.773397015044</v>
       </c>
       <c r="HS22" t="n">
-        <v>955.503113002327</v>
+        <v>981.414916940736</v>
       </c>
       <c r="HT22" t="n">
-        <v>961.67841777013</v>
+        <v>987.839021591346</v>
       </c>
       <c r="HU22" t="n">
-        <v>968.943608039826</v>
+        <v>995.399719489265</v>
       </c>
     </row>
     <row r="23">
@@ -17003,139 +17003,139 @@
         <v>0.0362333333333333</v>
       </c>
       <c r="GC23" t="n">
-        <v>0.0314324768579786</v>
+        <v>0.0313989538539444</v>
       </c>
       <c r="GD23" t="n">
-        <v>0.0348543638906952</v>
+        <v>0.0421150864010787</v>
       </c>
       <c r="GE23" t="n">
-        <v>0.0436972390686142</v>
+        <v>0.0487508300487732</v>
       </c>
       <c r="GF23" t="n">
-        <v>0.0537096185593085</v>
+        <v>0.0577389160734196</v>
       </c>
       <c r="GG23" t="n">
-        <v>0.0621418743937844</v>
+        <v>0.0653964703296235</v>
       </c>
       <c r="GH23" t="n">
-        <v>0.0693982950866891</v>
+        <v>0.071071119062714</v>
       </c>
       <c r="GI23" t="n">
-        <v>0.0751266995945514</v>
+        <v>0.0756460953604322</v>
       </c>
       <c r="GJ23" t="n">
-        <v>0.0789270555252945</v>
+        <v>0.0782042206508805</v>
       </c>
       <c r="GK23" t="n">
-        <v>0.0813311499510839</v>
+        <v>0.0795699053926581</v>
       </c>
       <c r="GL23" t="n">
-        <v>0.0823529045752757</v>
+        <v>0.0797187810770761</v>
       </c>
       <c r="GM23" t="n">
-        <v>0.0820389443938099</v>
+        <v>0.0786957917261237</v>
       </c>
       <c r="GN23" t="n">
-        <v>0.0798310352026281</v>
+        <v>0.0759125952791328</v>
       </c>
       <c r="GO23" t="n">
-        <v>0.0768451048619875</v>
+        <v>0.0724872179027902</v>
       </c>
       <c r="GP23" t="n">
-        <v>0.0733860711481737</v>
+        <v>0.0687086049537369</v>
       </c>
       <c r="GQ23" t="n">
-        <v>0.0694736632836268</v>
+        <v>0.0645659221147493</v>
       </c>
       <c r="GR23" t="n">
-        <v>0.0656528789725724</v>
+        <v>0.0606014134008382</v>
       </c>
       <c r="GS23" t="n">
-        <v>0.0618334384477611</v>
+        <v>0.0567054843736665</v>
       </c>
       <c r="GT23" t="n">
-        <v>0.0581863589962903</v>
+        <v>0.0530480658584758</v>
       </c>
       <c r="GU23" t="n">
-        <v>0.0545136734386255</v>
+        <v>0.0494154046841973</v>
       </c>
       <c r="GV23" t="n">
-        <v>0.0511090815793214</v>
+        <v>0.0461024303502146</v>
       </c>
       <c r="GW23" t="n">
-        <v>0.0479649970324944</v>
+        <v>0.0430906625040256</v>
       </c>
       <c r="GX23" t="n">
-        <v>0.0451527663040569</v>
+        <v>0.0404445384630477</v>
       </c>
       <c r="GY23" t="n">
-        <v>0.0425472301887731</v>
+        <v>0.0380238394740192</v>
       </c>
       <c r="GZ23" t="n">
-        <v>0.0404121247134287</v>
+        <v>0.0360858200850291</v>
       </c>
       <c r="HA23" t="n">
-        <v>0.0386536812384047</v>
+        <v>0.0345243135412693</v>
       </c>
       <c r="HB23" t="n">
-        <v>0.0373387037918807</v>
+        <v>0.0334025273280607</v>
       </c>
       <c r="HC23" t="n">
-        <v>0.0360408506936373</v>
+        <v>0.0322771316768383</v>
       </c>
       <c r="HD23" t="n">
-        <v>0.0353261163169835</v>
+        <v>0.0317251274730424</v>
       </c>
       <c r="HE23" t="n">
-        <v>0.03482595342113</v>
+        <v>0.031364616446779</v>
       </c>
       <c r="HF23" t="n">
-        <v>0.034592153634563</v>
+        <v>0.0312523518173651</v>
       </c>
       <c r="HG23" t="n">
-        <v>0.0344378672927621</v>
+        <v>0.0311982967626562</v>
       </c>
       <c r="HH23" t="n">
-        <v>0.0344556990227998</v>
+        <v>0.0312965268498377</v>
       </c>
       <c r="HI23" t="n">
-        <v>0.0346415120396794</v>
+        <v>0.0315452577287459</v>
       </c>
       <c r="HJ23" t="n">
-        <v>0.0349519298951971</v>
+        <v>0.0319037713355789</v>
       </c>
       <c r="HK23" t="n">
-        <v>0.0352042283943284</v>
+        <v>0.0321881504985048</v>
       </c>
       <c r="HL23" t="n">
-        <v>0.0355763679184775</v>
+        <v>0.0325792342905538</v>
       </c>
       <c r="HM23" t="n">
-        <v>0.0359992234833284</v>
+        <v>0.0330086542330379</v>
       </c>
       <c r="HN23" t="n">
-        <v>0.0364566357147273</v>
+        <v>0.0334639082080907</v>
       </c>
       <c r="HO23" t="n">
-        <v>0.0367702256368655</v>
+        <v>0.0337651236702528</v>
       </c>
       <c r="HP23" t="n">
-        <v>0.0370068986073209</v>
+        <v>0.0339802334369201</v>
       </c>
       <c r="HQ23" t="n">
-        <v>0.0372373190343826</v>
+        <v>0.0341836430158901</v>
       </c>
       <c r="HR23" t="n">
-        <v>0.0374449678545547</v>
+        <v>0.0343618385966022</v>
       </c>
       <c r="HS23" t="n">
-        <v>0.0371537085540228</v>
+        <v>0.0340270407292287</v>
       </c>
       <c r="HT23" t="n">
-        <v>0.0369807857756109</v>
+        <v>0.0338152336973944</v>
       </c>
       <c r="HU23" t="n">
-        <v>0.0366500948994805</v>
+        <v>0.0334403727977319</v>
       </c>
     </row>
     <row r="24">
@@ -17644,139 +17644,139 @@
         <v>0.04288</v>
       </c>
       <c r="GC24" t="n">
-        <v>0.0420196903969125</v>
+        <v>0.0420176539960489</v>
       </c>
       <c r="GD24" t="n">
-        <v>0.0414256897351744</v>
+        <v>0.0418648542175487</v>
       </c>
       <c r="GE24" t="n">
-        <v>0.0414092127342414</v>
+        <v>0.0421255316359192</v>
       </c>
       <c r="GF24" t="n">
-        <v>0.0420020707591373</v>
+        <v>0.0429144945825906</v>
       </c>
       <c r="GG24" t="n">
-        <v>0.0430668842733689</v>
+        <v>0.0441150310987217</v>
       </c>
       <c r="GH24" t="n">
-        <v>0.0445001651346085</v>
+        <v>0.0455787282507709</v>
       </c>
       <c r="GI24" t="n">
-        <v>0.0461840615363322</v>
+        <v>0.0472209081544774</v>
       </c>
       <c r="GJ24" t="n">
-        <v>0.0479844269505533</v>
+        <v>0.0489069299112585</v>
       </c>
       <c r="GK24" t="n">
-        <v>0.0498085316966101</v>
+        <v>0.0505613788619618</v>
       </c>
       <c r="GL24" t="n">
-        <v>0.051570791009773</v>
+        <v>0.0521124830446222</v>
       </c>
       <c r="GM24" t="n">
-        <v>0.0531942662860947</v>
+        <v>0.0534960762270323</v>
       </c>
       <c r="GN24" t="n">
-        <v>0.05457333473799</v>
+        <v>0.0546166114098969</v>
       </c>
       <c r="GO24" t="n">
-        <v>0.0556773372114963</v>
+        <v>0.0554529482333417</v>
       </c>
       <c r="GP24" t="n">
-        <v>0.0564962199092162</v>
+        <v>0.0560029348060052</v>
       </c>
       <c r="GQ24" t="n">
-        <v>0.0570218104772714</v>
+        <v>0.056263907271267</v>
       </c>
       <c r="GR24" t="n">
-        <v>0.0572795983513382</v>
+        <v>0.0562663220875256</v>
       </c>
       <c r="GS24" t="n">
-        <v>0.057287857275107</v>
+        <v>0.0560319093100217</v>
       </c>
       <c r="GT24" t="n">
-        <v>0.0570740083176781</v>
+        <v>0.0555912455299774</v>
       </c>
       <c r="GU24" t="n">
-        <v>0.0566515840187387</v>
+        <v>0.0549598455096158</v>
       </c>
       <c r="GV24" t="n">
-        <v>0.0560510388360761</v>
+        <v>0.0541700859743356</v>
       </c>
       <c r="GW24" t="n">
-        <v>0.0553002975792943</v>
+        <v>0.0532510216507828</v>
       </c>
       <c r="GX24" t="n">
-        <v>0.0544297221382116</v>
+        <v>0.0522336478812536</v>
       </c>
       <c r="GY24" t="n">
-        <v>0.0534600089205147</v>
+        <v>0.0511383366819299</v>
       </c>
       <c r="GZ24" t="n">
-        <v>0.0524264694122572</v>
+        <v>0.0499997034572961</v>
       </c>
       <c r="HA24" t="n">
-        <v>0.0513563202491445</v>
+        <v>0.0488435629065147</v>
       </c>
       <c r="HB24" t="n">
-        <v>0.0502789873150397</v>
+        <v>0.0476978157349736</v>
       </c>
       <c r="HC24" t="n">
-        <v>0.0491959988529505</v>
+        <v>0.0465615366494249</v>
       </c>
       <c r="HD24" t="n">
-        <v>0.0481431613953398</v>
+        <v>0.0454689139230046</v>
       </c>
       <c r="HE24" t="n">
-        <v>0.0471314611922666</v>
+        <v>0.0444286144498954</v>
       </c>
       <c r="HF24" t="n">
-        <v>0.046174284339993</v>
+        <v>0.0434521639253637</v>
       </c>
       <c r="HG24" t="n">
-        <v>0.045272757164266</v>
+        <v>0.0425387610448599</v>
       </c>
       <c r="HH24" t="n">
-        <v>0.0444335548734587</v>
+        <v>0.041693373686652</v>
       </c>
       <c r="HI24" t="n">
-        <v>0.0436626479274672</v>
+        <v>0.0409205238631088</v>
       </c>
       <c r="HJ24" t="n">
-        <v>0.0429629662448357</v>
+        <v>0.0402219529269906</v>
       </c>
       <c r="HK24" t="n">
-        <v>0.0423261408798465</v>
+        <v>0.0395881116382844</v>
       </c>
       <c r="HL24" t="n">
-        <v>0.0417551818453838</v>
+        <v>0.0390210847642605</v>
       </c>
       <c r="HM24" t="n">
-        <v>0.0412486955890567</v>
+        <v>0.0385186623147768</v>
       </c>
       <c r="HN24" t="n">
-        <v>0.040804401600579</v>
+        <v>0.0380780249683048</v>
       </c>
       <c r="HO24" t="n">
-        <v>0.0404093384115149</v>
+        <v>0.0376856183182336</v>
       </c>
       <c r="HP24" t="n">
-        <v>0.0400554892970848</v>
+        <v>0.037332935394967</v>
       </c>
       <c r="HQ24" t="n">
-        <v>0.0397396747233135</v>
+        <v>0.037016566980771</v>
       </c>
       <c r="HR24" t="n">
-        <v>0.0394579276720809</v>
+        <v>0.0367325145346337</v>
       </c>
       <c r="HS24" t="n">
-        <v>0.0391776270432565</v>
+        <v>0.0364474203087966</v>
       </c>
       <c r="HT24" t="n">
-        <v>0.0389058630942309</v>
+        <v>0.0361688263194418</v>
       </c>
       <c r="HU24" t="n">
-        <v>0.0386324720800233</v>
+        <v>0.0358863860679304</v>
       </c>
     </row>
     <row r="25">
@@ -18329,139 +18329,139 @@
       <c r="GA25"/>
       <c r="GB25"/>
       <c r="GC25" t="n">
-        <v>0.411049170711751</v>
+        <v>0.41104884007212</v>
       </c>
       <c r="GD25" t="n">
-        <v>0.397475392828582</v>
+        <v>0.397693250220635</v>
       </c>
       <c r="GE25" t="n">
-        <v>0.386022578275659</v>
+        <v>0.385814235697679</v>
       </c>
       <c r="GF25" t="n">
-        <v>0.381485965594769</v>
+        <v>0.381088652433932</v>
       </c>
       <c r="GG25" t="n">
-        <v>0.379042923835335</v>
+        <v>0.378453186594326</v>
       </c>
       <c r="GH25" t="n">
-        <v>0.376917367879265</v>
+        <v>0.375918384438078</v>
       </c>
       <c r="GI25" t="n">
-        <v>0.374208320319648</v>
+        <v>0.373604704040058</v>
       </c>
       <c r="GJ25" t="n">
-        <v>0.370244093699359</v>
+        <v>0.369940218168073</v>
       </c>
       <c r="GK25" t="n">
-        <v>0.36795557090265</v>
+        <v>0.368031132184108</v>
       </c>
       <c r="GL25" t="n">
-        <v>0.367151901146304</v>
+        <v>0.367602048052999</v>
       </c>
       <c r="GM25" t="n">
-        <v>0.369995550387041</v>
+        <v>0.370792547997141</v>
       </c>
       <c r="GN25" t="n">
-        <v>0.368595293502731</v>
+        <v>0.369673946698015</v>
       </c>
       <c r="GO25" t="n">
-        <v>0.367830348067817</v>
+        <v>0.36909916171812</v>
       </c>
       <c r="GP25" t="n">
-        <v>0.367596036252939</v>
+        <v>0.36896401097928</v>
       </c>
       <c r="GQ25" t="n">
-        <v>0.367759644203277</v>
+        <v>0.369137000317806</v>
       </c>
       <c r="GR25" t="n">
-        <v>0.36800520832696</v>
+        <v>0.369307254470831</v>
       </c>
       <c r="GS25" t="n">
-        <v>0.368586790139145</v>
+        <v>0.369739655975511</v>
       </c>
       <c r="GT25" t="n">
-        <v>0.369393010015748</v>
+        <v>0.370333536929859</v>
       </c>
       <c r="GU25" t="n">
-        <v>0.370298925617966</v>
+        <v>0.370974250236218</v>
       </c>
       <c r="GV25" t="n">
-        <v>0.371168080576732</v>
+        <v>0.371534932576541</v>
       </c>
       <c r="GW25" t="n">
-        <v>0.371994397786668</v>
+        <v>0.372019157222089</v>
       </c>
       <c r="GX25" t="n">
-        <v>0.372708962202849</v>
+        <v>0.372366972154892</v>
       </c>
       <c r="GY25" t="n">
-        <v>0.373269126559153</v>
+        <v>0.37254454987586</v>
       </c>
       <c r="GZ25" t="n">
-        <v>0.373641919538927</v>
+        <v>0.372527215185958</v>
       </c>
       <c r="HA25" t="n">
-        <v>0.373789475208652</v>
+        <v>0.372285201397918</v>
       </c>
       <c r="HB25" t="n">
-        <v>0.373765520191825</v>
+        <v>0.371879385388408</v>
       </c>
       <c r="HC25" t="n">
-        <v>0.373547481510742</v>
+        <v>0.371293263109187</v>
       </c>
       <c r="HD25" t="n">
-        <v>0.373140250318404</v>
+        <v>0.370536826657109</v>
       </c>
       <c r="HE25" t="n">
-        <v>0.372519231715524</v>
+        <v>0.369589355104529</v>
       </c>
       <c r="HF25" t="n">
-        <v>0.371701281876149</v>
+        <v>0.368470783083908</v>
       </c>
       <c r="HG25" t="n">
-        <v>0.370720441871777</v>
+        <v>0.36721656040722</v>
       </c>
       <c r="HH25" t="n">
-        <v>0.369586712277114</v>
+        <v>0.365837601091711</v>
       </c>
       <c r="HI25" t="n">
-        <v>0.368355709684803</v>
+        <v>0.364388882034349</v>
       </c>
       <c r="HJ25" t="n">
-        <v>0.367046677099376</v>
+        <v>0.362888542430392</v>
       </c>
       <c r="HK25" t="n">
-        <v>0.365689194091352</v>
+        <v>0.361364728964912</v>
       </c>
       <c r="HL25" t="n">
-        <v>0.364287608461997</v>
+        <v>0.359820010396496</v>
       </c>
       <c r="HM25" t="n">
-        <v>0.362911547008825</v>
+        <v>0.358321290790966</v>
       </c>
       <c r="HN25" t="n">
-        <v>0.361576183771784</v>
+        <v>0.356881503055364</v>
       </c>
       <c r="HO25" t="n">
-        <v>0.360294100623796</v>
+        <v>0.355511041818287</v>
       </c>
       <c r="HP25" t="n">
-        <v>0.359071913341043</v>
+        <v>0.35421436176688</v>
       </c>
       <c r="HQ25" t="n">
-        <v>0.357922864001368</v>
+        <v>0.353002347944092</v>
       </c>
       <c r="HR25" t="n">
-        <v>0.356849621022097</v>
+        <v>0.351875633347406</v>
       </c>
       <c r="HS25" t="n">
-        <v>0.355876102374133</v>
+        <v>0.350855646650341</v>
       </c>
       <c r="HT25" t="n">
-        <v>0.354971615796481</v>
+        <v>0.349911126398362</v>
       </c>
       <c r="HU25" t="n">
-        <v>0.354154015039799</v>
+        <v>0.34905711061274</v>
       </c>
     </row>
     <row r="26">
@@ -19018,139 +19018,139 @@
         <v>0.653633333333333</v>
       </c>
       <c r="GC26" t="n">
-        <v>0.667381241604625</v>
+        <v>0.667380773125949</v>
       </c>
       <c r="GD26" t="n">
-        <v>0.642170274514971</v>
+        <v>0.642374063302119</v>
       </c>
       <c r="GE26" t="n">
-        <v>0.62009041074678</v>
+        <v>0.619573902194391</v>
       </c>
       <c r="GF26" t="n">
-        <v>0.609831132315981</v>
+        <v>0.60898292827866</v>
       </c>
       <c r="GG26" t="n">
-        <v>0.602803360965677</v>
+        <v>0.60163210116838</v>
       </c>
       <c r="GH26" t="n">
-        <v>0.596416649053182</v>
+        <v>0.594588178416237</v>
       </c>
       <c r="GI26" t="n">
-        <v>0.589158251952803</v>
+        <v>0.587980149692322</v>
       </c>
       <c r="GJ26" t="n">
-        <v>0.579934085563705</v>
+        <v>0.57925505812771</v>
       </c>
       <c r="GK26" t="n">
-        <v>0.573472879254707</v>
+        <v>0.573418923578122</v>
       </c>
       <c r="GL26" t="n">
-        <v>0.569419165037289</v>
+        <v>0.569978389830929</v>
       </c>
       <c r="GM26" t="n">
-        <v>0.571203777211181</v>
+        <v>0.572328500571345</v>
       </c>
       <c r="GN26" t="n">
-        <v>0.566313023897683</v>
+        <v>0.567895028818787</v>
       </c>
       <c r="GO26" t="n">
-        <v>0.562478596182733</v>
+        <v>0.564371530644145</v>
       </c>
       <c r="GP26" t="n">
-        <v>0.559494335424508</v>
+        <v>0.561553827240129</v>
       </c>
       <c r="GQ26" t="n">
-        <v>0.557164408003792</v>
+        <v>0.559249859397383</v>
       </c>
       <c r="GR26" t="n">
-        <v>0.554998559407035</v>
+        <v>0.55697935108431</v>
       </c>
       <c r="GS26" t="n">
-        <v>0.553373424754604</v>
+        <v>0.555136986154041</v>
       </c>
       <c r="GT26" t="n">
-        <v>0.552101391916154</v>
+        <v>0.553552923904495</v>
       </c>
       <c r="GU26" t="n">
-        <v>0.550988631220378</v>
+        <v>0.552049835495304</v>
       </c>
       <c r="GV26" t="n">
-        <v>0.54984375016105</v>
+        <v>0.550452228501654</v>
       </c>
       <c r="GW26" t="n">
-        <v>0.548635500658005</v>
+        <v>0.548743919450009</v>
       </c>
       <c r="GX26" t="n">
-        <v>0.547257618354413</v>
+        <v>0.546832880038969</v>
       </c>
       <c r="GY26" t="n">
-        <v>0.545656237505498</v>
+        <v>0.544678787295645</v>
       </c>
       <c r="GZ26" t="n">
-        <v>0.54378325367761</v>
+        <v>0.542246458978607</v>
       </c>
       <c r="HA26" t="n">
-        <v>0.541582942342526</v>
+        <v>0.539492355547142</v>
       </c>
       <c r="HB26" t="n">
-        <v>0.539066959991254</v>
+        <v>0.53643865879796</v>
       </c>
       <c r="HC26" t="n">
-        <v>0.536257473628932</v>
+        <v>0.533116474792566</v>
       </c>
       <c r="HD26" t="n">
-        <v>0.533211658431727</v>
+        <v>0.529589755988126</v>
       </c>
       <c r="HE26" t="n">
-        <v>0.529845906395881</v>
+        <v>0.525780896493307</v>
       </c>
       <c r="HF26" t="n">
-        <v>0.526213995065924</v>
+        <v>0.521747225171385</v>
       </c>
       <c r="HG26" t="n">
-        <v>0.522365516033066</v>
+        <v>0.517539705730363</v>
       </c>
       <c r="HH26" t="n">
-        <v>0.518318531960276</v>
+        <v>0.513177332842779</v>
       </c>
       <c r="HI26" t="n">
-        <v>0.514153057075548</v>
+        <v>0.508738842236853</v>
       </c>
       <c r="HJ26" t="n">
-        <v>0.509898083690448</v>
+        <v>0.504251117543874</v>
       </c>
       <c r="HK26" t="n">
-        <v>0.505599919086597</v>
+        <v>0.499757647525994</v>
       </c>
       <c r="HL26" t="n">
-        <v>0.501264430806642</v>
+        <v>0.495261562030673</v>
       </c>
       <c r="HM26" t="n">
-        <v>0.496987949691623</v>
+        <v>0.490855162522443</v>
       </c>
       <c r="HN26" t="n">
-        <v>0.492790935785272</v>
+        <v>0.486555398030871</v>
       </c>
       <c r="HO26" t="n">
-        <v>0.488693605462124</v>
+        <v>0.482378767644486</v>
       </c>
       <c r="HP26" t="n">
-        <v>0.484703683455324</v>
+        <v>0.478329895610404</v>
       </c>
       <c r="HQ26" t="n">
-        <v>0.480836137189948</v>
+        <v>0.474420472862234</v>
       </c>
       <c r="HR26" t="n">
-        <v>0.47709288137884</v>
+        <v>0.470649384257593</v>
       </c>
       <c r="HS26" t="n">
-        <v>0.473478923581311</v>
+        <v>0.46701884707525</v>
       </c>
       <c r="HT26" t="n">
-        <v>0.470016697589686</v>
+        <v>0.463548001101287</v>
       </c>
       <c r="HU26" t="n">
-        <v>0.466666034452179</v>
+        <v>0.460195369460125</v>
       </c>
     </row>
     <row r="27">
@@ -19707,139 +19707,139 @@
         <v>95.2225040638737</v>
       </c>
       <c r="GC27" t="n">
-        <v>93.6633754503115</v>
+        <v>93.6634782988196</v>
       </c>
       <c r="GD27" t="n">
-        <v>95.0789547531596</v>
+        <v>95.0987768736227</v>
       </c>
       <c r="GE27" t="n">
-        <v>96.4700640273838</v>
+        <v>96.4617297778064</v>
       </c>
       <c r="GF27" t="n">
-        <v>97.3261626562374</v>
+        <v>97.324857664392</v>
       </c>
       <c r="GG27" t="n">
-        <v>98.3577949966798</v>
+        <v>98.3483765498065</v>
       </c>
       <c r="GH27" t="n">
-        <v>98.5979353160846</v>
+        <v>98.5907632147126</v>
       </c>
       <c r="GI27" t="n">
-        <v>98.7474624155861</v>
+        <v>98.7276406532607</v>
       </c>
       <c r="GJ27" t="n">
-        <v>98.9209815332057</v>
+        <v>98.891800465257</v>
       </c>
       <c r="GK27" t="n">
-        <v>99.0279128943074</v>
+        <v>98.9922345935848</v>
       </c>
       <c r="GL27" t="n">
-        <v>99.0321042042083</v>
+        <v>98.992343936613</v>
       </c>
       <c r="GM27" t="n">
-        <v>98.9000137210997</v>
+        <v>98.8593328450728</v>
       </c>
       <c r="GN27" t="n">
-        <v>98.8663987513156</v>
+        <v>98.8293893240529</v>
       </c>
       <c r="GO27" t="n">
-        <v>98.8216817046992</v>
+        <v>98.791184843782</v>
       </c>
       <c r="GP27" t="n">
-        <v>98.7947371547535</v>
+        <v>98.7735085344497</v>
       </c>
       <c r="GQ27" t="n">
-        <v>98.7597561628269</v>
+        <v>98.7497600698037</v>
       </c>
       <c r="GR27" t="n">
-        <v>98.7164822291532</v>
+        <v>98.7187753087579</v>
       </c>
       <c r="GS27" t="n">
-        <v>98.6708230827035</v>
+        <v>98.6858206686838</v>
       </c>
       <c r="GT27" t="n">
-        <v>98.662944876069</v>
+        <v>98.6903659251307</v>
       </c>
       <c r="GU27" t="n">
-        <v>98.6709981225525</v>
+        <v>98.7100325071618</v>
       </c>
       <c r="GV27" t="n">
-        <v>98.6731740832994</v>
+        <v>98.7223534696874</v>
       </c>
       <c r="GW27" t="n">
-        <v>98.6918848512787</v>
+        <v>98.7495623305601</v>
       </c>
       <c r="GX27" t="n">
-        <v>98.7241899618761</v>
+        <v>98.7884251096137</v>
       </c>
       <c r="GY27" t="n">
-        <v>98.76286118019</v>
+        <v>98.8315213670579</v>
       </c>
       <c r="GZ27" t="n">
-        <v>98.8078199701371</v>
+        <v>98.8786219616961</v>
       </c>
       <c r="HA27" t="n">
-        <v>98.8588653817152</v>
+        <v>98.9295297409939</v>
       </c>
       <c r="HB27" t="n">
-        <v>99.0317551123686</v>
+        <v>99.1007943683698</v>
       </c>
       <c r="HC27" t="n">
-        <v>99.2320301701466</v>
+        <v>99.2970882872221</v>
       </c>
       <c r="HD27" t="n">
-        <v>99.4040477087109</v>
+        <v>99.4636696025085</v>
       </c>
       <c r="HE27" t="n">
-        <v>99.6101570255765</v>
+        <v>99.6621843065608</v>
       </c>
       <c r="HF27" t="n">
-        <v>99.8148902693611</v>
+        <v>99.8579026191004</v>
       </c>
       <c r="HG27" t="n">
-        <v>100.022909342796</v>
+        <v>100.055543183689</v>
       </c>
       <c r="HH27" t="n">
-        <v>100.231807427716</v>
+        <v>100.252826896325</v>
       </c>
       <c r="HI27" t="n">
-        <v>100.440331137313</v>
+        <v>100.448634494016</v>
       </c>
       <c r="HJ27" t="n">
-        <v>100.646944513488</v>
+        <v>100.641643638148</v>
       </c>
       <c r="HK27" t="n">
-        <v>100.848784707362</v>
+        <v>100.829229925137</v>
       </c>
       <c r="HL27" t="n">
-        <v>101.04724026667</v>
+        <v>101.0127768602</v>
       </c>
       <c r="HM27" t="n">
-        <v>101.240999940788</v>
+        <v>101.191062546265</v>
       </c>
       <c r="HN27" t="n">
-        <v>101.429727369879</v>
+        <v>101.363906492745</v>
       </c>
       <c r="HO27" t="n">
-        <v>101.611099402849</v>
+        <v>101.529199913755</v>
       </c>
       <c r="HP27" t="n">
-        <v>101.787658746321</v>
+        <v>101.689404763801</v>
       </c>
       <c r="HQ27" t="n">
-        <v>101.959485942845</v>
+        <v>101.844679480739</v>
       </c>
       <c r="HR27" t="n">
-        <v>102.126584505326</v>
+        <v>101.995164093565</v>
       </c>
       <c r="HS27" t="n">
-        <v>102.331326545642</v>
+        <v>102.182008001432</v>
       </c>
       <c r="HT27" t="n">
-        <v>102.479154211534</v>
+        <v>102.313555867411</v>
       </c>
       <c r="HU27" t="n">
-        <v>102.661784573796</v>
+        <v>102.478704131841</v>
       </c>
     </row>
     <row r="28">
@@ -20208,139 +20208,139 @@
       <c r="GA28"/>
       <c r="GB28"/>
       <c r="GC28" t="n">
-        <v>15.0818305090182</v>
+        <v>14.9831277549456</v>
       </c>
       <c r="GD28" t="n">
-        <v>15.1209870698774</v>
+        <v>14.7803903592879</v>
       </c>
       <c r="GE28" t="n">
-        <v>15.3246302205419</v>
+        <v>14.9975773937295</v>
       </c>
       <c r="GF28" t="n">
-        <v>15.3881792217293</v>
+        <v>15.0840162893591</v>
       </c>
       <c r="GG28" t="n">
-        <v>15.3165608344826</v>
+        <v>15.0912172994908</v>
       </c>
       <c r="GH28" t="n">
-        <v>15.3897647048699</v>
+        <v>15.2058281658819</v>
       </c>
       <c r="GI28" t="n">
-        <v>15.5538069866276</v>
+        <v>15.4060420800951</v>
       </c>
       <c r="GJ28" t="n">
-        <v>16.0550773548501</v>
+        <v>15.9353074972012</v>
       </c>
       <c r="GK28" t="n">
-        <v>16.2582282963799</v>
+        <v>16.1617607035992</v>
       </c>
       <c r="GL28" t="n">
-        <v>16.5317222475186</v>
+        <v>16.444885334874</v>
       </c>
       <c r="GM28" t="n">
-        <v>16.8617075280417</v>
+        <v>16.7754573950817</v>
       </c>
       <c r="GN28" t="n">
-        <v>17.4763720194443</v>
+        <v>17.3877197915986</v>
       </c>
       <c r="GO28" t="n">
-        <v>17.7308493186448</v>
+        <v>17.637763967172</v>
       </c>
       <c r="GP28" t="n">
-        <v>18.0092058204772</v>
+        <v>17.9056080298453</v>
       </c>
       <c r="GQ28" t="n">
-        <v>18.3186406572699</v>
+        <v>18.2005738881279</v>
       </c>
       <c r="GR28" t="n">
-        <v>18.9345758461819</v>
+        <v>18.8029306502875</v>
       </c>
       <c r="GS28" t="n">
-        <v>19.1465152371563</v>
+        <v>19.0038871098439</v>
       </c>
       <c r="GT28" t="n">
-        <v>19.3690106279217</v>
+        <v>19.2102510594643</v>
       </c>
       <c r="GU28" t="n">
-        <v>19.6196334421423</v>
+        <v>19.4420452771697</v>
       </c>
       <c r="GV28" t="n">
-        <v>20.2008558914036</v>
+        <v>20.005850354776</v>
       </c>
       <c r="GW28" t="n">
-        <v>20.3400078370309</v>
+        <v>20.1320990531507</v>
       </c>
       <c r="GX28" t="n">
-        <v>20.4933621807569</v>
+        <v>20.2682451684861</v>
       </c>
       <c r="GY28" t="n">
-        <v>20.6670913981306</v>
+        <v>20.4231243659103</v>
       </c>
       <c r="GZ28" t="n">
-        <v>21.2002101493623</v>
+        <v>20.9395538063796</v>
       </c>
       <c r="HA28" t="n">
-        <v>21.251274228048</v>
+        <v>20.9814713844102</v>
       </c>
       <c r="HB28" t="n">
-        <v>21.3074273629296</v>
+        <v>21.0249942550768</v>
       </c>
       <c r="HC28" t="n">
-        <v>21.4071670063718</v>
+        <v>21.1110993525516</v>
       </c>
       <c r="HD28" t="n">
-        <v>21.8771090739949</v>
+        <v>21.5689018630686</v>
       </c>
       <c r="HE28" t="n">
-        <v>21.8532354649022</v>
+        <v>21.5421741043276</v>
       </c>
       <c r="HF28" t="n">
-        <v>21.8579629430614</v>
+        <v>21.5395534821217</v>
       </c>
       <c r="HG28" t="n">
-        <v>21.9014051002978</v>
+        <v>21.5739011399926</v>
       </c>
       <c r="HH28" t="n">
-        <v>22.3689990812288</v>
+        <v>22.0332003507227</v>
       </c>
       <c r="HI28" t="n">
-        <v>22.3092529586145</v>
+        <v>21.9742491789907</v>
       </c>
       <c r="HJ28" t="n">
-        <v>22.2913953675577</v>
+        <v>21.9519619593197</v>
       </c>
       <c r="HK28" t="n">
-        <v>22.3202568136696</v>
+        <v>21.973662242491</v>
       </c>
       <c r="HL28" t="n">
-        <v>22.8008322103916</v>
+        <v>22.4470889226277</v>
       </c>
       <c r="HM28" t="n">
-        <v>22.7307119437586</v>
+        <v>22.379348680645</v>
       </c>
       <c r="HN28" t="n">
-        <v>22.7095575179022</v>
+        <v>22.3545343667655</v>
       </c>
       <c r="HO28" t="n">
-        <v>22.7424736625849</v>
+        <v>22.3804810271942</v>
       </c>
       <c r="HP28" t="n">
-        <v>23.2595050795287</v>
+        <v>22.8900058795785</v>
       </c>
       <c r="HQ28" t="n">
-        <v>23.2001501593153</v>
+        <v>22.8327469784525</v>
       </c>
       <c r="HR28" t="n">
-        <v>23.1956294865779</v>
+        <v>22.8236030695624</v>
       </c>
       <c r="HS28" t="n">
-        <v>23.2795214885363</v>
+        <v>22.8992078134185</v>
       </c>
       <c r="HT28" t="n">
-        <v>23.8471900110401</v>
+        <v>23.4567188750527</v>
       </c>
       <c r="HU28" t="n">
-        <v>23.8267244703807</v>
+        <v>23.4370680655839</v>
       </c>
     </row>
     <row r="29">
@@ -20709,139 +20709,139 @@
       <c r="GA29"/>
       <c r="GB29"/>
       <c r="GC29" t="n">
-        <v>0.0000208743927052349</v>
+        <v>0.000020739434491577</v>
       </c>
       <c r="GD29" t="n">
-        <v>0.0000202950525145532</v>
+        <v>0.0000197905312967779</v>
       </c>
       <c r="GE29" t="n">
-        <v>0.0000202359123959127</v>
+        <v>0.000019790616135849</v>
       </c>
       <c r="GF29" t="n">
-        <v>0.000019767663995497</v>
+        <v>0.0000193789338317775</v>
       </c>
       <c r="GG29" t="n">
-        <v>0.0000192829003173742</v>
+        <v>0.0000190103441828797</v>
       </c>
       <c r="GH29" t="n">
-        <v>0.0000190249574802281</v>
+        <v>0.0000188193093186097</v>
       </c>
       <c r="GI29" t="n">
-        <v>0.0000188956356068635</v>
+        <v>0.0000187464669361299</v>
       </c>
       <c r="GJ29" t="n">
-        <v>0.0000191942718333016</v>
+        <v>0.0000190909747234986</v>
       </c>
       <c r="GK29" t="n">
-        <v>0.0000191226598082087</v>
+        <v>0.0000190577091269884</v>
       </c>
       <c r="GL29" t="n">
-        <v>0.0000191410380882789</v>
+        <v>0.0000190974739924567</v>
       </c>
       <c r="GM29" t="n">
-        <v>0.0000192348562475824</v>
+        <v>0.0000192027288659693</v>
       </c>
       <c r="GN29" t="n">
-        <v>0.0000196682908088505</v>
+        <v>0.000019645823931782</v>
       </c>
       <c r="GO29" t="n">
-        <v>0.0000196788934604357</v>
+        <v>0.000019662636814478</v>
       </c>
       <c r="GP29" t="n">
-        <v>0.0000197113142026785</v>
+        <v>0.0000196945649347864</v>
       </c>
       <c r="GQ29" t="n">
-        <v>0.0000197895602286786</v>
+        <v>0.0000197681777179976</v>
       </c>
       <c r="GR29" t="n">
-        <v>0.0000201880352944373</v>
+        <v>0.000020164702470752</v>
       </c>
       <c r="GS29" t="n">
-        <v>0.0000201533049114879</v>
+        <v>0.0000201279226239331</v>
       </c>
       <c r="GT29" t="n">
-        <v>0.0000201282384437574</v>
+        <v>0.0000200947409182313</v>
       </c>
       <c r="GU29" t="n">
-        <v>0.0000201442702998434</v>
+        <v>0.0000200995384093697</v>
       </c>
       <c r="GV29" t="n">
-        <v>0.00002048749641774</v>
+        <v>0.0000204350417154402</v>
       </c>
       <c r="GW29" t="n">
-        <v>0.000020378343008207</v>
+        <v>0.0000203192419564373</v>
       </c>
       <c r="GX29" t="n">
-        <v>0.0000202810529357874</v>
+        <v>0.0000202107338219834</v>
       </c>
       <c r="GY29" t="n">
-        <v>0.000020209207210018</v>
+        <v>0.0000201261055839312</v>
       </c>
       <c r="GZ29" t="n">
-        <v>0.0000204790888940467</v>
+        <v>0.0000203882653171432</v>
       </c>
       <c r="HA29" t="n">
-        <v>0.000020275286208044</v>
+        <v>0.0000201804749726341</v>
       </c>
       <c r="HB29" t="n">
-        <v>0.0000200698092475218</v>
+        <v>0.0000199676484198879</v>
       </c>
       <c r="HC29" t="n">
-        <v>0.0000199202894583508</v>
+        <v>0.0000198103213825342</v>
       </c>
       <c r="HD29" t="n">
-        <v>0.00002009637174507</v>
+        <v>0.0000199830745989778</v>
       </c>
       <c r="HE29" t="n">
-        <v>0.0000198190028696923</v>
+        <v>0.0000197072405990511</v>
       </c>
       <c r="HF29" t="n">
-        <v>0.0000195676724712688</v>
+        <v>0.0000194534754466793</v>
       </c>
       <c r="HG29" t="n">
-        <v>0.0000193587255094312</v>
+        <v>0.0000192408226777535</v>
       </c>
       <c r="HH29" t="n">
-        <v>0.0000195192049488821</v>
+        <v>0.0000194019031112829</v>
       </c>
       <c r="HI29" t="n">
-        <v>0.0000192142734484353</v>
+        <v>0.0000191014160873834</v>
       </c>
       <c r="HJ29" t="n">
-        <v>0.0000189478211507497</v>
+        <v>0.0000188351258980077</v>
       </c>
       <c r="HK29" t="n">
-        <v>0.0000187299068591564</v>
+        <v>0.000018615413705828</v>
       </c>
       <c r="HL29" t="n">
-        <v>0.0000188859686461706</v>
+        <v>0.0000187735568091277</v>
       </c>
       <c r="HM29" t="n">
-        <v>0.0000185817206185777</v>
+        <v>0.0000184750035020685</v>
       </c>
       <c r="HN29" t="n">
-        <v>0.0000183207736077472</v>
+        <v>0.0000182151013709246</v>
       </c>
       <c r="HO29" t="n">
-        <v>0.0000181128718353595</v>
+        <v>0.0000180060058909862</v>
       </c>
       <c r="HP29" t="n">
-        <v>0.0000182868602197491</v>
+        <v>0.0000181825427662589</v>
       </c>
       <c r="HQ29" t="n">
-        <v>0.0000180036820152358</v>
+        <v>0.0000179049230662723</v>
       </c>
       <c r="HR29" t="n">
-        <v>0.0000177663767857588</v>
+        <v>0.0000176682885495987</v>
       </c>
       <c r="HS29" t="n">
-        <v>0.0000176160841603059</v>
+        <v>0.0000175167599584814</v>
       </c>
       <c r="HT29" t="n">
-        <v>0.0000178162859617642</v>
+        <v>0.0000177183120564737</v>
       </c>
       <c r="HU29" t="n">
-        <v>0.0000175796431292398</v>
+        <v>0.0000174866693404629</v>
       </c>
     </row>
     <row r="30">
@@ -21210,139 +21210,139 @@
       <c r="GA30"/>
       <c r="GB30"/>
       <c r="GC30" t="n">
-        <v>844.956095850485</v>
+        <v>844.857393096413</v>
       </c>
       <c r="GD30" t="n">
-        <v>864.773631499334</v>
+        <v>864.333783411753</v>
       </c>
       <c r="GE30" t="n">
-        <v>884.978579592451</v>
+        <v>884.209196411711</v>
       </c>
       <c r="GF30" t="n">
-        <v>905.173697542289</v>
+        <v>904.095972370054</v>
       </c>
       <c r="GG30" t="n">
-        <v>925.421842103574</v>
+        <v>924.112901714552</v>
       </c>
       <c r="GH30" t="n">
-        <v>945.752350242807</v>
+        <v>944.252245895916</v>
       </c>
       <c r="GI30" t="n">
-        <v>966.284065456896</v>
+        <v>964.68098889018</v>
       </c>
       <c r="GJ30" t="n">
-        <v>987.423095497003</v>
+        <v>985.779613790243</v>
       </c>
       <c r="GK30" t="n">
-        <v>1008.95087575841</v>
+        <v>1007.31643729733</v>
       </c>
       <c r="GL30" t="n">
-        <v>1031.00353998853</v>
+        <v>1029.40747012444</v>
       </c>
       <c r="GM30" t="n">
-        <v>1053.6946157155</v>
+        <v>1052.14434074963</v>
       </c>
       <c r="GN30" t="n">
-        <v>1077.35409231819</v>
+        <v>1075.84467647387</v>
       </c>
       <c r="GO30" t="n">
-        <v>1101.65332491332</v>
+        <v>1100.16772172261</v>
       </c>
       <c r="GP30" t="n">
-        <v>1126.63438655524</v>
+        <v>1125.14102014165</v>
       </c>
       <c r="GQ30" t="n">
-        <v>1152.33523905317</v>
+        <v>1150.79145955602</v>
       </c>
       <c r="GR30" t="n">
-        <v>1179.05812749796</v>
+        <v>1177.41639841833</v>
       </c>
       <c r="GS30" t="n">
-        <v>1206.38016333406</v>
+        <v>1204.59089663621</v>
       </c>
       <c r="GT30" t="n">
-        <v>1234.28336484837</v>
+        <v>1232.28833772364</v>
       </c>
       <c r="GU30" t="n">
-        <v>1262.76300345139</v>
+        <v>1260.49883307092</v>
       </c>
       <c r="GV30" t="n">
-        <v>1292.1126261937</v>
+        <v>1289.51566382414</v>
       </c>
       <c r="GW30" t="n">
-        <v>1321.85636168206</v>
+        <v>1318.8665727491</v>
       </c>
       <c r="GX30" t="n">
-        <v>1351.97130734975</v>
+        <v>1348.52417791936</v>
       </c>
       <c r="GY30" t="n">
-        <v>1382.44244964767</v>
+        <v>1378.47229934638</v>
       </c>
       <c r="GZ30" t="n">
-        <v>1413.59347879923</v>
+        <v>1409.03779547149</v>
       </c>
       <c r="HA30" t="n">
-        <v>1444.91193473522</v>
+        <v>1439.71726006888</v>
       </c>
       <c r="HB30" t="n">
-        <v>1476.37175823028</v>
+        <v>1470.483283945</v>
       </c>
       <c r="HC30" t="n">
-        <v>1507.98906188493</v>
+        <v>1501.35349204286</v>
       </c>
       <c r="HD30" t="n">
-        <v>1540.10916515589</v>
+        <v>1532.67743863195</v>
       </c>
       <c r="HE30" t="n">
-        <v>1572.22132492699</v>
+        <v>1563.95644977566</v>
       </c>
       <c r="HF30" t="n">
-        <v>1604.3383412445</v>
+        <v>1595.20181134956</v>
       </c>
       <c r="HG30" t="n">
-        <v>1636.48876285672</v>
+        <v>1626.44320477033</v>
       </c>
       <c r="HH30" t="n">
-        <v>1669.08698192652</v>
+        <v>1658.09841759175</v>
       </c>
       <c r="HI30" t="n">
-        <v>1701.60594200095</v>
+        <v>1689.6517642752</v>
       </c>
       <c r="HJ30" t="n">
-        <v>1734.08722995369</v>
+        <v>1721.14177819587</v>
       </c>
       <c r="HK30" t="n">
-        <v>1766.58099688677</v>
+        <v>1752.6177191424</v>
       </c>
       <c r="HL30" t="n">
-        <v>1799.54361889706</v>
+        <v>1784.53746356621</v>
       </c>
       <c r="HM30" t="n">
-        <v>1832.43384982829</v>
+        <v>1816.37030762648</v>
       </c>
       <c r="HN30" t="n">
-        <v>1865.30912595582</v>
+        <v>1848.16860950717</v>
       </c>
       <c r="HO30" t="n">
-        <v>1898.23387366782</v>
+        <v>1879.99414466828</v>
       </c>
       <c r="HP30" t="n">
-        <v>1931.70178865946</v>
+        <v>1912.34044509593</v>
       </c>
       <c r="HQ30" t="n">
-        <v>1965.15019963794</v>
+        <v>1944.65441279556</v>
       </c>
       <c r="HR30" t="n">
-        <v>1998.64508095983</v>
+        <v>1976.99530664122</v>
       </c>
       <c r="HS30" t="n">
-        <v>2032.28657412079</v>
+        <v>2009.45939963458</v>
       </c>
       <c r="HT30" t="n">
-        <v>2066.56813807197</v>
+        <v>2042.53788005145</v>
       </c>
       <c r="HU30" t="n">
-        <v>2100.91233731129</v>
+        <v>2075.66356909838</v>
       </c>
     </row>
     <row r="31">
@@ -21902,7 +21902,7 @@
         <v>0.043535305024288</v>
       </c>
       <c r="GD31" t="n">
-        <v>0.0435353050242881</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="GE31" t="n">
         <v>0.043535305024288</v>
@@ -22001,7 +22001,7 @@
         <v>0.043535305024288</v>
       </c>
       <c r="HK31" t="n">
-        <v>0.0435353050242881</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HL31" t="n">
         <v>0.043535305024288</v>
@@ -22016,7 +22016,7 @@
         <v>0.043535305024288</v>
       </c>
       <c r="HP31" t="n">
-        <v>0.0435353050242881</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HQ31" t="n">
         <v>0.043535305024288</v>
@@ -22028,7 +22028,7 @@
         <v>0.043535305024288</v>
       </c>
       <c r="HT31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0435353050242881</v>
       </c>
       <c r="HU31" t="n">
         <v>0.043535305024288</v>
@@ -22588,139 +22588,139 @@
         <v>0.233491652414238</v>
       </c>
       <c r="GC32" t="n">
-        <v>0.236915441958085</v>
+        <v>0.236936917858783</v>
       </c>
       <c r="GD32" t="n">
-        <v>0.232967223869263</v>
+        <v>0.232440005048337</v>
       </c>
       <c r="GE32" t="n">
-        <v>0.233285362694306</v>
+        <v>0.233394095709435</v>
       </c>
       <c r="GF32" t="n">
-        <v>0.230386352538882</v>
+        <v>0.230667800200225</v>
       </c>
       <c r="GG32" t="n">
-        <v>0.229682814104195</v>
+        <v>0.230145926966961</v>
       </c>
       <c r="GH32" t="n">
-        <v>0.229291897872356</v>
+        <v>0.229913521069542</v>
       </c>
       <c r="GI32" t="n">
-        <v>0.229177580453934</v>
+        <v>0.229930659010228</v>
       </c>
       <c r="GJ32" t="n">
-        <v>0.229270887243102</v>
+        <v>0.230154653214519</v>
       </c>
       <c r="GK32" t="n">
-        <v>0.229281157994434</v>
+        <v>0.230280819277799</v>
       </c>
       <c r="GL32" t="n">
-        <v>0.229440217133751</v>
+        <v>0.230549729020334</v>
       </c>
       <c r="GM32" t="n">
-        <v>0.229788350846039</v>
+        <v>0.231011972877857</v>
       </c>
       <c r="GN32" t="n">
-        <v>0.229758904663866</v>
+        <v>0.231097590652736</v>
       </c>
       <c r="GO32" t="n">
-        <v>0.229572533583784</v>
+        <v>0.23102487155163</v>
       </c>
       <c r="GP32" t="n">
-        <v>0.229372213777244</v>
+        <v>0.230933276370575</v>
       </c>
       <c r="GQ32" t="n">
-        <v>0.229362590090049</v>
+        <v>0.231028278179631</v>
       </c>
       <c r="GR32" t="n">
-        <v>0.229311054630818</v>
+        <v>0.231071807729054</v>
       </c>
       <c r="GS32" t="n">
-        <v>0.229314819202131</v>
+        <v>0.231159963816852</v>
       </c>
       <c r="GT32" t="n">
-        <v>0.229308372073925</v>
+        <v>0.23122404512726</v>
       </c>
       <c r="GU32" t="n">
-        <v>0.229477862430882</v>
+        <v>0.231453603420165</v>
       </c>
       <c r="GV32" t="n">
-        <v>0.229574105575368</v>
+        <v>0.231598365093706</v>
       </c>
       <c r="GW32" t="n">
-        <v>0.229685801284219</v>
+        <v>0.231749266724201</v>
       </c>
       <c r="GX32" t="n">
-        <v>0.229757012045051</v>
+        <v>0.231850529341614</v>
       </c>
       <c r="GY32" t="n">
-        <v>0.229897817676451</v>
+        <v>0.232015984944638</v>
       </c>
       <c r="GZ32" t="n">
-        <v>0.229976973640873</v>
+        <v>0.232115845674111</v>
       </c>
       <c r="HA32" t="n">
-        <v>0.229999062546598</v>
+        <v>0.232155100301947</v>
       </c>
       <c r="HB32" t="n">
-        <v>0.22991113978964</v>
+        <v>0.232079083011315</v>
       </c>
       <c r="HC32" t="n">
-        <v>0.230000539404424</v>
+        <v>0.232181218923903</v>
       </c>
       <c r="HD32" t="n">
-        <v>0.22986544911674</v>
+        <v>0.232053741791337</v>
       </c>
       <c r="HE32" t="n">
-        <v>0.22977288174354</v>
+        <v>0.231969097570131</v>
       </c>
       <c r="HF32" t="n">
-        <v>0.229623209822612</v>
+        <v>0.231823833695587</v>
       </c>
       <c r="HG32" t="n">
-        <v>0.229541915414041</v>
+        <v>0.231745626241037</v>
       </c>
       <c r="HH32" t="n">
-        <v>0.229410400450314</v>
+        <v>0.2316166673679</v>
       </c>
       <c r="HI32" t="n">
-        <v>0.229227077436351</v>
+        <v>0.231434488361347</v>
       </c>
       <c r="HJ32" t="n">
-        <v>0.229017082365737</v>
+        <v>0.231223799860929</v>
       </c>
       <c r="HK32" t="n">
-        <v>0.228882703239293</v>
+        <v>0.231088497634166</v>
       </c>
       <c r="HL32" t="n">
-        <v>0.228700019617698</v>
+        <v>0.23090546935982</v>
       </c>
       <c r="HM32" t="n">
-        <v>0.228478022519514</v>
+        <v>0.230682968284136</v>
       </c>
       <c r="HN32" t="n">
-        <v>0.228239542695448</v>
+        <v>0.230443095757174</v>
       </c>
       <c r="HO32" t="n">
-        <v>0.228088937498853</v>
+        <v>0.230291651378359</v>
       </c>
       <c r="HP32" t="n">
-        <v>0.227913806713349</v>
+        <v>0.230117035167019</v>
       </c>
       <c r="HQ32" t="n">
-        <v>0.227703253067986</v>
+        <v>0.229906984346254</v>
       </c>
       <c r="HR32" t="n">
-        <v>0.227484648268088</v>
+        <v>0.229688106285017</v>
       </c>
       <c r="HS32" t="n">
-        <v>0.227520128769301</v>
+        <v>0.229728897424756</v>
       </c>
       <c r="HT32" t="n">
-        <v>0.227355780362617</v>
+        <v>0.22956526453186</v>
       </c>
       <c r="HU32" t="n">
-        <v>0.227279342235415</v>
+        <v>0.229493295930651</v>
       </c>
     </row>
     <row r="33">
@@ -23109,139 +23109,139 @@
         <v>82599</v>
       </c>
       <c r="GC33" t="n">
-        <v>82730.0045338344</v>
+        <v>82724.1708895118</v>
       </c>
       <c r="GD33" t="n">
-        <v>84321.2441617233</v>
+        <v>84465.7654103583</v>
       </c>
       <c r="GE33" t="n">
-        <v>85680.3975272089</v>
+        <v>85786.2651117149</v>
       </c>
       <c r="GF33" t="n">
-        <v>87471.1118921292</v>
+        <v>87450.5633069186</v>
       </c>
       <c r="GG33" t="n">
-        <v>89160.8213664285</v>
+        <v>89024.370858459</v>
       </c>
       <c r="GH33" t="n">
-        <v>90613.6003037998</v>
+        <v>90303.5456737264</v>
       </c>
       <c r="GI33" t="n">
-        <v>91827.62681118</v>
+        <v>91418.8819002486</v>
       </c>
       <c r="GJ33" t="n">
-        <v>92774.2311955532</v>
+        <v>92306.0203817792</v>
       </c>
       <c r="GK33" t="n">
-        <v>93583.1360925084</v>
+        <v>93065.2399601311</v>
       </c>
       <c r="GL33" t="n">
-        <v>94362.9610454857</v>
+        <v>93823.0030160202</v>
       </c>
       <c r="GM33" t="n">
-        <v>95066.0149121704</v>
+        <v>94504.8739641194</v>
       </c>
       <c r="GN33" t="n">
-        <v>95748.1325491151</v>
+        <v>95171.7657516056</v>
       </c>
       <c r="GO33" t="n">
-        <v>96278.764483901</v>
+        <v>95684.1273034821</v>
       </c>
       <c r="GP33" t="n">
-        <v>96906.6191730615</v>
+        <v>96293.4828609687</v>
       </c>
       <c r="GQ33" t="n">
-        <v>97451.2867583201</v>
+        <v>96819.2754932104</v>
       </c>
       <c r="GR33" t="n">
-        <v>98045.1716752286</v>
+        <v>97396.6980646816</v>
       </c>
       <c r="GS33" t="n">
-        <v>98622.6439894171</v>
+        <v>97961.5144614051</v>
       </c>
       <c r="GT33" t="n">
-        <v>99224.0015301039</v>
+        <v>98555.8174411528</v>
       </c>
       <c r="GU33" t="n">
-        <v>99795.9421671155</v>
+        <v>99126.8077321416</v>
       </c>
       <c r="GV33" t="n">
-        <v>100369.986949894</v>
+        <v>99705.2787728525</v>
       </c>
       <c r="GW33" t="n">
-        <v>100951.597093669</v>
+        <v>100295.553393575</v>
       </c>
       <c r="GX33" t="n">
-        <v>101556.359654764</v>
+        <v>100911.948589439</v>
       </c>
       <c r="GY33" t="n">
-        <v>102162.228543199</v>
+        <v>101530.977514083</v>
       </c>
       <c r="GZ33" t="n">
-        <v>102786.24296178</v>
+        <v>102167.845179498</v>
       </c>
       <c r="HA33" t="n">
-        <v>103438.03372993</v>
+        <v>102830.916067918</v>
       </c>
       <c r="HB33" t="n">
-        <v>104136.830740556</v>
+        <v>103538.973609983</v>
       </c>
       <c r="HC33" t="n">
-        <v>104830.482607297</v>
+        <v>104239.541358866</v>
       </c>
       <c r="HD33" t="n">
-        <v>105546.531468385</v>
+        <v>104959.846961418</v>
       </c>
       <c r="HE33" t="n">
-        <v>106279.196806135</v>
+        <v>105694.076656281</v>
       </c>
       <c r="HF33" t="n">
-        <v>107022.072999774</v>
+        <v>106436.311132736</v>
       </c>
       <c r="HG33" t="n">
-        <v>107749.171608195</v>
+        <v>107161.13985428</v>
       </c>
       <c r="HH33" t="n">
-        <v>108461.347394156</v>
+        <v>107869.174232782</v>
       </c>
       <c r="HI33" t="n">
-        <v>109168.923656873</v>
+        <v>108570.871817407</v>
       </c>
       <c r="HJ33" t="n">
-        <v>109875.01409602</v>
+        <v>109269.799729251</v>
       </c>
       <c r="HK33" t="n">
-        <v>110549.875719315</v>
+        <v>109936.587293902</v>
       </c>
       <c r="HL33" t="n">
-        <v>111202.094854671</v>
+        <v>110579.545001623</v>
       </c>
       <c r="HM33" t="n">
-        <v>111843.666651775</v>
+        <v>111210.642565656</v>
       </c>
       <c r="HN33" t="n">
-        <v>112475.331041877</v>
+        <v>111831.110706351</v>
       </c>
       <c r="HO33" t="n">
-        <v>113069.214097022</v>
+        <v>112413.525111625</v>
       </c>
       <c r="HP33" t="n">
-        <v>113629.779268746</v>
+        <v>112962.080900487</v>
       </c>
       <c r="HQ33" t="n">
-        <v>114174.105091784</v>
+        <v>113493.89919589</v>
       </c>
       <c r="HR33" t="n">
-        <v>114705.188992741</v>
+        <v>114012.487662769</v>
       </c>
       <c r="HS33" t="n">
-        <v>115188.033061984</v>
+        <v>114483.151573715</v>
       </c>
       <c r="HT33" t="n">
-        <v>115633.894716007</v>
+        <v>114916.99684252</v>
       </c>
       <c r="HU33" t="n">
-        <v>116071.666566925</v>
+        <v>115342.797040339</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sem_coredata.xlsx
+++ b/outputs/sem_coredata.xlsx
@@ -2754,139 +2754,139 @@
         <v>354377</v>
       </c>
       <c r="GC2" t="n">
-        <v>355091.626663159</v>
+        <v>355091.626663069</v>
       </c>
       <c r="GD2" t="n">
-        <v>360111.637408295</v>
+        <v>360111.637407478</v>
       </c>
       <c r="GE2" t="n">
-        <v>362966.815723289</v>
+        <v>362966.815722216</v>
       </c>
       <c r="GF2" t="n">
-        <v>366513.56131485</v>
+        <v>366513.561311229</v>
       </c>
       <c r="GG2" t="n">
-        <v>369343.65653203</v>
+        <v>369343.656520952</v>
       </c>
       <c r="GH2" t="n">
-        <v>371764.515144055</v>
+        <v>371764.515130078</v>
       </c>
       <c r="GI2" t="n">
-        <v>373741.073389824</v>
+        <v>373741.073366385</v>
       </c>
       <c r="GJ2" t="n">
-        <v>375470.918781582</v>
+        <v>375470.918749187</v>
       </c>
       <c r="GK2" t="n">
-        <v>377283.567466032</v>
+        <v>377283.567422444</v>
       </c>
       <c r="GL2" t="n">
-        <v>379125.691403618</v>
+        <v>379125.691348646</v>
       </c>
       <c r="GM2" t="n">
-        <v>380784.317869581</v>
+        <v>380784.317805237</v>
       </c>
       <c r="GN2" t="n">
-        <v>382307.490345511</v>
+        <v>382307.490272319</v>
       </c>
       <c r="GO2" t="n">
-        <v>384059.18819393</v>
+        <v>384059.188113549</v>
       </c>
       <c r="GP2" t="n">
-        <v>386011.016192965</v>
+        <v>386011.016107498</v>
       </c>
       <c r="GQ2" t="n">
-        <v>387799.538502192</v>
+        <v>387799.538413736</v>
       </c>
       <c r="GR2" t="n">
-        <v>389804.350803684</v>
+        <v>389804.350715036</v>
       </c>
       <c r="GS2" t="n">
-        <v>392020.281682245</v>
+        <v>392020.281594685</v>
       </c>
       <c r="GT2" t="n">
-        <v>394422.916539436</v>
+        <v>394422.916454055</v>
       </c>
       <c r="GU2" t="n">
-        <v>396625.977989916</v>
+        <v>396625.977907248</v>
       </c>
       <c r="GV2" t="n">
-        <v>399001.770005034</v>
+        <v>399001.76992623</v>
       </c>
       <c r="GW2" t="n">
-        <v>401600.960317238</v>
+        <v>401600.960242927</v>
       </c>
       <c r="GX2" t="n">
-        <v>404372.766736747</v>
+        <v>404372.766667307</v>
       </c>
       <c r="GY2" t="n">
-        <v>406945.693507214</v>
+        <v>406945.69344238</v>
       </c>
       <c r="GZ2" t="n">
-        <v>409686.461696267</v>
+        <v>409686.461636167</v>
       </c>
       <c r="HA2" t="n">
-        <v>412616.81008759</v>
+        <v>412616.810032024</v>
       </c>
       <c r="HB2" t="n">
-        <v>415689.571892267</v>
+        <v>415689.571841001</v>
       </c>
       <c r="HC2" t="n">
-        <v>418425.864141988</v>
+        <v>418425.864094204</v>
       </c>
       <c r="HD2" t="n">
-        <v>421316.136811352</v>
+        <v>421316.136766772</v>
       </c>
       <c r="HE2" t="n">
-        <v>424308.953161687</v>
+        <v>424308.9531196</v>
       </c>
       <c r="HF2" t="n">
-        <v>427360.250800108</v>
+        <v>427360.250759449</v>
       </c>
       <c r="HG2" t="n">
-        <v>430071.644645782</v>
+        <v>430071.644604869</v>
       </c>
       <c r="HH2" t="n">
-        <v>432810.305022509</v>
+        <v>432810.304980346</v>
       </c>
       <c r="HI2" t="n">
-        <v>435654.380400393</v>
+        <v>435654.380355762</v>
       </c>
       <c r="HJ2" t="n">
-        <v>438529.293802569</v>
+        <v>438529.293754509</v>
       </c>
       <c r="HK2" t="n">
-        <v>441038.018122278</v>
+        <v>441038.018069797</v>
       </c>
       <c r="HL2" t="n">
-        <v>443578.065262381</v>
+        <v>443578.065204849</v>
       </c>
       <c r="HM2" t="n">
-        <v>446209.067710323</v>
+        <v>446209.067647217</v>
       </c>
       <c r="HN2" t="n">
-        <v>448862.974386194</v>
+        <v>448862.974317128</v>
       </c>
       <c r="HO2" t="n">
-        <v>451133.358667824</v>
+        <v>451133.358592472</v>
       </c>
       <c r="HP2" t="n">
-        <v>453398.438581173</v>
+        <v>453398.438499591</v>
       </c>
       <c r="HQ2" t="n">
-        <v>455771.87818481</v>
+        <v>455771.878097093</v>
       </c>
       <c r="HR2" t="n">
-        <v>458182.393794065</v>
+        <v>458182.393700387</v>
       </c>
       <c r="HS2" t="n">
-        <v>460112.011705037</v>
+        <v>460112.011605524</v>
       </c>
       <c r="HT2" t="n">
-        <v>462135.122624696</v>
+        <v>462135.122519908</v>
       </c>
       <c r="HU2" t="n">
-        <v>464246.863894274</v>
+        <v>464246.863784685</v>
       </c>
     </row>
     <row r="3">
@@ -4135,136 +4135,136 @@
         <v>36864.8957689682</v>
       </c>
       <c r="GD4" t="n">
-        <v>37067.0321234082</v>
+        <v>37067.0321234074</v>
       </c>
       <c r="GE4" t="n">
-        <v>37241.6529393243</v>
+        <v>37241.6529393183</v>
       </c>
       <c r="GF4" t="n">
-        <v>37366.1984493942</v>
+        <v>37366.1984493968</v>
       </c>
       <c r="GG4" t="n">
-        <v>37326.3949317088</v>
+        <v>37326.3949317281</v>
       </c>
       <c r="GH4" t="n">
-        <v>37201.5948014705</v>
+        <v>37201.5948014852</v>
       </c>
       <c r="GI4" t="n">
-        <v>37027.6696104432</v>
+        <v>37027.6696104953</v>
       </c>
       <c r="GJ4" t="n">
-        <v>36908.9972932988</v>
+        <v>36908.9972933815</v>
       </c>
       <c r="GK4" t="n">
-        <v>36880.2350066421</v>
+        <v>36880.2350067634</v>
       </c>
       <c r="GL4" t="n">
-        <v>36964.5856614639</v>
+        <v>36964.5856616145</v>
       </c>
       <c r="GM4" t="n">
-        <v>37146.4706531439</v>
+        <v>37146.4706532988</v>
       </c>
       <c r="GN4" t="n">
-        <v>37391.9150101135</v>
+        <v>37391.9150102401</v>
       </c>
       <c r="GO4" t="n">
-        <v>37661.9482885952</v>
+        <v>37661.9482886244</v>
       </c>
       <c r="GP4" t="n">
-        <v>37926.6214422795</v>
+        <v>37926.6214421153</v>
       </c>
       <c r="GQ4" t="n">
-        <v>38165.0447148107</v>
+        <v>38165.0447143348</v>
       </c>
       <c r="GR4" t="n">
-        <v>38359.8279116673</v>
+        <v>38359.8279107349</v>
       </c>
       <c r="GS4" t="n">
-        <v>38506.0423271157</v>
+        <v>38506.0423255788</v>
       </c>
       <c r="GT4" t="n">
-        <v>38605.4985004893</v>
+        <v>38605.4984982038</v>
       </c>
       <c r="GU4" t="n">
-        <v>38667.1035923455</v>
+        <v>38667.1035891992</v>
       </c>
       <c r="GV4" t="n">
-        <v>38701.6561206232</v>
+        <v>38701.6561165574</v>
       </c>
       <c r="GW4" t="n">
-        <v>38724.7990810531</v>
+        <v>38724.7990760806</v>
       </c>
       <c r="GX4" t="n">
-        <v>38751.8275568061</v>
+        <v>38751.827551007</v>
       </c>
       <c r="GY4" t="n">
-        <v>38792.9873961775</v>
+        <v>38792.9873896796</v>
       </c>
       <c r="GZ4" t="n">
-        <v>38851.6988369897</v>
+        <v>38851.6988299463</v>
       </c>
       <c r="HA4" t="n">
-        <v>38930.7195260791</v>
+        <v>38930.7195186552</v>
       </c>
       <c r="HB4" t="n">
-        <v>39030.4748121544</v>
+        <v>39030.4748045109</v>
       </c>
       <c r="HC4" t="n">
-        <v>39148.6878407098</v>
+        <v>39148.6878329895</v>
       </c>
       <c r="HD4" t="n">
-        <v>39279.3211405225</v>
+        <v>39279.3211328398</v>
       </c>
       <c r="HE4" t="n">
-        <v>39421.5453587658</v>
+        <v>39421.5453512097</v>
       </c>
       <c r="HF4" t="n">
-        <v>39574.8636973929</v>
+        <v>39574.863690026</v>
       </c>
       <c r="HG4" t="n">
-        <v>39737.5408647172</v>
+        <v>39737.5408575742</v>
       </c>
       <c r="HH4" t="n">
-        <v>39906.3997087168</v>
+        <v>39906.3997018086</v>
       </c>
       <c r="HI4" t="n">
-        <v>40081.2831975642</v>
+        <v>40081.2831908876</v>
       </c>
       <c r="HJ4" t="n">
-        <v>40263.8838515558</v>
+        <v>40263.8838450976</v>
       </c>
       <c r="HK4" t="n">
-        <v>40453.8474176129</v>
+        <v>40453.8474113497</v>
       </c>
       <c r="HL4" t="n">
-        <v>40647.5150528972</v>
+        <v>40647.515046794</v>
       </c>
       <c r="HM4" t="n">
-        <v>40844.4435422706</v>
+        <v>40844.4435362812</v>
       </c>
       <c r="HN4" t="n">
-        <v>41044.6781158459</v>
+        <v>41044.6781099135</v>
       </c>
       <c r="HO4" t="n">
-        <v>41246.9612813887</v>
+        <v>41246.9612754461</v>
       </c>
       <c r="HP4" t="n">
-        <v>41447.1816180583</v>
+        <v>41447.1816120292</v>
       </c>
       <c r="HQ4" t="n">
-        <v>41644.8419514268</v>
+        <v>41644.8419452318</v>
       </c>
       <c r="HR4" t="n">
-        <v>41841.2713522708</v>
+        <v>41841.2713458308</v>
       </c>
       <c r="HS4" t="n">
-        <v>42036.4696194232</v>
+        <v>42036.4696126621</v>
       </c>
       <c r="HT4" t="n">
-        <v>42226.2625025448</v>
+        <v>42226.2624953921</v>
       </c>
       <c r="HU4" t="n">
-        <v>42412.3421229126</v>
+        <v>42412.3421153103</v>
       </c>
     </row>
     <row r="5">
@@ -4824,136 +4824,136 @@
         <v>11150.4565404427</v>
       </c>
       <c r="GD5" t="n">
-        <v>11211.5963480676</v>
+        <v>11211.5963480674</v>
       </c>
       <c r="GE5" t="n">
-        <v>11264.41358187</v>
+        <v>11264.4135818682</v>
       </c>
       <c r="GF5" t="n">
-        <v>11302.0846309364</v>
+        <v>11302.0846309372</v>
       </c>
       <c r="GG5" t="n">
-        <v>11290.0453348839</v>
+        <v>11290.0453348897</v>
       </c>
       <c r="GH5" t="n">
-        <v>11252.2972713281</v>
+        <v>11252.2972713326</v>
       </c>
       <c r="GI5" t="n">
-        <v>11199.6904418937</v>
+        <v>11199.6904419094</v>
       </c>
       <c r="GJ5" t="n">
-        <v>11163.795846581</v>
+        <v>11163.795846606</v>
       </c>
       <c r="GK5" t="n">
-        <v>11155.0961711667</v>
+        <v>11155.0961712034</v>
       </c>
       <c r="GL5" t="n">
-        <v>11180.609557035</v>
+        <v>11180.6095570806</v>
       </c>
       <c r="GM5" t="n">
-        <v>11235.6239725862</v>
+        <v>11235.6239726331</v>
       </c>
       <c r="GN5" t="n">
-        <v>11309.8630712843</v>
+        <v>11309.8630713226</v>
       </c>
       <c r="GO5" t="n">
-        <v>11391.5395353941</v>
+        <v>11391.5395354029</v>
       </c>
       <c r="GP5" t="n">
-        <v>11471.5947325137</v>
+        <v>11471.594732464</v>
       </c>
       <c r="GQ5" t="n">
-        <v>11543.7101768445</v>
+        <v>11543.7101767006</v>
       </c>
       <c r="GR5" t="n">
-        <v>11602.6258885549</v>
+        <v>11602.6258882729</v>
       </c>
       <c r="GS5" t="n">
-        <v>11646.8510911775</v>
+        <v>11646.8510907126</v>
       </c>
       <c r="GT5" t="n">
-        <v>11676.9334151811</v>
+        <v>11676.9334144898</v>
       </c>
       <c r="GU5" t="n">
-        <v>11695.5669928729</v>
+        <v>11695.5669919213</v>
       </c>
       <c r="GV5" t="n">
-        <v>11706.0180319139</v>
+        <v>11706.0180306841</v>
       </c>
       <c r="GW5" t="n">
-        <v>11713.0180401632</v>
+        <v>11713.0180386591</v>
       </c>
       <c r="GX5" t="n">
-        <v>11721.1932930142</v>
+        <v>11721.1932912602</v>
       </c>
       <c r="GY5" t="n">
-        <v>11733.6428331675</v>
+        <v>11733.6428312021</v>
       </c>
       <c r="GZ5" t="n">
-        <v>11751.4011736035</v>
+        <v>11751.4011714731</v>
       </c>
       <c r="HA5" t="n">
-        <v>11775.302414638</v>
+        <v>11775.3024123925</v>
       </c>
       <c r="HB5" t="n">
-        <v>11805.4752107048</v>
+        <v>11805.4752083929</v>
       </c>
       <c r="HC5" t="n">
-        <v>11841.2308858513</v>
+        <v>11841.2308835161</v>
       </c>
       <c r="HD5" t="n">
-        <v>11880.7432973721</v>
+        <v>11880.7432950483</v>
       </c>
       <c r="HE5" t="n">
-        <v>11923.7615924585</v>
+        <v>11923.761590173</v>
       </c>
       <c r="HF5" t="n">
-        <v>11970.1355055283</v>
+        <v>11970.1355033</v>
       </c>
       <c r="HG5" t="n">
-        <v>12019.3401661284</v>
+        <v>12019.3401639679</v>
       </c>
       <c r="HH5" t="n">
-        <v>12070.414586989</v>
+        <v>12070.4145848995</v>
       </c>
       <c r="HI5" t="n">
-        <v>12123.3112709849</v>
+        <v>12123.3112689655</v>
       </c>
       <c r="HJ5" t="n">
-        <v>12178.5421515861</v>
+        <v>12178.5421496327</v>
       </c>
       <c r="HK5" t="n">
-        <v>12236.0000785218</v>
+        <v>12236.0000766274</v>
       </c>
       <c r="HL5" t="n">
-        <v>12294.5783683958</v>
+        <v>12294.5783665498</v>
       </c>
       <c r="HM5" t="n">
-        <v>12354.1429627485</v>
+        <v>12354.1429609369</v>
       </c>
       <c r="HN5" t="n">
-        <v>12414.7075422481</v>
+        <v>12414.7075404538</v>
       </c>
       <c r="HO5" t="n">
-        <v>12475.8917555546</v>
+        <v>12475.8917537571</v>
       </c>
       <c r="HP5" t="n">
-        <v>12536.4520288438</v>
+        <v>12536.4520270202</v>
       </c>
       <c r="HQ5" t="n">
-        <v>12596.2379826901</v>
+        <v>12596.2379808164</v>
       </c>
       <c r="HR5" t="n">
-        <v>12655.6516186625</v>
+        <v>12655.6516167146</v>
       </c>
       <c r="HS5" t="n">
-        <v>12714.6928759142</v>
+        <v>12714.6928738692</v>
       </c>
       <c r="HT5" t="n">
-        <v>12772.0991766995</v>
+        <v>12772.0991745361</v>
       </c>
       <c r="HU5" t="n">
-        <v>12828.3823337977</v>
+        <v>12828.3823314982</v>
       </c>
     </row>
     <row r="6">
@@ -6845,136 +6845,136 @@
         <v>-20.3573504657543</v>
       </c>
       <c r="GD8" t="n">
-        <v>-90.2267479885777</v>
+        <v>-90.2267479940783</v>
       </c>
       <c r="GE8" t="n">
-        <v>1300.15462222291</v>
+        <v>1300.15462170143</v>
       </c>
       <c r="GF8" t="n">
-        <v>750.115392871114</v>
+        <v>750.115392416599</v>
       </c>
       <c r="GG8" t="n">
-        <v>1622.84160752018</v>
+        <v>1622.84160629017</v>
       </c>
       <c r="GH8" t="n">
-        <v>1388.8628645789</v>
+        <v>1388.8628626205</v>
       </c>
       <c r="GI8" t="n">
-        <v>1542.66794898894</v>
+        <v>1542.66794645082</v>
       </c>
       <c r="GJ8" t="n">
-        <v>1504.82924879182</v>
+        <v>1504.82924508708</v>
       </c>
       <c r="GK8" t="n">
-        <v>1448.01765546089</v>
+        <v>1448.01765096173</v>
       </c>
       <c r="GL8" t="n">
-        <v>1438.90367095036</v>
+        <v>1438.90366547572</v>
       </c>
       <c r="GM8" t="n">
-        <v>1405.02280541571</v>
+        <v>1405.02279910672</v>
       </c>
       <c r="GN8" t="n">
-        <v>1376.3765251381</v>
+        <v>1376.37651821572</v>
       </c>
       <c r="GO8" t="n">
-        <v>1263.83030050105</v>
+        <v>1263.83029302044</v>
       </c>
       <c r="GP8" t="n">
-        <v>1238.66428104902</v>
+        <v>1238.66427327847</v>
       </c>
       <c r="GQ8" t="n">
-        <v>1195.64947604897</v>
+        <v>1195.64946815255</v>
       </c>
       <c r="GR8" t="n">
-        <v>1131.03053443233</v>
+        <v>1131.03052656309</v>
       </c>
       <c r="GS8" t="n">
-        <v>1103.15937470915</v>
+        <v>1103.15936705007</v>
       </c>
       <c r="GT8" t="n">
-        <v>1063.8476710351</v>
+        <v>1063.84766366362</v>
       </c>
       <c r="GU8" t="n">
-        <v>1038.7648048368</v>
+        <v>1038.76479785377</v>
       </c>
       <c r="GV8" t="n">
-        <v>978.7361161359</v>
+        <v>978.736109595862</v>
       </c>
       <c r="GW8" t="n">
-        <v>967.462204679439</v>
+        <v>967.462198686117</v>
       </c>
       <c r="GX8" t="n">
-        <v>940.092699646426</v>
+        <v>940.09269424688</v>
       </c>
       <c r="GY8" t="n">
-        <v>931.674309202732</v>
+        <v>931.674304435961</v>
       </c>
       <c r="GZ8" t="n">
-        <v>903.798658655636</v>
+        <v>903.798654529091</v>
       </c>
       <c r="HA8" t="n">
-        <v>901.146800741553</v>
+        <v>901.146797295514</v>
       </c>
       <c r="HB8" t="n">
-        <v>902.067197531054</v>
+        <v>902.067194769246</v>
       </c>
       <c r="HC8" t="n">
-        <v>910.19703106425</v>
+        <v>910.197028988012</v>
       </c>
       <c r="HD8" t="n">
-        <v>866.462253498321</v>
+        <v>866.462252061086</v>
       </c>
       <c r="HE8" t="n">
-        <v>902.9678716505</v>
+        <v>902.967870824708</v>
       </c>
       <c r="HF8" t="n">
-        <v>888.612360439292</v>
+        <v>888.612360168772</v>
       </c>
       <c r="HG8" t="n">
-        <v>902.411000748863</v>
+        <v>902.411000945605</v>
       </c>
       <c r="HH8" t="n">
-        <v>887.3638488836</v>
+        <v>887.363849451271</v>
       </c>
       <c r="HI8" t="n">
-        <v>891.597339597734</v>
+        <v>891.597340488952</v>
       </c>
       <c r="HJ8" t="n">
-        <v>898.380844859144</v>
+        <v>898.38084599236</v>
       </c>
       <c r="HK8" t="n">
-        <v>905.821548136766</v>
+        <v>905.821549456188</v>
       </c>
       <c r="HL8" t="n">
-        <v>892.35852920037</v>
+        <v>892.358530647238</v>
       </c>
       <c r="HM8" t="n">
-        <v>895.498647183762</v>
+        <v>895.498648716515</v>
       </c>
       <c r="HN8" t="n">
-        <v>900.192165837361</v>
+        <v>900.192167421861</v>
       </c>
       <c r="HO8" t="n">
-        <v>904.466480011732</v>
+        <v>904.466481614683</v>
       </c>
       <c r="HP8" t="n">
-        <v>886.597160114878</v>
+        <v>886.597161710175</v>
       </c>
       <c r="HQ8" t="n">
-        <v>882.962041089049</v>
+        <v>882.962042668223</v>
       </c>
       <c r="HR8" t="n">
-        <v>882.816956517723</v>
+        <v>882.816958072741</v>
       </c>
       <c r="HS8" t="n">
-        <v>881.895998697844</v>
+        <v>881.896000223991</v>
       </c>
       <c r="HT8" t="n">
-        <v>809.527680856292</v>
+        <v>809.527682348329</v>
       </c>
       <c r="HU8" t="n">
-        <v>836.217219480255</v>
+        <v>836.217220947088</v>
       </c>
     </row>
     <row r="9">
@@ -8214,139 +8214,139 @@
         <v>680205</v>
       </c>
       <c r="GC10" t="n">
-        <v>686151.698852826</v>
+        <v>686151.698852727</v>
       </c>
       <c r="GD10" t="n">
-        <v>694469.036893127</v>
+        <v>694469.036883562</v>
       </c>
       <c r="GE10" t="n">
-        <v>701634.083487739</v>
+        <v>701634.083472192</v>
       </c>
       <c r="GF10" t="n">
-        <v>707838.19366459</v>
+        <v>707838.193632049</v>
       </c>
       <c r="GG10" t="n">
-        <v>714453.261756663</v>
+        <v>714453.26169773</v>
       </c>
       <c r="GH10" t="n">
-        <v>719156.513632876</v>
+        <v>719156.513545823</v>
       </c>
       <c r="GI10" t="n">
-        <v>723584.950029542</v>
+        <v>723584.949902403</v>
       </c>
       <c r="GJ10" t="n">
-        <v>727300.58684029</v>
+        <v>727300.586670054</v>
       </c>
       <c r="GK10" t="n">
-        <v>731077.234952298</v>
+        <v>731077.234734782</v>
       </c>
       <c r="GL10" t="n">
-        <v>735084.969436484</v>
+        <v>735084.969169306</v>
       </c>
       <c r="GM10" t="n">
-        <v>738943.676405493</v>
+        <v>738943.676090391</v>
       </c>
       <c r="GN10" t="n">
-        <v>742061.275995762</v>
+        <v>742061.275634361</v>
       </c>
       <c r="GO10" t="n">
-        <v>745200.995788866</v>
+        <v>745200.995385216</v>
       </c>
       <c r="GP10" t="n">
-        <v>748718.239887547</v>
+        <v>748718.239446365</v>
       </c>
       <c r="GQ10" t="n">
-        <v>751936.576780454</v>
+        <v>751936.576306462</v>
       </c>
       <c r="GR10" t="n">
-        <v>755352.39725432</v>
+        <v>755352.396752883</v>
       </c>
       <c r="GS10" t="n">
-        <v>758940.218613026</v>
+        <v>758940.218088405</v>
       </c>
       <c r="GT10" t="n">
-        <v>762671.887613351</v>
+        <v>762671.887069446</v>
       </c>
       <c r="GU10" t="n">
-        <v>766145.60080231</v>
+        <v>766145.600242602</v>
       </c>
       <c r="GV10" t="n">
-        <v>769744.054506591</v>
+        <v>769744.053934945</v>
       </c>
       <c r="GW10" t="n">
-        <v>773611.605871397</v>
+        <v>773611.605291337</v>
       </c>
       <c r="GX10" t="n">
-        <v>777666.857876584</v>
+        <v>777666.857291188</v>
       </c>
       <c r="GY10" t="n">
-        <v>781563.220815747</v>
+        <v>781563.220227576</v>
       </c>
       <c r="GZ10" t="n">
-        <v>785659.281869438</v>
+        <v>785659.281281269</v>
       </c>
       <c r="HA10" t="n">
-        <v>790022.802555796</v>
+        <v>790022.80197013</v>
       </c>
       <c r="HB10" t="n">
-        <v>794604.300495477</v>
+        <v>794604.299914567</v>
       </c>
       <c r="HC10" t="n">
-        <v>798873.090572194</v>
+        <v>798873.089997532</v>
       </c>
       <c r="HD10" t="n">
-        <v>803277.304734073</v>
+        <v>803277.304166793</v>
       </c>
       <c r="HE10" t="n">
-        <v>807893.32236988</v>
+        <v>807893.321810608</v>
       </c>
       <c r="HF10" t="n">
-        <v>812539.416419429</v>
+        <v>812539.415867795</v>
       </c>
       <c r="HG10" t="n">
-        <v>816868.543109336</v>
+        <v>816868.5425642</v>
       </c>
       <c r="HH10" t="n">
-        <v>821184.554477399</v>
+        <v>821184.553937992</v>
       </c>
       <c r="HI10" t="n">
-        <v>825626.773308382</v>
+        <v>825626.772773588</v>
       </c>
       <c r="HJ10" t="n">
-        <v>830109.660420463</v>
+        <v>830109.659889168</v>
       </c>
       <c r="HK10" t="n">
-        <v>834204.465185141</v>
+        <v>834204.464656314</v>
       </c>
       <c r="HL10" t="n">
-        <v>838288.076598739</v>
+        <v>838288.076071553</v>
       </c>
       <c r="HM10" t="n">
-        <v>842471.635115262</v>
+        <v>842471.63458907</v>
       </c>
       <c r="HN10" t="n">
-        <v>846673.326402296</v>
+        <v>846673.325876528</v>
       </c>
       <c r="HO10" t="n">
-        <v>850455.69044143</v>
+        <v>850455.689915724</v>
       </c>
       <c r="HP10" t="n">
-        <v>854171.453958644</v>
+        <v>854171.453433004</v>
       </c>
       <c r="HQ10" t="n">
-        <v>857989.739573044</v>
+        <v>857989.739047625</v>
       </c>
       <c r="HR10" t="n">
-        <v>861833.759763501</v>
+        <v>861833.759238553</v>
       </c>
       <c r="HS10" t="n">
-        <v>865146.576287026</v>
+        <v>865146.575762966</v>
       </c>
       <c r="HT10" t="n">
-        <v>868437.579641716</v>
+        <v>868437.579119187</v>
       </c>
       <c r="HU10" t="n">
-        <v>871903.39121881</v>
+        <v>871903.390698837</v>
       </c>
     </row>
     <row r="11">
@@ -8903,139 +8903,139 @@
         <v>170963</v>
       </c>
       <c r="GC11" t="n">
-        <v>167271.046249549</v>
+        <v>167271.04624954</v>
       </c>
       <c r="GD11" t="n">
-        <v>176031.075689716</v>
+        <v>176031.075688852</v>
       </c>
       <c r="GE11" t="n">
-        <v>170865.182394169</v>
+        <v>170865.182392949</v>
       </c>
       <c r="GF11" t="n">
-        <v>176644.965638819</v>
+        <v>176644.965636167</v>
       </c>
       <c r="GG11" t="n">
-        <v>176200.884370134</v>
+        <v>176200.88436541</v>
       </c>
       <c r="GH11" t="n">
-        <v>177377.736414144</v>
+        <v>177377.736407335</v>
       </c>
       <c r="GI11" t="n">
-        <v>178151.71278162</v>
+        <v>178151.712771635</v>
       </c>
       <c r="GJ11" t="n">
-        <v>178261.754958415</v>
+        <v>178261.754945155</v>
       </c>
       <c r="GK11" t="n">
-        <v>178815.627147161</v>
+        <v>178815.627130239</v>
       </c>
       <c r="GL11" t="n">
-        <v>179257.031787558</v>
+        <v>179257.031766782</v>
       </c>
       <c r="GM11" t="n">
-        <v>180016.825957266</v>
+        <v>180016.825932788</v>
       </c>
       <c r="GN11" t="n">
-        <v>179978.181390585</v>
+        <v>179978.181362474</v>
       </c>
       <c r="GO11" t="n">
-        <v>180405.008175008</v>
+        <v>180405.008143558</v>
       </c>
       <c r="GP11" t="n">
-        <v>180741.978653783</v>
+        <v>180741.978619332</v>
       </c>
       <c r="GQ11" t="n">
-        <v>180938.133373195</v>
+        <v>180938.133336089</v>
       </c>
       <c r="GR11" t="n">
-        <v>181250.524981689</v>
+        <v>181250.524942348</v>
       </c>
       <c r="GS11" t="n">
-        <v>181484.448091708</v>
+        <v>181484.448050463</v>
       </c>
       <c r="GT11" t="n">
-        <v>181758.469971378</v>
+        <v>181758.469928563</v>
       </c>
       <c r="GU11" t="n">
-        <v>181806.108455316</v>
+        <v>181806.108411248</v>
       </c>
       <c r="GV11" t="n">
-        <v>182121.450541807</v>
+        <v>182121.450496848</v>
       </c>
       <c r="GW11" t="n">
-        <v>182287.604716295</v>
+        <v>182287.604670782</v>
       </c>
       <c r="GX11" t="n">
-        <v>182526.076302904</v>
+        <v>182526.076257147</v>
       </c>
       <c r="GY11" t="n">
-        <v>182726.345893527</v>
+        <v>182726.345847796</v>
       </c>
       <c r="GZ11" t="n">
-        <v>182973.490123307</v>
+        <v>182973.490077899</v>
       </c>
       <c r="HA11" t="n">
-        <v>183242.679900441</v>
+        <v>183242.679855626</v>
       </c>
       <c r="HB11" t="n">
-        <v>183546.983033183</v>
+        <v>183546.982989212</v>
       </c>
       <c r="HC11" t="n">
-        <v>183443.217284496</v>
+        <v>183443.217241549</v>
       </c>
       <c r="HD11" t="n">
-        <v>183930.945772444</v>
+        <v>183930.94573068</v>
       </c>
       <c r="HE11" t="n">
-        <v>184060.468258546</v>
+        <v>184060.468218081</v>
       </c>
       <c r="HF11" t="n">
-        <v>184317.628546567</v>
+        <v>184317.628507436</v>
       </c>
       <c r="HG11" t="n">
-        <v>184540.729144367</v>
+        <v>184540.729106543</v>
       </c>
       <c r="HH11" t="n">
-        <v>184798.479703433</v>
+        <v>184798.479666928</v>
       </c>
       <c r="HI11" t="n">
-        <v>185086.010393281</v>
+        <v>185086.010358062</v>
       </c>
       <c r="HJ11" t="n">
-        <v>185395.630212838</v>
+        <v>185395.630178871</v>
       </c>
       <c r="HK11" t="n">
-        <v>185691.925744991</v>
+        <v>185691.92571223</v>
       </c>
       <c r="HL11" t="n">
-        <v>186014.436284361</v>
+        <v>186014.436252772</v>
       </c>
       <c r="HM11" t="n">
-        <v>186363.765723082</v>
+        <v>186363.765692636</v>
       </c>
       <c r="HN11" t="n">
-        <v>186730.311996738</v>
+        <v>186730.3119674</v>
       </c>
       <c r="HO11" t="n">
-        <v>187078.793668092</v>
+        <v>187078.793639832</v>
       </c>
       <c r="HP11" t="n">
-        <v>187446.061250915</v>
+        <v>187446.061223724</v>
       </c>
       <c r="HQ11" t="n">
-        <v>187838.127408312</v>
+        <v>187838.127382192</v>
       </c>
       <c r="HR11" t="n">
-        <v>188244.707910165</v>
+        <v>188244.70788512</v>
       </c>
       <c r="HS11" t="n">
-        <v>188027.033738587</v>
+        <v>188027.033714589</v>
       </c>
       <c r="HT11" t="n">
-        <v>188557.058287394</v>
+        <v>188557.0582645</v>
       </c>
       <c r="HU11" t="n">
-        <v>188598.578621348</v>
+        <v>188598.578599589</v>
       </c>
     </row>
     <row r="12">
@@ -9592,139 +9592,139 @@
         <v>162177</v>
       </c>
       <c r="GC12" t="n">
-        <v>164127.999631379</v>
+        <v>164127.999631347</v>
       </c>
       <c r="GD12" t="n">
-        <v>166239.28472695</v>
+        <v>166239.284723838</v>
       </c>
       <c r="GE12" t="n">
-        <v>167937.232204659</v>
+        <v>167937.23219837</v>
       </c>
       <c r="GF12" t="n">
-        <v>169303.160264164</v>
+        <v>169303.160251793</v>
       </c>
       <c r="GG12" t="n">
-        <v>170725.438426201</v>
+        <v>170725.438403386</v>
       </c>
       <c r="GH12" t="n">
-        <v>171680.898325422</v>
+        <v>171680.898290774</v>
       </c>
       <c r="GI12" t="n">
-        <v>172317.179089587</v>
+        <v>172317.179039621</v>
       </c>
       <c r="GJ12" t="n">
-        <v>172682.899339875</v>
+        <v>172682.899272737</v>
       </c>
       <c r="GK12" t="n">
-        <v>173114.338580482</v>
+        <v>173114.338495252</v>
       </c>
       <c r="GL12" t="n">
-        <v>173789.024288664</v>
+        <v>173789.024184772</v>
       </c>
       <c r="GM12" t="n">
-        <v>174742.11602585</v>
+        <v>174742.115904171</v>
       </c>
       <c r="GN12" t="n">
-        <v>175369.851845832</v>
+        <v>175369.851707981</v>
       </c>
       <c r="GO12" t="n">
-        <v>176004.791162634</v>
+        <v>176004.79101067</v>
       </c>
       <c r="GP12" t="n">
-        <v>176870.73038177</v>
+        <v>176870.730218012</v>
       </c>
       <c r="GQ12" t="n">
-        <v>177791.069599422</v>
+        <v>177791.069426114</v>
       </c>
       <c r="GR12" t="n">
-        <v>178811.854088297</v>
+        <v>178811.853907665</v>
       </c>
       <c r="GS12" t="n">
-        <v>180002.215002907</v>
+        <v>180002.21481667</v>
       </c>
       <c r="GT12" t="n">
-        <v>181339.807857352</v>
+        <v>181339.807666797</v>
       </c>
       <c r="GU12" t="n">
-        <v>182679.735025345</v>
+        <v>182679.734831497</v>
       </c>
       <c r="GV12" t="n">
-        <v>184079.125247573</v>
+        <v>184079.125051405</v>
       </c>
       <c r="GW12" t="n">
-        <v>185634.647243332</v>
+        <v>185634.647045657</v>
       </c>
       <c r="GX12" t="n">
-        <v>187330.211164966</v>
+        <v>187330.210966362</v>
       </c>
       <c r="GY12" t="n">
-        <v>189027.074370099</v>
+        <v>189027.074170939</v>
       </c>
       <c r="GZ12" t="n">
-        <v>190786.82471245</v>
+        <v>190786.824513089</v>
       </c>
       <c r="HA12" t="n">
-        <v>192675.659863394</v>
+        <v>192675.659664138</v>
       </c>
       <c r="HB12" t="n">
-        <v>194683.920846349</v>
+        <v>194683.920647423</v>
       </c>
       <c r="HC12" t="n">
-        <v>196612.082723308</v>
+        <v>196612.082524768</v>
       </c>
       <c r="HD12" t="n">
-        <v>198531.443002212</v>
+        <v>198531.44280393</v>
       </c>
       <c r="HE12" t="n">
-        <v>200530.244647584</v>
+        <v>200530.244449268</v>
       </c>
       <c r="HF12" t="n">
-        <v>202553.034821691</v>
+        <v>202553.034622749</v>
       </c>
       <c r="HG12" t="n">
-        <v>204450.972474851</v>
+        <v>204450.972274439</v>
       </c>
       <c r="HH12" t="n">
-        <v>206276.578665875</v>
+        <v>206276.578463262</v>
       </c>
       <c r="HI12" t="n">
-        <v>208126.568088835</v>
+        <v>208126.567883317</v>
       </c>
       <c r="HJ12" t="n">
-        <v>209991.700053094</v>
+        <v>209991.699844028</v>
       </c>
       <c r="HK12" t="n">
-        <v>211710.894272675</v>
+        <v>211710.894059617</v>
       </c>
       <c r="HL12" t="n">
-        <v>213353.146507385</v>
+        <v>213353.146290048</v>
       </c>
       <c r="HM12" t="n">
-        <v>215021.366850103</v>
+        <v>215021.366628337</v>
       </c>
       <c r="HN12" t="n">
-        <v>216705.657919522</v>
+        <v>216705.657693303</v>
       </c>
       <c r="HO12" t="n">
-        <v>218242.222005186</v>
+        <v>218242.221774699</v>
       </c>
       <c r="HP12" t="n">
-        <v>219693.46952269</v>
+        <v>219693.469288297</v>
       </c>
       <c r="HQ12" t="n">
-        <v>221179.431208337</v>
+        <v>221179.430970478</v>
       </c>
       <c r="HR12" t="n">
-        <v>222700.395233656</v>
+        <v>222700.394992835</v>
       </c>
       <c r="HS12" t="n">
-        <v>224050.96023316</v>
+        <v>224050.959990048</v>
       </c>
       <c r="HT12" t="n">
-        <v>225329.288560287</v>
+        <v>225329.288315607</v>
       </c>
       <c r="HU12" t="n">
-        <v>226690.202499314</v>
+        <v>226690.202253854</v>
       </c>
     </row>
     <row r="13">
@@ -10281,139 +10281,139 @@
         <v>688271</v>
       </c>
       <c r="GC13" t="n">
-        <v>688864.763365552</v>
+        <v>688864.763365476</v>
       </c>
       <c r="GD13" t="n">
-        <v>703830.84954872</v>
+        <v>703830.849541404</v>
       </c>
       <c r="GE13" t="n">
-        <v>704132.055984009</v>
+        <v>704132.055973531</v>
       </c>
       <c r="GF13" t="n">
-        <v>714750.021573421</v>
+        <v>714750.021550599</v>
       </c>
       <c r="GG13" t="n">
-        <v>719498.731692409</v>
+        <v>719498.731651568</v>
       </c>
       <c r="GH13" t="n">
-        <v>724423.374010534</v>
+        <v>724423.373951321</v>
       </c>
       <c r="GI13" t="n">
-        <v>728989.507649247</v>
+        <v>728989.50756209</v>
       </c>
       <c r="GJ13" t="n">
-        <v>732449.466179321</v>
+        <v>732449.466062963</v>
       </c>
       <c r="GK13" t="n">
-        <v>736348.54674915</v>
+        <v>736348.546599943</v>
       </c>
       <c r="GL13" t="n">
-        <v>740122.999693959</v>
+        <v>740122.999509897</v>
       </c>
       <c r="GM13" t="n">
-        <v>743788.40869606</v>
+        <v>743788.408478161</v>
       </c>
       <c r="GN13" t="n">
-        <v>746239.627935882</v>
+        <v>746239.627684222</v>
       </c>
       <c r="GO13" t="n">
-        <v>749171.237096983</v>
+        <v>749171.236813848</v>
       </c>
       <c r="GP13" t="n">
-        <v>752159.512213833</v>
+        <v>752159.511901959</v>
       </c>
       <c r="GQ13" t="n">
-        <v>754653.664396219</v>
+        <v>754653.664058429</v>
       </c>
       <c r="GR13" t="n">
-        <v>757361.091511131</v>
+        <v>757361.091150985</v>
       </c>
       <c r="GS13" t="n">
-        <v>759992.474538354</v>
+        <v>759992.474158724</v>
       </c>
       <c r="GT13" t="n">
-        <v>762660.573817417</v>
+        <v>762660.573421252</v>
       </c>
       <c r="GU13" t="n">
-        <v>764841.997617819</v>
+        <v>764841.997207891</v>
       </c>
       <c r="GV13" t="n">
-        <v>767356.404221362</v>
+        <v>767356.403800925</v>
       </c>
       <c r="GW13" t="n">
-        <v>769834.58665443</v>
+        <v>769834.586226534</v>
       </c>
       <c r="GX13" t="n">
-        <v>772432.746960698</v>
+        <v>772432.746528149</v>
       </c>
       <c r="GY13" t="n">
-        <v>774832.516786322</v>
+        <v>774832.516351579</v>
       </c>
       <c r="GZ13" t="n">
-        <v>777415.971921536</v>
+        <v>777415.971487319</v>
       </c>
       <c r="HA13" t="n">
-        <v>780159.847202067</v>
+        <v>780159.846770841</v>
       </c>
       <c r="HB13" t="n">
-        <v>783037.389057773</v>
+        <v>783037.388631817</v>
       </c>
       <c r="HC13" t="n">
-        <v>785274.251252425</v>
+        <v>785274.250833356</v>
       </c>
       <c r="HD13" t="n">
-        <v>788246.832876149</v>
+        <v>788246.832465388</v>
       </c>
       <c r="HE13" t="n">
-        <v>790993.572697295</v>
+        <v>790993.572295875</v>
       </c>
       <c r="HF13" t="n">
-        <v>793874.03583562</v>
+        <v>793874.035443795</v>
       </c>
       <c r="HG13" t="n">
-        <v>796528.326599885</v>
+        <v>796528.326217336</v>
       </c>
       <c r="HH13" t="n">
-        <v>799276.483460888</v>
+        <v>799276.483087589</v>
       </c>
       <c r="HI13" t="n">
-        <v>802156.242258312</v>
+        <v>802156.241893817</v>
       </c>
       <c r="HJ13" t="n">
-        <v>805083.61810318</v>
+        <v>805083.617746983</v>
       </c>
       <c r="HK13" t="n">
-        <v>807755.525110946</v>
+        <v>807755.524762415</v>
       </c>
       <c r="HL13" t="n">
-        <v>810519.395674786</v>
+        <v>810519.395333347</v>
       </c>
       <c r="HM13" t="n">
-        <v>813384.061657148</v>
+        <v>813384.061322275</v>
       </c>
       <c r="HN13" t="n">
-        <v>816268.00886243</v>
+        <v>816268.008533543</v>
       </c>
       <c r="HO13" t="n">
-        <v>818862.291296526</v>
+        <v>818862.290973044</v>
       </c>
       <c r="HP13" t="n">
-        <v>821494.075798863</v>
+        <v>821494.075480425</v>
       </c>
       <c r="HQ13" t="n">
-        <v>824218.466765003</v>
+        <v>824218.466451323</v>
       </c>
       <c r="HR13" t="n">
-        <v>826948.101658237</v>
+        <v>826948.101349064</v>
       </c>
       <c r="HS13" t="n">
-        <v>828692.680348822</v>
+        <v>828692.680043875</v>
       </c>
       <c r="HT13" t="n">
-        <v>831235.381014186</v>
+        <v>831235.380713444</v>
       </c>
       <c r="HU13" t="n">
-        <v>833381.797542954</v>
+        <v>833381.797246681</v>
       </c>
     </row>
     <row r="14">
@@ -10802,139 +10802,139 @@
         <v>681761</v>
       </c>
       <c r="GC14" t="n">
-        <v>686013.110077929</v>
+        <v>686013.11007783</v>
       </c>
       <c r="GD14" t="n">
-        <v>694400.273349485</v>
+        <v>694400.273339925</v>
       </c>
       <c r="GE14" t="n">
-        <v>700174.941883743</v>
+        <v>700174.941868718</v>
       </c>
       <c r="GF14" t="n">
-        <v>706929.088411136</v>
+        <v>706929.08837905</v>
       </c>
       <c r="GG14" t="n">
-        <v>712671.431778864</v>
+        <v>712671.431721161</v>
       </c>
       <c r="GH14" t="n">
-        <v>717608.661606568</v>
+        <v>717608.661521473</v>
       </c>
       <c r="GI14" t="n">
-        <v>721883.294219463</v>
+        <v>721883.294094862</v>
       </c>
       <c r="GJ14" t="n">
-        <v>725636.769639405</v>
+        <v>725636.769472873</v>
       </c>
       <c r="GK14" t="n">
-        <v>729470.228951247</v>
+        <v>729470.228738231</v>
       </c>
       <c r="GL14" t="n">
-        <v>733487.077052758</v>
+        <v>733487.076791055</v>
       </c>
       <c r="GM14" t="n">
-        <v>737379.66480841</v>
+        <v>737379.664499617</v>
       </c>
       <c r="GN14" t="n">
-        <v>740525.910482556</v>
+        <v>740525.910128077</v>
       </c>
       <c r="GO14" t="n">
-        <v>743778.177580505</v>
+        <v>743778.177184336</v>
       </c>
       <c r="GP14" t="n">
-        <v>747320.587442893</v>
+        <v>747320.587009481</v>
       </c>
       <c r="GQ14" t="n">
-        <v>750581.939056286</v>
+        <v>750581.938590191</v>
       </c>
       <c r="GR14" t="n">
-        <v>754062.378227655</v>
+        <v>754062.377734088</v>
       </c>
       <c r="GS14" t="n">
-        <v>757678.07051085</v>
+        <v>757678.069993888</v>
       </c>
       <c r="GT14" t="n">
-        <v>761449.052235006</v>
+        <v>761449.051698472</v>
       </c>
       <c r="GU14" t="n">
-        <v>764947.848035862</v>
+        <v>764947.847483137</v>
       </c>
       <c r="GV14" t="n">
-        <v>768606.331382509</v>
+        <v>768606.330817403</v>
       </c>
       <c r="GW14" t="n">
-        <v>772485.156007613</v>
+        <v>772485.155433547</v>
       </c>
       <c r="GX14" t="n">
-        <v>776567.77807509</v>
+        <v>776567.777495093</v>
       </c>
       <c r="GY14" t="n">
-        <v>780472.559873225</v>
+        <v>780472.55928982</v>
       </c>
       <c r="GZ14" t="n">
-        <v>784596.496739006</v>
+        <v>784596.496154962</v>
       </c>
       <c r="HA14" t="n">
-        <v>788962.669178936</v>
+        <v>788962.668596715</v>
       </c>
       <c r="HB14" t="n">
-        <v>793543.247837884</v>
+        <v>793543.247259735</v>
       </c>
       <c r="HC14" t="n">
-        <v>797803.907770255</v>
+        <v>797803.907197669</v>
       </c>
       <c r="HD14" t="n">
-        <v>802251.85591178</v>
+        <v>802251.855345938</v>
       </c>
       <c r="HE14" t="n">
-        <v>806831.368628584</v>
+        <v>806831.368070138</v>
       </c>
       <c r="HF14" t="n">
-        <v>811491.817153433</v>
+        <v>811491.816602069</v>
       </c>
       <c r="HG14" t="n">
-        <v>815807.145706852</v>
+        <v>815807.145161518</v>
       </c>
       <c r="HH14" t="n">
-        <v>820138.204594016</v>
+        <v>820138.204054042</v>
       </c>
       <c r="HI14" t="n">
-        <v>824576.188596444</v>
+        <v>824576.188060757</v>
       </c>
       <c r="HJ14" t="n">
-        <v>829052.292312132</v>
+        <v>829052.291779703</v>
       </c>
       <c r="HK14" t="n">
-        <v>833139.656556559</v>
+        <v>833139.656026412</v>
       </c>
       <c r="HL14" t="n">
-        <v>837236.731124829</v>
+        <v>837236.730596195</v>
       </c>
       <c r="HM14" t="n">
-        <v>841417.148015816</v>
+        <v>841417.147488091</v>
       </c>
       <c r="HN14" t="n">
-        <v>845614.145780745</v>
+        <v>845614.145253391</v>
       </c>
       <c r="HO14" t="n">
-        <v>849392.235641785</v>
+        <v>849392.235114475</v>
       </c>
       <c r="HP14" t="n">
-        <v>853125.868677454</v>
+        <v>853125.868150218</v>
       </c>
       <c r="HQ14" t="n">
-        <v>856947.789587209</v>
+        <v>856947.78906021</v>
       </c>
       <c r="HR14" t="n">
-        <v>860791.953423659</v>
+        <v>860791.952897155</v>
       </c>
       <c r="HS14" t="n">
-        <v>864105.691493479</v>
+        <v>864105.690967893</v>
       </c>
       <c r="HT14" t="n">
-        <v>867469.06358935</v>
+        <v>867469.063065328</v>
       </c>
       <c r="HU14" t="n">
-        <v>870908.184557711</v>
+        <v>870908.184036271</v>
       </c>
     </row>
     <row r="15">
@@ -11491,139 +11491,139 @@
         <v>718591</v>
       </c>
       <c r="GC15" t="n">
-        <v>722446.302045062</v>
+        <v>722446.302044982</v>
       </c>
       <c r="GD15" t="n">
-        <v>746841.514138348</v>
+        <v>746841.514130855</v>
       </c>
       <c r="GE15" t="n">
-        <v>757812.555747706</v>
+        <v>757812.555736813</v>
       </c>
       <c r="GF15" t="n">
-        <v>778371.835122549</v>
+        <v>778371.835098437</v>
       </c>
       <c r="GG15" t="n">
-        <v>793842.402552691</v>
+        <v>793842.402508656</v>
       </c>
       <c r="GH15" t="n">
-        <v>807990.766741129</v>
+        <v>807990.76667608</v>
       </c>
       <c r="GI15" t="n">
-        <v>821810.431404711</v>
+        <v>821810.431307194</v>
       </c>
       <c r="GJ15" t="n">
-        <v>834703.713560883</v>
+        <v>834703.713428229</v>
       </c>
       <c r="GK15" t="n">
-        <v>848043.203719166</v>
+        <v>848043.203545536</v>
       </c>
       <c r="GL15" t="n">
-        <v>861102.643279916</v>
+        <v>861102.643061212</v>
       </c>
       <c r="GM15" t="n">
-        <v>873597.576270051</v>
+        <v>873597.576005307</v>
       </c>
       <c r="GN15" t="n">
-        <v>885059.331284632</v>
+        <v>885059.330973302</v>
       </c>
       <c r="GO15" t="n">
-        <v>897019.262146209</v>
+        <v>897019.261789473</v>
       </c>
       <c r="GP15" t="n">
-        <v>909164.944193245</v>
+        <v>909164.943793132</v>
       </c>
       <c r="GQ15" t="n">
-        <v>920700.640583452</v>
+        <v>920700.640142711</v>
       </c>
       <c r="GR15" t="n">
-        <v>932467.547069454</v>
+        <v>932467.546592016</v>
       </c>
       <c r="GS15" t="n">
-        <v>944155.413596801</v>
+        <v>944155.41308597</v>
       </c>
       <c r="GT15" t="n">
-        <v>955984.012813794</v>
+        <v>955984.012273151</v>
       </c>
       <c r="GU15" t="n">
-        <v>967288.147677384</v>
+        <v>967288.147110588</v>
       </c>
       <c r="GV15" t="n">
-        <v>978997.28482864</v>
+        <v>978997.284240044</v>
       </c>
       <c r="GW15" t="n">
-        <v>990789.867865746</v>
+        <v>990789.867259504</v>
       </c>
       <c r="GX15" t="n">
-        <v>1002845.58428255</v>
+        <v>1002845.58366263</v>
       </c>
       <c r="GY15" t="n">
-        <v>1014757.8865042</v>
+        <v>1014757.88587424</v>
       </c>
       <c r="GZ15" t="n">
-        <v>1027039.49946996</v>
+        <v>1027039.49883388</v>
       </c>
       <c r="HA15" t="n">
-        <v>1039691.65308855</v>
+        <v>1039691.65244991</v>
       </c>
       <c r="HB15" t="n">
-        <v>1052952.94733534</v>
+        <v>1052952.94669761</v>
       </c>
       <c r="HC15" t="n">
-        <v>1065661.62884991</v>
+        <v>1065661.62821555</v>
       </c>
       <c r="HD15" t="n">
-        <v>1079358.52194496</v>
+        <v>1079358.52131661</v>
       </c>
       <c r="HE15" t="n">
-        <v>1093109.61096019</v>
+        <v>1093109.6103393</v>
       </c>
       <c r="HF15" t="n">
-        <v>1107234.20815783</v>
+        <v>1107234.2075451</v>
       </c>
       <c r="HG15" t="n">
-        <v>1121256.68955603</v>
+        <v>1121256.68895134</v>
       </c>
       <c r="HH15" t="n">
-        <v>1135620.57414407</v>
+        <v>1135620.57354751</v>
       </c>
       <c r="HI15" t="n">
-        <v>1150398.95882404</v>
+        <v>1150398.95823496</v>
       </c>
       <c r="HJ15" t="n">
-        <v>1165479.96961579</v>
+        <v>1165479.96903339</v>
       </c>
       <c r="HK15" t="n">
-        <v>1180401.49897993</v>
+        <v>1180401.49840334</v>
       </c>
       <c r="HL15" t="n">
-        <v>1195675.87276343</v>
+        <v>1195675.87219166</v>
       </c>
       <c r="HM15" t="n">
-        <v>1211331.22806387</v>
+        <v>1211331.22749581</v>
       </c>
       <c r="HN15" t="n">
-        <v>1227252.81136499</v>
+        <v>1227252.81079942</v>
       </c>
       <c r="HO15" t="n">
-        <v>1242945.33516719</v>
+        <v>1242945.33460305</v>
       </c>
       <c r="HP15" t="n">
-        <v>1258900.15350632</v>
+        <v>1258900.15294271</v>
       </c>
       <c r="HQ15" t="n">
-        <v>1275221.73057883</v>
+        <v>1275221.73001482</v>
       </c>
       <c r="HR15" t="n">
-        <v>1291783.46875486</v>
+        <v>1291783.46818958</v>
       </c>
       <c r="HS15" t="n">
-        <v>1307274.16872154</v>
+        <v>1307274.1681537</v>
       </c>
       <c r="HT15" t="n">
-        <v>1323868.70714823</v>
+        <v>1323868.70657816</v>
       </c>
       <c r="HU15" t="n">
-        <v>1340281.99477371</v>
+        <v>1340281.99420086</v>
       </c>
     </row>
     <row r="16">
@@ -12183,136 +12183,136 @@
         <v>1.04874901737806</v>
       </c>
       <c r="GD16" t="n">
-        <v>1.06110937297941</v>
+        <v>1.0611093729798</v>
       </c>
       <c r="GE16" t="n">
-        <v>1.0762364089767</v>
+        <v>1.07623640897724</v>
       </c>
       <c r="GF16" t="n">
-        <v>1.08901267043912</v>
+        <v>1.08901267044016</v>
       </c>
       <c r="GG16" t="n">
-        <v>1.10332702677654</v>
+        <v>1.10332702677796</v>
       </c>
       <c r="GH16" t="n">
-        <v>1.11535710904923</v>
+        <v>1.1153571090506</v>
       </c>
       <c r="GI16" t="n">
-        <v>1.12732819417544</v>
+        <v>1.12732819417645</v>
       </c>
       <c r="GJ16" t="n">
-        <v>1.13960586602926</v>
+        <v>1.13960586602919</v>
       </c>
       <c r="GK16" t="n">
-        <v>1.15168720392873</v>
+        <v>1.1516872039263</v>
       </c>
       <c r="GL16" t="n">
-        <v>1.16345882946938</v>
+        <v>1.16345882946323</v>
       </c>
       <c r="GM16" t="n">
-        <v>1.17452431628372</v>
+        <v>1.17452431627187</v>
       </c>
       <c r="GN16" t="n">
-        <v>1.18602563439812</v>
+        <v>1.18602563438089</v>
       </c>
       <c r="GO16" t="n">
-        <v>1.19734877146588</v>
+        <v>1.19734877144222</v>
       </c>
       <c r="GP16" t="n">
-        <v>1.20873954028807</v>
+        <v>1.20873954025731</v>
       </c>
       <c r="GQ16" t="n">
-        <v>1.22003070218728</v>
+        <v>1.22003070214935</v>
       </c>
       <c r="GR16" t="n">
-        <v>1.23120603552548</v>
+        <v>1.23120603548056</v>
       </c>
       <c r="GS16" t="n">
-        <v>1.24232205618705</v>
+        <v>1.24232205613546</v>
       </c>
       <c r="GT16" t="n">
-        <v>1.25348555610129</v>
+        <v>1.25348555604352</v>
       </c>
       <c r="GU16" t="n">
-        <v>1.26469016000331</v>
+        <v>1.26469015994008</v>
       </c>
       <c r="GV16" t="n">
-        <v>1.27580519375047</v>
+        <v>1.27580519368244</v>
       </c>
       <c r="GW16" t="n">
-        <v>1.28701656908349</v>
+        <v>1.28701656901135</v>
       </c>
       <c r="GX16" t="n">
-        <v>1.29829501498549</v>
+        <v>1.29829501490994</v>
       </c>
       <c r="GY16" t="n">
-        <v>1.30964803986344</v>
+        <v>1.30964803978524</v>
       </c>
       <c r="GZ16" t="n">
-        <v>1.3210939013468</v>
+        <v>1.32109390126648</v>
       </c>
       <c r="HA16" t="n">
-        <v>1.33266490950204</v>
+        <v>1.33266490942006</v>
       </c>
       <c r="HB16" t="n">
-        <v>1.34470328059357</v>
+        <v>1.34470328051064</v>
       </c>
       <c r="HC16" t="n">
-        <v>1.35705662675721</v>
+        <v>1.35705662667359</v>
       </c>
       <c r="HD16" t="n">
-        <v>1.36931538863851</v>
+        <v>1.36931538855492</v>
       </c>
       <c r="HE16" t="n">
-        <v>1.3819449919264</v>
+        <v>1.38194499184277</v>
       </c>
       <c r="HF16" t="n">
-        <v>1.39472277999806</v>
+        <v>1.39472277991461</v>
       </c>
       <c r="HG16" t="n">
-        <v>1.40767960809104</v>
+        <v>1.40767960800794</v>
       </c>
       <c r="HH16" t="n">
-        <v>1.42081068251165</v>
+        <v>1.42081068242886</v>
       </c>
       <c r="HI16" t="n">
-        <v>1.43413326300208</v>
+        <v>1.43413326291936</v>
       </c>
       <c r="HJ16" t="n">
-        <v>1.44765081817792</v>
+        <v>1.447650818095</v>
       </c>
       <c r="HK16" t="n">
-        <v>1.46133508187091</v>
+        <v>1.46133508178763</v>
       </c>
       <c r="HL16" t="n">
-        <v>1.47519709607504</v>
+        <v>1.47519709599104</v>
       </c>
       <c r="HM16" t="n">
-        <v>1.48924876921977</v>
+        <v>1.4892487691345</v>
       </c>
       <c r="HN16" t="n">
-        <v>1.50349245726812</v>
+        <v>1.50349245718103</v>
       </c>
       <c r="HO16" t="n">
-        <v>1.51789297178096</v>
+        <v>1.51789297169165</v>
       </c>
       <c r="HP16" t="n">
-        <v>1.53245187132347</v>
+        <v>1.53245187123142</v>
       </c>
       <c r="HQ16" t="n">
-        <v>1.547188956263</v>
+        <v>1.54718895616753</v>
       </c>
       <c r="HR16" t="n">
-        <v>1.56210945261425</v>
+        <v>1.56210945251471</v>
       </c>
       <c r="HS16" t="n">
-        <v>1.5775138072232</v>
+        <v>1.57751380711848</v>
       </c>
       <c r="HT16" t="n">
-        <v>1.59265198835721</v>
+        <v>1.59265198824762</v>
       </c>
       <c r="HU16" t="n">
-        <v>1.60824483242988</v>
+        <v>1.60824483231424</v>
       </c>
     </row>
     <row r="17">
@@ -12872,136 +12872,136 @@
         <v>144.861693768467</v>
       </c>
       <c r="GD17" t="n">
-        <v>146.572442197371</v>
+        <v>146.572442197292</v>
       </c>
       <c r="GE17" t="n">
-        <v>148.246978513999</v>
+        <v>148.246978513822</v>
       </c>
       <c r="GF17" t="n">
-        <v>150.071786547243</v>
+        <v>150.071786546797</v>
       </c>
       <c r="GG17" t="n">
-        <v>151.922234841203</v>
+        <v>151.922234840272</v>
       </c>
       <c r="GH17" t="n">
-        <v>153.814321481773</v>
+        <v>153.814321480111</v>
       </c>
       <c r="GI17" t="n">
-        <v>155.7401265663</v>
+        <v>155.740126563532</v>
       </c>
       <c r="GJ17" t="n">
-        <v>157.671477678942</v>
+        <v>157.671477674703</v>
       </c>
       <c r="GK17" t="n">
-        <v>159.601649428925</v>
+        <v>159.601649422809</v>
       </c>
       <c r="GL17" t="n">
-        <v>161.516062281551</v>
+        <v>161.516062273167</v>
       </c>
       <c r="GM17" t="n">
-        <v>163.39466789876</v>
+        <v>163.394667887774</v>
       </c>
       <c r="GN17" t="n">
-        <v>165.242238262515</v>
+        <v>165.242238248684</v>
       </c>
       <c r="GO17" t="n">
-        <v>167.069663394763</v>
+        <v>167.069663377946</v>
       </c>
       <c r="GP17" t="n">
-        <v>168.876185763166</v>
+        <v>168.876185743287</v>
       </c>
       <c r="GQ17" t="n">
-        <v>170.659398523144</v>
+        <v>170.659398500221</v>
       </c>
       <c r="GR17" t="n">
-        <v>172.432569548588</v>
+        <v>172.432569522716</v>
       </c>
       <c r="GS17" t="n">
-        <v>174.191904282396</v>
+        <v>174.19190425373</v>
       </c>
       <c r="GT17" t="n">
-        <v>175.943644203024</v>
+        <v>175.943644171773</v>
       </c>
       <c r="GU17" t="n">
-        <v>177.685588533037</v>
+        <v>177.685588499466</v>
       </c>
       <c r="GV17" t="n">
-        <v>179.427279954816</v>
+        <v>179.427279919219</v>
       </c>
       <c r="GW17" t="n">
-        <v>181.169140122598</v>
+        <v>181.169140085289</v>
       </c>
       <c r="GX17" t="n">
-        <v>182.915188843591</v>
+        <v>182.915188804892</v>
       </c>
       <c r="GY17" t="n">
-        <v>184.665705424226</v>
+        <v>184.665705384469</v>
       </c>
       <c r="GZ17" t="n">
-        <v>186.429953443277</v>
+        <v>186.429953402784</v>
       </c>
       <c r="HA17" t="n">
-        <v>188.207223893322</v>
+        <v>188.207223852408</v>
       </c>
       <c r="HB17" t="n">
-        <v>190.002523766819</v>
+        <v>190.002523725785</v>
       </c>
       <c r="HC17" t="n">
-        <v>191.812302508562</v>
+        <v>191.812302467701</v>
       </c>
       <c r="HD17" t="n">
-        <v>193.649904101166</v>
+        <v>193.64990406074</v>
       </c>
       <c r="HE17" t="n">
-        <v>195.509052412018</v>
+        <v>195.509052372263</v>
       </c>
       <c r="HF17" t="n">
-        <v>197.394813030331</v>
+        <v>197.394812991453</v>
       </c>
       <c r="HG17" t="n">
-        <v>199.304926863459</v>
+        <v>199.304926825626</v>
       </c>
       <c r="HH17" t="n">
-        <v>201.243989917157</v>
+        <v>201.243989880503</v>
       </c>
       <c r="HI17" t="n">
-        <v>203.211414099388</v>
+        <v>203.211414064004</v>
       </c>
       <c r="HJ17" t="n">
-        <v>205.207627810989</v>
+        <v>205.207627776931</v>
       </c>
       <c r="HK17" t="n">
-        <v>207.230117487494</v>
+        <v>207.230117454785</v>
       </c>
       <c r="HL17" t="n">
-        <v>209.284264076582</v>
+        <v>209.284264045213</v>
       </c>
       <c r="HM17" t="n">
-        <v>211.366910118493</v>
+        <v>211.366910088428</v>
       </c>
       <c r="HN17" t="n">
-        <v>213.478403201183</v>
+        <v>213.478403172362</v>
       </c>
       <c r="HO17" t="n">
-        <v>215.61524459475</v>
+        <v>215.615244567098</v>
       </c>
       <c r="HP17" t="n">
-        <v>217.779053027811</v>
+        <v>217.77905300124</v>
       </c>
       <c r="HQ17" t="n">
-        <v>219.969664715775</v>
+        <v>219.969664690187</v>
       </c>
       <c r="HR17" t="n">
-        <v>222.186232501744</v>
+        <v>222.186232477037</v>
       </c>
       <c r="HS17" t="n">
-        <v>224.419645633369</v>
+        <v>224.419645609435</v>
       </c>
       <c r="HT17" t="n">
-        <v>226.680508107175</v>
+        <v>226.680508083916</v>
       </c>
       <c r="HU17" t="n">
-        <v>228.960312390774</v>
+        <v>228.960312368092</v>
       </c>
     </row>
     <row r="18">
@@ -13558,139 +13558,139 @@
         <v>26114</v>
       </c>
       <c r="GC18" t="n">
-        <v>26415.8830093047</v>
+        <v>26415.8830093051</v>
       </c>
       <c r="GD18" t="n">
-        <v>26492.9760390177</v>
+        <v>26492.9760390459</v>
       </c>
       <c r="GE18" t="n">
-        <v>26908.4998345478</v>
+        <v>26908.4998345285</v>
       </c>
       <c r="GF18" t="n">
-        <v>27194.188425767</v>
+        <v>27194.1884257227</v>
       </c>
       <c r="GG18" t="n">
-        <v>27579.0279012739</v>
+        <v>27579.0279011303</v>
       </c>
       <c r="GH18" t="n">
-        <v>27948.2647503312</v>
+        <v>27948.2647499832</v>
       </c>
       <c r="GI18" t="n">
-        <v>28319.2813117101</v>
+        <v>28319.2813110859</v>
       </c>
       <c r="GJ18" t="n">
-        <v>28694.0313009322</v>
+        <v>28694.0312998817</v>
       </c>
       <c r="GK18" t="n">
-        <v>29056.4632192764</v>
+        <v>29056.4632176604</v>
       </c>
       <c r="GL18" t="n">
-        <v>29417.2781784838</v>
+        <v>29417.2781761537</v>
       </c>
       <c r="GM18" t="n">
-        <v>29772.853481495</v>
+        <v>29772.8534783001</v>
       </c>
       <c r="GN18" t="n">
-        <v>30129.496390783</v>
+        <v>30129.4963866396</v>
       </c>
       <c r="GO18" t="n">
-        <v>30461.5077241288</v>
+        <v>30461.5077189</v>
       </c>
       <c r="GP18" t="n">
-        <v>30785.7252249589</v>
+        <v>30785.7252185823</v>
       </c>
       <c r="GQ18" t="n">
-        <v>31106.8539232835</v>
+        <v>31106.8539157397</v>
       </c>
       <c r="GR18" t="n">
-        <v>31417.3019428128</v>
+        <v>31417.301934077</v>
       </c>
       <c r="GS18" t="n">
-        <v>31727.1166548907</v>
+        <v>31727.116644998</v>
       </c>
       <c r="GT18" t="n">
-        <v>32032.024829105</v>
+        <v>32032.024818086</v>
       </c>
       <c r="GU18" t="n">
-        <v>32338.0159717256</v>
+        <v>32338.0159596432</v>
       </c>
       <c r="GV18" t="n">
-        <v>32636.5399257858</v>
+        <v>32636.5399126794</v>
       </c>
       <c r="GW18" t="n">
-        <v>32934.7109528472</v>
+        <v>32934.7109387874</v>
       </c>
       <c r="GX18" t="n">
-        <v>33231.3112814155</v>
+        <v>33231.3112664711</v>
       </c>
       <c r="GY18" t="n">
-        <v>33530.2055487578</v>
+        <v>33530.2055330081</v>
       </c>
       <c r="GZ18" t="n">
-        <v>33825.4120834859</v>
+        <v>33825.4120669909</v>
       </c>
       <c r="HA18" t="n">
-        <v>34124.4773785053</v>
+        <v>34124.4773613397</v>
       </c>
       <c r="HB18" t="n">
-        <v>34424.8658973166</v>
+        <v>34424.8658795476</v>
       </c>
       <c r="HC18" t="n">
-        <v>34734.1806153503</v>
+        <v>34734.1805970594</v>
       </c>
       <c r="HD18" t="n">
-        <v>35035.6348260656</v>
+        <v>35035.6348073003</v>
       </c>
       <c r="HE18" t="n">
-        <v>35347.7493426255</v>
+        <v>35347.7493234583</v>
       </c>
       <c r="HF18" t="n">
-        <v>35661.4931649903</v>
+        <v>35661.4931454761</v>
       </c>
       <c r="HG18" t="n">
-        <v>35981.6872041953</v>
+        <v>35981.6871843858</v>
       </c>
       <c r="HH18" t="n">
-        <v>36302.2672054098</v>
+        <v>36302.267185337</v>
       </c>
       <c r="HI18" t="n">
-        <v>36626.5902284406</v>
+        <v>36626.5902081348</v>
       </c>
       <c r="HJ18" t="n">
-        <v>36955.1738117896</v>
+        <v>36955.1737912724</v>
       </c>
       <c r="HK18" t="n">
-        <v>37290.0971982124</v>
+        <v>37290.0971774992</v>
       </c>
       <c r="HL18" t="n">
-        <v>37624.649403052</v>
+        <v>37624.6493821499</v>
       </c>
       <c r="HM18" t="n">
-        <v>37964.3450682821</v>
+        <v>37964.3450471936</v>
       </c>
       <c r="HN18" t="n">
-        <v>38307.8809545883</v>
+        <v>38307.8809333141</v>
       </c>
       <c r="HO18" t="n">
-        <v>38657.7902660193</v>
+        <v>38657.7902445565</v>
       </c>
       <c r="HP18" t="n">
-        <v>39008.3076459045</v>
+        <v>39008.3076242471</v>
       </c>
       <c r="HQ18" t="n">
-        <v>39360.4019992674</v>
+        <v>39360.4019774099</v>
       </c>
       <c r="HR18" t="n">
-        <v>39716.0245306316</v>
+        <v>39716.0245085691</v>
       </c>
       <c r="HS18" t="n">
-        <v>40081.6510225739</v>
+        <v>40081.6510003041</v>
       </c>
       <c r="HT18" t="n">
-        <v>40435.3896746406</v>
+        <v>40435.3896521552</v>
       </c>
       <c r="HU18" t="n">
-        <v>40797.5470071353</v>
+        <v>40797.5469844338</v>
       </c>
     </row>
     <row r="19">
@@ -14247,139 +14247,139 @@
         <v>14608.7589597667</v>
       </c>
       <c r="GC19" t="n">
-        <v>14660.0841628213</v>
+        <v>14660.0841628209</v>
       </c>
       <c r="GD19" t="n">
-        <v>14786.4151985371</v>
+        <v>14786.4151985</v>
       </c>
       <c r="GE19" t="n">
-        <v>14875.5153552457</v>
+        <v>14875.5153551704</v>
       </c>
       <c r="GF19" t="n">
-        <v>14981.754526318</v>
+        <v>14981.7545261638</v>
       </c>
       <c r="GG19" t="n">
-        <v>15075.0817687218</v>
+        <v>15075.0817684402</v>
       </c>
       <c r="GH19" t="n">
-        <v>15155.1216279783</v>
+        <v>15155.1216275371</v>
       </c>
       <c r="GI19" t="n">
-        <v>15222.3257128973</v>
+        <v>15222.3257122377</v>
       </c>
       <c r="GJ19" t="n">
-        <v>15276.2876915861</v>
+        <v>15276.2876906586</v>
       </c>
       <c r="GK19" t="n">
-        <v>15323.2132188084</v>
+        <v>15323.2132175702</v>
       </c>
       <c r="GL19" t="n">
-        <v>15365.5244142257</v>
+        <v>15365.5244126423</v>
       </c>
       <c r="GM19" t="n">
-        <v>15403.5976853831</v>
+        <v>15403.5976834406</v>
       </c>
       <c r="GN19" t="n">
-        <v>15429.3415231498</v>
+        <v>15429.3415208268</v>
       </c>
       <c r="GO19" t="n">
-        <v>15452.5589983592</v>
+        <v>15452.5589956743</v>
       </c>
       <c r="GP19" t="n">
-        <v>15475.904271072</v>
+        <v>15475.9042680644</v>
       </c>
       <c r="GQ19" t="n">
-        <v>15497.7356650074</v>
+        <v>15497.7356617207</v>
       </c>
       <c r="GR19" t="n">
-        <v>15519.973628704</v>
+        <v>15519.9736252033</v>
       </c>
       <c r="GS19" t="n">
-        <v>15543.5665950894</v>
+        <v>15543.5665914353</v>
       </c>
       <c r="GT19" t="n">
-        <v>15569.1731281506</v>
+        <v>15569.1731244045</v>
       </c>
       <c r="GU19" t="n">
-        <v>15594.2685174887</v>
+        <v>15594.2685137004</v>
       </c>
       <c r="GV19" t="n">
-        <v>15621.7117540327</v>
+        <v>15621.7117502586</v>
       </c>
       <c r="GW19" t="n">
-        <v>15651.2247484682</v>
+        <v>15651.2247447593</v>
       </c>
       <c r="GX19" t="n">
-        <v>15683.4772501057</v>
+        <v>15683.477246508</v>
       </c>
       <c r="GY19" t="n">
-        <v>15716.9262464326</v>
+        <v>15716.9262429811</v>
       </c>
       <c r="GZ19" t="n">
-        <v>15752.3422455204</v>
+        <v>15752.3422422514</v>
       </c>
       <c r="HA19" t="n">
-        <v>15790.7055481895</v>
+        <v>15790.7055451312</v>
       </c>
       <c r="HB19" t="n">
-        <v>15832.59851018</v>
+        <v>15832.5985073567</v>
       </c>
       <c r="HC19" t="n">
-        <v>15873.4466149731</v>
+        <v>15873.4466123927</v>
       </c>
       <c r="HD19" t="n">
-        <v>15917.4689822978</v>
+        <v>15917.4689799737</v>
       </c>
       <c r="HE19" t="n">
-        <v>15962.9273050483</v>
+        <v>15962.9273029802</v>
       </c>
       <c r="HF19" t="n">
-        <v>16010.0970849613</v>
+        <v>16010.0970831418</v>
       </c>
       <c r="HG19" t="n">
-        <v>16057.0335658978</v>
+        <v>16057.0335643086</v>
       </c>
       <c r="HH19" t="n">
-        <v>16104.1631580298</v>
+        <v>16104.1631566518</v>
       </c>
       <c r="HI19" t="n">
-        <v>16152.3105114046</v>
+        <v>16152.3105102156</v>
       </c>
       <c r="HJ19" t="n">
-        <v>16201.368606645</v>
+        <v>16201.3686056214</v>
       </c>
       <c r="HK19" t="n">
-        <v>16249.3746566893</v>
+        <v>16249.3746558055</v>
       </c>
       <c r="HL19" t="n">
-        <v>16296.7874904412</v>
+        <v>16296.7874896749</v>
       </c>
       <c r="HM19" t="n">
-        <v>16344.6206480772</v>
+        <v>16344.6206474078</v>
       </c>
       <c r="HN19" t="n">
-        <v>16392.7683198211</v>
+        <v>16392.7683192302</v>
       </c>
       <c r="HO19" t="n">
-        <v>16439.301931376</v>
+        <v>16439.3019308464</v>
       </c>
       <c r="HP19" t="n">
-        <v>16484.9699858475</v>
+        <v>16484.9699853665</v>
       </c>
       <c r="HQ19" t="n">
-        <v>16530.6479813617</v>
+        <v>16530.6479809201</v>
       </c>
       <c r="HR19" t="n">
-        <v>16576.4040907042</v>
+        <v>16576.4040902958</v>
       </c>
       <c r="HS19" t="n">
-        <v>16616.8771073567</v>
+        <v>16616.8771069734</v>
       </c>
       <c r="HT19" t="n">
-        <v>16658.2078999565</v>
+        <v>16658.2078995983</v>
       </c>
       <c r="HU19" t="n">
-        <v>16698.4480025269</v>
+        <v>16698.4480021953</v>
       </c>
     </row>
     <row r="20">
@@ -14936,139 +14936,139 @@
         <v>0.669101939</v>
       </c>
       <c r="GC20" t="n">
-        <v>0.668738350026895</v>
+        <v>0.668738350026894</v>
       </c>
       <c r="GD20" t="n">
-        <v>0.668210262714031</v>
+        <v>0.668210262713964</v>
       </c>
       <c r="GE20" t="n">
-        <v>0.668897178462775</v>
+        <v>0.668897178462281</v>
       </c>
       <c r="GF20" t="n">
-        <v>0.669289317781248</v>
+        <v>0.669289317780209</v>
       </c>
       <c r="GG20" t="n">
-        <v>0.670019318874565</v>
+        <v>0.67001931887247</v>
       </c>
       <c r="GH20" t="n">
-        <v>0.670583167884301</v>
+        <v>0.670583167880582</v>
       </c>
       <c r="GI20" t="n">
-        <v>0.67083355469851</v>
+        <v>0.670833554692703</v>
       </c>
       <c r="GJ20" t="n">
-        <v>0.671046577454215</v>
+        <v>0.671046577445568</v>
       </c>
       <c r="GK20" t="n">
-        <v>0.671066602822236</v>
+        <v>0.671066602810135</v>
       </c>
       <c r="GL20" t="n">
-        <v>0.671018836037757</v>
+        <v>0.671018836021629</v>
       </c>
       <c r="GM20" t="n">
-        <v>0.67088942289252</v>
+        <v>0.670889422871896</v>
       </c>
       <c r="GN20" t="n">
-        <v>0.670675377966698</v>
+        <v>0.670675377941332</v>
       </c>
       <c r="GO20" t="n">
-        <v>0.670330680446722</v>
+        <v>0.670330680416356</v>
       </c>
       <c r="GP20" t="n">
-        <v>0.669935462460628</v>
+        <v>0.669935462425436</v>
       </c>
       <c r="GQ20" t="n">
-        <v>0.669520034157097</v>
+        <v>0.669520034117484</v>
       </c>
       <c r="GR20" t="n">
-        <v>0.669085946566653</v>
+        <v>0.669085946523152</v>
       </c>
       <c r="GS20" t="n">
-        <v>0.668675887292883</v>
+        <v>0.668675887246278</v>
       </c>
       <c r="GT20" t="n">
-        <v>0.668273778135251</v>
+        <v>0.668273778086302</v>
       </c>
       <c r="GU20" t="n">
-        <v>0.667889334423273</v>
+        <v>0.667889334372775</v>
       </c>
       <c r="GV20" t="n">
-        <v>0.6675080847</v>
+        <v>0.667508084648673</v>
       </c>
       <c r="GW20" t="n">
-        <v>0.667150595683309</v>
+        <v>0.667150595631915</v>
       </c>
       <c r="GX20" t="n">
-        <v>0.66682171722335</v>
+        <v>0.666821717172609</v>
       </c>
       <c r="GY20" t="n">
-        <v>0.66652563566975</v>
+        <v>0.666525635620313</v>
       </c>
       <c r="GZ20" t="n">
-        <v>0.666255995128093</v>
+        <v>0.666255995080504</v>
       </c>
       <c r="HA20" t="n">
-        <v>0.666030795073682</v>
+        <v>0.666030795028449</v>
       </c>
       <c r="HB20" t="n">
-        <v>0.665846575317287</v>
+        <v>0.665846575274832</v>
       </c>
       <c r="HC20" t="n">
-        <v>0.665702108430934</v>
+        <v>0.665702108391599</v>
       </c>
       <c r="HD20" t="n">
-        <v>0.665566555365318</v>
+        <v>0.665566555329287</v>
       </c>
       <c r="HE20" t="n">
-        <v>0.665479652936596</v>
+        <v>0.665479652904041</v>
       </c>
       <c r="HF20" t="n">
-        <v>0.665416462469405</v>
+        <v>0.665416462440354</v>
       </c>
       <c r="HG20" t="n">
-        <v>0.665376240024433</v>
+        <v>0.665376239998806</v>
       </c>
       <c r="HH20" t="n">
-        <v>0.665345047743474</v>
+        <v>0.665345047721078</v>
       </c>
       <c r="HI20" t="n">
-        <v>0.665324469772037</v>
+        <v>0.665324469752625</v>
       </c>
       <c r="HJ20" t="n">
-        <v>0.665319669279469</v>
+        <v>0.665319669262758</v>
       </c>
       <c r="HK20" t="n">
-        <v>0.665324357713518</v>
+        <v>0.665324357699194</v>
       </c>
       <c r="HL20" t="n">
-        <v>0.665325332771863</v>
+        <v>0.665325332759596</v>
       </c>
       <c r="HM20" t="n">
-        <v>0.665334261103139</v>
+        <v>0.665334261092613</v>
       </c>
       <c r="HN20" t="n">
-        <v>0.665347896150233</v>
+        <v>0.665347896141157</v>
       </c>
       <c r="HO20" t="n">
-        <v>0.665363094446729</v>
+        <v>0.665363094438835</v>
       </c>
       <c r="HP20" t="n">
-        <v>0.665364856244272</v>
+        <v>0.665364856237318</v>
       </c>
       <c r="HQ20" t="n">
-        <v>0.665356329439756</v>
+        <v>0.665356329433547</v>
       </c>
       <c r="HR20" t="n">
-        <v>0.665346031744335</v>
+        <v>0.665346031738721</v>
       </c>
       <c r="HS20" t="n">
-        <v>0.665327017754076</v>
+        <v>0.66532701774894</v>
       </c>
       <c r="HT20" t="n">
-        <v>0.665264358126137</v>
+        <v>0.665264358121371</v>
       </c>
       <c r="HU20" t="n">
-        <v>0.66520377417675</v>
+        <v>0.665203774172323</v>
       </c>
     </row>
     <row r="21">
@@ -15625,139 +15625,139 @@
         <v>0.0430614370315685</v>
       </c>
       <c r="GC21" t="n">
-        <v>0.047638941993144</v>
+        <v>0.047638941993171</v>
       </c>
       <c r="GD21" t="n">
-        <v>0.042820119813057</v>
+        <v>0.0428201198153555</v>
       </c>
       <c r="GE21" t="n">
-        <v>0.0421785988397355</v>
+        <v>0.0421785988438807</v>
       </c>
       <c r="GF21" t="n">
-        <v>0.039601450334911</v>
+        <v>0.039601450343304</v>
       </c>
       <c r="GG21" t="n">
-        <v>0.0383648270973903</v>
+        <v>0.0383648271123463</v>
       </c>
       <c r="GH21" t="n">
-        <v>0.0377576647260996</v>
+        <v>0.0377576647487839</v>
       </c>
       <c r="GI21" t="n">
-        <v>0.0375282277070139</v>
+        <v>0.0375282277403831</v>
       </c>
       <c r="GJ21" t="n">
-        <v>0.0379136900922971</v>
+        <v>0.0379136901383097</v>
       </c>
       <c r="GK21" t="n">
-        <v>0.0384670586359749</v>
+        <v>0.0384670586963278</v>
       </c>
       <c r="GL21" t="n">
-        <v>0.0392118206718482</v>
+        <v>0.0392118207477614</v>
       </c>
       <c r="GM21" t="n">
-        <v>0.0401018528669038</v>
+        <v>0.0401018529584469</v>
       </c>
       <c r="GN21" t="n">
-        <v>0.041584336870502</v>
+        <v>0.0415843369785524</v>
       </c>
       <c r="GO21" t="n">
-        <v>0.0430282999846384</v>
+        <v>0.0430283001075633</v>
       </c>
       <c r="GP21" t="n">
-        <v>0.0443833674735848</v>
+        <v>0.0443833676091023</v>
       </c>
       <c r="GQ21" t="n">
-        <v>0.0457941454911124</v>
+        <v>0.0457941456370177</v>
       </c>
       <c r="GR21" t="n">
-        <v>0.0470249214543294</v>
+        <v>0.0470249216073248</v>
       </c>
       <c r="GS21" t="n">
-        <v>0.0481983373583822</v>
+        <v>0.048198337515805</v>
       </c>
       <c r="GT21" t="n">
-        <v>0.0492519954716373</v>
+        <v>0.0492519956307578</v>
       </c>
       <c r="GU21" t="n">
-        <v>0.0503545230638067</v>
+        <v>0.0503545232227043</v>
       </c>
       <c r="GV21" t="n">
-        <v>0.0513232247433072</v>
+        <v>0.0513232248995515</v>
       </c>
       <c r="GW21" t="n">
-        <v>0.0521933076971457</v>
+        <v>0.0521933078487409</v>
       </c>
       <c r="GX21" t="n">
-        <v>0.0529322867467246</v>
+        <v>0.05293228689191</v>
       </c>
       <c r="GY21" t="n">
-        <v>0.0536404373561586</v>
+        <v>0.0536404374937876</v>
       </c>
       <c r="GZ21" t="n">
-        <v>0.0541561327556985</v>
+        <v>0.0541561328844275</v>
       </c>
       <c r="HA21" t="n">
-        <v>0.0545541557683491</v>
+        <v>0.0545541558872522</v>
       </c>
       <c r="HB21" t="n">
-        <v>0.0547963529653803</v>
+        <v>0.0547963530736673</v>
       </c>
       <c r="HC21" t="n">
-        <v>0.0551551349157153</v>
+        <v>0.0551551350134763</v>
       </c>
       <c r="HD21" t="n">
-        <v>0.0552532161444418</v>
+        <v>0.0552532162312405</v>
       </c>
       <c r="HE21" t="n">
-        <v>0.0553342236378556</v>
+        <v>0.0553342237140306</v>
       </c>
       <c r="HF21" t="n">
-        <v>0.0553472655612472</v>
+        <v>0.0553472656273705</v>
       </c>
       <c r="HG21" t="n">
-        <v>0.0554065973024424</v>
+        <v>0.0554065973595507</v>
       </c>
       <c r="HH21" t="n">
-        <v>0.055423322310881</v>
+        <v>0.0554233223599101</v>
       </c>
       <c r="HI21" t="n">
-        <v>0.0553956218826285</v>
+        <v>0.0553956219246031</v>
       </c>
       <c r="HJ21" t="n">
-        <v>0.0553375940419492</v>
+        <v>0.0553375940779122</v>
       </c>
       <c r="HK21" t="n">
-        <v>0.0553548873343689</v>
+        <v>0.0553548873654045</v>
       </c>
       <c r="HL21" t="n">
-        <v>0.0553211836005975</v>
+        <v>0.055321183627602</v>
       </c>
       <c r="HM21" t="n">
-        <v>0.0552746606293788</v>
+        <v>0.0552746606531255</v>
       </c>
       <c r="HN21" t="n">
-        <v>0.0552170142599571</v>
+        <v>0.0552170142811305</v>
       </c>
       <c r="HO21" t="n">
-        <v>0.055254767809915</v>
+        <v>0.0552547678291397</v>
       </c>
       <c r="HP21" t="n">
-        <v>0.0553263696373388</v>
+        <v>0.0553263696550279</v>
       </c>
       <c r="HQ21" t="n">
-        <v>0.055382465089571</v>
+        <v>0.0553824651059852</v>
       </c>
       <c r="HR21" t="n">
-        <v>0.0554312721345353</v>
+        <v>0.0554312721498369</v>
       </c>
       <c r="HS21" t="n">
-        <v>0.0557676133854563</v>
+        <v>0.0557676133999534</v>
       </c>
       <c r="HT21" t="n">
-        <v>0.0559807445390241</v>
+        <v>0.0559807445525617</v>
       </c>
       <c r="HU21" t="n">
-        <v>0.0562568166774583</v>
+        <v>0.05625681668992</v>
       </c>
     </row>
     <row r="22">
@@ -16314,139 +16314,139 @@
         <v>657.3819662</v>
       </c>
       <c r="GC22" t="n">
-        <v>733.325147173915</v>
+        <v>733.325147174317</v>
       </c>
       <c r="GD22" t="n">
-        <v>661.480870113943</v>
+        <v>661.480870149429</v>
       </c>
       <c r="GE22" t="n">
-        <v>655.057908559333</v>
+        <v>655.057908623185</v>
       </c>
       <c r="GF22" t="n">
-        <v>617.76363918953</v>
+        <v>617.76363931951</v>
       </c>
       <c r="GG22" t="n">
-        <v>601.4266234385</v>
+        <v>601.426623671099</v>
       </c>
       <c r="GH22" t="n">
-        <v>594.675643822669</v>
+        <v>594.675644176608</v>
       </c>
       <c r="GI22" t="n">
-        <v>593.541550088641</v>
+        <v>593.541550611319</v>
       </c>
       <c r="GJ22" t="n">
-        <v>602.00474276495</v>
+        <v>602.004743487783</v>
       </c>
       <c r="GK22" t="n">
-        <v>613.020108019176</v>
+        <v>613.020108969942</v>
       </c>
       <c r="GL22" t="n">
-        <v>627.100009315198</v>
+        <v>627.100010514187</v>
       </c>
       <c r="GM22" t="n">
-        <v>643.519209467659</v>
+        <v>643.519210916902</v>
       </c>
       <c r="GN22" t="n">
-        <v>669.457999935479</v>
+        <v>669.458001649667</v>
       </c>
       <c r="GO22" t="n">
-        <v>694.793228333447</v>
+        <v>694.793230286865</v>
       </c>
       <c r="GP22" t="n">
-        <v>718.774497308385</v>
+        <v>718.77449946528</v>
       </c>
       <c r="GQ22" t="n">
-        <v>743.765804250173</v>
+        <v>743.765806575924</v>
       </c>
       <c r="GR22" t="n">
-        <v>765.839193636459</v>
+        <v>765.839196078345</v>
       </c>
       <c r="GS22" t="n">
-        <v>787.111665306009</v>
+        <v>787.111667821957</v>
       </c>
       <c r="GT22" t="n">
-        <v>806.536509039401</v>
+        <v>806.536511586057</v>
       </c>
       <c r="GU22" t="n">
-        <v>826.879190772568</v>
+        <v>826.879193319368</v>
       </c>
       <c r="GV22" t="n">
-        <v>845.131638527697</v>
+        <v>845.131641035568</v>
       </c>
       <c r="GW22" t="n">
-        <v>861.873338736932</v>
+        <v>861.87334117381</v>
       </c>
       <c r="GX22" t="n">
-        <v>876.560814674587</v>
+        <v>876.56081701216</v>
       </c>
       <c r="GY22" t="n">
-        <v>890.84842965896</v>
+        <v>890.848431878603</v>
       </c>
       <c r="GZ22" t="n">
-        <v>901.931174651043</v>
+        <v>901.931176730504</v>
       </c>
       <c r="HA22" t="n">
-        <v>911.156093143134</v>
+        <v>911.156095067181</v>
       </c>
       <c r="HB22" t="n">
-        <v>917.864416979552</v>
+        <v>917.864418734884</v>
       </c>
       <c r="HC22" t="n">
-        <v>926.609498155445</v>
+        <v>926.609499743119</v>
       </c>
       <c r="HD22" t="n">
-        <v>930.928268523903</v>
+        <v>930.928269935934</v>
       </c>
       <c r="HE22" t="n">
-        <v>935.035808746257</v>
+        <v>935.035809987719</v>
       </c>
       <c r="HF22" t="n">
-        <v>938.032779130679</v>
+        <v>938.032780210331</v>
       </c>
       <c r="HG22" t="n">
-        <v>941.850461413065</v>
+        <v>941.850462347566</v>
       </c>
       <c r="HH22" t="n">
-        <v>944.916798698639</v>
+        <v>944.916799502796</v>
       </c>
       <c r="HI22" t="n">
-        <v>947.24039783113</v>
+        <v>947.240398521251</v>
       </c>
       <c r="HJ22" t="n">
-        <v>949.063813150355</v>
+        <v>949.063813743249</v>
       </c>
       <c r="HK22" t="n">
-        <v>952.190873398507</v>
+        <v>952.190873911903</v>
       </c>
       <c r="HL22" t="n">
-        <v>954.353705644407</v>
+        <v>954.353706092676</v>
       </c>
       <c r="HM22" t="n">
-        <v>956.302824617953</v>
+        <v>956.302825013678</v>
       </c>
       <c r="HN22" t="n">
-        <v>958.061153876519</v>
+        <v>958.061154230811</v>
       </c>
       <c r="HO22" t="n">
-        <v>961.476110396539</v>
+        <v>961.476110719639</v>
       </c>
       <c r="HP22" t="n">
-        <v>965.469638259608</v>
+        <v>965.469638558243</v>
       </c>
       <c r="HQ22" t="n">
-        <v>969.184004207298</v>
+        <v>969.184004485567</v>
       </c>
       <c r="HR22" t="n">
-        <v>972.773397015044</v>
+        <v>972.773397275352</v>
       </c>
       <c r="HS22" t="n">
-        <v>981.414916940736</v>
+        <v>981.414917188235</v>
       </c>
       <c r="HT22" t="n">
-        <v>987.839021591346</v>
+        <v>987.839021823154</v>
       </c>
       <c r="HU22" t="n">
-        <v>995.399719489265</v>
+        <v>995.399719703095</v>
       </c>
     </row>
     <row r="23">
@@ -17003,139 +17003,139 @@
         <v>0.0362333333333333</v>
       </c>
       <c r="GC23" t="n">
-        <v>0.0313989538539444</v>
+        <v>0.0313989538538978</v>
       </c>
       <c r="GD23" t="n">
-        <v>0.0421150864010787</v>
+        <v>0.0421150863970587</v>
       </c>
       <c r="GE23" t="n">
-        <v>0.0487508300487732</v>
+        <v>0.0487508300408782</v>
       </c>
       <c r="GF23" t="n">
-        <v>0.0577389160734196</v>
+        <v>0.0577389160567415</v>
       </c>
       <c r="GG23" t="n">
-        <v>0.0653964703296235</v>
+        <v>0.0653964702985591</v>
       </c>
       <c r="GH23" t="n">
-        <v>0.071071119062714</v>
+        <v>0.0710711190131653</v>
       </c>
       <c r="GI23" t="n">
-        <v>0.0756460953604322</v>
+        <v>0.0756460952845919</v>
       </c>
       <c r="GJ23" t="n">
-        <v>0.0782042206508805</v>
+        <v>0.0782042205424685</v>
       </c>
       <c r="GK23" t="n">
-        <v>0.0795699053926581</v>
+        <v>0.079569905245927</v>
       </c>
       <c r="GL23" t="n">
-        <v>0.0797187810770761</v>
+        <v>0.0797187808873608</v>
       </c>
       <c r="GM23" t="n">
-        <v>0.0786957917261237</v>
+        <v>0.0786957914916309</v>
       </c>
       <c r="GN23" t="n">
-        <v>0.0759125952791328</v>
+        <v>0.0759125949979281</v>
       </c>
       <c r="GO23" t="n">
-        <v>0.0724872179027902</v>
+        <v>0.0724872175781647</v>
       </c>
       <c r="GP23" t="n">
-        <v>0.0687086049537369</v>
+        <v>0.0687086045913122</v>
       </c>
       <c r="GQ23" t="n">
-        <v>0.0645659221147493</v>
+        <v>0.0645659217210807</v>
       </c>
       <c r="GR23" t="n">
-        <v>0.0606014134008382</v>
+        <v>0.0606014129848455</v>
       </c>
       <c r="GS23" t="n">
-        <v>0.0567054843736665</v>
+        <v>0.0567054839436087</v>
       </c>
       <c r="GT23" t="n">
-        <v>0.0530480658584758</v>
+        <v>0.0530480654228205</v>
       </c>
       <c r="GU23" t="n">
-        <v>0.0494154046841973</v>
+        <v>0.0494154042500037</v>
       </c>
       <c r="GV23" t="n">
-        <v>0.0461024303502146</v>
+        <v>0.0461024299249995</v>
       </c>
       <c r="GW23" t="n">
-        <v>0.0430906625040256</v>
+        <v>0.0430906620942521</v>
       </c>
       <c r="GX23" t="n">
-        <v>0.0404445384630477</v>
+        <v>0.0404445380743263</v>
       </c>
       <c r="GY23" t="n">
-        <v>0.0380238394740192</v>
+        <v>0.0380238391104575</v>
       </c>
       <c r="GZ23" t="n">
-        <v>0.0360858200850291</v>
+        <v>0.0360858197504699</v>
       </c>
       <c r="HA23" t="n">
-        <v>0.0345243135412693</v>
+        <v>0.0345243132384224</v>
       </c>
       <c r="HB23" t="n">
-        <v>0.0334025273280607</v>
+        <v>0.0334025270589707</v>
       </c>
       <c r="HC23" t="n">
-        <v>0.0322771316768383</v>
+        <v>0.0322771314417567</v>
       </c>
       <c r="HD23" t="n">
-        <v>0.0317251274730424</v>
+        <v>0.0317251272726318</v>
       </c>
       <c r="HE23" t="n">
-        <v>0.031364616446779</v>
+        <v>0.0313646162801688</v>
       </c>
       <c r="HF23" t="n">
-        <v>0.0312523518173651</v>
+        <v>0.031252351682965</v>
       </c>
       <c r="HG23" t="n">
-        <v>0.0311982967626562</v>
+        <v>0.0311982966577939</v>
       </c>
       <c r="HH23" t="n">
-        <v>0.0312965268498377</v>
+        <v>0.0312965267716933</v>
       </c>
       <c r="HI23" t="n">
-        <v>0.0315452577287459</v>
+        <v>0.0315452576741338</v>
       </c>
       <c r="HJ23" t="n">
-        <v>0.0319037713355789</v>
+        <v>0.0319037713011128</v>
       </c>
       <c r="HK23" t="n">
-        <v>0.0321881504985048</v>
+        <v>0.0321881504806393</v>
       </c>
       <c r="HL23" t="n">
-        <v>0.0325792342905538</v>
+        <v>0.0325792342859997</v>
       </c>
       <c r="HM23" t="n">
-        <v>0.0330086542330379</v>
+        <v>0.0330086542387562</v>
       </c>
       <c r="HN23" t="n">
-        <v>0.0334639082080907</v>
+        <v>0.0334639082212899</v>
       </c>
       <c r="HO23" t="n">
-        <v>0.0337651236702528</v>
+        <v>0.0337651236883806</v>
       </c>
       <c r="HP23" t="n">
-        <v>0.0339802334369201</v>
+        <v>0.0339802334579402</v>
       </c>
       <c r="HQ23" t="n">
-        <v>0.0341836430158901</v>
+        <v>0.0341836430382171</v>
       </c>
       <c r="HR23" t="n">
-        <v>0.0343618385966022</v>
+        <v>0.0343618386190286</v>
       </c>
       <c r="HS23" t="n">
-        <v>0.0340270407292287</v>
+        <v>0.0340270407505213</v>
       </c>
       <c r="HT23" t="n">
-        <v>0.0338152336973944</v>
+        <v>0.0338152337172525</v>
       </c>
       <c r="HU23" t="n">
-        <v>0.0334403727977319</v>
+        <v>0.0334403728160072</v>
       </c>
     </row>
     <row r="24">
@@ -17644,139 +17644,139 @@
         <v>0.04288</v>
       </c>
       <c r="GC24" t="n">
-        <v>0.0420176539960489</v>
+        <v>0.0420176539960461</v>
       </c>
       <c r="GD24" t="n">
-        <v>0.0418648542175487</v>
+        <v>0.0418648542173019</v>
       </c>
       <c r="GE24" t="n">
-        <v>0.0421255316359192</v>
+        <v>0.0421255316352095</v>
       </c>
       <c r="GF24" t="n">
-        <v>0.0429144945825906</v>
+        <v>0.042914494580916</v>
       </c>
       <c r="GG24" t="n">
-        <v>0.0441150310987217</v>
+        <v>0.0441150310952739</v>
       </c>
       <c r="GH24" t="n">
-        <v>0.0455787282507709</v>
+        <v>0.0455787282445473</v>
       </c>
       <c r="GI24" t="n">
-        <v>0.0472209081544774</v>
+        <v>0.0472209081440696</v>
       </c>
       <c r="GJ24" t="n">
-        <v>0.0489069299112585</v>
+        <v>0.0489069298949721</v>
       </c>
       <c r="GK24" t="n">
-        <v>0.0505613788619618</v>
+        <v>0.0505613788378684</v>
       </c>
       <c r="GL24" t="n">
-        <v>0.0521124830446222</v>
+        <v>0.0521124830106409</v>
       </c>
       <c r="GM24" t="n">
-        <v>0.0534960762270323</v>
+        <v>0.0534960761811148</v>
       </c>
       <c r="GN24" t="n">
-        <v>0.0546166114098969</v>
+        <v>0.0546166113500164</v>
       </c>
       <c r="GO24" t="n">
-        <v>0.0554529482333417</v>
+        <v>0.0554529481578092</v>
       </c>
       <c r="GP24" t="n">
-        <v>0.0560029348060052</v>
+        <v>0.0560029347135877</v>
       </c>
       <c r="GQ24" t="n">
-        <v>0.056263907271267</v>
+        <v>0.0562639071612136</v>
       </c>
       <c r="GR24" t="n">
-        <v>0.0562663220875256</v>
+        <v>0.0562663219596782</v>
       </c>
       <c r="GS24" t="n">
-        <v>0.0560319093100217</v>
+        <v>0.0560319091647347</v>
       </c>
       <c r="GT24" t="n">
-        <v>0.0555912455299774</v>
+        <v>0.0555912453680954</v>
       </c>
       <c r="GU24" t="n">
-        <v>0.0549598455096158</v>
+        <v>0.0549598453323549</v>
       </c>
       <c r="GV24" t="n">
-        <v>0.0541700859743356</v>
+        <v>0.0541700857832859</v>
       </c>
       <c r="GW24" t="n">
-        <v>0.0532510216507828</v>
+        <v>0.053251021447819</v>
       </c>
       <c r="GX24" t="n">
-        <v>0.0522336478812536</v>
+        <v>0.052233647668464</v>
       </c>
       <c r="GY24" t="n">
-        <v>0.0511383366819299</v>
+        <v>0.0511383364615102</v>
       </c>
       <c r="GZ24" t="n">
-        <v>0.0499997034572961</v>
+        <v>0.0499997032315265</v>
       </c>
       <c r="HA24" t="n">
-        <v>0.0488435629065147</v>
+        <v>0.048843562677685</v>
       </c>
       <c r="HB24" t="n">
-        <v>0.0476978157349736</v>
+        <v>0.0476978155053423</v>
       </c>
       <c r="HC24" t="n">
-        <v>0.0465615366494249</v>
+        <v>0.0465615364211123</v>
       </c>
       <c r="HD24" t="n">
-        <v>0.0454689139230046</v>
+        <v>0.0454689136980274</v>
       </c>
       <c r="HE24" t="n">
-        <v>0.0444286144498954</v>
+        <v>0.0444286142300801</v>
       </c>
       <c r="HF24" t="n">
-        <v>0.0434521639253637</v>
+        <v>0.0434521637123164</v>
       </c>
       <c r="HG24" t="n">
-        <v>0.0425387610448599</v>
+        <v>0.0425387608399151</v>
       </c>
       <c r="HH24" t="n">
-        <v>0.041693373686652</v>
+        <v>0.0416933734908824</v>
       </c>
       <c r="HI24" t="n">
-        <v>0.0409205238631088</v>
+        <v>0.0409205236773205</v>
       </c>
       <c r="HJ24" t="n">
-        <v>0.0402219529269906</v>
+        <v>0.0402219527517294</v>
       </c>
       <c r="HK24" t="n">
-        <v>0.0395881116382844</v>
+        <v>0.0395881114738436</v>
       </c>
       <c r="HL24" t="n">
-        <v>0.0390210847642605</v>
+        <v>0.0390210846107137</v>
       </c>
       <c r="HM24" t="n">
-        <v>0.0385186623147768</v>
+        <v>0.0385186621720079</v>
       </c>
       <c r="HN24" t="n">
-        <v>0.0380780249683048</v>
+        <v>0.0380780248360361</v>
       </c>
       <c r="HO24" t="n">
-        <v>0.0376856183182336</v>
+        <v>0.0376856181960514</v>
       </c>
       <c r="HP24" t="n">
-        <v>0.037332935394967</v>
+        <v>0.0373329352823615</v>
       </c>
       <c r="HQ24" t="n">
-        <v>0.037016566980771</v>
+        <v>0.0370165668771712</v>
       </c>
       <c r="HR24" t="n">
-        <v>0.0367325145346337</v>
+        <v>0.036732514439434</v>
       </c>
       <c r="HS24" t="n">
-        <v>0.0364474203087966</v>
+        <v>0.0364474202213573</v>
       </c>
       <c r="HT24" t="n">
-        <v>0.0361688263194418</v>
+        <v>0.0361688262391487</v>
       </c>
       <c r="HU24" t="n">
-        <v>0.0358863860679304</v>
+        <v>0.0358863859942018</v>
       </c>
     </row>
     <row r="25">
@@ -18332,136 +18332,136 @@
         <v>0.41104884007212</v>
       </c>
       <c r="GD25" t="n">
-        <v>0.397693250220635</v>
+        <v>0.397693250220591</v>
       </c>
       <c r="GE25" t="n">
-        <v>0.385814235697679</v>
+        <v>0.385814235697723</v>
       </c>
       <c r="GF25" t="n">
-        <v>0.381088652433932</v>
+        <v>0.381088652434019</v>
       </c>
       <c r="GG25" t="n">
-        <v>0.378453186594326</v>
+        <v>0.378453186594657</v>
       </c>
       <c r="GH25" t="n">
-        <v>0.375918384438078</v>
+        <v>0.375918384439092</v>
       </c>
       <c r="GI25" t="n">
-        <v>0.373604704040058</v>
+        <v>0.373604704042022</v>
       </c>
       <c r="GJ25" t="n">
-        <v>0.369940218168073</v>
+        <v>0.36994021817173</v>
       </c>
       <c r="GK25" t="n">
-        <v>0.368031132184108</v>
+        <v>0.368031132189974</v>
       </c>
       <c r="GL25" t="n">
-        <v>0.367602048052999</v>
+        <v>0.367602048061369</v>
       </c>
       <c r="GM25" t="n">
-        <v>0.370792547997141</v>
+        <v>0.370792548008146</v>
       </c>
       <c r="GN25" t="n">
-        <v>0.369673946698015</v>
+        <v>0.369673946710972</v>
       </c>
       <c r="GO25" t="n">
-        <v>0.36909916171812</v>
+        <v>0.36909916173173</v>
       </c>
       <c r="GP25" t="n">
-        <v>0.36896401097928</v>
+        <v>0.368964010991388</v>
       </c>
       <c r="GQ25" t="n">
-        <v>0.369137000317806</v>
+        <v>0.369137000325543</v>
       </c>
       <c r="GR25" t="n">
-        <v>0.369307254470831</v>
+        <v>0.369307254470724</v>
       </c>
       <c r="GS25" t="n">
-        <v>0.369739655975511</v>
+        <v>0.369739655963767</v>
       </c>
       <c r="GT25" t="n">
-        <v>0.370333536929859</v>
+        <v>0.37033353690268</v>
       </c>
       <c r="GU25" t="n">
-        <v>0.370974250236218</v>
+        <v>0.370974250189942</v>
       </c>
       <c r="GV25" t="n">
-        <v>0.371534932576541</v>
+        <v>0.371534932507843</v>
       </c>
       <c r="GW25" t="n">
-        <v>0.372019157222089</v>
+        <v>0.372019157128132</v>
       </c>
       <c r="GX25" t="n">
-        <v>0.372366972154892</v>
+        <v>0.372366972033463</v>
       </c>
       <c r="GY25" t="n">
-        <v>0.37254454987586</v>
+        <v>0.372544549725455</v>
       </c>
       <c r="GZ25" t="n">
-        <v>0.372527215185958</v>
+        <v>0.372527215005814</v>
       </c>
       <c r="HA25" t="n">
-        <v>0.372285201397918</v>
+        <v>0.37228520118805</v>
       </c>
       <c r="HB25" t="n">
-        <v>0.371879385388408</v>
+        <v>0.371879385149547</v>
       </c>
       <c r="HC25" t="n">
-        <v>0.371293263109187</v>
+        <v>0.371293262842694</v>
       </c>
       <c r="HD25" t="n">
-        <v>0.370536826657109</v>
+        <v>0.370536826364937</v>
       </c>
       <c r="HE25" t="n">
-        <v>0.369589355104529</v>
+        <v>0.369589354789083</v>
       </c>
       <c r="HF25" t="n">
-        <v>0.368470783083908</v>
+        <v>0.368470782747992</v>
       </c>
       <c r="HG25" t="n">
-        <v>0.36721656040722</v>
+        <v>0.367216560053892</v>
       </c>
       <c r="HH25" t="n">
-        <v>0.365837601091711</v>
+        <v>0.365837600724231</v>
       </c>
       <c r="HI25" t="n">
-        <v>0.364388882034349</v>
+        <v>0.364388881656024</v>
       </c>
       <c r="HJ25" t="n">
-        <v>0.362888542430392</v>
+        <v>0.362888542044528</v>
       </c>
       <c r="HK25" t="n">
-        <v>0.361364728964912</v>
+        <v>0.361364728574739</v>
       </c>
       <c r="HL25" t="n">
-        <v>0.359820010396496</v>
+        <v>0.359820010005107</v>
       </c>
       <c r="HM25" t="n">
-        <v>0.358321290790966</v>
+        <v>0.358321290401191</v>
       </c>
       <c r="HN25" t="n">
-        <v>0.356881503055364</v>
+        <v>0.356881502669775</v>
       </c>
       <c r="HO25" t="n">
-        <v>0.355511041818287</v>
+        <v>0.355511041439176</v>
       </c>
       <c r="HP25" t="n">
-        <v>0.35421436176688</v>
+        <v>0.354214361396232</v>
       </c>
       <c r="HQ25" t="n">
-        <v>0.353002347944092</v>
+        <v>0.353002347583564</v>
       </c>
       <c r="HR25" t="n">
-        <v>0.351875633347406</v>
+        <v>0.351875632998343</v>
       </c>
       <c r="HS25" t="n">
-        <v>0.350855646650341</v>
+        <v>0.350855646313728</v>
       </c>
       <c r="HT25" t="n">
-        <v>0.349911126398362</v>
+        <v>0.349911126075008</v>
       </c>
       <c r="HU25" t="n">
-        <v>0.34905711061274</v>
+        <v>0.349057110303104</v>
       </c>
     </row>
     <row r="26">
@@ -19021,136 +19021,136 @@
         <v>0.667380773125949</v>
       </c>
       <c r="GD26" t="n">
-        <v>0.642374063302119</v>
+        <v>0.642374063301982</v>
       </c>
       <c r="GE26" t="n">
-        <v>0.619573902194391</v>
+        <v>0.619573902194374</v>
       </c>
       <c r="GF26" t="n">
-        <v>0.60898292827866</v>
+        <v>0.608982928278637</v>
       </c>
       <c r="GG26" t="n">
-        <v>0.60163210116838</v>
+        <v>0.601632101168693</v>
       </c>
       <c r="GH26" t="n">
-        <v>0.594588178416237</v>
+        <v>0.594588178417656</v>
       </c>
       <c r="GI26" t="n">
-        <v>0.587980149692322</v>
+        <v>0.587980149695304</v>
       </c>
       <c r="GJ26" t="n">
-        <v>0.57925505812771</v>
+        <v>0.57925505813352</v>
       </c>
       <c r="GK26" t="n">
-        <v>0.573418923578122</v>
+        <v>0.573418923587722</v>
       </c>
       <c r="GL26" t="n">
-        <v>0.569978389830929</v>
+        <v>0.569978389844927</v>
       </c>
       <c r="GM26" t="n">
-        <v>0.572328500571345</v>
+        <v>0.572328500590182</v>
       </c>
       <c r="GN26" t="n">
-        <v>0.567895028818787</v>
+        <v>0.56789502884128</v>
       </c>
       <c r="GO26" t="n">
-        <v>0.564371530644145</v>
+        <v>0.564371530668375</v>
       </c>
       <c r="GP26" t="n">
-        <v>0.561553827240129</v>
+        <v>0.561553827262834</v>
       </c>
       <c r="GQ26" t="n">
-        <v>0.559249859397383</v>
+        <v>0.559249859414171</v>
       </c>
       <c r="GR26" t="n">
-        <v>0.55697935108431</v>
+        <v>0.556979351089894</v>
       </c>
       <c r="GS26" t="n">
-        <v>0.555136986154041</v>
+        <v>0.555136986142704</v>
       </c>
       <c r="GT26" t="n">
-        <v>0.553552923904495</v>
+        <v>0.553552923870564</v>
       </c>
       <c r="GU26" t="n">
-        <v>0.552049835495304</v>
+        <v>0.552049835433366</v>
       </c>
       <c r="GV26" t="n">
-        <v>0.550452228501654</v>
+        <v>0.550452228406873</v>
       </c>
       <c r="GW26" t="n">
-        <v>0.548743919450009</v>
+        <v>0.548743919318344</v>
       </c>
       <c r="GX26" t="n">
-        <v>0.546832880038969</v>
+        <v>0.546832879867364</v>
       </c>
       <c r="GY26" t="n">
-        <v>0.544678787295645</v>
+        <v>0.544678787082129</v>
       </c>
       <c r="GZ26" t="n">
-        <v>0.542246458978607</v>
+        <v>0.54224645872236</v>
       </c>
       <c r="HA26" t="n">
-        <v>0.539492355547142</v>
+        <v>0.539492355248509</v>
       </c>
       <c r="HB26" t="n">
-        <v>0.53643865879796</v>
+        <v>0.536438658458349</v>
       </c>
       <c r="HC26" t="n">
-        <v>0.533116474792566</v>
+        <v>0.53311647441432</v>
       </c>
       <c r="HD26" t="n">
-        <v>0.529589755988126</v>
+        <v>0.529589755574338</v>
       </c>
       <c r="HE26" t="n">
-        <v>0.525780896493307</v>
+        <v>0.525780896047806</v>
       </c>
       <c r="HF26" t="n">
-        <v>0.521747225171385</v>
+        <v>0.521747224698475</v>
       </c>
       <c r="HG26" t="n">
-        <v>0.517539705730363</v>
+        <v>0.517539705234665</v>
       </c>
       <c r="HH26" t="n">
-        <v>0.513177332842779</v>
+        <v>0.513177332329158</v>
       </c>
       <c r="HI26" t="n">
-        <v>0.508738842236853</v>
+        <v>0.508738841710196</v>
       </c>
       <c r="HJ26" t="n">
-        <v>0.504251117543874</v>
+        <v>0.504251117009003</v>
       </c>
       <c r="HK26" t="n">
-        <v>0.499757647525994</v>
+        <v>0.499757646987545</v>
       </c>
       <c r="HL26" t="n">
-        <v>0.495261562030673</v>
+        <v>0.495261561493041</v>
       </c>
       <c r="HM26" t="n">
-        <v>0.490855162522443</v>
+        <v>0.490855161989614</v>
       </c>
       <c r="HN26" t="n">
-        <v>0.486555398030871</v>
+        <v>0.486555397506421</v>
       </c>
       <c r="HO26" t="n">
-        <v>0.482378767644486</v>
+        <v>0.482378767131528</v>
       </c>
       <c r="HP26" t="n">
-        <v>0.478329895610404</v>
+        <v>0.478329895111603</v>
       </c>
       <c r="HQ26" t="n">
-        <v>0.474420472862234</v>
+        <v>0.474420472379776</v>
       </c>
       <c r="HR26" t="n">
-        <v>0.470649384257593</v>
+        <v>0.470649383793212</v>
       </c>
       <c r="HS26" t="n">
-        <v>0.46701884707525</v>
+        <v>0.467018846630223</v>
       </c>
       <c r="HT26" t="n">
-        <v>0.463548001101287</v>
+        <v>0.463548000676459</v>
       </c>
       <c r="HU26" t="n">
-        <v>0.460195369460125</v>
+        <v>0.460195369056035</v>
       </c>
     </row>
     <row r="27">
@@ -19707,139 +19707,139 @@
         <v>95.2225040638737</v>
       </c>
       <c r="GC27" t="n">
-        <v>93.6634782988196</v>
+        <v>93.6634782988197</v>
       </c>
       <c r="GD27" t="n">
-        <v>95.0987768736227</v>
+        <v>95.0987768736497</v>
       </c>
       <c r="GE27" t="n">
-        <v>96.4617297778064</v>
+        <v>96.4617297778711</v>
       </c>
       <c r="GF27" t="n">
-        <v>97.324857664392</v>
+        <v>97.3248576645324</v>
       </c>
       <c r="GG27" t="n">
-        <v>98.3483765498065</v>
+        <v>98.3483765500985</v>
       </c>
       <c r="GH27" t="n">
-        <v>98.5907632147126</v>
+        <v>98.5907632151609</v>
       </c>
       <c r="GI27" t="n">
-        <v>98.7276406532607</v>
+        <v>98.7276406539345</v>
       </c>
       <c r="GJ27" t="n">
-        <v>98.891800465257</v>
+        <v>98.8918004662197</v>
       </c>
       <c r="GK27" t="n">
-        <v>98.9922345935848</v>
+        <v>98.9922345948615</v>
       </c>
       <c r="GL27" t="n">
-        <v>98.992343936613</v>
+        <v>98.992343938236</v>
       </c>
       <c r="GM27" t="n">
-        <v>98.8593328450728</v>
+        <v>98.8593328470086</v>
       </c>
       <c r="GN27" t="n">
-        <v>98.8293893240529</v>
+        <v>98.829389326441</v>
       </c>
       <c r="GO27" t="n">
-        <v>98.791184843782</v>
+        <v>98.791184846636</v>
       </c>
       <c r="GP27" t="n">
-        <v>98.7735085344497</v>
+        <v>98.7735085378068</v>
       </c>
       <c r="GQ27" t="n">
-        <v>98.7497600698037</v>
+        <v>98.7497600736996</v>
       </c>
       <c r="GR27" t="n">
-        <v>98.7187753087579</v>
+        <v>98.7187753132185</v>
       </c>
       <c r="GS27" t="n">
-        <v>98.6858206686838</v>
+        <v>98.6858206737084</v>
       </c>
       <c r="GT27" t="n">
-        <v>98.6903659251307</v>
+        <v>98.6903659307074</v>
       </c>
       <c r="GU27" t="n">
-        <v>98.7100325071618</v>
+        <v>98.7100325132375</v>
       </c>
       <c r="GV27" t="n">
-        <v>98.7223534696874</v>
+        <v>98.7223534761881</v>
       </c>
       <c r="GW27" t="n">
-        <v>98.7495623305601</v>
+        <v>98.7495623373757</v>
       </c>
       <c r="GX27" t="n">
-        <v>98.7884251096137</v>
+        <v>98.788425116625</v>
       </c>
       <c r="GY27" t="n">
-        <v>98.8315213670579</v>
+        <v>98.8315213741247</v>
       </c>
       <c r="GZ27" t="n">
-        <v>98.8786219616961</v>
+        <v>98.8786219686643</v>
       </c>
       <c r="HA27" t="n">
-        <v>98.9295297409939</v>
+        <v>98.9295297477021</v>
       </c>
       <c r="HB27" t="n">
-        <v>99.1007943683698</v>
+        <v>99.1007943747267</v>
       </c>
       <c r="HC27" t="n">
-        <v>99.2970882872221</v>
+        <v>99.2970882930298</v>
       </c>
       <c r="HD27" t="n">
-        <v>99.4636696025085</v>
+        <v>99.4636696076803</v>
       </c>
       <c r="HE27" t="n">
-        <v>99.6621843065608</v>
+        <v>99.6621843109</v>
       </c>
       <c r="HF27" t="n">
-        <v>99.8579026191004</v>
+        <v>99.8579026224858</v>
       </c>
       <c r="HG27" t="n">
-        <v>100.055543183689</v>
+        <v>100.055543185995</v>
       </c>
       <c r="HH27" t="n">
-        <v>100.252826896325</v>
+        <v>100.25282689744</v>
       </c>
       <c r="HI27" t="n">
-        <v>100.448634494016</v>
+        <v>100.448634493837</v>
       </c>
       <c r="HJ27" t="n">
-        <v>100.641643638148</v>
+        <v>100.641643636595</v>
       </c>
       <c r="HK27" t="n">
-        <v>100.829229925137</v>
+        <v>100.829229922154</v>
       </c>
       <c r="HL27" t="n">
-        <v>101.0127768602</v>
+        <v>101.012776855744</v>
       </c>
       <c r="HM27" t="n">
-        <v>101.191062546265</v>
+        <v>101.191062540303</v>
       </c>
       <c r="HN27" t="n">
-        <v>101.363906492745</v>
+        <v>101.363906485268</v>
       </c>
       <c r="HO27" t="n">
-        <v>101.529199913755</v>
+        <v>101.529199904779</v>
       </c>
       <c r="HP27" t="n">
-        <v>101.689404763801</v>
+        <v>101.689404753351</v>
       </c>
       <c r="HQ27" t="n">
-        <v>101.844679480739</v>
+        <v>101.844679468849</v>
       </c>
       <c r="HR27" t="n">
-        <v>101.995164093565</v>
+        <v>101.995164080287</v>
       </c>
       <c r="HS27" t="n">
-        <v>102.182008001432</v>
+        <v>102.182007986739</v>
       </c>
       <c r="HT27" t="n">
-        <v>102.313555867411</v>
+        <v>102.313555851495</v>
       </c>
       <c r="HU27" t="n">
-        <v>102.478704131841</v>
+        <v>102.478704114697</v>
       </c>
     </row>
     <row r="28">
@@ -20208,139 +20208,139 @@
       <c r="GA28"/>
       <c r="GB28"/>
       <c r="GC28" t="n">
-        <v>14.9831277549456</v>
+        <v>14.983127754949</v>
       </c>
       <c r="GD28" t="n">
-        <v>14.7803903592879</v>
+        <v>14.7803903595972</v>
       </c>
       <c r="GE28" t="n">
-        <v>14.9975773937295</v>
+        <v>14.9975773940315</v>
       </c>
       <c r="GF28" t="n">
-        <v>15.0840162893591</v>
+        <v>15.0840162906029</v>
       </c>
       <c r="GG28" t="n">
-        <v>15.0912172994908</v>
+        <v>15.0912173015564</v>
       </c>
       <c r="GH28" t="n">
-        <v>15.2058281658819</v>
+        <v>15.2058281693194</v>
       </c>
       <c r="GI28" t="n">
-        <v>15.4060420800951</v>
+        <v>15.4060420853197</v>
       </c>
       <c r="GJ28" t="n">
-        <v>15.9353074972012</v>
+        <v>15.9353075045993</v>
       </c>
       <c r="GK28" t="n">
-        <v>16.1617607035992</v>
+        <v>16.1617607135596</v>
       </c>
       <c r="GL28" t="n">
-        <v>16.444885334874</v>
+        <v>16.4448853475277</v>
       </c>
       <c r="GM28" t="n">
-        <v>16.7754573950817</v>
+        <v>16.7754574103949</v>
       </c>
       <c r="GN28" t="n">
-        <v>17.3877197915986</v>
+        <v>17.3877198095368</v>
       </c>
       <c r="GO28" t="n">
-        <v>17.637763967172</v>
+        <v>17.6377639873403</v>
       </c>
       <c r="GP28" t="n">
-        <v>17.9056080298453</v>
+        <v>17.9056080519334</v>
       </c>
       <c r="GQ28" t="n">
-        <v>18.2005738881279</v>
+        <v>18.200573911669</v>
       </c>
       <c r="GR28" t="n">
-        <v>18.8029306502875</v>
+        <v>18.802930674972</v>
       </c>
       <c r="GS28" t="n">
-        <v>19.0038871098439</v>
+        <v>19.0038871351117</v>
       </c>
       <c r="GT28" t="n">
-        <v>19.2102510594643</v>
+        <v>19.2102510849767</v>
       </c>
       <c r="GU28" t="n">
-        <v>19.4420452771697</v>
+        <v>19.4420453026036</v>
       </c>
       <c r="GV28" t="n">
-        <v>20.005850354776</v>
+        <v>20.0058503799694</v>
       </c>
       <c r="GW28" t="n">
-        <v>20.1320990531507</v>
+        <v>20.1320990776394</v>
       </c>
       <c r="GX28" t="n">
-        <v>20.2682451684861</v>
+        <v>20.26824519207</v>
       </c>
       <c r="GY28" t="n">
-        <v>20.4231243659103</v>
+        <v>20.4231243884187</v>
       </c>
       <c r="GZ28" t="n">
-        <v>20.9395538063796</v>
+        <v>20.9395538277723</v>
       </c>
       <c r="HA28" t="n">
-        <v>20.9814713844102</v>
+        <v>20.9814714044155</v>
       </c>
       <c r="HB28" t="n">
-        <v>21.0249942550768</v>
+        <v>21.0249942736124</v>
       </c>
       <c r="HC28" t="n">
-        <v>21.1110993525516</v>
+        <v>21.111099369573</v>
       </c>
       <c r="HD28" t="n">
-        <v>21.5689018630686</v>
+        <v>21.5689018785568</v>
       </c>
       <c r="HE28" t="n">
-        <v>21.5421741043276</v>
+        <v>21.5421741182314</v>
       </c>
       <c r="HF28" t="n">
-        <v>21.5395534821217</v>
+        <v>21.5395534945287</v>
       </c>
       <c r="HG28" t="n">
-        <v>21.5739011399926</v>
+        <v>21.5739011510106</v>
       </c>
       <c r="HH28" t="n">
-        <v>22.0332003507227</v>
+        <v>22.0332003604323</v>
       </c>
       <c r="HI28" t="n">
-        <v>21.9742491789907</v>
+        <v>21.9742491875876</v>
       </c>
       <c r="HJ28" t="n">
-        <v>21.9519619593197</v>
+        <v>21.9519619669646</v>
       </c>
       <c r="HK28" t="n">
-        <v>21.973662242491</v>
+        <v>21.9736622493362</v>
       </c>
       <c r="HL28" t="n">
-        <v>22.4470889226277</v>
+        <v>22.4470889287171</v>
       </c>
       <c r="HM28" t="n">
-        <v>22.379348680645</v>
+        <v>22.3793486862437</v>
       </c>
       <c r="HN28" t="n">
-        <v>22.3545343667655</v>
+        <v>22.3545343720046</v>
       </c>
       <c r="HO28" t="n">
-        <v>22.3804810271942</v>
+        <v>22.3804810321742</v>
       </c>
       <c r="HP28" t="n">
-        <v>22.8900058795785</v>
+        <v>22.8900058842432</v>
       </c>
       <c r="HQ28" t="n">
-        <v>22.8327469784525</v>
+        <v>22.832746983037</v>
       </c>
       <c r="HR28" t="n">
-        <v>22.8236030695624</v>
+        <v>22.8236030741114</v>
       </c>
       <c r="HS28" t="n">
-        <v>22.8992078134185</v>
+        <v>22.8992078179666</v>
       </c>
       <c r="HT28" t="n">
-        <v>23.4567188750527</v>
+        <v>23.4567188794245</v>
       </c>
       <c r="HU28" t="n">
-        <v>23.4370680655839</v>
+        <v>23.4370680699504</v>
       </c>
     </row>
     <row r="29">
@@ -20709,139 +20709,139 @@
       <c r="GA29"/>
       <c r="GB29"/>
       <c r="GC29" t="n">
-        <v>0.000020739434491577</v>
+        <v>0.0000207394344915839</v>
       </c>
       <c r="GD29" t="n">
-        <v>0.0000197905312967779</v>
+        <v>0.0000197905312973904</v>
       </c>
       <c r="GE29" t="n">
-        <v>0.000019790616135849</v>
+        <v>0.0000197906161365319</v>
       </c>
       <c r="GF29" t="n">
-        <v>0.0000193789338317775</v>
+        <v>0.0000193789338339758</v>
       </c>
       <c r="GG29" t="n">
-        <v>0.0000190103441828797</v>
+        <v>0.0000190103441865362</v>
       </c>
       <c r="GH29" t="n">
-        <v>0.0000188193093186097</v>
+        <v>0.0000188193093243792</v>
       </c>
       <c r="GI29" t="n">
-        <v>0.0000187464669361299</v>
+        <v>0.0000187464669447118</v>
       </c>
       <c r="GJ29" t="n">
-        <v>0.0000190909747234986</v>
+        <v>0.0000190909747353957</v>
       </c>
       <c r="GK29" t="n">
-        <v>0.0000190577091269884</v>
+        <v>0.0000190577091426354</v>
       </c>
       <c r="GL29" t="n">
-        <v>0.0000190974739924567</v>
+        <v>0.000019097474012002</v>
       </c>
       <c r="GM29" t="n">
-        <v>0.0000192027288659693</v>
+        <v>0.0000192027288893175</v>
       </c>
       <c r="GN29" t="n">
-        <v>0.000019645823931782</v>
+        <v>0.0000196458239589605</v>
       </c>
       <c r="GO29" t="n">
-        <v>0.000019662636814478</v>
+        <v>0.0000196626368447814</v>
       </c>
       <c r="GP29" t="n">
-        <v>0.0000196945649347864</v>
+        <v>0.0000196945649677487</v>
       </c>
       <c r="GQ29" t="n">
-        <v>0.0000197681777179976</v>
+        <v>0.0000197681777530293</v>
       </c>
       <c r="GR29" t="n">
-        <v>0.000020164702470752</v>
+        <v>0.000020164702507549</v>
       </c>
       <c r="GS29" t="n">
-        <v>0.0000201279226239331</v>
+        <v>0.0000201279226615855</v>
       </c>
       <c r="GT29" t="n">
-        <v>0.0000200947409182313</v>
+        <v>0.0000200947409562826</v>
       </c>
       <c r="GU29" t="n">
-        <v>0.0000200995384093697</v>
+        <v>0.0000200995384474414</v>
       </c>
       <c r="GV29" t="n">
-        <v>0.0000204350417154402</v>
+        <v>0.0000204350417534602</v>
       </c>
       <c r="GW29" t="n">
-        <v>0.0000203192419564373</v>
+        <v>0.0000203192419935866</v>
       </c>
       <c r="GX29" t="n">
-        <v>0.0000202107338219834</v>
+        <v>0.0000202107338579941</v>
       </c>
       <c r="GY29" t="n">
-        <v>0.0000201261055839312</v>
+        <v>0.0000201261056186063</v>
       </c>
       <c r="GZ29" t="n">
-        <v>0.0000203882653171432</v>
+        <v>0.0000203882653505999</v>
       </c>
       <c r="HA29" t="n">
-        <v>0.0000201804749726341</v>
+        <v>0.0000201804750042718</v>
       </c>
       <c r="HB29" t="n">
-        <v>0.0000199676484198879</v>
+        <v>0.0000199676484495848</v>
       </c>
       <c r="HC29" t="n">
-        <v>0.0000198103213825342</v>
+        <v>0.0000198103214102994</v>
       </c>
       <c r="HD29" t="n">
-        <v>0.0000199830745989778</v>
+        <v>0.0000199830746249604</v>
       </c>
       <c r="HE29" t="n">
-        <v>0.0000197072405990511</v>
+        <v>0.0000197072406229643</v>
       </c>
       <c r="HF29" t="n">
-        <v>0.0000194534754466793</v>
+        <v>0.00001945347546865</v>
       </c>
       <c r="HG29" t="n">
-        <v>0.0000192408226777535</v>
+        <v>0.0000192408226979566</v>
       </c>
       <c r="HH29" t="n">
-        <v>0.0000194019031112829</v>
+        <v>0.000019401903130025</v>
       </c>
       <c r="HI29" t="n">
-        <v>0.0000191014160873834</v>
+        <v>0.0000191014161046376</v>
       </c>
       <c r="HJ29" t="n">
-        <v>0.0000188351258980077</v>
+        <v>0.0000188351259139793</v>
       </c>
       <c r="HK29" t="n">
-        <v>0.000018615413705828</v>
+        <v>0.0000186154137207201</v>
       </c>
       <c r="HL29" t="n">
-        <v>0.0000187735568091277</v>
+        <v>0.0000187735568231981</v>
       </c>
       <c r="HM29" t="n">
-        <v>0.0000184750035020685</v>
+        <v>0.0000184750035153544</v>
       </c>
       <c r="HN29" t="n">
-        <v>0.0000182151013709246</v>
+        <v>0.0000182151013835879</v>
       </c>
       <c r="HO29" t="n">
-        <v>0.0000180060058909862</v>
+        <v>0.0000180060059031652</v>
       </c>
       <c r="HP29" t="n">
-        <v>0.0000181825427662589</v>
+        <v>0.0000181825427781046</v>
       </c>
       <c r="HQ29" t="n">
-        <v>0.0000179049230662723</v>
+        <v>0.0000179049230777864</v>
       </c>
       <c r="HR29" t="n">
-        <v>0.0000176682885495987</v>
+        <v>0.0000176682885608517</v>
       </c>
       <c r="HS29" t="n">
-        <v>0.0000175167599584814</v>
+        <v>0.0000175167599695691</v>
       </c>
       <c r="HT29" t="n">
-        <v>0.0000177183120564737</v>
+        <v>0.0000177183120674057</v>
       </c>
       <c r="HU29" t="n">
-        <v>0.0000174866693404629</v>
+        <v>0.0000174866693511948</v>
       </c>
     </row>
     <row r="30">
@@ -21210,139 +21210,139 @@
       <c r="GA30"/>
       <c r="GB30"/>
       <c r="GC30" t="n">
-        <v>844.857393096413</v>
+        <v>844.857393096416</v>
       </c>
       <c r="GD30" t="n">
-        <v>864.333783411753</v>
+        <v>864.333783412066</v>
       </c>
       <c r="GE30" t="n">
-        <v>884.209196411711</v>
+        <v>884.209196412328</v>
       </c>
       <c r="GF30" t="n">
-        <v>904.095972370054</v>
+        <v>904.095972371918</v>
       </c>
       <c r="GG30" t="n">
-        <v>924.112901714552</v>
+        <v>924.112901718491</v>
       </c>
       <c r="GH30" t="n">
-        <v>944.252245895916</v>
+        <v>944.252245903314</v>
       </c>
       <c r="GI30" t="n">
-        <v>964.68098889018</v>
+        <v>964.680988902812</v>
       </c>
       <c r="GJ30" t="n">
-        <v>985.779613790243</v>
+        <v>985.779613810254</v>
       </c>
       <c r="GK30" t="n">
-        <v>1007.31643729733</v>
+        <v>1007.3164373272</v>
       </c>
       <c r="GL30" t="n">
-        <v>1029.40747012444</v>
+        <v>1029.40747016669</v>
       </c>
       <c r="GM30" t="n">
-        <v>1052.14434074963</v>
+        <v>1052.14434080662</v>
       </c>
       <c r="GN30" t="n">
-        <v>1075.84467647387</v>
+        <v>1075.84467654775</v>
       </c>
       <c r="GO30" t="n">
-        <v>1100.16772172261</v>
+        <v>1100.16772181489</v>
       </c>
       <c r="GP30" t="n">
-        <v>1125.14102014165</v>
+        <v>1125.14102025324</v>
       </c>
       <c r="GQ30" t="n">
-        <v>1150.79145955602</v>
+        <v>1150.79145968704</v>
       </c>
       <c r="GR30" t="n">
-        <v>1177.41639841833</v>
+        <v>1177.41639856821</v>
       </c>
       <c r="GS30" t="n">
-        <v>1204.59089663621</v>
+        <v>1204.59089680344</v>
       </c>
       <c r="GT30" t="n">
-        <v>1232.28833772364</v>
+        <v>1232.28833790601</v>
       </c>
       <c r="GU30" t="n">
-        <v>1260.49883307092</v>
+        <v>1260.49883326554</v>
       </c>
       <c r="GV30" t="n">
-        <v>1289.51566382414</v>
+        <v>1289.51566402772</v>
       </c>
       <c r="GW30" t="n">
-        <v>1318.8665727491</v>
+        <v>1318.86657295767</v>
       </c>
       <c r="GX30" t="n">
-        <v>1348.52417791936</v>
+        <v>1348.52417812866</v>
       </c>
       <c r="GY30" t="n">
-        <v>1378.47229934638</v>
+        <v>1378.47229955193</v>
       </c>
       <c r="GZ30" t="n">
-        <v>1409.03779547149</v>
+        <v>1409.03779566882</v>
       </c>
       <c r="HA30" t="n">
-        <v>1439.71726006888</v>
+        <v>1439.71726025337</v>
       </c>
       <c r="HB30" t="n">
-        <v>1470.483283945</v>
+        <v>1470.48328411215</v>
       </c>
       <c r="HC30" t="n">
-        <v>1501.35349204286</v>
+        <v>1501.35349218839</v>
       </c>
       <c r="HD30" t="n">
-        <v>1532.67743863195</v>
+        <v>1532.67743875187</v>
       </c>
       <c r="HE30" t="n">
-        <v>1563.95644977566</v>
+        <v>1563.95644986627</v>
       </c>
       <c r="HF30" t="n">
-        <v>1595.20181134956</v>
+        <v>1595.20181140767</v>
       </c>
       <c r="HG30" t="n">
-        <v>1626.44320477033</v>
+        <v>1626.44320479327</v>
       </c>
       <c r="HH30" t="n">
-        <v>1658.09841759175</v>
+        <v>1658.09841757735</v>
       </c>
       <c r="HI30" t="n">
-        <v>1689.6517642752</v>
+        <v>1689.65176422192</v>
       </c>
       <c r="HJ30" t="n">
-        <v>1721.14177819587</v>
+        <v>1721.14177810274</v>
       </c>
       <c r="HK30" t="n">
-        <v>1752.6177191424</v>
+        <v>1752.61771900901</v>
       </c>
       <c r="HL30" t="n">
-        <v>1784.53746356621</v>
+        <v>1784.53746339255</v>
       </c>
       <c r="HM30" t="n">
-        <v>1816.37030762648</v>
+        <v>1816.37030741311</v>
       </c>
       <c r="HN30" t="n">
-        <v>1848.16860950717</v>
+        <v>1848.16860925506</v>
       </c>
       <c r="HO30" t="n">
-        <v>1879.99414466828</v>
+        <v>1879.99414437871</v>
       </c>
       <c r="HP30" t="n">
-        <v>1912.34044509593</v>
+        <v>1912.34044477028</v>
       </c>
       <c r="HQ30" t="n">
-        <v>1944.65441279556</v>
+        <v>1944.65441243558</v>
       </c>
       <c r="HR30" t="n">
-        <v>1976.99530664122</v>
+        <v>1976.99530624875</v>
       </c>
       <c r="HS30" t="n">
-        <v>2009.45939963458</v>
+        <v>2009.45939921153</v>
       </c>
       <c r="HT30" t="n">
-        <v>2042.53788005145</v>
+        <v>2042.53787959955</v>
       </c>
       <c r="HU30" t="n">
-        <v>2075.66356909838</v>
+        <v>2075.66356861948</v>
       </c>
     </row>
     <row r="31">
@@ -22028,10 +22028,10 @@
         <v>0.043535305024288</v>
       </c>
       <c r="HT31" t="n">
+        <v>0.043535305024288</v>
+      </c>
+      <c r="HU31" t="n">
         <v>0.0435353050242881</v>
-      </c>
-      <c r="HU31" t="n">
-        <v>0.043535305024288</v>
       </c>
     </row>
     <row r="32">
@@ -22588,139 +22588,139 @@
         <v>0.233491652414238</v>
       </c>
       <c r="GC32" t="n">
-        <v>0.236936917858783</v>
+        <v>0.236936917858813</v>
       </c>
       <c r="GD32" t="n">
-        <v>0.232440005048337</v>
+        <v>0.232440005051002</v>
       </c>
       <c r="GE32" t="n">
-        <v>0.233394095709435</v>
+        <v>0.233394095713182</v>
       </c>
       <c r="GF32" t="n">
-        <v>0.230667800200225</v>
+        <v>0.230667800208296</v>
       </c>
       <c r="GG32" t="n">
-        <v>0.230145926966961</v>
+        <v>0.230145926981288</v>
       </c>
       <c r="GH32" t="n">
-        <v>0.229913521069542</v>
+        <v>0.229913521090224</v>
       </c>
       <c r="GI32" t="n">
-        <v>0.229930659010228</v>
+        <v>0.229930659040657</v>
       </c>
       <c r="GJ32" t="n">
-        <v>0.230154653214519</v>
+        <v>0.230154653255076</v>
       </c>
       <c r="GK32" t="n">
-        <v>0.230280819277799</v>
+        <v>0.230280819329806</v>
       </c>
       <c r="GL32" t="n">
-        <v>0.230549729020334</v>
+        <v>0.230549729084501</v>
       </c>
       <c r="GM32" t="n">
-        <v>0.231011972877857</v>
+        <v>0.231011972953985</v>
       </c>
       <c r="GN32" t="n">
-        <v>0.231097590652736</v>
+        <v>0.231097590740446</v>
       </c>
       <c r="GO32" t="n">
-        <v>0.23102487155163</v>
+        <v>0.231024871649847</v>
       </c>
       <c r="GP32" t="n">
-        <v>0.230933276370575</v>
+        <v>0.23093327647818</v>
       </c>
       <c r="GQ32" t="n">
-        <v>0.231028278179631</v>
+        <v>0.231028278295552</v>
       </c>
       <c r="GR32" t="n">
-        <v>0.231071807729054</v>
+        <v>0.231071807851752</v>
       </c>
       <c r="GS32" t="n">
-        <v>0.231159963816852</v>
+        <v>0.231159963945165</v>
       </c>
       <c r="GT32" t="n">
-        <v>0.23122404512726</v>
+        <v>0.231224045259924</v>
       </c>
       <c r="GU32" t="n">
-        <v>0.231453603420165</v>
+        <v>0.2314536035562</v>
       </c>
       <c r="GV32" t="n">
-        <v>0.231598365093706</v>
+        <v>0.231598365231694</v>
       </c>
       <c r="GW32" t="n">
-        <v>0.231749266724201</v>
+        <v>0.23174926686297</v>
       </c>
       <c r="GX32" t="n">
-        <v>0.231850529341614</v>
+        <v>0.231850529480019</v>
       </c>
       <c r="GY32" t="n">
-        <v>0.232015984944638</v>
+        <v>0.232015985081798</v>
       </c>
       <c r="GZ32" t="n">
-        <v>0.232115845674111</v>
+        <v>0.232115845808949</v>
       </c>
       <c r="HA32" t="n">
-        <v>0.232155100301947</v>
+        <v>0.23215510043353</v>
       </c>
       <c r="HB32" t="n">
-        <v>0.232079083011315</v>
+        <v>0.232079083138703</v>
       </c>
       <c r="HC32" t="n">
-        <v>0.232181218923903</v>
+        <v>0.232181219046773</v>
       </c>
       <c r="HD32" t="n">
-        <v>0.232053741791337</v>
+        <v>0.23205374190888</v>
       </c>
       <c r="HE32" t="n">
-        <v>0.231969097570131</v>
+        <v>0.231969097682149</v>
       </c>
       <c r="HF32" t="n">
-        <v>0.231823833695587</v>
+        <v>0.231823833801955</v>
       </c>
       <c r="HG32" t="n">
-        <v>0.231745626241037</v>
+        <v>0.231745626341952</v>
       </c>
       <c r="HH32" t="n">
-        <v>0.2316166673679</v>
+        <v>0.231616667463376</v>
       </c>
       <c r="HI32" t="n">
-        <v>0.231434488361347</v>
+        <v>0.231434488451571</v>
       </c>
       <c r="HJ32" t="n">
-        <v>0.231223799860929</v>
+        <v>0.231223799946128</v>
       </c>
       <c r="HK32" t="n">
-        <v>0.231088497634166</v>
+        <v>0.231088497714667</v>
       </c>
       <c r="HL32" t="n">
-        <v>0.23090546935982</v>
+        <v>0.23090546943586</v>
       </c>
       <c r="HM32" t="n">
-        <v>0.230682968284136</v>
+        <v>0.230682968355973</v>
       </c>
       <c r="HN32" t="n">
-        <v>0.230443095757174</v>
+        <v>0.230443095825101</v>
       </c>
       <c r="HO32" t="n">
-        <v>0.230291651378359</v>
+        <v>0.23029165144271</v>
       </c>
       <c r="HP32" t="n">
-        <v>0.230117035167019</v>
+        <v>0.230117035228003</v>
       </c>
       <c r="HQ32" t="n">
-        <v>0.229906984346254</v>
+        <v>0.229906984404075</v>
       </c>
       <c r="HR32" t="n">
-        <v>0.229688106285017</v>
+        <v>0.229688106339886</v>
       </c>
       <c r="HS32" t="n">
-        <v>0.229728897424756</v>
+        <v>0.229728897477132</v>
       </c>
       <c r="HT32" t="n">
-        <v>0.22956526453186</v>
+        <v>0.229565264581598</v>
       </c>
       <c r="HU32" t="n">
-        <v>0.229493295930651</v>
+        <v>0.229493295977955</v>
       </c>
     </row>
     <row r="33">
@@ -23109,139 +23109,139 @@
         <v>82599</v>
       </c>
       <c r="GC33" t="n">
-        <v>82724.1708895118</v>
+        <v>82724.1708895037</v>
       </c>
       <c r="GD33" t="n">
-        <v>84465.7654103583</v>
+        <v>84465.7654016171</v>
       </c>
       <c r="GE33" t="n">
-        <v>85786.2651117149</v>
+        <v>85786.2650977703</v>
       </c>
       <c r="GF33" t="n">
-        <v>87450.5633069186</v>
+        <v>87450.5632784499</v>
       </c>
       <c r="GG33" t="n">
-        <v>89024.370858459</v>
+        <v>89024.3708118083</v>
       </c>
       <c r="GH33" t="n">
-        <v>90303.5456737264</v>
+        <v>90303.5456025897</v>
       </c>
       <c r="GI33" t="n">
-        <v>91418.8819002486</v>
+        <v>91418.8817990193</v>
       </c>
       <c r="GJ33" t="n">
-        <v>92306.0203817792</v>
+        <v>92306.0202475345</v>
       </c>
       <c r="GK33" t="n">
-        <v>93065.2399601311</v>
+        <v>93065.2397905449</v>
       </c>
       <c r="GL33" t="n">
-        <v>93823.0030160202</v>
+        <v>93823.0028090925</v>
       </c>
       <c r="GM33" t="n">
-        <v>94504.8739641194</v>
+        <v>94504.8737194695</v>
       </c>
       <c r="GN33" t="n">
-        <v>95171.7657516056</v>
+        <v>95171.7654701547</v>
       </c>
       <c r="GO33" t="n">
-        <v>95684.1273034821</v>
+        <v>95684.126987656</v>
       </c>
       <c r="GP33" t="n">
-        <v>96293.4828609687</v>
+        <v>96293.4825132375</v>
       </c>
       <c r="GQ33" t="n">
-        <v>96819.2754932104</v>
+        <v>96819.2751161914</v>
       </c>
       <c r="GR33" t="n">
-        <v>97396.6980646816</v>
+        <v>97396.6976609764</v>
       </c>
       <c r="GS33" t="n">
-        <v>97961.5144614051</v>
+        <v>97961.5140340047</v>
       </c>
       <c r="GT33" t="n">
-        <v>98555.8174411528</v>
+        <v>98555.8169929774</v>
       </c>
       <c r="GU33" t="n">
-        <v>99126.8077321416</v>
+        <v>99126.8072661831</v>
       </c>
       <c r="GV33" t="n">
-        <v>99705.2787728525</v>
+        <v>99705.2782918464</v>
       </c>
       <c r="GW33" t="n">
-        <v>100295.553393575</v>
+        <v>100295.552900296</v>
       </c>
       <c r="GX33" t="n">
-        <v>100911.948589439</v>
+        <v>100911.948086435</v>
       </c>
       <c r="GY33" t="n">
-        <v>101530.977514083</v>
+        <v>101530.977003976</v>
       </c>
       <c r="GZ33" t="n">
-        <v>102167.845179498</v>
+        <v>102167.844664728</v>
       </c>
       <c r="HA33" t="n">
-        <v>102830.916067918</v>
+        <v>102830.915550931</v>
       </c>
       <c r="HB33" t="n">
-        <v>103538.973609983</v>
+        <v>103538.973093055</v>
       </c>
       <c r="HC33" t="n">
-        <v>104239.541358866</v>
+        <v>104239.54084412</v>
       </c>
       <c r="HD33" t="n">
-        <v>104959.846961418</v>
+        <v>104959.846450162</v>
       </c>
       <c r="HE33" t="n">
-        <v>105694.076656281</v>
+        <v>105694.076149764</v>
       </c>
       <c r="HF33" t="n">
-        <v>106436.311132736</v>
+        <v>106436.310631626</v>
       </c>
       <c r="HG33" t="n">
-        <v>107161.13985428</v>
+        <v>107161.139359163</v>
       </c>
       <c r="HH33" t="n">
-        <v>107869.174232782</v>
+        <v>107869.173743968</v>
       </c>
       <c r="HI33" t="n">
-        <v>108570.871817407</v>
+        <v>108570.871335047</v>
       </c>
       <c r="HJ33" t="n">
-        <v>109269.799729251</v>
+        <v>109269.799253294</v>
       </c>
       <c r="HK33" t="n">
-        <v>109936.587293902</v>
+        <v>109936.586824394</v>
       </c>
       <c r="HL33" t="n">
-        <v>110579.545001623</v>
+        <v>110579.54453847</v>
       </c>
       <c r="HM33" t="n">
-        <v>111210.642565656</v>
+        <v>111210.642108837</v>
       </c>
       <c r="HN33" t="n">
-        <v>111831.110706351</v>
+        <v>111831.11025579</v>
       </c>
       <c r="HO33" t="n">
-        <v>112413.525111625</v>
+        <v>112413.524667407</v>
       </c>
       <c r="HP33" t="n">
-        <v>112962.080900487</v>
+        <v>112962.080462685</v>
       </c>
       <c r="HQ33" t="n">
-        <v>113493.89919589</v>
+        <v>113493.898764677</v>
       </c>
       <c r="HR33" t="n">
-        <v>114012.487662769</v>
+        <v>114012.487238331</v>
       </c>
       <c r="HS33" t="n">
-        <v>114483.151573715</v>
+        <v>114483.151156447</v>
       </c>
       <c r="HT33" t="n">
-        <v>114916.99684252</v>
+        <v>114916.996432602</v>
       </c>
       <c r="HU33" t="n">
-        <v>115342.797040339</v>
+        <v>115342.796638389</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sem_coredata.xlsx
+++ b/outputs/sem_coredata.xlsx
@@ -2754,139 +2754,139 @@
         <v>354377</v>
       </c>
       <c r="GC2" t="n">
-        <v>355091.626663069</v>
+        <v>355093.061268826</v>
       </c>
       <c r="GD2" t="n">
-        <v>360111.637407478</v>
+        <v>360057.784065344</v>
       </c>
       <c r="GE2" t="n">
-        <v>362966.815722216</v>
+        <v>362937.789785227</v>
       </c>
       <c r="GF2" t="n">
-        <v>366513.561311229</v>
+        <v>366473.809693835</v>
       </c>
       <c r="GG2" t="n">
-        <v>369343.656520952</v>
+        <v>369339.814436186</v>
       </c>
       <c r="GH2" t="n">
-        <v>371764.515130078</v>
+        <v>371785.376588256</v>
       </c>
       <c r="GI2" t="n">
-        <v>373741.073366385</v>
+        <v>373790.181068688</v>
       </c>
       <c r="GJ2" t="n">
-        <v>375470.918749187</v>
+        <v>375539.160649502</v>
       </c>
       <c r="GK2" t="n">
-        <v>377283.567422444</v>
+        <v>377359.172187142</v>
       </c>
       <c r="GL2" t="n">
-        <v>379125.691348646</v>
+        <v>379195.880919388</v>
       </c>
       <c r="GM2" t="n">
-        <v>380784.317805237</v>
+        <v>380837.882620577</v>
       </c>
       <c r="GN2" t="n">
-        <v>382307.490272319</v>
+        <v>382332.873070651</v>
       </c>
       <c r="GO2" t="n">
-        <v>384059.188113549</v>
+        <v>384044.253230457</v>
       </c>
       <c r="GP2" t="n">
-        <v>386011.016107498</v>
+        <v>385944.148380431</v>
       </c>
       <c r="GQ2" t="n">
-        <v>387799.538413736</v>
+        <v>387673.975856514</v>
       </c>
       <c r="GR2" t="n">
-        <v>389804.350715036</v>
+        <v>389612.03339764</v>
       </c>
       <c r="GS2" t="n">
-        <v>392020.281594685</v>
+        <v>391756.563853357</v>
       </c>
       <c r="GT2" t="n">
-        <v>394422.916454055</v>
+        <v>394082.925895971</v>
       </c>
       <c r="GU2" t="n">
-        <v>396625.977907248</v>
+        <v>396208.183594643</v>
       </c>
       <c r="GV2" t="n">
-        <v>399001.76992623</v>
+        <v>398503.25039253</v>
       </c>
       <c r="GW2" t="n">
-        <v>401600.960242927</v>
+        <v>401020.572361829</v>
       </c>
       <c r="GX2" t="n">
-        <v>404372.766667307</v>
+        <v>403709.434652402</v>
       </c>
       <c r="GY2" t="n">
-        <v>406945.69344238</v>
+        <v>406200.441932707</v>
       </c>
       <c r="GZ2" t="n">
-        <v>409686.461636167</v>
+        <v>408859.757902305</v>
       </c>
       <c r="HA2" t="n">
-        <v>412616.810032024</v>
+        <v>411709.959454713</v>
       </c>
       <c r="HB2" t="n">
-        <v>415689.571841001</v>
+        <v>414703.659834883</v>
       </c>
       <c r="HC2" t="n">
-        <v>418425.864094204</v>
+        <v>417365.103638016</v>
       </c>
       <c r="HD2" t="n">
-        <v>421316.136766772</v>
+        <v>420181.785554543</v>
       </c>
       <c r="HE2" t="n">
-        <v>424308.9531196</v>
+        <v>423104.405924654</v>
       </c>
       <c r="HF2" t="n">
-        <v>427360.250759449</v>
+        <v>426087.907232089</v>
       </c>
       <c r="HG2" t="n">
-        <v>430071.644604869</v>
+        <v>428735.444686371</v>
       </c>
       <c r="HH2" t="n">
-        <v>432810.304980346</v>
+        <v>431412.894429119</v>
       </c>
       <c r="HI2" t="n">
-        <v>435654.380355762</v>
+        <v>434197.980378483</v>
       </c>
       <c r="HJ2" t="n">
-        <v>438529.293754509</v>
+        <v>437015.956812562</v>
       </c>
       <c r="HK2" t="n">
-        <v>441038.018069797</v>
+        <v>439470.628080736</v>
       </c>
       <c r="HL2" t="n">
-        <v>443578.065204849</v>
+        <v>441958.297159013</v>
       </c>
       <c r="HM2" t="n">
-        <v>446209.067647217</v>
+        <v>444538.084235254</v>
       </c>
       <c r="HN2" t="n">
-        <v>448862.974317128</v>
+        <v>447141.780415184</v>
       </c>
       <c r="HO2" t="n">
-        <v>451133.358592472</v>
+        <v>449363.800258332</v>
       </c>
       <c r="HP2" t="n">
-        <v>453398.438499591</v>
+        <v>451581.251814514</v>
       </c>
       <c r="HQ2" t="n">
-        <v>455771.878097093</v>
+        <v>453907.281516455</v>
       </c>
       <c r="HR2" t="n">
-        <v>458182.393700387</v>
+        <v>456270.456935422</v>
       </c>
       <c r="HS2" t="n">
-        <v>460112.011605524</v>
+        <v>458154.476213753</v>
       </c>
       <c r="HT2" t="n">
-        <v>462135.122519908</v>
+        <v>460131.309445219</v>
       </c>
       <c r="HU2" t="n">
-        <v>464246.863784685</v>
+        <v>462196.668520795</v>
       </c>
     </row>
     <row r="3">
@@ -4135,136 +4135,136 @@
         <v>36864.8957689682</v>
       </c>
       <c r="GD4" t="n">
-        <v>37067.0321234074</v>
+        <v>37067.0424615201</v>
       </c>
       <c r="GE4" t="n">
-        <v>37241.6529393183</v>
+        <v>37241.2523090563</v>
       </c>
       <c r="GF4" t="n">
-        <v>37366.1984493968</v>
+        <v>37366.4033785709</v>
       </c>
       <c r="GG4" t="n">
-        <v>37326.3949317281</v>
+        <v>37327.7724128136</v>
       </c>
       <c r="GH4" t="n">
-        <v>37201.5948014852</v>
+        <v>37204.0844715228</v>
       </c>
       <c r="GI4" t="n">
-        <v>37027.6696104953</v>
+        <v>37030.7396951707</v>
       </c>
       <c r="GJ4" t="n">
-        <v>36908.9972933815</v>
+        <v>36911.1636241773</v>
       </c>
       <c r="GK4" t="n">
-        <v>36880.2350067634</v>
+        <v>36880.3199809674</v>
       </c>
       <c r="GL4" t="n">
-        <v>36964.5856616145</v>
+        <v>36961.5004781343</v>
       </c>
       <c r="GM4" t="n">
-        <v>37146.4706532988</v>
+        <v>37139.7680086486</v>
       </c>
       <c r="GN4" t="n">
-        <v>37391.9150102401</v>
+        <v>37381.7643538881</v>
       </c>
       <c r="GO4" t="n">
-        <v>37661.9482886244</v>
+        <v>37649.051207505</v>
       </c>
       <c r="GP4" t="n">
-        <v>37926.6214421153</v>
+        <v>37912.0089799848</v>
       </c>
       <c r="GQ4" t="n">
-        <v>38165.0447143348</v>
+        <v>38149.8728264283</v>
       </c>
       <c r="GR4" t="n">
-        <v>38359.8279107349</v>
+        <v>38345.2078402655</v>
       </c>
       <c r="GS4" t="n">
-        <v>38506.0423255788</v>
+        <v>38492.8216019205</v>
       </c>
       <c r="GT4" t="n">
-        <v>38605.4984982038</v>
+        <v>38594.108585265</v>
       </c>
       <c r="GU4" t="n">
-        <v>38667.1035891992</v>
+        <v>38657.484892767</v>
       </c>
       <c r="GV4" t="n">
-        <v>38701.6561165574</v>
+        <v>38693.2740485583</v>
       </c>
       <c r="GW4" t="n">
-        <v>38724.7990760806</v>
+        <v>38716.7404512673</v>
       </c>
       <c r="GX4" t="n">
-        <v>38751.827551007</v>
+        <v>38742.9444864644</v>
       </c>
       <c r="GY4" t="n">
-        <v>38792.9873896796</v>
+        <v>38782.0734206202</v>
       </c>
       <c r="GZ4" t="n">
-        <v>38851.6988299463</v>
+        <v>38837.6172344702</v>
       </c>
       <c r="HA4" t="n">
-        <v>38930.7195186552</v>
+        <v>38912.4962197519</v>
       </c>
       <c r="HB4" t="n">
-        <v>39030.4748045109</v>
+        <v>39007.3344574251</v>
       </c>
       <c r="HC4" t="n">
-        <v>39148.6878329895</v>
+        <v>39120.0644260793</v>
       </c>
       <c r="HD4" t="n">
-        <v>39279.3211328398</v>
+        <v>39244.854277343</v>
       </c>
       <c r="HE4" t="n">
-        <v>39421.5453512097</v>
+        <v>39381.0213189521</v>
       </c>
       <c r="HF4" t="n">
-        <v>39574.863690026</v>
+        <v>39528.1869507086</v>
       </c>
       <c r="HG4" t="n">
-        <v>39737.5408575742</v>
+        <v>39684.7007116105</v>
       </c>
       <c r="HH4" t="n">
-        <v>39906.3997018086</v>
+        <v>39847.4333622701</v>
       </c>
       <c r="HI4" t="n">
-        <v>40081.2831908876</v>
+        <v>40016.2647540735</v>
       </c>
       <c r="HJ4" t="n">
-        <v>40263.8838450976</v>
+        <v>40192.9000937155</v>
       </c>
       <c r="HK4" t="n">
-        <v>40453.8474113497</v>
+        <v>40377.0052074737</v>
       </c>
       <c r="HL4" t="n">
-        <v>40647.515046794</v>
+        <v>40564.9447804072</v>
       </c>
       <c r="HM4" t="n">
-        <v>40844.4435362812</v>
+        <v>40756.2993767962</v>
       </c>
       <c r="HN4" t="n">
-        <v>41044.6781099135</v>
+        <v>40951.132939814</v>
       </c>
       <c r="HO4" t="n">
-        <v>41246.9612754461</v>
+        <v>41148.2023008556</v>
       </c>
       <c r="HP4" t="n">
-        <v>41447.1816120292</v>
+        <v>41343.4089970277</v>
       </c>
       <c r="HQ4" t="n">
-        <v>41644.8419452318</v>
+        <v>41536.2594137818</v>
       </c>
       <c r="HR4" t="n">
-        <v>41841.2713458308</v>
+        <v>41728.0743728611</v>
       </c>
       <c r="HS4" t="n">
-        <v>42036.4696126621</v>
+        <v>41918.8355612078</v>
       </c>
       <c r="HT4" t="n">
-        <v>42226.2624953921</v>
+        <v>42104.3549724863</v>
       </c>
       <c r="HU4" t="n">
-        <v>42412.3421153103</v>
+        <v>42286.289457163</v>
       </c>
     </row>
     <row r="5">
@@ -4824,136 +4824,136 @@
         <v>11150.4565404427</v>
       </c>
       <c r="GD5" t="n">
-        <v>11211.5963480674</v>
+        <v>11211.5994750171</v>
       </c>
       <c r="GE5" t="n">
-        <v>11264.4135818682</v>
+        <v>11264.2924039771</v>
       </c>
       <c r="GF5" t="n">
-        <v>11302.0846309372</v>
+        <v>11302.1466154838</v>
       </c>
       <c r="GG5" t="n">
-        <v>11290.0453348897</v>
+        <v>11290.4619790348</v>
       </c>
       <c r="GH5" t="n">
-        <v>11252.2972713326</v>
+        <v>11253.0503172039</v>
       </c>
       <c r="GI5" t="n">
-        <v>11199.6904419094</v>
+        <v>11200.619044718</v>
       </c>
       <c r="GJ5" t="n">
-        <v>11163.795846606</v>
+        <v>11164.4510926574</v>
       </c>
       <c r="GK5" t="n">
-        <v>11155.0961712034</v>
+        <v>11155.1218731931</v>
       </c>
       <c r="GL5" t="n">
-        <v>11180.6095570806</v>
+        <v>11179.6763873646</v>
       </c>
       <c r="GM5" t="n">
-        <v>11235.6239726331</v>
+        <v>11233.5966361571</v>
       </c>
       <c r="GN5" t="n">
-        <v>11309.8630713226</v>
+        <v>11306.7928211524</v>
       </c>
       <c r="GO5" t="n">
-        <v>11391.5395354029</v>
+        <v>11387.6385792352</v>
       </c>
       <c r="GP5" t="n">
-        <v>11471.594732464</v>
+        <v>11467.1749281885</v>
       </c>
       <c r="GQ5" t="n">
-        <v>11543.7101767006</v>
+        <v>11539.1211639499</v>
       </c>
       <c r="GR5" t="n">
-        <v>11602.6258882729</v>
+        <v>11598.2037827172</v>
       </c>
       <c r="GS5" t="n">
-        <v>11646.8510907126</v>
+        <v>11642.8522429874</v>
       </c>
       <c r="GT5" t="n">
-        <v>11676.9334144898</v>
+        <v>11673.4883286819</v>
       </c>
       <c r="GU5" t="n">
-        <v>11695.5669919213</v>
+        <v>11692.6576426798</v>
       </c>
       <c r="GV5" t="n">
-        <v>11706.0180306841</v>
+        <v>11703.4827221476</v>
       </c>
       <c r="GW5" t="n">
-        <v>11713.0180386591</v>
+        <v>11710.5805613821</v>
       </c>
       <c r="GX5" t="n">
-        <v>11721.1932912602</v>
+        <v>11718.5064472298</v>
       </c>
       <c r="GY5" t="n">
-        <v>11733.6428312021</v>
+        <v>11730.3417032552</v>
       </c>
       <c r="GZ5" t="n">
-        <v>11751.4011714731</v>
+        <v>11747.1419374484</v>
       </c>
       <c r="HA5" t="n">
-        <v>11775.3024123925</v>
+        <v>11769.7904450261</v>
       </c>
       <c r="HB5" t="n">
-        <v>11805.4752083929</v>
+        <v>11798.475990597</v>
       </c>
       <c r="HC5" t="n">
-        <v>11841.2308835161</v>
+        <v>11832.5732148008</v>
       </c>
       <c r="HD5" t="n">
-        <v>11880.7432950483</v>
+        <v>11870.3181692942</v>
       </c>
       <c r="HE5" t="n">
-        <v>11923.761590173</v>
+        <v>11911.5043614163</v>
       </c>
       <c r="HF5" t="n">
-        <v>11970.1355033</v>
+        <v>11956.0172766686</v>
       </c>
       <c r="HG5" t="n">
-        <v>12019.3401639679</v>
+        <v>12003.3577031778</v>
       </c>
       <c r="HH5" t="n">
-        <v>12070.4145848995</v>
+        <v>12052.5791457193</v>
       </c>
       <c r="HI5" t="n">
-        <v>12123.3112689655</v>
+        <v>12103.6452631651</v>
       </c>
       <c r="HJ5" t="n">
-        <v>12178.5421496327</v>
+        <v>12157.0718262165</v>
       </c>
       <c r="HK5" t="n">
-        <v>12236.0000766274</v>
+        <v>12212.7577579685</v>
       </c>
       <c r="HL5" t="n">
-        <v>12294.5783665498</v>
+        <v>12269.603491464</v>
       </c>
       <c r="HM5" t="n">
-        <v>12354.1429609369</v>
+        <v>12327.4821607602</v>
       </c>
       <c r="HN5" t="n">
-        <v>12414.7075404538</v>
+        <v>12386.4131066298</v>
       </c>
       <c r="HO5" t="n">
-        <v>12475.8917537571</v>
+        <v>12446.0203101743</v>
       </c>
       <c r="HP5" t="n">
-        <v>12536.4520270202</v>
+        <v>12505.0641169359</v>
       </c>
       <c r="HQ5" t="n">
-        <v>12596.2379808164</v>
+        <v>12563.3952242391</v>
       </c>
       <c r="HR5" t="n">
-        <v>12655.6516167146</v>
+        <v>12621.413138583</v>
       </c>
       <c r="HS5" t="n">
-        <v>12714.6928738692</v>
+        <v>12679.112320851</v>
       </c>
       <c r="HT5" t="n">
-        <v>12772.0991745361</v>
+        <v>12735.2260325467</v>
       </c>
       <c r="HU5" t="n">
-        <v>12828.3823314982</v>
+        <v>12790.2554181526</v>
       </c>
     </row>
     <row r="6">
@@ -6845,136 +6845,136 @@
         <v>-20.3573504657543</v>
       </c>
       <c r="GD8" t="n">
-        <v>-90.2267479940783</v>
+        <v>-90.0759339011565</v>
       </c>
       <c r="GE8" t="n">
-        <v>1300.15462170143</v>
+        <v>1283.86181475656</v>
       </c>
       <c r="GF8" t="n">
-        <v>750.115392416599</v>
+        <v>750.238097339461</v>
       </c>
       <c r="GG8" t="n">
-        <v>1622.84160629017</v>
+        <v>1613.00181133728</v>
       </c>
       <c r="GH8" t="n">
-        <v>1388.8628626205</v>
+        <v>1387.08059932239</v>
       </c>
       <c r="GI8" t="n">
-        <v>1542.66794645082</v>
+        <v>1538.35912363903</v>
       </c>
       <c r="GJ8" t="n">
-        <v>1504.82924508708</v>
+        <v>1502.44466556777</v>
       </c>
       <c r="GK8" t="n">
-        <v>1448.01765096173</v>
+        <v>1444.33137693201</v>
       </c>
       <c r="GL8" t="n">
-        <v>1438.90366547572</v>
+        <v>1434.62482067631</v>
       </c>
       <c r="GM8" t="n">
-        <v>1405.02279910672</v>
+        <v>1398.58863633068</v>
       </c>
       <c r="GN8" t="n">
-        <v>1376.37651821572</v>
+        <v>1368.21690276757</v>
       </c>
       <c r="GO8" t="n">
-        <v>1263.83029302044</v>
+        <v>1252.61697293192</v>
       </c>
       <c r="GP8" t="n">
-        <v>1238.66427327847</v>
+        <v>1225.3734387086</v>
       </c>
       <c r="GQ8" t="n">
-        <v>1195.64946815255</v>
+        <v>1178.83980102706</v>
       </c>
       <c r="GR8" t="n">
-        <v>1131.03052656309</v>
+        <v>1111.68396726577</v>
       </c>
       <c r="GS8" t="n">
-        <v>1103.15936705007</v>
+        <v>1080.48617301864</v>
       </c>
       <c r="GT8" t="n">
-        <v>1063.84766366362</v>
+        <v>1038.39991182275</v>
       </c>
       <c r="GU8" t="n">
-        <v>1038.76479785377</v>
+        <v>1010.16694336393</v>
       </c>
       <c r="GV8" t="n">
-        <v>978.736109595862</v>
+        <v>947.386735776003</v>
       </c>
       <c r="GW8" t="n">
-        <v>967.462198686117</v>
+        <v>933.146076486271</v>
       </c>
       <c r="GX8" t="n">
-        <v>940.09269424688</v>
+        <v>903.049899964797</v>
       </c>
       <c r="GY8" t="n">
-        <v>931.674304435961</v>
+        <v>891.865317585325</v>
       </c>
       <c r="GZ8" t="n">
-        <v>903.798654529091</v>
+        <v>861.484324850491</v>
       </c>
       <c r="HA8" t="n">
-        <v>901.146797295514</v>
+        <v>856.406357147876</v>
       </c>
       <c r="HB8" t="n">
-        <v>902.067194769246</v>
+        <v>855.121311908733</v>
       </c>
       <c r="HC8" t="n">
-        <v>910.197028988012</v>
+        <v>861.122485371074</v>
       </c>
       <c r="HD8" t="n">
-        <v>866.462252061086</v>
+        <v>815.79164748246</v>
       </c>
       <c r="HE8" t="n">
-        <v>902.967870824708</v>
+        <v>850.63276718781</v>
       </c>
       <c r="HF8" t="n">
-        <v>888.612360168772</v>
+        <v>835.086489492736</v>
       </c>
       <c r="HG8" t="n">
-        <v>902.411000945605</v>
+        <v>847.787866162806</v>
       </c>
       <c r="HH8" t="n">
-        <v>887.363849451271</v>
+        <v>832.039432542748</v>
       </c>
       <c r="HI8" t="n">
-        <v>891.597340488952</v>
+        <v>835.747590565967</v>
       </c>
       <c r="HJ8" t="n">
-        <v>898.38084599236</v>
+        <v>842.205697125901</v>
       </c>
       <c r="HK8" t="n">
-        <v>905.821549456188</v>
+        <v>849.481425804785</v>
       </c>
       <c r="HL8" t="n">
-        <v>892.358530647238</v>
+        <v>836.1382355034</v>
       </c>
       <c r="HM8" t="n">
-        <v>895.498648716515</v>
+        <v>839.536183942022</v>
       </c>
       <c r="HN8" t="n">
-        <v>900.192167421861</v>
+        <v>844.603408431372</v>
       </c>
       <c r="HO8" t="n">
-        <v>904.466481614683</v>
+        <v>849.35250752233</v>
       </c>
       <c r="HP8" t="n">
-        <v>886.597161710175</v>
+        <v>832.194262148754</v>
       </c>
       <c r="HQ8" t="n">
-        <v>882.962042668223</v>
+        <v>829.356615165394</v>
       </c>
       <c r="HR8" t="n">
-        <v>882.816958072741</v>
+        <v>830.044123144442</v>
       </c>
       <c r="HS8" t="n">
-        <v>881.896000223991</v>
+        <v>829.989692996809</v>
       </c>
       <c r="HT8" t="n">
-        <v>809.527682348329</v>
+        <v>758.936917471554</v>
       </c>
       <c r="HU8" t="n">
-        <v>836.217220947088</v>
+        <v>786.536246196076</v>
       </c>
     </row>
     <row r="9">
@@ -8214,139 +8214,139 @@
         <v>680205</v>
       </c>
       <c r="GC10" t="n">
-        <v>686151.698852727</v>
+        <v>686130.388292905</v>
       </c>
       <c r="GD10" t="n">
-        <v>694469.036883562</v>
+        <v>694123.931954122</v>
       </c>
       <c r="GE10" t="n">
-        <v>701634.083472192</v>
+        <v>701330.195912389</v>
       </c>
       <c r="GF10" t="n">
-        <v>707838.193632049</v>
+        <v>707446.366820035</v>
       </c>
       <c r="GG10" t="n">
-        <v>714453.26169773</v>
+        <v>714089.518561653</v>
       </c>
       <c r="GH10" t="n">
-        <v>719156.513545823</v>
+        <v>718799.253714875</v>
       </c>
       <c r="GI10" t="n">
-        <v>723584.949902403</v>
+        <v>723246.573398806</v>
       </c>
       <c r="GJ10" t="n">
-        <v>727300.586670054</v>
+        <v>726964.811189347</v>
       </c>
       <c r="GK10" t="n">
-        <v>731077.234734782</v>
+        <v>730735.341269051</v>
       </c>
       <c r="GL10" t="n">
-        <v>735084.969169306</v>
+        <v>734713.803829733</v>
       </c>
       <c r="GM10" t="n">
-        <v>738943.676090391</v>
+        <v>738534.837917606</v>
       </c>
       <c r="GN10" t="n">
-        <v>742061.275634361</v>
+        <v>741589.182168337</v>
       </c>
       <c r="GO10" t="n">
-        <v>745200.995385216</v>
+        <v>744664.200964413</v>
       </c>
       <c r="GP10" t="n">
-        <v>748718.239446365</v>
+        <v>748094.596225114</v>
       </c>
       <c r="GQ10" t="n">
-        <v>751936.576306462</v>
+        <v>751224.332925385</v>
       </c>
       <c r="GR10" t="n">
-        <v>755352.396752883</v>
+        <v>754540.274047451</v>
       </c>
       <c r="GS10" t="n">
-        <v>758940.218088405</v>
+        <v>758026.372730235</v>
       </c>
       <c r="GT10" t="n">
-        <v>762671.887069446</v>
+        <v>761649.892886924</v>
       </c>
       <c r="GU10" t="n">
-        <v>766145.600242602</v>
+        <v>765015.189610289</v>
       </c>
       <c r="GV10" t="n">
-        <v>769744.053934945</v>
+        <v>768500.87166757</v>
       </c>
       <c r="GW10" t="n">
-        <v>773611.605291337</v>
+        <v>772254.050240332</v>
       </c>
       <c r="GX10" t="n">
-        <v>777666.857291188</v>
+        <v>776192.323704298</v>
       </c>
       <c r="GY10" t="n">
-        <v>781563.220227576</v>
+        <v>779971.94028594</v>
       </c>
       <c r="GZ10" t="n">
-        <v>785659.281281269</v>
+        <v>783950.886785687</v>
       </c>
       <c r="HA10" t="n">
-        <v>790022.80197013</v>
+        <v>788198.342666767</v>
       </c>
       <c r="HB10" t="n">
-        <v>794604.299914567</v>
+        <v>792663.786272314</v>
       </c>
       <c r="HC10" t="n">
-        <v>798873.089997532</v>
+        <v>796822.488683259</v>
       </c>
       <c r="HD10" t="n">
-        <v>803277.304166793</v>
+        <v>801117.846618793</v>
       </c>
       <c r="HE10" t="n">
-        <v>807893.321810608</v>
+        <v>805629.814584663</v>
       </c>
       <c r="HF10" t="n">
-        <v>812539.415867795</v>
+        <v>810175.733537357</v>
       </c>
       <c r="HG10" t="n">
-        <v>816868.5425642</v>
+        <v>814410.274255052</v>
       </c>
       <c r="HH10" t="n">
-        <v>821184.553937992</v>
+        <v>818636.161412883</v>
       </c>
       <c r="HI10" t="n">
-        <v>825626.772773588</v>
+        <v>822992.236445759</v>
       </c>
       <c r="HJ10" t="n">
-        <v>830109.659889168</v>
+        <v>827392.556382648</v>
       </c>
       <c r="HK10" t="n">
-        <v>834204.464656314</v>
+        <v>831409.30810803</v>
       </c>
       <c r="HL10" t="n">
-        <v>838288.076071553</v>
+        <v>835418.081067445</v>
       </c>
       <c r="HM10" t="n">
-        <v>842471.63458907</v>
+        <v>839529.457526661</v>
       </c>
       <c r="HN10" t="n">
-        <v>846673.325876528</v>
+        <v>843661.182589545</v>
       </c>
       <c r="HO10" t="n">
-        <v>850455.689915724</v>
+        <v>847376.724668062</v>
       </c>
       <c r="HP10" t="n">
-        <v>854171.453433004</v>
+        <v>851027.664308335</v>
       </c>
       <c r="HQ10" t="n">
-        <v>857989.739047625</v>
+        <v>854782.4247462</v>
       </c>
       <c r="HR10" t="n">
-        <v>861833.759238553</v>
+        <v>858563.84038523</v>
       </c>
       <c r="HS10" t="n">
-        <v>865146.575762966</v>
+        <v>861816.608105436</v>
       </c>
       <c r="HT10" t="n">
-        <v>868437.579119187</v>
+        <v>865048.02161228</v>
       </c>
       <c r="HU10" t="n">
-        <v>871903.390698837</v>
+        <v>868454.063864541</v>
       </c>
     </row>
     <row r="11">
@@ -8903,139 +8903,139 @@
         <v>170963</v>
       </c>
       <c r="GC11" t="n">
-        <v>167271.04624954</v>
+        <v>167287.8406755</v>
       </c>
       <c r="GD11" t="n">
-        <v>176031.075688852</v>
+        <v>176028.608526147</v>
       </c>
       <c r="GE11" t="n">
-        <v>170865.182392949</v>
+        <v>170895.291288516</v>
       </c>
       <c r="GF11" t="n">
-        <v>176644.965636167</v>
+        <v>176676.351790996</v>
       </c>
       <c r="GG11" t="n">
-        <v>176200.88436541</v>
+        <v>176249.481114534</v>
       </c>
       <c r="GH11" t="n">
-        <v>177377.736407335</v>
+        <v>177436.967474815</v>
       </c>
       <c r="GI11" t="n">
-        <v>178151.712771635</v>
+        <v>178221.622328201</v>
       </c>
       <c r="GJ11" t="n">
-        <v>178261.754945155</v>
+        <v>178338.930059092</v>
       </c>
       <c r="GK11" t="n">
-        <v>178815.627130239</v>
+        <v>178897.241361745</v>
       </c>
       <c r="GL11" t="n">
-        <v>179257.031766782</v>
+        <v>179339.283427159</v>
       </c>
       <c r="GM11" t="n">
-        <v>180016.825932788</v>
+        <v>180096.906778716</v>
       </c>
       <c r="GN11" t="n">
-        <v>179978.181362474</v>
+        <v>180053.033957221</v>
       </c>
       <c r="GO11" t="n">
-        <v>180405.008143558</v>
+        <v>180472.710664317</v>
       </c>
       <c r="GP11" t="n">
-        <v>180741.978619332</v>
+        <v>180798.671087506</v>
       </c>
       <c r="GQ11" t="n">
-        <v>180938.133336089</v>
+        <v>180982.189845958</v>
       </c>
       <c r="GR11" t="n">
-        <v>181250.524942348</v>
+        <v>181279.057703492</v>
       </c>
       <c r="GS11" t="n">
-        <v>181484.448050463</v>
+        <v>181495.715523276</v>
       </c>
       <c r="GT11" t="n">
-        <v>181758.469928563</v>
+        <v>181750.002045299</v>
       </c>
       <c r="GU11" t="n">
-        <v>181806.108411248</v>
+        <v>181776.380238549</v>
       </c>
       <c r="GV11" t="n">
-        <v>182121.450496848</v>
+        <v>182068.093841855</v>
       </c>
       <c r="GW11" t="n">
-        <v>182287.604670782</v>
+        <v>182209.111495653</v>
       </c>
       <c r="GX11" t="n">
-        <v>182526.076257147</v>
+        <v>182420.530557358</v>
       </c>
       <c r="GY11" t="n">
-        <v>182726.345847796</v>
+        <v>182592.262190969</v>
       </c>
       <c r="GZ11" t="n">
-        <v>182973.490077899</v>
+        <v>182809.315329328</v>
       </c>
       <c r="HA11" t="n">
-        <v>183242.679855626</v>
+        <v>183047.097514119</v>
       </c>
       <c r="HB11" t="n">
-        <v>183546.982989212</v>
+        <v>183318.395360838</v>
       </c>
       <c r="HC11" t="n">
-        <v>183443.217241549</v>
+        <v>183181.696419935</v>
       </c>
       <c r="HD11" t="n">
-        <v>183930.94573068</v>
+        <v>183633.957620699</v>
       </c>
       <c r="HE11" t="n">
-        <v>184060.468218081</v>
+        <v>183728.199948979</v>
       </c>
       <c r="HF11" t="n">
-        <v>184317.628507436</v>
+        <v>183948.890307</v>
       </c>
       <c r="HG11" t="n">
-        <v>184540.729106543</v>
+        <v>184134.932596503</v>
       </c>
       <c r="HH11" t="n">
-        <v>184798.479666928</v>
+        <v>184354.91088314</v>
       </c>
       <c r="HI11" t="n">
-        <v>185086.010358062</v>
+        <v>184603.980810015</v>
       </c>
       <c r="HJ11" t="n">
-        <v>185395.630178871</v>
+        <v>184874.444065138</v>
       </c>
       <c r="HK11" t="n">
-        <v>185691.92571223</v>
+        <v>185131.049588737</v>
       </c>
       <c r="HL11" t="n">
-        <v>186014.436252772</v>
+        <v>185413.309128548</v>
       </c>
       <c r="HM11" t="n">
-        <v>186363.765692636</v>
+        <v>185721.780882848</v>
       </c>
       <c r="HN11" t="n">
-        <v>186730.3119674</v>
+        <v>186046.852960098</v>
       </c>
       <c r="HO11" t="n">
-        <v>187078.793639832</v>
+        <v>186353.418745367</v>
       </c>
       <c r="HP11" t="n">
-        <v>187446.061223724</v>
+        <v>186678.300831718</v>
       </c>
       <c r="HQ11" t="n">
-        <v>187838.127382192</v>
+        <v>187027.41845733</v>
       </c>
       <c r="HR11" t="n">
-        <v>188244.70788512</v>
+        <v>187390.472397357</v>
       </c>
       <c r="HS11" t="n">
-        <v>188027.033714589</v>
+        <v>187132.690573497</v>
       </c>
       <c r="HT11" t="n">
-        <v>188557.0582645</v>
+        <v>187617.69402097</v>
       </c>
       <c r="HU11" t="n">
-        <v>188598.578599589</v>
+        <v>187617.097553214</v>
       </c>
     </row>
     <row r="12">
@@ -9592,139 +9592,139 @@
         <v>162177</v>
       </c>
       <c r="GC12" t="n">
-        <v>164127.999631347</v>
+        <v>164121.411935033</v>
       </c>
       <c r="GD12" t="n">
-        <v>166239.284723838</v>
+        <v>166117.728343011</v>
       </c>
       <c r="GE12" t="n">
-        <v>167937.23219837</v>
+        <v>167790.444828236</v>
       </c>
       <c r="GF12" t="n">
-        <v>169303.160251793</v>
+        <v>169139.804903508</v>
       </c>
       <c r="GG12" t="n">
-        <v>170725.438403386</v>
+        <v>170571.028589492</v>
       </c>
       <c r="GH12" t="n">
-        <v>171680.898290774</v>
+        <v>171549.476908179</v>
       </c>
       <c r="GI12" t="n">
-        <v>172317.179039621</v>
+        <v>172212.20872938</v>
       </c>
       <c r="GJ12" t="n">
-        <v>172682.899272737</v>
+        <v>172604.146530576</v>
       </c>
       <c r="GK12" t="n">
-        <v>173114.338495252</v>
+        <v>173058.848183035</v>
       </c>
       <c r="GL12" t="n">
-        <v>173789.024184772</v>
+        <v>173751.07238465</v>
       </c>
       <c r="GM12" t="n">
-        <v>174742.115904171</v>
+        <v>174719.029325649</v>
       </c>
       <c r="GN12" t="n">
-        <v>175369.851707981</v>
+        <v>175355.65955725</v>
       </c>
       <c r="GO12" t="n">
-        <v>176004.79101067</v>
+        <v>175999.036054163</v>
       </c>
       <c r="GP12" t="n">
-        <v>176870.730218012</v>
+        <v>176870.397181691</v>
       </c>
       <c r="GQ12" t="n">
-        <v>177791.069426114</v>
+        <v>177797.083840841</v>
       </c>
       <c r="GR12" t="n">
-        <v>178811.853907665</v>
+        <v>178825.290774572</v>
       </c>
       <c r="GS12" t="n">
-        <v>180002.21481667</v>
+        <v>180026.124928434</v>
       </c>
       <c r="GT12" t="n">
-        <v>181339.807666797</v>
+        <v>181377.095052725</v>
       </c>
       <c r="GU12" t="n">
-        <v>182679.734831497</v>
+        <v>182734.500957596</v>
       </c>
       <c r="GV12" t="n">
-        <v>184079.125051405</v>
+        <v>184154.795852241</v>
       </c>
       <c r="GW12" t="n">
-        <v>185634.647045657</v>
+        <v>185735.051058505</v>
       </c>
       <c r="GX12" t="n">
-        <v>187330.210966362</v>
+        <v>187458.930949901</v>
       </c>
       <c r="GY12" t="n">
-        <v>189027.074170939</v>
+        <v>189187.856798074</v>
       </c>
       <c r="GZ12" t="n">
-        <v>190786.824513089</v>
+        <v>190983.378321472</v>
       </c>
       <c r="HA12" t="n">
-        <v>192675.659664138</v>
+        <v>192911.883133129</v>
       </c>
       <c r="HB12" t="n">
-        <v>194683.920647423</v>
+        <v>194962.966695847</v>
       </c>
       <c r="HC12" t="n">
-        <v>196612.082524768</v>
+        <v>196938.016329644</v>
       </c>
       <c r="HD12" t="n">
-        <v>198531.44280393</v>
+        <v>198906.926270174</v>
       </c>
       <c r="HE12" t="n">
-        <v>200530.244449268</v>
+        <v>200958.584912856</v>
       </c>
       <c r="HF12" t="n">
-        <v>202553.034622749</v>
+        <v>203036.898681978</v>
       </c>
       <c r="HG12" t="n">
-        <v>204450.972274439</v>
+        <v>204992.144039156</v>
       </c>
       <c r="HH12" t="n">
-        <v>206276.578463262</v>
+        <v>206876.372529804</v>
       </c>
       <c r="HI12" t="n">
-        <v>208126.567883317</v>
+        <v>208785.964015499</v>
       </c>
       <c r="HJ12" t="n">
-        <v>209991.699844028</v>
+        <v>210710.973570084</v>
       </c>
       <c r="HK12" t="n">
-        <v>211710.894059617</v>
+        <v>212489.06345431</v>
       </c>
       <c r="HL12" t="n">
-        <v>213353.146290048</v>
+        <v>214188.900057864</v>
       </c>
       <c r="HM12" t="n">
-        <v>215021.366628337</v>
+        <v>215913.339169994</v>
       </c>
       <c r="HN12" t="n">
-        <v>216705.657693303</v>
+        <v>217651.898803033</v>
       </c>
       <c r="HO12" t="n">
-        <v>218242.221774699</v>
+        <v>219239.496876667</v>
       </c>
       <c r="HP12" t="n">
-        <v>219693.469288297</v>
+        <v>220738.48988957</v>
       </c>
       <c r="HQ12" t="n">
-        <v>221179.430970478</v>
+        <v>222269.292049267</v>
       </c>
       <c r="HR12" t="n">
-        <v>222700.394992835</v>
+        <v>223831.879388473</v>
       </c>
       <c r="HS12" t="n">
-        <v>224050.959990048</v>
+        <v>225219.764186373</v>
       </c>
       <c r="HT12" t="n">
-        <v>225329.288315607</v>
+        <v>226530.980192166</v>
       </c>
       <c r="HU12" t="n">
-        <v>226690.202253854</v>
+        <v>227921.528468876</v>
       </c>
     </row>
     <row r="13">
@@ -10281,139 +10281,139 @@
         <v>688271</v>
       </c>
       <c r="GC13" t="n">
-        <v>688864.763365476</v>
+        <v>688866.834437336</v>
       </c>
       <c r="GD13" t="n">
-        <v>703830.849541404</v>
+        <v>703604.834099491</v>
       </c>
       <c r="GE13" t="n">
-        <v>704132.055973531</v>
+        <v>704005.064952184</v>
       </c>
       <c r="GF13" t="n">
-        <v>714750.021550599</v>
+        <v>714552.936601672</v>
       </c>
       <c r="GG13" t="n">
-        <v>719498.731651568</v>
+        <v>719337.993500757</v>
       </c>
       <c r="GH13" t="n">
-        <v>724423.373951321</v>
+        <v>724256.766959714</v>
       </c>
       <c r="GI13" t="n">
-        <v>728989.50756209</v>
+        <v>728826.009338396</v>
       </c>
       <c r="GJ13" t="n">
-        <v>732449.466062963</v>
+        <v>732269.616815641</v>
       </c>
       <c r="GK13" t="n">
-        <v>736348.546599943</v>
+        <v>736143.75793828</v>
       </c>
       <c r="GL13" t="n">
-        <v>740122.999509897</v>
+        <v>739872.03783298</v>
       </c>
       <c r="GM13" t="n">
-        <v>743788.408478161</v>
+        <v>743482.737877553</v>
       </c>
       <c r="GN13" t="n">
-        <v>746239.627684222</v>
+        <v>745856.57904107</v>
       </c>
       <c r="GO13" t="n">
-        <v>749171.236813848</v>
+        <v>748707.897906413</v>
       </c>
       <c r="GP13" t="n">
-        <v>752159.511901959</v>
+        <v>751592.894140744</v>
       </c>
       <c r="GQ13" t="n">
-        <v>754653.664058429</v>
+        <v>753979.462689626</v>
       </c>
       <c r="GR13" t="n">
-        <v>757361.091150985</v>
+        <v>756564.064240828</v>
       </c>
       <c r="GS13" t="n">
-        <v>759992.474158724</v>
+        <v>759065.98605977</v>
       </c>
       <c r="GT13" t="n">
-        <v>762660.573421252</v>
+        <v>761592.823866241</v>
       </c>
       <c r="GU13" t="n">
-        <v>764841.997207891</v>
+        <v>763627.092196222</v>
       </c>
       <c r="GV13" t="n">
-        <v>767356.403800925</v>
+        <v>765984.194020966</v>
       </c>
       <c r="GW13" t="n">
-        <v>769834.586226534</v>
+        <v>768298.133975158</v>
       </c>
       <c r="GX13" t="n">
-        <v>772432.746528149</v>
+        <v>770723.947290241</v>
       </c>
       <c r="GY13" t="n">
-        <v>774832.516351579</v>
+        <v>772946.37021075</v>
       </c>
       <c r="GZ13" t="n">
-        <v>777415.971487319</v>
+        <v>775346.848578081</v>
       </c>
       <c r="HA13" t="n">
-        <v>780159.846770841</v>
+        <v>777903.581862182</v>
       </c>
       <c r="HB13" t="n">
-        <v>783037.388631817</v>
+        <v>780589.239487958</v>
       </c>
       <c r="HC13" t="n">
-        <v>785274.250833356</v>
+        <v>782636.19523891</v>
       </c>
       <c r="HD13" t="n">
-        <v>788246.832465388</v>
+        <v>785414.903749895</v>
       </c>
       <c r="HE13" t="n">
-        <v>790993.572295875</v>
+        <v>787969.456827305</v>
       </c>
       <c r="HF13" t="n">
-        <v>793874.035443795</v>
+        <v>790657.75139772</v>
       </c>
       <c r="HG13" t="n">
-        <v>796528.326217336</v>
+        <v>793123.090245786</v>
       </c>
       <c r="HH13" t="n">
-        <v>799276.483087589</v>
+        <v>795684.726125681</v>
       </c>
       <c r="HI13" t="n">
-        <v>802156.241893817</v>
+        <v>798380.280612548</v>
       </c>
       <c r="HJ13" t="n">
-        <v>805083.617746983</v>
+        <v>801126.055199086</v>
       </c>
       <c r="HK13" t="n">
-        <v>807755.524762415</v>
+        <v>803621.323560566</v>
       </c>
       <c r="HL13" t="n">
-        <v>810519.395333347</v>
+        <v>806212.517921321</v>
       </c>
       <c r="HM13" t="n">
-        <v>813384.061322275</v>
+        <v>808907.927836385</v>
       </c>
       <c r="HN13" t="n">
-        <v>816268.008533543</v>
+        <v>811626.16610836</v>
       </c>
       <c r="HO13" t="n">
-        <v>818862.290973044</v>
+        <v>814060.676762744</v>
       </c>
       <c r="HP13" t="n">
-        <v>821494.075480425</v>
+        <v>816537.503885304</v>
       </c>
       <c r="HQ13" t="n">
-        <v>824218.466451323</v>
+        <v>819110.580630811</v>
       </c>
       <c r="HR13" t="n">
-        <v>826948.101349064</v>
+        <v>821692.463706748</v>
       </c>
       <c r="HS13" t="n">
-        <v>828692.680043875</v>
+        <v>823299.566182623</v>
       </c>
       <c r="HT13" t="n">
-        <v>831235.380713444</v>
+        <v>825704.765540611</v>
       </c>
       <c r="HU13" t="n">
-        <v>833381.797246681</v>
+        <v>827719.664282396</v>
       </c>
     </row>
     <row r="14">
@@ -10802,139 +10802,139 @@
         <v>681761</v>
       </c>
       <c r="GC14" t="n">
-        <v>686013.11007783</v>
+        <v>685991.791043501</v>
       </c>
       <c r="GD14" t="n">
-        <v>694400.273339925</v>
+        <v>694055.018363493</v>
       </c>
       <c r="GE14" t="n">
-        <v>700174.941868718</v>
+        <v>699887.347689977</v>
       </c>
       <c r="GF14" t="n">
-        <v>706929.08837905</v>
+        <v>706537.139488966</v>
       </c>
       <c r="GG14" t="n">
-        <v>712671.431721161</v>
+        <v>712317.527750436</v>
       </c>
       <c r="GH14" t="n">
-        <v>717608.661521473</v>
+        <v>717253.184551191</v>
       </c>
       <c r="GI14" t="n">
-        <v>721883.294094862</v>
+        <v>721549.225771469</v>
       </c>
       <c r="GJ14" t="n">
-        <v>725636.769472873</v>
+        <v>725303.377919799</v>
       </c>
       <c r="GK14" t="n">
-        <v>729470.228738231</v>
+        <v>729132.022139139</v>
       </c>
       <c r="GL14" t="n">
-        <v>733487.076791055</v>
+        <v>733120.190865349</v>
       </c>
       <c r="GM14" t="n">
-        <v>737379.664499617</v>
+        <v>736977.261021407</v>
       </c>
       <c r="GN14" t="n">
-        <v>740525.910128077</v>
+        <v>740061.976762008</v>
       </c>
       <c r="GO14" t="n">
-        <v>743778.177184336</v>
+        <v>743252.595195788</v>
       </c>
       <c r="GP14" t="n">
-        <v>747320.587009481</v>
+        <v>746710.235007898</v>
       </c>
       <c r="GQ14" t="n">
-        <v>750581.938590191</v>
+        <v>749886.505202338</v>
       </c>
       <c r="GR14" t="n">
-        <v>754062.377734088</v>
+        <v>753269.601873048</v>
       </c>
       <c r="GS14" t="n">
-        <v>757678.069993888</v>
+        <v>756786.898085005</v>
       </c>
       <c r="GT14" t="n">
-        <v>761449.051698472</v>
+        <v>760452.50550832</v>
       </c>
       <c r="GU14" t="n">
-        <v>764947.847483137</v>
+        <v>763846.034939334</v>
       </c>
       <c r="GV14" t="n">
-        <v>768606.330817403</v>
+        <v>767394.498167388</v>
       </c>
       <c r="GW14" t="n">
-        <v>772485.155433547</v>
+        <v>771161.916771051</v>
       </c>
       <c r="GX14" t="n">
-        <v>776567.777495093</v>
+        <v>775130.287005242</v>
       </c>
       <c r="GY14" t="n">
-        <v>780472.55928982</v>
+        <v>778921.088682289</v>
       </c>
       <c r="GZ14" t="n">
-        <v>784596.496154962</v>
+        <v>782930.416389031</v>
       </c>
       <c r="HA14" t="n">
-        <v>788962.668596715</v>
+        <v>787182.950190867</v>
       </c>
       <c r="HB14" t="n">
-        <v>793543.247259735</v>
+        <v>791649.678470892</v>
       </c>
       <c r="HC14" t="n">
-        <v>797803.907197669</v>
+        <v>795802.381023361</v>
       </c>
       <c r="HD14" t="n">
-        <v>802251.855345938</v>
+        <v>800143.069053169</v>
       </c>
       <c r="HE14" t="n">
-        <v>806831.368070138</v>
+        <v>804620.196678336</v>
       </c>
       <c r="HF14" t="n">
-        <v>811491.816602069</v>
+        <v>809181.660911197</v>
       </c>
       <c r="HG14" t="n">
-        <v>815807.145161518</v>
+        <v>813403.500838375</v>
       </c>
       <c r="HH14" t="n">
-        <v>820138.204054042</v>
+        <v>817645.135263155</v>
       </c>
       <c r="HI14" t="n">
-        <v>824576.188060757</v>
+        <v>821997.502411545</v>
       </c>
       <c r="HJ14" t="n">
-        <v>829052.291779703</v>
+        <v>826391.364404439</v>
       </c>
       <c r="HK14" t="n">
-        <v>833139.656026412</v>
+        <v>830400.840635878</v>
       </c>
       <c r="HL14" t="n">
-        <v>837236.730596195</v>
+        <v>834422.955365071</v>
       </c>
       <c r="HM14" t="n">
-        <v>841417.147488091</v>
+        <v>838530.933944782</v>
       </c>
       <c r="HN14" t="n">
-        <v>845614.145253391</v>
+        <v>842657.591811736</v>
       </c>
       <c r="HO14" t="n">
-        <v>849392.235114475</v>
+        <v>846368.38494938</v>
       </c>
       <c r="HP14" t="n">
-        <v>853125.868150218</v>
+        <v>850036.481487656</v>
       </c>
       <c r="HQ14" t="n">
-        <v>856947.78906021</v>
+        <v>853794.079735351</v>
       </c>
       <c r="HR14" t="n">
-        <v>860791.952897155</v>
+        <v>857574.807977382</v>
       </c>
       <c r="HS14" t="n">
-        <v>864105.690967893</v>
+        <v>860827.630737255</v>
       </c>
       <c r="HT14" t="n">
-        <v>867469.063065328</v>
+        <v>864130.095852412</v>
       </c>
       <c r="HU14" t="n">
-        <v>870908.184036271</v>
+        <v>867508.539246715</v>
       </c>
     </row>
     <row r="15">
@@ -11491,139 +11491,139 @@
         <v>718591</v>
       </c>
       <c r="GC15" t="n">
-        <v>722446.302044982</v>
+        <v>722465.949587139</v>
       </c>
       <c r="GD15" t="n">
-        <v>746841.514130855</v>
+        <v>746181.017728034</v>
       </c>
       <c r="GE15" t="n">
-        <v>757812.555736813</v>
+        <v>757754.677230078</v>
       </c>
       <c r="GF15" t="n">
-        <v>778371.835098437</v>
+        <v>778154.727028813</v>
       </c>
       <c r="GG15" t="n">
-        <v>793842.402508656</v>
+        <v>793998.240851665</v>
       </c>
       <c r="GH15" t="n">
-        <v>807990.76667608</v>
+        <v>808487.251754077</v>
       </c>
       <c r="GI15" t="n">
-        <v>821810.431307194</v>
+        <v>822675.202475851</v>
       </c>
       <c r="GJ15" t="n">
-        <v>834703.713428229</v>
+        <v>835914.927649359</v>
       </c>
       <c r="GK15" t="n">
-        <v>848043.203545536</v>
+        <v>849589.245250948</v>
       </c>
       <c r="GL15" t="n">
-        <v>861102.643061212</v>
+        <v>862977.320864642</v>
       </c>
       <c r="GM15" t="n">
-        <v>873597.576005307</v>
+        <v>875811.629631768</v>
       </c>
       <c r="GN15" t="n">
-        <v>885059.330973302</v>
+        <v>887542.565981364</v>
       </c>
       <c r="GO15" t="n">
-        <v>897019.261789473</v>
+        <v>899743.539305915</v>
       </c>
       <c r="GP15" t="n">
-        <v>909164.943793132</v>
+        <v>912095.44884515</v>
       </c>
       <c r="GQ15" t="n">
-        <v>920700.640142711</v>
+        <v>923823.061888901</v>
       </c>
       <c r="GR15" t="n">
-        <v>932467.546592016</v>
+        <v>935745.519103922</v>
       </c>
       <c r="GS15" t="n">
-        <v>944155.41308597</v>
+        <v>947570.887432621</v>
       </c>
       <c r="GT15" t="n">
-        <v>955984.012273151</v>
+        <v>959506.139166591</v>
       </c>
       <c r="GU15" t="n">
-        <v>967288.147110588</v>
+        <v>970900.106436179</v>
       </c>
       <c r="GV15" t="n">
-        <v>978997.284240044</v>
+        <v>982665.921934762</v>
       </c>
       <c r="GW15" t="n">
-        <v>990789.867259504</v>
+        <v>994497.890951462</v>
       </c>
       <c r="GX15" t="n">
-        <v>1002845.58366263</v>
+        <v>1006569.01947697</v>
       </c>
       <c r="GY15" t="n">
-        <v>1014757.88587424</v>
+        <v>1018478.23916277</v>
       </c>
       <c r="GZ15" t="n">
-        <v>1027039.49883388</v>
+        <v>1030737.92397927</v>
       </c>
       <c r="HA15" t="n">
-        <v>1039691.65244991</v>
+        <v>1043353.01808655</v>
       </c>
       <c r="HB15" t="n">
-        <v>1052952.94669761</v>
+        <v>1056555.96821226</v>
       </c>
       <c r="HC15" t="n">
-        <v>1065661.62821555</v>
+        <v>1069206.08627052</v>
       </c>
       <c r="HD15" t="n">
-        <v>1079358.52131661</v>
+        <v>1082818.26008875</v>
       </c>
       <c r="HE15" t="n">
-        <v>1093109.6103393</v>
+        <v>1096486.54863624</v>
       </c>
       <c r="HF15" t="n">
-        <v>1107234.2075451</v>
+        <v>1110518.25366374</v>
       </c>
       <c r="HG15" t="n">
-        <v>1121256.68895134</v>
+        <v>1124442.90325998</v>
       </c>
       <c r="HH15" t="n">
-        <v>1135620.57354751</v>
+        <v>1138703.5886623</v>
       </c>
       <c r="HI15" t="n">
-        <v>1150398.95823496</v>
+        <v>1153375.20589264</v>
       </c>
       <c r="HJ15" t="n">
-        <v>1165479.96903339</v>
+        <v>1168346.54163771</v>
       </c>
       <c r="HK15" t="n">
-        <v>1180401.49840334</v>
+        <v>1183156.66758373</v>
       </c>
       <c r="HL15" t="n">
-        <v>1195675.87219166</v>
+        <v>1198317.7352477</v>
       </c>
       <c r="HM15" t="n">
-        <v>1211331.22749581</v>
+        <v>1213859.23120743</v>
       </c>
       <c r="HN15" t="n">
-        <v>1227252.81079942</v>
+        <v>1229666.74742651</v>
       </c>
       <c r="HO15" t="n">
-        <v>1242945.33460305</v>
+        <v>1245245.94134398</v>
       </c>
       <c r="HP15" t="n">
-        <v>1258900.15294271</v>
+        <v>1261087.84410499</v>
       </c>
       <c r="HQ15" t="n">
-        <v>1275221.73001482</v>
+        <v>1277297.22856201</v>
       </c>
       <c r="HR15" t="n">
-        <v>1291783.46818958</v>
+        <v>1293747.63565143</v>
       </c>
       <c r="HS15" t="n">
-        <v>1307274.1681537</v>
+        <v>1309144.37751116</v>
       </c>
       <c r="HT15" t="n">
-        <v>1323868.70657816</v>
+        <v>1325627.40889273</v>
       </c>
       <c r="HU15" t="n">
-        <v>1340281.99420086</v>
+        <v>1341942.38324988</v>
       </c>
     </row>
     <row r="16">
@@ -12180,139 +12180,139 @@
         <v>1.04405241540033</v>
       </c>
       <c r="GC16" t="n">
-        <v>1.04874901737806</v>
+        <v>1.04877443846513</v>
       </c>
       <c r="GD16" t="n">
-        <v>1.0611093729798</v>
+        <v>1.0605114968813</v>
       </c>
       <c r="GE16" t="n">
-        <v>1.07623640897724</v>
+        <v>1.07634833202215</v>
       </c>
       <c r="GF16" t="n">
-        <v>1.08901267044016</v>
+        <v>1.08900920062394</v>
       </c>
       <c r="GG16" t="n">
-        <v>1.10332702677796</v>
+        <v>1.10379021035014</v>
       </c>
       <c r="GH16" t="n">
-        <v>1.1153571090506</v>
+        <v>1.11629919471804</v>
       </c>
       <c r="GI16" t="n">
-        <v>1.12732819417645</v>
+        <v>1.12876761544896</v>
       </c>
       <c r="GJ16" t="n">
-        <v>1.13960586602919</v>
+        <v>1.1415398144616</v>
       </c>
       <c r="GK16" t="n">
-        <v>1.1516872039263</v>
+        <v>1.15410778348069</v>
       </c>
       <c r="GL16" t="n">
-        <v>1.16345882946323</v>
+        <v>1.16638725699936</v>
       </c>
       <c r="GM16" t="n">
-        <v>1.17452431627187</v>
+        <v>1.17798515164696</v>
       </c>
       <c r="GN16" t="n">
-        <v>1.18602563438089</v>
+        <v>1.18996411355285</v>
       </c>
       <c r="GO16" t="n">
-        <v>1.19734877144222</v>
+        <v>1.2017283903317</v>
       </c>
       <c r="GP16" t="n">
-        <v>1.20873954025731</v>
+        <v>1.21354985479394</v>
       </c>
       <c r="GQ16" t="n">
-        <v>1.22003070214935</v>
+        <v>1.22526289759581</v>
       </c>
       <c r="GR16" t="n">
-        <v>1.23120603548056</v>
+        <v>1.23683579876483</v>
       </c>
       <c r="GS16" t="n">
-        <v>1.24232205613546</v>
+        <v>1.2483379634755</v>
       </c>
       <c r="GT16" t="n">
-        <v>1.25348555604352</v>
+        <v>1.25986762137777</v>
       </c>
       <c r="GU16" t="n">
-        <v>1.26469015994008</v>
+        <v>1.27143224307188</v>
       </c>
       <c r="GV16" t="n">
-        <v>1.27580519368244</v>
+        <v>1.28288015638918</v>
       </c>
       <c r="GW16" t="n">
-        <v>1.28701656901135</v>
+        <v>1.29441664262318</v>
       </c>
       <c r="GX16" t="n">
-        <v>1.29829501490994</v>
+        <v>1.30600459871772</v>
       </c>
       <c r="GY16" t="n">
-        <v>1.30964803978524</v>
+        <v>1.31765705646768</v>
       </c>
       <c r="GZ16" t="n">
-        <v>1.32109390126648</v>
+        <v>1.32938945348251</v>
       </c>
       <c r="HA16" t="n">
-        <v>1.33266490942006</v>
+        <v>1.34123693596291</v>
       </c>
       <c r="HB16" t="n">
-        <v>1.34470328051064</v>
+        <v>1.35353642117406</v>
       </c>
       <c r="HC16" t="n">
-        <v>1.35705662667359</v>
+        <v>1.36615976842889</v>
       </c>
       <c r="HD16" t="n">
-        <v>1.36931538855492</v>
+        <v>1.37865763764365</v>
       </c>
       <c r="HE16" t="n">
-        <v>1.38194499184277</v>
+        <v>1.39153432135158</v>
       </c>
       <c r="HF16" t="n">
-        <v>1.39472277991461</v>
+        <v>1.40454987633027</v>
       </c>
       <c r="HG16" t="n">
-        <v>1.40767960800794</v>
+        <v>1.41774071300658</v>
       </c>
       <c r="HH16" t="n">
-        <v>1.42081068242886</v>
+        <v>1.43109895414821</v>
       </c>
       <c r="HI16" t="n">
-        <v>1.43413326291936</v>
+        <v>1.44464389113164</v>
       </c>
       <c r="HJ16" t="n">
-        <v>1.447650818095</v>
+        <v>1.45838039060894</v>
       </c>
       <c r="HK16" t="n">
-        <v>1.46133508178763</v>
+        <v>1.47228130842214</v>
       </c>
       <c r="HL16" t="n">
-        <v>1.47519709599104</v>
+        <v>1.48635464401876</v>
       </c>
       <c r="HM16" t="n">
-        <v>1.4892487691345</v>
+        <v>1.50061480747268</v>
       </c>
       <c r="HN16" t="n">
-        <v>1.50349245718103</v>
+        <v>1.51506540846529</v>
       </c>
       <c r="HO16" t="n">
-        <v>1.51789297169165</v>
+        <v>1.5296721199659</v>
       </c>
       <c r="HP16" t="n">
-        <v>1.53245187123142</v>
+        <v>1.54443343625454</v>
       </c>
       <c r="HQ16" t="n">
-        <v>1.54718895616753</v>
+        <v>1.55937090309028</v>
       </c>
       <c r="HR16" t="n">
-        <v>1.56210945251471</v>
+        <v>1.57449127055225</v>
       </c>
       <c r="HS16" t="n">
-        <v>1.57751380711848</v>
+        <v>1.59011908356432</v>
       </c>
       <c r="HT16" t="n">
-        <v>1.59265198824762</v>
+        <v>1.60544959629668</v>
       </c>
       <c r="HU16" t="n">
-        <v>1.60824483231424</v>
+        <v>1.62125223457099</v>
       </c>
     </row>
     <row r="17">
@@ -12869,139 +12869,139 @@
         <v>143.5</v>
       </c>
       <c r="GC17" t="n">
-        <v>144.861693768467</v>
+        <v>144.861825055634</v>
       </c>
       <c r="GD17" t="n">
-        <v>146.572442197292</v>
+        <v>146.567278244737</v>
       </c>
       <c r="GE17" t="n">
-        <v>148.246978513822</v>
+        <v>148.241631120265</v>
       </c>
       <c r="GF17" t="n">
-        <v>150.071786546797</v>
+        <v>150.062870020521</v>
       </c>
       <c r="GG17" t="n">
-        <v>151.922234840272</v>
+        <v>151.91321024026</v>
       </c>
       <c r="GH17" t="n">
-        <v>153.814321480111</v>
+        <v>153.807079458362</v>
       </c>
       <c r="GI17" t="n">
-        <v>155.740126563532</v>
+        <v>155.737810919236</v>
       </c>
       <c r="GJ17" t="n">
-        <v>157.671477674703</v>
+        <v>157.676999880166</v>
       </c>
       <c r="GK17" t="n">
-        <v>159.601649422809</v>
+        <v>159.6177057527</v>
       </c>
       <c r="GL17" t="n">
-        <v>161.516062273167</v>
+        <v>161.545074996623</v>
       </c>
       <c r="GM17" t="n">
-        <v>163.394667887774</v>
+        <v>163.438776337616</v>
       </c>
       <c r="GN17" t="n">
-        <v>165.242238248684</v>
+        <v>165.302610888808</v>
       </c>
       <c r="GO17" t="n">
-        <v>167.069663377946</v>
+        <v>167.147038037792</v>
       </c>
       <c r="GP17" t="n">
-        <v>168.876185743287</v>
+        <v>168.970765945683</v>
       </c>
       <c r="GQ17" t="n">
-        <v>170.659398500221</v>
+        <v>170.77115354191</v>
       </c>
       <c r="GR17" t="n">
-        <v>172.432569522716</v>
+        <v>172.561048489083</v>
       </c>
       <c r="GS17" t="n">
-        <v>174.19190425373</v>
+        <v>174.336530102246</v>
       </c>
       <c r="GT17" t="n">
-        <v>175.943644171773</v>
+        <v>176.103582601012</v>
       </c>
       <c r="GU17" t="n">
-        <v>177.685588499466</v>
+        <v>177.859926888798</v>
       </c>
       <c r="GV17" t="n">
-        <v>179.427279919219</v>
+        <v>179.614958938004</v>
       </c>
       <c r="GW17" t="n">
-        <v>181.169140085289</v>
+        <v>181.369117713858</v>
       </c>
       <c r="GX17" t="n">
-        <v>182.915188804892</v>
+        <v>183.126374965408</v>
       </c>
       <c r="GY17" t="n">
-        <v>184.665705384469</v>
+        <v>184.887022449267</v>
       </c>
       <c r="GZ17" t="n">
-        <v>186.429953402784</v>
+        <v>186.660358457495</v>
       </c>
       <c r="HA17" t="n">
-        <v>188.207223852408</v>
+        <v>188.445721695767</v>
       </c>
       <c r="HB17" t="n">
-        <v>190.002523725785</v>
+        <v>190.248135015593</v>
       </c>
       <c r="HC17" t="n">
-        <v>191.812302467701</v>
+        <v>192.064175415484</v>
       </c>
       <c r="HD17" t="n">
-        <v>193.64990406074</v>
+        <v>193.90718286428</v>
       </c>
       <c r="HE17" t="n">
-        <v>195.509052372263</v>
+        <v>195.771040480141</v>
       </c>
       <c r="HF17" t="n">
-        <v>197.394812991453</v>
+        <v>197.660860449584</v>
       </c>
       <c r="HG17" t="n">
-        <v>199.304926825626</v>
+        <v>199.574500577281</v>
       </c>
       <c r="HH17" t="n">
-        <v>201.243989880503</v>
+        <v>201.516645638089</v>
       </c>
       <c r="HI17" t="n">
-        <v>203.211414064004</v>
+        <v>203.486792985758</v>
       </c>
       <c r="HJ17" t="n">
-        <v>205.207627776931</v>
+        <v>205.48545485647</v>
       </c>
       <c r="HK17" t="n">
-        <v>207.230117454785</v>
+        <v>207.510211756145</v>
       </c>
       <c r="HL17" t="n">
-        <v>209.284264045213</v>
+        <v>209.56651188207</v>
       </c>
       <c r="HM17" t="n">
-        <v>211.366910088428</v>
+        <v>211.65125364358</v>
       </c>
       <c r="HN17" t="n">
-        <v>213.478403172362</v>
+        <v>213.764840738643</v>
       </c>
       <c r="HO17" t="n">
-        <v>215.615244567098</v>
+        <v>215.903849087981</v>
       </c>
       <c r="HP17" t="n">
-        <v>217.77905300124</v>
+        <v>218.069946203578</v>
       </c>
       <c r="HQ17" t="n">
-        <v>219.969664690187</v>
+        <v>220.262992738915</v>
       </c>
       <c r="HR17" t="n">
-        <v>222.186232477037</v>
+        <v>222.482166892017</v>
       </c>
       <c r="HS17" t="n">
-        <v>224.419645609435</v>
+        <v>224.718530376565</v>
       </c>
       <c r="HT17" t="n">
-        <v>226.680508083916</v>
+        <v>226.982582642591</v>
       </c>
       <c r="HU17" t="n">
-        <v>228.960312368092</v>
+        <v>229.265897580588</v>
       </c>
     </row>
     <row r="18">
@@ -13558,139 +13558,139 @@
         <v>26114</v>
       </c>
       <c r="GC18" t="n">
-        <v>26415.8830093051</v>
+        <v>26415.8365035052</v>
       </c>
       <c r="GD18" t="n">
-        <v>26492.9760390459</v>
+        <v>26494.6807941305</v>
       </c>
       <c r="GE18" t="n">
-        <v>26908.4998345285</v>
+        <v>26905.6263127601</v>
       </c>
       <c r="GF18" t="n">
-        <v>27194.1884257227</v>
+        <v>27192.0542936201</v>
       </c>
       <c r="GG18" t="n">
-        <v>27579.0279011303</v>
+        <v>27574.8384278043</v>
       </c>
       <c r="GH18" t="n">
-        <v>27948.2647499832</v>
+        <v>27944.2034058628</v>
       </c>
       <c r="GI18" t="n">
-        <v>28319.2813110859</v>
+        <v>28315.8022889771</v>
       </c>
       <c r="GJ18" t="n">
-        <v>28694.0312998817</v>
+        <v>28692.1529859001</v>
       </c>
       <c r="GK18" t="n">
-        <v>29056.4632176604</v>
+        <v>29056.9952456738</v>
       </c>
       <c r="GL18" t="n">
-        <v>29417.2781761537</v>
+        <v>29420.8575650557</v>
       </c>
       <c r="GM18" t="n">
-        <v>29772.8534783001</v>
+        <v>29779.9763970763</v>
       </c>
       <c r="GN18" t="n">
-        <v>30129.4963866396</v>
+        <v>30140.6131534836</v>
       </c>
       <c r="GO18" t="n">
-        <v>30461.5077189</v>
+        <v>30476.8632209282</v>
       </c>
       <c r="GP18" t="n">
-        <v>30785.7252185823</v>
+        <v>30805.4304622013</v>
       </c>
       <c r="GQ18" t="n">
-        <v>31106.8539157397</v>
+        <v>31130.6660409328</v>
       </c>
       <c r="GR18" t="n">
-        <v>31417.301934077</v>
+        <v>31445.198940009</v>
       </c>
       <c r="GS18" t="n">
-        <v>31727.116644998</v>
+        <v>31758.7693423531</v>
       </c>
       <c r="GT18" t="n">
-        <v>32032.024818086</v>
+        <v>32067.2452474595</v>
       </c>
       <c r="GU18" t="n">
-        <v>32338.0159596432</v>
+        <v>32376.4355403382</v>
       </c>
       <c r="GV18" t="n">
-        <v>32636.5399126794</v>
+        <v>32677.9587089752</v>
       </c>
       <c r="GW18" t="n">
-        <v>32934.7109387874</v>
+        <v>32978.7671159119</v>
       </c>
       <c r="GX18" t="n">
-        <v>33231.3112664711</v>
+        <v>33277.718497008</v>
       </c>
       <c r="GY18" t="n">
-        <v>33530.2055330081</v>
+        <v>33578.619780337</v>
       </c>
       <c r="GZ18" t="n">
-        <v>33825.4120669909</v>
+        <v>33875.5493965322</v>
       </c>
       <c r="HA18" t="n">
-        <v>34124.4773613397</v>
+        <v>34176.0191724479</v>
       </c>
       <c r="HB18" t="n">
-        <v>34424.8658795476</v>
+        <v>34477.5448238568</v>
       </c>
       <c r="HC18" t="n">
-        <v>34734.1805970594</v>
+        <v>34787.6353792272</v>
       </c>
       <c r="HD18" t="n">
-        <v>35035.6348073003</v>
+        <v>35089.6839370613</v>
       </c>
       <c r="HE18" t="n">
-        <v>35347.7493234583</v>
+        <v>35402.0530858433</v>
       </c>
       <c r="HF18" t="n">
-        <v>35661.4931454761</v>
+        <v>35715.842903768</v>
       </c>
       <c r="HG18" t="n">
-        <v>35981.6871843858</v>
+        <v>36035.8415776012</v>
       </c>
       <c r="HH18" t="n">
-        <v>36302.267185337</v>
+        <v>36356.0144216383</v>
       </c>
       <c r="HI18" t="n">
-        <v>36626.5902081348</v>
+        <v>36679.7317284234</v>
       </c>
       <c r="HJ18" t="n">
-        <v>36955.1737912724</v>
+        <v>37007.5228251437</v>
       </c>
       <c r="HK18" t="n">
-        <v>37290.0971774992</v>
+        <v>37341.4834016358</v>
       </c>
       <c r="HL18" t="n">
-        <v>37624.6493821499</v>
+        <v>37674.8924336375</v>
       </c>
       <c r="HM18" t="n">
-        <v>37964.3450471936</v>
+        <v>38013.2953805912</v>
       </c>
       <c r="HN18" t="n">
-        <v>38307.8809333141</v>
+        <v>38355.3904522713</v>
       </c>
       <c r="HO18" t="n">
-        <v>38657.7902445565</v>
+        <v>38703.7272997378</v>
       </c>
       <c r="HP18" t="n">
-        <v>39008.3076242471</v>
+        <v>39052.5267003419</v>
       </c>
       <c r="HQ18" t="n">
-        <v>39360.4019774099</v>
+        <v>39402.7738412741</v>
       </c>
       <c r="HR18" t="n">
-        <v>39716.0245085691</v>
+        <v>39756.4349257364</v>
       </c>
       <c r="HS18" t="n">
-        <v>40081.6510003041</v>
+        <v>40120.0056887909</v>
       </c>
       <c r="HT18" t="n">
-        <v>40435.3896521552</v>
+        <v>40471.584643582</v>
       </c>
       <c r="HU18" t="n">
-        <v>40797.5469844338</v>
+        <v>40831.4840751055</v>
       </c>
     </row>
     <row r="19">
@@ -14247,139 +14247,139 @@
         <v>14608.7589597667</v>
       </c>
       <c r="GC19" t="n">
-        <v>14660.0841628209</v>
+        <v>14660.1382923385</v>
       </c>
       <c r="GD19" t="n">
-        <v>14786.4151985</v>
+        <v>14784.3907884891</v>
       </c>
       <c r="GE19" t="n">
-        <v>14875.5153551704</v>
+        <v>14873.7006956972</v>
       </c>
       <c r="GF19" t="n">
-        <v>14981.7545261638</v>
+        <v>14979.6240019468</v>
       </c>
       <c r="GG19" t="n">
-        <v>15075.0817684402</v>
+        <v>15073.6227726833</v>
       </c>
       <c r="GH19" t="n">
-        <v>15155.1216275371</v>
+        <v>15154.7536184065</v>
       </c>
       <c r="GI19" t="n">
-        <v>15222.3257122377</v>
+        <v>15223.4317449289</v>
       </c>
       <c r="GJ19" t="n">
-        <v>15276.2876906586</v>
+        <v>15278.9814911632</v>
       </c>
       <c r="GK19" t="n">
-        <v>15323.2132175702</v>
+        <v>15327.5557380951</v>
       </c>
       <c r="GL19" t="n">
-        <v>15365.5244126423</v>
+        <v>15371.4471596381</v>
       </c>
       <c r="GM19" t="n">
-        <v>15403.5976834406</v>
+        <v>15411.0513271861</v>
       </c>
       <c r="GN19" t="n">
-        <v>15429.3415208268</v>
+        <v>15438.1692357958</v>
       </c>
       <c r="GO19" t="n">
-        <v>15452.5589956743</v>
+        <v>15462.5237053484</v>
       </c>
       <c r="GP19" t="n">
-        <v>15475.9042680644</v>
+        <v>15486.6849791247</v>
       </c>
       <c r="GQ19" t="n">
-        <v>15497.7356617207</v>
+        <v>15509.0997682217</v>
       </c>
       <c r="GR19" t="n">
-        <v>15519.9736252033</v>
+        <v>15531.6194771866</v>
       </c>
       <c r="GS19" t="n">
-        <v>15543.5665914353</v>
+        <v>15555.2674474206</v>
       </c>
       <c r="GT19" t="n">
-        <v>15569.1731244045</v>
+        <v>15580.6922220198</v>
       </c>
       <c r="GU19" t="n">
-        <v>15594.2685137004</v>
+        <v>15605.4442687677</v>
       </c>
       <c r="GV19" t="n">
-        <v>15621.7117502586</v>
+        <v>15632.3490535868</v>
       </c>
       <c r="GW19" t="n">
-        <v>15651.2247447593</v>
+        <v>15661.1732742521</v>
       </c>
       <c r="GX19" t="n">
-        <v>15683.477246508</v>
+        <v>15692.5940361631</v>
       </c>
       <c r="GY19" t="n">
-        <v>15716.9262429811</v>
+        <v>15725.107508994</v>
       </c>
       <c r="GZ19" t="n">
-        <v>15752.3422422514</v>
+        <v>15759.4890730033</v>
       </c>
       <c r="HA19" t="n">
-        <v>15790.7055451312</v>
+        <v>15796.7509629593</v>
       </c>
       <c r="HB19" t="n">
-        <v>15832.5985073567</v>
+        <v>15837.4747189529</v>
       </c>
       <c r="HC19" t="n">
-        <v>15873.4466123927</v>
+        <v>15877.1565979911</v>
       </c>
       <c r="HD19" t="n">
-        <v>15917.4689799737</v>
+        <v>15919.9771535063</v>
       </c>
       <c r="HE19" t="n">
-        <v>15962.9273029802</v>
+        <v>15964.2554949907</v>
       </c>
       <c r="HF19" t="n">
-        <v>16010.0970831418</v>
+        <v>16010.2679804134</v>
       </c>
       <c r="HG19" t="n">
-        <v>16057.0335643086</v>
+        <v>16056.0867431059</v>
       </c>
       <c r="HH19" t="n">
-        <v>16104.1631566518</v>
+        <v>16102.1438433491</v>
       </c>
       <c r="HI19" t="n">
-        <v>16152.3105102156</v>
+        <v>16149.2688366964</v>
       </c>
       <c r="HJ19" t="n">
-        <v>16201.3686056214</v>
+        <v>16197.3550392527</v>
       </c>
       <c r="HK19" t="n">
-        <v>16249.3746558055</v>
+        <v>16244.4397363465</v>
       </c>
       <c r="HL19" t="n">
-        <v>16296.7874896749</v>
+        <v>16290.9862757092</v>
       </c>
       <c r="HM19" t="n">
-        <v>16344.6206474078</v>
+        <v>16338.0042141144</v>
       </c>
       <c r="HN19" t="n">
-        <v>16392.7683192302</v>
+        <v>16385.3837858151</v>
       </c>
       <c r="HO19" t="n">
-        <v>16439.3019308464</v>
+        <v>16431.1898745545</v>
       </c>
       <c r="HP19" t="n">
-        <v>16484.9699853665</v>
+        <v>16476.1725615083</v>
       </c>
       <c r="HQ19" t="n">
-        <v>16530.6479809201</v>
+        <v>16521.205950644</v>
       </c>
       <c r="HR19" t="n">
-        <v>16576.4040902958</v>
+        <v>16566.3518577967</v>
       </c>
       <c r="HS19" t="n">
-        <v>16616.8771069734</v>
+        <v>16606.2503449746</v>
       </c>
       <c r="HT19" t="n">
-        <v>16658.2078995983</v>
+        <v>16647.0336193902</v>
       </c>
       <c r="HU19" t="n">
-        <v>16698.4480021953</v>
+        <v>16686.7569145983</v>
       </c>
     </row>
     <row r="20">
@@ -14936,139 +14936,139 @@
         <v>0.669101939</v>
       </c>
       <c r="GC20" t="n">
-        <v>0.668738350026894</v>
+        <v>0.668738443496059</v>
       </c>
       <c r="GD20" t="n">
-        <v>0.668210262713964</v>
+        <v>0.668207338805949</v>
       </c>
       <c r="GE20" t="n">
-        <v>0.668897178462281</v>
+        <v>0.668874023244265</v>
       </c>
       <c r="GF20" t="n">
-        <v>0.669289317780209</v>
+        <v>0.669265864397426</v>
       </c>
       <c r="GG20" t="n">
-        <v>0.67001931887247</v>
+        <v>0.669992092127643</v>
       </c>
       <c r="GH20" t="n">
-        <v>0.670583167880582</v>
+        <v>0.670563621014639</v>
       </c>
       <c r="GI20" t="n">
-        <v>0.670833554692703</v>
+        <v>0.67082887992208</v>
       </c>
       <c r="GJ20" t="n">
-        <v>0.671046577445568</v>
+        <v>0.671058691068006</v>
       </c>
       <c r="GK20" t="n">
-        <v>0.671066602810135</v>
+        <v>0.671099902770927</v>
       </c>
       <c r="GL20" t="n">
-        <v>0.671018836021629</v>
+        <v>0.671073274636327</v>
       </c>
       <c r="GM20" t="n">
-        <v>0.670889422871896</v>
+        <v>0.67096527099764</v>
       </c>
       <c r="GN20" t="n">
-        <v>0.670675377941332</v>
+        <v>0.67077205619218</v>
       </c>
       <c r="GO20" t="n">
-        <v>0.670330680416356</v>
+        <v>0.670446497943183</v>
       </c>
       <c r="GP20" t="n">
-        <v>0.669935462425436</v>
+        <v>0.670067619270057</v>
       </c>
       <c r="GQ20" t="n">
-        <v>0.669520034117484</v>
+        <v>0.669664801567653</v>
       </c>
       <c r="GR20" t="n">
-        <v>0.669085946523152</v>
+        <v>0.669240053728921</v>
       </c>
       <c r="GS20" t="n">
-        <v>0.668675887246278</v>
+        <v>0.668835524919603</v>
       </c>
       <c r="GT20" t="n">
-        <v>0.668273778086302</v>
+        <v>0.668435740434553</v>
       </c>
       <c r="GU20" t="n">
-        <v>0.667889334372775</v>
+        <v>0.668050433701609</v>
       </c>
       <c r="GV20" t="n">
-        <v>0.667508084648673</v>
+        <v>0.667665679818809</v>
       </c>
       <c r="GW20" t="n">
-        <v>0.667150595631915</v>
+        <v>0.667301985719807</v>
       </c>
       <c r="GX20" t="n">
-        <v>0.666821717172609</v>
+        <v>0.666964589903316</v>
       </c>
       <c r="GY20" t="n">
-        <v>0.666525635620313</v>
+        <v>0.666657932640853</v>
       </c>
       <c r="GZ20" t="n">
-        <v>0.666255995080504</v>
+        <v>0.666376047185408</v>
       </c>
       <c r="HA20" t="n">
-        <v>0.666030795028449</v>
+        <v>0.666137196485821</v>
       </c>
       <c r="HB20" t="n">
-        <v>0.665846575274832</v>
+        <v>0.665938232988956</v>
       </c>
       <c r="HC20" t="n">
-        <v>0.665702108391599</v>
+        <v>0.665778140482826</v>
       </c>
       <c r="HD20" t="n">
-        <v>0.665566555329287</v>
+        <v>0.665626714174029</v>
       </c>
       <c r="HE20" t="n">
-        <v>0.665479652904041</v>
+        <v>0.665523552790394</v>
       </c>
       <c r="HF20" t="n">
-        <v>0.665416462440354</v>
+        <v>0.665444285213617</v>
       </c>
       <c r="HG20" t="n">
-        <v>0.665376239998806</v>
+        <v>0.665388284711509</v>
       </c>
       <c r="HH20" t="n">
-        <v>0.665345047721078</v>
+        <v>0.665341796281577</v>
       </c>
       <c r="HI20" t="n">
-        <v>0.665324469752625</v>
+        <v>0.665306580744837</v>
       </c>
       <c r="HJ20" t="n">
-        <v>0.665319669262758</v>
+        <v>0.665287820186819</v>
       </c>
       <c r="HK20" t="n">
-        <v>0.665324357699194</v>
+        <v>0.665279292202685</v>
       </c>
       <c r="HL20" t="n">
-        <v>0.665325332759596</v>
+        <v>0.665267800745063</v>
       </c>
       <c r="HM20" t="n">
-        <v>0.665334261092613</v>
+        <v>0.66526505441499</v>
       </c>
       <c r="HN20" t="n">
-        <v>0.665347896141157</v>
+        <v>0.665267772078693</v>
       </c>
       <c r="HO20" t="n">
-        <v>0.665363094438835</v>
+        <v>0.665272761568176</v>
       </c>
       <c r="HP20" t="n">
-        <v>0.665364856237318</v>
+        <v>0.665264955367931</v>
       </c>
       <c r="HQ20" t="n">
-        <v>0.665356329433547</v>
+        <v>0.665247491229117</v>
       </c>
       <c r="HR20" t="n">
-        <v>0.665346031738721</v>
+        <v>0.665228855514821</v>
       </c>
       <c r="HS20" t="n">
-        <v>0.66532701774894</v>
+        <v>0.665202036526277</v>
       </c>
       <c r="HT20" t="n">
-        <v>0.665264358121371</v>
+        <v>0.665132082570181</v>
       </c>
       <c r="HU20" t="n">
-        <v>0.665203774172323</v>
+        <v>0.66506462542686</v>
       </c>
     </row>
     <row r="21">
@@ -15625,139 +15625,139 @@
         <v>0.0430614370315685</v>
       </c>
       <c r="GC21" t="n">
-        <v>0.047638941993171</v>
+        <v>0.047635545119364</v>
       </c>
       <c r="GD21" t="n">
-        <v>0.0428201198153555</v>
+        <v>0.0429469797638726</v>
       </c>
       <c r="GE21" t="n">
-        <v>0.0421785988438807</v>
+        <v>0.0422622892330235</v>
       </c>
       <c r="GF21" t="n">
-        <v>0.039601450343304</v>
+        <v>0.0397043757479701</v>
       </c>
       <c r="GG21" t="n">
-        <v>0.0383648271123463</v>
+        <v>0.0384188218837082</v>
       </c>
       <c r="GH21" t="n">
-        <v>0.0377576647487839</v>
+        <v>0.0377529821387966</v>
       </c>
       <c r="GI21" t="n">
-        <v>0.0375282277403831</v>
+        <v>0.0374515887364424</v>
       </c>
       <c r="GJ21" t="n">
-        <v>0.0379136901383097</v>
+        <v>0.0377614077764547</v>
       </c>
       <c r="GK21" t="n">
-        <v>0.0384670586963278</v>
+        <v>0.0382422900829223</v>
       </c>
       <c r="GL21" t="n">
-        <v>0.0392118207477614</v>
+        <v>0.0389194493706399</v>
       </c>
       <c r="GM21" t="n">
-        <v>0.0401018529584469</v>
+        <v>0.0397459308345794</v>
       </c>
       <c r="GN21" t="n">
-        <v>0.0415843369785524</v>
+        <v>0.0411742063976497</v>
       </c>
       <c r="GO21" t="n">
-        <v>0.0430283001075633</v>
+        <v>0.042576610303911</v>
       </c>
       <c r="GP21" t="n">
-        <v>0.0443833676091023</v>
+        <v>0.0439062800315088</v>
       </c>
       <c r="GQ21" t="n">
-        <v>0.0457941456370177</v>
+        <v>0.0453008809430374</v>
       </c>
       <c r="GR21" t="n">
-        <v>0.0470249216073248</v>
+        <v>0.0465294382073364</v>
       </c>
       <c r="GS21" t="n">
-        <v>0.048198337515805</v>
+        <v>0.0477091895074912</v>
       </c>
       <c r="GT21" t="n">
-        <v>0.0492519956307578</v>
+        <v>0.048779107332555</v>
       </c>
       <c r="GU21" t="n">
-        <v>0.0503545232227043</v>
+        <v>0.0499031223260768</v>
       </c>
       <c r="GV21" t="n">
-        <v>0.0513232248995515</v>
+        <v>0.0509013193196546</v>
       </c>
       <c r="GW21" t="n">
-        <v>0.0521933078487409</v>
+        <v>0.0518060097932792</v>
       </c>
       <c r="GX21" t="n">
-        <v>0.05293228689191</v>
+        <v>0.0525847501748503</v>
       </c>
       <c r="GY21" t="n">
-        <v>0.0536404374937876</v>
+        <v>0.0533357221987654</v>
       </c>
       <c r="GZ21" t="n">
-        <v>0.0541561328844275</v>
+        <v>0.0538974816373526</v>
       </c>
       <c r="HA21" t="n">
-        <v>0.0545541558872522</v>
+        <v>0.0543432684194741</v>
       </c>
       <c r="HB21" t="n">
-        <v>0.0547963530736673</v>
+        <v>0.0546353797921269</v>
       </c>
       <c r="HC21" t="n">
-        <v>0.0551551350134763</v>
+        <v>0.055042230370541</v>
       </c>
       <c r="HD21" t="n">
-        <v>0.0552532162312405</v>
+        <v>0.055189748262159</v>
       </c>
       <c r="HE21" t="n">
-        <v>0.0553342237140306</v>
+        <v>0.0553179413680615</v>
       </c>
       <c r="HF21" t="n">
-        <v>0.0553472656273705</v>
+        <v>0.0553766794533445</v>
       </c>
       <c r="HG21" t="n">
-        <v>0.0554065973595507</v>
+        <v>0.0554793944484464</v>
       </c>
       <c r="HH21" t="n">
-        <v>0.0554233223599101</v>
+        <v>0.0555371488560755</v>
       </c>
       <c r="HI21" t="n">
-        <v>0.0553956219246031</v>
+        <v>0.0555481083869366</v>
       </c>
       <c r="HJ21" t="n">
-        <v>0.0553375940779122</v>
+        <v>0.0555264033311041</v>
       </c>
       <c r="HK21" t="n">
-        <v>0.0553548873654045</v>
+        <v>0.0555778053174229</v>
       </c>
       <c r="HL21" t="n">
-        <v>0.055321183627602</v>
+        <v>0.0555757981595824</v>
       </c>
       <c r="HM21" t="n">
-        <v>0.0552746606531255</v>
+        <v>0.0555588544418541</v>
       </c>
       <c r="HN21" t="n">
-        <v>0.0552170142811305</v>
+        <v>0.0555288783700227</v>
       </c>
       <c r="HO21" t="n">
-        <v>0.0552547678291397</v>
+        <v>0.0555927400645496</v>
       </c>
       <c r="HP21" t="n">
-        <v>0.0553263696550279</v>
+        <v>0.0556887249542633</v>
       </c>
       <c r="HQ21" t="n">
-        <v>0.0553824651059852</v>
+        <v>0.0557675592310736</v>
       </c>
       <c r="HR21" t="n">
-        <v>0.0554312721498369</v>
+        <v>0.0558377965009224</v>
       </c>
       <c r="HS21" t="n">
-        <v>0.0557676133999534</v>
+        <v>0.0561941721797361</v>
       </c>
       <c r="HT21" t="n">
-        <v>0.0559807445525617</v>
+        <v>0.0564263786468954</v>
       </c>
       <c r="HU21" t="n">
-        <v>0.05625681668992</v>
+        <v>0.0567202426446619</v>
       </c>
     </row>
     <row r="22">
@@ -16314,139 +16314,139 @@
         <v>657.3819662</v>
       </c>
       <c r="GC22" t="n">
-        <v>733.325147174317</v>
+        <v>733.273169184469</v>
       </c>
       <c r="GD22" t="n">
-        <v>661.480870149429</v>
+        <v>663.437684330631</v>
       </c>
       <c r="GE22" t="n">
-        <v>655.057908623185</v>
+        <v>656.334946139747</v>
       </c>
       <c r="GF22" t="n">
-        <v>617.76363931951</v>
+        <v>619.347521806121</v>
       </c>
       <c r="GG22" t="n">
-        <v>601.426623671099</v>
+        <v>602.248592581574</v>
       </c>
       <c r="GH22" t="n">
-        <v>594.675644176608</v>
+        <v>594.584561593167</v>
       </c>
       <c r="GI22" t="n">
-        <v>593.541550611319</v>
+        <v>592.325303469564</v>
       </c>
       <c r="GJ22" t="n">
-        <v>602.004743487783</v>
+        <v>599.59757530649</v>
       </c>
       <c r="GK22" t="n">
-        <v>613.020108969942</v>
+        <v>609.468383192889</v>
       </c>
       <c r="GL22" t="n">
-        <v>627.100010514187</v>
+        <v>622.474717885207</v>
       </c>
       <c r="GM22" t="n">
-        <v>643.519210916902</v>
+        <v>637.879791242465</v>
       </c>
       <c r="GN22" t="n">
-        <v>669.458001649667</v>
+        <v>662.950938116104</v>
       </c>
       <c r="GO22" t="n">
-        <v>694.793230286865</v>
+        <v>687.618406939422</v>
       </c>
       <c r="GP22" t="n">
-        <v>718.77449946528</v>
+        <v>711.188480678537</v>
       </c>
       <c r="GQ22" t="n">
-        <v>743.765806575924</v>
+        <v>735.913530393185</v>
       </c>
       <c r="GR22" t="n">
-        <v>765.839196078345</v>
+        <v>757.944373571294</v>
       </c>
       <c r="GS22" t="n">
-        <v>787.111667821957</v>
+        <v>779.309548924104</v>
       </c>
       <c r="GT22" t="n">
-        <v>806.536511586057</v>
+        <v>798.986219083115</v>
       </c>
       <c r="GU22" t="n">
-        <v>826.879193319368</v>
+        <v>819.664327785826</v>
       </c>
       <c r="GV22" t="n">
-        <v>845.131641035568</v>
+        <v>838.382073370121</v>
       </c>
       <c r="GW22" t="n">
-        <v>861.87334117381</v>
+        <v>855.671970698684</v>
       </c>
       <c r="GX22" t="n">
-        <v>876.56081701216</v>
+        <v>870.992168933442</v>
       </c>
       <c r="GY22" t="n">
-        <v>890.848431878603</v>
+        <v>885.963601876429</v>
       </c>
       <c r="GZ22" t="n">
-        <v>901.931176730504</v>
+        <v>897.785265436512</v>
       </c>
       <c r="HA22" t="n">
-        <v>911.156095067181</v>
+        <v>907.778875815775</v>
       </c>
       <c r="HB22" t="n">
-        <v>917.864418734884</v>
+        <v>915.294007302435</v>
       </c>
       <c r="HC22" t="n">
-        <v>926.609499743119</v>
+        <v>924.818305422112</v>
       </c>
       <c r="HD22" t="n">
-        <v>930.928269935934</v>
+        <v>929.942979586385</v>
       </c>
       <c r="HE22" t="n">
-        <v>935.035809987719</v>
+        <v>934.822330736701</v>
       </c>
       <c r="HF22" t="n">
-        <v>938.032780210331</v>
+        <v>938.570527826581</v>
       </c>
       <c r="HG22" t="n">
-        <v>941.850462347566</v>
+        <v>943.104999188534</v>
       </c>
       <c r="HH22" t="n">
-        <v>944.916799502796</v>
+        <v>946.852796558887</v>
       </c>
       <c r="HI22" t="n">
-        <v>947.240398521251</v>
+        <v>949.822305395299</v>
       </c>
       <c r="HJ22" t="n">
-        <v>949.063813743249</v>
+        <v>952.256383154041</v>
       </c>
       <c r="HK22" t="n">
-        <v>952.190873911903</v>
+        <v>955.960651763864</v>
       </c>
       <c r="HL22" t="n">
-        <v>954.353706092676</v>
+        <v>958.663179315667</v>
       </c>
       <c r="HM22" t="n">
-        <v>956.302825013678</v>
+        <v>961.119652449788</v>
       </c>
       <c r="HN22" t="n">
-        <v>958.061154230811</v>
+        <v>963.356225948351</v>
       </c>
       <c r="HO22" t="n">
-        <v>961.476110719639</v>
+        <v>967.225754299838</v>
       </c>
       <c r="HP22" t="n">
-        <v>965.469638558243</v>
+        <v>971.646974996256</v>
       </c>
       <c r="HQ22" t="n">
-        <v>969.184004485567</v>
+        <v>975.763432864209</v>
       </c>
       <c r="HR22" t="n">
-        <v>972.773397275352</v>
+        <v>979.734987834167</v>
       </c>
       <c r="HS22" t="n">
-        <v>981.414917188235</v>
+        <v>988.735852134658</v>
       </c>
       <c r="HT22" t="n">
-        <v>987.839021823154</v>
+        <v>995.50471096607</v>
       </c>
       <c r="HU22" t="n">
-        <v>995.399719703095</v>
+        <v>1003.38957046326</v>
       </c>
     </row>
     <row r="23">
@@ -17003,139 +17003,139 @@
         <v>0.0362333333333333</v>
       </c>
       <c r="GC23" t="n">
-        <v>0.0313989538538978</v>
+        <v>0.0314049555370946</v>
       </c>
       <c r="GD23" t="n">
-        <v>0.0421150863970587</v>
+        <v>0.0418909248980678</v>
       </c>
       <c r="GE23" t="n">
-        <v>0.0487508300408782</v>
+        <v>0.0485642617616931</v>
       </c>
       <c r="GF23" t="n">
-        <v>0.0577389160567415</v>
+        <v>0.057490046358188</v>
       </c>
       <c r="GG23" t="n">
-        <v>0.0653964702985591</v>
+        <v>0.0652008461326639</v>
       </c>
       <c r="GH23" t="n">
-        <v>0.0710711190131653</v>
+        <v>0.0709882065523347</v>
       </c>
       <c r="GI23" t="n">
-        <v>0.0756460952845919</v>
+        <v>0.0757193610803496</v>
       </c>
       <c r="GJ23" t="n">
-        <v>0.0782042205424685</v>
+        <v>0.0784820554037434</v>
       </c>
       <c r="GK23" t="n">
-        <v>0.079569905245927</v>
+        <v>0.0800725990060011</v>
       </c>
       <c r="GL23" t="n">
-        <v>0.0797187808873608</v>
+        <v>0.0804565360785741</v>
       </c>
       <c r="GM23" t="n">
-        <v>0.0786957914916309</v>
+        <v>0.0796686173918926</v>
       </c>
       <c r="GN23" t="n">
-        <v>0.0759125949979281</v>
+        <v>0.0771015703813831</v>
       </c>
       <c r="GO23" t="n">
-        <v>0.0724872175781647</v>
+        <v>0.073859743649193</v>
       </c>
       <c r="GP23" t="n">
-        <v>0.0687086045913122</v>
+        <v>0.0702196390946762</v>
       </c>
       <c r="GQ23" t="n">
-        <v>0.0645659217210807</v>
+        <v>0.0661769196519819</v>
       </c>
       <c r="GR23" t="n">
-        <v>0.0606014129848455</v>
+        <v>0.0622662907952723</v>
       </c>
       <c r="GS23" t="n">
-        <v>0.0567054839436087</v>
+        <v>0.0583876197371345</v>
       </c>
       <c r="GT23" t="n">
-        <v>0.0530480654228205</v>
+        <v>0.0547110597449208</v>
       </c>
       <c r="GU23" t="n">
-        <v>0.0494154042500037</v>
+        <v>0.0510325726501974</v>
       </c>
       <c r="GV23" t="n">
-        <v>0.0461024299249995</v>
+        <v>0.0476458147885842</v>
       </c>
       <c r="GW23" t="n">
-        <v>0.0430906620942521</v>
+        <v>0.044539365316029</v>
       </c>
       <c r="GX23" t="n">
-        <v>0.0404445380743263</v>
+        <v>0.0417804044582965</v>
       </c>
       <c r="GY23" t="n">
-        <v>0.0380238391104575</v>
+        <v>0.0392343296395313</v>
       </c>
       <c r="GZ23" t="n">
-        <v>0.0360858197504699</v>
+        <v>0.0371605471177376</v>
       </c>
       <c r="HA23" t="n">
-        <v>0.0345243132384224</v>
+        <v>0.0354571221143882</v>
       </c>
       <c r="HB23" t="n">
-        <v>0.0334025270589707</v>
+        <v>0.0341881441707878</v>
       </c>
       <c r="HC23" t="n">
-        <v>0.0322771314417567</v>
+        <v>0.0329181028464435</v>
       </c>
       <c r="HD23" t="n">
-        <v>0.0317251272726318</v>
+        <v>0.0322201521263637</v>
       </c>
       <c r="HE23" t="n">
-        <v>0.0313646162801688</v>
+        <v>0.0317190482093268</v>
       </c>
       <c r="HF23" t="n">
-        <v>0.031252351682965</v>
+        <v>0.031471423707355</v>
       </c>
       <c r="HG23" t="n">
-        <v>0.0311982966577939</v>
+        <v>0.0312891462861728</v>
       </c>
       <c r="HH23" t="n">
-        <v>0.0312965267716933</v>
+        <v>0.0312671573846681</v>
       </c>
       <c r="HI23" t="n">
-        <v>0.0315452576741338</v>
+        <v>0.0314039543717521</v>
       </c>
       <c r="HJ23" t="n">
-        <v>0.0319037713011128</v>
+        <v>0.0316590436482185</v>
       </c>
       <c r="HK23" t="n">
-        <v>0.0321881504806393</v>
+        <v>0.0318483838791073</v>
       </c>
       <c r="HL23" t="n">
-        <v>0.0325792342859997</v>
+        <v>0.0321530577107797</v>
       </c>
       <c r="HM23" t="n">
-        <v>0.0330086542387562</v>
+        <v>0.0325040808655626</v>
       </c>
       <c r="HN23" t="n">
-        <v>0.0334639082212899</v>
+        <v>0.0328883637444108</v>
       </c>
       <c r="HO23" t="n">
-        <v>0.0337651236883806</v>
+        <v>0.0331251879589588</v>
       </c>
       <c r="HP23" t="n">
-        <v>0.0339802334579402</v>
+        <v>0.0332824340416075</v>
       </c>
       <c r="HQ23" t="n">
-        <v>0.0341836430382171</v>
+        <v>0.0334340501264075</v>
       </c>
       <c r="HR23" t="n">
-        <v>0.0343618386190286</v>
+        <v>0.0335656401939877</v>
       </c>
       <c r="HS23" t="n">
-        <v>0.0340270407505213</v>
+        <v>0.0331895508556336</v>
       </c>
       <c r="HT23" t="n">
-        <v>0.0338152337172525</v>
+        <v>0.032940585364853</v>
       </c>
       <c r="HU23" t="n">
-        <v>0.0334403728160072</v>
+        <v>0.0325330020829802</v>
       </c>
     </row>
     <row r="24">
@@ -17644,139 +17644,139 @@
         <v>0.04288</v>
       </c>
       <c r="GC24" t="n">
-        <v>0.0420176539960461</v>
+        <v>0.0420180185765244</v>
       </c>
       <c r="GD24" t="n">
-        <v>0.0418648542173019</v>
+        <v>0.0418515770337133</v>
       </c>
       <c r="GE24" t="n">
-        <v>0.0421255316352095</v>
+        <v>0.0421018230383782</v>
       </c>
       <c r="GF24" t="n">
-        <v>0.042914494580916</v>
+        <v>0.0428772786023373</v>
       </c>
       <c r="GG24" t="n">
-        <v>0.0441150310952739</v>
+        <v>0.0440684597782565</v>
       </c>
       <c r="GH24" t="n">
-        <v>0.0455787282445473</v>
+        <v>0.0455302839340232</v>
       </c>
       <c r="GI24" t="n">
-        <v>0.0472209081440696</v>
+        <v>0.0471802053368479</v>
       </c>
       <c r="GJ24" t="n">
-        <v>0.0489069298949721</v>
+        <v>0.0488858695312313</v>
       </c>
       <c r="GK24" t="n">
-        <v>0.0505613788378684</v>
+        <v>0.0505722859483853</v>
       </c>
       <c r="GL24" t="n">
-        <v>0.0521124830106409</v>
+        <v>0.0521674651409459</v>
       </c>
       <c r="GM24" t="n">
-        <v>0.0534960761811148</v>
+        <v>0.0536064189622667</v>
       </c>
       <c r="GN24" t="n">
-        <v>0.0546166113500164</v>
+        <v>0.0547916843726832</v>
       </c>
       <c r="GO24" t="n">
-        <v>0.0554529481578092</v>
+        <v>0.0556995042681334</v>
       </c>
       <c r="GP24" t="n">
-        <v>0.0560029347135877</v>
+        <v>0.0563245318763212</v>
       </c>
       <c r="GQ24" t="n">
-        <v>0.0562639071612136</v>
+        <v>0.0566615201756999</v>
       </c>
       <c r="GR24" t="n">
-        <v>0.0562663219596782</v>
+        <v>0.0567380599977979</v>
       </c>
       <c r="GS24" t="n">
-        <v>0.0560319091647347</v>
+        <v>0.0565737851969425</v>
       </c>
       <c r="GT24" t="n">
-        <v>0.0555912453680954</v>
+        <v>0.0561973320730861</v>
       </c>
       <c r="GU24" t="n">
-        <v>0.0549598453323549</v>
+        <v>0.0556229970543329</v>
       </c>
       <c r="GV24" t="n">
-        <v>0.0541700857832859</v>
+        <v>0.0548819439545783</v>
       </c>
       <c r="GW24" t="n">
-        <v>0.053251021447819</v>
+        <v>0.0540025258228202</v>
       </c>
       <c r="GX24" t="n">
-        <v>0.052233647668464</v>
+        <v>0.0530152506111242</v>
       </c>
       <c r="GY24" t="n">
-        <v>0.0511383364615102</v>
+        <v>0.0519403772167629</v>
       </c>
       <c r="GZ24" t="n">
-        <v>0.0499997032315265</v>
+        <v>0.0508125463181669</v>
       </c>
       <c r="HA24" t="n">
-        <v>0.048843562677685</v>
+        <v>0.049657853248763</v>
       </c>
       <c r="HB24" t="n">
-        <v>0.0476978155053423</v>
+        <v>0.0485045138661292</v>
       </c>
       <c r="HC24" t="n">
-        <v>0.0465615364211123</v>
+        <v>0.0473523716164033</v>
       </c>
       <c r="HD24" t="n">
-        <v>0.0454689136980274</v>
+        <v>0.0462360976056032</v>
       </c>
       <c r="HE24" t="n">
-        <v>0.0444286142300801</v>
+        <v>0.0451652129962846</v>
       </c>
       <c r="HF24" t="n">
-        <v>0.0434521637123164</v>
+        <v>0.0441520323942986</v>
       </c>
       <c r="HG24" t="n">
-        <v>0.0425387608399151</v>
+        <v>0.0431966055048977</v>
       </c>
       <c r="HH24" t="n">
-        <v>0.0416933734908824</v>
+        <v>0.0423047460047415</v>
       </c>
       <c r="HI24" t="n">
-        <v>0.0409205236773205</v>
+        <v>0.041481781362044</v>
       </c>
       <c r="HJ24" t="n">
-        <v>0.0402219527517294</v>
+        <v>0.040730217305373</v>
       </c>
       <c r="HK24" t="n">
-        <v>0.0395881114738436</v>
+        <v>0.0400412095032255</v>
       </c>
       <c r="HL24" t="n">
-        <v>0.0390210846107137</v>
+        <v>0.0394175145424152</v>
       </c>
       <c r="HM24" t="n">
-        <v>0.0385186621720079</v>
+        <v>0.0388575112073935</v>
       </c>
       <c r="HN24" t="n">
-        <v>0.0380780248360361</v>
+        <v>0.0383588932678097</v>
       </c>
       <c r="HO24" t="n">
-        <v>0.0376856181960514</v>
+        <v>0.0379085331715294</v>
       </c>
       <c r="HP24" t="n">
-        <v>0.0373329352823615</v>
+        <v>0.0374983186306434</v>
       </c>
       <c r="HQ24" t="n">
-        <v>0.0370165668771712</v>
+        <v>0.0371251805141752</v>
       </c>
       <c r="HR24" t="n">
-        <v>0.036732514439434</v>
+        <v>0.036785383674441</v>
       </c>
       <c r="HS24" t="n">
-        <v>0.0364474202213573</v>
+        <v>0.0364458235221847</v>
       </c>
       <c r="HT24" t="n">
-        <v>0.0361688262391487</v>
+        <v>0.0361142062914783</v>
       </c>
       <c r="HU24" t="n">
-        <v>0.0358863859942018</v>
+        <v>0.0357803569561626</v>
       </c>
     </row>
     <row r="25">
@@ -18329,139 +18329,139 @@
       <c r="GA25"/>
       <c r="GB25"/>
       <c r="GC25" t="n">
-        <v>0.41104884007212</v>
+        <v>0.411055361866531</v>
       </c>
       <c r="GD25" t="n">
-        <v>0.397693250220591</v>
+        <v>0.397564504015474</v>
       </c>
       <c r="GE25" t="n">
-        <v>0.385814235697723</v>
+        <v>0.385801463369563</v>
       </c>
       <c r="GF25" t="n">
-        <v>0.381088652434019</v>
+        <v>0.381070270846001</v>
       </c>
       <c r="GG25" t="n">
-        <v>0.378453186594657</v>
+        <v>0.378539109767697</v>
       </c>
       <c r="GH25" t="n">
-        <v>0.375918384439092</v>
+        <v>0.376143065908777</v>
       </c>
       <c r="GI25" t="n">
-        <v>0.373604704042022</v>
+        <v>0.373973392374181</v>
       </c>
       <c r="GJ25" t="n">
-        <v>0.36994021817173</v>
+        <v>0.370467293867481</v>
       </c>
       <c r="GK25" t="n">
-        <v>0.368031132189974</v>
+        <v>0.368712477944196</v>
       </c>
       <c r="GL25" t="n">
-        <v>0.367602048061369</v>
+        <v>0.368447321819495</v>
       </c>
       <c r="GM25" t="n">
-        <v>0.370792548008146</v>
+        <v>0.371823412334895</v>
       </c>
       <c r="GN25" t="n">
-        <v>0.369673946710972</v>
+        <v>0.370877679420827</v>
       </c>
       <c r="GO25" t="n">
-        <v>0.36909916173173</v>
+        <v>0.37048073940284</v>
       </c>
       <c r="GP25" t="n">
-        <v>0.368964010991388</v>
+        <v>0.370535676739303</v>
       </c>
       <c r="GQ25" t="n">
-        <v>0.369137000325543</v>
+        <v>0.37091473550667</v>
       </c>
       <c r="GR25" t="n">
-        <v>0.369307254470724</v>
+        <v>0.371304966532879</v>
       </c>
       <c r="GS25" t="n">
-        <v>0.369739655963767</v>
+        <v>0.371974621370414</v>
       </c>
       <c r="GT25" t="n">
-        <v>0.37033353690268</v>
+        <v>0.372819169301234</v>
       </c>
       <c r="GU25" t="n">
-        <v>0.370974250189942</v>
+        <v>0.37372332816331</v>
       </c>
       <c r="GV25" t="n">
-        <v>0.371534932507843</v>
+        <v>0.374552183162383</v>
       </c>
       <c r="GW25" t="n">
-        <v>0.372019157128132</v>
+        <v>0.375308784631339</v>
       </c>
       <c r="GX25" t="n">
-        <v>0.372366972033463</v>
+        <v>0.375927222505698</v>
       </c>
       <c r="GY25" t="n">
-        <v>0.372544549725455</v>
+        <v>0.376370112337683</v>
       </c>
       <c r="GZ25" t="n">
-        <v>0.372527215005814</v>
+        <v>0.376608411010761</v>
       </c>
       <c r="HA25" t="n">
-        <v>0.37228520118805</v>
+        <v>0.376608523758739</v>
       </c>
       <c r="HB25" t="n">
-        <v>0.371879385149547</v>
+        <v>0.376426801826615</v>
       </c>
       <c r="HC25" t="n">
-        <v>0.371293262842694</v>
+        <v>0.376049121737037</v>
       </c>
       <c r="HD25" t="n">
-        <v>0.370536826364937</v>
+        <v>0.375476235429661</v>
       </c>
       <c r="HE25" t="n">
-        <v>0.369589354789083</v>
+        <v>0.374692150895481</v>
       </c>
       <c r="HF25" t="n">
-        <v>0.368470782747992</v>
+        <v>0.373713075435714</v>
       </c>
       <c r="HG25" t="n">
-        <v>0.367216560053892</v>
+        <v>0.372575338301338</v>
       </c>
       <c r="HH25" t="n">
-        <v>0.365837600724231</v>
+        <v>0.371289653092655</v>
       </c>
       <c r="HI25" t="n">
-        <v>0.364388881656024</v>
+        <v>0.369912024737157</v>
       </c>
       <c r="HJ25" t="n">
-        <v>0.362888542044528</v>
+        <v>0.368461634599269</v>
       </c>
       <c r="HK25" t="n">
-        <v>0.361364728574739</v>
+        <v>0.36696814296447</v>
       </c>
       <c r="HL25" t="n">
-        <v>0.359820010005107</v>
+        <v>0.365435027462415</v>
       </c>
       <c r="HM25" t="n">
-        <v>0.358321290401191</v>
+        <v>0.363931616621715</v>
       </c>
       <c r="HN25" t="n">
-        <v>0.356881502669775</v>
+        <v>0.362472484531083</v>
       </c>
       <c r="HO25" t="n">
-        <v>0.355511041439176</v>
+        <v>0.36106982648693</v>
       </c>
       <c r="HP25" t="n">
-        <v>0.354214361396232</v>
+        <v>0.359729425467946</v>
       </c>
       <c r="HQ25" t="n">
-        <v>0.353002347583564</v>
+        <v>0.358463665691843</v>
       </c>
       <c r="HR25" t="n">
-        <v>0.351875632998343</v>
+        <v>0.357274560110373</v>
       </c>
       <c r="HS25" t="n">
-        <v>0.350855646313728</v>
+        <v>0.356189524977682</v>
       </c>
       <c r="HT25" t="n">
-        <v>0.349911126075008</v>
+        <v>0.355169937279026</v>
       </c>
       <c r="HU25" t="n">
-        <v>0.349057110303104</v>
+        <v>0.3542386299792</v>
       </c>
     </row>
     <row r="26">
@@ -19018,139 +19018,139 @@
         <v>0.653633333333333</v>
       </c>
       <c r="GC26" t="n">
-        <v>0.667380773125949</v>
+        <v>0.667386922597105</v>
       </c>
       <c r="GD26" t="n">
-        <v>0.642374063301982</v>
+        <v>0.642265803309994</v>
       </c>
       <c r="GE26" t="n">
-        <v>0.619573902194374</v>
+        <v>0.619534909343541</v>
       </c>
       <c r="GF26" t="n">
-        <v>0.608982928278637</v>
+        <v>0.608953726937546</v>
       </c>
       <c r="GG26" t="n">
-        <v>0.601632101168693</v>
+        <v>0.601699020313382</v>
       </c>
       <c r="GH26" t="n">
-        <v>0.594588178417656</v>
+        <v>0.594806071749658</v>
       </c>
       <c r="GI26" t="n">
-        <v>0.587980149695304</v>
+        <v>0.588355473462683</v>
       </c>
       <c r="GJ26" t="n">
-        <v>0.57925505813352</v>
+        <v>0.579812837238533</v>
       </c>
       <c r="GK26" t="n">
-        <v>0.573418923587722</v>
+        <v>0.574153106604152</v>
       </c>
       <c r="GL26" t="n">
-        <v>0.569978389844927</v>
+        <v>0.570899809227844</v>
       </c>
       <c r="GM26" t="n">
-        <v>0.572328500590182</v>
+        <v>0.573462710951917</v>
       </c>
       <c r="GN26" t="n">
-        <v>0.56789502884128</v>
+        <v>0.569233989949267</v>
       </c>
       <c r="GO26" t="n">
-        <v>0.564371530668375</v>
+        <v>0.565926495476232</v>
       </c>
       <c r="GP26" t="n">
-        <v>0.561553827262834</v>
+        <v>0.563343451038879</v>
       </c>
       <c r="GQ26" t="n">
-        <v>0.559249859414171</v>
+        <v>0.56129802653135</v>
       </c>
       <c r="GR26" t="n">
-        <v>0.556979351089894</v>
+        <v>0.559308855410215</v>
       </c>
       <c r="GS26" t="n">
-        <v>0.555136986142704</v>
+        <v>0.557773194584175</v>
       </c>
       <c r="GT26" t="n">
-        <v>0.553552923870564</v>
+        <v>0.556516179841725</v>
       </c>
       <c r="GU26" t="n">
-        <v>0.552049835433366</v>
+        <v>0.555357661421977</v>
       </c>
       <c r="GV26" t="n">
-        <v>0.550452228406873</v>
+        <v>0.554112663421072</v>
       </c>
       <c r="GW26" t="n">
-        <v>0.548743919318344</v>
+        <v>0.55276168784498</v>
       </c>
       <c r="GX26" t="n">
-        <v>0.546832879867364</v>
+        <v>0.551204783371838</v>
       </c>
       <c r="GY26" t="n">
-        <v>0.544678787082129</v>
+        <v>0.549395854405325</v>
       </c>
       <c r="GZ26" t="n">
-        <v>0.54224645872236</v>
+        <v>0.547293771354329</v>
       </c>
       <c r="HA26" t="n">
-        <v>0.539492355248509</v>
+        <v>0.544849288222467</v>
       </c>
       <c r="HB26" t="n">
-        <v>0.536438658458349</v>
+        <v>0.5420781892058</v>
       </c>
       <c r="HC26" t="n">
-        <v>0.53311647441432</v>
+        <v>0.53901301772219</v>
       </c>
       <c r="HD26" t="n">
-        <v>0.529589755574338</v>
+        <v>0.535709291707776</v>
       </c>
       <c r="HE26" t="n">
-        <v>0.525780896047806</v>
+        <v>0.532092182943127</v>
       </c>
       <c r="HF26" t="n">
-        <v>0.521747224698475</v>
+        <v>0.528216040056358</v>
       </c>
       <c r="HG26" t="n">
-        <v>0.517539705234665</v>
+        <v>0.524132828682307</v>
       </c>
       <c r="HH26" t="n">
-        <v>0.513177332329158</v>
+        <v>0.519861995169055</v>
       </c>
       <c r="HI26" t="n">
-        <v>0.508738841710196</v>
+        <v>0.515483794599243</v>
       </c>
       <c r="HJ26" t="n">
-        <v>0.504251117009003</v>
+        <v>0.511026799795606</v>
       </c>
       <c r="HK26" t="n">
-        <v>0.499757646987545</v>
+        <v>0.506536845934151</v>
       </c>
       <c r="HL26" t="n">
-        <v>0.495261561493041</v>
+        <v>0.502018975359536</v>
       </c>
       <c r="HM26" t="n">
-        <v>0.490855161989614</v>
+        <v>0.497568759200159</v>
       </c>
       <c r="HN26" t="n">
-        <v>0.486555397506421</v>
+        <v>0.493205552612968</v>
       </c>
       <c r="HO26" t="n">
-        <v>0.482378767131528</v>
+        <v>0.488948505263574</v>
       </c>
       <c r="HP26" t="n">
-        <v>0.478329895111603</v>
+        <v>0.484804547205776</v>
       </c>
       <c r="HQ26" t="n">
-        <v>0.474420472379776</v>
+        <v>0.480787405882121</v>
       </c>
       <c r="HR26" t="n">
-        <v>0.470649383793212</v>
+        <v>0.47689786802077</v>
       </c>
       <c r="HS26" t="n">
-        <v>0.467018846630223</v>
+        <v>0.473144142016137</v>
       </c>
       <c r="HT26" t="n">
-        <v>0.463548000676459</v>
+        <v>0.469540584718753</v>
       </c>
       <c r="HU26" t="n">
-        <v>0.460195369056035</v>
+        <v>0.466051853564763</v>
       </c>
     </row>
     <row r="27">
@@ -19707,139 +19707,139 @@
         <v>95.2225040638737</v>
       </c>
       <c r="GC27" t="n">
-        <v>93.6634782988197</v>
+        <v>93.6743249298867</v>
       </c>
       <c r="GD27" t="n">
-        <v>95.0987768736497</v>
+        <v>94.8742527922511</v>
       </c>
       <c r="GE27" t="n">
-        <v>96.4617297778711</v>
+        <v>96.5107824808816</v>
       </c>
       <c r="GF27" t="n">
-        <v>97.3248576645324</v>
+        <v>97.330519996262</v>
       </c>
       <c r="GG27" t="n">
-        <v>98.3483765500985</v>
+        <v>98.5307020647199</v>
       </c>
       <c r="GH27" t="n">
-        <v>98.5907632151609</v>
+        <v>98.9471611089672</v>
       </c>
       <c r="GI27" t="n">
-        <v>98.7276406539345</v>
+        <v>99.2598842239717</v>
       </c>
       <c r="GJ27" t="n">
-        <v>98.8918004662197</v>
+        <v>99.5913708812774</v>
       </c>
       <c r="GK27" t="n">
-        <v>98.9922345948615</v>
+        <v>99.8505004816782</v>
       </c>
       <c r="GL27" t="n">
-        <v>98.992343938236</v>
+        <v>100.012759968698</v>
       </c>
       <c r="GM27" t="n">
-        <v>98.8593328470086</v>
+        <v>100.050004348195</v>
       </c>
       <c r="GN27" t="n">
-        <v>98.829389326441</v>
+        <v>100.160891309279</v>
       </c>
       <c r="GO27" t="n">
-        <v>98.791184846636</v>
+        <v>100.245995750179</v>
       </c>
       <c r="GP27" t="n">
-        <v>98.7735085378068</v>
+        <v>100.345850362412</v>
       </c>
       <c r="GQ27" t="n">
-        <v>98.7497600736996</v>
+        <v>100.435236881462</v>
       </c>
       <c r="GR27" t="n">
-        <v>98.7187753132185</v>
+        <v>100.50636673308</v>
       </c>
       <c r="GS27" t="n">
-        <v>98.6858206737084</v>
+        <v>100.571380013477</v>
       </c>
       <c r="GT27" t="n">
-        <v>98.6903659307074</v>
+        <v>100.665924842129</v>
       </c>
       <c r="GU27" t="n">
-        <v>98.7100325132375</v>
+        <v>100.773954343196</v>
       </c>
       <c r="GV27" t="n">
-        <v>98.7223534761881</v>
+        <v>100.862828786901</v>
       </c>
       <c r="GW27" t="n">
-        <v>98.7495623373757</v>
+        <v>100.964304560494</v>
       </c>
       <c r="GX27" t="n">
-        <v>98.788425116625</v>
+        <v>101.070595404254</v>
       </c>
       <c r="GY27" t="n">
-        <v>98.8315213741247</v>
+        <v>101.176536909438</v>
       </c>
       <c r="GZ27" t="n">
-        <v>98.8786219686643</v>
+        <v>101.280852151854</v>
       </c>
       <c r="HA27" t="n">
-        <v>98.9295297477021</v>
+        <v>101.384064023186</v>
       </c>
       <c r="HB27" t="n">
-        <v>99.1007943747267</v>
+        <v>101.601465686942</v>
       </c>
       <c r="HC27" t="n">
-        <v>99.2970882930298</v>
+        <v>101.847518436889</v>
       </c>
       <c r="HD27" t="n">
-        <v>99.4636696076803</v>
+        <v>102.048761262252</v>
       </c>
       <c r="HE27" t="n">
-        <v>99.6621843109</v>
+        <v>102.285603502334</v>
       </c>
       <c r="HF27" t="n">
-        <v>99.8579026224858</v>
+        <v>102.513925399895</v>
       </c>
       <c r="HG27" t="n">
-        <v>100.055543185995</v>
+        <v>102.741701497834</v>
       </c>
       <c r="HH27" t="n">
-        <v>100.25282689744</v>
+        <v>102.965738116741</v>
       </c>
       <c r="HI27" t="n">
-        <v>100.448634493837</v>
+        <v>103.18550404438</v>
       </c>
       <c r="HJ27" t="n">
-        <v>100.641643636595</v>
+        <v>103.399950266852</v>
       </c>
       <c r="HK27" t="n">
-        <v>100.829229922154</v>
+        <v>103.607051968022</v>
       </c>
       <c r="HL27" t="n">
-        <v>101.012776855744</v>
+        <v>103.807796049471</v>
       </c>
       <c r="HM27" t="n">
-        <v>101.191062540303</v>
+        <v>104.001450488044</v>
       </c>
       <c r="HN27" t="n">
-        <v>101.363906485268</v>
+        <v>104.188088147456</v>
       </c>
       <c r="HO27" t="n">
-        <v>101.529199904779</v>
+        <v>104.366057376482</v>
       </c>
       <c r="HP27" t="n">
-        <v>101.689404753351</v>
+        <v>104.537473884861</v>
       </c>
       <c r="HQ27" t="n">
-        <v>101.844679468849</v>
+        <v>104.702571549126</v>
       </c>
       <c r="HR27" t="n">
-        <v>101.995164080287</v>
+        <v>104.861684050827</v>
       </c>
       <c r="HS27" t="n">
-        <v>102.182007986739</v>
+        <v>105.066581927777</v>
       </c>
       <c r="HT27" t="n">
-        <v>102.313555851495</v>
+        <v>105.202502021531</v>
       </c>
       <c r="HU27" t="n">
-        <v>102.478704114697</v>
+        <v>105.379475633708</v>
       </c>
     </row>
     <row r="28">
@@ -20208,139 +20208,139 @@
       <c r="GA28"/>
       <c r="GB28"/>
       <c r="GC28" t="n">
-        <v>14.983127754949</v>
+        <v>14.9825957220847</v>
       </c>
       <c r="GD28" t="n">
-        <v>14.7803903595972</v>
+        <v>14.7999522910792</v>
       </c>
       <c r="GE28" t="n">
-        <v>14.9975773940315</v>
+        <v>15.0045938735138</v>
       </c>
       <c r="GF28" t="n">
-        <v>15.0840162906029</v>
+        <v>15.0960140075995</v>
       </c>
       <c r="GG28" t="n">
-        <v>15.0912173015564</v>
+        <v>15.0926637755266</v>
       </c>
       <c r="GH28" t="n">
-        <v>15.2058281693194</v>
+        <v>15.1964159162555</v>
       </c>
       <c r="GI28" t="n">
-        <v>15.4060420853197</v>
+        <v>15.3831351717457</v>
       </c>
       <c r="GJ28" t="n">
-        <v>15.9353075045993</v>
+        <v>15.8992042529269</v>
       </c>
       <c r="GK28" t="n">
-        <v>16.1617607135596</v>
+        <v>16.1128382871909</v>
       </c>
       <c r="GL28" t="n">
-        <v>16.4448853475277</v>
+        <v>16.3843279628453</v>
       </c>
       <c r="GM28" t="n">
-        <v>16.7754574103949</v>
+        <v>16.7040802781067</v>
       </c>
       <c r="GN28" t="n">
-        <v>17.3877198095368</v>
+        <v>17.3087030178455</v>
       </c>
       <c r="GO28" t="n">
-        <v>17.6377639873403</v>
+        <v>17.5534909280176</v>
       </c>
       <c r="GP28" t="n">
-        <v>17.9056080519334</v>
+        <v>17.8185668493054</v>
       </c>
       <c r="GQ28" t="n">
-        <v>18.200573911669</v>
+        <v>18.1124704559156</v>
       </c>
       <c r="GR28" t="n">
-        <v>18.802930674972</v>
+        <v>18.7158060516601</v>
       </c>
       <c r="GS28" t="n">
-        <v>19.0038871351117</v>
+        <v>18.919132258165</v>
       </c>
       <c r="GT28" t="n">
-        <v>19.2102510849767</v>
+        <v>19.1293571923977</v>
       </c>
       <c r="GU28" t="n">
-        <v>19.4420453026036</v>
+        <v>19.3659397504562</v>
       </c>
       <c r="GV28" t="n">
-        <v>20.0058503799694</v>
+        <v>19.9358634751398</v>
       </c>
       <c r="GW28" t="n">
-        <v>20.1320990776394</v>
+        <v>20.0687442754496</v>
       </c>
       <c r="GX28" t="n">
-        <v>20.26824519207</v>
+        <v>20.212245786015</v>
       </c>
       <c r="GY28" t="n">
-        <v>20.4231243884187</v>
+        <v>20.3749845637636</v>
       </c>
       <c r="GZ28" t="n">
-        <v>20.9395538277723</v>
+        <v>20.9001680645872</v>
       </c>
       <c r="HA28" t="n">
-        <v>20.9814714044155</v>
+        <v>20.950538107274</v>
       </c>
       <c r="HB28" t="n">
-        <v>21.0249942736124</v>
+        <v>21.0027871410428</v>
       </c>
       <c r="HC28" t="n">
-        <v>21.111099369573</v>
+        <v>21.0975328293665</v>
       </c>
       <c r="HD28" t="n">
-        <v>21.5689018785568</v>
+        <v>21.5651478717183</v>
       </c>
       <c r="HE28" t="n">
-        <v>21.5421741182314</v>
+        <v>21.5469189032454</v>
       </c>
       <c r="HF28" t="n">
-        <v>21.5395534945287</v>
+        <v>21.5527894164564</v>
       </c>
       <c r="HG28" t="n">
-        <v>21.5739011510106</v>
+        <v>21.5954884540862</v>
       </c>
       <c r="HH28" t="n">
-        <v>22.0332003604323</v>
+        <v>22.0641594417065</v>
       </c>
       <c r="HI28" t="n">
-        <v>21.9742491875876</v>
+        <v>22.012791700335</v>
       </c>
       <c r="HJ28" t="n">
-        <v>21.9519619669646</v>
+        <v>21.9978986269347</v>
       </c>
       <c r="HK28" t="n">
-        <v>21.9736622493362</v>
+        <v>22.0268218958148</v>
       </c>
       <c r="HL28" t="n">
-        <v>22.4470889287171</v>
+        <v>22.5087038868661</v>
       </c>
       <c r="HM28" t="n">
-        <v>22.3793486862437</v>
+        <v>22.4472269206339</v>
       </c>
       <c r="HN28" t="n">
-        <v>22.3545343720046</v>
+        <v>22.4285008541476</v>
       </c>
       <c r="HO28" t="n">
-        <v>22.3804810321742</v>
+        <v>22.4604043350345</v>
       </c>
       <c r="HP28" t="n">
-        <v>22.8900058842432</v>
+        <v>22.9773644183049</v>
       </c>
       <c r="HQ28" t="n">
-        <v>22.832746983037</v>
+        <v>22.9250847863669</v>
       </c>
       <c r="HR28" t="n">
-        <v>22.8236030741114</v>
+        <v>22.9208322110601</v>
       </c>
       <c r="HS28" t="n">
-        <v>22.8992078179666</v>
+        <v>23.0010444852556</v>
       </c>
       <c r="HT28" t="n">
-        <v>23.4567188794245</v>
+        <v>23.5650462991482</v>
       </c>
       <c r="HU28" t="n">
-        <v>23.4370680699504</v>
+        <v>23.5491931698423</v>
       </c>
     </row>
     <row r="29">
@@ -20709,139 +20709,139 @@
       <c r="GA29"/>
       <c r="GB29"/>
       <c r="GC29" t="n">
-        <v>0.0000207394344915839</v>
+        <v>0.0000207381340679747</v>
       </c>
       <c r="GD29" t="n">
-        <v>0.0000197905312973904</v>
+        <v>0.0000198342653316777</v>
       </c>
       <c r="GE29" t="n">
-        <v>0.0000197906161365319</v>
+        <v>0.000019801387341299</v>
       </c>
       <c r="GF29" t="n">
-        <v>0.0000193789338339758</v>
+        <v>0.0000193997587924959</v>
       </c>
       <c r="GG29" t="n">
-        <v>0.0000190103441865362</v>
+        <v>0.000019008434778568</v>
       </c>
       <c r="GH29" t="n">
-        <v>0.0000188193093243792</v>
+        <v>0.0000187961107405041</v>
       </c>
       <c r="GI29" t="n">
-        <v>0.0000187464669447118</v>
+        <v>0.0000186989168087843</v>
       </c>
       <c r="GJ29" t="n">
-        <v>0.0000190909747353957</v>
+        <v>0.0000190201224156104</v>
       </c>
       <c r="GK29" t="n">
-        <v>0.0000190577091426354</v>
+        <v>0.0000189654452163311</v>
       </c>
       <c r="GL29" t="n">
-        <v>0.000019097474012002</v>
+        <v>0.0000189858152314239</v>
       </c>
       <c r="GM29" t="n">
-        <v>0.0000192027288893175</v>
+        <v>0.0000190726860810582</v>
       </c>
       <c r="GN29" t="n">
-        <v>0.0000196458239589605</v>
+        <v>0.0000195018286235175</v>
       </c>
       <c r="GO29" t="n">
-        <v>0.0000196626368447814</v>
+        <v>0.0000195094381467399</v>
       </c>
       <c r="GP29" t="n">
-        <v>0.0000196945649677487</v>
+        <v>0.0000195358576472083</v>
       </c>
       <c r="GQ29" t="n">
-        <v>0.0000197681777530293</v>
+        <v>0.000019605995133832</v>
       </c>
       <c r="GR29" t="n">
-        <v>0.000020164702507549</v>
+        <v>0.0000200009571721835</v>
       </c>
       <c r="GS29" t="n">
-        <v>0.0000201279226615855</v>
+        <v>0.0000199659281528003</v>
       </c>
       <c r="GT29" t="n">
-        <v>0.0000200947409562826</v>
+        <v>0.0000199366699300258</v>
       </c>
       <c r="GU29" t="n">
-        <v>0.0000200995384474414</v>
+        <v>0.0000199463772040787</v>
       </c>
       <c r="GV29" t="n">
-        <v>0.0000204350417534602</v>
+        <v>0.0000202875290881038</v>
       </c>
       <c r="GW29" t="n">
-        <v>0.0000203192419935866</v>
+        <v>0.0000201797756013834</v>
       </c>
       <c r="GX29" t="n">
-        <v>0.0000202107338579941</v>
+        <v>0.000020080337656843</v>
       </c>
       <c r="GY29" t="n">
-        <v>0.0000201261056186063</v>
+        <v>0.0000200053214494917</v>
       </c>
       <c r="GZ29" t="n">
-        <v>0.0000203882653505999</v>
+        <v>0.0000202768983059243</v>
       </c>
       <c r="HA29" t="n">
-        <v>0.0000201804750042718</v>
+        <v>0.0000200800091091854</v>
       </c>
       <c r="HB29" t="n">
-        <v>0.0000199676484495848</v>
+        <v>0.0000198785372218195</v>
       </c>
       <c r="HC29" t="n">
-        <v>0.0000198103214102994</v>
+        <v>0.000019731961031906</v>
       </c>
       <c r="HD29" t="n">
-        <v>0.0000199830746249604</v>
+        <v>0.0000199157593352284</v>
       </c>
       <c r="HE29" t="n">
-        <v>0.0000197072406229643</v>
+        <v>0.0000196508739026891</v>
       </c>
       <c r="HF29" t="n">
-        <v>0.00001945347546865</v>
+        <v>0.0000194078659628971</v>
       </c>
       <c r="HG29" t="n">
-        <v>0.0000192408226979566</v>
+        <v>0.000019205500245034</v>
       </c>
       <c r="HH29" t="n">
-        <v>0.000019401903130025</v>
+        <v>0.0000193765609078537</v>
       </c>
       <c r="HI29" t="n">
-        <v>0.0000191014161046376</v>
+        <v>0.000019085542664582</v>
       </c>
       <c r="HJ29" t="n">
-        <v>0.0000188351259139793</v>
+        <v>0.0000188282310453023</v>
       </c>
       <c r="HK29" t="n">
-        <v>0.0000186154137207201</v>
+        <v>0.0000186169951108829</v>
       </c>
       <c r="HL29" t="n">
-        <v>0.0000187735568231981</v>
+        <v>0.0000187835857091887</v>
       </c>
       <c r="HM29" t="n">
-        <v>0.0000184750035153544</v>
+        <v>0.0000184924465238902</v>
       </c>
       <c r="HN29" t="n">
-        <v>0.0000182151013835879</v>
+        <v>0.0000182394952950356</v>
       </c>
       <c r="HO29" t="n">
-        <v>0.0000180060059031652</v>
+        <v>0.0000180369223374406</v>
       </c>
       <c r="HP29" t="n">
-        <v>0.0000181825427781046</v>
+        <v>0.0000182202727000452</v>
       </c>
       <c r="HQ29" t="n">
-        <v>0.0000179049230777864</v>
+        <v>0.0000179481206674002</v>
       </c>
       <c r="HR29" t="n">
-        <v>0.0000176682885608517</v>
+        <v>0.0000177166176613099</v>
       </c>
       <c r="HS29" t="n">
-        <v>0.0000175167599695691</v>
+        <v>0.000017569524706651</v>
       </c>
       <c r="HT29" t="n">
-        <v>0.0000177183120674057</v>
+        <v>0.0000177765231324174</v>
       </c>
       <c r="HU29" t="n">
-        <v>0.0000174866693511948</v>
+        <v>0.0000175485873788497</v>
       </c>
     </row>
     <row r="30">
@@ -21210,139 +21210,139 @@
       <c r="GA30"/>
       <c r="GB30"/>
       <c r="GC30" t="n">
-        <v>844.857393096416</v>
+        <v>844.856861063552</v>
       </c>
       <c r="GD30" t="n">
-        <v>864.333783412066</v>
+        <v>864.352810353467</v>
       </c>
       <c r="GE30" t="n">
-        <v>884.209196412328</v>
+        <v>884.235347211048</v>
       </c>
       <c r="GF30" t="n">
-        <v>904.095972371918</v>
+        <v>904.134262930945</v>
       </c>
       <c r="GG30" t="n">
-        <v>924.112901718491</v>
+        <v>924.152847366806</v>
       </c>
       <c r="GH30" t="n">
-        <v>944.252245903314</v>
+        <v>944.28303536361</v>
       </c>
       <c r="GI30" t="n">
-        <v>964.680988902812</v>
+        <v>964.687442255001</v>
       </c>
       <c r="GJ30" t="n">
-        <v>985.779613810254</v>
+        <v>985.747092474335</v>
       </c>
       <c r="GK30" t="n">
-        <v>1007.3164373272</v>
+        <v>1007.23015507212</v>
       </c>
       <c r="GL30" t="n">
-        <v>1029.40747016669</v>
+        <v>1029.25418689355</v>
       </c>
       <c r="GM30" t="n">
-        <v>1052.14434080662</v>
+        <v>1051.91245745069</v>
       </c>
       <c r="GN30" t="n">
-        <v>1075.84467654775</v>
+        <v>1075.52694509536</v>
       </c>
       <c r="GO30" t="n">
-        <v>1100.16772181489</v>
+        <v>1099.76086495108</v>
       </c>
       <c r="GP30" t="n">
-        <v>1125.14102025324</v>
+        <v>1124.64603253928</v>
       </c>
       <c r="GQ30" t="n">
-        <v>1150.79145968704</v>
+        <v>1150.21294771361</v>
       </c>
       <c r="GR30" t="n">
-        <v>1177.41639856821</v>
+        <v>1176.76295560897</v>
       </c>
       <c r="GS30" t="n">
-        <v>1204.59089680344</v>
+        <v>1203.87434071864</v>
       </c>
       <c r="GT30" t="n">
-        <v>1232.28833790601</v>
+        <v>1231.52355276949</v>
       </c>
       <c r="GU30" t="n">
-        <v>1260.49883326554</v>
+        <v>1259.70282230761</v>
       </c>
       <c r="GV30" t="n">
-        <v>1289.51566402772</v>
+        <v>1288.70761542911</v>
       </c>
       <c r="GW30" t="n">
-        <v>1318.86657295767</v>
+        <v>1318.06663504328</v>
       </c>
       <c r="GX30" t="n">
-        <v>1348.52417812866</v>
+        <v>1347.75329382916</v>
       </c>
       <c r="GY30" t="n">
-        <v>1378.47229955193</v>
+        <v>1377.75161791624</v>
       </c>
       <c r="GZ30" t="n">
-        <v>1409.03779566882</v>
+        <v>1408.38878270047</v>
       </c>
       <c r="HA30" t="n">
-        <v>1439.71726025337</v>
+        <v>1439.16023127404</v>
       </c>
       <c r="HB30" t="n">
-        <v>1470.48328411215</v>
+        <v>1470.03769615077</v>
       </c>
       <c r="HC30" t="n">
-        <v>1501.35349218839</v>
+        <v>1501.03736752869</v>
       </c>
       <c r="HD30" t="n">
-        <v>1532.67743875187</v>
+        <v>1532.50846950798</v>
       </c>
       <c r="HE30" t="n">
-        <v>1563.95644986627</v>
+        <v>1563.94942587629</v>
       </c>
       <c r="HF30" t="n">
-        <v>1595.20181140767</v>
+        <v>1595.36978843082</v>
       </c>
       <c r="HG30" t="n">
-        <v>1626.44320479327</v>
+        <v>1626.79730763524</v>
       </c>
       <c r="HH30" t="n">
-        <v>1658.09841757735</v>
+        <v>1658.6490372459</v>
       </c>
       <c r="HI30" t="n">
-        <v>1689.65176422192</v>
+        <v>1690.40578644993</v>
       </c>
       <c r="HJ30" t="n">
-        <v>1721.14177810274</v>
+        <v>1722.10419896403</v>
       </c>
       <c r="HK30" t="n">
-        <v>1752.61771900901</v>
+        <v>1753.79174839532</v>
       </c>
       <c r="HL30" t="n">
-        <v>1784.53746339255</v>
+        <v>1785.92604210347</v>
       </c>
       <c r="HM30" t="n">
-        <v>1816.37030741311</v>
+        <v>1817.97284986802</v>
       </c>
       <c r="HN30" t="n">
-        <v>1848.16860925506</v>
+        <v>1849.98309331301</v>
       </c>
       <c r="HO30" t="n">
-        <v>1879.99414437871</v>
+        <v>1882.01729421627</v>
       </c>
       <c r="HP30" t="n">
-        <v>1912.34044477028</v>
+        <v>1914.56947615472</v>
       </c>
       <c r="HQ30" t="n">
-        <v>1944.65441243558</v>
+        <v>1947.0832685462</v>
       </c>
       <c r="HR30" t="n">
-        <v>1976.99530624875</v>
+        <v>1979.61710677482</v>
       </c>
       <c r="HS30" t="n">
-        <v>2009.45939921153</v>
+        <v>2012.26636630844</v>
       </c>
       <c r="HT30" t="n">
-        <v>2042.53787959955</v>
+        <v>2045.52360791217</v>
       </c>
       <c r="HU30" t="n">
-        <v>2075.66356861948</v>
+        <v>2078.81856753088</v>
       </c>
     </row>
     <row r="31">
@@ -22016,7 +22016,7 @@
         <v>0.043535305024288</v>
       </c>
       <c r="HP31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0435353050242881</v>
       </c>
       <c r="HQ31" t="n">
         <v>0.043535305024288</v>
@@ -22025,13 +22025,13 @@
         <v>0.043535305024288</v>
       </c>
       <c r="HS31" t="n">
+        <v>0.0435353050242881</v>
+      </c>
+      <c r="HT31" t="n">
+        <v>0.0435353050242881</v>
+      </c>
+      <c r="HU31" t="n">
         <v>0.043535305024288</v>
-      </c>
-      <c r="HT31" t="n">
-        <v>0.043535305024288</v>
-      </c>
-      <c r="HU31" t="n">
-        <v>0.0435353050242881</v>
       </c>
     </row>
     <row r="32">
@@ -22588,139 +22588,139 @@
         <v>0.233491652414238</v>
       </c>
       <c r="GC32" t="n">
-        <v>0.236936917858813</v>
+        <v>0.236930433634667</v>
       </c>
       <c r="GD32" t="n">
-        <v>0.232440005051002</v>
+        <v>0.232655001031785</v>
       </c>
       <c r="GE32" t="n">
-        <v>0.233394095713182</v>
+        <v>0.233411142269931</v>
       </c>
       <c r="GF32" t="n">
-        <v>0.230667800208296</v>
+        <v>0.23073739522142</v>
       </c>
       <c r="GG32" t="n">
-        <v>0.230145926981288</v>
+        <v>0.230101821454184</v>
       </c>
       <c r="GH32" t="n">
-        <v>0.229913521090224</v>
+        <v>0.229777607132103</v>
       </c>
       <c r="GI32" t="n">
-        <v>0.229930659040657</v>
+        <v>0.229698723668434</v>
       </c>
       <c r="GJ32" t="n">
-        <v>0.230154653255076</v>
+        <v>0.229840295037597</v>
       </c>
       <c r="GK32" t="n">
-        <v>0.230280819329806</v>
+        <v>0.229893730325423</v>
       </c>
       <c r="GL32" t="n">
-        <v>0.230549729084501</v>
+        <v>0.230098248460385</v>
       </c>
       <c r="GM32" t="n">
-        <v>0.231011972953985</v>
+        <v>0.230498734625617</v>
       </c>
       <c r="GN32" t="n">
-        <v>0.231097590740446</v>
+        <v>0.230547797064099</v>
       </c>
       <c r="GO32" t="n">
-        <v>0.231024871649847</v>
+        <v>0.230451383621005</v>
       </c>
       <c r="GP32" t="n">
-        <v>0.23093327647818</v>
+        <v>0.230350469159198</v>
       </c>
       <c r="GQ32" t="n">
-        <v>0.231028278295552</v>
+        <v>0.230442437648382</v>
       </c>
       <c r="GR32" t="n">
-        <v>0.231071807851752</v>
+        <v>0.230496262484992</v>
       </c>
       <c r="GS32" t="n">
-        <v>0.231159963945165</v>
+        <v>0.230601724083885</v>
       </c>
       <c r="GT32" t="n">
-        <v>0.231224045259924</v>
+        <v>0.230693610102124</v>
       </c>
       <c r="GU32" t="n">
-        <v>0.2314536035562</v>
+        <v>0.230956216627356</v>
       </c>
       <c r="GV32" t="n">
-        <v>0.231598365231694</v>
+        <v>0.231144455298809</v>
       </c>
       <c r="GW32" t="n">
-        <v>0.23174926686297</v>
+        <v>0.231344314740483</v>
       </c>
       <c r="GX32" t="n">
-        <v>0.231850529480019</v>
+        <v>0.231501629685755</v>
       </c>
       <c r="GY32" t="n">
-        <v>0.232015985081798</v>
+        <v>0.231727928536643</v>
       </c>
       <c r="GZ32" t="n">
-        <v>0.232115845808949</v>
+        <v>0.231893864641347</v>
       </c>
       <c r="HA32" t="n">
-        <v>0.23215510043353</v>
+        <v>0.23200311807709</v>
       </c>
       <c r="HB32" t="n">
-        <v>0.232079083138703</v>
+        <v>0.232002286297776</v>
       </c>
       <c r="HC32" t="n">
-        <v>0.232181219046773</v>
+        <v>0.232178725408374</v>
       </c>
       <c r="HD32" t="n">
-        <v>0.23205374190888</v>
+        <v>0.232131443626714</v>
       </c>
       <c r="HE32" t="n">
-        <v>0.231969097682149</v>
+        <v>0.23212561422437</v>
       </c>
       <c r="HF32" t="n">
-        <v>0.231823833801955</v>
+        <v>0.23206051947183</v>
       </c>
       <c r="HG32" t="n">
-        <v>0.231745626341952</v>
+        <v>0.232062249034204</v>
       </c>
       <c r="HH32" t="n">
-        <v>0.231616667463376</v>
+        <v>0.232013120222383</v>
       </c>
       <c r="HI32" t="n">
-        <v>0.231434488451571</v>
+        <v>0.231910106997469</v>
       </c>
       <c r="HJ32" t="n">
-        <v>0.231223799946128</v>
+        <v>0.231777607685055</v>
       </c>
       <c r="HK32" t="n">
-        <v>0.231088497714667</v>
+        <v>0.231719183998638</v>
       </c>
       <c r="HL32" t="n">
-        <v>0.23090546943586</v>
+        <v>0.23161159343475</v>
       </c>
       <c r="HM32" t="n">
-        <v>0.230682968355973</v>
+        <v>0.231462747751042</v>
       </c>
       <c r="HN32" t="n">
-        <v>0.230443095825101</v>
+        <v>0.231294602874975</v>
       </c>
       <c r="HO32" t="n">
-        <v>0.23029165144271</v>
+        <v>0.231212934544571</v>
       </c>
       <c r="HP32" t="n">
-        <v>0.230117035228003</v>
+        <v>0.231105916431139</v>
       </c>
       <c r="HQ32" t="n">
-        <v>0.229906984404075</v>
+        <v>0.230961176979868</v>
       </c>
       <c r="HR32" t="n">
-        <v>0.229688106339886</v>
+        <v>0.230805337934807</v>
       </c>
       <c r="HS32" t="n">
-        <v>0.229728897477132</v>
+        <v>0.230905009810835</v>
       </c>
       <c r="HT32" t="n">
-        <v>0.229565264581598</v>
+        <v>0.230800530047243</v>
       </c>
       <c r="HU32" t="n">
-        <v>0.229493295977955</v>
+        <v>0.23078380194875</v>
       </c>
     </row>
     <row r="33">
@@ -23109,139 +23109,139 @@
         <v>82599</v>
       </c>
       <c r="GC33" t="n">
-        <v>82724.1708895037</v>
+        <v>82701.4172494172</v>
       </c>
       <c r="GD33" t="n">
-        <v>84465.7654016171</v>
+        <v>84174.3503022568</v>
       </c>
       <c r="GE33" t="n">
-        <v>85786.2650977703</v>
+        <v>85528.2186641719</v>
       </c>
       <c r="GF33" t="n">
-        <v>87450.5632784499</v>
+        <v>87098.0990920393</v>
       </c>
       <c r="GG33" t="n">
-        <v>89024.3708118083</v>
+        <v>88672.514800619</v>
       </c>
       <c r="GH33" t="n">
-        <v>90303.5456025897</v>
+        <v>89923.9644582211</v>
       </c>
       <c r="GI33" t="n">
-        <v>91418.8817990193</v>
+        <v>91031.7070858401</v>
       </c>
       <c r="GJ33" t="n">
-        <v>92306.0202475345</v>
+        <v>91901.5652172986</v>
       </c>
       <c r="GK33" t="n">
-        <v>93065.2397905449</v>
+        <v>92651.3177505619</v>
       </c>
       <c r="GL33" t="n">
-        <v>93823.0028090925</v>
+        <v>93389.9456658418</v>
       </c>
       <c r="GM33" t="n">
-        <v>94504.8737194695</v>
+        <v>94057.6354070455</v>
       </c>
       <c r="GN33" t="n">
-        <v>95171.7654701547</v>
+        <v>94695.6702122744</v>
       </c>
       <c r="GO33" t="n">
-        <v>95684.126987656</v>
+        <v>95190.2779194866</v>
       </c>
       <c r="GP33" t="n">
-        <v>96293.4825132375</v>
+        <v>95769.030505128</v>
       </c>
       <c r="GQ33" t="n">
-        <v>96819.2751161914</v>
+        <v>96269.1651862168</v>
       </c>
       <c r="GR33" t="n">
-        <v>97396.6976609764</v>
+        <v>96815.2812933578</v>
       </c>
       <c r="GS33" t="n">
-        <v>97961.5140340047</v>
+        <v>97351.2794378337</v>
       </c>
       <c r="GT33" t="n">
-        <v>98555.8169929774</v>
+        <v>97914.0963596563</v>
       </c>
       <c r="GU33" t="n">
-        <v>99126.8072661831</v>
+        <v>98455.3170806586</v>
       </c>
       <c r="GV33" t="n">
-        <v>99705.2782918464</v>
+        <v>99002.8825520675</v>
       </c>
       <c r="GW33" t="n">
-        <v>100295.552900296</v>
+        <v>99563.1982209889</v>
       </c>
       <c r="GX33" t="n">
-        <v>100911.948086435</v>
+        <v>100149.359520062</v>
       </c>
       <c r="GY33" t="n">
-        <v>101530.977003976</v>
+        <v>100738.973003124</v>
       </c>
       <c r="GZ33" t="n">
-        <v>102167.844664728</v>
+        <v>101346.80946216</v>
       </c>
       <c r="HA33" t="n">
-        <v>102830.915550931</v>
+        <v>101981.782988665</v>
       </c>
       <c r="HB33" t="n">
-        <v>103538.973093055</v>
+        <v>102661.455875212</v>
       </c>
       <c r="HC33" t="n">
-        <v>104239.54084412</v>
+        <v>103336.056201626</v>
       </c>
       <c r="HD33" t="n">
-        <v>104959.846450162</v>
+        <v>104030.303350874</v>
       </c>
       <c r="HE33" t="n">
-        <v>105694.076149764</v>
+        <v>104740.233213921</v>
       </c>
       <c r="HF33" t="n">
-        <v>106436.310631626</v>
+        <v>105459.293434063</v>
       </c>
       <c r="HG33" t="n">
-        <v>107161.139359163</v>
+        <v>106162.517561271</v>
       </c>
       <c r="HH33" t="n">
-        <v>107869.173743968</v>
+        <v>106850.317283027</v>
       </c>
       <c r="HI33" t="n">
-        <v>108570.871335047</v>
+        <v>107533.270105729</v>
       </c>
       <c r="HJ33" t="n">
-        <v>109269.799253294</v>
+        <v>108214.662894775</v>
       </c>
       <c r="HK33" t="n">
-        <v>109936.586824394</v>
+        <v>108865.245945456</v>
       </c>
       <c r="HL33" t="n">
-        <v>110579.54453847</v>
+        <v>109493.082494654</v>
       </c>
       <c r="HM33" t="n">
-        <v>111210.642108837</v>
+        <v>110110.216937152</v>
       </c>
       <c r="HN33" t="n">
-        <v>111831.11025579</v>
+        <v>110717.590320002</v>
       </c>
       <c r="HO33" t="n">
-        <v>112413.524667407</v>
+        <v>111287.863254625</v>
       </c>
       <c r="HP33" t="n">
-        <v>112962.080462685</v>
+        <v>111825.041010286</v>
       </c>
       <c r="HQ33" t="n">
-        <v>113493.898764677</v>
+        <v>112346.211308484</v>
       </c>
       <c r="HR33" t="n">
-        <v>114012.487238331</v>
+        <v>112854.714534625</v>
       </c>
       <c r="HS33" t="n">
-        <v>114483.151156447</v>
+        <v>113315.840922053</v>
       </c>
       <c r="HT33" t="n">
-        <v>114916.996432602</v>
+        <v>113740.62295927</v>
       </c>
       <c r="HU33" t="n">
-        <v>115342.796638389</v>
+        <v>114157.526684215</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sem_coredata.xlsx
+++ b/outputs/sem_coredata.xlsx
@@ -2754,139 +2754,139 @@
         <v>354377</v>
       </c>
       <c r="GC2" t="n">
-        <v>355093.061268826</v>
+        <v>355093.061230489</v>
       </c>
       <c r="GD2" t="n">
-        <v>360057.784065344</v>
+        <v>360057.783987501</v>
       </c>
       <c r="GE2" t="n">
-        <v>362937.789785227</v>
+        <v>362937.789666279</v>
       </c>
       <c r="GF2" t="n">
-        <v>366473.809693835</v>
+        <v>366473.809550388</v>
       </c>
       <c r="GG2" t="n">
-        <v>369339.814436186</v>
+        <v>369339.814282417</v>
       </c>
       <c r="GH2" t="n">
-        <v>371785.376588256</v>
+        <v>371785.376433554</v>
       </c>
       <c r="GI2" t="n">
-        <v>373790.181068688</v>
+        <v>373790.180930009</v>
       </c>
       <c r="GJ2" t="n">
-        <v>375539.160649502</v>
+        <v>375539.160539227</v>
       </c>
       <c r="GK2" t="n">
-        <v>377359.172187142</v>
+        <v>377359.172118566</v>
       </c>
       <c r="GL2" t="n">
-        <v>379195.880919388</v>
+        <v>379195.880901556</v>
       </c>
       <c r="GM2" t="n">
-        <v>380837.882620577</v>
+        <v>380837.882653327</v>
       </c>
       <c r="GN2" t="n">
-        <v>382332.873070651</v>
+        <v>382332.873153968</v>
       </c>
       <c r="GO2" t="n">
-        <v>384044.253230457</v>
+        <v>384044.25336919</v>
       </c>
       <c r="GP2" t="n">
-        <v>385944.148380431</v>
+        <v>385944.148580009</v>
       </c>
       <c r="GQ2" t="n">
-        <v>387673.975856514</v>
+        <v>387673.976116972</v>
       </c>
       <c r="GR2" t="n">
-        <v>389612.03339764</v>
+        <v>389612.033720876</v>
       </c>
       <c r="GS2" t="n">
-        <v>391756.563853357</v>
+        <v>391756.564237653</v>
       </c>
       <c r="GT2" t="n">
-        <v>394082.925895971</v>
+        <v>394082.926339524</v>
       </c>
       <c r="GU2" t="n">
-        <v>396208.183594643</v>
+        <v>396208.184092239</v>
       </c>
       <c r="GV2" t="n">
-        <v>398503.25039253</v>
+        <v>398503.250939809</v>
       </c>
       <c r="GW2" t="n">
-        <v>401020.572361829</v>
+        <v>401020.572954027</v>
       </c>
       <c r="GX2" t="n">
-        <v>403709.434652402</v>
+        <v>403709.43528421</v>
       </c>
       <c r="GY2" t="n">
-        <v>406200.441932707</v>
+        <v>406200.442596775</v>
       </c>
       <c r="GZ2" t="n">
-        <v>408859.757902305</v>
+        <v>408859.758593226</v>
       </c>
       <c r="HA2" t="n">
-        <v>411709.959454713</v>
+        <v>411709.960166294</v>
       </c>
       <c r="HB2" t="n">
-        <v>414703.659834883</v>
+        <v>414703.660560691</v>
       </c>
       <c r="HC2" t="n">
-        <v>417365.103638016</v>
+        <v>417365.104369556</v>
       </c>
       <c r="HD2" t="n">
-        <v>420181.785554543</v>
+        <v>420181.786286364</v>
       </c>
       <c r="HE2" t="n">
-        <v>423104.405924654</v>
+        <v>423104.406650936</v>
       </c>
       <c r="HF2" t="n">
-        <v>426087.907232089</v>
+        <v>426087.907947669</v>
       </c>
       <c r="HG2" t="n">
-        <v>428735.444686371</v>
+        <v>428735.445384839</v>
       </c>
       <c r="HH2" t="n">
-        <v>431412.894429119</v>
+        <v>431412.895106344</v>
       </c>
       <c r="HI2" t="n">
-        <v>434197.980378483</v>
+        <v>434197.981031085</v>
       </c>
       <c r="HJ2" t="n">
-        <v>437015.956812562</v>
+        <v>437015.957437043</v>
       </c>
       <c r="HK2" t="n">
-        <v>439470.628080736</v>
+        <v>439470.628671841</v>
       </c>
       <c r="HL2" t="n">
-        <v>441958.297159013</v>
+        <v>441958.297714343</v>
       </c>
       <c r="HM2" t="n">
-        <v>444538.084235254</v>
+        <v>444538.084752457</v>
       </c>
       <c r="HN2" t="n">
-        <v>447141.780415184</v>
+        <v>447141.780892027</v>
       </c>
       <c r="HO2" t="n">
-        <v>449363.800258332</v>
+        <v>449363.800690713</v>
       </c>
       <c r="HP2" t="n">
-        <v>451581.251814514</v>
+        <v>451581.252200743</v>
       </c>
       <c r="HQ2" t="n">
-        <v>453907.281516455</v>
+        <v>453907.281855652</v>
       </c>
       <c r="HR2" t="n">
-        <v>456270.456935422</v>
+        <v>456270.457226596</v>
       </c>
       <c r="HS2" t="n">
-        <v>458154.476213753</v>
+        <v>458154.476454183</v>
       </c>
       <c r="HT2" t="n">
-        <v>460131.309445219</v>
+        <v>460131.309634874</v>
       </c>
       <c r="HU2" t="n">
-        <v>462196.668520795</v>
+        <v>462196.668659974</v>
       </c>
     </row>
     <row r="3">
@@ -4135,136 +4135,136 @@
         <v>36864.8957689682</v>
       </c>
       <c r="GD4" t="n">
-        <v>37067.0424615201</v>
+        <v>37067.0424609753</v>
       </c>
       <c r="GE4" t="n">
-        <v>37241.2523090563</v>
+        <v>37241.2523083342</v>
       </c>
       <c r="GF4" t="n">
-        <v>37366.4033785709</v>
+        <v>37366.4033790698</v>
       </c>
       <c r="GG4" t="n">
-        <v>37327.7724128136</v>
+        <v>37327.7724162639</v>
       </c>
       <c r="GH4" t="n">
-        <v>37204.0844715228</v>
+        <v>37204.0844795898</v>
       </c>
       <c r="GI4" t="n">
-        <v>37030.7396951707</v>
+        <v>37030.7397082828</v>
       </c>
       <c r="GJ4" t="n">
-        <v>36911.1636241773</v>
+        <v>36911.1636418051</v>
       </c>
       <c r="GK4" t="n">
-        <v>36880.3199809674</v>
+        <v>36880.3200019542</v>
       </c>
       <c r="GL4" t="n">
-        <v>36961.5004781343</v>
+        <v>36961.5005011521</v>
       </c>
       <c r="GM4" t="n">
-        <v>37139.7680086486</v>
+        <v>37139.7680324348</v>
       </c>
       <c r="GN4" t="n">
-        <v>37381.7643538881</v>
+        <v>37381.7643773445</v>
       </c>
       <c r="GO4" t="n">
-        <v>37649.051207505</v>
+        <v>37649.0512300486</v>
       </c>
       <c r="GP4" t="n">
-        <v>37912.0089799848</v>
+        <v>37912.0090017895</v>
       </c>
       <c r="GQ4" t="n">
-        <v>38149.8728264283</v>
+        <v>38149.8728483592</v>
       </c>
       <c r="GR4" t="n">
-        <v>38345.2078402655</v>
+        <v>38345.2078635615</v>
       </c>
       <c r="GS4" t="n">
-        <v>38492.8216019205</v>
+        <v>38492.8216278855</v>
       </c>
       <c r="GT4" t="n">
-        <v>38594.108585265</v>
+        <v>38594.1086151134</v>
       </c>
       <c r="GU4" t="n">
-        <v>38657.484892767</v>
+        <v>38657.484927624</v>
       </c>
       <c r="GV4" t="n">
-        <v>38693.2740485583</v>
+        <v>38693.2740894899</v>
       </c>
       <c r="GW4" t="n">
-        <v>38716.7404512673</v>
+        <v>38716.7404992865</v>
       </c>
       <c r="GX4" t="n">
-        <v>38742.9444864644</v>
+        <v>38742.9445425113</v>
       </c>
       <c r="GY4" t="n">
-        <v>38782.0734206202</v>
+        <v>38782.0734854792</v>
       </c>
       <c r="GZ4" t="n">
-        <v>38837.6172344702</v>
+        <v>38837.6173087132</v>
       </c>
       <c r="HA4" t="n">
-        <v>38912.4962197519</v>
+        <v>38912.4963037247</v>
       </c>
       <c r="HB4" t="n">
-        <v>39007.3344574251</v>
+        <v>39007.3345512394</v>
       </c>
       <c r="HC4" t="n">
-        <v>39120.0644260793</v>
+        <v>39120.0645296093</v>
       </c>
       <c r="HD4" t="n">
-        <v>39244.854277343</v>
+        <v>39244.8543902504</v>
       </c>
       <c r="HE4" t="n">
-        <v>39381.0213189521</v>
+        <v>39381.021440756</v>
       </c>
       <c r="HF4" t="n">
-        <v>39528.1869507086</v>
+        <v>39528.1870808198</v>
       </c>
       <c r="HG4" t="n">
-        <v>39684.7007116105</v>
+        <v>39684.7008493398</v>
       </c>
       <c r="HH4" t="n">
-        <v>39847.4333622701</v>
+        <v>39847.4335068441</v>
       </c>
       <c r="HI4" t="n">
-        <v>40016.2647540735</v>
+        <v>40016.2649046782</v>
       </c>
       <c r="HJ4" t="n">
-        <v>40192.9000937155</v>
+        <v>40192.9002495292</v>
       </c>
       <c r="HK4" t="n">
-        <v>40377.0052074737</v>
+        <v>40377.0053676567</v>
       </c>
       <c r="HL4" t="n">
-        <v>40564.9447804072</v>
+        <v>40564.944944097</v>
       </c>
       <c r="HM4" t="n">
-        <v>40756.2993767962</v>
+        <v>40756.299543157</v>
       </c>
       <c r="HN4" t="n">
-        <v>40951.132939814</v>
+        <v>40951.1331080524</v>
       </c>
       <c r="HO4" t="n">
-        <v>41148.2023008556</v>
+        <v>41148.202470213</v>
       </c>
       <c r="HP4" t="n">
-        <v>41343.4089970277</v>
+        <v>41343.4091667664</v>
       </c>
       <c r="HQ4" t="n">
-        <v>41536.2594137818</v>
+        <v>41536.2595832221</v>
       </c>
       <c r="HR4" t="n">
-        <v>41728.0743728611</v>
+        <v>41728.0745413987</v>
       </c>
       <c r="HS4" t="n">
-        <v>41918.8355612078</v>
+        <v>41918.8357282876</v>
       </c>
       <c r="HT4" t="n">
-        <v>42104.3549724863</v>
+        <v>42104.3551375688</v>
       </c>
       <c r="HU4" t="n">
-        <v>42286.289457163</v>
+        <v>42286.2896197607</v>
       </c>
     </row>
     <row r="5">
@@ -4824,136 +4824,136 @@
         <v>11150.4565404427</v>
       </c>
       <c r="GD5" t="n">
-        <v>11211.5994750171</v>
+        <v>11211.5994748524</v>
       </c>
       <c r="GE5" t="n">
-        <v>11264.2924039771</v>
+        <v>11264.2924037587</v>
       </c>
       <c r="GF5" t="n">
-        <v>11302.1466154838</v>
+        <v>11302.1466156347</v>
       </c>
       <c r="GG5" t="n">
-        <v>11290.4619790348</v>
+        <v>11290.4619800784</v>
       </c>
       <c r="GH5" t="n">
-        <v>11253.0503172039</v>
+        <v>11253.0503196439</v>
       </c>
       <c r="GI5" t="n">
-        <v>11200.619044718</v>
+        <v>11200.619048684</v>
       </c>
       <c r="GJ5" t="n">
-        <v>11164.4510926574</v>
+        <v>11164.4510979893</v>
       </c>
       <c r="GK5" t="n">
-        <v>11155.1218731931</v>
+        <v>11155.1218795409</v>
       </c>
       <c r="GL5" t="n">
-        <v>11179.6763873646</v>
+        <v>11179.6763943267</v>
       </c>
       <c r="GM5" t="n">
-        <v>11233.5966361571</v>
+        <v>11233.5966433516</v>
       </c>
       <c r="GN5" t="n">
-        <v>11306.7928211524</v>
+        <v>11306.7928282472</v>
       </c>
       <c r="GO5" t="n">
-        <v>11387.6385792352</v>
+        <v>11387.6385860539</v>
       </c>
       <c r="GP5" t="n">
-        <v>11467.1749281885</v>
+        <v>11467.1749347837</v>
       </c>
       <c r="GQ5" t="n">
-        <v>11539.1211639499</v>
+        <v>11539.1211705833</v>
       </c>
       <c r="GR5" t="n">
-        <v>11598.2037827172</v>
+        <v>11598.2037897636</v>
       </c>
       <c r="GS5" t="n">
-        <v>11642.8522429874</v>
+        <v>11642.852250841</v>
       </c>
       <c r="GT5" t="n">
-        <v>11673.4883286819</v>
+        <v>11673.4883377101</v>
       </c>
       <c r="GU5" t="n">
-        <v>11692.6576426798</v>
+        <v>11692.6576532229</v>
       </c>
       <c r="GV5" t="n">
-        <v>11703.4827221476</v>
+        <v>11703.4827345281</v>
       </c>
       <c r="GW5" t="n">
-        <v>11710.5805613821</v>
+        <v>11710.5805759064</v>
       </c>
       <c r="GX5" t="n">
-        <v>11718.5064472298</v>
+        <v>11718.5064641821</v>
       </c>
       <c r="GY5" t="n">
-        <v>11730.3417032552</v>
+        <v>11730.341722873</v>
       </c>
       <c r="GZ5" t="n">
-        <v>11747.1419374484</v>
+        <v>11747.1419599045</v>
       </c>
       <c r="HA5" t="n">
-        <v>11769.7904450261</v>
+        <v>11769.7904704252</v>
       </c>
       <c r="HB5" t="n">
-        <v>11798.475990597</v>
+        <v>11798.4760189728</v>
       </c>
       <c r="HC5" t="n">
-        <v>11832.5732148008</v>
+        <v>11832.5732461153</v>
       </c>
       <c r="HD5" t="n">
-        <v>11870.3181692942</v>
+        <v>11870.3182034451</v>
       </c>
       <c r="HE5" t="n">
-        <v>11911.5043614163</v>
+        <v>11911.5043982582</v>
       </c>
       <c r="HF5" t="n">
-        <v>11956.0172766686</v>
+        <v>11956.0173160231</v>
       </c>
       <c r="HG5" t="n">
-        <v>12003.3577031778</v>
+        <v>12003.3577448365</v>
       </c>
       <c r="HH5" t="n">
-        <v>12052.5791457193</v>
+        <v>12052.5791894483</v>
       </c>
       <c r="HI5" t="n">
-        <v>12103.6452631651</v>
+        <v>12103.6453087182</v>
       </c>
       <c r="HJ5" t="n">
-        <v>12157.0718262165</v>
+        <v>12157.0718733452</v>
       </c>
       <c r="HK5" t="n">
-        <v>12212.7577579685</v>
+        <v>12212.7578064187</v>
       </c>
       <c r="HL5" t="n">
-        <v>12269.603491464</v>
+        <v>12269.603540975</v>
       </c>
       <c r="HM5" t="n">
-        <v>12327.4821607602</v>
+        <v>12327.482211079</v>
       </c>
       <c r="HN5" t="n">
-        <v>12386.4131066298</v>
+        <v>12386.4131575165</v>
       </c>
       <c r="HO5" t="n">
-        <v>12446.0203101743</v>
+        <v>12446.0203613995</v>
       </c>
       <c r="HP5" t="n">
-        <v>12505.0641169359</v>
+        <v>12505.0641682765</v>
       </c>
       <c r="HQ5" t="n">
-        <v>12563.3952242391</v>
+        <v>12563.3952754894</v>
       </c>
       <c r="HR5" t="n">
-        <v>12621.413138583</v>
+        <v>12621.4131895603</v>
       </c>
       <c r="HS5" t="n">
-        <v>12679.112320851</v>
+        <v>12679.1123713873</v>
       </c>
       <c r="HT5" t="n">
-        <v>12735.2260325467</v>
+        <v>12735.2260824789</v>
       </c>
       <c r="HU5" t="n">
-        <v>12790.2554181526</v>
+        <v>12790.2554673333</v>
       </c>
     </row>
     <row r="6">
@@ -6845,136 +6845,136 @@
         <v>-20.3573504657543</v>
       </c>
       <c r="GD8" t="n">
-        <v>-90.0759339011565</v>
+        <v>-90.0759506726754</v>
       </c>
       <c r="GE8" t="n">
-        <v>1283.86181475656</v>
+        <v>1283.86179741978</v>
       </c>
       <c r="GF8" t="n">
-        <v>750.238097339461</v>
+        <v>750.23807123382</v>
       </c>
       <c r="GG8" t="n">
-        <v>1613.00181133728</v>
+        <v>1613.0017822542</v>
       </c>
       <c r="GH8" t="n">
-        <v>1387.08059932239</v>
+        <v>1387.08056422888</v>
       </c>
       <c r="GI8" t="n">
-        <v>1538.35912363903</v>
+        <v>1538.35908561526</v>
       </c>
       <c r="GJ8" t="n">
-        <v>1502.44466556777</v>
+        <v>1502.44462474791</v>
       </c>
       <c r="GK8" t="n">
-        <v>1444.33137693201</v>
+        <v>1444.33133542823</v>
       </c>
       <c r="GL8" t="n">
-        <v>1434.62482067631</v>
+        <v>1434.62477809589</v>
       </c>
       <c r="GM8" t="n">
-        <v>1398.58863633068</v>
+        <v>1398.58859328352</v>
       </c>
       <c r="GN8" t="n">
-        <v>1368.21690276757</v>
+        <v>1368.21685737261</v>
       </c>
       <c r="GO8" t="n">
-        <v>1252.61697293192</v>
+        <v>1252.61692824503</v>
       </c>
       <c r="GP8" t="n">
-        <v>1225.3734387086</v>
+        <v>1225.37339399132</v>
       </c>
       <c r="GQ8" t="n">
-        <v>1178.83980102706</v>
+        <v>1178.83975756163</v>
       </c>
       <c r="GR8" t="n">
-        <v>1111.68396726577</v>
+        <v>1111.68392461681</v>
       </c>
       <c r="GS8" t="n">
-        <v>1080.48617301864</v>
+        <v>1080.48613215526</v>
       </c>
       <c r="GT8" t="n">
-        <v>1038.39991182275</v>
+        <v>1038.39987236864</v>
       </c>
       <c r="GU8" t="n">
-        <v>1010.16694336393</v>
+        <v>1010.16690562316</v>
       </c>
       <c r="GV8" t="n">
-        <v>947.386735776003</v>
+        <v>947.386699673225</v>
       </c>
       <c r="GW8" t="n">
-        <v>933.146076486271</v>
+        <v>933.146042164881</v>
       </c>
       <c r="GX8" t="n">
-        <v>903.049899964797</v>
+        <v>903.049867272464</v>
       </c>
       <c r="GY8" t="n">
-        <v>891.865317585325</v>
+        <v>891.865286467393</v>
       </c>
       <c r="GZ8" t="n">
-        <v>861.484324850491</v>
+        <v>861.484295283764</v>
       </c>
       <c r="HA8" t="n">
-        <v>856.406357147876</v>
+        <v>856.406329146732</v>
       </c>
       <c r="HB8" t="n">
-        <v>855.121311908733</v>
+        <v>855.121285262139</v>
       </c>
       <c r="HC8" t="n">
-        <v>861.122485371074</v>
+        <v>861.122459923849</v>
       </c>
       <c r="HD8" t="n">
-        <v>815.79164748246</v>
+        <v>815.791623333324</v>
       </c>
       <c r="HE8" t="n">
-        <v>850.63276718781</v>
+        <v>850.632744220347</v>
       </c>
       <c r="HF8" t="n">
-        <v>835.086489492736</v>
+        <v>835.086467655638</v>
       </c>
       <c r="HG8" t="n">
-        <v>847.787866162806</v>
+        <v>847.787845368148</v>
       </c>
       <c r="HH8" t="n">
-        <v>832.039432542748</v>
+        <v>832.039412896091</v>
       </c>
       <c r="HI8" t="n">
-        <v>835.747590565967</v>
+        <v>835.747572098509</v>
       </c>
       <c r="HJ8" t="n">
-        <v>842.205697125901</v>
+        <v>842.205679705803</v>
       </c>
       <c r="HK8" t="n">
-        <v>849.481425804785</v>
+        <v>849.481409332977</v>
       </c>
       <c r="HL8" t="n">
-        <v>836.1382355034</v>
+        <v>836.138219990622</v>
       </c>
       <c r="HM8" t="n">
-        <v>839.536183942022</v>
+        <v>839.536169417552</v>
       </c>
       <c r="HN8" t="n">
-        <v>844.603408431372</v>
+        <v>844.603394653561</v>
       </c>
       <c r="HO8" t="n">
-        <v>849.35250752233</v>
+        <v>849.352494362945</v>
       </c>
       <c r="HP8" t="n">
-        <v>832.194262148754</v>
+        <v>832.194249561493</v>
       </c>
       <c r="HQ8" t="n">
-        <v>829.356615165394</v>
+        <v>829.356603118358</v>
       </c>
       <c r="HR8" t="n">
-        <v>830.044123144442</v>
+        <v>830.044111411291</v>
       </c>
       <c r="HS8" t="n">
-        <v>829.989692996809</v>
+        <v>829.989681413426</v>
       </c>
       <c r="HT8" t="n">
-        <v>758.936917471554</v>
+        <v>758.936906360876</v>
       </c>
       <c r="HU8" t="n">
-        <v>786.536246196076</v>
+        <v>786.536234995525</v>
       </c>
     </row>
     <row r="9">
@@ -8214,139 +8214,139 @@
         <v>680205</v>
       </c>
       <c r="GC10" t="n">
-        <v>686130.388292905</v>
+        <v>686130.388232023</v>
       </c>
       <c r="GD10" t="n">
-        <v>694123.931954122</v>
+        <v>694123.93185288</v>
       </c>
       <c r="GE10" t="n">
-        <v>701330.195912389</v>
+        <v>701330.195724649</v>
       </c>
       <c r="GF10" t="n">
-        <v>707446.366820035</v>
+        <v>707446.366603154</v>
       </c>
       <c r="GG10" t="n">
-        <v>714089.518561653</v>
+        <v>714089.518326989</v>
       </c>
       <c r="GH10" t="n">
-        <v>718799.253714875</v>
+        <v>718799.253491191</v>
       </c>
       <c r="GI10" t="n">
-        <v>723246.573398806</v>
+        <v>723246.573208056</v>
       </c>
       <c r="GJ10" t="n">
-        <v>726964.811189347</v>
+        <v>726964.811057511</v>
       </c>
       <c r="GK10" t="n">
-        <v>730735.341269051</v>
+        <v>730735.3412123</v>
       </c>
       <c r="GL10" t="n">
-        <v>734713.803829733</v>
+        <v>734713.803866633</v>
       </c>
       <c r="GM10" t="n">
-        <v>738534.837917606</v>
+        <v>738534.838046901</v>
       </c>
       <c r="GN10" t="n">
-        <v>741589.182168337</v>
+        <v>741589.182394796</v>
       </c>
       <c r="GO10" t="n">
-        <v>744664.200964413</v>
+        <v>744664.201288273</v>
       </c>
       <c r="GP10" t="n">
-        <v>748094.596225114</v>
+        <v>748094.596661641</v>
       </c>
       <c r="GQ10" t="n">
-        <v>751224.332925385</v>
+        <v>751224.333475302</v>
       </c>
       <c r="GR10" t="n">
-        <v>754540.274047451</v>
+        <v>754540.274719342</v>
       </c>
       <c r="GS10" t="n">
-        <v>758026.372730235</v>
+        <v>758026.373525207</v>
       </c>
       <c r="GT10" t="n">
-        <v>761649.892886924</v>
+        <v>761649.893806956</v>
       </c>
       <c r="GU10" t="n">
-        <v>765015.189610289</v>
+        <v>765015.190651824</v>
       </c>
       <c r="GV10" t="n">
-        <v>768500.87166757</v>
+        <v>768500.872828056</v>
       </c>
       <c r="GW10" t="n">
-        <v>772254.050240332</v>
+        <v>772254.051516402</v>
       </c>
       <c r="GX10" t="n">
-        <v>776192.323704298</v>
+        <v>776192.325091794</v>
       </c>
       <c r="GY10" t="n">
-        <v>779971.94028594</v>
+        <v>779971.941777628</v>
       </c>
       <c r="GZ10" t="n">
-        <v>783950.886785687</v>
+        <v>783950.888376166</v>
       </c>
       <c r="HA10" t="n">
-        <v>788198.342666767</v>
+        <v>788198.344349394</v>
       </c>
       <c r="HB10" t="n">
-        <v>792663.786272314</v>
+        <v>792663.788039034</v>
       </c>
       <c r="HC10" t="n">
-        <v>796822.488683259</v>
+        <v>796822.490523239</v>
       </c>
       <c r="HD10" t="n">
-        <v>801117.846618793</v>
+        <v>801117.848523909</v>
       </c>
       <c r="HE10" t="n">
-        <v>805629.814584663</v>
+        <v>805629.816546808</v>
       </c>
       <c r="HF10" t="n">
-        <v>810175.733537357</v>
+        <v>810175.735548494</v>
       </c>
       <c r="HG10" t="n">
-        <v>814410.274255052</v>
+        <v>814410.276305478</v>
       </c>
       <c r="HH10" t="n">
-        <v>818636.161412883</v>
+        <v>818636.163495131</v>
       </c>
       <c r="HI10" t="n">
-        <v>822992.236445759</v>
+        <v>822992.238553518</v>
       </c>
       <c r="HJ10" t="n">
-        <v>827392.556382648</v>
+        <v>827392.558509386</v>
       </c>
       <c r="HK10" t="n">
-        <v>831409.30810803</v>
+        <v>831409.310244661</v>
       </c>
       <c r="HL10" t="n">
-        <v>835418.081067445</v>
+        <v>835418.083208215</v>
       </c>
       <c r="HM10" t="n">
-        <v>839529.457526661</v>
+        <v>839529.459666267</v>
       </c>
       <c r="HN10" t="n">
-        <v>843661.182589545</v>
+        <v>843661.184722751</v>
       </c>
       <c r="HO10" t="n">
-        <v>847376.724668062</v>
+        <v>847376.726787098</v>
       </c>
       <c r="HP10" t="n">
-        <v>851027.664308335</v>
+        <v>851027.666408238</v>
       </c>
       <c r="HQ10" t="n">
-        <v>854782.4247462</v>
+        <v>854782.426823519</v>
       </c>
       <c r="HR10" t="n">
-        <v>858563.84038523</v>
+        <v>858563.842436521</v>
       </c>
       <c r="HS10" t="n">
-        <v>861816.608105436</v>
+        <v>861816.610124648</v>
       </c>
       <c r="HT10" t="n">
-        <v>865048.02161228</v>
+        <v>865048.023597367</v>
       </c>
       <c r="HU10" t="n">
-        <v>868454.063864541</v>
+        <v>868454.065813542</v>
       </c>
     </row>
     <row r="11">
@@ -8903,139 +8903,139 @@
         <v>170963</v>
       </c>
       <c r="GC11" t="n">
-        <v>167287.8406755</v>
+        <v>167287.840655172</v>
       </c>
       <c r="GD11" t="n">
-        <v>176028.608526147</v>
+        <v>176028.608487566</v>
       </c>
       <c r="GE11" t="n">
-        <v>170895.291288516</v>
+        <v>170895.291228008</v>
       </c>
       <c r="GF11" t="n">
-        <v>176676.351790996</v>
+        <v>176676.351709163</v>
       </c>
       <c r="GG11" t="n">
-        <v>176249.481114534</v>
+        <v>176249.481009137</v>
       </c>
       <c r="GH11" t="n">
-        <v>177436.967474815</v>
+        <v>177436.967346086</v>
       </c>
       <c r="GI11" t="n">
-        <v>178221.622328201</v>
+        <v>178221.622176243</v>
       </c>
       <c r="GJ11" t="n">
-        <v>178338.930059092</v>
+        <v>178338.929885873</v>
       </c>
       <c r="GK11" t="n">
-        <v>178897.241361745</v>
+        <v>178897.241166983</v>
       </c>
       <c r="GL11" t="n">
-        <v>179339.283427159</v>
+        <v>179339.283210966</v>
       </c>
       <c r="GM11" t="n">
-        <v>180096.906778716</v>
+        <v>180096.906538021</v>
       </c>
       <c r="GN11" t="n">
-        <v>180053.033957221</v>
+        <v>180053.03369369</v>
       </c>
       <c r="GO11" t="n">
-        <v>180472.710664317</v>
+        <v>180472.710377468</v>
       </c>
       <c r="GP11" t="n">
-        <v>180798.671087506</v>
+        <v>180798.670778312</v>
       </c>
       <c r="GQ11" t="n">
-        <v>180982.189845958</v>
+        <v>180982.189514074</v>
       </c>
       <c r="GR11" t="n">
-        <v>181279.057703492</v>
+        <v>181279.057349384</v>
       </c>
       <c r="GS11" t="n">
-        <v>181495.715523276</v>
+        <v>181495.715146604</v>
       </c>
       <c r="GT11" t="n">
-        <v>181750.002045299</v>
+        <v>181750.001645794</v>
       </c>
       <c r="GU11" t="n">
-        <v>181776.380238549</v>
+        <v>181776.379816106</v>
       </c>
       <c r="GV11" t="n">
-        <v>182068.093841855</v>
+        <v>182068.093395764</v>
       </c>
       <c r="GW11" t="n">
-        <v>182209.111495653</v>
+        <v>182209.111025512</v>
       </c>
       <c r="GX11" t="n">
-        <v>182420.530557358</v>
+        <v>182420.53006238</v>
       </c>
       <c r="GY11" t="n">
-        <v>182592.262190969</v>
+        <v>182592.261670591</v>
       </c>
       <c r="GZ11" t="n">
-        <v>182809.315329328</v>
+        <v>182809.314782904</v>
       </c>
       <c r="HA11" t="n">
-        <v>183047.097514119</v>
+        <v>183047.096940745</v>
       </c>
       <c r="HB11" t="n">
-        <v>183318.395360838</v>
+        <v>183318.394759414</v>
       </c>
       <c r="HC11" t="n">
-        <v>183181.696419935</v>
+        <v>183181.695790935</v>
       </c>
       <c r="HD11" t="n">
-        <v>183633.957620699</v>
+        <v>183633.956961836</v>
       </c>
       <c r="HE11" t="n">
-        <v>183728.199948979</v>
+        <v>183728.199260562</v>
       </c>
       <c r="HF11" t="n">
-        <v>183948.890307</v>
+        <v>183948.889587943</v>
       </c>
       <c r="HG11" t="n">
-        <v>184134.932596503</v>
+        <v>184134.931846419</v>
       </c>
       <c r="HH11" t="n">
-        <v>184354.91088314</v>
+        <v>184354.91010152</v>
       </c>
       <c r="HI11" t="n">
-        <v>184603.980810015</v>
+        <v>184603.979996167</v>
       </c>
       <c r="HJ11" t="n">
-        <v>184874.444065138</v>
+        <v>184874.443218341</v>
       </c>
       <c r="HK11" t="n">
-        <v>185131.049588737</v>
+        <v>185131.048708482</v>
       </c>
       <c r="HL11" t="n">
-        <v>185413.309128548</v>
+        <v>185413.30821438</v>
       </c>
       <c r="HM11" t="n">
-        <v>185721.780882848</v>
+        <v>185721.779933997</v>
       </c>
       <c r="HN11" t="n">
-        <v>186046.852960098</v>
+        <v>186046.851975801</v>
       </c>
       <c r="HO11" t="n">
-        <v>186353.418745367</v>
+        <v>186353.417725057</v>
       </c>
       <c r="HP11" t="n">
-        <v>186678.300831718</v>
+        <v>186678.299774856</v>
       </c>
       <c r="HQ11" t="n">
-        <v>187027.41845733</v>
+        <v>187027.417363127</v>
       </c>
       <c r="HR11" t="n">
-        <v>187390.472397357</v>
+        <v>187390.471265004</v>
       </c>
       <c r="HS11" t="n">
-        <v>187132.690573497</v>
+        <v>187132.689407024</v>
       </c>
       <c r="HT11" t="n">
-        <v>187617.69402097</v>
+        <v>187617.692814515</v>
       </c>
       <c r="HU11" t="n">
-        <v>187617.097553214</v>
+        <v>187617.096310076</v>
       </c>
     </row>
     <row r="12">
@@ -9592,139 +9592,139 @@
         <v>162177</v>
       </c>
       <c r="GC12" t="n">
-        <v>164121.411935033</v>
+        <v>164121.412084132</v>
       </c>
       <c r="GD12" t="n">
-        <v>166117.728343011</v>
+        <v>166117.728578113</v>
       </c>
       <c r="GE12" t="n">
-        <v>167790.444828236</v>
+        <v>167790.445143048</v>
       </c>
       <c r="GF12" t="n">
-        <v>169139.804903508</v>
+        <v>169139.805344906</v>
       </c>
       <c r="GG12" t="n">
-        <v>170571.028589492</v>
+        <v>170571.029190531</v>
       </c>
       <c r="GH12" t="n">
-        <v>171549.476908179</v>
+        <v>171549.477686434</v>
       </c>
       <c r="GI12" t="n">
-        <v>172212.20872938</v>
+        <v>172212.209700047</v>
       </c>
       <c r="GJ12" t="n">
-        <v>172604.146530576</v>
+        <v>172604.147697744</v>
       </c>
       <c r="GK12" t="n">
-        <v>173058.848183035</v>
+        <v>173058.849559539</v>
       </c>
       <c r="GL12" t="n">
-        <v>173751.07238465</v>
+        <v>173751.073983909</v>
       </c>
       <c r="GM12" t="n">
-        <v>174719.029325649</v>
+        <v>174719.031166794</v>
       </c>
       <c r="GN12" t="n">
-        <v>175355.65955725</v>
+        <v>175355.66161808</v>
       </c>
       <c r="GO12" t="n">
-        <v>175999.036054163</v>
+        <v>175999.038328654</v>
       </c>
       <c r="GP12" t="n">
-        <v>176870.397181691</v>
+        <v>176870.399670533</v>
       </c>
       <c r="GQ12" t="n">
-        <v>177797.083840841</v>
+        <v>177797.086539289</v>
       </c>
       <c r="GR12" t="n">
-        <v>178825.290774572</v>
+        <v>178825.293676859</v>
       </c>
       <c r="GS12" t="n">
-        <v>180026.124928434</v>
+        <v>180026.128029746</v>
       </c>
       <c r="GT12" t="n">
-        <v>181377.095052725</v>
+        <v>181377.098347047</v>
       </c>
       <c r="GU12" t="n">
-        <v>182734.500957596</v>
+        <v>182734.504434684</v>
       </c>
       <c r="GV12" t="n">
-        <v>184154.795852241</v>
+        <v>184154.799501935</v>
       </c>
       <c r="GW12" t="n">
-        <v>185735.051058505</v>
+        <v>185735.054872612</v>
       </c>
       <c r="GX12" t="n">
-        <v>187458.930949901</v>
+        <v>187458.934919667</v>
       </c>
       <c r="GY12" t="n">
-        <v>189187.856798074</v>
+        <v>189187.86091114</v>
       </c>
       <c r="GZ12" t="n">
-        <v>190983.378321472</v>
+        <v>190983.382566951</v>
       </c>
       <c r="HA12" t="n">
-        <v>192911.883133129</v>
+        <v>192911.88750152</v>
       </c>
       <c r="HB12" t="n">
-        <v>194962.966695847</v>
+        <v>194962.971176942</v>
       </c>
       <c r="HC12" t="n">
-        <v>196938.016329644</v>
+        <v>196938.020908495</v>
       </c>
       <c r="HD12" t="n">
-        <v>198906.926270174</v>
+        <v>198906.930934023</v>
       </c>
       <c r="HE12" t="n">
-        <v>200958.584912856</v>
+        <v>200958.589651449</v>
       </c>
       <c r="HF12" t="n">
-        <v>203036.898681978</v>
+        <v>203036.903484276</v>
       </c>
       <c r="HG12" t="n">
-        <v>204992.144039156</v>
+        <v>204992.148890827</v>
       </c>
       <c r="HH12" t="n">
-        <v>206876.372529804</v>
+        <v>206876.37741855</v>
       </c>
       <c r="HI12" t="n">
-        <v>208785.964015499</v>
+        <v>208785.968932409</v>
       </c>
       <c r="HJ12" t="n">
-        <v>210710.973570084</v>
+        <v>210710.978506641</v>
       </c>
       <c r="HK12" t="n">
-        <v>212489.06345431</v>
+        <v>212489.068398295</v>
       </c>
       <c r="HL12" t="n">
-        <v>214188.900057864</v>
+        <v>214188.904999786</v>
       </c>
       <c r="HM12" t="n">
-        <v>215913.339169994</v>
+        <v>215913.344103991</v>
       </c>
       <c r="HN12" t="n">
-        <v>217651.898803033</v>
+        <v>217651.903723733</v>
       </c>
       <c r="HO12" t="n">
-        <v>219239.496876667</v>
+        <v>219239.501775156</v>
       </c>
       <c r="HP12" t="n">
-        <v>220738.48988957</v>
+        <v>220738.494759442</v>
       </c>
       <c r="HQ12" t="n">
-        <v>222269.292049267</v>
+        <v>222269.296888062</v>
       </c>
       <c r="HR12" t="n">
-        <v>223831.879388473</v>
+        <v>223831.88419443</v>
       </c>
       <c r="HS12" t="n">
-        <v>225219.764186373</v>
+        <v>225219.768953428</v>
       </c>
       <c r="HT12" t="n">
-        <v>226530.980192166</v>
+        <v>226530.98491757</v>
       </c>
       <c r="HU12" t="n">
-        <v>227921.528468876</v>
+        <v>227921.533153777</v>
       </c>
     </row>
     <row r="13">
@@ -10281,139 +10281,139 @@
         <v>688271</v>
       </c>
       <c r="GC13" t="n">
-        <v>688866.834437336</v>
+        <v>688866.834207019</v>
       </c>
       <c r="GD13" t="n">
-        <v>703604.834099491</v>
+        <v>703604.833724565</v>
       </c>
       <c r="GE13" t="n">
-        <v>704005.064952184</v>
+        <v>704005.064389124</v>
       </c>
       <c r="GF13" t="n">
-        <v>714552.936601672</v>
+        <v>714552.93586156</v>
       </c>
       <c r="GG13" t="n">
-        <v>719337.993500757</v>
+        <v>719337.992559658</v>
       </c>
       <c r="GH13" t="n">
-        <v>724256.766959714</v>
+        <v>724256.765829046</v>
       </c>
       <c r="GI13" t="n">
-        <v>728826.009338396</v>
+        <v>728826.008025022</v>
       </c>
       <c r="GJ13" t="n">
-        <v>732269.616815641</v>
+        <v>732269.61534342</v>
       </c>
       <c r="GK13" t="n">
-        <v>736143.75793828</v>
+        <v>736143.756310264</v>
       </c>
       <c r="GL13" t="n">
-        <v>739872.03783298</v>
+        <v>739872.036054429</v>
       </c>
       <c r="GM13" t="n">
-        <v>743482.737877553</v>
+        <v>743482.735925008</v>
       </c>
       <c r="GN13" t="n">
-        <v>745856.57904107</v>
+        <v>745856.57694317</v>
       </c>
       <c r="GO13" t="n">
-        <v>748707.897906413</v>
+        <v>748707.895668934</v>
       </c>
       <c r="GP13" t="n">
-        <v>751592.894140744</v>
+        <v>751592.891779237</v>
       </c>
       <c r="GQ13" t="n">
-        <v>753979.462689626</v>
+        <v>753979.460209213</v>
       </c>
       <c r="GR13" t="n">
-        <v>756564.064240828</v>
+        <v>756564.061656325</v>
       </c>
       <c r="GS13" t="n">
-        <v>759065.98605977</v>
+        <v>759065.983376761</v>
       </c>
       <c r="GT13" t="n">
-        <v>761592.823866241</v>
+        <v>761592.821092448</v>
       </c>
       <c r="GU13" t="n">
-        <v>763627.092196222</v>
+        <v>763627.089338228</v>
       </c>
       <c r="GV13" t="n">
-        <v>765984.194020966</v>
+        <v>765984.19108567</v>
       </c>
       <c r="GW13" t="n">
-        <v>768298.133975158</v>
+        <v>768298.130966983</v>
       </c>
       <c r="GX13" t="n">
-        <v>770723.947290241</v>
+        <v>770723.944212995</v>
       </c>
       <c r="GY13" t="n">
-        <v>772946.37021075</v>
+        <v>772946.367068996</v>
       </c>
       <c r="GZ13" t="n">
-        <v>775346.848578081</v>
+        <v>775346.84537666</v>
       </c>
       <c r="HA13" t="n">
-        <v>777903.581862182</v>
+        <v>777903.578603048</v>
       </c>
       <c r="HB13" t="n">
-        <v>780589.239487958</v>
+        <v>780589.236172161</v>
       </c>
       <c r="HC13" t="n">
-        <v>782636.19523891</v>
+        <v>782636.191871042</v>
       </c>
       <c r="HD13" t="n">
-        <v>785414.903749895</v>
+        <v>785414.900332301</v>
       </c>
       <c r="HE13" t="n">
-        <v>787969.456827305</v>
+        <v>787969.453362443</v>
       </c>
       <c r="HF13" t="n">
-        <v>790657.75139772</v>
+        <v>790657.747887504</v>
       </c>
       <c r="HG13" t="n">
-        <v>793123.090245786</v>
+        <v>793123.08669446</v>
       </c>
       <c r="HH13" t="n">
-        <v>795684.726125681</v>
+        <v>795684.722537564</v>
       </c>
       <c r="HI13" t="n">
-        <v>798380.280612548</v>
+        <v>798380.276989552</v>
       </c>
       <c r="HJ13" t="n">
-        <v>801126.055199086</v>
+        <v>801126.051542471</v>
       </c>
       <c r="HK13" t="n">
-        <v>803621.323560566</v>
+        <v>803621.31987296</v>
       </c>
       <c r="HL13" t="n">
-        <v>806212.517921321</v>
+        <v>806212.514206004</v>
       </c>
       <c r="HM13" t="n">
-        <v>808907.927836385</v>
+        <v>808907.924093146</v>
       </c>
       <c r="HN13" t="n">
-        <v>811626.16610836</v>
+        <v>811626.162336572</v>
       </c>
       <c r="HO13" t="n">
-        <v>814060.676762744</v>
+        <v>814060.672962983</v>
       </c>
       <c r="HP13" t="n">
-        <v>816537.503885304</v>
+        <v>816537.500058475</v>
       </c>
       <c r="HQ13" t="n">
-        <v>819110.580630811</v>
+        <v>819110.576775134</v>
       </c>
       <c r="HR13" t="n">
-        <v>821692.463706748</v>
+        <v>821692.459819732</v>
       </c>
       <c r="HS13" t="n">
-        <v>823299.566182623</v>
+        <v>823299.562268308</v>
       </c>
       <c r="HT13" t="n">
-        <v>825704.765540611</v>
+        <v>825704.761593842</v>
       </c>
       <c r="HU13" t="n">
-        <v>827719.664282396</v>
+        <v>827719.66030336</v>
       </c>
     </row>
     <row r="14">
@@ -10802,139 +10802,139 @@
         <v>681761</v>
       </c>
       <c r="GC14" t="n">
-        <v>685991.791043501</v>
+        <v>685991.790982611</v>
       </c>
       <c r="GD14" t="n">
-        <v>694055.018363493</v>
+        <v>694055.018279022</v>
       </c>
       <c r="GE14" t="n">
-        <v>699887.347689977</v>
+        <v>699887.347519575</v>
       </c>
       <c r="GF14" t="n">
-        <v>706537.139488966</v>
+        <v>706537.13929819</v>
       </c>
       <c r="GG14" t="n">
-        <v>712317.527750436</v>
+        <v>712317.527544856</v>
       </c>
       <c r="GH14" t="n">
-        <v>717253.184551191</v>
+        <v>717253.184362601</v>
       </c>
       <c r="GI14" t="n">
-        <v>721549.225771469</v>
+        <v>721549.225618743</v>
       </c>
       <c r="GJ14" t="n">
-        <v>725303.377919799</v>
+        <v>725303.377828785</v>
       </c>
       <c r="GK14" t="n">
-        <v>729132.022139139</v>
+        <v>729132.022123893</v>
       </c>
       <c r="GL14" t="n">
-        <v>733120.190865349</v>
+        <v>733120.190944831</v>
       </c>
       <c r="GM14" t="n">
-        <v>736977.261021407</v>
+        <v>736977.26119375</v>
       </c>
       <c r="GN14" t="n">
-        <v>740061.976762008</v>
+        <v>740061.977033863</v>
       </c>
       <c r="GO14" t="n">
-        <v>743252.595195788</v>
+        <v>743252.595564336</v>
       </c>
       <c r="GP14" t="n">
-        <v>746710.235007898</v>
+        <v>746710.235489145</v>
       </c>
       <c r="GQ14" t="n">
-        <v>749886.505202338</v>
+        <v>749886.505795723</v>
       </c>
       <c r="GR14" t="n">
-        <v>753269.601873048</v>
+        <v>753269.60258759</v>
       </c>
       <c r="GS14" t="n">
-        <v>756786.898085005</v>
+        <v>756786.898920844</v>
       </c>
       <c r="GT14" t="n">
-        <v>760452.50550832</v>
+        <v>760452.50646781</v>
       </c>
       <c r="GU14" t="n">
-        <v>763846.034939334</v>
+        <v>763846.036018613</v>
       </c>
       <c r="GV14" t="n">
-        <v>767394.498167388</v>
+        <v>767394.499363981</v>
       </c>
       <c r="GW14" t="n">
-        <v>771161.916771051</v>
+        <v>771161.918081446</v>
       </c>
       <c r="GX14" t="n">
-        <v>775130.287005242</v>
+        <v>775130.288425432</v>
       </c>
       <c r="GY14" t="n">
-        <v>778921.088682289</v>
+        <v>778921.090205098</v>
       </c>
       <c r="GZ14" t="n">
-        <v>782930.416389031</v>
+        <v>782930.41800908</v>
       </c>
       <c r="HA14" t="n">
-        <v>787182.950190867</v>
+        <v>787182.951901498</v>
       </c>
       <c r="HB14" t="n">
-        <v>791649.678470892</v>
+        <v>791649.680264262</v>
       </c>
       <c r="HC14" t="n">
-        <v>795802.381023361</v>
+        <v>795802.382888791</v>
       </c>
       <c r="HD14" t="n">
-        <v>800143.069053169</v>
+        <v>800143.070982437</v>
       </c>
       <c r="HE14" t="n">
-        <v>804620.196678336</v>
+        <v>804620.198663451</v>
       </c>
       <c r="HF14" t="n">
-        <v>809181.660911197</v>
+        <v>809181.662944173</v>
       </c>
       <c r="HG14" t="n">
-        <v>813403.500838375</v>
+        <v>813403.502909599</v>
       </c>
       <c r="HH14" t="n">
-        <v>817645.135263155</v>
+        <v>817645.137365052</v>
       </c>
       <c r="HI14" t="n">
-        <v>821997.502411545</v>
+        <v>821997.504537775</v>
       </c>
       <c r="HJ14" t="n">
-        <v>826391.364404439</v>
+        <v>826391.3665486</v>
       </c>
       <c r="HK14" t="n">
-        <v>830400.840635878</v>
+        <v>830400.842788984</v>
       </c>
       <c r="HL14" t="n">
-        <v>834422.955365071</v>
+        <v>834422.957521357</v>
       </c>
       <c r="HM14" t="n">
-        <v>838530.933944782</v>
+        <v>838530.936098915</v>
       </c>
       <c r="HN14" t="n">
-        <v>842657.591811736</v>
+        <v>842657.593958723</v>
       </c>
       <c r="HO14" t="n">
-        <v>846368.38494938</v>
+        <v>846368.387081578</v>
       </c>
       <c r="HP14" t="n">
-        <v>850036.481487656</v>
+        <v>850036.483600149</v>
       </c>
       <c r="HQ14" t="n">
-        <v>853794.079735351</v>
+        <v>853794.08182472</v>
       </c>
       <c r="HR14" t="n">
-        <v>857574.807977382</v>
+        <v>857574.810040409</v>
       </c>
       <c r="HS14" t="n">
-        <v>860827.630737255</v>
+        <v>860827.632768053</v>
       </c>
       <c r="HT14" t="n">
-        <v>864130.095852412</v>
+        <v>864130.097848613</v>
       </c>
       <c r="HU14" t="n">
-        <v>867508.539246715</v>
+        <v>867508.541206919</v>
       </c>
     </row>
     <row r="15">
@@ -11491,139 +11491,139 @@
         <v>718591</v>
       </c>
       <c r="GC15" t="n">
-        <v>722465.949587139</v>
+        <v>722465.949255665</v>
       </c>
       <c r="GD15" t="n">
-        <v>746181.017728034</v>
+        <v>746181.017015557</v>
       </c>
       <c r="GE15" t="n">
-        <v>757754.677230078</v>
+        <v>757754.676205725</v>
       </c>
       <c r="GF15" t="n">
-        <v>778154.727028813</v>
+        <v>778154.725561157</v>
       </c>
       <c r="GG15" t="n">
-        <v>793998.240851665</v>
+        <v>793998.23894833</v>
       </c>
       <c r="GH15" t="n">
-        <v>808487.251754077</v>
+        <v>808487.249401088</v>
       </c>
       <c r="GI15" t="n">
-        <v>822675.202475851</v>
+        <v>822675.19967192</v>
       </c>
       <c r="GJ15" t="n">
-        <v>835914.927649359</v>
+        <v>835914.924429802</v>
       </c>
       <c r="GK15" t="n">
-        <v>849589.245250948</v>
+        <v>849589.241603711</v>
       </c>
       <c r="GL15" t="n">
-        <v>862977.320864642</v>
+        <v>862977.316797541</v>
       </c>
       <c r="GM15" t="n">
-        <v>875811.629631768</v>
+        <v>875811.625105886</v>
       </c>
       <c r="GN15" t="n">
-        <v>887542.565981364</v>
+        <v>887542.561041571</v>
       </c>
       <c r="GO15" t="n">
-        <v>899743.539305915</v>
+        <v>899743.533952259</v>
       </c>
       <c r="GP15" t="n">
-        <v>912095.44884515</v>
+        <v>912095.443110715</v>
       </c>
       <c r="GQ15" t="n">
-        <v>923823.061888901</v>
+        <v>923823.055790985</v>
       </c>
       <c r="GR15" t="n">
-        <v>935745.519103922</v>
+        <v>935745.512663679</v>
       </c>
       <c r="GS15" t="n">
-        <v>947570.887432621</v>
+        <v>947570.880671052</v>
       </c>
       <c r="GT15" t="n">
-        <v>959506.139166591</v>
+        <v>959506.13209917</v>
       </c>
       <c r="GU15" t="n">
-        <v>970900.106436179</v>
+        <v>970900.099086042</v>
       </c>
       <c r="GV15" t="n">
-        <v>982665.921934762</v>
+        <v>982665.914307902</v>
       </c>
       <c r="GW15" t="n">
-        <v>994497.890951462</v>
+        <v>994497.88306729</v>
       </c>
       <c r="GX15" t="n">
-        <v>1006569.01947697</v>
+        <v>1006569.01134535</v>
       </c>
       <c r="GY15" t="n">
-        <v>1018478.23916277</v>
+        <v>1018478.23079495</v>
       </c>
       <c r="GZ15" t="n">
-        <v>1030737.92397927</v>
+        <v>1030737.9153832</v>
       </c>
       <c r="HA15" t="n">
-        <v>1043353.01808655</v>
+        <v>1043353.00926784</v>
       </c>
       <c r="HB15" t="n">
-        <v>1056555.96821226</v>
+        <v>1056555.95916543</v>
       </c>
       <c r="HC15" t="n">
-        <v>1069206.08627052</v>
+        <v>1069206.0770135</v>
       </c>
       <c r="HD15" t="n">
-        <v>1082818.26008875</v>
+        <v>1082818.25060279</v>
       </c>
       <c r="HE15" t="n">
-        <v>1096486.54863624</v>
+        <v>1096486.53893352</v>
       </c>
       <c r="HF15" t="n">
-        <v>1110518.25366374</v>
+        <v>1110518.243741</v>
       </c>
       <c r="HG15" t="n">
-        <v>1124442.90325998</v>
+        <v>1124442.8931187</v>
       </c>
       <c r="HH15" t="n">
-        <v>1138703.5886623</v>
+        <v>1138703.57830132</v>
       </c>
       <c r="HI15" t="n">
-        <v>1153375.20589264</v>
+        <v>1153375.19530958</v>
       </c>
       <c r="HJ15" t="n">
-        <v>1168346.54163771</v>
+        <v>1168346.53082982</v>
       </c>
       <c r="HK15" t="n">
-        <v>1183156.66758373</v>
+        <v>1183156.65654964</v>
       </c>
       <c r="HL15" t="n">
-        <v>1198317.7352477</v>
+        <v>1198317.72398417</v>
       </c>
       <c r="HM15" t="n">
-        <v>1213859.23120743</v>
+        <v>1213859.21970902</v>
       </c>
       <c r="HN15" t="n">
-        <v>1229666.74742651</v>
+        <v>1229666.73568783</v>
       </c>
       <c r="HO15" t="n">
-        <v>1245245.94134398</v>
+        <v>1245245.92936126</v>
       </c>
       <c r="HP15" t="n">
-        <v>1261087.84410499</v>
+        <v>1261087.83187208</v>
       </c>
       <c r="HQ15" t="n">
-        <v>1277297.22856201</v>
+        <v>1277297.21607073</v>
       </c>
       <c r="HR15" t="n">
-        <v>1293747.63565143</v>
+        <v>1293747.62289365</v>
       </c>
       <c r="HS15" t="n">
-        <v>1309144.37751116</v>
+        <v>1309144.36450333</v>
       </c>
       <c r="HT15" t="n">
-        <v>1325627.40889273</v>
+        <v>1325627.39560341</v>
       </c>
       <c r="HU15" t="n">
-        <v>1341942.38324988</v>
+        <v>1341942.36968465</v>
       </c>
     </row>
     <row r="16">
@@ -12180,139 +12180,139 @@
         <v>1.04405241540033</v>
       </c>
       <c r="GC16" t="n">
-        <v>1.04877443846513</v>
+        <v>1.04877443833457</v>
       </c>
       <c r="GD16" t="n">
-        <v>1.0605114968813</v>
+        <v>1.0605114964338</v>
       </c>
       <c r="GE16" t="n">
-        <v>1.07634833202215</v>
+        <v>1.07634833142797</v>
       </c>
       <c r="GF16" t="n">
-        <v>1.08900920062394</v>
+        <v>1.08900919969795</v>
       </c>
       <c r="GG16" t="n">
-        <v>1.10379021035014</v>
+        <v>1.10379020914826</v>
       </c>
       <c r="GH16" t="n">
-        <v>1.11629919471804</v>
+        <v>1.11629919321191</v>
       </c>
       <c r="GI16" t="n">
-        <v>1.12876761544896</v>
+        <v>1.12876761363586</v>
       </c>
       <c r="GJ16" t="n">
-        <v>1.1415398144616</v>
+        <v>1.14153981235997</v>
       </c>
       <c r="GK16" t="n">
-        <v>1.15410778348069</v>
+        <v>1.15410778107853</v>
       </c>
       <c r="GL16" t="n">
-        <v>1.16638725699936</v>
+        <v>1.16638725430616</v>
       </c>
       <c r="GM16" t="n">
-        <v>1.17798515164696</v>
+        <v>1.17798514865319</v>
       </c>
       <c r="GN16" t="n">
-        <v>1.18996411355285</v>
+        <v>1.18996411027693</v>
       </c>
       <c r="GO16" t="n">
-        <v>1.2017283903317</v>
+        <v>1.20172838677248</v>
       </c>
       <c r="GP16" t="n">
-        <v>1.21354985479394</v>
+        <v>1.21354985097721</v>
       </c>
       <c r="GQ16" t="n">
-        <v>1.22526289759581</v>
+        <v>1.22526289353899</v>
       </c>
       <c r="GR16" t="n">
-        <v>1.23683579876483</v>
+        <v>1.2368357944775</v>
       </c>
       <c r="GS16" t="n">
-        <v>1.2483379634755</v>
+        <v>1.24833795898015</v>
       </c>
       <c r="GT16" t="n">
-        <v>1.25986762137777</v>
+        <v>1.25986761668654</v>
       </c>
       <c r="GU16" t="n">
-        <v>1.27143224307188</v>
+        <v>1.27143223820511</v>
       </c>
       <c r="GV16" t="n">
-        <v>1.28288015638918</v>
+        <v>1.28288015134831</v>
       </c>
       <c r="GW16" t="n">
-        <v>1.29441664262318</v>
+        <v>1.29441663742944</v>
       </c>
       <c r="GX16" t="n">
-        <v>1.30600459871772</v>
+        <v>1.30600459338153</v>
       </c>
       <c r="GY16" t="n">
-        <v>1.31765705646768</v>
+        <v>1.31765705099761</v>
       </c>
       <c r="GZ16" t="n">
-        <v>1.32938945348251</v>
+        <v>1.32938944788484</v>
       </c>
       <c r="HA16" t="n">
-        <v>1.34123693596291</v>
+        <v>1.34123693024569</v>
       </c>
       <c r="HB16" t="n">
-        <v>1.35353642117406</v>
+        <v>1.35353641533388</v>
       </c>
       <c r="HC16" t="n">
-        <v>1.36615976842889</v>
+        <v>1.36615976247981</v>
       </c>
       <c r="HD16" t="n">
-        <v>1.37865763764365</v>
+        <v>1.37865763156499</v>
       </c>
       <c r="HE16" t="n">
-        <v>1.39153432135158</v>
+        <v>1.39153431515686</v>
       </c>
       <c r="HF16" t="n">
-        <v>1.40454987633027</v>
+        <v>1.40454987001595</v>
       </c>
       <c r="HG16" t="n">
-        <v>1.41774071300658</v>
+        <v>1.41774070656821</v>
       </c>
       <c r="HH16" t="n">
-        <v>1.43109895414821</v>
+        <v>1.43109894758024</v>
       </c>
       <c r="HI16" t="n">
-        <v>1.44464389113164</v>
+        <v>1.44464388443167</v>
       </c>
       <c r="HJ16" t="n">
-        <v>1.45838039060894</v>
+        <v>1.45838038377461</v>
       </c>
       <c r="HK16" t="n">
-        <v>1.47228130842214</v>
+        <v>1.47228130144759</v>
       </c>
       <c r="HL16" t="n">
-        <v>1.48635464401876</v>
+        <v>1.48635463689748</v>
       </c>
       <c r="HM16" t="n">
-        <v>1.50061480747268</v>
+        <v>1.50061480020207</v>
       </c>
       <c r="HN16" t="n">
-        <v>1.51506540846529</v>
+        <v>1.51506540104293</v>
       </c>
       <c r="HO16" t="n">
-        <v>1.5296721199659</v>
+        <v>1.5296721123862</v>
       </c>
       <c r="HP16" t="n">
-        <v>1.54443343625454</v>
+        <v>1.54443342851132</v>
       </c>
       <c r="HQ16" t="n">
-        <v>1.55937090309028</v>
+        <v>1.55937089518065</v>
       </c>
       <c r="HR16" t="n">
-        <v>1.57449127055225</v>
+        <v>1.57449126247415</v>
       </c>
       <c r="HS16" t="n">
-        <v>1.59011908356432</v>
+        <v>1.59011907532479</v>
       </c>
       <c r="HT16" t="n">
-        <v>1.60544959629668</v>
+        <v>1.60544958787601</v>
       </c>
       <c r="HU16" t="n">
-        <v>1.62125223457099</v>
+        <v>1.62125222597604</v>
       </c>
     </row>
     <row r="17">
@@ -12869,139 +12869,139 @@
         <v>143.5</v>
       </c>
       <c r="GC17" t="n">
-        <v>144.861825055634</v>
+        <v>144.861825036032</v>
       </c>
       <c r="GD17" t="n">
-        <v>146.567278244737</v>
+        <v>146.567278204913</v>
       </c>
       <c r="GE17" t="n">
-        <v>148.241631120265</v>
+        <v>148.241631055667</v>
       </c>
       <c r="GF17" t="n">
-        <v>150.062870020521</v>
+        <v>150.062869922578</v>
       </c>
       <c r="GG17" t="n">
-        <v>151.91321024026</v>
+        <v>151.913210100911</v>
       </c>
       <c r="GH17" t="n">
-        <v>153.807079458362</v>
+        <v>153.807079270962</v>
       </c>
       <c r="GI17" t="n">
-        <v>155.737810919236</v>
+        <v>155.737810677994</v>
       </c>
       <c r="GJ17" t="n">
-        <v>157.676999880166</v>
+        <v>157.676999581605</v>
       </c>
       <c r="GK17" t="n">
-        <v>159.6177057527</v>
+        <v>159.617705393002</v>
       </c>
       <c r="GL17" t="n">
-        <v>161.545074996623</v>
+        <v>161.54507457248</v>
       </c>
       <c r="GM17" t="n">
-        <v>163.438776337616</v>
+        <v>163.438775844355</v>
       </c>
       <c r="GN17" t="n">
-        <v>165.302610888808</v>
+        <v>165.302610326867</v>
       </c>
       <c r="GO17" t="n">
-        <v>167.147038037792</v>
+        <v>167.147037406829</v>
       </c>
       <c r="GP17" t="n">
-        <v>168.970765945683</v>
+        <v>168.97076524576</v>
       </c>
       <c r="GQ17" t="n">
-        <v>170.77115354191</v>
+        <v>170.771152773423</v>
       </c>
       <c r="GR17" t="n">
-        <v>172.561048489083</v>
+        <v>172.561047652913</v>
       </c>
       <c r="GS17" t="n">
-        <v>174.336530102246</v>
+        <v>174.336529199355</v>
       </c>
       <c r="GT17" t="n">
-        <v>176.103582601012</v>
+        <v>176.103581632536</v>
       </c>
       <c r="GU17" t="n">
-        <v>177.859926888798</v>
+        <v>177.859925856128</v>
       </c>
       <c r="GV17" t="n">
-        <v>179.614958938004</v>
+        <v>179.61495784256</v>
       </c>
       <c r="GW17" t="n">
-        <v>181.369117713858</v>
+        <v>181.369116557117</v>
       </c>
       <c r="GX17" t="n">
-        <v>183.126374965408</v>
+        <v>183.126373748861</v>
       </c>
       <c r="GY17" t="n">
-        <v>184.887022449267</v>
+        <v>184.887021174485</v>
       </c>
       <c r="GZ17" t="n">
-        <v>186.660358457495</v>
+        <v>186.66035712596</v>
       </c>
       <c r="HA17" t="n">
-        <v>188.445721695767</v>
+        <v>188.445720308962</v>
       </c>
       <c r="HB17" t="n">
-        <v>190.248135015593</v>
+        <v>190.2481335749</v>
       </c>
       <c r="HC17" t="n">
-        <v>192.064175415484</v>
+        <v>192.064173922479</v>
       </c>
       <c r="HD17" t="n">
-        <v>193.90718286428</v>
+        <v>193.907181320183</v>
       </c>
       <c r="HE17" t="n">
-        <v>195.771040480141</v>
+        <v>195.77103888629</v>
       </c>
       <c r="HF17" t="n">
-        <v>197.660860449584</v>
+        <v>197.660858807234</v>
       </c>
       <c r="HG17" t="n">
-        <v>199.574500577281</v>
+        <v>199.5744988877</v>
       </c>
       <c r="HH17" t="n">
-        <v>201.516645638089</v>
+        <v>201.516643902451</v>
       </c>
       <c r="HI17" t="n">
-        <v>203.486792985758</v>
+        <v>203.486791205144</v>
       </c>
       <c r="HJ17" t="n">
-        <v>205.48545485647</v>
+        <v>205.485453031879</v>
       </c>
       <c r="HK17" t="n">
-        <v>207.510211756145</v>
+        <v>207.510209888551</v>
       </c>
       <c r="HL17" t="n">
-        <v>209.56651188207</v>
+        <v>209.566509972304</v>
       </c>
       <c r="HM17" t="n">
-        <v>211.65125364358</v>
+        <v>211.65125169234</v>
       </c>
       <c r="HN17" t="n">
-        <v>213.764840738643</v>
+        <v>213.764838746508</v>
       </c>
       <c r="HO17" t="n">
-        <v>215.903849087981</v>
+        <v>215.903847055471</v>
       </c>
       <c r="HP17" t="n">
-        <v>218.069946203578</v>
+        <v>218.069944131086</v>
       </c>
       <c r="HQ17" t="n">
-        <v>220.262992738915</v>
+        <v>220.26299062667</v>
       </c>
       <c r="HR17" t="n">
-        <v>222.482166892017</v>
+        <v>222.482164740121</v>
       </c>
       <c r="HS17" t="n">
-        <v>224.718530376565</v>
+        <v>224.718528185303</v>
       </c>
       <c r="HT17" t="n">
-        <v>226.982582642591</v>
+        <v>226.982580411847</v>
       </c>
       <c r="HU17" t="n">
-        <v>229.265897580588</v>
+        <v>229.265895310311</v>
       </c>
     </row>
     <row r="18">
@@ -13558,139 +13558,139 @@
         <v>26114</v>
       </c>
       <c r="GC18" t="n">
-        <v>26415.8365035052</v>
+        <v>26415.8365048095</v>
       </c>
       <c r="GD18" t="n">
-        <v>26494.6807941305</v>
+        <v>26494.6807937833</v>
       </c>
       <c r="GE18" t="n">
-        <v>26905.6263127601</v>
+        <v>26905.6263101691</v>
       </c>
       <c r="GF18" t="n">
-        <v>27192.0542936201</v>
+        <v>27192.0542864247</v>
       </c>
       <c r="GG18" t="n">
-        <v>27574.8384278043</v>
+        <v>27574.8384154166</v>
       </c>
       <c r="GH18" t="n">
-        <v>27944.2034058628</v>
+        <v>27944.2033868636</v>
       </c>
       <c r="GI18" t="n">
-        <v>28315.8022889771</v>
+        <v>28315.8022620169</v>
       </c>
       <c r="GJ18" t="n">
-        <v>28692.1529859001</v>
+        <v>28692.1529500277</v>
       </c>
       <c r="GK18" t="n">
-        <v>29056.9952456738</v>
+        <v>29056.995200083</v>
       </c>
       <c r="GL18" t="n">
-        <v>29420.8575650557</v>
+        <v>29420.8575092684</v>
       </c>
       <c r="GM18" t="n">
-        <v>29779.9763970763</v>
+        <v>29779.9763309022</v>
       </c>
       <c r="GN18" t="n">
-        <v>30140.6131534836</v>
+        <v>30140.613076668</v>
       </c>
       <c r="GO18" t="n">
-        <v>30476.8632209282</v>
+        <v>30476.8631330847</v>
       </c>
       <c r="GP18" t="n">
-        <v>30805.4304622013</v>
+        <v>30805.4303632754</v>
       </c>
       <c r="GQ18" t="n">
-        <v>31130.6660409328</v>
+        <v>31130.6659313617</v>
       </c>
       <c r="GR18" t="n">
-        <v>31445.198940009</v>
+        <v>31445.1988198879</v>
       </c>
       <c r="GS18" t="n">
-        <v>31758.7693423531</v>
+        <v>31758.7692120974</v>
       </c>
       <c r="GT18" t="n">
-        <v>32067.2452474595</v>
+        <v>32067.2451073433</v>
       </c>
       <c r="GU18" t="n">
-        <v>32376.4355403382</v>
+        <v>32376.4353907693</v>
       </c>
       <c r="GV18" t="n">
-        <v>32677.9587089752</v>
+        <v>32677.9585502006</v>
       </c>
       <c r="GW18" t="n">
-        <v>32978.7671159119</v>
+        <v>32978.7669482435</v>
       </c>
       <c r="GX18" t="n">
-        <v>33277.718497008</v>
+        <v>33277.7183207276</v>
       </c>
       <c r="GY18" t="n">
-        <v>33578.619780337</v>
+        <v>33578.6195957268</v>
       </c>
       <c r="GZ18" t="n">
-        <v>33875.5493965322</v>
+        <v>33875.5492037495</v>
       </c>
       <c r="HA18" t="n">
-        <v>34176.0191724479</v>
+        <v>34176.0189717193</v>
       </c>
       <c r="HB18" t="n">
-        <v>34477.5448238568</v>
+        <v>34477.544615345</v>
       </c>
       <c r="HC18" t="n">
-        <v>34787.6353792272</v>
+        <v>34787.635163077</v>
       </c>
       <c r="HD18" t="n">
-        <v>35089.6839370613</v>
+        <v>35089.6837133239</v>
       </c>
       <c r="HE18" t="n">
-        <v>35402.0530858433</v>
+        <v>35402.0528546136</v>
       </c>
       <c r="HF18" t="n">
-        <v>35715.842903768</v>
+        <v>35715.8426651062</v>
       </c>
       <c r="HG18" t="n">
-        <v>36035.8415776012</v>
+        <v>36035.8413315641</v>
       </c>
       <c r="HH18" t="n">
-        <v>36356.0144216383</v>
+        <v>36356.0141682394</v>
       </c>
       <c r="HI18" t="n">
-        <v>36679.7317284234</v>
+        <v>36679.7314677092</v>
       </c>
       <c r="HJ18" t="n">
-        <v>37007.5228251437</v>
+        <v>37007.522557153</v>
       </c>
       <c r="HK18" t="n">
-        <v>37341.4834016358</v>
+        <v>37341.4831264051</v>
       </c>
       <c r="HL18" t="n">
-        <v>37674.8924336375</v>
+        <v>37674.8921511431</v>
       </c>
       <c r="HM18" t="n">
-        <v>38013.2953805912</v>
+        <v>38013.29509086</v>
       </c>
       <c r="HN18" t="n">
-        <v>38355.3904522713</v>
+        <v>38355.3901552987</v>
       </c>
       <c r="HO18" t="n">
-        <v>38703.7272997378</v>
+        <v>38703.7269955204</v>
       </c>
       <c r="HP18" t="n">
-        <v>39052.5267003419</v>
+        <v>39052.5263888293</v>
       </c>
       <c r="HQ18" t="n">
-        <v>39402.7738412741</v>
+        <v>39402.7735224389</v>
       </c>
       <c r="HR18" t="n">
-        <v>39756.4349257364</v>
+        <v>39756.4345995389</v>
       </c>
       <c r="HS18" t="n">
-        <v>40120.0056887909</v>
+        <v>40120.0053551711</v>
       </c>
       <c r="HT18" t="n">
-        <v>40471.584643582</v>
+        <v>40471.5843025318</v>
       </c>
       <c r="HU18" t="n">
-        <v>40831.4840751055</v>
+        <v>40831.4837265466</v>
       </c>
     </row>
     <row r="19">
@@ -14247,139 +14247,139 @@
         <v>14608.7589597667</v>
       </c>
       <c r="GC19" t="n">
-        <v>14660.1382923385</v>
+        <v>14660.1382908138</v>
       </c>
       <c r="GD19" t="n">
-        <v>14784.3907884891</v>
+        <v>14784.3907849657</v>
       </c>
       <c r="GE19" t="n">
-        <v>14873.7006956972</v>
+        <v>14873.7006897608</v>
       </c>
       <c r="GF19" t="n">
-        <v>14979.6240019468</v>
+        <v>14979.6239936873</v>
       </c>
       <c r="GG19" t="n">
-        <v>15073.6227726833</v>
+        <v>15073.6227619722</v>
       </c>
       <c r="GH19" t="n">
-        <v>15154.7536184065</v>
+        <v>15154.7536053024</v>
       </c>
       <c r="GI19" t="n">
-        <v>15223.4317449289</v>
+        <v>15223.4317295647</v>
       </c>
       <c r="GJ19" t="n">
-        <v>15278.9814911632</v>
+        <v>15278.9814737081</v>
       </c>
       <c r="GK19" t="n">
-        <v>15327.5557380951</v>
+        <v>15327.5557187814</v>
       </c>
       <c r="GL19" t="n">
-        <v>15371.4471596381</v>
+        <v>15371.4471386894</v>
       </c>
       <c r="GM19" t="n">
-        <v>15411.0513271861</v>
+        <v>15411.0513046542</v>
       </c>
       <c r="GN19" t="n">
-        <v>15438.1692357958</v>
+        <v>15438.1692116841</v>
       </c>
       <c r="GO19" t="n">
-        <v>15462.5237053484</v>
+        <v>15462.5236798803</v>
       </c>
       <c r="GP19" t="n">
-        <v>15486.6849791247</v>
+        <v>15486.6849526166</v>
       </c>
       <c r="GQ19" t="n">
-        <v>15509.0997682217</v>
+        <v>15509.099740885</v>
       </c>
       <c r="GR19" t="n">
-        <v>15531.6194771866</v>
+        <v>15531.6194493314</v>
       </c>
       <c r="GS19" t="n">
-        <v>15555.2674474206</v>
+        <v>15555.2674192707</v>
       </c>
       <c r="GT19" t="n">
-        <v>15580.6922220198</v>
+        <v>15580.6921937828</v>
       </c>
       <c r="GU19" t="n">
-        <v>15605.4442687677</v>
+        <v>15605.4442405689</v>
       </c>
       <c r="GV19" t="n">
-        <v>15632.3490535868</v>
+        <v>15632.3490255688</v>
       </c>
       <c r="GW19" t="n">
-        <v>15661.1732742521</v>
+        <v>15661.173246529</v>
       </c>
       <c r="GX19" t="n">
-        <v>15692.5940361631</v>
+        <v>15692.5940088257</v>
       </c>
       <c r="GY19" t="n">
-        <v>15725.107508994</v>
+        <v>15725.1074820831</v>
       </c>
       <c r="GZ19" t="n">
-        <v>15759.4890730033</v>
+        <v>15759.4890465908</v>
       </c>
       <c r="HA19" t="n">
-        <v>15796.7509629593</v>
+        <v>15796.7509370761</v>
       </c>
       <c r="HB19" t="n">
-        <v>15837.4747189529</v>
+        <v>15837.4746936044</v>
       </c>
       <c r="HC19" t="n">
-        <v>15877.1565979911</v>
+        <v>15877.1565731392</v>
       </c>
       <c r="HD19" t="n">
-        <v>15919.9771535063</v>
+        <v>15919.9771291619</v>
       </c>
       <c r="HE19" t="n">
-        <v>15964.2554949907</v>
+        <v>15964.2554711333</v>
       </c>
       <c r="HF19" t="n">
-        <v>16010.2679804134</v>
+        <v>16010.2679570229</v>
       </c>
       <c r="HG19" t="n">
-        <v>16056.0867431059</v>
+        <v>16056.0867201441</v>
       </c>
       <c r="HH19" t="n">
-        <v>16102.1438433491</v>
+        <v>16102.1438208044</v>
       </c>
       <c r="HI19" t="n">
-        <v>16149.2688366964</v>
+        <v>16149.2688145554</v>
       </c>
       <c r="HJ19" t="n">
-        <v>16197.3550392527</v>
+        <v>16197.3550174937</v>
       </c>
       <c r="HK19" t="n">
-        <v>16244.4397363465</v>
+        <v>16244.4397149243</v>
       </c>
       <c r="HL19" t="n">
-        <v>16290.9862757092</v>
+        <v>16290.9862546113</v>
       </c>
       <c r="HM19" t="n">
-        <v>16338.0042141144</v>
+        <v>16338.0041933129</v>
       </c>
       <c r="HN19" t="n">
-        <v>16385.3837858151</v>
+        <v>16385.3837652746</v>
       </c>
       <c r="HO19" t="n">
-        <v>16431.1898745545</v>
+        <v>16431.1898542148</v>
       </c>
       <c r="HP19" t="n">
-        <v>16476.1725615083</v>
+        <v>16476.1725413265</v>
       </c>
       <c r="HQ19" t="n">
-        <v>16521.205950644</v>
+        <v>16521.2059305811</v>
       </c>
       <c r="HR19" t="n">
-        <v>16566.3518577967</v>
+        <v>16566.3518378067</v>
       </c>
       <c r="HS19" t="n">
-        <v>16606.2503449746</v>
+        <v>16606.2503249918</v>
       </c>
       <c r="HT19" t="n">
-        <v>16647.0336193902</v>
+        <v>16647.0335993825</v>
       </c>
       <c r="HU19" t="n">
-        <v>16686.7569145983</v>
+        <v>16686.756894527</v>
       </c>
     </row>
     <row r="20">
@@ -14936,139 +14936,139 @@
         <v>0.669101939</v>
       </c>
       <c r="GC20" t="n">
-        <v>0.668738443496059</v>
+        <v>0.668738443493437</v>
       </c>
       <c r="GD20" t="n">
-        <v>0.668207338805949</v>
+        <v>0.668207338782978</v>
       </c>
       <c r="GE20" t="n">
-        <v>0.668874023244265</v>
+        <v>0.668874023193749</v>
       </c>
       <c r="GF20" t="n">
-        <v>0.669265864397426</v>
+        <v>0.669265864313209</v>
       </c>
       <c r="GG20" t="n">
-        <v>0.669992092127643</v>
+        <v>0.669992092008903</v>
       </c>
       <c r="GH20" t="n">
-        <v>0.670563621014639</v>
+        <v>0.670563620862076</v>
       </c>
       <c r="GI20" t="n">
-        <v>0.67082887992208</v>
+        <v>0.670828879735494</v>
       </c>
       <c r="GJ20" t="n">
-        <v>0.671058691068006</v>
+        <v>0.671058690849045</v>
       </c>
       <c r="GK20" t="n">
-        <v>0.671099902770927</v>
+        <v>0.671099902521527</v>
       </c>
       <c r="GL20" t="n">
-        <v>0.671073274636327</v>
+        <v>0.671073274359972</v>
       </c>
       <c r="GM20" t="n">
-        <v>0.67096527099764</v>
+        <v>0.670965270697196</v>
       </c>
       <c r="GN20" t="n">
-        <v>0.67077205619218</v>
+        <v>0.670772055868517</v>
       </c>
       <c r="GO20" t="n">
-        <v>0.670446497943183</v>
+        <v>0.67044649759709</v>
       </c>
       <c r="GP20" t="n">
-        <v>0.670067619270057</v>
+        <v>0.670067618904415</v>
       </c>
       <c r="GQ20" t="n">
-        <v>0.669664801567653</v>
+        <v>0.669664801186322</v>
       </c>
       <c r="GR20" t="n">
-        <v>0.669240053728921</v>
+        <v>0.669240053335417</v>
       </c>
       <c r="GS20" t="n">
-        <v>0.668835524919603</v>
+        <v>0.668835524517931</v>
       </c>
       <c r="GT20" t="n">
-        <v>0.668435740434553</v>
+        <v>0.668435740027791</v>
       </c>
       <c r="GU20" t="n">
-        <v>0.668050433701609</v>
+        <v>0.668050433292613</v>
       </c>
       <c r="GV20" t="n">
-        <v>0.667665679818809</v>
+        <v>0.667665679409849</v>
       </c>
       <c r="GW20" t="n">
-        <v>0.667301985719807</v>
+        <v>0.667301985313034</v>
       </c>
       <c r="GX20" t="n">
-        <v>0.666964589903316</v>
+        <v>0.666964589500615</v>
       </c>
       <c r="GY20" t="n">
-        <v>0.666657932640853</v>
+        <v>0.666657932243705</v>
       </c>
       <c r="GZ20" t="n">
-        <v>0.666376047185408</v>
+        <v>0.666376046794848</v>
       </c>
       <c r="HA20" t="n">
-        <v>0.666137196485821</v>
+        <v>0.66613719610291</v>
       </c>
       <c r="HB20" t="n">
-        <v>0.665938232988956</v>
+        <v>0.66593823261433</v>
       </c>
       <c r="HC20" t="n">
-        <v>0.665778140482826</v>
+        <v>0.665778140116756</v>
       </c>
       <c r="HD20" t="n">
-        <v>0.665626714174029</v>
+        <v>0.665626713816379</v>
       </c>
       <c r="HE20" t="n">
-        <v>0.665523552790394</v>
+        <v>0.665523552441271</v>
       </c>
       <c r="HF20" t="n">
-        <v>0.665444285213617</v>
+        <v>0.665444284872856</v>
       </c>
       <c r="HG20" t="n">
-        <v>0.665388284711509</v>
+        <v>0.665388284378883</v>
       </c>
       <c r="HH20" t="n">
-        <v>0.665341796281577</v>
+        <v>0.665341795956703</v>
       </c>
       <c r="HI20" t="n">
-        <v>0.665306580744837</v>
+        <v>0.665306580427461</v>
       </c>
       <c r="HJ20" t="n">
-        <v>0.665287820186819</v>
+        <v>0.665287819876703</v>
       </c>
       <c r="HK20" t="n">
-        <v>0.665279292202685</v>
+        <v>0.665279291899466</v>
       </c>
       <c r="HL20" t="n">
-        <v>0.665267800745063</v>
+        <v>0.665267800448204</v>
       </c>
       <c r="HM20" t="n">
-        <v>0.66526505441499</v>
+        <v>0.665265054124157</v>
       </c>
       <c r="HN20" t="n">
-        <v>0.665267772078693</v>
+        <v>0.665267771793435</v>
       </c>
       <c r="HO20" t="n">
-        <v>0.665272761568176</v>
+        <v>0.665272761287944</v>
       </c>
       <c r="HP20" t="n">
-        <v>0.665264955367931</v>
+        <v>0.665264955091977</v>
       </c>
       <c r="HQ20" t="n">
-        <v>0.665247491229117</v>
+        <v>0.665247490956784</v>
       </c>
       <c r="HR20" t="n">
-        <v>0.665228855514821</v>
+        <v>0.665228855245502</v>
       </c>
       <c r="HS20" t="n">
-        <v>0.665202036526277</v>
+        <v>0.66520203625928</v>
       </c>
       <c r="HT20" t="n">
-        <v>0.665132082570181</v>
+        <v>0.665132082304693</v>
       </c>
       <c r="HU20" t="n">
-        <v>0.66506462542686</v>
+        <v>0.665064625162319</v>
       </c>
     </row>
     <row r="21">
@@ -15625,139 +15625,139 @@
         <v>0.0430614370315685</v>
       </c>
       <c r="GC21" t="n">
-        <v>0.047635545119364</v>
+        <v>0.0476355452146825</v>
       </c>
       <c r="GD21" t="n">
-        <v>0.0429469797638726</v>
+        <v>0.0429469799590524</v>
       </c>
       <c r="GE21" t="n">
-        <v>0.0422622892330235</v>
+        <v>0.0422622895429496</v>
       </c>
       <c r="GF21" t="n">
-        <v>0.0397043757479701</v>
+        <v>0.0397043761566259</v>
       </c>
       <c r="GG21" t="n">
-        <v>0.0384188218837082</v>
+        <v>0.0384188223965749</v>
       </c>
       <c r="GH21" t="n">
-        <v>0.0377529821387966</v>
+        <v>0.0377529827519163</v>
       </c>
       <c r="GI21" t="n">
-        <v>0.0374515887364424</v>
+        <v>0.0374515894401633</v>
       </c>
       <c r="GJ21" t="n">
-        <v>0.0377614077764547</v>
+        <v>0.0377614085617731</v>
       </c>
       <c r="GK21" t="n">
-        <v>0.0382422900829223</v>
+        <v>0.0382422909373827</v>
       </c>
       <c r="GL21" t="n">
-        <v>0.0389194493706399</v>
+        <v>0.0389194502846442</v>
       </c>
       <c r="GM21" t="n">
-        <v>0.0397459308345794</v>
+        <v>0.0397459318085481</v>
       </c>
       <c r="GN21" t="n">
-        <v>0.0411742063976497</v>
+        <v>0.0411742074325166</v>
       </c>
       <c r="GO21" t="n">
-        <v>0.042576610303911</v>
+        <v>0.042576611386634</v>
       </c>
       <c r="GP21" t="n">
-        <v>0.0439062800315088</v>
+        <v>0.0439062811463092</v>
       </c>
       <c r="GQ21" t="n">
-        <v>0.0453008809430374</v>
+        <v>0.0453008820821677</v>
       </c>
       <c r="GR21" t="n">
-        <v>0.0465294382073364</v>
+        <v>0.0465294393567139</v>
       </c>
       <c r="GS21" t="n">
-        <v>0.0477091895074912</v>
+        <v>0.0477091906589183</v>
       </c>
       <c r="GT21" t="n">
-        <v>0.048779107332555</v>
+        <v>0.0487791084776117</v>
       </c>
       <c r="GU21" t="n">
-        <v>0.0499031223260768</v>
+        <v>0.0499031234612238</v>
       </c>
       <c r="GV21" t="n">
-        <v>0.0509013193196546</v>
+        <v>0.0509013204393899</v>
       </c>
       <c r="GW21" t="n">
-        <v>0.0518060097932792</v>
+        <v>0.0518060108937556</v>
       </c>
       <c r="GX21" t="n">
-        <v>0.0525847501748503</v>
+        <v>0.0525847512532759</v>
       </c>
       <c r="GY21" t="n">
-        <v>0.0533357221987654</v>
+        <v>0.0533357232548638</v>
       </c>
       <c r="GZ21" t="n">
-        <v>0.0538974816373526</v>
+        <v>0.0538974826684908</v>
       </c>
       <c r="HA21" t="n">
-        <v>0.0543432684194741</v>
+        <v>0.0543432694253603</v>
       </c>
       <c r="HB21" t="n">
-        <v>0.0546353797921269</v>
+        <v>0.0546353807734029</v>
       </c>
       <c r="HC21" t="n">
-        <v>0.055042230370541</v>
+        <v>0.0550422313300796</v>
       </c>
       <c r="HD21" t="n">
-        <v>0.055189748262159</v>
+        <v>0.0551897491992756</v>
       </c>
       <c r="HE21" t="n">
-        <v>0.0553179413680615</v>
+        <v>0.0553179422842544</v>
       </c>
       <c r="HF21" t="n">
-        <v>0.0553766794533445</v>
+        <v>0.0553766803496886</v>
       </c>
       <c r="HG21" t="n">
-        <v>0.0554793944484464</v>
+        <v>0.0554793953270457</v>
       </c>
       <c r="HH21" t="n">
-        <v>0.0555371488560755</v>
+        <v>0.0555371497172604</v>
       </c>
       <c r="HI21" t="n">
-        <v>0.0555481083869366</v>
+        <v>0.055548109231266</v>
       </c>
       <c r="HJ21" t="n">
-        <v>0.0555264033311041</v>
+        <v>0.055526404159625</v>
       </c>
       <c r="HK21" t="n">
-        <v>0.0555778053174229</v>
+        <v>0.0555778061324279</v>
       </c>
       <c r="HL21" t="n">
-        <v>0.0555757981595824</v>
+        <v>0.0555757989612515</v>
       </c>
       <c r="HM21" t="n">
-        <v>0.0555588544418541</v>
+        <v>0.0555588552314353</v>
       </c>
       <c r="HN21" t="n">
-        <v>0.0555288783700227</v>
+        <v>0.0555288791490229</v>
       </c>
       <c r="HO21" t="n">
-        <v>0.0555927400645496</v>
+        <v>0.0555927408357918</v>
       </c>
       <c r="HP21" t="n">
-        <v>0.0556887249542633</v>
+        <v>0.0556887257192587</v>
       </c>
       <c r="HQ21" t="n">
-        <v>0.0557675592310736</v>
+        <v>0.0557675599911851</v>
       </c>
       <c r="HR21" t="n">
-        <v>0.0558377965009224</v>
+        <v>0.0558377972579612</v>
       </c>
       <c r="HS21" t="n">
-        <v>0.0561941721797361</v>
+        <v>0.05619417293662</v>
       </c>
       <c r="HT21" t="n">
-        <v>0.0564263786468954</v>
+        <v>0.0564263794043315</v>
       </c>
       <c r="HU21" t="n">
-        <v>0.0567202426446619</v>
+        <v>0.0567202434040637</v>
       </c>
     </row>
     <row r="22">
@@ -16314,139 +16314,139 @@
         <v>657.3819662</v>
       </c>
       <c r="GC22" t="n">
-        <v>733.273169184469</v>
+        <v>733.273170648825</v>
       </c>
       <c r="GD22" t="n">
-        <v>663.437684330631</v>
+        <v>663.437687322963</v>
       </c>
       <c r="GE22" t="n">
-        <v>656.334946139747</v>
+        <v>656.334950903321</v>
       </c>
       <c r="GF22" t="n">
-        <v>619.347521806121</v>
+        <v>619.347528102749</v>
       </c>
       <c r="GG22" t="n">
-        <v>602.248592581574</v>
+        <v>602.248600514517</v>
       </c>
       <c r="GH22" t="n">
-        <v>594.584561593167</v>
+        <v>594.584571114145</v>
       </c>
       <c r="GI22" t="n">
-        <v>592.325303469564</v>
+        <v>592.325314434715</v>
       </c>
       <c r="GJ22" t="n">
-        <v>599.59757530649</v>
+        <v>599.597587580534</v>
       </c>
       <c r="GK22" t="n">
-        <v>609.468383192889</v>
+        <v>609.468396583936</v>
       </c>
       <c r="GL22" t="n">
-        <v>622.474717885207</v>
+        <v>622.474732247418</v>
       </c>
       <c r="GM22" t="n">
-        <v>637.879791242465</v>
+        <v>637.879806587987</v>
       </c>
       <c r="GN22" t="n">
-        <v>662.950938116104</v>
+        <v>662.950954458693</v>
       </c>
       <c r="GO22" t="n">
-        <v>687.618406939422</v>
+        <v>687.618424070593</v>
       </c>
       <c r="GP22" t="n">
-        <v>711.188480678537</v>
+        <v>711.188498347827</v>
       </c>
       <c r="GQ22" t="n">
-        <v>735.913530393185</v>
+        <v>735.913548479324</v>
       </c>
       <c r="GR22" t="n">
-        <v>757.944373571294</v>
+        <v>757.944391848467</v>
       </c>
       <c r="GS22" t="n">
-        <v>779.309548924104</v>
+        <v>779.309567264168</v>
       </c>
       <c r="GT22" t="n">
-        <v>798.986219083115</v>
+        <v>798.98623735259</v>
       </c>
       <c r="GU22" t="n">
-        <v>819.664327785826</v>
+        <v>819.664345928875</v>
       </c>
       <c r="GV22" t="n">
-        <v>838.382073370121</v>
+        <v>838.382091299467</v>
       </c>
       <c r="GW22" t="n">
-        <v>855.671970698684</v>
+        <v>855.671988353482</v>
       </c>
       <c r="GX22" t="n">
-        <v>870.992168933442</v>
+        <v>870.992186270141</v>
       </c>
       <c r="GY22" t="n">
-        <v>885.963601876429</v>
+        <v>885.963618891605</v>
       </c>
       <c r="GZ22" t="n">
-        <v>897.785265436512</v>
+        <v>897.785282086257</v>
       </c>
       <c r="HA22" t="n">
-        <v>907.778875815775</v>
+        <v>907.778892096838</v>
       </c>
       <c r="HB22" t="n">
-        <v>915.294007302435</v>
+        <v>915.29402322659</v>
       </c>
       <c r="HC22" t="n">
-        <v>924.818305422112</v>
+        <v>924.818321035711</v>
       </c>
       <c r="HD22" t="n">
-        <v>929.942979586385</v>
+        <v>929.942994877063</v>
       </c>
       <c r="HE22" t="n">
-        <v>934.822330736701</v>
+        <v>934.822345729101</v>
       </c>
       <c r="HF22" t="n">
-        <v>938.570527826581</v>
+        <v>938.57054253792</v>
       </c>
       <c r="HG22" t="n">
-        <v>943.104999188534</v>
+        <v>943.105013652543</v>
       </c>
       <c r="HH22" t="n">
-        <v>946.852796558887</v>
+        <v>946.852810778906</v>
       </c>
       <c r="HI22" t="n">
-        <v>949.822305395299</v>
+        <v>949.82231937946</v>
       </c>
       <c r="HJ22" t="n">
-        <v>952.256383154041</v>
+        <v>952.256396918936</v>
       </c>
       <c r="HK22" t="n">
-        <v>955.960651763864</v>
+        <v>955.960665346567</v>
       </c>
       <c r="HL22" t="n">
-        <v>958.663179315667</v>
+        <v>958.663192716411</v>
       </c>
       <c r="HM22" t="n">
-        <v>961.119652449788</v>
+        <v>961.119665688657</v>
       </c>
       <c r="HN22" t="n">
-        <v>963.356225948351</v>
+        <v>963.356239049899</v>
       </c>
       <c r="HO22" t="n">
-        <v>967.225754299838</v>
+        <v>967.225767310832</v>
       </c>
       <c r="HP22" t="n">
-        <v>971.646974996256</v>
+        <v>971.64698794072</v>
       </c>
       <c r="HQ22" t="n">
-        <v>975.763432864209</v>
+        <v>975.763445764391</v>
       </c>
       <c r="HR22" t="n">
-        <v>979.734987834167</v>
+        <v>979.735000720568</v>
       </c>
       <c r="HS22" t="n">
-        <v>988.735852134658</v>
+        <v>988.735865055183</v>
       </c>
       <c r="HT22" t="n">
-        <v>995.50471096607</v>
+        <v>995.504723931772</v>
       </c>
       <c r="HU22" t="n">
-        <v>1003.38957046326</v>
+        <v>1003.38958349806</v>
       </c>
     </row>
     <row r="23">
@@ -17003,139 +17003,139 @@
         <v>0.0362333333333333</v>
       </c>
       <c r="GC23" t="n">
-        <v>0.0314049555370946</v>
+        <v>0.0314049553003385</v>
       </c>
       <c r="GD23" t="n">
-        <v>0.0418909248980678</v>
+        <v>0.0418909243457843</v>
       </c>
       <c r="GE23" t="n">
-        <v>0.0485642617616931</v>
+        <v>0.048564260801248</v>
       </c>
       <c r="GF23" t="n">
-        <v>0.057490046358188</v>
+        <v>0.0574900449324341</v>
       </c>
       <c r="GG23" t="n">
-        <v>0.0652008461326639</v>
+        <v>0.0652008442306751</v>
       </c>
       <c r="GH23" t="n">
-        <v>0.0709882065523347</v>
+        <v>0.0709882041567446</v>
       </c>
       <c r="GI23" t="n">
-        <v>0.0757193610803496</v>
+        <v>0.0757193581888692</v>
       </c>
       <c r="GJ23" t="n">
-        <v>0.0784820554037434</v>
+        <v>0.078482052044651</v>
       </c>
       <c r="GK23" t="n">
-        <v>0.0800725990060011</v>
+        <v>0.0800725952304393</v>
       </c>
       <c r="GL23" t="n">
-        <v>0.0804565360785741</v>
+        <v>0.0804565319409796</v>
       </c>
       <c r="GM23" t="n">
-        <v>0.0796686173918926</v>
+        <v>0.0796686129262509</v>
       </c>
       <c r="GN23" t="n">
-        <v>0.0771015703813831</v>
+        <v>0.0771015656263362</v>
       </c>
       <c r="GO23" t="n">
-        <v>0.073859743649193</v>
+        <v>0.0738597386672685</v>
       </c>
       <c r="GP23" t="n">
-        <v>0.0702196390946762</v>
+        <v>0.0702196339544976</v>
       </c>
       <c r="GQ23" t="n">
-        <v>0.0661769196519819</v>
+        <v>0.0661769144169075</v>
       </c>
       <c r="GR23" t="n">
-        <v>0.0622662907952723</v>
+        <v>0.0622662855250369</v>
       </c>
       <c r="GS23" t="n">
-        <v>0.0583876197371345</v>
+        <v>0.0583876144763562</v>
       </c>
       <c r="GT23" t="n">
-        <v>0.0547110597449208</v>
+        <v>0.05471105453302</v>
       </c>
       <c r="GU23" t="n">
-        <v>0.0510325726501974</v>
+        <v>0.05103256751457</v>
       </c>
       <c r="GV23" t="n">
-        <v>0.0476458147885842</v>
+        <v>0.0476458097545583</v>
       </c>
       <c r="GW23" t="n">
-        <v>0.044539365316029</v>
+        <v>0.0445393604028814</v>
       </c>
       <c r="GX23" t="n">
-        <v>0.0417804044582965</v>
+        <v>0.0417803996804782</v>
       </c>
       <c r="GY23" t="n">
-        <v>0.0392343296395313</v>
+        <v>0.0392343250046122</v>
       </c>
       <c r="GZ23" t="n">
-        <v>0.0371605471177376</v>
+        <v>0.0371605426344513</v>
       </c>
       <c r="HA23" t="n">
-        <v>0.0354571221143882</v>
+        <v>0.0354571177860221</v>
       </c>
       <c r="HB23" t="n">
-        <v>0.0341881441707878</v>
+        <v>0.0341881399973922</v>
       </c>
       <c r="HC23" t="n">
-        <v>0.0329181028464435</v>
+        <v>0.0329180988234901</v>
       </c>
       <c r="HD23" t="n">
-        <v>0.0322201521263637</v>
+        <v>0.0322201482533588</v>
       </c>
       <c r="HE23" t="n">
-        <v>0.0317190482093268</v>
+        <v>0.0317190444818548</v>
       </c>
       <c r="HF23" t="n">
-        <v>0.031471423707355</v>
+        <v>0.0314714201212209</v>
       </c>
       <c r="HG23" t="n">
-        <v>0.0312891462861728</v>
+        <v>0.0312891428347487</v>
       </c>
       <c r="HH23" t="n">
-        <v>0.0312671573846681</v>
+        <v>0.0312671540641927</v>
       </c>
       <c r="HI23" t="n">
-        <v>0.0314039543717521</v>
+        <v>0.0314039511778042</v>
       </c>
       <c r="HJ23" t="n">
-        <v>0.0316590436482185</v>
+        <v>0.0316590405753057</v>
       </c>
       <c r="HK23" t="n">
-        <v>0.0318483838791073</v>
+        <v>0.0318483809193854</v>
       </c>
       <c r="HL23" t="n">
-        <v>0.0321530577107797</v>
+        <v>0.0321530548592867</v>
       </c>
       <c r="HM23" t="n">
-        <v>0.0325040808655626</v>
+        <v>0.0325040781154078</v>
       </c>
       <c r="HN23" t="n">
-        <v>0.0328883637444108</v>
+        <v>0.0328883610879304</v>
       </c>
       <c r="HO23" t="n">
-        <v>0.0331251879589588</v>
+        <v>0.0331251853860166</v>
       </c>
       <c r="HP23" t="n">
-        <v>0.0332824340416075</v>
+        <v>0.0332824315437678</v>
       </c>
       <c r="HQ23" t="n">
-        <v>0.0334340501264075</v>
+        <v>0.0334340476953785</v>
       </c>
       <c r="HR23" t="n">
-        <v>0.0335656401939877</v>
+        <v>0.0335656378207202</v>
       </c>
       <c r="HS23" t="n">
-        <v>0.0331895508556336</v>
+        <v>0.0331895485298051</v>
       </c>
       <c r="HT23" t="n">
-        <v>0.032940585364853</v>
+        <v>0.0329405830793991</v>
       </c>
       <c r="HU23" t="n">
-        <v>0.0325330020829802</v>
+        <v>0.0325329998302493</v>
       </c>
     </row>
     <row r="24">
@@ -17644,139 +17644,139 @@
         <v>0.04288</v>
       </c>
       <c r="GC24" t="n">
-        <v>0.0420180185765244</v>
+        <v>0.0420180185621423</v>
       </c>
       <c r="GD24" t="n">
-        <v>0.0418515770337133</v>
+        <v>0.041851576986759</v>
       </c>
       <c r="GE24" t="n">
-        <v>0.0421018230383782</v>
+        <v>0.04210182293627</v>
       </c>
       <c r="GF24" t="n">
-        <v>0.0428772786023373</v>
+        <v>0.042877278420556</v>
       </c>
       <c r="GG24" t="n">
-        <v>0.0440684597782565</v>
+        <v>0.0440684594932849</v>
       </c>
       <c r="GH24" t="n">
-        <v>0.0455302839340232</v>
+        <v>0.0455302835228866</v>
       </c>
       <c r="GI24" t="n">
-        <v>0.0471802053368479</v>
+        <v>0.0471802047779933</v>
       </c>
       <c r="GJ24" t="n">
-        <v>0.0488858695312313</v>
+        <v>0.0488858688062876</v>
       </c>
       <c r="GK24" t="n">
-        <v>0.0505722859483853</v>
+        <v>0.050572285043336</v>
       </c>
       <c r="GL24" t="n">
-        <v>0.0521674651409459</v>
+        <v>0.0521674640460337</v>
       </c>
       <c r="GM24" t="n">
-        <v>0.0536064189622667</v>
+        <v>0.0536064176704616</v>
       </c>
       <c r="GN24" t="n">
-        <v>0.0547916843726832</v>
+        <v>0.0547916828797798</v>
       </c>
       <c r="GO24" t="n">
-        <v>0.0556995042681334</v>
+        <v>0.0556995025740107</v>
       </c>
       <c r="GP24" t="n">
-        <v>0.0563245318763212</v>
+        <v>0.0563245299850348</v>
       </c>
       <c r="GQ24" t="n">
-        <v>0.0566615201756999</v>
+        <v>0.0566615180948787</v>
       </c>
       <c r="GR24" t="n">
-        <v>0.0567380599977979</v>
+        <v>0.0567380577381814</v>
       </c>
       <c r="GS24" t="n">
-        <v>0.0565737851969425</v>
+        <v>0.0565737827712509</v>
       </c>
       <c r="GT24" t="n">
-        <v>0.0561973320730861</v>
+        <v>0.0561973294955701</v>
       </c>
       <c r="GU24" t="n">
-        <v>0.0556229970543329</v>
+        <v>0.0556229943399395</v>
       </c>
       <c r="GV24" t="n">
-        <v>0.0548819439545783</v>
+        <v>0.0548819411187777</v>
       </c>
       <c r="GW24" t="n">
-        <v>0.0540025258228202</v>
+        <v>0.0540025228812025</v>
       </c>
       <c r="GX24" t="n">
-        <v>0.0530152506111242</v>
+        <v>0.0530152475790985</v>
       </c>
       <c r="GY24" t="n">
-        <v>0.0519403772167629</v>
+        <v>0.0519403741091514</v>
       </c>
       <c r="GZ24" t="n">
-        <v>0.0508125463181669</v>
+        <v>0.0508125431493152</v>
       </c>
       <c r="HA24" t="n">
-        <v>0.049657853248763</v>
+        <v>0.0496578500322422</v>
       </c>
       <c r="HB24" t="n">
-        <v>0.0485045138661292</v>
+        <v>0.0485045106145913</v>
       </c>
       <c r="HC24" t="n">
-        <v>0.0473523716164033</v>
+        <v>0.0473523683413659</v>
       </c>
       <c r="HD24" t="n">
-        <v>0.0462360976056032</v>
+        <v>0.0462360943177715</v>
       </c>
       <c r="HE24" t="n">
-        <v>0.0451652129962846</v>
+        <v>0.0451652097053683</v>
       </c>
       <c r="HF24" t="n">
-        <v>0.0441520323942986</v>
+        <v>0.044152029109093</v>
       </c>
       <c r="HG24" t="n">
-        <v>0.0431966055048977</v>
+        <v>0.043196602233198</v>
       </c>
       <c r="HH24" t="n">
-        <v>0.0423047460047415</v>
+        <v>0.042304742753585</v>
       </c>
       <c r="HI24" t="n">
-        <v>0.041481781362044</v>
+        <v>0.0414817781377211</v>
       </c>
       <c r="HJ24" t="n">
-        <v>0.040730217305373</v>
+        <v>0.0407302141134133</v>
       </c>
       <c r="HK24" t="n">
-        <v>0.0400412095032255</v>
+        <v>0.0400412063483066</v>
       </c>
       <c r="HL24" t="n">
-        <v>0.0394175145424152</v>
+        <v>0.0394175114285953</v>
       </c>
       <c r="HM24" t="n">
-        <v>0.0388575112073935</v>
+        <v>0.0388575081380368</v>
       </c>
       <c r="HN24" t="n">
-        <v>0.0383588932678097</v>
+        <v>0.038358890245586</v>
       </c>
       <c r="HO24" t="n">
-        <v>0.0379085331715294</v>
+        <v>0.0379085301983115</v>
       </c>
       <c r="HP24" t="n">
-        <v>0.0374983186306434</v>
+        <v>0.0374983157076646</v>
       </c>
       <c r="HQ24" t="n">
-        <v>0.0371251805141752</v>
+        <v>0.0371251776420812</v>
       </c>
       <c r="HR24" t="n">
-        <v>0.036785383674441</v>
+        <v>0.0367853808532839</v>
       </c>
       <c r="HS24" t="n">
-        <v>0.0364458235221847</v>
+        <v>0.0364458207513861</v>
       </c>
       <c r="HT24" t="n">
-        <v>0.0361142062914783</v>
+        <v>0.0361142035700699</v>
       </c>
       <c r="HU24" t="n">
-        <v>0.0357803569561626</v>
+        <v>0.035780354282777</v>
       </c>
     </row>
     <row r="25">
@@ -18329,139 +18329,139 @@
       <c r="GA25"/>
       <c r="GB25"/>
       <c r="GC25" t="n">
-        <v>0.411055361866531</v>
+        <v>0.41105536552998</v>
       </c>
       <c r="GD25" t="n">
-        <v>0.397564504015474</v>
+        <v>0.397564508381742</v>
       </c>
       <c r="GE25" t="n">
-        <v>0.385801463369563</v>
+        <v>0.385801468224219</v>
       </c>
       <c r="GF25" t="n">
-        <v>0.381070270846001</v>
+        <v>0.381070276743108</v>
       </c>
       <c r="GG25" t="n">
-        <v>0.378539109767697</v>
+        <v>0.378539116755105</v>
       </c>
       <c r="GH25" t="n">
-        <v>0.376143065908777</v>
+        <v>0.376143073808586</v>
       </c>
       <c r="GI25" t="n">
-        <v>0.373973392374181</v>
+        <v>0.373973401049868</v>
       </c>
       <c r="GJ25" t="n">
-        <v>0.370467293867481</v>
+        <v>0.370467302998928</v>
       </c>
       <c r="GK25" t="n">
-        <v>0.368712477944196</v>
+        <v>0.368712487630497</v>
       </c>
       <c r="GL25" t="n">
-        <v>0.368447321819495</v>
+        <v>0.368447332140239</v>
       </c>
       <c r="GM25" t="n">
-        <v>0.371823412334895</v>
+        <v>0.371823423685883</v>
       </c>
       <c r="GN25" t="n">
-        <v>0.370877679420827</v>
+        <v>0.370877691097061</v>
       </c>
       <c r="GO25" t="n">
-        <v>0.37048073940284</v>
+        <v>0.37048075138471</v>
       </c>
       <c r="GP25" t="n">
-        <v>0.370535676739303</v>
+        <v>0.370535688999875</v>
       </c>
       <c r="GQ25" t="n">
-        <v>0.37091473550667</v>
+        <v>0.370914748011809</v>
       </c>
       <c r="GR25" t="n">
-        <v>0.371304966532879</v>
+        <v>0.371304979202976</v>
       </c>
       <c r="GS25" t="n">
-        <v>0.371974621370414</v>
+        <v>0.371974634179583</v>
       </c>
       <c r="GT25" t="n">
-        <v>0.372819169301234</v>
+        <v>0.37281918221676</v>
       </c>
       <c r="GU25" t="n">
-        <v>0.37372332816331</v>
+        <v>0.373723341146536</v>
       </c>
       <c r="GV25" t="n">
-        <v>0.374552183162383</v>
+        <v>0.374552196163985</v>
       </c>
       <c r="GW25" t="n">
-        <v>0.375308784631339</v>
+        <v>0.37530879761111</v>
       </c>
       <c r="GX25" t="n">
-        <v>0.375927222505698</v>
+        <v>0.375927235421027</v>
       </c>
       <c r="GY25" t="n">
-        <v>0.376370112337683</v>
+        <v>0.376370125147654</v>
       </c>
       <c r="GZ25" t="n">
-        <v>0.376608411010761</v>
+        <v>0.376608423676483</v>
       </c>
       <c r="HA25" t="n">
-        <v>0.376608523758739</v>
+        <v>0.376608536242074</v>
       </c>
       <c r="HB25" t="n">
-        <v>0.376426801826615</v>
+        <v>0.376426814095744</v>
       </c>
       <c r="HC25" t="n">
-        <v>0.376049121737037</v>
+        <v>0.376049133765252</v>
       </c>
       <c r="HD25" t="n">
-        <v>0.375476235429661</v>
+        <v>0.375476247194699</v>
       </c>
       <c r="HE25" t="n">
-        <v>0.374692150895481</v>
+        <v>0.374692162374743</v>
       </c>
       <c r="HF25" t="n">
-        <v>0.373713075435714</v>
+        <v>0.373713086611747</v>
       </c>
       <c r="HG25" t="n">
-        <v>0.372575338301338</v>
+        <v>0.372575349163205</v>
       </c>
       <c r="HH25" t="n">
-        <v>0.371289653092655</v>
+        <v>0.371289663632633</v>
       </c>
       <c r="HI25" t="n">
-        <v>0.369912024737157</v>
+        <v>0.369912034955833</v>
       </c>
       <c r="HJ25" t="n">
-        <v>0.368461634599269</v>
+        <v>0.368461644500431</v>
       </c>
       <c r="HK25" t="n">
-        <v>0.36696814296447</v>
+        <v>0.366968152556243</v>
       </c>
       <c r="HL25" t="n">
-        <v>0.365435027462415</v>
+        <v>0.365435036753396</v>
       </c>
       <c r="HM25" t="n">
-        <v>0.363931616621715</v>
+        <v>0.363931625629774</v>
       </c>
       <c r="HN25" t="n">
-        <v>0.362472484531083</v>
+        <v>0.362472493275674</v>
       </c>
       <c r="HO25" t="n">
-        <v>0.36106982648693</v>
+        <v>0.361069834988679</v>
       </c>
       <c r="HP25" t="n">
-        <v>0.359729425467946</v>
+        <v>0.359729433747638</v>
       </c>
       <c r="HQ25" t="n">
-        <v>0.358463665691843</v>
+        <v>0.358463673771221</v>
       </c>
       <c r="HR25" t="n">
-        <v>0.357274560110373</v>
+        <v>0.357274568010654</v>
       </c>
       <c r="HS25" t="n">
-        <v>0.356189524977682</v>
+        <v>0.356189532721321</v>
       </c>
       <c r="HT25" t="n">
-        <v>0.355169937279026</v>
+        <v>0.355169944885022</v>
       </c>
       <c r="HU25" t="n">
-        <v>0.3542386299792</v>
+        <v>0.354238637466337</v>
       </c>
     </row>
     <row r="26">
@@ -19018,139 +19018,139 @@
         <v>0.653633333333333</v>
       </c>
       <c r="GC26" t="n">
-        <v>0.667386922597105</v>
+        <v>0.667386928644671</v>
       </c>
       <c r="GD26" t="n">
-        <v>0.642265803309994</v>
+        <v>0.642265810530617</v>
       </c>
       <c r="GE26" t="n">
-        <v>0.619534909343541</v>
+        <v>0.61953491733582</v>
       </c>
       <c r="GF26" t="n">
-        <v>0.608953726937546</v>
+        <v>0.608953736628208</v>
       </c>
       <c r="GG26" t="n">
-        <v>0.601699020313382</v>
+        <v>0.60169903174749</v>
       </c>
       <c r="GH26" t="n">
-        <v>0.594806071749658</v>
+        <v>0.594806084628679</v>
       </c>
       <c r="GI26" t="n">
-        <v>0.588355473462683</v>
+        <v>0.588355487553681</v>
       </c>
       <c r="GJ26" t="n">
-        <v>0.579812837238533</v>
+        <v>0.579812852014796</v>
       </c>
       <c r="GK26" t="n">
-        <v>0.574153106604152</v>
+        <v>0.574153122218484</v>
       </c>
       <c r="GL26" t="n">
-        <v>0.570899809227844</v>
+        <v>0.570899825797015</v>
       </c>
       <c r="GM26" t="n">
-        <v>0.573462710951917</v>
+        <v>0.573462729094722</v>
       </c>
       <c r="GN26" t="n">
-        <v>0.569233989949267</v>
+        <v>0.569234008542803</v>
       </c>
       <c r="GO26" t="n">
-        <v>0.565926495476232</v>
+        <v>0.565926514487328</v>
       </c>
       <c r="GP26" t="n">
-        <v>0.563343451038879</v>
+        <v>0.563343470418823</v>
       </c>
       <c r="GQ26" t="n">
-        <v>0.56129802653135</v>
+        <v>0.561298046222871</v>
       </c>
       <c r="GR26" t="n">
-        <v>0.559308855410215</v>
+        <v>0.559308875288119</v>
       </c>
       <c r="GS26" t="n">
-        <v>0.557773194584175</v>
+        <v>0.557773214605252</v>
       </c>
       <c r="GT26" t="n">
-        <v>0.556516179841725</v>
+        <v>0.55651619995379</v>
       </c>
       <c r="GU26" t="n">
-        <v>0.555357661421977</v>
+        <v>0.555357681563284</v>
       </c>
       <c r="GV26" t="n">
-        <v>0.554112663421072</v>
+        <v>0.554112683517531</v>
       </c>
       <c r="GW26" t="n">
-        <v>0.55276168784498</v>
+        <v>0.552761707833688</v>
       </c>
       <c r="GX26" t="n">
-        <v>0.551204783371838</v>
+        <v>0.551204803188239</v>
       </c>
       <c r="GY26" t="n">
-        <v>0.549395854405325</v>
+        <v>0.549395873988608</v>
       </c>
       <c r="GZ26" t="n">
-        <v>0.547293771354329</v>
+        <v>0.547293790647624</v>
       </c>
       <c r="HA26" t="n">
-        <v>0.544849288222467</v>
+        <v>0.544849307170345</v>
       </c>
       <c r="HB26" t="n">
-        <v>0.5420781892058</v>
+        <v>0.542078207761664</v>
       </c>
       <c r="HC26" t="n">
-        <v>0.53901301772219</v>
+        <v>0.539013035847341</v>
       </c>
       <c r="HD26" t="n">
-        <v>0.535709291707776</v>
+        <v>0.535709309376279</v>
       </c>
       <c r="HE26" t="n">
-        <v>0.532092182943127</v>
+        <v>0.532092200123059</v>
       </c>
       <c r="HF26" t="n">
-        <v>0.528216040056358</v>
+        <v>0.52821605672656</v>
       </c>
       <c r="HG26" t="n">
-        <v>0.524132828682307</v>
+        <v>0.524132844831271</v>
       </c>
       <c r="HH26" t="n">
-        <v>0.519861995169055</v>
+        <v>0.519862010790204</v>
       </c>
       <c r="HI26" t="n">
-        <v>0.515483794599243</v>
+        <v>0.5154838096976</v>
       </c>
       <c r="HJ26" t="n">
-        <v>0.511026799795606</v>
+        <v>0.5110268143807</v>
       </c>
       <c r="HK26" t="n">
-        <v>0.506536845934151</v>
+        <v>0.506536860021983</v>
       </c>
       <c r="HL26" t="n">
-        <v>0.502018975359536</v>
+        <v>0.502018988966613</v>
       </c>
       <c r="HM26" t="n">
-        <v>0.497568759200159</v>
+        <v>0.497568772355377</v>
       </c>
       <c r="HN26" t="n">
-        <v>0.493205552612968</v>
+        <v>0.493205565347043</v>
       </c>
       <c r="HO26" t="n">
-        <v>0.488948505263574</v>
+        <v>0.488948517608843</v>
       </c>
       <c r="HP26" t="n">
-        <v>0.484804547205776</v>
+        <v>0.484804559194423</v>
       </c>
       <c r="HQ26" t="n">
-        <v>0.480787405882121</v>
+        <v>0.480787417546875</v>
       </c>
       <c r="HR26" t="n">
-        <v>0.47689786802077</v>
+        <v>0.476897879393128</v>
       </c>
       <c r="HS26" t="n">
-        <v>0.473144142016137</v>
+        <v>0.473144153127359</v>
       </c>
       <c r="HT26" t="n">
-        <v>0.469540584718753</v>
+        <v>0.469540595599146</v>
       </c>
       <c r="HU26" t="n">
-        <v>0.466051853564763</v>
+        <v>0.466051864239941</v>
       </c>
     </row>
     <row r="27">
@@ -19707,139 +19707,139 @@
         <v>95.2225040638737</v>
       </c>
       <c r="GC27" t="n">
-        <v>93.6743249298867</v>
+        <v>93.6743249295834</v>
       </c>
       <c r="GD27" t="n">
-        <v>94.8742527922511</v>
+        <v>94.87425276081</v>
       </c>
       <c r="GE27" t="n">
-        <v>96.5107824808816</v>
+        <v>96.5107824628378</v>
       </c>
       <c r="GF27" t="n">
-        <v>97.330519996262</v>
+        <v>97.3305199655195</v>
       </c>
       <c r="GG27" t="n">
-        <v>98.5307020647199</v>
+        <v>98.5307020386827</v>
       </c>
       <c r="GH27" t="n">
-        <v>98.9471611089672</v>
+        <v>98.9471610955952</v>
       </c>
       <c r="GI27" t="n">
-        <v>99.2598842239717</v>
+        <v>99.2598842320185</v>
       </c>
       <c r="GJ27" t="n">
-        <v>99.5913708812774</v>
+        <v>99.5913709192454</v>
       </c>
       <c r="GK27" t="n">
-        <v>99.8505004816782</v>
+        <v>99.8505005530976</v>
       </c>
       <c r="GL27" t="n">
-        <v>100.012759968698</v>
+        <v>100.012760078045</v>
       </c>
       <c r="GM27" t="n">
-        <v>100.050004348195</v>
+        <v>100.050004498582</v>
       </c>
       <c r="GN27" t="n">
-        <v>100.160891309279</v>
+        <v>100.160891505686</v>
       </c>
       <c r="GO27" t="n">
-        <v>100.245995750179</v>
+        <v>100.245995995487</v>
       </c>
       <c r="GP27" t="n">
-        <v>100.345850362412</v>
+        <v>100.345850658661</v>
       </c>
       <c r="GQ27" t="n">
-        <v>100.435236881462</v>
+        <v>100.435237230207</v>
       </c>
       <c r="GR27" t="n">
-        <v>100.50636673308</v>
+        <v>100.50636713451</v>
       </c>
       <c r="GS27" t="n">
-        <v>100.571380013477</v>
+        <v>100.571380468734</v>
       </c>
       <c r="GT27" t="n">
-        <v>100.665924842129</v>
+        <v>100.66592535057</v>
       </c>
       <c r="GU27" t="n">
-        <v>100.773954343196</v>
+        <v>100.773954905298</v>
       </c>
       <c r="GV27" t="n">
-        <v>100.862828786901</v>
+        <v>100.862829400227</v>
       </c>
       <c r="GW27" t="n">
-        <v>100.964304560494</v>
+        <v>100.964305225057</v>
       </c>
       <c r="GX27" t="n">
-        <v>101.070595404254</v>
+        <v>101.070596118268</v>
       </c>
       <c r="GY27" t="n">
-        <v>101.176536909438</v>
+        <v>101.176537671139</v>
       </c>
       <c r="GZ27" t="n">
-        <v>101.280852151854</v>
+        <v>101.280852959267</v>
       </c>
       <c r="HA27" t="n">
-        <v>101.384064023186</v>
+        <v>101.384064874326</v>
       </c>
       <c r="HB27" t="n">
-        <v>101.601465686942</v>
+        <v>101.601466579383</v>
       </c>
       <c r="HC27" t="n">
-        <v>101.847518436889</v>
+        <v>101.847519370294</v>
       </c>
       <c r="HD27" t="n">
-        <v>102.048761262252</v>
+        <v>102.048762231272</v>
       </c>
       <c r="HE27" t="n">
-        <v>102.285603502334</v>
+        <v>102.285604506841</v>
       </c>
       <c r="HF27" t="n">
-        <v>102.513925399895</v>
+        <v>102.513926436979</v>
       </c>
       <c r="HG27" t="n">
-        <v>102.741701497834</v>
+        <v>102.741702565135</v>
       </c>
       <c r="HH27" t="n">
-        <v>102.965738116741</v>
+        <v>102.965739211925</v>
       </c>
       <c r="HI27" t="n">
-        <v>103.18550404438</v>
+        <v>103.185505165325</v>
       </c>
       <c r="HJ27" t="n">
-        <v>103.399950266852</v>
+        <v>103.399951411447</v>
       </c>
       <c r="HK27" t="n">
-        <v>103.607051968022</v>
+        <v>103.607053134067</v>
       </c>
       <c r="HL27" t="n">
-        <v>103.807796049471</v>
+        <v>103.807797235033</v>
       </c>
       <c r="HM27" t="n">
-        <v>104.001450488044</v>
+        <v>104.001451691406</v>
       </c>
       <c r="HN27" t="n">
-        <v>104.188088147456</v>
+        <v>104.188089366964</v>
       </c>
       <c r="HO27" t="n">
-        <v>104.366057376482</v>
+        <v>104.36605861044</v>
       </c>
       <c r="HP27" t="n">
-        <v>104.537473884861</v>
+        <v>104.537475131869</v>
       </c>
       <c r="HQ27" t="n">
-        <v>104.702571549126</v>
+        <v>104.70257280797</v>
       </c>
       <c r="HR27" t="n">
-        <v>104.861684050827</v>
+        <v>104.861685320412</v>
       </c>
       <c r="HS27" t="n">
-        <v>105.066581927777</v>
+        <v>105.06658320918</v>
       </c>
       <c r="HT27" t="n">
-        <v>105.202502021531</v>
+        <v>105.20250331121</v>
       </c>
       <c r="HU27" t="n">
-        <v>105.379475633708</v>
+        <v>105.379476932854</v>
       </c>
     </row>
     <row r="28">
@@ -20208,139 +20208,139 @@
       <c r="GA28"/>
       <c r="GB28"/>
       <c r="GC28" t="n">
-        <v>14.9825957220847</v>
+        <v>14.9825957301002</v>
       </c>
       <c r="GD28" t="n">
-        <v>14.7999522910792</v>
+        <v>14.7999523106963</v>
       </c>
       <c r="GE28" t="n">
-        <v>15.0045938735138</v>
+        <v>15.0045939048353</v>
       </c>
       <c r="GF28" t="n">
-        <v>15.0960140075995</v>
+        <v>15.096014053437</v>
       </c>
       <c r="GG28" t="n">
-        <v>15.0926637755266</v>
+        <v>15.0926638360319</v>
       </c>
       <c r="GH28" t="n">
-        <v>15.1964159162555</v>
+        <v>15.1964159893201</v>
       </c>
       <c r="GI28" t="n">
-        <v>15.3831351717457</v>
+        <v>15.3831352554629</v>
       </c>
       <c r="GJ28" t="n">
-        <v>15.8992042529269</v>
+        <v>15.8992043441839</v>
       </c>
       <c r="GK28" t="n">
-        <v>16.1128382871909</v>
+        <v>16.1128383822835</v>
       </c>
       <c r="GL28" t="n">
-        <v>16.3843279628453</v>
+        <v>16.3843280586527</v>
       </c>
       <c r="GM28" t="n">
-        <v>16.7040802781067</v>
+        <v>16.7040803726411</v>
       </c>
       <c r="GN28" t="n">
-        <v>17.3087030178455</v>
+        <v>17.3087031086214</v>
       </c>
       <c r="GO28" t="n">
-        <v>17.5534909280176</v>
+        <v>17.5534910120164</v>
       </c>
       <c r="GP28" t="n">
-        <v>17.8185668493054</v>
+        <v>17.8185669243765</v>
       </c>
       <c r="GQ28" t="n">
-        <v>18.1124704559156</v>
+        <v>18.11247052044</v>
       </c>
       <c r="GR28" t="n">
-        <v>18.7158060516601</v>
+        <v>18.7158061046024</v>
       </c>
       <c r="GS28" t="n">
-        <v>18.919132258165</v>
+        <v>18.9191322981048</v>
       </c>
       <c r="GT28" t="n">
-        <v>19.1293571923977</v>
+        <v>19.129357218753</v>
       </c>
       <c r="GU28" t="n">
-        <v>19.3659397504562</v>
+        <v>19.3659397628908</v>
       </c>
       <c r="GV28" t="n">
-        <v>19.9358634751398</v>
+        <v>19.9358634737677</v>
       </c>
       <c r="GW28" t="n">
-        <v>20.0687442754496</v>
+        <v>20.0687442601551</v>
       </c>
       <c r="GX28" t="n">
-        <v>20.212245786015</v>
+        <v>20.2122457570947</v>
       </c>
       <c r="GY28" t="n">
-        <v>20.3749845637636</v>
+        <v>20.3749845216232</v>
       </c>
       <c r="GZ28" t="n">
-        <v>20.9001680645872</v>
+        <v>20.9001680092045</v>
       </c>
       <c r="HA28" t="n">
-        <v>20.950538107274</v>
+        <v>20.9505380396513</v>
       </c>
       <c r="HB28" t="n">
-        <v>21.0027871410428</v>
+        <v>21.0027870619913</v>
       </c>
       <c r="HC28" t="n">
-        <v>21.0975328293665</v>
+        <v>21.0975327392379</v>
       </c>
       <c r="HD28" t="n">
-        <v>21.5651478717183</v>
+        <v>21.5651477705093</v>
       </c>
       <c r="HE28" t="n">
-        <v>21.5469189032454</v>
+        <v>21.546918792502</v>
       </c>
       <c r="HF28" t="n">
-        <v>21.5527894164564</v>
+        <v>21.5527892966631</v>
       </c>
       <c r="HG28" t="n">
-        <v>21.5954884540862</v>
+        <v>21.5954883257786</v>
       </c>
       <c r="HH28" t="n">
-        <v>22.0641594417065</v>
+        <v>22.0641593039013</v>
       </c>
       <c r="HI28" t="n">
-        <v>22.012791700335</v>
+        <v>22.0127915551978</v>
       </c>
       <c r="HJ28" t="n">
-        <v>21.9978986269347</v>
+        <v>21.9978984748128</v>
       </c>
       <c r="HK28" t="n">
-        <v>22.0268218958148</v>
+        <v>22.026821737091</v>
       </c>
       <c r="HL28" t="n">
-        <v>22.5087038868661</v>
+        <v>22.5087037200347</v>
       </c>
       <c r="HM28" t="n">
-        <v>22.4472269206339</v>
+        <v>22.4472267483666</v>
       </c>
       <c r="HN28" t="n">
-        <v>22.4285008541476</v>
+        <v>22.4285006766918</v>
       </c>
       <c r="HO28" t="n">
-        <v>22.4604043350345</v>
+        <v>22.460404152736</v>
       </c>
       <c r="HP28" t="n">
-        <v>22.9773644183049</v>
+        <v>22.9773642292672</v>
       </c>
       <c r="HQ28" t="n">
-        <v>22.9250847863669</v>
+        <v>22.9250845937161</v>
       </c>
       <c r="HR28" t="n">
-        <v>22.9208322110601</v>
+        <v>22.9208320150047</v>
       </c>
       <c r="HS28" t="n">
-        <v>23.0010444852556</v>
+        <v>23.0010442856034</v>
       </c>
       <c r="HT28" t="n">
-        <v>23.5650462991482</v>
+        <v>23.5650460939984</v>
       </c>
       <c r="HU28" t="n">
-        <v>23.5491931698423</v>
+        <v>23.5491929624306</v>
       </c>
     </row>
     <row r="29">
@@ -20709,139 +20709,139 @@
       <c r="GA29"/>
       <c r="GB29"/>
       <c r="GC29" t="n">
-        <v>0.0000207381340679747</v>
+        <v>0.0000207381340885841</v>
       </c>
       <c r="GD29" t="n">
-        <v>0.0000198342653316777</v>
+        <v>0.0000198342653769061</v>
       </c>
       <c r="GE29" t="n">
-        <v>0.000019801387341299</v>
+        <v>0.0000198013874094017</v>
       </c>
       <c r="GF29" t="n">
-        <v>0.0000193997587924959</v>
+        <v>0.0000193997588879907</v>
       </c>
       <c r="GG29" t="n">
-        <v>0.000019008434778568</v>
+        <v>0.0000190084349003374</v>
       </c>
       <c r="GH29" t="n">
-        <v>0.0000187961107405041</v>
+        <v>0.0000187961108855796</v>
       </c>
       <c r="GI29" t="n">
-        <v>0.0000186989168087843</v>
+        <v>0.0000186989169742781</v>
       </c>
       <c r="GJ29" t="n">
-        <v>0.0000190201224156104</v>
+        <v>0.0000190201225980373</v>
       </c>
       <c r="GK29" t="n">
-        <v>0.0000189654452163311</v>
+        <v>0.0000189654454096763</v>
       </c>
       <c r="GL29" t="n">
-        <v>0.0000189858152314239</v>
+        <v>0.0000189858154319212</v>
       </c>
       <c r="GM29" t="n">
-        <v>0.0000190726860810582</v>
+        <v>0.0000190726862875582</v>
       </c>
       <c r="GN29" t="n">
-        <v>0.0000195018286235175</v>
+        <v>0.0000195018288343366</v>
       </c>
       <c r="GO29" t="n">
-        <v>0.0000195094381467399</v>
+        <v>0.0000195094383561837</v>
       </c>
       <c r="GP29" t="n">
-        <v>0.0000195358576472083</v>
+        <v>0.0000195358578523384</v>
       </c>
       <c r="GQ29" t="n">
-        <v>0.000019605995133832</v>
+        <v>0.0000196059953330911</v>
       </c>
       <c r="GR29" t="n">
-        <v>0.0000200009571721835</v>
+        <v>0.0000200009573664171</v>
       </c>
       <c r="GS29" t="n">
-        <v>0.0000199659281528003</v>
+        <v>0.0000199659283374206</v>
       </c>
       <c r="GT29" t="n">
-        <v>0.0000199366699300258</v>
+        <v>0.0000199366701043406</v>
       </c>
       <c r="GU29" t="n">
-        <v>0.0000199463772040787</v>
+        <v>0.0000199463773678888</v>
       </c>
       <c r="GV29" t="n">
-        <v>0.0000202875290881038</v>
+        <v>0.000020287529244167</v>
       </c>
       <c r="GW29" t="n">
-        <v>0.0000201797756013834</v>
+        <v>0.0000201797757459854</v>
       </c>
       <c r="GX29" t="n">
-        <v>0.000020080337656843</v>
+        <v>0.0000200803377903316</v>
       </c>
       <c r="GY29" t="n">
-        <v>0.0000200053214494917</v>
+        <v>0.0000200053215724798</v>
       </c>
       <c r="GZ29" t="n">
-        <v>0.0000202768983059243</v>
+        <v>0.000020276898421297</v>
       </c>
       <c r="HA29" t="n">
-        <v>0.0000200800091091854</v>
+        <v>0.0000200800092140944</v>
       </c>
       <c r="HB29" t="n">
-        <v>0.0000198785372218195</v>
+        <v>0.0000198785373172108</v>
       </c>
       <c r="HC29" t="n">
-        <v>0.000019731961031906</v>
+        <v>0.0000197319611184472</v>
       </c>
       <c r="HD29" t="n">
-        <v>0.0000199157593352284</v>
+        <v>0.0000199157594162311</v>
       </c>
       <c r="HE29" t="n">
-        <v>0.0000196508739026891</v>
+        <v>0.0000196508739755796</v>
       </c>
       <c r="HF29" t="n">
-        <v>0.0000194078659628971</v>
+        <v>0.0000194078660284394</v>
       </c>
       <c r="HG29" t="n">
-        <v>0.000019205500245034</v>
+        <v>0.0000192055003041394</v>
       </c>
       <c r="HH29" t="n">
-        <v>0.0000193765609078537</v>
+        <v>0.0000193765609631401</v>
       </c>
       <c r="HI29" t="n">
-        <v>0.000019085542664582</v>
+        <v>0.0000190855427138688</v>
       </c>
       <c r="HJ29" t="n">
-        <v>0.0000188282310453023</v>
+        <v>0.0000188282310892718</v>
       </c>
       <c r="HK29" t="n">
-        <v>0.0000186169951108829</v>
+        <v>0.0000186169951503517</v>
       </c>
       <c r="HL29" t="n">
-        <v>0.0000187835857091887</v>
+        <v>0.0000187835857465229</v>
       </c>
       <c r="HM29" t="n">
-        <v>0.0000184924465238902</v>
+        <v>0.0000184924465571449</v>
       </c>
       <c r="HN29" t="n">
-        <v>0.0000182394952950356</v>
+        <v>0.0000182394953248419</v>
       </c>
       <c r="HO29" t="n">
-        <v>0.0000180369223374406</v>
+        <v>0.0000180369223646102</v>
       </c>
       <c r="HP29" t="n">
-        <v>0.0000182202727000452</v>
+        <v>0.0000182202727268865</v>
       </c>
       <c r="HQ29" t="n">
-        <v>0.0000179481206674002</v>
+        <v>0.0000179481206920964</v>
       </c>
       <c r="HR29" t="n">
-        <v>0.0000177166176613099</v>
+        <v>0.0000177166176844746</v>
       </c>
       <c r="HS29" t="n">
-        <v>0.000017569524706651</v>
+        <v>0.0000175695247287182</v>
       </c>
       <c r="HT29" t="n">
-        <v>0.0000177765231324174</v>
+        <v>0.000017776523155869</v>
       </c>
       <c r="HU29" t="n">
-        <v>0.0000175485873788497</v>
+        <v>0.0000175485874016815</v>
       </c>
     </row>
     <row r="30">
@@ -21210,139 +21210,139 @@
       <c r="GA30"/>
       <c r="GB30"/>
       <c r="GC30" t="n">
-        <v>844.856861063552</v>
+        <v>844.856861071567</v>
       </c>
       <c r="GD30" t="n">
-        <v>864.352810353467</v>
+        <v>864.352810381144</v>
       </c>
       <c r="GE30" t="n">
-        <v>884.235347211048</v>
+        <v>884.235347270203</v>
       </c>
       <c r="GF30" t="n">
-        <v>904.134262930945</v>
+        <v>904.134263036259</v>
       </c>
       <c r="GG30" t="n">
-        <v>924.152847366806</v>
+        <v>924.152847533199</v>
       </c>
       <c r="GH30" t="n">
-        <v>944.28303536361</v>
+        <v>944.283035602267</v>
       </c>
       <c r="GI30" t="n">
-        <v>964.687442255001</v>
+        <v>964.687442573011</v>
       </c>
       <c r="GJ30" t="n">
-        <v>985.747092474335</v>
+        <v>985.747092872787</v>
       </c>
       <c r="GK30" t="n">
-        <v>1007.23015507212</v>
+        <v>1007.23015554507</v>
       </c>
       <c r="GL30" t="n">
-        <v>1029.25418689355</v>
+        <v>1029.25418742849</v>
       </c>
       <c r="GM30" t="n">
-        <v>1051.91245745069</v>
+        <v>1051.91245802948</v>
       </c>
       <c r="GN30" t="n">
-        <v>1075.52694509536</v>
+        <v>1075.52694569371</v>
       </c>
       <c r="GO30" t="n">
-        <v>1099.76086495108</v>
+        <v>1099.76086553808</v>
       </c>
       <c r="GP30" t="n">
-        <v>1124.64603253928</v>
+        <v>1124.64603307865</v>
       </c>
       <c r="GQ30" t="n">
-        <v>1150.21294771361</v>
+        <v>1150.21294816463</v>
       </c>
       <c r="GR30" t="n">
-        <v>1176.76295560897</v>
+        <v>1176.76295592722</v>
       </c>
       <c r="GS30" t="n">
-        <v>1203.87434071864</v>
+        <v>1203.87434085583</v>
       </c>
       <c r="GT30" t="n">
-        <v>1231.52355276949</v>
+        <v>1231.52355267487</v>
       </c>
       <c r="GU30" t="n">
-        <v>1259.70282230761</v>
+        <v>1259.70282192881</v>
       </c>
       <c r="GV30" t="n">
-        <v>1288.70761542911</v>
+        <v>1288.70761471316</v>
       </c>
       <c r="GW30" t="n">
-        <v>1318.06663504328</v>
+        <v>1318.06663393689</v>
       </c>
       <c r="GX30" t="n">
-        <v>1347.75329382916</v>
+        <v>1347.75329227966</v>
       </c>
       <c r="GY30" t="n">
-        <v>1377.75161791624</v>
+        <v>1377.75161587216</v>
       </c>
       <c r="GZ30" t="n">
-        <v>1408.38878270047</v>
+        <v>1408.3887801114</v>
       </c>
       <c r="HA30" t="n">
-        <v>1439.16023127404</v>
+        <v>1439.16022809184</v>
       </c>
       <c r="HB30" t="n">
-        <v>1470.03769615077</v>
+        <v>1470.03769232979</v>
       </c>
       <c r="HC30" t="n">
-        <v>1501.03736752869</v>
+        <v>1501.03736302553</v>
       </c>
       <c r="HD30" t="n">
-        <v>1532.50846950798</v>
+        <v>1532.50846428121</v>
       </c>
       <c r="HE30" t="n">
-        <v>1563.94942587629</v>
+        <v>1563.949419888</v>
       </c>
       <c r="HF30" t="n">
-        <v>1595.36978843082</v>
+        <v>1595.3697816458</v>
       </c>
       <c r="HG30" t="n">
-        <v>1626.79730763524</v>
+        <v>1626.797300021</v>
       </c>
       <c r="HH30" t="n">
-        <v>1658.6490372459</v>
+        <v>1658.64902877111</v>
       </c>
       <c r="HI30" t="n">
-        <v>1690.40578644993</v>
+        <v>1690.40577708732</v>
       </c>
       <c r="HJ30" t="n">
-        <v>1722.10419896403</v>
+        <v>1722.10418868876</v>
       </c>
       <c r="HK30" t="n">
-        <v>1753.79174839532</v>
+        <v>1753.79173718486</v>
       </c>
       <c r="HL30" t="n">
-        <v>1785.92604210347</v>
+        <v>1785.92602993561</v>
       </c>
       <c r="HM30" t="n">
-        <v>1817.97284986802</v>
+        <v>1817.97283672475</v>
       </c>
       <c r="HN30" t="n">
-        <v>1849.98309331301</v>
+        <v>1849.98307917824</v>
       </c>
       <c r="HO30" t="n">
-        <v>1882.01729421627</v>
+        <v>1882.01727907577</v>
       </c>
       <c r="HP30" t="n">
-        <v>1914.56947615472</v>
+        <v>1914.56945999373</v>
       </c>
       <c r="HQ30" t="n">
-        <v>1947.0832685462</v>
+        <v>1947.08325135416</v>
       </c>
       <c r="HR30" t="n">
-        <v>1979.61710677482</v>
+        <v>1979.61708854251</v>
       </c>
       <c r="HS30" t="n">
-        <v>2012.26636630844</v>
+        <v>2012.26634702745</v>
       </c>
       <c r="HT30" t="n">
-        <v>2045.52360791217</v>
+        <v>2045.52358757299</v>
       </c>
       <c r="HU30" t="n">
-        <v>2078.81856753088</v>
+        <v>2078.81854612771</v>
       </c>
     </row>
     <row r="31">
@@ -21899,7 +21899,7 @@
         <v>0.0546735510183915</v>
       </c>
       <c r="GC31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0435353050242881</v>
       </c>
       <c r="GD31" t="n">
         <v>0.043535305024288</v>
@@ -22004,7 +22004,7 @@
         <v>0.043535305024288</v>
       </c>
       <c r="HL31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0435353050242881</v>
       </c>
       <c r="HM31" t="n">
         <v>0.043535305024288</v>
@@ -22016,19 +22016,19 @@
         <v>0.043535305024288</v>
       </c>
       <c r="HP31" t="n">
-        <v>0.0435353050242881</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HQ31" t="n">
         <v>0.043535305024288</v>
       </c>
       <c r="HR31" t="n">
+        <v>0.0435353050242881</v>
+      </c>
+      <c r="HS31" t="n">
         <v>0.043535305024288</v>
       </c>
-      <c r="HS31" t="n">
-        <v>0.0435353050242881</v>
-      </c>
       <c r="HT31" t="n">
-        <v>0.0435353050242881</v>
+        <v>0.043535305024288</v>
       </c>
       <c r="HU31" t="n">
         <v>0.043535305024288</v>
@@ -22588,139 +22588,139 @@
         <v>0.233491652414238</v>
       </c>
       <c r="GC32" t="n">
-        <v>0.236930433634667</v>
+        <v>0.236930433753953</v>
       </c>
       <c r="GD32" t="n">
-        <v>0.232655001031785</v>
+        <v>0.232655001277829</v>
       </c>
       <c r="GE32" t="n">
-        <v>0.233411142269931</v>
+        <v>0.233411142625028</v>
       </c>
       <c r="GF32" t="n">
-        <v>0.23073739522142</v>
+        <v>0.23073739570846</v>
       </c>
       <c r="GG32" t="n">
-        <v>0.230101821454184</v>
+        <v>0.230101822073248</v>
       </c>
       <c r="GH32" t="n">
-        <v>0.229777607132103</v>
+        <v>0.229777607882814</v>
       </c>
       <c r="GI32" t="n">
-        <v>0.229698723668434</v>
+        <v>0.229698724547084</v>
       </c>
       <c r="GJ32" t="n">
-        <v>0.229840295037597</v>
+        <v>0.229840296030326</v>
       </c>
       <c r="GK32" t="n">
-        <v>0.229893730325423</v>
+        <v>0.229893731429405</v>
       </c>
       <c r="GL32" t="n">
-        <v>0.230098248460385</v>
+        <v>0.230098249669954</v>
       </c>
       <c r="GM32" t="n">
-        <v>0.230498734625617</v>
+        <v>0.230498735950011</v>
       </c>
       <c r="GN32" t="n">
-        <v>0.230547797064099</v>
+        <v>0.230547798487021</v>
       </c>
       <c r="GO32" t="n">
-        <v>0.230451383621005</v>
+        <v>0.23045138513604</v>
       </c>
       <c r="GP32" t="n">
-        <v>0.230350469159198</v>
+        <v>0.230350470753427</v>
       </c>
       <c r="GQ32" t="n">
-        <v>0.230442437648382</v>
+        <v>0.230442439316751</v>
       </c>
       <c r="GR32" t="n">
-        <v>0.230496262484992</v>
+        <v>0.230496264218319</v>
       </c>
       <c r="GS32" t="n">
-        <v>0.230601724083885</v>
+        <v>0.230601725875261</v>
       </c>
       <c r="GT32" t="n">
-        <v>0.230693610102124</v>
+        <v>0.230693611945172</v>
       </c>
       <c r="GU32" t="n">
-        <v>0.230956216627356</v>
+        <v>0.230956218517119</v>
       </c>
       <c r="GV32" t="n">
-        <v>0.231144455298809</v>
+        <v>0.231144457230778</v>
       </c>
       <c r="GW32" t="n">
-        <v>0.231344314740483</v>
+        <v>0.231344316708669</v>
       </c>
       <c r="GX32" t="n">
-        <v>0.231501629685755</v>
+        <v>0.231501631685717</v>
       </c>
       <c r="GY32" t="n">
-        <v>0.231727928536643</v>
+        <v>0.231727930565459</v>
       </c>
       <c r="GZ32" t="n">
-        <v>0.231893864641347</v>
+        <v>0.231893866694728</v>
       </c>
       <c r="HA32" t="n">
-        <v>0.23200311807709</v>
+        <v>0.232003120151533</v>
       </c>
       <c r="HB32" t="n">
-        <v>0.232002286297776</v>
+        <v>0.232002288391236</v>
       </c>
       <c r="HC32" t="n">
-        <v>0.232178725408374</v>
+        <v>0.232178727518382</v>
       </c>
       <c r="HD32" t="n">
-        <v>0.232131443626714</v>
+        <v>0.232131445752099</v>
       </c>
       <c r="HE32" t="n">
-        <v>0.23212561422437</v>
+        <v>0.232125616361614</v>
       </c>
       <c r="HF32" t="n">
-        <v>0.23206051947183</v>
+        <v>0.232060521619057</v>
       </c>
       <c r="HG32" t="n">
-        <v>0.232062249034204</v>
+        <v>0.232062251190573</v>
       </c>
       <c r="HH32" t="n">
-        <v>0.232013120222383</v>
+        <v>0.232013122385574</v>
       </c>
       <c r="HI32" t="n">
-        <v>0.231910106997469</v>
+        <v>0.231910109165374</v>
       </c>
       <c r="HJ32" t="n">
-        <v>0.231777607685055</v>
+        <v>0.231777609856087</v>
       </c>
       <c r="HK32" t="n">
-        <v>0.231719183998638</v>
+        <v>0.231719186172751</v>
       </c>
       <c r="HL32" t="n">
-        <v>0.23161159343475</v>
+        <v>0.231611595610083</v>
       </c>
       <c r="HM32" t="n">
-        <v>0.231462747751042</v>
+        <v>0.231462749926391</v>
       </c>
       <c r="HN32" t="n">
-        <v>0.231294602874975</v>
+        <v>0.231294605049541</v>
       </c>
       <c r="HO32" t="n">
-        <v>0.231212934544571</v>
+        <v>0.23121293671918</v>
       </c>
       <c r="HP32" t="n">
-        <v>0.231105916431139</v>
+        <v>0.231105918605049</v>
       </c>
       <c r="HQ32" t="n">
-        <v>0.230961176979868</v>
+        <v>0.230961179152578</v>
       </c>
       <c r="HR32" t="n">
-        <v>0.230805337934807</v>
+        <v>0.230805340106321</v>
       </c>
       <c r="HS32" t="n">
-        <v>0.230905009810835</v>
+        <v>0.230905011981552</v>
       </c>
       <c r="HT32" t="n">
-        <v>0.230800530047243</v>
+        <v>0.230800532218018</v>
       </c>
       <c r="HU32" t="n">
-        <v>0.23078380194875</v>
+        <v>0.230783804118948</v>
       </c>
     </row>
     <row r="33">
@@ -23109,139 +23109,139 @@
         <v>82599</v>
       </c>
       <c r="GC33" t="n">
-        <v>82701.4172494172</v>
+        <v>82701.4172268635</v>
       </c>
       <c r="GD33" t="n">
-        <v>84174.3503022568</v>
+        <v>84174.3502963379</v>
       </c>
       <c r="GE33" t="n">
-        <v>85528.2186641719</v>
+        <v>85528.2186136584</v>
       </c>
       <c r="GF33" t="n">
-        <v>87098.0990920393</v>
+        <v>87098.0990440609</v>
       </c>
       <c r="GG33" t="n">
-        <v>88672.514800619</v>
+        <v>88672.5147443145</v>
       </c>
       <c r="GH33" t="n">
-        <v>89923.9644582211</v>
+        <v>89923.964413826</v>
       </c>
       <c r="GI33" t="n">
-        <v>91031.7070858401</v>
+        <v>91031.7070547143</v>
       </c>
       <c r="GJ33" t="n">
-        <v>91901.5652172986</v>
+        <v>91901.5652135989</v>
       </c>
       <c r="GK33" t="n">
-        <v>92651.3177505619</v>
+        <v>92651.3177765577</v>
       </c>
       <c r="GL33" t="n">
-        <v>93389.9456658418</v>
+        <v>93389.9457331753</v>
       </c>
       <c r="GM33" t="n">
-        <v>94057.6354070455</v>
+        <v>94057.6355156578</v>
       </c>
       <c r="GN33" t="n">
-        <v>94695.6702122744</v>
+        <v>94695.6703702621</v>
       </c>
       <c r="GO33" t="n">
-        <v>95190.2779194866</v>
+        <v>95190.27811994</v>
       </c>
       <c r="GP33" t="n">
-        <v>95769.030505128</v>
+        <v>95769.0307583966</v>
       </c>
       <c r="GQ33" t="n">
-        <v>96269.1651862168</v>
+        <v>96269.1654905802</v>
       </c>
       <c r="GR33" t="n">
-        <v>96815.2812933578</v>
+        <v>96815.2816543206</v>
       </c>
       <c r="GS33" t="n">
-        <v>97351.2794378337</v>
+        <v>97351.2798555573</v>
       </c>
       <c r="GT33" t="n">
-        <v>97914.0963596563</v>
+        <v>97914.0968367157</v>
       </c>
       <c r="GU33" t="n">
-        <v>98455.3170806586</v>
+        <v>98455.3176169412</v>
       </c>
       <c r="GV33" t="n">
-        <v>99002.8825520675</v>
+        <v>99002.8831480685</v>
       </c>
       <c r="GW33" t="n">
-        <v>99563.1982209889</v>
+        <v>99563.1988766417</v>
       </c>
       <c r="GX33" t="n">
-        <v>100149.359520062</v>
+        <v>100149.360235446</v>
       </c>
       <c r="GY33" t="n">
-        <v>100738.973003124</v>
+        <v>100738.973777388</v>
       </c>
       <c r="GZ33" t="n">
-        <v>101346.80946216</v>
+        <v>101346.810294589</v>
       </c>
       <c r="HA33" t="n">
-        <v>101981.782988665</v>
+        <v>101981.783878343</v>
       </c>
       <c r="HB33" t="n">
-        <v>102661.455875212</v>
+        <v>102661.456820583</v>
       </c>
       <c r="HC33" t="n">
-        <v>103336.056201626</v>
+        <v>103336.057200671</v>
       </c>
       <c r="HD33" t="n">
-        <v>104030.303350874</v>
+        <v>104030.304401262</v>
       </c>
       <c r="HE33" t="n">
-        <v>104740.233213921</v>
+        <v>104740.23431411</v>
       </c>
       <c r="HF33" t="n">
-        <v>105459.293434063</v>
+        <v>105459.294581994</v>
       </c>
       <c r="HG33" t="n">
-        <v>106162.517561271</v>
+        <v>106162.518754639</v>
       </c>
       <c r="HH33" t="n">
-        <v>106850.317283027</v>
+        <v>106850.318519396</v>
       </c>
       <c r="HI33" t="n">
-        <v>107533.270105729</v>
+        <v>107533.2713832</v>
       </c>
       <c r="HJ33" t="n">
-        <v>108214.662894775</v>
+        <v>108214.664211513</v>
       </c>
       <c r="HK33" t="n">
-        <v>108865.245945456</v>
+        <v>108865.247298823</v>
       </c>
       <c r="HL33" t="n">
-        <v>109493.082494654</v>
+        <v>109493.08388241</v>
       </c>
       <c r="HM33" t="n">
-        <v>110110.216937152</v>
+        <v>110110.218357403</v>
       </c>
       <c r="HN33" t="n">
-        <v>110717.590320002</v>
+        <v>110717.591771021</v>
       </c>
       <c r="HO33" t="n">
-        <v>111287.863254625</v>
+        <v>111287.864733859</v>
       </c>
       <c r="HP33" t="n">
-        <v>111825.041010286</v>
+        <v>111825.042515471</v>
       </c>
       <c r="HQ33" t="n">
-        <v>112346.211308484</v>
+        <v>112346.212837964</v>
       </c>
       <c r="HR33" t="n">
-        <v>112854.714534625</v>
+        <v>112854.716086963</v>
       </c>
       <c r="HS33" t="n">
-        <v>113315.840922053</v>
+        <v>113315.842494805</v>
       </c>
       <c r="HT33" t="n">
-        <v>113740.62295927</v>
+        <v>113740.624550801</v>
       </c>
       <c r="HU33" t="n">
-        <v>114157.526684215</v>
+        <v>114157.528293462</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sem_coredata.xlsx
+++ b/outputs/sem_coredata.xlsx
@@ -2754,139 +2754,139 @@
         <v>354377</v>
       </c>
       <c r="GC2" t="n">
-        <v>355093.061230489</v>
+        <v>355990</v>
       </c>
       <c r="GD2" t="n">
-        <v>360057.783987501</v>
+        <v>358679.92554077</v>
       </c>
       <c r="GE2" t="n">
-        <v>362937.789666279</v>
+        <v>363452.801511882</v>
       </c>
       <c r="GF2" t="n">
-        <v>366473.809550388</v>
+        <v>367393.564968015</v>
       </c>
       <c r="GG2" t="n">
-        <v>369339.814282417</v>
+        <v>370839.921549641</v>
       </c>
       <c r="GH2" t="n">
-        <v>371785.376433554</v>
+        <v>373879.179835035</v>
       </c>
       <c r="GI2" t="n">
-        <v>373790.180930009</v>
+        <v>376450.967286461</v>
       </c>
       <c r="GJ2" t="n">
-        <v>375539.160539227</v>
+        <v>378837.955610913</v>
       </c>
       <c r="GK2" t="n">
-        <v>377359.172118566</v>
+        <v>381233.250577459</v>
       </c>
       <c r="GL2" t="n">
-        <v>379195.880901556</v>
+        <v>383658.086362284</v>
       </c>
       <c r="GM2" t="n">
-        <v>380837.882653327</v>
+        <v>385941.667840372</v>
       </c>
       <c r="GN2" t="n">
-        <v>382332.873153968</v>
+        <v>388066.828552129</v>
       </c>
       <c r="GO2" t="n">
-        <v>384044.25336919</v>
+        <v>390366.167094631</v>
       </c>
       <c r="GP2" t="n">
-        <v>385944.148580009</v>
+        <v>392792.47431239</v>
       </c>
       <c r="GQ2" t="n">
-        <v>387673.976116972</v>
+        <v>395030.803632912</v>
       </c>
       <c r="GR2" t="n">
-        <v>389612.033720876</v>
+        <v>397436.205822793</v>
       </c>
       <c r="GS2" t="n">
-        <v>391756.564237653</v>
+        <v>400008.214308838</v>
       </c>
       <c r="GT2" t="n">
-        <v>394082.926339524</v>
+        <v>402729.477763665</v>
       </c>
       <c r="GU2" t="n">
-        <v>396208.184092239</v>
+        <v>405233.03971708</v>
       </c>
       <c r="GV2" t="n">
-        <v>398503.250939809</v>
+        <v>407884.975769207</v>
       </c>
       <c r="GW2" t="n">
-        <v>401020.572954027</v>
+        <v>410734.583800286</v>
       </c>
       <c r="GX2" t="n">
-        <v>403709.43528421</v>
+        <v>413748.427759138</v>
       </c>
       <c r="GY2" t="n">
-        <v>406200.442596775</v>
+        <v>416571.064220722</v>
       </c>
       <c r="GZ2" t="n">
-        <v>408859.758593226</v>
+        <v>419571.466219704</v>
       </c>
       <c r="HA2" t="n">
-        <v>411709.960166294</v>
+        <v>422767.540291178</v>
       </c>
       <c r="HB2" t="n">
-        <v>414703.660560691</v>
+        <v>426128.179854273</v>
       </c>
       <c r="HC2" t="n">
-        <v>417365.104369556</v>
+        <v>429185.096789337</v>
       </c>
       <c r="HD2" t="n">
-        <v>420181.786286364</v>
+        <v>432420.858058694</v>
       </c>
       <c r="HE2" t="n">
-        <v>423104.406650936</v>
+        <v>435776.957457544</v>
       </c>
       <c r="HF2" t="n">
-        <v>426087.907947669</v>
+        <v>439218.999831592</v>
       </c>
       <c r="HG2" t="n">
-        <v>428735.445384839</v>
+        <v>442347.477686051</v>
       </c>
       <c r="HH2" t="n">
-        <v>431412.895106344</v>
+        <v>445526.974548546</v>
       </c>
       <c r="HI2" t="n">
-        <v>434197.981031085</v>
+        <v>448822.135726204</v>
       </c>
       <c r="HJ2" t="n">
-        <v>437015.957437043</v>
+        <v>452166.345284197</v>
       </c>
       <c r="HK2" t="n">
-        <v>439470.628671841</v>
+        <v>455161.763238418</v>
       </c>
       <c r="HL2" t="n">
-        <v>441958.297714343</v>
+        <v>458204.219486237</v>
       </c>
       <c r="HM2" t="n">
-        <v>444538.084752457</v>
+        <v>461339.737095008</v>
       </c>
       <c r="HN2" t="n">
-        <v>447141.780892027</v>
+        <v>464509.031487579</v>
       </c>
       <c r="HO2" t="n">
-        <v>449363.800690713</v>
+        <v>467303.610493163</v>
       </c>
       <c r="HP2" t="n">
-        <v>451581.252200743</v>
+        <v>470100.599043283</v>
       </c>
       <c r="HQ2" t="n">
-        <v>453907.281855652</v>
+        <v>473000.525476385</v>
       </c>
       <c r="HR2" t="n">
-        <v>456270.457226596</v>
+        <v>475940.661864245</v>
       </c>
       <c r="HS2" t="n">
-        <v>458154.476454183</v>
+        <v>478404.53363683</v>
       </c>
       <c r="HT2" t="n">
-        <v>460131.309634874</v>
+        <v>480957.940400347</v>
       </c>
       <c r="HU2" t="n">
-        <v>462196.668659974</v>
+        <v>483588.974176903</v>
       </c>
     </row>
     <row r="3">
@@ -3443,7 +3443,7 @@
         <v>158467</v>
       </c>
       <c r="GC3" t="n">
-        <v>159893.923149704</v>
+        <v>159537</v>
       </c>
       <c r="GD3" t="n">
         <v>160982.036125316</v>
@@ -4132,139 +4132,139 @@
         <v>36720</v>
       </c>
       <c r="GC4" t="n">
-        <v>36864.8957689682</v>
+        <v>36955</v>
       </c>
       <c r="GD4" t="n">
-        <v>37067.0424609753</v>
+        <v>37286.110007495</v>
       </c>
       <c r="GE4" t="n">
-        <v>37241.2523083342</v>
+        <v>37634.5580288465</v>
       </c>
       <c r="GF4" t="n">
-        <v>37366.4033790698</v>
+        <v>37880.1485398342</v>
       </c>
       <c r="GG4" t="n">
-        <v>37327.7724162639</v>
+        <v>37986.2597598353</v>
       </c>
       <c r="GH4" t="n">
-        <v>37204.0844795898</v>
+        <v>37972.2137441676</v>
       </c>
       <c r="GI4" t="n">
-        <v>37030.7397082828</v>
+        <v>37888.0919226647</v>
       </c>
       <c r="GJ4" t="n">
-        <v>36911.1636418051</v>
+        <v>37810.5412024564</v>
       </c>
       <c r="GK4" t="n">
-        <v>36880.3200019542</v>
+        <v>37784.9718597464</v>
       </c>
       <c r="GL4" t="n">
-        <v>36961.5005011521</v>
+        <v>37843.3667845049</v>
       </c>
       <c r="GM4" t="n">
-        <v>37139.7680324348</v>
+        <v>37997.8196644238</v>
       </c>
       <c r="GN4" t="n">
-        <v>37381.7643773445</v>
+        <v>38237.4855339962</v>
       </c>
       <c r="GO4" t="n">
-        <v>37649.0512300486</v>
+        <v>38534.2981509344</v>
       </c>
       <c r="GP4" t="n">
-        <v>37912.0090017895</v>
+        <v>38859.780130636</v>
       </c>
       <c r="GQ4" t="n">
-        <v>38149.8728483592</v>
+        <v>39188.0300415771</v>
       </c>
       <c r="GR4" t="n">
-        <v>38345.2078635615</v>
+        <v>39493.7747153546</v>
       </c>
       <c r="GS4" t="n">
-        <v>38492.8216278855</v>
+        <v>39759.5932835791</v>
       </c>
       <c r="GT4" t="n">
-        <v>38594.1086151134</v>
+        <v>39978.1565096514</v>
       </c>
       <c r="GU4" t="n">
-        <v>38657.484927624</v>
+        <v>40150.3484977856</v>
       </c>
       <c r="GV4" t="n">
-        <v>38693.2740894899</v>
+        <v>40280.9301582002</v>
       </c>
       <c r="GW4" t="n">
-        <v>38716.7404992865</v>
+        <v>40383.8980054863</v>
       </c>
       <c r="GX4" t="n">
-        <v>38742.9445425113</v>
+        <v>40475.1888311396</v>
       </c>
       <c r="GY4" t="n">
-        <v>38782.0734854792</v>
+        <v>40568.4239916265</v>
       </c>
       <c r="GZ4" t="n">
-        <v>38837.6173087132</v>
+        <v>40670.0422382771</v>
       </c>
       <c r="HA4" t="n">
-        <v>38912.4963037247</v>
+        <v>40786.5295962066</v>
       </c>
       <c r="HB4" t="n">
-        <v>39007.3345512394</v>
+        <v>40920.8624170544</v>
       </c>
       <c r="HC4" t="n">
-        <v>39120.0645296093</v>
+        <v>41072.7266120389</v>
       </c>
       <c r="HD4" t="n">
-        <v>39244.8543902504</v>
+        <v>41236.0996496585</v>
       </c>
       <c r="HE4" t="n">
-        <v>39381.021440756</v>
+        <v>41410.5695613574</v>
       </c>
       <c r="HF4" t="n">
-        <v>39528.1870808198</v>
+        <v>41595.4894128569</v>
       </c>
       <c r="HG4" t="n">
-        <v>39684.7008493398</v>
+        <v>41789.5753431089</v>
       </c>
       <c r="HH4" t="n">
-        <v>39847.4335068441</v>
+        <v>41988.4859543326</v>
       </c>
       <c r="HI4" t="n">
-        <v>40016.2649046782</v>
+        <v>42193.4100524208</v>
       </c>
       <c r="HJ4" t="n">
-        <v>40192.9002495292</v>
+        <v>42406.2859133677</v>
       </c>
       <c r="HK4" t="n">
-        <v>40377.0053676567</v>
+        <v>42628.0525776512</v>
       </c>
       <c r="HL4" t="n">
-        <v>40564.944944097</v>
+        <v>42855.4146354717</v>
       </c>
       <c r="HM4" t="n">
-        <v>40756.299543157</v>
+        <v>43088.7204191226</v>
       </c>
       <c r="HN4" t="n">
-        <v>40951.1331080524</v>
+        <v>43328.5662849495</v>
       </c>
       <c r="HO4" t="n">
-        <v>41148.202470213</v>
+        <v>43574.2385854533</v>
       </c>
       <c r="HP4" t="n">
-        <v>41343.4091667664</v>
+        <v>43821.1166550501</v>
       </c>
       <c r="HQ4" t="n">
-        <v>41536.2595832221</v>
+        <v>44068.6594168521</v>
       </c>
       <c r="HR4" t="n">
-        <v>41728.0745413987</v>
+        <v>44317.8365837495</v>
       </c>
       <c r="HS4" t="n">
-        <v>41918.8357282876</v>
+        <v>44568.7515971768</v>
       </c>
       <c r="HT4" t="n">
-        <v>42104.3551375688</v>
+        <v>44816.1968063789</v>
       </c>
       <c r="HU4" t="n">
-        <v>42286.2896197607</v>
+        <v>45061.2403013745</v>
       </c>
     </row>
     <row r="5">
@@ -4821,139 +4821,139 @@
         <v>11236</v>
       </c>
       <c r="GC5" t="n">
-        <v>11150.4565404427</v>
+        <v>11677</v>
       </c>
       <c r="GD5" t="n">
-        <v>11211.5994748524</v>
+        <v>11324.3159168084</v>
       </c>
       <c r="GE5" t="n">
-        <v>11264.2924037587</v>
+        <v>11430.1444806779</v>
       </c>
       <c r="GF5" t="n">
-        <v>11302.1466156347</v>
+        <v>11504.7337722944</v>
       </c>
       <c r="GG5" t="n">
-        <v>11290.4619800784</v>
+        <v>11536.961241917</v>
       </c>
       <c r="GH5" t="n">
-        <v>11253.0503196439</v>
+        <v>11532.6952694473</v>
       </c>
       <c r="GI5" t="n">
-        <v>11200.619048684</v>
+        <v>11507.1462893578</v>
       </c>
       <c r="GJ5" t="n">
-        <v>11164.4510979893</v>
+        <v>11483.5930451326</v>
       </c>
       <c r="GK5" t="n">
-        <v>11155.1218795409</v>
+        <v>11475.8272762021</v>
       </c>
       <c r="GL5" t="n">
-        <v>11179.6763943267</v>
+        <v>11493.5626359855</v>
       </c>
       <c r="GM5" t="n">
-        <v>11233.5966433516</v>
+        <v>11540.4721474929</v>
       </c>
       <c r="GN5" t="n">
-        <v>11306.7928282472</v>
+        <v>11613.2620422008</v>
       </c>
       <c r="GO5" t="n">
-        <v>11387.6385860539</v>
+        <v>11703.4082076663</v>
       </c>
       <c r="GP5" t="n">
-        <v>11467.1749347837</v>
+        <v>11802.2616617443</v>
       </c>
       <c r="GQ5" t="n">
-        <v>11539.1211705833</v>
+        <v>11901.9557754615</v>
       </c>
       <c r="GR5" t="n">
-        <v>11598.2037897636</v>
+        <v>11994.8147321894</v>
       </c>
       <c r="GS5" t="n">
-        <v>11642.852250841</v>
+        <v>12075.5475692304</v>
       </c>
       <c r="GT5" t="n">
-        <v>11673.4883377101</v>
+        <v>12141.9282943675</v>
       </c>
       <c r="GU5" t="n">
-        <v>11692.6576532229</v>
+        <v>12194.2254224826</v>
       </c>
       <c r="GV5" t="n">
-        <v>11703.4827345281</v>
+        <v>12233.8849089557</v>
       </c>
       <c r="GW5" t="n">
-        <v>11710.5805759064</v>
+        <v>12265.1576920834</v>
       </c>
       <c r="GX5" t="n">
-        <v>11718.5064641821</v>
+        <v>12292.8839995421</v>
       </c>
       <c r="GY5" t="n">
-        <v>11730.341722873</v>
+        <v>12321.2008288304</v>
       </c>
       <c r="GZ5" t="n">
-        <v>11747.1419599045</v>
+        <v>12352.0637192674</v>
       </c>
       <c r="HA5" t="n">
-        <v>11769.7904704252</v>
+        <v>12387.4425678854</v>
       </c>
       <c r="HB5" t="n">
-        <v>11798.4760189728</v>
+        <v>12428.2413345299</v>
       </c>
       <c r="HC5" t="n">
-        <v>11832.5732461153</v>
+        <v>12474.3646260213</v>
       </c>
       <c r="HD5" t="n">
-        <v>11870.3182034451</v>
+        <v>12523.9833148553</v>
       </c>
       <c r="HE5" t="n">
-        <v>11911.5043982582</v>
+        <v>12576.9722803885</v>
       </c>
       <c r="HF5" t="n">
-        <v>11956.0173160231</v>
+        <v>12633.1350395835</v>
       </c>
       <c r="HG5" t="n">
-        <v>12003.3577448365</v>
+        <v>12692.0816657867</v>
       </c>
       <c r="HH5" t="n">
-        <v>12052.5791894483</v>
+        <v>12752.4936154443</v>
       </c>
       <c r="HI5" t="n">
-        <v>12103.6453087182</v>
+        <v>12814.7319456228</v>
       </c>
       <c r="HJ5" t="n">
-        <v>12157.0718733452</v>
+        <v>12879.3853379971</v>
       </c>
       <c r="HK5" t="n">
-        <v>12212.7578064187</v>
+        <v>12946.7389923649</v>
       </c>
       <c r="HL5" t="n">
-        <v>12269.603540975</v>
+        <v>13015.7920464308</v>
       </c>
       <c r="HM5" t="n">
-        <v>12327.482211079</v>
+        <v>13086.6502936105</v>
       </c>
       <c r="HN5" t="n">
-        <v>12386.4131575165</v>
+        <v>13159.494855712</v>
       </c>
       <c r="HO5" t="n">
-        <v>12446.0203613995</v>
+        <v>13234.1089879547</v>
       </c>
       <c r="HP5" t="n">
-        <v>12505.0641682765</v>
+        <v>13309.0893292261</v>
       </c>
       <c r="HQ5" t="n">
-        <v>12563.3952754894</v>
+        <v>13384.271546867</v>
       </c>
       <c r="HR5" t="n">
-        <v>12621.4131895603</v>
+        <v>13459.9501563179</v>
       </c>
       <c r="HS5" t="n">
-        <v>12679.1123713873</v>
+        <v>13536.1565741971</v>
       </c>
       <c r="HT5" t="n">
-        <v>12735.2260824789</v>
+        <v>13611.3091637416</v>
       </c>
       <c r="HU5" t="n">
-        <v>12790.2554673333</v>
+        <v>13685.7323189094</v>
       </c>
     </row>
     <row r="6">
@@ -5510,7 +5510,7 @@
         <v>26565</v>
       </c>
       <c r="GC6" t="n">
-        <v>28230.3912902088</v>
+        <v>27386</v>
       </c>
       <c r="GD6" t="n">
         <v>28422.5052521678</v>
@@ -6199,7 +6199,7 @@
         <v>11797</v>
       </c>
       <c r="GC7" t="n">
-        <v>12057.6457759338</v>
+        <v>11597</v>
       </c>
       <c r="GD7" t="n">
         <v>12139.7006818719</v>
@@ -6841,140 +6841,138 @@
       <c r="FZ8"/>
       <c r="GA8"/>
       <c r="GB8"/>
-      <c r="GC8" t="n">
-        <v>-20.3573504657543</v>
-      </c>
+      <c r="GC8"/>
       <c r="GD8" t="n">
-        <v>-90.0759506726754</v>
+        <v>192.42108822029</v>
       </c>
       <c r="GE8" t="n">
-        <v>1283.86179741978</v>
+        <v>630.922641968413</v>
       </c>
       <c r="GF8" t="n">
-        <v>750.23807123382</v>
+        <v>1039.69910427497</v>
       </c>
       <c r="GG8" t="n">
-        <v>1613.0017822542</v>
+        <v>1213.75048107048</v>
       </c>
       <c r="GH8" t="n">
-        <v>1387.08056422888</v>
+        <v>1346.19926197777</v>
       </c>
       <c r="GI8" t="n">
-        <v>1538.35908561526</v>
+        <v>1403.65459397336</v>
       </c>
       <c r="GJ8" t="n">
-        <v>1502.44462474791</v>
+        <v>1436.78984432749</v>
       </c>
       <c r="GK8" t="n">
-        <v>1444.33133542823</v>
+        <v>1388.84642894816</v>
       </c>
       <c r="GL8" t="n">
-        <v>1434.62477809589</v>
+        <v>1411.0130591185</v>
       </c>
       <c r="GM8" t="n">
-        <v>1398.58859328352</v>
+        <v>1399.97265187363</v>
       </c>
       <c r="GN8" t="n">
-        <v>1368.21685737261</v>
+        <v>1418.77364865856</v>
       </c>
       <c r="GO8" t="n">
-        <v>1252.61692824503</v>
+        <v>1322.28163917142</v>
       </c>
       <c r="GP8" t="n">
-        <v>1225.37339399132</v>
+        <v>1327.19010581428</v>
       </c>
       <c r="GQ8" t="n">
-        <v>1178.83975756163</v>
+        <v>1298.34379016687</v>
       </c>
       <c r="GR8" t="n">
-        <v>1111.68392461681</v>
+        <v>1257.28688316507</v>
       </c>
       <c r="GS8" t="n">
-        <v>1080.48613215526</v>
+        <v>1243.64013828541</v>
       </c>
       <c r="GT8" t="n">
-        <v>1038.39987236864</v>
+        <v>1219.84974859876</v>
       </c>
       <c r="GU8" t="n">
-        <v>1010.16690562316</v>
+        <v>1205.59145501355</v>
       </c>
       <c r="GV8" t="n">
-        <v>947.386699673225</v>
+        <v>1156.46740726408</v>
       </c>
       <c r="GW8" t="n">
-        <v>933.146042164881</v>
+        <v>1152.21388801342</v>
       </c>
       <c r="GX8" t="n">
-        <v>903.049867272464</v>
+        <v>1130.29252761381</v>
       </c>
       <c r="GY8" t="n">
-        <v>891.865286467393</v>
+        <v>1126.14670616138</v>
       </c>
       <c r="GZ8" t="n">
-        <v>861.484295283764</v>
+        <v>1102.72074317388</v>
       </c>
       <c r="HA8" t="n">
-        <v>856.406329146732</v>
+        <v>1104.01920607229</v>
       </c>
       <c r="HB8" t="n">
-        <v>855.121285262139</v>
+        <v>1108.66203941553</v>
       </c>
       <c r="HC8" t="n">
-        <v>861.122459923849</v>
+        <v>1121.40566822435</v>
       </c>
       <c r="HD8" t="n">
-        <v>815.791623333324</v>
+        <v>1083.74631131414</v>
       </c>
       <c r="HE8" t="n">
-        <v>850.632744220347</v>
+        <v>1125.65990220636</v>
       </c>
       <c r="HF8" t="n">
-        <v>835.086467655638</v>
+        <v>1117.1420820746</v>
       </c>
       <c r="HG8" t="n">
-        <v>847.787845368148</v>
+        <v>1137.42632585193</v>
       </c>
       <c r="HH8" t="n">
-        <v>832.039412896091</v>
+        <v>1129.05846217967</v>
       </c>
       <c r="HI8" t="n">
-        <v>835.747572098509</v>
+        <v>1139.94408708971</v>
       </c>
       <c r="HJ8" t="n">
-        <v>842.205679705803</v>
+        <v>1152.81502229269</v>
       </c>
       <c r="HK8" t="n">
-        <v>849.481409332977</v>
+        <v>1166.7915918169</v>
       </c>
       <c r="HL8" t="n">
-        <v>836.138219990622</v>
+        <v>1159.85211012498</v>
       </c>
       <c r="HM8" t="n">
-        <v>839.536169417552</v>
+        <v>1169.38552503206</v>
       </c>
       <c r="HN8" t="n">
-        <v>844.603394653561</v>
+        <v>1179.77312418274</v>
       </c>
       <c r="HO8" t="n">
-        <v>849.352494362945</v>
+        <v>1190.11042846684</v>
       </c>
       <c r="HP8" t="n">
-        <v>832.194249561493</v>
+        <v>1177.97702666876</v>
       </c>
       <c r="HQ8" t="n">
-        <v>829.356603118358</v>
+        <v>1179.71708089329</v>
       </c>
       <c r="HR8" t="n">
-        <v>830.044111411291</v>
+        <v>1184.03921947256</v>
       </c>
       <c r="HS8" t="n">
-        <v>829.989681413426</v>
+        <v>1187.70082682965</v>
       </c>
       <c r="HT8" t="n">
-        <v>758.936906360876</v>
+        <v>1119.70966184587</v>
       </c>
       <c r="HU8" t="n">
-        <v>786.536234995525</v>
+        <v>1149.29581198801</v>
       </c>
     </row>
     <row r="9">
@@ -7524,9 +7522,7 @@
       <c r="FZ9"/>
       <c r="GA9"/>
       <c r="GB9"/>
-      <c r="GC9" t="n">
-        <v>0</v>
-      </c>
+      <c r="GC9"/>
       <c r="GD9" t="n">
         <v>0</v>
       </c>
@@ -8214,139 +8210,139 @@
         <v>680205</v>
       </c>
       <c r="GC10" t="n">
-        <v>686130.388232023</v>
+        <v>687292</v>
       </c>
       <c r="GD10" t="n">
-        <v>694123.93185288</v>
+        <v>694633.554875089</v>
       </c>
       <c r="GE10" t="n">
-        <v>701330.195724649</v>
+        <v>703516.506127552</v>
       </c>
       <c r="GF10" t="n">
-        <v>707446.366603154</v>
+        <v>711303.242641748</v>
       </c>
       <c r="GG10" t="n">
-        <v>714089.518326989</v>
+        <v>718256.266223779</v>
       </c>
       <c r="GH10" t="n">
-        <v>718799.253491191</v>
+        <v>724318.134797049</v>
       </c>
       <c r="GI10" t="n">
-        <v>723246.573208056</v>
+        <v>729609.340208632</v>
       </c>
       <c r="GJ10" t="n">
-        <v>726964.811057511</v>
+        <v>734284.617009634</v>
       </c>
       <c r="GK10" t="n">
-        <v>730735.3412123</v>
+        <v>738920.312649108</v>
       </c>
       <c r="GL10" t="n">
-        <v>734713.803866633</v>
+        <v>743702.741885958</v>
       </c>
       <c r="GM10" t="n">
-        <v>738534.838046901</v>
+        <v>748445.825055315</v>
       </c>
       <c r="GN10" t="n">
-        <v>741589.182394796</v>
+        <v>752402.559696202</v>
       </c>
       <c r="GO10" t="n">
-        <v>744664.201288273</v>
+        <v>756454.460780569</v>
       </c>
       <c r="GP10" t="n">
-        <v>748094.596661641</v>
+        <v>760758.264161621</v>
       </c>
       <c r="GQ10" t="n">
-        <v>751224.333475302</v>
+        <v>764809.670312205</v>
       </c>
       <c r="GR10" t="n">
-        <v>754540.274719342</v>
+        <v>769005.663312565</v>
       </c>
       <c r="GS10" t="n">
-        <v>758026.373525207</v>
+        <v>773351.81442336</v>
       </c>
       <c r="GT10" t="n">
-        <v>761649.893806956</v>
+        <v>777787.375524028</v>
       </c>
       <c r="GU10" t="n">
-        <v>765015.190651824</v>
+        <v>781936.028308246</v>
       </c>
       <c r="GV10" t="n">
-        <v>768500.872828056</v>
+        <v>786154.622282008</v>
       </c>
       <c r="GW10" t="n">
-        <v>772254.051516402</v>
+        <v>790588.754308737</v>
       </c>
       <c r="GX10" t="n">
-        <v>776192.325091794</v>
+        <v>795173.476681639</v>
       </c>
       <c r="GY10" t="n">
-        <v>779971.941777628</v>
+        <v>799589.299237868</v>
       </c>
       <c r="GZ10" t="n">
-        <v>783950.888376166</v>
+        <v>804203.089608331</v>
       </c>
       <c r="HA10" t="n">
-        <v>788198.344349394</v>
+        <v>809086.724188749</v>
       </c>
       <c r="HB10" t="n">
-        <v>792663.788039034</v>
+        <v>814212.206001055</v>
       </c>
       <c r="HC10" t="n">
-        <v>796822.490523239</v>
+        <v>819067.994476142</v>
       </c>
       <c r="HD10" t="n">
-        <v>801117.848523909</v>
+        <v>824092.887043603</v>
       </c>
       <c r="HE10" t="n">
-        <v>805629.816546808</v>
+        <v>829356.576222303</v>
       </c>
       <c r="HF10" t="n">
-        <v>810175.735548494</v>
+        <v>834686.87837138</v>
       </c>
       <c r="HG10" t="n">
-        <v>814410.276305478</v>
+        <v>839736.718934739</v>
       </c>
       <c r="HH10" t="n">
-        <v>818636.163495131</v>
+        <v>844804.074498608</v>
       </c>
       <c r="HI10" t="n">
-        <v>822992.238553518</v>
+        <v>850015.89658712</v>
       </c>
       <c r="HJ10" t="n">
-        <v>827392.558509386</v>
+        <v>855294.19332346</v>
       </c>
       <c r="HK10" t="n">
-        <v>831409.310244661</v>
+        <v>860211.63213697</v>
       </c>
       <c r="HL10" t="n">
-        <v>835418.083208215</v>
+        <v>865142.971746254</v>
       </c>
       <c r="HM10" t="n">
-        <v>839529.459666267</v>
+        <v>870186.574327041</v>
       </c>
       <c r="HN10" t="n">
-        <v>843661.184722751</v>
+        <v>875269.454708044</v>
       </c>
       <c r="HO10" t="n">
-        <v>847376.726787098</v>
+        <v>879953.336594202</v>
       </c>
       <c r="HP10" t="n">
-        <v>851027.666408238</v>
+        <v>884587.662520685</v>
       </c>
       <c r="HQ10" t="n">
-        <v>854782.426823519</v>
+        <v>889328.229981264</v>
       </c>
       <c r="HR10" t="n">
-        <v>858563.842436521</v>
+        <v>894105.736734029</v>
       </c>
       <c r="HS10" t="n">
-        <v>861816.610124648</v>
+        <v>898364.773869531</v>
       </c>
       <c r="HT10" t="n">
-        <v>865048.023597367</v>
+        <v>902603.898807574</v>
       </c>
       <c r="HU10" t="n">
-        <v>868454.065813542</v>
+        <v>907011.094302913</v>
       </c>
     </row>
     <row r="11">
@@ -8903,139 +8899,139 @@
         <v>170963</v>
       </c>
       <c r="GC11" t="n">
-        <v>167287.840655172</v>
+        <v>173860</v>
       </c>
       <c r="GD11" t="n">
-        <v>176028.608487566</v>
+        <v>173832.150075086</v>
       </c>
       <c r="GE11" t="n">
-        <v>170895.291228008</v>
+        <v>175153.109120394</v>
       </c>
       <c r="GF11" t="n">
-        <v>176676.351709163</v>
+        <v>176075.39648189</v>
       </c>
       <c r="GG11" t="n">
-        <v>176249.481009137</v>
+        <v>176870.964524854</v>
       </c>
       <c r="GH11" t="n">
-        <v>177436.967346086</v>
+        <v>177707.544846933</v>
       </c>
       <c r="GI11" t="n">
-        <v>178221.622176243</v>
+        <v>178546.686301575</v>
       </c>
       <c r="GJ11" t="n">
-        <v>178338.929885873</v>
+        <v>178623.592507158</v>
       </c>
       <c r="GK11" t="n">
-        <v>178897.241166983</v>
+        <v>179178.558219252</v>
       </c>
       <c r="GL11" t="n">
-        <v>179339.283210966</v>
+        <v>179621.715553874</v>
       </c>
       <c r="GM11" t="n">
-        <v>180096.906538021</v>
+        <v>180424.446436781</v>
       </c>
       <c r="GN11" t="n">
-        <v>180053.03369369</v>
+        <v>180417.454267001</v>
       </c>
       <c r="GO11" t="n">
-        <v>180472.710377468</v>
+        <v>180886.254347933</v>
       </c>
       <c r="GP11" t="n">
-        <v>180798.670778312</v>
+        <v>181257.067404824</v>
       </c>
       <c r="GQ11" t="n">
-        <v>180982.189514074</v>
+        <v>181498.820037104</v>
       </c>
       <c r="GR11" t="n">
-        <v>181279.057349384</v>
+        <v>181855.114434441</v>
       </c>
       <c r="GS11" t="n">
-        <v>181495.715146604</v>
+        <v>182135.851373178</v>
       </c>
       <c r="GT11" t="n">
-        <v>181750.001645794</v>
+        <v>182455.232477848</v>
       </c>
       <c r="GU11" t="n">
-        <v>181776.379816106</v>
+        <v>182550.10067833</v>
       </c>
       <c r="GV11" t="n">
-        <v>182068.093395764</v>
+        <v>182910.261642182</v>
       </c>
       <c r="GW11" t="n">
-        <v>182209.111025512</v>
+        <v>183120.301383623</v>
       </c>
       <c r="GX11" t="n">
-        <v>182420.53006238</v>
+        <v>183402.19169194</v>
       </c>
       <c r="GY11" t="n">
-        <v>182592.261670591</v>
+        <v>183647.712290034</v>
       </c>
       <c r="GZ11" t="n">
-        <v>182809.314782904</v>
+        <v>183941.924282718</v>
       </c>
       <c r="HA11" t="n">
-        <v>183047.096940745</v>
+        <v>184260.283743727</v>
       </c>
       <c r="HB11" t="n">
-        <v>183318.394759414</v>
+        <v>184617.730303491</v>
       </c>
       <c r="HC11" t="n">
-        <v>183181.695790935</v>
+        <v>184573.309108361</v>
       </c>
       <c r="HD11" t="n">
-        <v>183633.956961836</v>
+        <v>185123.110517768</v>
       </c>
       <c r="HE11" t="n">
-        <v>183728.199260562</v>
+        <v>185319.684614747</v>
       </c>
       <c r="HF11" t="n">
-        <v>183948.889587943</v>
+        <v>185648.531918967</v>
       </c>
       <c r="HG11" t="n">
-        <v>184134.931846419</v>
+        <v>185948.325195999</v>
       </c>
       <c r="HH11" t="n">
-        <v>184354.91010152</v>
+        <v>186287.244393034</v>
       </c>
       <c r="HI11" t="n">
-        <v>184603.979996167</v>
+        <v>186659.756960075</v>
       </c>
       <c r="HJ11" t="n">
-        <v>184874.443218341</v>
+        <v>187059.147986199</v>
       </c>
       <c r="HK11" t="n">
-        <v>185131.048708482</v>
+        <v>187450.017211446</v>
       </c>
       <c r="HL11" t="n">
-        <v>185413.30821438</v>
+        <v>187871.754410984</v>
       </c>
       <c r="HM11" t="n">
-        <v>185721.779933997</v>
+        <v>188324.155124009</v>
       </c>
       <c r="HN11" t="n">
-        <v>186046.851975801</v>
+        <v>188798.641492869</v>
       </c>
       <c r="HO11" t="n">
-        <v>186353.417725057</v>
+        <v>189259.625405845</v>
       </c>
       <c r="HP11" t="n">
-        <v>186678.299774856</v>
+        <v>189743.663748257</v>
       </c>
       <c r="HQ11" t="n">
-        <v>187027.417363127</v>
+        <v>190255.962701961</v>
       </c>
       <c r="HR11" t="n">
-        <v>187390.471265004</v>
+        <v>190787.130010564</v>
       </c>
       <c r="HS11" t="n">
-        <v>187132.689407024</v>
+        <v>190697.079830802</v>
       </c>
       <c r="HT11" t="n">
-        <v>187617.692814515</v>
+        <v>191358.71283916</v>
       </c>
       <c r="HU11" t="n">
-        <v>187617.096310076</v>
+        <v>191533.612411349</v>
       </c>
     </row>
     <row r="12">
@@ -9592,139 +9588,139 @@
         <v>162177</v>
       </c>
       <c r="GC12" t="n">
-        <v>164121.412084132</v>
+        <v>165144</v>
       </c>
       <c r="GD12" t="n">
-        <v>166117.728578113</v>
+        <v>167176.642880362</v>
       </c>
       <c r="GE12" t="n">
-        <v>167790.445143048</v>
+        <v>169640.169638413</v>
       </c>
       <c r="GF12" t="n">
-        <v>169139.805344906</v>
+        <v>171958.798867896</v>
       </c>
       <c r="GG12" t="n">
-        <v>170571.029190531</v>
+        <v>173929.545685074</v>
       </c>
       <c r="GH12" t="n">
-        <v>171549.477686434</v>
+        <v>175603.916480278</v>
       </c>
       <c r="GI12" t="n">
-        <v>172212.209700047</v>
+        <v>176846.960658284</v>
       </c>
       <c r="GJ12" t="n">
-        <v>172604.147697744</v>
+        <v>177761.913693009</v>
       </c>
       <c r="GK12" t="n">
-        <v>173058.849559539</v>
+        <v>178616.084520742</v>
       </c>
       <c r="GL12" t="n">
-        <v>173751.073983909</v>
+        <v>179561.104764388</v>
       </c>
       <c r="GM12" t="n">
-        <v>174719.031166794</v>
+        <v>180565.585677729</v>
       </c>
       <c r="GN12" t="n">
-        <v>175355.66161808</v>
+        <v>181369.896037215</v>
       </c>
       <c r="GO12" t="n">
-        <v>175999.038328654</v>
+        <v>182161.532030807</v>
       </c>
       <c r="GP12" t="n">
-        <v>176870.399670533</v>
+        <v>183118.90089184</v>
       </c>
       <c r="GQ12" t="n">
-        <v>177797.086539289</v>
+        <v>184094.881121377</v>
       </c>
       <c r="GR12" t="n">
-        <v>178825.293676859</v>
+        <v>185137.014834352</v>
       </c>
       <c r="GS12" t="n">
-        <v>180026.128029746</v>
+        <v>186314.106686688</v>
       </c>
       <c r="GT12" t="n">
-        <v>181377.098347047</v>
+        <v>187600.931958892</v>
       </c>
       <c r="GU12" t="n">
-        <v>182734.504434684</v>
+        <v>188858.105850868</v>
       </c>
       <c r="GV12" t="n">
-        <v>184154.799501935</v>
+        <v>190141.773704906</v>
       </c>
       <c r="GW12" t="n">
-        <v>185735.054872612</v>
+        <v>191549.416053342</v>
       </c>
       <c r="GX12" t="n">
-        <v>187458.934919667</v>
+        <v>193072.673141985</v>
       </c>
       <c r="GY12" t="n">
-        <v>189187.86091114</v>
+        <v>194585.62096964</v>
       </c>
       <c r="GZ12" t="n">
-        <v>190983.382566951</v>
+        <v>196158.131875255</v>
       </c>
       <c r="HA12" t="n">
-        <v>192911.88750152</v>
+        <v>197859.804900856</v>
       </c>
       <c r="HB12" t="n">
-        <v>194962.971176942</v>
+        <v>199689.121558909</v>
       </c>
       <c r="HC12" t="n">
-        <v>196938.020908495</v>
+        <v>201456.17327936</v>
       </c>
       <c r="HD12" t="n">
-        <v>198906.930934023</v>
+        <v>203231.268065036</v>
       </c>
       <c r="HE12" t="n">
-        <v>200958.589651449</v>
+        <v>205098.542500644</v>
       </c>
       <c r="HF12" t="n">
-        <v>203036.903484276</v>
+        <v>207003.801747777</v>
       </c>
       <c r="HG12" t="n">
-        <v>204992.148890827</v>
+        <v>208800.964882625</v>
       </c>
       <c r="HH12" t="n">
-        <v>206876.37741855</v>
+        <v>210539.367292765</v>
       </c>
       <c r="HI12" t="n">
-        <v>208785.968932409</v>
+        <v>212309.517155905</v>
       </c>
       <c r="HJ12" t="n">
-        <v>210710.978506641</v>
+        <v>214102.799384831</v>
       </c>
       <c r="HK12" t="n">
-        <v>212489.068398295</v>
+        <v>215762.215081235</v>
       </c>
       <c r="HL12" t="n">
-        <v>214188.904999786</v>
+        <v>217355.218841031</v>
       </c>
       <c r="HM12" t="n">
-        <v>215913.344103991</v>
+        <v>218979.043859517</v>
       </c>
       <c r="HN12" t="n">
-        <v>217651.903723733</v>
+        <v>220625.470598025</v>
       </c>
       <c r="HO12" t="n">
-        <v>219239.501775156</v>
+        <v>222135.646589314</v>
       </c>
       <c r="HP12" t="n">
-        <v>220738.494759442</v>
+        <v>223570.085250458</v>
       </c>
       <c r="HQ12" t="n">
-        <v>222269.296888062</v>
+        <v>225042.345154794</v>
       </c>
       <c r="HR12" t="n">
-        <v>223831.88419443</v>
+        <v>226554.198531152</v>
       </c>
       <c r="HS12" t="n">
-        <v>225219.768953428</v>
+        <v>227907.872097349</v>
       </c>
       <c r="HT12" t="n">
-        <v>226530.98491757</v>
+        <v>229196.335958797</v>
       </c>
       <c r="HU12" t="n">
-        <v>227921.533153777</v>
+        <v>230568.146541385</v>
       </c>
     </row>
     <row r="13">
@@ -10281,139 +10277,139 @@
         <v>688271</v>
       </c>
       <c r="GC13" t="n">
-        <v>688866.834207019</v>
+        <v>694551</v>
       </c>
       <c r="GD13" t="n">
-        <v>703604.833724565</v>
+        <v>699832.083472807</v>
       </c>
       <c r="GE13" t="n">
-        <v>704005.064389124</v>
+        <v>707572.4673704</v>
       </c>
       <c r="GF13" t="n">
-        <v>714552.93586156</v>
+        <v>713962.862058057</v>
       </c>
       <c r="GG13" t="n">
-        <v>719337.992559658</v>
+        <v>719740.7075308</v>
       </c>
       <c r="GH13" t="n">
-        <v>724256.765829046</v>
+        <v>724964.786333567</v>
       </c>
       <c r="GI13" t="n">
-        <v>728826.008025022</v>
+        <v>729852.089150932</v>
       </c>
       <c r="GJ13" t="n">
-        <v>732269.61534342</v>
+        <v>733689.317667511</v>
       </c>
       <c r="GK13" t="n">
-        <v>736143.756310264</v>
+        <v>738025.809426788</v>
       </c>
       <c r="GL13" t="n">
-        <v>739872.036054429</v>
+        <v>742306.374437168</v>
       </c>
       <c r="GM13" t="n">
-        <v>743482.735925008</v>
+        <v>746847.708968012</v>
       </c>
       <c r="GN13" t="n">
-        <v>745856.57694317</v>
+        <v>749993.14002661</v>
       </c>
       <c r="GO13" t="n">
-        <v>748707.895668934</v>
+        <v>753722.205919857</v>
       </c>
       <c r="GP13" t="n">
-        <v>751592.891779237</v>
+        <v>757439.45327626</v>
       </c>
       <c r="GQ13" t="n">
-        <v>753979.460209213</v>
+        <v>760756.632499964</v>
       </c>
       <c r="GR13" t="n">
-        <v>756564.061656325</v>
+        <v>764266.786053998</v>
       </c>
       <c r="GS13" t="n">
-        <v>759065.983376761</v>
+        <v>767716.582060501</v>
       </c>
       <c r="GT13" t="n">
-        <v>761592.821092448</v>
+        <v>771184.698840391</v>
       </c>
       <c r="GU13" t="n">
-        <v>763627.089338228</v>
+        <v>774171.046688245</v>
       </c>
       <c r="GV13" t="n">
-        <v>765984.19108567</v>
+        <v>777466.133262899</v>
       </c>
       <c r="GW13" t="n">
-        <v>768298.130966983</v>
+        <v>780702.662727419</v>
       </c>
       <c r="GX13" t="n">
-        <v>770723.944212995</v>
+        <v>784046.018118761</v>
       </c>
       <c r="GY13" t="n">
-        <v>772946.367068996</v>
+        <v>787194.414120666</v>
       </c>
       <c r="GZ13" t="n">
-        <v>775346.84537666</v>
+        <v>790529.90539203</v>
       </c>
       <c r="HA13" t="n">
-        <v>777903.578603048</v>
+        <v>794030.227846487</v>
       </c>
       <c r="HB13" t="n">
-        <v>780589.236172161</v>
+        <v>797683.839439064</v>
       </c>
       <c r="HC13" t="n">
-        <v>782636.191871042</v>
+        <v>800728.155549615</v>
       </c>
       <c r="HD13" t="n">
-        <v>785414.900332301</v>
+        <v>804527.75368949</v>
       </c>
       <c r="HE13" t="n">
-        <v>787969.453362443</v>
+        <v>808120.743784972</v>
       </c>
       <c r="HF13" t="n">
-        <v>790657.747887504</v>
+        <v>811874.634757333</v>
       </c>
       <c r="HG13" t="n">
-        <v>793123.08669446</v>
+        <v>815427.105394197</v>
       </c>
       <c r="HH13" t="n">
-        <v>795684.722537564</v>
+        <v>819094.978339893</v>
       </c>
       <c r="HI13" t="n">
-        <v>798380.276989552</v>
+        <v>822909.161837616</v>
       </c>
       <c r="HJ13" t="n">
-        <v>801126.051542471</v>
+        <v>826793.567835491</v>
       </c>
       <c r="HK13" t="n">
-        <v>803621.31987296</v>
+        <v>830442.461779349</v>
       </c>
       <c r="HL13" t="n">
-        <v>806212.514206004</v>
+        <v>834202.533280158</v>
       </c>
       <c r="HM13" t="n">
-        <v>808907.924093146</v>
+        <v>838074.711909319</v>
       </c>
       <c r="HN13" t="n">
-        <v>811626.162336572</v>
+        <v>841985.652198625</v>
       </c>
       <c r="HO13" t="n">
-        <v>814060.672962983</v>
+        <v>845620.343480419</v>
       </c>
       <c r="HP13" t="n">
-        <v>816537.500058475</v>
+        <v>849304.269210229</v>
       </c>
       <c r="HQ13" t="n">
-        <v>819110.576775134</v>
+        <v>853084.876123208</v>
       </c>
       <c r="HR13" t="n">
-        <v>821692.459819732</v>
+        <v>856881.697129547</v>
       </c>
       <c r="HS13" t="n">
-        <v>823299.562268308</v>
+        <v>859697.010381363</v>
       </c>
       <c r="HT13" t="n">
-        <v>825704.761593842</v>
+        <v>863309.304199387</v>
       </c>
       <c r="HU13" t="n">
-        <v>827719.66030336</v>
+        <v>866519.587608792</v>
       </c>
     </row>
     <row r="14">
@@ -10802,139 +10798,139 @@
         <v>681761</v>
       </c>
       <c r="GC14" t="n">
-        <v>685991.790982611</v>
+        <v>686078</v>
       </c>
       <c r="GD14" t="n">
-        <v>694055.018279022</v>
+        <v>693096.148438719</v>
       </c>
       <c r="GE14" t="n">
-        <v>699887.347519575</v>
+        <v>701540.595102093</v>
       </c>
       <c r="GF14" t="n">
-        <v>706537.13929819</v>
+        <v>708918.557128131</v>
       </c>
       <c r="GG14" t="n">
-        <v>712317.527544856</v>
+        <v>715697.531113741</v>
       </c>
       <c r="GH14" t="n">
-        <v>717253.184362601</v>
+        <v>721626.952345445</v>
       </c>
       <c r="GI14" t="n">
-        <v>721549.225618743</v>
+        <v>726860.70346726</v>
       </c>
       <c r="GJ14" t="n">
-        <v>725303.377828785</v>
+        <v>731502.845084088</v>
       </c>
       <c r="GK14" t="n">
-        <v>729132.022123893</v>
+        <v>736186.484911038</v>
       </c>
       <c r="GL14" t="n">
-        <v>733120.190944831</v>
+        <v>740946.746484907</v>
       </c>
       <c r="GM14" t="n">
-        <v>736977.26119375</v>
+        <v>745700.871147767</v>
       </c>
       <c r="GN14" t="n">
-        <v>740061.977033863</v>
+        <v>749638.805629339</v>
       </c>
       <c r="GO14" t="n">
-        <v>743252.595564336</v>
+        <v>753787.198640218</v>
       </c>
       <c r="GP14" t="n">
-        <v>746710.235489145</v>
+        <v>758086.093396878</v>
       </c>
       <c r="GQ14" t="n">
-        <v>749886.505795723</v>
+        <v>762166.347424333</v>
       </c>
       <c r="GR14" t="n">
-        <v>753269.60258759</v>
+        <v>766403.396825694</v>
       </c>
       <c r="GS14" t="n">
-        <v>756786.898920844</v>
+        <v>770763.19451922</v>
       </c>
       <c r="GT14" t="n">
-        <v>760452.50646781</v>
+        <v>775222.545779299</v>
       </c>
       <c r="GU14" t="n">
-        <v>763846.036018613</v>
+        <v>779385.458711069</v>
       </c>
       <c r="GV14" t="n">
-        <v>767394.499363981</v>
+        <v>783653.175742675</v>
       </c>
       <c r="GW14" t="n">
-        <v>771161.918081446</v>
+        <v>788091.561371874</v>
       </c>
       <c r="GX14" t="n">
-        <v>775130.288425432</v>
+        <v>792698.204691125</v>
       </c>
       <c r="GY14" t="n">
-        <v>778921.090205098</v>
+        <v>797118.174330315</v>
       </c>
       <c r="GZ14" t="n">
-        <v>782930.41800908</v>
+        <v>801755.390108482</v>
       </c>
       <c r="HA14" t="n">
-        <v>787182.951901498</v>
+        <v>806637.727361358</v>
       </c>
       <c r="HB14" t="n">
-        <v>791649.680264262</v>
+        <v>811758.565886189</v>
       </c>
       <c r="HC14" t="n">
-        <v>795802.382888791</v>
+        <v>816601.612421242</v>
       </c>
       <c r="HD14" t="n">
-        <v>800143.070982437</v>
+        <v>821664.162064583</v>
       </c>
       <c r="HE14" t="n">
-        <v>804620.198663451</v>
+        <v>826885.939097066</v>
       </c>
       <c r="HF14" t="n">
-        <v>809181.662944173</v>
+        <v>832224.759492016</v>
       </c>
       <c r="HG14" t="n">
-        <v>813403.502909599</v>
+        <v>837254.316235072</v>
       </c>
       <c r="HH14" t="n">
-        <v>817645.137365052</v>
+        <v>842330.040044829</v>
       </c>
       <c r="HI14" t="n">
-        <v>821997.504537775</v>
+        <v>847530.974886952</v>
       </c>
       <c r="HJ14" t="n">
-        <v>826391.3665486</v>
+        <v>852796.400968349</v>
       </c>
       <c r="HK14" t="n">
-        <v>830400.842788984</v>
+        <v>857699.865391406</v>
       </c>
       <c r="HL14" t="n">
-        <v>834422.957521357</v>
+        <v>862638.14269591</v>
       </c>
       <c r="HM14" t="n">
-        <v>838530.936098915</v>
+        <v>867672.211981305</v>
       </c>
       <c r="HN14" t="n">
-        <v>842657.593958723</v>
+        <v>872744.704923136</v>
       </c>
       <c r="HO14" t="n">
-        <v>846368.387081578</v>
+        <v>877418.251667419</v>
       </c>
       <c r="HP14" t="n">
-        <v>850036.483600149</v>
+        <v>882064.711085892</v>
       </c>
       <c r="HQ14" t="n">
-        <v>853794.08182472</v>
+        <v>886803.538691006</v>
       </c>
       <c r="HR14" t="n">
-        <v>857574.810040409</v>
+        <v>891576.723556808</v>
       </c>
       <c r="HS14" t="n">
-        <v>860827.632768053</v>
+        <v>895832.100807313</v>
       </c>
       <c r="HT14" t="n">
-        <v>864130.097848613</v>
+        <v>900139.215534622</v>
       </c>
       <c r="HU14" t="n">
-        <v>867508.541206919</v>
+        <v>904516.82427405</v>
       </c>
     </row>
     <row r="15">
@@ -11491,139 +11487,139 @@
         <v>718591</v>
       </c>
       <c r="GC15" t="n">
-        <v>722465.949255665</v>
+        <v>732456</v>
       </c>
       <c r="GD15" t="n">
-        <v>746181.017015557</v>
+        <v>747746.362275588</v>
       </c>
       <c r="GE15" t="n">
-        <v>757754.676205725</v>
+        <v>765104.837299486</v>
       </c>
       <c r="GF15" t="n">
-        <v>778154.725561157</v>
+        <v>781406.614363189</v>
       </c>
       <c r="GG15" t="n">
-        <v>793998.23894833</v>
+        <v>797281.158341983</v>
       </c>
       <c r="GH15" t="n">
-        <v>808487.249401088</v>
+        <v>811327.820689667</v>
       </c>
       <c r="GI15" t="n">
-        <v>822675.19967192</v>
+        <v>825028.67209153</v>
       </c>
       <c r="GJ15" t="n">
-        <v>835914.924429802</v>
+        <v>837833.89103062</v>
       </c>
       <c r="GK15" t="n">
-        <v>849589.241603711</v>
+        <v>851209.414181235</v>
       </c>
       <c r="GL15" t="n">
-        <v>862977.316797541</v>
+        <v>864479.336012588</v>
       </c>
       <c r="GM15" t="n">
-        <v>875811.625105886</v>
+        <v>877915.878626468</v>
       </c>
       <c r="GN15" t="n">
-        <v>887542.561041571</v>
+        <v>889720.875379534</v>
       </c>
       <c r="GO15" t="n">
-        <v>899743.533952259</v>
+        <v>902024.190935432</v>
       </c>
       <c r="GP15" t="n">
-        <v>912095.443110715</v>
+        <v>914336.698427995</v>
       </c>
       <c r="GQ15" t="n">
-        <v>923823.055790985</v>
+        <v>926120.599917584</v>
       </c>
       <c r="GR15" t="n">
-        <v>935745.512663679</v>
+        <v>938064.121594139</v>
       </c>
       <c r="GS15" t="n">
-        <v>947570.880671052</v>
+        <v>949890.549163912</v>
       </c>
       <c r="GT15" t="n">
-        <v>959506.13209917</v>
+        <v>961774.43738956</v>
       </c>
       <c r="GU15" t="n">
-        <v>970900.099086042</v>
+        <v>973083.457009861</v>
       </c>
       <c r="GV15" t="n">
-        <v>982665.914307902</v>
+        <v>984702.951478993</v>
       </c>
       <c r="GW15" t="n">
-        <v>994497.88306729</v>
+        <v>996301.747575855</v>
       </c>
       <c r="GX15" t="n">
-        <v>1006569.01134535</v>
+        <v>1008073.70526744</v>
       </c>
       <c r="GY15" t="n">
-        <v>1018478.23079495</v>
+        <v>1019655.0151253</v>
       </c>
       <c r="GZ15" t="n">
-        <v>1030737.9153832</v>
+        <v>1031540.2663076</v>
       </c>
       <c r="HA15" t="n">
-        <v>1043353.00926784</v>
+        <v>1043735.97507518</v>
       </c>
       <c r="HB15" t="n">
-        <v>1056555.95916543</v>
+        <v>1056515.74364704</v>
       </c>
       <c r="HC15" t="n">
-        <v>1069206.0770135</v>
+        <v>1068740.50848007</v>
       </c>
       <c r="HD15" t="n">
-        <v>1082818.25060279</v>
+        <v>1081949.5461418</v>
       </c>
       <c r="HE15" t="n">
-        <v>1096486.53893352</v>
+        <v>1095180.53245386</v>
       </c>
       <c r="HF15" t="n">
-        <v>1110518.243741</v>
+        <v>1108780.55323872</v>
       </c>
       <c r="HG15" t="n">
-        <v>1124442.8931187</v>
+        <v>1122309.42136595</v>
       </c>
       <c r="HH15" t="n">
-        <v>1138703.57830132</v>
+        <v>1136176.59965133</v>
       </c>
       <c r="HI15" t="n">
-        <v>1153375.19530958</v>
+        <v>1150444.88399742</v>
       </c>
       <c r="HJ15" t="n">
-        <v>1168346.53082982</v>
+        <v>1165018.86885411</v>
       </c>
       <c r="HK15" t="n">
-        <v>1183156.65654964</v>
+        <v>1179474.32967787</v>
       </c>
       <c r="HL15" t="n">
-        <v>1198317.72398417</v>
+        <v>1194286.58677645</v>
       </c>
       <c r="HM15" t="n">
-        <v>1213859.21970902</v>
+        <v>1209470.08660834</v>
       </c>
       <c r="HN15" t="n">
-        <v>1229666.73568783</v>
+        <v>1224926.60681789</v>
       </c>
       <c r="HO15" t="n">
-        <v>1245245.92936126</v>
+        <v>1240199.08936653</v>
       </c>
       <c r="HP15" t="n">
-        <v>1261087.83187208</v>
+        <v>1255735.76969729</v>
       </c>
       <c r="HQ15" t="n">
-        <v>1277297.21607073</v>
+        <v>1271619.00382411</v>
       </c>
       <c r="HR15" t="n">
-        <v>1293747.62289365</v>
+        <v>1287737.18740854</v>
       </c>
       <c r="HS15" t="n">
-        <v>1309144.36450333</v>
+        <v>1302788.50253174</v>
       </c>
       <c r="HT15" t="n">
-        <v>1325627.39560341</v>
+        <v>1318959.20558984</v>
       </c>
       <c r="HU15" t="n">
-        <v>1341942.36968465</v>
+        <v>1334882.19355118</v>
       </c>
     </row>
     <row r="16">
@@ -12180,139 +12176,139 @@
         <v>1.04405241540033</v>
       </c>
       <c r="GC16" t="n">
-        <v>1.04877443833457</v>
+        <v>1.05457482603869</v>
       </c>
       <c r="GD16" t="n">
-        <v>1.0605114964338</v>
+        <v>1.06846539838674</v>
       </c>
       <c r="GE16" t="n">
-        <v>1.07634833142797</v>
+        <v>1.0813095062928</v>
       </c>
       <c r="GF16" t="n">
-        <v>1.08900919969795</v>
+        <v>1.09446394915834</v>
       </c>
       <c r="GG16" t="n">
-        <v>1.10379020914826</v>
+        <v>1.10773386863375</v>
       </c>
       <c r="GH16" t="n">
-        <v>1.11629919321191</v>
+        <v>1.1191272143505</v>
       </c>
       <c r="GI16" t="n">
-        <v>1.12876761363586</v>
+        <v>1.13040530765657</v>
       </c>
       <c r="GJ16" t="n">
-        <v>1.14153981235997</v>
+        <v>1.14194642868435</v>
       </c>
       <c r="GK16" t="n">
-        <v>1.15410778107853</v>
+        <v>1.15335996306168</v>
       </c>
       <c r="GL16" t="n">
-        <v>1.16638725430616</v>
+        <v>1.16458563713133</v>
       </c>
       <c r="GM16" t="n">
-        <v>1.17798514865319</v>
+        <v>1.17549518502881</v>
       </c>
       <c r="GN16" t="n">
-        <v>1.18996411027693</v>
+        <v>1.18630536373974</v>
       </c>
       <c r="GO16" t="n">
-        <v>1.20172838677248</v>
+        <v>1.19675948748938</v>
       </c>
       <c r="GP16" t="n">
-        <v>1.21354985097721</v>
+        <v>1.20714164623477</v>
       </c>
       <c r="GQ16" t="n">
-        <v>1.22526289353899</v>
+        <v>1.21736777889168</v>
       </c>
       <c r="GR16" t="n">
-        <v>1.2368357944775</v>
+        <v>1.2274040305294</v>
       </c>
       <c r="GS16" t="n">
-        <v>1.24833795898015</v>
+        <v>1.23729327117709</v>
       </c>
       <c r="GT16" t="n">
-        <v>1.25986761668654</v>
+        <v>1.24713891596774</v>
       </c>
       <c r="GU16" t="n">
-        <v>1.27143223820511</v>
+        <v>1.25693601558942</v>
       </c>
       <c r="GV16" t="n">
-        <v>1.28288015134831</v>
+        <v>1.26655415911636</v>
       </c>
       <c r="GW16" t="n">
-        <v>1.29441663742944</v>
+        <v>1.27616032099384</v>
       </c>
       <c r="GX16" t="n">
-        <v>1.30600459338153</v>
+        <v>1.28573284555556</v>
       </c>
       <c r="GY16" t="n">
-        <v>1.31765705099761</v>
+        <v>1.29530267317134</v>
       </c>
       <c r="GZ16" t="n">
-        <v>1.32938944788484</v>
+        <v>1.30487192504355</v>
       </c>
       <c r="HA16" t="n">
-        <v>1.34123693024569</v>
+        <v>1.31447891033659</v>
       </c>
       <c r="HB16" t="n">
-        <v>1.35353641533388</v>
+        <v>1.32447932917233</v>
       </c>
       <c r="HC16" t="n">
-        <v>1.36615976247981</v>
+        <v>1.33471080720747</v>
       </c>
       <c r="HD16" t="n">
-        <v>1.37865763156499</v>
+        <v>1.3448256489424</v>
       </c>
       <c r="HE16" t="n">
-        <v>1.39153431515686</v>
+        <v>1.35521894944951</v>
       </c>
       <c r="HF16" t="n">
-        <v>1.40454987001595</v>
+        <v>1.36570416010842</v>
       </c>
       <c r="HG16" t="n">
-        <v>1.41774070656821</v>
+        <v>1.37634550948517</v>
       </c>
       <c r="HH16" t="n">
-        <v>1.43109894758024</v>
+        <v>1.38711217042576</v>
       </c>
       <c r="HI16" t="n">
-        <v>1.44464388443167</v>
+        <v>1.398021737328</v>
       </c>
       <c r="HJ16" t="n">
-        <v>1.45838038377461</v>
+        <v>1.40908072609164</v>
       </c>
       <c r="HK16" t="n">
-        <v>1.47228130144759</v>
+        <v>1.42029628529736</v>
       </c>
       <c r="HL16" t="n">
-        <v>1.48635463689748</v>
+        <v>1.43165065042355</v>
       </c>
       <c r="HM16" t="n">
-        <v>1.50061480020207</v>
+        <v>1.44315307671749</v>
       </c>
       <c r="HN16" t="n">
-        <v>1.51506540104293</v>
+        <v>1.45480699813692</v>
       </c>
       <c r="HO16" t="n">
-        <v>1.5296721123862</v>
+        <v>1.46661455499808</v>
       </c>
       <c r="HP16" t="n">
-        <v>1.54443342851132</v>
+        <v>1.47854641698365</v>
       </c>
       <c r="HQ16" t="n">
-        <v>1.55937089518065</v>
+        <v>1.490612544901</v>
       </c>
       <c r="HR16" t="n">
-        <v>1.57449126247415</v>
+        <v>1.50281795742413</v>
       </c>
       <c r="HS16" t="n">
-        <v>1.59011907532479</v>
+        <v>1.5154042687561</v>
       </c>
       <c r="HT16" t="n">
-        <v>1.60544958787601</v>
+        <v>1.52779451669565</v>
       </c>
       <c r="HU16" t="n">
-        <v>1.62125222597604</v>
+        <v>1.54051013708252</v>
       </c>
     </row>
     <row r="17">
@@ -12869,139 +12865,139 @@
         <v>143.5</v>
       </c>
       <c r="GC17" t="n">
-        <v>144.861825036032</v>
+        <v>144.6</v>
       </c>
       <c r="GD17" t="n">
-        <v>146.567278204913</v>
+        <v>145.602786429181</v>
       </c>
       <c r="GE17" t="n">
-        <v>148.241631055667</v>
+        <v>146.92234042679</v>
       </c>
       <c r="GF17" t="n">
-        <v>150.062869922578</v>
+        <v>148.312955752293</v>
       </c>
       <c r="GG17" t="n">
-        <v>151.913210100911</v>
+        <v>149.789568441815</v>
       </c>
       <c r="GH17" t="n">
-        <v>153.807079270962</v>
+        <v>151.313568092358</v>
       </c>
       <c r="GI17" t="n">
-        <v>155.737810677994</v>
+        <v>152.88037464213</v>
       </c>
       <c r="GJ17" t="n">
-        <v>157.676999581605</v>
+        <v>154.463486819158</v>
       </c>
       <c r="GK17" t="n">
-        <v>159.617705393002</v>
+        <v>156.050755092539</v>
       </c>
       <c r="GL17" t="n">
-        <v>161.54507457248</v>
+        <v>157.634550593569</v>
       </c>
       <c r="GM17" t="n">
-        <v>163.438775844355</v>
+        <v>159.213548100527</v>
       </c>
       <c r="GN17" t="n">
-        <v>165.302610326867</v>
+        <v>160.750212355454</v>
       </c>
       <c r="GO17" t="n">
-        <v>167.147037406829</v>
+        <v>162.265173370885</v>
       </c>
       <c r="GP17" t="n">
-        <v>168.97076524576</v>
+        <v>163.755794155683</v>
       </c>
       <c r="GQ17" t="n">
-        <v>170.771152773423</v>
+        <v>165.220820850622</v>
       </c>
       <c r="GR17" t="n">
-        <v>172.561047652913</v>
+        <v>166.670636116422</v>
       </c>
       <c r="GS17" t="n">
-        <v>174.336529199355</v>
+        <v>168.101549082093</v>
       </c>
       <c r="GT17" t="n">
-        <v>176.103581632536</v>
+        <v>169.518606735727</v>
       </c>
       <c r="GU17" t="n">
-        <v>177.859925856128</v>
+        <v>170.919529625841</v>
       </c>
       <c r="GV17" t="n">
-        <v>179.61495784256</v>
+        <v>172.312494736845</v>
       </c>
       <c r="GW17" t="n">
-        <v>181.369116557117</v>
+        <v>173.69801642778</v>
       </c>
       <c r="GX17" t="n">
-        <v>183.126373748861</v>
+        <v>175.079718897251</v>
       </c>
       <c r="GY17" t="n">
-        <v>184.887021174485</v>
+        <v>176.458115283257</v>
       </c>
       <c r="GZ17" t="n">
-        <v>186.66035712596</v>
+        <v>177.842007049096</v>
       </c>
       <c r="HA17" t="n">
-        <v>188.445720308962</v>
+        <v>179.231136028477</v>
       </c>
       <c r="HB17" t="n">
-        <v>190.2481335749</v>
+        <v>180.630760267222</v>
       </c>
       <c r="HC17" t="n">
-        <v>192.064173922479</v>
+        <v>182.03813841952</v>
       </c>
       <c r="HD17" t="n">
-        <v>193.907181320183</v>
+        <v>183.465818555689</v>
       </c>
       <c r="HE17" t="n">
-        <v>195.77103888629</v>
+        <v>184.909121603141</v>
       </c>
       <c r="HF17" t="n">
-        <v>197.660858807234</v>
+        <v>186.37295665852</v>
       </c>
       <c r="HG17" t="n">
-        <v>199.5744988877</v>
+        <v>187.85595588273</v>
       </c>
       <c r="HH17" t="n">
-        <v>201.516643902451</v>
+        <v>189.36251829358</v>
       </c>
       <c r="HI17" t="n">
-        <v>203.486791205144</v>
+        <v>190.892484607628</v>
       </c>
       <c r="HJ17" t="n">
-        <v>205.485453031879</v>
+        <v>192.446614291509</v>
       </c>
       <c r="HK17" t="n">
-        <v>207.510209888551</v>
+        <v>194.022909112333</v>
       </c>
       <c r="HL17" t="n">
-        <v>209.566509972304</v>
+        <v>195.626239786653</v>
       </c>
       <c r="HM17" t="n">
-        <v>211.65125169234</v>
+        <v>197.253786545919</v>
       </c>
       <c r="HN17" t="n">
-        <v>213.764838746508</v>
+        <v>198.90592742779</v>
       </c>
       <c r="HO17" t="n">
-        <v>215.903847055471</v>
+        <v>200.579477743225</v>
       </c>
       <c r="HP17" t="n">
-        <v>218.069944131086</v>
+        <v>202.275358532948</v>
       </c>
       <c r="HQ17" t="n">
-        <v>220.26299062667</v>
+        <v>203.99319249574</v>
       </c>
       <c r="HR17" t="n">
-        <v>222.482164740121</v>
+        <v>205.732054696493</v>
       </c>
       <c r="HS17" t="n">
-        <v>224.718528185303</v>
+        <v>207.483008111214</v>
       </c>
       <c r="HT17" t="n">
-        <v>226.982580411847</v>
+        <v>209.254502785731</v>
       </c>
       <c r="HU17" t="n">
-        <v>229.265895310311</v>
+        <v>211.039003301173</v>
       </c>
     </row>
     <row r="18">
@@ -13558,139 +13554,139 @@
         <v>26114</v>
       </c>
       <c r="GC18" t="n">
-        <v>26415.8365048095</v>
+        <v>26364</v>
       </c>
       <c r="GD18" t="n">
-        <v>26494.6807937833</v>
+        <v>26669.9548135571</v>
       </c>
       <c r="GE18" t="n">
-        <v>26905.6263101691</v>
+        <v>26896.4693862502</v>
       </c>
       <c r="GF18" t="n">
-        <v>27192.0542864247</v>
+        <v>27276.085021759</v>
       </c>
       <c r="GG18" t="n">
-        <v>27574.8384154166</v>
+        <v>27646.9143829087</v>
       </c>
       <c r="GH18" t="n">
-        <v>27944.2033868636</v>
+        <v>28029.9510712096</v>
       </c>
       <c r="GI18" t="n">
-        <v>28315.8022620169</v>
+        <v>28409.0723856215</v>
       </c>
       <c r="GJ18" t="n">
-        <v>28692.1529500277</v>
+        <v>28784.8402337269</v>
       </c>
       <c r="GK18" t="n">
-        <v>29056.995200083</v>
+        <v>29150.74289949</v>
       </c>
       <c r="GL18" t="n">
-        <v>29420.8575092684</v>
+        <v>29510.1106395063</v>
       </c>
       <c r="GM18" t="n">
-        <v>29779.9763309022</v>
+        <v>29861.7008227629</v>
       </c>
       <c r="GN18" t="n">
-        <v>30140.613076668</v>
+        <v>30216.4757277637</v>
       </c>
       <c r="GO18" t="n">
-        <v>30476.8631330847</v>
+        <v>30545.9678870164</v>
       </c>
       <c r="GP18" t="n">
-        <v>30805.4303632754</v>
+        <v>30868.2921429934</v>
       </c>
       <c r="GQ18" t="n">
-        <v>31130.6659313617</v>
+        <v>31184.2632318041</v>
       </c>
       <c r="GR18" t="n">
-        <v>31445.1988198879</v>
+        <v>31489.3828507416</v>
       </c>
       <c r="GS18" t="n">
-        <v>31758.7692120974</v>
+        <v>31792.5116920336</v>
       </c>
       <c r="GT18" t="n">
-        <v>32067.2451073433</v>
+        <v>32090.0675463865</v>
       </c>
       <c r="GU18" t="n">
-        <v>32376.4353907693</v>
+        <v>32387.2498025838</v>
       </c>
       <c r="GV18" t="n">
-        <v>32677.9585502006</v>
+        <v>32676.6014633415</v>
       </c>
       <c r="GW18" t="n">
-        <v>32978.7669482435</v>
+        <v>32964.4557611911</v>
       </c>
       <c r="GX18" t="n">
-        <v>33277.7183207276</v>
+        <v>33249.6343635042</v>
       </c>
       <c r="GY18" t="n">
-        <v>33578.6195957268</v>
+        <v>33535.5963196868</v>
       </c>
       <c r="GZ18" t="n">
-        <v>33875.5492037495</v>
+        <v>33817.0701920853</v>
       </c>
       <c r="HA18" t="n">
-        <v>34176.0189717193</v>
+        <v>34101.373897121</v>
       </c>
       <c r="HB18" t="n">
-        <v>34477.544615345</v>
+        <v>34385.9848650755</v>
       </c>
       <c r="HC18" t="n">
-        <v>34787.635163077</v>
+        <v>34678.2441847284</v>
       </c>
       <c r="HD18" t="n">
-        <v>35089.6837133239</v>
+        <v>34962.9712220141</v>
       </c>
       <c r="HE18" t="n">
-        <v>35402.0528546136</v>
+        <v>35257.6312443398</v>
       </c>
       <c r="HF18" t="n">
-        <v>35715.8426651062</v>
+        <v>35553.817634056</v>
       </c>
       <c r="HG18" t="n">
-        <v>36035.8413315641</v>
+        <v>35856.1293588207</v>
       </c>
       <c r="HH18" t="n">
-        <v>36356.0141682394</v>
+        <v>36159.2715254901</v>
       </c>
       <c r="HI18" t="n">
-        <v>36679.7314677092</v>
+        <v>36466.495771862</v>
       </c>
       <c r="HJ18" t="n">
-        <v>37007.522557153</v>
+        <v>36778.1401859351</v>
       </c>
       <c r="HK18" t="n">
-        <v>37341.4831264051</v>
+        <v>37096.1661321953</v>
       </c>
       <c r="HL18" t="n">
-        <v>37674.8921511431</v>
+        <v>37414.5853034137</v>
       </c>
       <c r="HM18" t="n">
-        <v>38013.29509086</v>
+        <v>37738.7144862118</v>
       </c>
       <c r="HN18" t="n">
-        <v>38355.3901552987</v>
+        <v>38067.0520372903</v>
       </c>
       <c r="HO18" t="n">
-        <v>38703.7269955204</v>
+        <v>38401.9582793825</v>
       </c>
       <c r="HP18" t="n">
-        <v>39052.5263888293</v>
+        <v>38738.3665048471</v>
       </c>
       <c r="HQ18" t="n">
-        <v>39402.7735224389</v>
+        <v>39077.0997244572</v>
       </c>
       <c r="HR18" t="n">
-        <v>39756.4345995389</v>
+        <v>39419.7595953619</v>
       </c>
       <c r="HS18" t="n">
-        <v>40120.0053551711</v>
+        <v>39772.1542117098</v>
       </c>
       <c r="HT18" t="n">
-        <v>40471.5843025318</v>
+        <v>40114.5108991185</v>
       </c>
       <c r="HU18" t="n">
-        <v>40831.4837265466</v>
+        <v>40465.102306864</v>
       </c>
     </row>
     <row r="19">
@@ -14247,139 +14243,139 @@
         <v>14608.7589597667</v>
       </c>
       <c r="GC19" t="n">
-        <v>14660.1382908138</v>
+        <v>14636.2891356667</v>
       </c>
       <c r="GD19" t="n">
-        <v>14784.3907849657</v>
+        <v>14771.6738184608</v>
       </c>
       <c r="GE19" t="n">
-        <v>14873.7006897608</v>
+        <v>14901.0388661503</v>
       </c>
       <c r="GF19" t="n">
-        <v>14979.6239936873</v>
+        <v>15013.0791103666</v>
       </c>
       <c r="GG19" t="n">
-        <v>15073.6227619722</v>
+        <v>15110.3312908388</v>
       </c>
       <c r="GH19" t="n">
-        <v>15154.7536053024</v>
+        <v>15191.2912741126</v>
       </c>
       <c r="GI19" t="n">
-        <v>15223.4317295647</v>
+        <v>15259.6043437241</v>
       </c>
       <c r="GJ19" t="n">
-        <v>15278.9814737081</v>
+        <v>15311.7449608615</v>
       </c>
       <c r="GK19" t="n">
-        <v>15327.5557187814</v>
+        <v>15357.0120474212</v>
       </c>
       <c r="GL19" t="n">
-        <v>15371.4471386894</v>
+        <v>15397.1721730849</v>
       </c>
       <c r="GM19" t="n">
-        <v>15411.0513046542</v>
+        <v>15435.1287213343</v>
       </c>
       <c r="GN19" t="n">
-        <v>15438.1692116841</v>
+        <v>15461.230567912</v>
       </c>
       <c r="GO19" t="n">
-        <v>15462.5236798803</v>
+        <v>15484.7473089033</v>
       </c>
       <c r="GP19" t="n">
-        <v>15486.6849526166</v>
+        <v>15507.6621847011</v>
       </c>
       <c r="GQ19" t="n">
-        <v>15509.099740885</v>
+        <v>15529.1589057482</v>
       </c>
       <c r="GR19" t="n">
-        <v>15531.6194493314</v>
+        <v>15550.7165432239</v>
       </c>
       <c r="GS19" t="n">
-        <v>15555.2674192707</v>
+        <v>15573.5154848468</v>
       </c>
       <c r="GT19" t="n">
-        <v>15580.6921937828</v>
+        <v>15598.0375589127</v>
       </c>
       <c r="GU19" t="n">
-        <v>15605.4442405689</v>
+        <v>15622.0585436827</v>
       </c>
       <c r="GV19" t="n">
-        <v>15632.3490255688</v>
+        <v>15648.0632440044</v>
       </c>
       <c r="GW19" t="n">
-        <v>15661.173246529</v>
+        <v>15675.7446636613</v>
       </c>
       <c r="GX19" t="n">
-        <v>15692.5940088257</v>
+        <v>15705.7514691685</v>
       </c>
       <c r="GY19" t="n">
-        <v>15725.1074820831</v>
+        <v>15736.8318405696</v>
       </c>
       <c r="GZ19" t="n">
-        <v>15759.4890465908</v>
+        <v>15769.7248436292</v>
       </c>
       <c r="HA19" t="n">
-        <v>15796.7509370761</v>
+        <v>15805.4899961582</v>
       </c>
       <c r="HB19" t="n">
-        <v>15837.4746936044</v>
+        <v>15844.8642174264</v>
       </c>
       <c r="HC19" t="n">
-        <v>15877.1565731392</v>
+        <v>15883.7758958973</v>
       </c>
       <c r="HD19" t="n">
-        <v>15919.9771291619</v>
+        <v>15926.1211928164</v>
       </c>
       <c r="HE19" t="n">
-        <v>15964.2554711333</v>
+        <v>15970.3441195773</v>
       </c>
       <c r="HF19" t="n">
-        <v>16010.2679570229</v>
+        <v>16016.720728095</v>
       </c>
       <c r="HG19" t="n">
-        <v>16056.0867201441</v>
+        <v>16063.4906006388</v>
       </c>
       <c r="HH19" t="n">
-        <v>16102.1438208044</v>
+        <v>16110.9421290454</v>
       </c>
       <c r="HI19" t="n">
-        <v>16149.2688145554</v>
+        <v>16159.7553314462</v>
       </c>
       <c r="HJ19" t="n">
-        <v>16197.3550174937</v>
+        <v>16209.8066317227</v>
       </c>
       <c r="HK19" t="n">
-        <v>16244.4397149243</v>
+        <v>16259.289328847</v>
       </c>
       <c r="HL19" t="n">
-        <v>16290.9862546113</v>
+        <v>16308.4960742148</v>
       </c>
       <c r="HM19" t="n">
-        <v>16338.0041933129</v>
+        <v>16358.2982278307</v>
       </c>
       <c r="HN19" t="n">
-        <v>16385.3837652746</v>
+        <v>16408.5780668784</v>
       </c>
       <c r="HO19" t="n">
-        <v>16431.1898542148</v>
+        <v>16457.5725125064</v>
       </c>
       <c r="HP19" t="n">
-        <v>16476.1725413265</v>
+        <v>16505.875473688</v>
       </c>
       <c r="HQ19" t="n">
-        <v>16521.2059305811</v>
+        <v>16554.182014214</v>
       </c>
       <c r="HR19" t="n">
-        <v>16566.3518378067</v>
+        <v>16602.5427562164</v>
       </c>
       <c r="HS19" t="n">
-        <v>16606.2503249918</v>
+        <v>16646.0226118538</v>
       </c>
       <c r="HT19" t="n">
-        <v>16647.0335993825</v>
+        <v>16690.1299655197</v>
       </c>
       <c r="HU19" t="n">
-        <v>16686.756894527</v>
+        <v>16733.02554284</v>
       </c>
     </row>
     <row r="20">
@@ -14936,139 +14932,139 @@
         <v>0.669101939</v>
       </c>
       <c r="GC20" t="n">
-        <v>0.668738443493437</v>
+        <v>0.667316483666667</v>
       </c>
       <c r="GD20" t="n">
-        <v>0.668207338782978</v>
+        <v>0.668104304042333</v>
       </c>
       <c r="GE20" t="n">
-        <v>0.668874023193749</v>
+        <v>0.668516955070981</v>
       </c>
       <c r="GF20" t="n">
-        <v>0.669265864313209</v>
+        <v>0.669412237640828</v>
       </c>
       <c r="GG20" t="n">
-        <v>0.669992092008903</v>
+        <v>0.670212959207424</v>
       </c>
       <c r="GH20" t="n">
-        <v>0.670563620862076</v>
+        <v>0.670820538850624</v>
       </c>
       <c r="GI20" t="n">
-        <v>0.670828879735494</v>
+        <v>0.67125495894601</v>
       </c>
       <c r="GJ20" t="n">
-        <v>0.671058690849045</v>
+        <v>0.67144124349237</v>
       </c>
       <c r="GK20" t="n">
-        <v>0.671099902521527</v>
+        <v>0.671501790071365</v>
       </c>
       <c r="GL20" t="n">
-        <v>0.671073274359972</v>
+        <v>0.671452065448435</v>
       </c>
       <c r="GM20" t="n">
-        <v>0.670965270697196</v>
+        <v>0.67132353163385</v>
       </c>
       <c r="GN20" t="n">
-        <v>0.670772055868517</v>
+        <v>0.67112832600475</v>
       </c>
       <c r="GO20" t="n">
-        <v>0.67044649759709</v>
+        <v>0.670801927921234</v>
       </c>
       <c r="GP20" t="n">
-        <v>0.670067618904415</v>
+        <v>0.670424062995236</v>
       </c>
       <c r="GQ20" t="n">
-        <v>0.669664801186322</v>
+        <v>0.670015374320545</v>
       </c>
       <c r="GR20" t="n">
-        <v>0.669240053335417</v>
+        <v>0.669582130216579</v>
       </c>
       <c r="GS20" t="n">
-        <v>0.668835524517931</v>
+        <v>0.669168924726183</v>
       </c>
       <c r="GT20" t="n">
-        <v>0.668435740027791</v>
+        <v>0.668760644223389</v>
       </c>
       <c r="GU20" t="n">
-        <v>0.668050433292613</v>
+        <v>0.668366949352061</v>
       </c>
       <c r="GV20" t="n">
-        <v>0.667665679409849</v>
+        <v>0.6679736606174</v>
       </c>
       <c r="GW20" t="n">
-        <v>0.667301985313034</v>
+        <v>0.667599181160528</v>
       </c>
       <c r="GX20" t="n">
-        <v>0.666964589500615</v>
+        <v>0.667247751717641</v>
       </c>
       <c r="GY20" t="n">
-        <v>0.666657932243705</v>
+        <v>0.666923997093547</v>
       </c>
       <c r="GZ20" t="n">
-        <v>0.666376046794848</v>
+        <v>0.666623792382767</v>
       </c>
       <c r="HA20" t="n">
-        <v>0.66613719610291</v>
+        <v>0.666365810908538</v>
       </c>
       <c r="HB20" t="n">
-        <v>0.66593823261433</v>
+        <v>0.666147527045138</v>
       </c>
       <c r="HC20" t="n">
-        <v>0.665778140116756</v>
+        <v>0.665970280292895</v>
       </c>
       <c r="HD20" t="n">
-        <v>0.665626713816379</v>
+        <v>0.665807012734054</v>
       </c>
       <c r="HE20" t="n">
-        <v>0.665523552441271</v>
+        <v>0.66569615891111</v>
       </c>
       <c r="HF20" t="n">
-        <v>0.665444284872856</v>
+        <v>0.66561436969413</v>
       </c>
       <c r="HG20" t="n">
-        <v>0.665388284378883</v>
+        <v>0.665561406570705</v>
       </c>
       <c r="HH20" t="n">
-        <v>0.665341795956703</v>
+        <v>0.665524748483023</v>
       </c>
       <c r="HI20" t="n">
-        <v>0.665306580427461</v>
+        <v>0.665505140367949</v>
       </c>
       <c r="HJ20" t="n">
-        <v>0.665287819876703</v>
+        <v>0.665506395549951</v>
       </c>
       <c r="HK20" t="n">
-        <v>0.665279291899466</v>
+        <v>0.665522177794346</v>
       </c>
       <c r="HL20" t="n">
-        <v>0.665267800448204</v>
+        <v>0.665540019002139</v>
       </c>
       <c r="HM20" t="n">
-        <v>0.665265054124157</v>
+        <v>0.665570242072181</v>
       </c>
       <c r="HN20" t="n">
-        <v>0.665267771793435</v>
+        <v>0.66560815108048</v>
       </c>
       <c r="HO20" t="n">
-        <v>0.665272761287944</v>
+        <v>0.665650441118894</v>
       </c>
       <c r="HP20" t="n">
-        <v>0.665264955091977</v>
+        <v>0.665682905305749</v>
       </c>
       <c r="HQ20" t="n">
-        <v>0.665247490956784</v>
+        <v>0.665707234831275</v>
       </c>
       <c r="HR20" t="n">
-        <v>0.665228855245502</v>
+        <v>0.665730369373521</v>
       </c>
       <c r="HS20" t="n">
-        <v>0.66520203625928</v>
+        <v>0.665745555066561</v>
       </c>
       <c r="HT20" t="n">
-        <v>0.665132082304693</v>
+        <v>0.665719821323794</v>
       </c>
       <c r="HU20" t="n">
-        <v>0.665064625162319</v>
+        <v>0.665694618366085</v>
       </c>
     </row>
     <row r="21">
@@ -15625,139 +15621,139 @@
         <v>0.0430614370315685</v>
       </c>
       <c r="GC21" t="n">
-        <v>0.0476355452146825</v>
+        <v>0.0425731268402279</v>
       </c>
       <c r="GD21" t="n">
-        <v>0.0429469799590524</v>
+        <v>0.0436227329718427</v>
       </c>
       <c r="GE21" t="n">
-        <v>0.0422622895429496</v>
+        <v>0.0399894608571969</v>
       </c>
       <c r="GF21" t="n">
-        <v>0.0397043761566259</v>
+        <v>0.0377701246829486</v>
       </c>
       <c r="GG21" t="n">
-        <v>0.0384188223965749</v>
+        <v>0.0363947611075235</v>
       </c>
       <c r="GH21" t="n">
-        <v>0.0377529827519163</v>
+        <v>0.0358024551873029</v>
       </c>
       <c r="GI21" t="n">
-        <v>0.0374515894401633</v>
+        <v>0.0357768956047281</v>
       </c>
       <c r="GJ21" t="n">
-        <v>0.0377614085617731</v>
+        <v>0.036247443822446</v>
       </c>
       <c r="GK21" t="n">
-        <v>0.0382422909373827</v>
+        <v>0.0369707069185794</v>
       </c>
       <c r="GL21" t="n">
-        <v>0.0389194502846442</v>
+        <v>0.0378541156511121</v>
       </c>
       <c r="GM21" t="n">
-        <v>0.0397459318085481</v>
+        <v>0.0387589365501333</v>
       </c>
       <c r="GN21" t="n">
-        <v>0.0411742074325166</v>
+        <v>0.0402516830232445</v>
       </c>
       <c r="GO21" t="n">
-        <v>0.042576611386634</v>
+        <v>0.0417085784948226</v>
       </c>
       <c r="GP21" t="n">
-        <v>0.0439062811463092</v>
+        <v>0.0431202382006993</v>
       </c>
       <c r="GQ21" t="n">
-        <v>0.0453008820821677</v>
+        <v>0.0445662714883572</v>
       </c>
       <c r="GR21" t="n">
-        <v>0.0465294393567139</v>
+        <v>0.0458448005444122</v>
       </c>
       <c r="GS21" t="n">
-        <v>0.0477091906589183</v>
+        <v>0.0470670674626929</v>
       </c>
       <c r="GT21" t="n">
-        <v>0.0487791084776117</v>
+        <v>0.0481828023714652</v>
       </c>
       <c r="GU21" t="n">
-        <v>0.0499031234612238</v>
+        <v>0.0493420217562821</v>
       </c>
       <c r="GV21" t="n">
-        <v>0.0509013204393899</v>
+        <v>0.050385294047746</v>
       </c>
       <c r="GW21" t="n">
-        <v>0.0518060108937556</v>
+        <v>0.0513463004241572</v>
       </c>
       <c r="GX21" t="n">
-        <v>0.0525847512532759</v>
+        <v>0.0521927894104572</v>
       </c>
       <c r="GY21" t="n">
-        <v>0.0533357232548638</v>
+        <v>0.0530078583002039</v>
       </c>
       <c r="GZ21" t="n">
-        <v>0.0538974826684908</v>
+        <v>0.0536348325019986</v>
       </c>
       <c r="HA21" t="n">
-        <v>0.0543432694253603</v>
+        <v>0.054144730503899</v>
       </c>
       <c r="HB21" t="n">
-        <v>0.0546353807734029</v>
+        <v>0.0544914506226718</v>
       </c>
       <c r="HC21" t="n">
-        <v>0.0550422313300796</v>
+        <v>0.0549210195520002</v>
       </c>
       <c r="HD21" t="n">
-        <v>0.0551897491992756</v>
+        <v>0.0550810692772723</v>
       </c>
       <c r="HE21" t="n">
-        <v>0.0553179422842544</v>
+        <v>0.0552026888563049</v>
       </c>
       <c r="HF21" t="n">
-        <v>0.0553766803496886</v>
+        <v>0.0552374407343645</v>
       </c>
       <c r="HG21" t="n">
-        <v>0.0554793953270457</v>
+        <v>0.055289653095162</v>
       </c>
       <c r="HH21" t="n">
-        <v>0.0555371497172604</v>
+        <v>0.0552808676474769</v>
       </c>
       <c r="HI21" t="n">
-        <v>0.055548109231266</v>
+        <v>0.055216803489489</v>
       </c>
       <c r="HJ21" t="n">
-        <v>0.055526404159625</v>
+        <v>0.0551107870858183</v>
       </c>
       <c r="HK21" t="n">
-        <v>0.0555778061324279</v>
+        <v>0.0550594682786558</v>
       </c>
       <c r="HL21" t="n">
-        <v>0.0555757989612515</v>
+        <v>0.0549474234825232</v>
       </c>
       <c r="HM21" t="n">
-        <v>0.0555588552314353</v>
+        <v>0.0548193331055893</v>
       </c>
       <c r="HN21" t="n">
-        <v>0.0555288791490229</v>
+        <v>0.0546756077152599</v>
       </c>
       <c r="HO21" t="n">
-        <v>0.0555927408357918</v>
+        <v>0.0546130658370774</v>
       </c>
       <c r="HP21" t="n">
-        <v>0.0556887257192587</v>
+        <v>0.0545803005743967</v>
       </c>
       <c r="HQ21" t="n">
-        <v>0.0557675599911851</v>
+        <v>0.0545362887576884</v>
       </c>
       <c r="HR21" t="n">
-        <v>0.0558377972579612</v>
+        <v>0.0544880009169487</v>
       </c>
       <c r="HS21" t="n">
-        <v>0.05619417293662</v>
+        <v>0.0547061209249295</v>
       </c>
       <c r="HT21" t="n">
-        <v>0.0564263794043315</v>
+        <v>0.0548188343382414</v>
       </c>
       <c r="HU21" t="n">
-        <v>0.0567202434040637</v>
+        <v>0.0549999125211977</v>
       </c>
     </row>
     <row r="22">
@@ -16314,139 +16310,139 @@
         <v>657.3819662</v>
       </c>
       <c r="GC22" t="n">
-        <v>733.273170648825</v>
+        <v>650.820037866667</v>
       </c>
       <c r="GD22" t="n">
-        <v>663.437687322963</v>
+        <v>673.772664125239</v>
       </c>
       <c r="GE22" t="n">
-        <v>656.334950903321</v>
+        <v>620.70630354258</v>
       </c>
       <c r="GF22" t="n">
-        <v>619.347528102749</v>
+        <v>589.304020308437</v>
       </c>
       <c r="GG22" t="n">
-        <v>602.248600514517</v>
+        <v>570.70772337623</v>
       </c>
       <c r="GH22" t="n">
-        <v>594.584571114145</v>
+        <v>564.081062463098</v>
       </c>
       <c r="GI22" t="n">
-        <v>592.325314434715</v>
+        <v>566.198131351071</v>
       </c>
       <c r="GJ22" t="n">
-        <v>599.597587580534</v>
+        <v>575.886054414061</v>
       </c>
       <c r="GK22" t="n">
-        <v>609.468396583936</v>
+        <v>589.555939950915</v>
       </c>
       <c r="GL22" t="n">
-        <v>622.474732247418</v>
+        <v>605.777557112291</v>
       </c>
       <c r="GM22" t="n">
-        <v>637.879806587987</v>
+        <v>622.371693481924</v>
       </c>
       <c r="GN22" t="n">
-        <v>662.950954458693</v>
+        <v>648.441457576895</v>
       </c>
       <c r="GO22" t="n">
-        <v>687.618424070593</v>
+        <v>673.956626996269</v>
       </c>
       <c r="GP22" t="n">
-        <v>711.188498347827</v>
+        <v>698.827764229463</v>
       </c>
       <c r="GQ22" t="n">
-        <v>735.913548479324</v>
+        <v>724.358735665519</v>
       </c>
       <c r="GR22" t="n">
-        <v>757.944391848467</v>
+        <v>747.173582622438</v>
       </c>
       <c r="GS22" t="n">
-        <v>779.309567264168</v>
+        <v>769.203939057852</v>
       </c>
       <c r="GT22" t="n">
-        <v>798.98623735259</v>
+        <v>789.602484575496</v>
       </c>
       <c r="GU22" t="n">
-        <v>819.664345928875</v>
+        <v>810.832105944926</v>
       </c>
       <c r="GV22" t="n">
-        <v>838.382091299467</v>
+        <v>830.265501160538</v>
       </c>
       <c r="GW22" t="n">
-        <v>855.671988353482</v>
+        <v>848.456667749473</v>
       </c>
       <c r="GX22" t="n">
-        <v>870.992186270141</v>
+        <v>864.866856062425</v>
       </c>
       <c r="GY22" t="n">
-        <v>885.963618891605</v>
+        <v>880.868780469951</v>
       </c>
       <c r="GZ22" t="n">
-        <v>897.785282086257</v>
+        <v>893.74233402788</v>
       </c>
       <c r="HA22" t="n">
-        <v>907.778892096838</v>
+        <v>904.772740383292</v>
       </c>
       <c r="HB22" t="n">
-        <v>915.29402322659</v>
+        <v>913.1696441603</v>
       </c>
       <c r="HC22" t="n">
-        <v>924.818321035711</v>
+        <v>923.047962551344</v>
       </c>
       <c r="HD22" t="n">
-        <v>929.942994877063</v>
+        <v>928.363084520788</v>
       </c>
       <c r="HE22" t="n">
-        <v>934.822345729101</v>
+        <v>933.116547681304</v>
       </c>
       <c r="HF22" t="n">
-        <v>938.57054253792</v>
+        <v>936.449824851074</v>
       </c>
       <c r="HG22" t="n">
-        <v>943.105013652543</v>
+        <v>940.124020367057</v>
       </c>
       <c r="HH22" t="n">
-        <v>946.852810778906</v>
+        <v>942.742554639772</v>
       </c>
       <c r="HI22" t="n">
-        <v>949.82231937946</v>
+        <v>944.439005459735</v>
       </c>
       <c r="HJ22" t="n">
-        <v>952.256396918936</v>
+        <v>945.439167912129</v>
       </c>
       <c r="HK22" t="n">
-        <v>955.960665346567</v>
+        <v>947.390721766151</v>
       </c>
       <c r="HL22" t="n">
-        <v>958.663192716411</v>
+        <v>948.211695528749</v>
       </c>
       <c r="HM22" t="n">
-        <v>961.119665688657</v>
+        <v>948.761541948723</v>
       </c>
       <c r="HN22" t="n">
-        <v>963.356239049899</v>
+        <v>949.038290704382</v>
       </c>
       <c r="HO22" t="n">
-        <v>967.225767310832</v>
+        <v>950.720306844123</v>
       </c>
       <c r="HP22" t="n">
-        <v>971.64698794072</v>
+        <v>952.905582781685</v>
       </c>
       <c r="HQ22" t="n">
-        <v>975.763445764391</v>
+        <v>954.879289725792</v>
       </c>
       <c r="HR22" t="n">
-        <v>979.735000720568</v>
+        <v>956.772026907049</v>
       </c>
       <c r="HS22" t="n">
-        <v>988.735865055183</v>
+        <v>963.339971208967</v>
       </c>
       <c r="HT22" t="n">
-        <v>995.504723931772</v>
+        <v>967.998055607102</v>
       </c>
       <c r="HU22" t="n">
-        <v>1003.38958349806</v>
+        <v>973.878212046791</v>
       </c>
     </row>
     <row r="23">
@@ -17003,139 +16999,139 @@
         <v>0.0362333333333333</v>
       </c>
       <c r="GC23" t="n">
-        <v>0.0314049553003385</v>
+        <v>0.0364</v>
       </c>
       <c r="GD23" t="n">
-        <v>0.0418909243457843</v>
+        <v>0.0308188427353728</v>
       </c>
       <c r="GE23" t="n">
-        <v>0.048564260801248</v>
+        <v>0.0354618218186897</v>
       </c>
       <c r="GF23" t="n">
-        <v>0.0574900449324341</v>
+        <v>0.0379465240728807</v>
       </c>
       <c r="GG23" t="n">
-        <v>0.0652008442306751</v>
+        <v>0.0414629689491403</v>
       </c>
       <c r="GH23" t="n">
-        <v>0.0709882041567446</v>
+        <v>0.0458439748448419</v>
       </c>
       <c r="GI23" t="n">
-        <v>0.0757193581888692</v>
+        <v>0.0494705303562171</v>
       </c>
       <c r="GJ23" t="n">
-        <v>0.078482052044651</v>
+        <v>0.0520628943175811</v>
       </c>
       <c r="GK23" t="n">
-        <v>0.0800725952304393</v>
+        <v>0.0536422782707552</v>
       </c>
       <c r="GL23" t="n">
-        <v>0.0804565319409796</v>
+        <v>0.0542702610019473</v>
       </c>
       <c r="GM23" t="n">
-        <v>0.0796686129262509</v>
+        <v>0.0541418025349544</v>
       </c>
       <c r="GN23" t="n">
-        <v>0.0771015656263362</v>
+        <v>0.052317898736197</v>
       </c>
       <c r="GO23" t="n">
-        <v>0.0738597386672685</v>
+        <v>0.0498427586720002</v>
       </c>
       <c r="GP23" t="n">
-        <v>0.0702196339544976</v>
+        <v>0.046863339637514</v>
       </c>
       <c r="GQ23" t="n">
-        <v>0.0661769144169075</v>
+        <v>0.0433498719429204</v>
       </c>
       <c r="GR23" t="n">
-        <v>0.0622662855250369</v>
+        <v>0.0398714788281475</v>
       </c>
       <c r="GS23" t="n">
-        <v>0.0583876144763562</v>
+        <v>0.0363515097904291</v>
       </c>
       <c r="GT23" t="n">
-        <v>0.05471105453302</v>
+        <v>0.0329568320068077</v>
       </c>
       <c r="GU23" t="n">
-        <v>0.05103256751457</v>
+        <v>0.0295098903831422</v>
       </c>
       <c r="GV23" t="n">
-        <v>0.0476458097545583</v>
+        <v>0.0262818738727745</v>
       </c>
       <c r="GW23" t="n">
-        <v>0.0445393604028814</v>
+        <v>0.0232646057290438</v>
       </c>
       <c r="GX23" t="n">
-        <v>0.0417803996804782</v>
+        <v>0.0205314465525754</v>
       </c>
       <c r="GY23" t="n">
-        <v>0.0392343250046122</v>
+        <v>0.0179781845952567</v>
       </c>
       <c r="GZ23" t="n">
-        <v>0.0371605426344513</v>
+        <v>0.0158662246416724</v>
       </c>
       <c r="HA23" t="n">
-        <v>0.0354571177860221</v>
+        <v>0.0141048321820836</v>
       </c>
       <c r="HB23" t="n">
-        <v>0.0341881399973922</v>
+        <v>0.0127798523140044</v>
       </c>
       <c r="HC23" t="n">
-        <v>0.0329180988234901</v>
+        <v>0.0114997601866425</v>
       </c>
       <c r="HD23" t="n">
-        <v>0.0322201482533588</v>
+        <v>0.0108115105999268</v>
       </c>
       <c r="HE23" t="n">
-        <v>0.0317190444818548</v>
+        <v>0.0103603078159976</v>
       </c>
       <c r="HF23" t="n">
-        <v>0.0314714201212209</v>
+        <v>0.0102042197586925</v>
       </c>
       <c r="HG23" t="n">
-        <v>0.0312891428347487</v>
+        <v>0.0101729124115666</v>
       </c>
       <c r="HH23" t="n">
-        <v>0.0312671540641927</v>
+        <v>0.0103484833221106</v>
       </c>
       <c r="HI23" t="n">
-        <v>0.0314039511778042</v>
+        <v>0.0107160010199962</v>
       </c>
       <c r="HJ23" t="n">
-        <v>0.0316590405753057</v>
+        <v>0.0112352180198577</v>
       </c>
       <c r="HK23" t="n">
-        <v>0.0318483809193854</v>
+        <v>0.0117347589503023</v>
       </c>
       <c r="HL23" t="n">
-        <v>0.0321530548592867</v>
+        <v>0.01237703316963</v>
       </c>
       <c r="HM23" t="n">
-        <v>0.0325040781154078</v>
+        <v>0.0130804288921551</v>
       </c>
       <c r="HN23" t="n">
-        <v>0.0328883610879304</v>
+        <v>0.0138307201792861</v>
       </c>
       <c r="HO23" t="n">
-        <v>0.0331251853860166</v>
+        <v>0.0144601533201768</v>
       </c>
       <c r="HP23" t="n">
-        <v>0.0332824315437678</v>
+        <v>0.0150179893971247</v>
       </c>
       <c r="HQ23" t="n">
-        <v>0.0334340476953785</v>
+        <v>0.0155611973205695</v>
       </c>
       <c r="HR23" t="n">
-        <v>0.0335656378207202</v>
+        <v>0.0160738453060443</v>
       </c>
       <c r="HS23" t="n">
-        <v>0.0331895485298051</v>
+        <v>0.0161022034975641</v>
       </c>
       <c r="HT23" t="n">
-        <v>0.0329405830793991</v>
+        <v>0.0162173304842193</v>
       </c>
       <c r="HU23" t="n">
-        <v>0.0325329998302493</v>
+        <v>0.0161483703764847</v>
       </c>
     </row>
     <row r="24">
@@ -17644,139 +17640,139 @@
         <v>0.04288</v>
       </c>
       <c r="GC24" t="n">
-        <v>0.0420180185621423</v>
+        <v>0.0445633333333333</v>
       </c>
       <c r="GD24" t="n">
-        <v>0.041851576986759</v>
+        <v>0.0434902274703835</v>
       </c>
       <c r="GE24" t="n">
-        <v>0.04210182293627</v>
+        <v>0.0427720370049569</v>
       </c>
       <c r="GF24" t="n">
-        <v>0.042877278420556</v>
+        <v>0.0422535365462884</v>
       </c>
       <c r="GG24" t="n">
-        <v>0.0440684594932849</v>
+        <v>0.041983891262411</v>
       </c>
       <c r="GH24" t="n">
-        <v>0.0455302835228866</v>
+        <v>0.0419987732147737</v>
       </c>
       <c r="GI24" t="n">
-        <v>0.0471802047779933</v>
+        <v>0.0422330437143248</v>
       </c>
       <c r="GJ24" t="n">
-        <v>0.0488858688062876</v>
+        <v>0.0426089791062831</v>
       </c>
       <c r="GK24" t="n">
-        <v>0.050572285043336</v>
+        <v>0.0430554137756201</v>
       </c>
       <c r="GL24" t="n">
-        <v>0.0521674640460337</v>
+        <v>0.0435097488193704</v>
       </c>
       <c r="GM24" t="n">
-        <v>0.0536064176704616</v>
+        <v>0.0439254773080977</v>
       </c>
       <c r="GN24" t="n">
-        <v>0.0547916828797798</v>
+        <v>0.044202178760977</v>
       </c>
       <c r="GO24" t="n">
-        <v>0.0556995025740107</v>
+        <v>0.044309700211816</v>
       </c>
       <c r="GP24" t="n">
-        <v>0.0563245299850348</v>
+        <v>0.0442288638532084</v>
       </c>
       <c r="GQ24" t="n">
-        <v>0.0566615180948787</v>
+        <v>0.043939982756564</v>
       </c>
       <c r="GR24" t="n">
-        <v>0.0567380577381814</v>
+        <v>0.0434592920293859</v>
       </c>
       <c r="GS24" t="n">
-        <v>0.0565737827712509</v>
+        <v>0.0427972678919347</v>
       </c>
       <c r="GT24" t="n">
-        <v>0.0561973294955701</v>
+        <v>0.0419738174268129</v>
       </c>
       <c r="GU24" t="n">
-        <v>0.0556229943399395</v>
+        <v>0.0409967076078172</v>
       </c>
       <c r="GV24" t="n">
-        <v>0.0548819411187777</v>
+        <v>0.0398896599018188</v>
       </c>
       <c r="GW24" t="n">
-        <v>0.0540025228812025</v>
+        <v>0.0386742907520909</v>
       </c>
       <c r="GX24" t="n">
-        <v>0.0530152475790985</v>
+        <v>0.0373752095655033</v>
       </c>
       <c r="GY24" t="n">
-        <v>0.0519403741091514</v>
+        <v>0.0360090241762387</v>
       </c>
       <c r="GZ24" t="n">
-        <v>0.0508125431493152</v>
+        <v>0.0346071029675218</v>
       </c>
       <c r="HA24" t="n">
-        <v>0.0496578500322422</v>
+        <v>0.0331931736086711</v>
       </c>
       <c r="HB24" t="n">
-        <v>0.0485045106145913</v>
+        <v>0.0317945723338695</v>
       </c>
       <c r="HC24" t="n">
-        <v>0.0473523683413659</v>
+        <v>0.0304129880124343</v>
       </c>
       <c r="HD24" t="n">
-        <v>0.0462360943177715</v>
+        <v>0.029083235220816</v>
       </c>
       <c r="HE24" t="n">
-        <v>0.0451652097053683</v>
+        <v>0.0278162063539816</v>
       </c>
       <c r="HF24" t="n">
-        <v>0.044152029109093</v>
+        <v>0.0266255843769781</v>
       </c>
       <c r="HG24" t="n">
-        <v>0.043196602233198</v>
+        <v>0.0255137729318082</v>
       </c>
       <c r="HH24" t="n">
-        <v>0.042304742753585</v>
+        <v>0.0244880020469231</v>
       </c>
       <c r="HI24" t="n">
-        <v>0.0414817781377211</v>
+        <v>0.0235541041882574</v>
       </c>
       <c r="HJ24" t="n">
-        <v>0.0407302141134133</v>
+        <v>0.0227150704656627</v>
       </c>
       <c r="HK24" t="n">
-        <v>0.0400412063483066</v>
+        <v>0.0219632741885559</v>
       </c>
       <c r="HL24" t="n">
-        <v>0.0394175114285953</v>
+        <v>0.0213014758230091</v>
       </c>
       <c r="HM24" t="n">
-        <v>0.0388575081380368</v>
+        <v>0.0207272888910895</v>
       </c>
       <c r="HN24" t="n">
-        <v>0.038358890245586</v>
+        <v>0.0202376241401386</v>
       </c>
       <c r="HO24" t="n">
-        <v>0.0379085301983115</v>
+        <v>0.019819406809438</v>
       </c>
       <c r="HP24" t="n">
-        <v>0.0374983157076646</v>
+        <v>0.0194634422402724</v>
       </c>
       <c r="HQ24" t="n">
-        <v>0.0371251776420812</v>
+        <v>0.0191646212702594</v>
       </c>
       <c r="HR24" t="n">
-        <v>0.0367853808532839</v>
+        <v>0.018917212865441</v>
       </c>
       <c r="HS24" t="n">
-        <v>0.0364458207513861</v>
+        <v>0.0186882998849254</v>
       </c>
       <c r="HT24" t="n">
-        <v>0.0361142035700699</v>
+        <v>0.0184819017275573</v>
       </c>
       <c r="HU24" t="n">
-        <v>0.035780354282777</v>
+        <v>0.018285304533195</v>
       </c>
     </row>
     <row r="25">
@@ -18328,140 +18324,138 @@
       </c>
       <c r="GA25"/>
       <c r="GB25"/>
-      <c r="GC25" t="n">
-        <v>0.41105536552998</v>
-      </c>
+      <c r="GC25"/>
       <c r="GD25" t="n">
-        <v>0.397564508381742</v>
+        <v>0.414193112636424</v>
       </c>
       <c r="GE25" t="n">
-        <v>0.385801468224219</v>
+        <v>0.406833386813701</v>
       </c>
       <c r="GF25" t="n">
-        <v>0.381070276743108</v>
+        <v>0.401943746482866</v>
       </c>
       <c r="GG25" t="n">
-        <v>0.378539116755105</v>
+        <v>0.400199130484376</v>
       </c>
       <c r="GH25" t="n">
-        <v>0.376143073808586</v>
+        <v>0.398816469473639</v>
       </c>
       <c r="GI25" t="n">
-        <v>0.373973401049868</v>
+        <v>0.395714960377853</v>
       </c>
       <c r="GJ25" t="n">
-        <v>0.370467302998928</v>
+        <v>0.391629890351498</v>
       </c>
       <c r="GK25" t="n">
-        <v>0.368712487630497</v>
+        <v>0.387802549833971</v>
       </c>
       <c r="GL25" t="n">
-        <v>0.368447332140239</v>
+        <v>0.384417255144258</v>
       </c>
       <c r="GM25" t="n">
-        <v>0.371823423685883</v>
+        <v>0.381503061106446</v>
       </c>
       <c r="GN25" t="n">
-        <v>0.370877691097061</v>
+        <v>0.379192717324614</v>
       </c>
       <c r="GO25" t="n">
-        <v>0.37048075138471</v>
+        <v>0.3772402256579</v>
       </c>
       <c r="GP25" t="n">
-        <v>0.370535688999875</v>
+        <v>0.375617745564635</v>
       </c>
       <c r="GQ25" t="n">
-        <v>0.370914748011809</v>
+        <v>0.374249801937697</v>
       </c>
       <c r="GR25" t="n">
-        <v>0.371304979202976</v>
+        <v>0.372961208672517</v>
       </c>
       <c r="GS25" t="n">
-        <v>0.371974634179583</v>
+        <v>0.372003669298704</v>
       </c>
       <c r="GT25" t="n">
-        <v>0.37281918221676</v>
+        <v>0.371287031988194</v>
       </c>
       <c r="GU25" t="n">
-        <v>0.373723341146536</v>
+        <v>0.370700572385156</v>
       </c>
       <c r="GV25" t="n">
-        <v>0.374552196163985</v>
+        <v>0.37012338425055</v>
       </c>
       <c r="GW25" t="n">
-        <v>0.37530879761111</v>
+        <v>0.369559179678595</v>
       </c>
       <c r="GX25" t="n">
-        <v>0.375927235421027</v>
+        <v>0.368946111517849</v>
       </c>
       <c r="GY25" t="n">
-        <v>0.376370125147654</v>
+        <v>0.368245799922327</v>
       </c>
       <c r="GZ25" t="n">
-        <v>0.376608423676483</v>
+        <v>0.367427928968588</v>
       </c>
       <c r="HA25" t="n">
-        <v>0.376608536242074</v>
+        <v>0.366455095752044</v>
       </c>
       <c r="HB25" t="n">
-        <v>0.376426814095744</v>
+        <v>0.365379152157267</v>
       </c>
       <c r="HC25" t="n">
-        <v>0.376049133765252</v>
+        <v>0.364175604811609</v>
       </c>
       <c r="HD25" t="n">
-        <v>0.375476247194699</v>
+        <v>0.362846492102772</v>
       </c>
       <c r="HE25" t="n">
-        <v>0.374692162374743</v>
+        <v>0.361365893536917</v>
       </c>
       <c r="HF25" t="n">
-        <v>0.373713086611747</v>
+        <v>0.359746954718141</v>
       </c>
       <c r="HG25" t="n">
-        <v>0.372575349163205</v>
+        <v>0.358020793329101</v>
       </c>
       <c r="HH25" t="n">
-        <v>0.371289663632633</v>
+        <v>0.35619527672709</v>
       </c>
       <c r="HI25" t="n">
-        <v>0.369912034955833</v>
+        <v>0.35432106152231</v>
       </c>
       <c r="HJ25" t="n">
-        <v>0.368461644500431</v>
+        <v>0.35241630553931</v>
       </c>
       <c r="HK25" t="n">
-        <v>0.366968152556243</v>
+        <v>0.350508426074948</v>
       </c>
       <c r="HL25" t="n">
-        <v>0.365435036753396</v>
+        <v>0.348600598651895</v>
       </c>
       <c r="HM25" t="n">
-        <v>0.363931625629774</v>
+        <v>0.346759081305696</v>
       </c>
       <c r="HN25" t="n">
-        <v>0.362472493275674</v>
+        <v>0.34499781573736</v>
       </c>
       <c r="HO25" t="n">
-        <v>0.361069834988679</v>
+        <v>0.343328810504582</v>
       </c>
       <c r="HP25" t="n">
-        <v>0.359729433747638</v>
+        <v>0.341757752011341</v>
       </c>
       <c r="HQ25" t="n">
-        <v>0.358463673771221</v>
+        <v>0.34029699631074</v>
       </c>
       <c r="HR25" t="n">
-        <v>0.357274568010654</v>
+        <v>0.338949093342343</v>
       </c>
       <c r="HS25" t="n">
-        <v>0.356189532721321</v>
+        <v>0.337734728435197</v>
       </c>
       <c r="HT25" t="n">
-        <v>0.355169944885022</v>
+        <v>0.336627607129303</v>
       </c>
       <c r="HU25" t="n">
-        <v>0.354238637466337</v>
+        <v>0.335642741854164</v>
       </c>
     </row>
     <row r="26">
@@ -19018,139 +19012,139 @@
         <v>0.653633333333333</v>
       </c>
       <c r="GC26" t="n">
-        <v>0.667386928644671</v>
+        <v>0.659233333333333</v>
       </c>
       <c r="GD26" t="n">
-        <v>0.642265810530617</v>
+        <v>0.645729445237087</v>
       </c>
       <c r="GE26" t="n">
-        <v>0.61953491733582</v>
+        <v>0.631072421098431</v>
       </c>
       <c r="GF26" t="n">
-        <v>0.608953736628208</v>
+        <v>0.620379917769408</v>
       </c>
       <c r="GG26" t="n">
-        <v>0.60169903174749</v>
+        <v>0.614676206334373</v>
       </c>
       <c r="GH26" t="n">
-        <v>0.594806084628679</v>
+        <v>0.609593684567643</v>
       </c>
       <c r="GI26" t="n">
-        <v>0.588355487553681</v>
+        <v>0.601932858671343</v>
       </c>
       <c r="GJ26" t="n">
-        <v>0.579812852014796</v>
+        <v>0.592801470275443</v>
       </c>
       <c r="GK26" t="n">
-        <v>0.574153122218484</v>
+        <v>0.584172597712887</v>
       </c>
       <c r="GL26" t="n">
-        <v>0.570899825797015</v>
+        <v>0.576293227063696</v>
       </c>
       <c r="GM26" t="n">
-        <v>0.573462729094722</v>
+        <v>0.569245574570442</v>
       </c>
       <c r="GN26" t="n">
-        <v>0.569234008542803</v>
+        <v>0.563186216452678</v>
       </c>
       <c r="GO26" t="n">
-        <v>0.565926514487328</v>
+        <v>0.557766235049662</v>
       </c>
       <c r="GP26" t="n">
-        <v>0.563343470418823</v>
+        <v>0.552898937276125</v>
       </c>
       <c r="GQ26" t="n">
-        <v>0.561298046222871</v>
+        <v>0.548472887865994</v>
       </c>
       <c r="GR26" t="n">
-        <v>0.559308875288119</v>
+        <v>0.544226836866786</v>
       </c>
       <c r="GS26" t="n">
-        <v>0.557773214605252</v>
+        <v>0.540522658791871</v>
       </c>
       <c r="GT26" t="n">
-        <v>0.55651619995379</v>
+        <v>0.537209971465729</v>
       </c>
       <c r="GU26" t="n">
-        <v>0.555357681563284</v>
+        <v>0.53412077943288</v>
       </c>
       <c r="GV26" t="n">
-        <v>0.554112683517531</v>
+        <v>0.531091821872694</v>
       </c>
       <c r="GW26" t="n">
-        <v>0.552761707833688</v>
+        <v>0.528107546282544</v>
       </c>
       <c r="GX26" t="n">
-        <v>0.551204803188239</v>
+        <v>0.525073032565936</v>
       </c>
       <c r="GY26" t="n">
-        <v>0.549395873988608</v>
+        <v>0.521937748150448</v>
       </c>
       <c r="GZ26" t="n">
-        <v>0.547293790647624</v>
+        <v>0.518659287864712</v>
       </c>
       <c r="HA26" t="n">
-        <v>0.544849307170345</v>
+        <v>0.51518184627435</v>
       </c>
       <c r="HB26" t="n">
-        <v>0.542078207761664</v>
+        <v>0.511511413111723</v>
       </c>
       <c r="HC26" t="n">
-        <v>0.539013035847341</v>
+        <v>0.507665834620458</v>
       </c>
       <c r="HD26" t="n">
-        <v>0.535709309376279</v>
+        <v>0.503687788988511</v>
       </c>
       <c r="HE26" t="n">
-        <v>0.532092200123059</v>
+        <v>0.499501005734254</v>
       </c>
       <c r="HF26" t="n">
-        <v>0.52821605672656</v>
+        <v>0.495146568399087</v>
       </c>
       <c r="HG26" t="n">
-        <v>0.524132844831271</v>
+        <v>0.490663630196635</v>
       </c>
       <c r="HH26" t="n">
-        <v>0.519862010790204</v>
+        <v>0.486068312947941</v>
       </c>
       <c r="HI26" t="n">
-        <v>0.5154838096976</v>
+        <v>0.481430492506155</v>
       </c>
       <c r="HJ26" t="n">
-        <v>0.5110268143807</v>
+        <v>0.476775476478355</v>
       </c>
       <c r="HK26" t="n">
-        <v>0.506536860021983</v>
+        <v>0.472140744458106</v>
       </c>
       <c r="HL26" t="n">
-        <v>0.502018988966613</v>
+        <v>0.467532532570514</v>
       </c>
       <c r="HM26" t="n">
-        <v>0.497568772355377</v>
+        <v>0.463039735711478</v>
       </c>
       <c r="HN26" t="n">
-        <v>0.493205565347043</v>
+        <v>0.458679808353471</v>
       </c>
       <c r="HO26" t="n">
-        <v>0.488948517608843</v>
+        <v>0.454467413664441</v>
       </c>
       <c r="HP26" t="n">
-        <v>0.484804559194423</v>
+        <v>0.450411213238689</v>
       </c>
       <c r="HQ26" t="n">
-        <v>0.480787417546875</v>
+        <v>0.446525098579464</v>
       </c>
       <c r="HR26" t="n">
-        <v>0.476897879393128</v>
+        <v>0.442810171566914</v>
       </c>
       <c r="HS26" t="n">
-        <v>0.473144153127359</v>
+        <v>0.439272000827655</v>
       </c>
       <c r="HT26" t="n">
-        <v>0.469540595599146</v>
+        <v>0.435921363816955</v>
       </c>
       <c r="HU26" t="n">
-        <v>0.466051864239941</v>
+        <v>0.432733388492917</v>
       </c>
     </row>
     <row r="27">
@@ -19707,139 +19701,139 @@
         <v>95.2225040638737</v>
       </c>
       <c r="GC27" t="n">
-        <v>93.6743249295834</v>
+        <v>95.339448756992</v>
       </c>
       <c r="GD27" t="n">
-        <v>94.87425276081</v>
+        <v>96.297901317553</v>
       </c>
       <c r="GE27" t="n">
-        <v>96.5107824628378</v>
+        <v>97.443446965251</v>
       </c>
       <c r="GF27" t="n">
-        <v>97.3305199655195</v>
+        <v>98.5751502157275</v>
       </c>
       <c r="GG27" t="n">
-        <v>98.5307020386827</v>
+        <v>99.7000671608539</v>
       </c>
       <c r="GH27" t="n">
-        <v>98.9471610955952</v>
+        <v>100.107683366593</v>
       </c>
       <c r="GI27" t="n">
-        <v>99.2598842320185</v>
+        <v>100.424760680131</v>
       </c>
       <c r="GJ27" t="n">
-        <v>99.5913709192454</v>
+        <v>100.772329378732</v>
       </c>
       <c r="GK27" t="n">
-        <v>99.8505005530976</v>
+        <v>101.072158211912</v>
       </c>
       <c r="GL27" t="n">
-        <v>100.012760078045</v>
+        <v>101.29583072467</v>
       </c>
       <c r="GM27" t="n">
-        <v>100.050004498582</v>
+        <v>101.4340072904</v>
       </c>
       <c r="GN27" t="n">
-        <v>100.160891505686</v>
+        <v>101.569963411447</v>
       </c>
       <c r="GO27" t="n">
-        <v>100.245995995487</v>
+        <v>101.656073827349</v>
       </c>
       <c r="GP27" t="n">
-        <v>100.345850658661</v>
+        <v>101.758710485391</v>
       </c>
       <c r="GQ27" t="n">
-        <v>100.435237230207</v>
+        <v>101.850251293179</v>
       </c>
       <c r="GR27" t="n">
-        <v>100.50636713451</v>
+        <v>101.923562990612</v>
       </c>
       <c r="GS27" t="n">
-        <v>100.571380468734</v>
+        <v>101.986624396915</v>
       </c>
       <c r="GT27" t="n">
-        <v>100.66592535057</v>
+        <v>102.07874314082</v>
       </c>
       <c r="GU27" t="n">
-        <v>100.773954905298</v>
+        <v>102.179578060542</v>
       </c>
       <c r="GV27" t="n">
-        <v>100.862829400227</v>
+        <v>102.263592640891</v>
       </c>
       <c r="GW27" t="n">
-        <v>100.964305225057</v>
+        <v>102.356103498204</v>
       </c>
       <c r="GX27" t="n">
-        <v>101.070596118268</v>
+        <v>102.453644075736</v>
       </c>
       <c r="GY27" t="n">
-        <v>101.176537671139</v>
+        <v>102.550449155959</v>
       </c>
       <c r="GZ27" t="n">
-        <v>101.280852959267</v>
+        <v>102.645969214769</v>
       </c>
       <c r="HA27" t="n">
-        <v>101.384064874326</v>
+        <v>102.740821930864</v>
       </c>
       <c r="HB27" t="n">
-        <v>101.601466579383</v>
+        <v>102.956202962057</v>
       </c>
       <c r="HC27" t="n">
-        <v>101.847519370294</v>
+        <v>103.195471791272</v>
       </c>
       <c r="HD27" t="n">
-        <v>102.048762231272</v>
+        <v>103.401496546668</v>
       </c>
       <c r="HE27" t="n">
-        <v>102.285604506841</v>
+        <v>103.638256019067</v>
       </c>
       <c r="HF27" t="n">
-        <v>102.513926436979</v>
+        <v>103.870388203088</v>
       </c>
       <c r="HG27" t="n">
-        <v>102.741702565135</v>
+        <v>104.104130675894</v>
       </c>
       <c r="HH27" t="n">
-        <v>102.965739211925</v>
+        <v>104.33612424923</v>
       </c>
       <c r="HI27" t="n">
-        <v>103.185505165325</v>
+        <v>104.565214081065</v>
       </c>
       <c r="HJ27" t="n">
-        <v>103.399951411447</v>
+        <v>104.790292679306</v>
       </c>
       <c r="HK27" t="n">
-        <v>103.607053134067</v>
+        <v>105.009889568516</v>
       </c>
       <c r="HL27" t="n">
-        <v>103.807797235033</v>
+        <v>105.224116475154</v>
       </c>
       <c r="HM27" t="n">
-        <v>104.001451691406</v>
+        <v>105.431690696271</v>
       </c>
       <c r="HN27" t="n">
-        <v>104.188089366964</v>
+        <v>105.632620492186</v>
       </c>
       <c r="HO27" t="n">
-        <v>104.36605861044</v>
+        <v>105.826040877917</v>
       </c>
       <c r="HP27" t="n">
-        <v>104.537475131869</v>
+        <v>106.013205482187</v>
       </c>
       <c r="HQ27" t="n">
-        <v>104.70257280797</v>
+        <v>106.194111227506</v>
       </c>
       <c r="HR27" t="n">
-        <v>104.861685320412</v>
+        <v>106.36921416693</v>
       </c>
       <c r="HS27" t="n">
-        <v>105.06658320918</v>
+        <v>106.579936209951</v>
       </c>
       <c r="HT27" t="n">
-        <v>105.20250331121</v>
+        <v>106.735875252775</v>
       </c>
       <c r="HU27" t="n">
-        <v>105.379476932854</v>
+        <v>106.923461352428</v>
       </c>
     </row>
     <row r="28">
@@ -20204,143 +20198,149 @@
       <c r="FY28" t="n">
         <v>14.1375</v>
       </c>
-      <c r="FZ28"/>
-      <c r="GA28"/>
-      <c r="GB28"/>
+      <c r="FZ28" t="n">
+        <v>22.44375</v>
+      </c>
+      <c r="GA28" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="GB28" t="n">
+        <v>28.096</v>
+      </c>
       <c r="GC28" t="n">
-        <v>14.9825957301002</v>
+        <v>25.442</v>
       </c>
       <c r="GD28" t="n">
-        <v>14.7999523106963</v>
+        <v>25.9197188669675</v>
       </c>
       <c r="GE28" t="n">
-        <v>15.0045939048353</v>
+        <v>25.9026610015279</v>
       </c>
       <c r="GF28" t="n">
-        <v>15.096014053437</v>
+        <v>26.1485713221966</v>
       </c>
       <c r="GG28" t="n">
-        <v>15.0926638360319</v>
+        <v>26.0828005584297</v>
       </c>
       <c r="GH28" t="n">
-        <v>15.1964159893201</v>
+        <v>26.1982799461816</v>
       </c>
       <c r="GI28" t="n">
-        <v>15.3831352554629</v>
+        <v>26.3720809634212</v>
       </c>
       <c r="GJ28" t="n">
-        <v>15.8992043441839</v>
+        <v>26.8856987950299</v>
       </c>
       <c r="GK28" t="n">
-        <v>16.1128383822835</v>
+        <v>27.0751977830056</v>
       </c>
       <c r="GL28" t="n">
-        <v>16.3843280586527</v>
+        <v>27.3168475226151</v>
       </c>
       <c r="GM28" t="n">
-        <v>16.7040803726411</v>
+        <v>27.5833162566823</v>
       </c>
       <c r="GN28" t="n">
-        <v>17.3087031086214</v>
+        <v>28.1505644939097</v>
       </c>
       <c r="GO28" t="n">
-        <v>17.5534910120164</v>
+        <v>28.3421243923825</v>
       </c>
       <c r="GP28" t="n">
-        <v>17.8185669243765</v>
+        <v>28.5579060884369</v>
       </c>
       <c r="GQ28" t="n">
-        <v>18.11247052044</v>
+        <v>28.8026307281327</v>
       </c>
       <c r="GR28" t="n">
-        <v>18.7158061046024</v>
+        <v>29.3730508360183</v>
       </c>
       <c r="GS28" t="n">
-        <v>18.9191322981048</v>
+        <v>29.5284602693043</v>
       </c>
       <c r="GT28" t="n">
-        <v>19.129357218753</v>
+        <v>29.6947007911469</v>
       </c>
       <c r="GU28" t="n">
-        <v>19.3659397628908</v>
+        <v>29.8910430648369</v>
       </c>
       <c r="GV28" t="n">
-        <v>19.9358634737677</v>
+        <v>30.4387224985807</v>
       </c>
       <c r="GW28" t="n">
-        <v>20.0687442601551</v>
+        <v>30.5332347529627</v>
       </c>
       <c r="GX28" t="n">
-        <v>20.2122457570947</v>
+        <v>30.6413087947378</v>
       </c>
       <c r="GY28" t="n">
-        <v>20.3749845216232</v>
+        <v>30.7701507134309</v>
       </c>
       <c r="GZ28" t="n">
-        <v>20.9001680092045</v>
+        <v>31.2778238470794</v>
       </c>
       <c r="HA28" t="n">
-        <v>20.9505380396513</v>
+        <v>31.2886622782296</v>
       </c>
       <c r="HB28" t="n">
-        <v>21.0027870619913</v>
+        <v>31.299120089564</v>
       </c>
       <c r="HC28" t="n">
-        <v>21.0975327392379</v>
+        <v>31.3511541473885</v>
       </c>
       <c r="HD28" t="n">
-        <v>21.5651477705093</v>
+        <v>31.7888407333578</v>
       </c>
       <c r="HE28" t="n">
-        <v>21.546918792502</v>
+        <v>31.715673948772</v>
       </c>
       <c r="HF28" t="n">
-        <v>21.5527892966631</v>
+        <v>31.6639583738029</v>
       </c>
       <c r="HG28" t="n">
-        <v>21.5954883257786</v>
+        <v>31.646196320765</v>
       </c>
       <c r="HH28" t="n">
-        <v>22.0641593039013</v>
+        <v>32.0689016781501</v>
       </c>
       <c r="HI28" t="n">
-        <v>22.0127915551978</v>
+        <v>31.9457254946675</v>
       </c>
       <c r="HJ28" t="n">
-        <v>21.9978984748128</v>
+        <v>31.8574537437565</v>
       </c>
       <c r="HK28" t="n">
-        <v>22.026821737091</v>
+        <v>31.8109967531776</v>
       </c>
       <c r="HL28" t="n">
-        <v>22.5087037200347</v>
+        <v>32.2324809259042</v>
       </c>
       <c r="HM28" t="n">
-        <v>22.4472267483666</v>
+        <v>32.0864674706685</v>
       </c>
       <c r="HN28" t="n">
-        <v>22.4285006766918</v>
+        <v>31.9829009454856</v>
       </c>
       <c r="HO28" t="n">
-        <v>22.460404152736</v>
+        <v>31.9293174972413</v>
       </c>
       <c r="HP28" t="n">
-        <v>22.9773642292672</v>
+        <v>32.3767141897506</v>
       </c>
       <c r="HQ28" t="n">
-        <v>22.9250845937161</v>
+        <v>32.2337553299922</v>
       </c>
       <c r="HR28" t="n">
-        <v>22.9208320150047</v>
+        <v>32.1402294466606</v>
       </c>
       <c r="HS28" t="n">
-        <v>23.0010442856034</v>
+        <v>32.1345005885878</v>
       </c>
       <c r="HT28" t="n">
-        <v>23.5650460939984</v>
+        <v>32.6275476656049</v>
       </c>
       <c r="HU28" t="n">
-        <v>23.5491929624306</v>
+        <v>32.524097295911</v>
       </c>
     </row>
     <row r="29">
@@ -20705,143 +20705,149 @@
       <c r="FY29" t="n">
         <v>0.0000204786833383549</v>
       </c>
-      <c r="FZ29"/>
-      <c r="GA29"/>
-      <c r="GB29"/>
+      <c r="FZ29" t="n">
+        <v>0.0000321014803690195</v>
+      </c>
+      <c r="GA29" t="n">
+        <v>0.0000435888276519017</v>
+      </c>
+      <c r="GB29" t="n">
+        <v>0.0000390987362769642</v>
+      </c>
       <c r="GC29" t="n">
-        <v>0.0000207381340885841</v>
+        <v>0.0000347351922845877</v>
       </c>
       <c r="GD29" t="n">
-        <v>0.0000198342653769061</v>
+        <v>0.000034663784639603</v>
       </c>
       <c r="GE29" t="n">
-        <v>0.0000198013874094017</v>
+        <v>0.0000338550480127062</v>
       </c>
       <c r="GF29" t="n">
-        <v>0.0000193997588879907</v>
+        <v>0.0000334634629929598</v>
       </c>
       <c r="GG29" t="n">
-        <v>0.0000190084349003374</v>
+        <v>0.0000327146832526072</v>
       </c>
       <c r="GH29" t="n">
-        <v>0.0000187961108855796</v>
+        <v>0.0000322906219632797</v>
       </c>
       <c r="GI29" t="n">
-        <v>0.0000186989169742781</v>
+        <v>0.0000319650478286595</v>
       </c>
       <c r="GJ29" t="n">
-        <v>0.0000190201225980373</v>
+        <v>0.0000320895335971165</v>
       </c>
       <c r="GK29" t="n">
-        <v>0.0000189654454096763</v>
+        <v>0.0000318079162799777</v>
       </c>
       <c r="GL29" t="n">
-        <v>0.0000189858154319212</v>
+        <v>0.0000315991908477698</v>
       </c>
       <c r="GM29" t="n">
-        <v>0.0000190726862875582</v>
+        <v>0.0000314190880108438</v>
       </c>
       <c r="GN29" t="n">
-        <v>0.0000195018288343366</v>
+        <v>0.0000316397707111248</v>
       </c>
       <c r="GO29" t="n">
-        <v>0.0000195094383561837</v>
+        <v>0.0000314205812628935</v>
       </c>
       <c r="GP29" t="n">
-        <v>0.0000195358578523384</v>
+        <v>0.0000312334680840615</v>
       </c>
       <c r="GQ29" t="n">
-        <v>0.0000196059953330911</v>
+        <v>0.0000311003024127699</v>
       </c>
       <c r="GR29" t="n">
-        <v>0.0000200009573664171</v>
+        <v>0.0000313124126164232</v>
       </c>
       <c r="GS29" t="n">
-        <v>0.0000199659283374206</v>
+        <v>0.0000310861712386707</v>
       </c>
       <c r="GT29" t="n">
-        <v>0.0000199366701043406</v>
+        <v>0.000030874911659894</v>
       </c>
       <c r="GU29" t="n">
-        <v>0.0000199463773678888</v>
+        <v>0.0000307178617101225</v>
       </c>
       <c r="GV29" t="n">
-        <v>0.000020287529244167</v>
+        <v>0.0000309115784134319</v>
       </c>
       <c r="GW29" t="n">
-        <v>0.0000201797757459854</v>
+        <v>0.0000306465735177665</v>
       </c>
       <c r="GX29" t="n">
-        <v>0.0000200803377903316</v>
+        <v>0.0000303959012467334</v>
       </c>
       <c r="GY29" t="n">
-        <v>0.0000200053215724798</v>
+        <v>0.0000301770209109889</v>
       </c>
       <c r="GZ29" t="n">
-        <v>0.000020276898421297</v>
+        <v>0.0000303214764063824</v>
       </c>
       <c r="HA29" t="n">
-        <v>0.0000200800092140944</v>
+        <v>0.0000299775642743135</v>
       </c>
       <c r="HB29" t="n">
-        <v>0.0000198785373172108</v>
+        <v>0.0000296248496794956</v>
       </c>
       <c r="HC29" t="n">
-        <v>0.0000197319611184472</v>
+        <v>0.0000293346737572201</v>
       </c>
       <c r="HD29" t="n">
-        <v>0.0000199157594162311</v>
+        <v>0.0000293810749740743</v>
       </c>
       <c r="HE29" t="n">
-        <v>0.0000196508739755796</v>
+        <v>0.0000289593112815016</v>
       </c>
       <c r="HF29" t="n">
-        <v>0.0000194078660284394</v>
+        <v>0.0000285574618722464</v>
       </c>
       <c r="HG29" t="n">
-        <v>0.0000192055003041394</v>
+        <v>0.0000281973898804563</v>
       </c>
       <c r="HH29" t="n">
-        <v>0.0000193765609631401</v>
+        <v>0.0000282252791405766</v>
       </c>
       <c r="HI29" t="n">
-        <v>0.0000190855427138688</v>
+        <v>0.0000277681494689834</v>
       </c>
       <c r="HJ29" t="n">
-        <v>0.0000188282310892718</v>
+        <v>0.0000273450109654368</v>
       </c>
       <c r="HK29" t="n">
-        <v>0.0000186169951503517</v>
+        <v>0.0000269704867267994</v>
       </c>
       <c r="HL29" t="n">
-        <v>0.0000187835857465229</v>
+        <v>0.000026988899718705</v>
       </c>
       <c r="HM29" t="n">
-        <v>0.0000184924465571449</v>
+        <v>0.0000265293601106308</v>
       </c>
       <c r="HN29" t="n">
-        <v>0.0000182394953248419</v>
+        <v>0.0000261100548942852</v>
       </c>
       <c r="HO29" t="n">
-        <v>0.0000180369223646102</v>
+        <v>0.0000257453160311142</v>
       </c>
       <c r="HP29" t="n">
-        <v>0.0000182202727268865</v>
+        <v>0.0000257830627836263</v>
       </c>
       <c r="HQ29" t="n">
-        <v>0.0000179481206920964</v>
+        <v>0.0000253485951633756</v>
       </c>
       <c r="HR29" t="n">
-        <v>0.0000177166176844746</v>
+        <v>0.0000249586870371741</v>
       </c>
       <c r="HS29" t="n">
-        <v>0.0000175695247287182</v>
+        <v>0.0000246659381212991</v>
       </c>
       <c r="HT29" t="n">
-        <v>0.000017776523155869</v>
+        <v>0.0000247373440568344</v>
       </c>
       <c r="HU29" t="n">
-        <v>0.0000175485874016815</v>
+        <v>0.0000243647697549904</v>
       </c>
     </row>
     <row r="30">
@@ -21206,143 +21212,149 @@
       <c r="FY30" t="n">
         <v>825.6</v>
       </c>
-      <c r="FZ30"/>
-      <c r="GA30"/>
-      <c r="GB30"/>
+      <c r="FZ30" t="n">
+        <v>852.72851824648</v>
+      </c>
+      <c r="GA30" t="n">
+        <v>887.932958983057</v>
+      </c>
+      <c r="GB30" t="n">
+        <v>920.85570562852</v>
+      </c>
       <c r="GC30" t="n">
-        <v>844.856861071567</v>
+        <v>951.06512523494</v>
       </c>
       <c r="GD30" t="n">
-        <v>864.352810381144</v>
+        <v>982.271182154697</v>
       </c>
       <c r="GE30" t="n">
-        <v>884.235347270203</v>
+        <v>1013.71725409219</v>
       </c>
       <c r="GF30" t="n">
-        <v>904.134263036259</v>
+        <v>1045.37203408476</v>
       </c>
       <c r="GG30" t="n">
-        <v>924.152847533199</v>
+        <v>1077.15024948538</v>
       </c>
       <c r="GH30" t="n">
-        <v>944.283035602267</v>
+        <v>1109.4474596353</v>
       </c>
       <c r="GI30" t="n">
-        <v>964.687442573011</v>
+        <v>1141.95007208974</v>
       </c>
       <c r="GJ30" t="n">
-        <v>985.747092872787</v>
+        <v>1175.04169925415</v>
       </c>
       <c r="GK30" t="n">
-        <v>1007.23015554507</v>
+        <v>1208.42525097198</v>
       </c>
       <c r="GL30" t="n">
-        <v>1029.25418742849</v>
+        <v>1242.1882749346</v>
       </c>
       <c r="GM30" t="n">
-        <v>1051.91245802948</v>
+        <v>1276.40022059247</v>
       </c>
       <c r="GN30" t="n">
-        <v>1075.52694569371</v>
+        <v>1311.39997109576</v>
       </c>
       <c r="GO30" t="n">
-        <v>1099.76086553808</v>
+        <v>1346.84173024615</v>
       </c>
       <c r="GP30" t="n">
-        <v>1124.64603307865</v>
+        <v>1382.76754171007</v>
       </c>
       <c r="GQ30" t="n">
-        <v>1150.21294816463</v>
+        <v>1419.21443263285</v>
       </c>
       <c r="GR30" t="n">
-        <v>1176.76295592722</v>
+        <v>1456.50819536531</v>
       </c>
       <c r="GS30" t="n">
-        <v>1203.87434085583</v>
+        <v>1494.21671240254</v>
       </c>
       <c r="GT30" t="n">
-        <v>1231.52355267487</v>
+        <v>1532.32366200894</v>
       </c>
       <c r="GU30" t="n">
-        <v>1259.70282192881</v>
+        <v>1570.82575286843</v>
       </c>
       <c r="GV30" t="n">
-        <v>1288.70761471316</v>
+        <v>1610.03423324513</v>
       </c>
       <c r="GW30" t="n">
-        <v>1318.06663393689</v>
+        <v>1649.45778948263</v>
       </c>
       <c r="GX30" t="n">
-        <v>1347.75329227966</v>
+        <v>1689.06836542985</v>
       </c>
       <c r="GY30" t="n">
-        <v>1377.75161587216</v>
+        <v>1728.84645450126</v>
       </c>
       <c r="GZ30" t="n">
-        <v>1408.3887801114</v>
+        <v>1769.12972198682</v>
       </c>
       <c r="HA30" t="n">
-        <v>1439.16022809184</v>
+        <v>1809.38481753596</v>
       </c>
       <c r="HB30" t="n">
-        <v>1470.03769232979</v>
+        <v>1849.57498671601</v>
       </c>
       <c r="HC30" t="n">
-        <v>1501.03736302553</v>
+        <v>1889.70939175185</v>
       </c>
       <c r="HD30" t="n">
-        <v>1532.50846428121</v>
+        <v>1930.14405034883</v>
       </c>
       <c r="HE30" t="n">
-        <v>1563.949419888</v>
+        <v>1970.34673355591</v>
       </c>
       <c r="HF30" t="n">
-        <v>1595.3697816458</v>
+        <v>2010.32050288798</v>
       </c>
       <c r="HG30" t="n">
-        <v>1626.797300021</v>
+        <v>2050.08785792145</v>
       </c>
       <c r="HH30" t="n">
-        <v>1658.64902877111</v>
+        <v>2090.07869456148</v>
       </c>
       <c r="HI30" t="n">
-        <v>1690.40577708732</v>
+        <v>2129.7477584288</v>
       </c>
       <c r="HJ30" t="n">
-        <v>1722.10418868876</v>
+        <v>2169.13227910124</v>
       </c>
       <c r="HK30" t="n">
-        <v>1753.79173718486</v>
+        <v>2208.28139728217</v>
       </c>
       <c r="HL30" t="n">
-        <v>1785.92602993561</v>
+        <v>2247.67248994885</v>
       </c>
       <c r="HM30" t="n">
-        <v>1817.97283672475</v>
+        <v>2286.75232074034</v>
       </c>
       <c r="HN30" t="n">
-        <v>1849.98307917824</v>
+        <v>2325.57883446567</v>
       </c>
       <c r="HO30" t="n">
-        <v>1882.01727907577</v>
+        <v>2364.22004246757</v>
       </c>
       <c r="HP30" t="n">
-        <v>1914.56945999373</v>
+        <v>2403.19433698191</v>
       </c>
       <c r="HQ30" t="n">
-        <v>1947.08325135416</v>
+        <v>2441.93235831044</v>
       </c>
       <c r="HR30" t="n">
-        <v>1979.61708854251</v>
+        <v>2480.50354820669</v>
       </c>
       <c r="HS30" t="n">
-        <v>2012.26634702745</v>
+        <v>2519.01626279948</v>
       </c>
       <c r="HT30" t="n">
-        <v>2045.52358757299</v>
+        <v>2557.98719927432</v>
       </c>
       <c r="HU30" t="n">
-        <v>2078.81854612771</v>
+        <v>2596.83712961885</v>
       </c>
     </row>
     <row r="31">
@@ -21899,139 +21911,139 @@
         <v>0.0546735510183915</v>
       </c>
       <c r="GC31" t="n">
-        <v>0.0435353050242881</v>
+        <v>0.0641978669500195</v>
       </c>
       <c r="GD31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GE31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GF31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GG31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GH31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GI31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GJ31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GK31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GL31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GM31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GN31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GO31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GP31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GQ31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GR31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GS31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GT31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GU31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GV31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GW31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GX31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GY31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="GZ31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HA31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HB31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HC31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HD31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HE31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HF31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HG31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HH31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HI31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HJ31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HK31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HL31" t="n">
-        <v>0.0435353050242881</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HM31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HN31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HO31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HP31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HQ31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HR31" t="n">
-        <v>0.0435353050242881</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HS31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HT31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
       <c r="HU31" t="n">
-        <v>0.043535305024288</v>
+        <v>0.0479366122416527</v>
       </c>
     </row>
     <row r="32">
@@ -22588,139 +22600,139 @@
         <v>0.233491652414238</v>
       </c>
       <c r="GC32" t="n">
-        <v>0.236930433753953</v>
+        <v>0.232995565603941</v>
       </c>
       <c r="GD32" t="n">
-        <v>0.232655001277829</v>
+        <v>0.232653476492205</v>
       </c>
       <c r="GE32" t="n">
-        <v>0.233411142625028</v>
+        <v>0.231078531543783</v>
       </c>
       <c r="GF32" t="n">
-        <v>0.23073739570846</v>
+        <v>0.230170897047142</v>
       </c>
       <c r="GG32" t="n">
-        <v>0.230101822073248</v>
+        <v>0.229445997830055</v>
       </c>
       <c r="GH32" t="n">
-        <v>0.229777607882814</v>
+        <v>0.229391618450398</v>
       </c>
       <c r="GI32" t="n">
-        <v>0.229698724547084</v>
+        <v>0.229507987949849</v>
       </c>
       <c r="GJ32" t="n">
-        <v>0.229840296030326</v>
+        <v>0.229823264178969</v>
       </c>
       <c r="GK32" t="n">
-        <v>0.229893731429405</v>
+        <v>0.229993641160799</v>
       </c>
       <c r="GL32" t="n">
-        <v>0.230098249669954</v>
+        <v>0.23023619094576</v>
       </c>
       <c r="GM32" t="n">
-        <v>0.230498735950011</v>
+        <v>0.230446140342963</v>
       </c>
       <c r="GN32" t="n">
-        <v>0.230547798487021</v>
+        <v>0.230420517428527</v>
       </c>
       <c r="GO32" t="n">
-        <v>0.23045138513604</v>
+        <v>0.230222051933572</v>
       </c>
       <c r="GP32" t="n">
-        <v>0.230350470753427</v>
+        <v>0.230039024111852</v>
       </c>
       <c r="GQ32" t="n">
-        <v>0.230442439316751</v>
+        <v>0.229998535362794</v>
       </c>
       <c r="GR32" t="n">
-        <v>0.230496264218319</v>
+        <v>0.229911667097274</v>
       </c>
       <c r="GS32" t="n">
-        <v>0.230601725875261</v>
+        <v>0.229860840601242</v>
       </c>
       <c r="GT32" t="n">
-        <v>0.230693611945172</v>
+        <v>0.229792140625127</v>
       </c>
       <c r="GU32" t="n">
-        <v>0.230956218517119</v>
+        <v>0.229883003967988</v>
       </c>
       <c r="GV32" t="n">
-        <v>0.231144457230778</v>
+        <v>0.229899091758697</v>
       </c>
       <c r="GW32" t="n">
-        <v>0.231344316708669</v>
+        <v>0.229931034808582</v>
       </c>
       <c r="GX32" t="n">
-        <v>0.231501631685717</v>
+        <v>0.229920501312743</v>
       </c>
       <c r="GY32" t="n">
-        <v>0.231727930565459</v>
+        <v>0.229969310892686</v>
       </c>
       <c r="GZ32" t="n">
-        <v>0.231893866694728</v>
+        <v>0.229954457781055</v>
       </c>
       <c r="HA32" t="n">
-        <v>0.232003120151533</v>
+        <v>0.229879465713186</v>
       </c>
       <c r="HB32" t="n">
-        <v>0.232002288391236</v>
+        <v>0.22968264777007</v>
       </c>
       <c r="HC32" t="n">
-        <v>0.232178727518382</v>
+        <v>0.229648692426597</v>
       </c>
       <c r="HD32" t="n">
-        <v>0.232131445752099</v>
+        <v>0.229378418197055</v>
       </c>
       <c r="HE32" t="n">
-        <v>0.232125616361614</v>
+        <v>0.229145816379785</v>
       </c>
       <c r="HF32" t="n">
-        <v>0.232060521619057</v>
+        <v>0.228844491400096</v>
       </c>
       <c r="HG32" t="n">
-        <v>0.232062251190573</v>
+        <v>0.228593569456367</v>
       </c>
       <c r="HH32" t="n">
-        <v>0.232013122385574</v>
+        <v>0.228285689065411</v>
       </c>
       <c r="HI32" t="n">
-        <v>0.231910109165374</v>
+        <v>0.22792116462526</v>
       </c>
       <c r="HJ32" t="n">
-        <v>0.231777609856087</v>
+        <v>0.227521372337824</v>
       </c>
       <c r="HK32" t="n">
-        <v>0.231719186172751</v>
+        <v>0.227182036215413</v>
       </c>
       <c r="HL32" t="n">
-        <v>0.231611595610083</v>
+        <v>0.226790587758283</v>
       </c>
       <c r="HM32" t="n">
-        <v>0.231462749926391</v>
+        <v>0.226358316569932</v>
       </c>
       <c r="HN32" t="n">
-        <v>0.231294605049541</v>
+        <v>0.225903965302457</v>
       </c>
       <c r="HO32" t="n">
-        <v>0.23121293671918</v>
+        <v>0.225525110721312</v>
       </c>
       <c r="HP32" t="n">
-        <v>0.231105918605049</v>
+        <v>0.225121356954972</v>
       </c>
       <c r="HQ32" t="n">
-        <v>0.230961179152578</v>
+        <v>0.224685020682815</v>
       </c>
       <c r="HR32" t="n">
-        <v>0.230805340106321</v>
+        <v>0.224239355817066</v>
       </c>
       <c r="HS32" t="n">
-        <v>0.230905011981552</v>
+        <v>0.224045033671211</v>
       </c>
       <c r="HT32" t="n">
-        <v>0.230800532218018</v>
+        <v>0.223649252684779</v>
       </c>
       <c r="HU32" t="n">
-        <v>0.230783804118948</v>
+        <v>0.223352737789401</v>
       </c>
     </row>
     <row r="33">
@@ -23109,139 +23121,139 @@
         <v>82599</v>
       </c>
       <c r="GC33" t="n">
-        <v>82701.4172268635</v>
+        <v>82936</v>
       </c>
       <c r="GD33" t="n">
-        <v>84174.3502963379</v>
+        <v>84261.5549142899</v>
       </c>
       <c r="GE33" t="n">
-        <v>85528.2186136584</v>
+        <v>86107.2965531408</v>
       </c>
       <c r="GF33" t="n">
-        <v>87098.0990440609</v>
+        <v>87843.4291389507</v>
       </c>
       <c r="GG33" t="n">
-        <v>88672.5147443145</v>
+        <v>89647.4244405649</v>
       </c>
       <c r="GH33" t="n">
-        <v>89923.964413826</v>
+        <v>91156.1547808082</v>
       </c>
       <c r="GI33" t="n">
-        <v>91031.7070547143</v>
+        <v>92518.519091724</v>
       </c>
       <c r="GJ33" t="n">
-        <v>91901.5652135989</v>
+        <v>93583.7178894221</v>
       </c>
       <c r="GK33" t="n">
-        <v>92651.3177765577</v>
+        <v>94606.3448503557</v>
       </c>
       <c r="GL33" t="n">
-        <v>93389.9457331753</v>
+        <v>95558.5432875114</v>
       </c>
       <c r="GM33" t="n">
-        <v>94057.6355156578</v>
+        <v>96512.5331464988</v>
       </c>
       <c r="GN33" t="n">
-        <v>94695.6703702621</v>
+        <v>97376.3531969709</v>
       </c>
       <c r="GO33" t="n">
-        <v>95190.27811994</v>
+        <v>98201.9509278824</v>
       </c>
       <c r="GP33" t="n">
-        <v>95769.0307583966</v>
+        <v>99013.7050779414</v>
       </c>
       <c r="GQ33" t="n">
-        <v>96269.1654905802</v>
+        <v>99791.1878051537</v>
       </c>
       <c r="GR33" t="n">
-        <v>96815.2816543206</v>
+        <v>100579.725996289</v>
       </c>
       <c r="GS33" t="n">
-        <v>97351.2798555573</v>
+        <v>101376.458408665</v>
       </c>
       <c r="GT33" t="n">
-        <v>97914.0968367157</v>
+        <v>102185.096872868</v>
       </c>
       <c r="GU33" t="n">
-        <v>98455.3176169412</v>
+        <v>102975.453345135</v>
       </c>
       <c r="GV33" t="n">
-        <v>99002.8831480685</v>
+        <v>103761.776454227</v>
       </c>
       <c r="GW33" t="n">
-        <v>99563.1988766417</v>
+        <v>104557.096698434</v>
       </c>
       <c r="GX33" t="n">
-        <v>100149.360235446</v>
+        <v>105371.662202222</v>
       </c>
       <c r="GY33" t="n">
-        <v>100738.973777388</v>
+        <v>106188.226666552</v>
       </c>
       <c r="GZ33" t="n">
-        <v>101346.810294589</v>
+        <v>107022.728078586</v>
       </c>
       <c r="HA33" t="n">
-        <v>101981.783878343</v>
+        <v>107887.293823377</v>
       </c>
       <c r="HB33" t="n">
-        <v>102661.456820583</v>
+        <v>108802.529967557</v>
       </c>
       <c r="HC33" t="n">
-        <v>103336.057200671</v>
+        <v>109720.840851005</v>
       </c>
       <c r="HD33" t="n">
-        <v>104030.304401262</v>
+        <v>110667.41334026</v>
       </c>
       <c r="HE33" t="n">
-        <v>104740.23431411</v>
+        <v>111638.407938384</v>
       </c>
       <c r="HF33" t="n">
-        <v>105459.294581994</v>
+        <v>112626.879190315</v>
       </c>
       <c r="HG33" t="n">
-        <v>106162.518754639</v>
+        <v>113607.70136418</v>
       </c>
       <c r="HH33" t="n">
-        <v>106850.318519396</v>
+        <v>114580.174883487</v>
       </c>
       <c r="HI33" t="n">
-        <v>107533.2713832</v>
+        <v>115554.35525261</v>
       </c>
       <c r="HJ33" t="n">
-        <v>108214.664211513</v>
+        <v>116533.611655617</v>
       </c>
       <c r="HK33" t="n">
-        <v>108865.247298823</v>
+        <v>117488.106938727</v>
       </c>
       <c r="HL33" t="n">
-        <v>109493.08388241</v>
+        <v>118425.689088239</v>
       </c>
       <c r="HM33" t="n">
-        <v>110110.218357403</v>
+        <v>119358.252938745</v>
       </c>
       <c r="HN33" t="n">
-        <v>110717.591771021</v>
+        <v>120286.93726479</v>
       </c>
       <c r="HO33" t="n">
-        <v>111287.864733859</v>
+        <v>121183.794775455</v>
       </c>
       <c r="HP33" t="n">
-        <v>111825.042515471</v>
+        <v>122052.19050944</v>
       </c>
       <c r="HQ33" t="n">
-        <v>112346.212837964</v>
+        <v>122909.149978511</v>
       </c>
       <c r="HR33" t="n">
-        <v>112854.716086963</v>
+        <v>123758.125956605</v>
       </c>
       <c r="HS33" t="n">
-        <v>113315.842494805</v>
+        <v>124563.293279719</v>
       </c>
       <c r="HT33" t="n">
-        <v>113740.624550801</v>
+        <v>125335.186721265</v>
       </c>
       <c r="HU33" t="n">
-        <v>114157.528293462</v>
+        <v>126103.078310474</v>
       </c>
     </row>
   </sheetData>
